--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -414,8 +414,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -440,15 +444,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>initScore</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>allowRotate</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>*shapeRows</t>
         </is>
@@ -477,15 +486,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>初始分</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>图标资源路径</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>是否允许旋转摆放</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>菜品形状行列表</t>
         </is>
@@ -514,15 +528,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
@@ -542,17 +561,20 @@
       <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Sprites/Dishes/rice</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -572,17 +594,20 @@
       <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Sprites/Dishes/egg</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -602,17 +627,20 @@
       <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Sprites/Dishes/soup</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -632,17 +660,20 @@
       <c r="D7" t="n">
         <v>15</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Sprites/Dishes/fish</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>XXX</t>
         </is>
@@ -662,24 +693,27 @@
       <c r="D8" t="n">
         <v>12</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Sprites/Dishes/noodle</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>X.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -699,24 +733,27 @@
       <c r="D10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>11</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Sprites/Dishes/dumpling</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>.X</t>
         </is>
@@ -736,17 +773,20 @@
       <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Sprites/Dishes/chili</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -766,24 +806,27 @@
       <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Sprites/Dishes/orange</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -803,24 +846,27 @@
       <c r="D15" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Sprites/Dishes/cake</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>XXX</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>.X.</t>
         </is>
@@ -840,17 +886,20 @@
       <c r="D17" t="n">
         <v>25</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="n">
+        <v>25</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Sprites/Dishes/feast</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>XXXX</t>
         </is>
@@ -867,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,30 +947,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>hiddenMin</t>
+          <t>baseWeight</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>hiddenMax</t>
+          <t>price</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>baseWeight</t>
+          <t>hiddenRange</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>maxRollCount</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>*inherentTags</t>
         </is>
@@ -955,30 +994,20 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>出现隐藏分下限</t>
+          <t>随机基础权重</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>出现隐藏分上限</t>
+          <t>商店价格</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>随机基础权重</t>
+          <t>出现隐藏分区间(单元格: min,max)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>商店价格</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>最大刷新出现次数</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
         <is>
           <t>固有标签ID列表</t>
         </is>
@@ -1012,30 +1041,20 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>HiddenRange</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
@@ -1053,19 +1072,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" t="n">
-        <v>150</v>
-      </c>
-      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1,10</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1080,21 +1095,17 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="n">
-        <v>120</v>
-      </c>
-      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>5,20</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>t_fresh</t>
         </is>
@@ -1112,21 +1123,17 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
-      </c>
-      <c r="H6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>8,24</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>t_lonely</t>
         </is>
@@ -1144,21 +1151,17 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
-      </c>
-      <c r="H7" t="n">
-        <v>80</v>
-      </c>
-      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>20,40</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>t_fresh</t>
         </is>
@@ -1176,21 +1179,17 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G8" t="n">
-        <v>35</v>
-      </c>
-      <c r="H8" t="n">
-        <v>90</v>
-      </c>
-      <c r="I8" t="n">
         <v>4</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>15,35</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>t_hearty</t>
         </is>
@@ -1208,21 +1207,17 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H9" t="n">
-        <v>90</v>
-      </c>
-      <c r="I9" t="n">
         <v>4</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12,32</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>t_hearty</t>
         </is>
@@ -1240,21 +1235,17 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="G10" t="n">
-        <v>18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>110</v>
-      </c>
-      <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>t_spicy</t>
         </is>
@@ -1272,21 +1263,17 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" t="n">
-        <v>100</v>
-      </c>
-      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10,30</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>t_sweet</t>
         </is>
@@ -1304,21 +1291,17 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>50</v>
-      </c>
-      <c r="H12" t="n">
-        <v>60</v>
-      </c>
-      <c r="I12" t="n">
         <v>6</v>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>30,50</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>t_sweet</t>
         </is>
@@ -1339,18 +1322,14 @@
         <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>70</v>
-      </c>
-      <c r="H13" t="n">
-        <v>40</v>
-      </c>
-      <c r="I13" t="n">
         <v>8</v>
       </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>40,70</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>t_feast</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -444,20 +444,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>initScore</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>allowRotate</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>allowRotate</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
         <is>
           <t>*shapeRows</t>
         </is>
@@ -486,20 +481,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初始分</t>
+          <t>图标资源路径</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>图标资源路径</t>
+          <t>是否允许旋转摆放</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
-        <is>
-          <t>是否允许旋转摆放</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
         <is>
           <t>菜品形状行列表</t>
         </is>
@@ -528,20 +518,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
@@ -561,20 +546,17 @@
       <c r="D4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>5</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/rice</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/rice</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -594,20 +576,17 @@
       <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="E5" t="n">
-        <v>8</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/egg</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/egg</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -627,20 +606,17 @@
       <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="E6" t="n">
-        <v>9</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/soup</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/soup</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -660,20 +636,17 @@
       <c r="D7" t="n">
         <v>15</v>
       </c>
-      <c r="E7" t="n">
-        <v>15</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/fish</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/fish</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>XXX</t>
         </is>
@@ -693,27 +666,24 @@
       <c r="D8" t="n">
         <v>12</v>
       </c>
-      <c r="E8" t="n">
-        <v>12</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/noodle</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/noodle</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
           <t>X.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="H9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -733,27 +703,24 @@
       <c r="D10" t="n">
         <v>11</v>
       </c>
-      <c r="E10" t="n">
-        <v>11</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/dumpling</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/dumpling</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
           <t>XX</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>.X</t>
         </is>
@@ -773,20 +740,17 @@
       <c r="D12" t="n">
         <v>4</v>
       </c>
-      <c r="E12" t="n">
-        <v>4</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/chili</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/chili</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -806,27 +770,24 @@
       <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/orange</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/orange</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
           <t>XX</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -846,27 +807,24 @@
       <c r="D15" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="n">
-        <v>20</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/cake</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/cake</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
           <t>XXX</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>.X.</t>
         </is>
@@ -886,20 +844,17 @@
       <c r="D17" t="n">
         <v>25</v>
       </c>
-      <c r="E17" t="n">
-        <v>25</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sprites/Dishes/feast</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sprites/Dishes/feast</t>
+          <t>true</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
         <is>
           <t>XXXX</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,32 +892,27 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>aTagId</t>
+          <t>flavorId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>bTagId</t>
+          <t>baseWeight</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>baseWeight</t>
+          <t>price</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>price</t>
+          <t>hiddenRange</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>hiddenRange</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>*inherentTags</t>
+          <t>*skills</t>
         </is>
       </c>
     </row>
@@ -939,32 +934,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>唯一A标签ID</t>
+          <t>风味标签ID(可空,单槽)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>唯一B标签ID</t>
+          <t>随机基础权重</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>随机基础权重</t>
+          <t>商店价格</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>商店价格</t>
+          <t>出现隐藏分区间(单元格: min,max)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>出现隐藏分区间(单元格: min,max)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>固有标签ID列表</t>
+          <t>技能标签ID列表</t>
         </is>
       </c>
     </row>
@@ -991,25 +981,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>float</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>HiddenRange</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>HiddenRange</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>list,string</t>
         </is>
@@ -1026,13 +1011,13 @@
           <t>rice</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>150</v>
+      </c>
       <c r="F4" t="n">
-        <v>150</v>
-      </c>
-      <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1,10</t>
         </is>
@@ -1049,18 +1034,18 @@
           <t>egg</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>120</v>
+      </c>
       <c r="F5" t="n">
-        <v>120</v>
-      </c>
-      <c r="G5" t="n">
         <v>3</v>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>5,20</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>5,20</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>t_fresh</t>
         </is>
@@ -1077,18 +1062,18 @@
           <t>soup</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
       <c r="F6" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" t="n">
         <v>3</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8,24</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>8,24</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>t_lonely</t>
         </is>
@@ -1105,18 +1090,18 @@
           <t>fish</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>80</v>
+      </c>
       <c r="F7" t="n">
-        <v>80</v>
-      </c>
-      <c r="G7" t="n">
         <v>5</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>20,40</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>20,40</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
         <is>
           <t>t_fresh</t>
         </is>
@@ -1133,18 +1118,18 @@
           <t>noodle</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>90</v>
+      </c>
       <c r="F8" t="n">
-        <v>90</v>
-      </c>
-      <c r="G8" t="n">
         <v>4</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15,35</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
-        <is>
-          <t>15,35</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>t_hearty</t>
         </is>
@@ -1161,18 +1146,18 @@
           <t>dumpling</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>90</v>
+      </c>
       <c r="F9" t="n">
-        <v>90</v>
-      </c>
-      <c r="G9" t="n">
         <v>4</v>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>12,32</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
-        <is>
-          <t>12,32</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
         <is>
           <t>t_hearty</t>
         </is>
@@ -1189,18 +1174,18 @@
           <t>chili</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>110</v>
+      </c>
       <c r="F10" t="n">
-        <v>110</v>
-      </c>
-      <c r="G10" t="n">
         <v>2</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3,18</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
-        <is>
-          <t>3,18</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
         <is>
           <t>t_spicy</t>
         </is>
@@ -1217,18 +1202,18 @@
           <t>orange</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
       <c r="F11" t="n">
-        <v>100</v>
-      </c>
-      <c r="G11" t="n">
         <v>3</v>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10,30</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
-        <is>
-          <t>10,30</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
         <is>
           <t>t_sweet</t>
         </is>
@@ -1245,18 +1230,18 @@
           <t>cake</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>60</v>
+      </c>
       <c r="F12" t="n">
-        <v>60</v>
-      </c>
-      <c r="G12" t="n">
         <v>6</v>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>30,50</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
-        <is>
-          <t>30,50</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>t_sweet</t>
         </is>
@@ -1273,20 +1258,20 @@
           <t>feast</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>t_feast</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>40</v>
+      </c>
       <c r="F13" t="n">
-        <v>40</v>
-      </c>
-      <c r="G13" t="n">
         <v>8</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>40,70</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>t_feast</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,7 +585,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -613,7 +615,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -643,7 +645,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -673,7 +675,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -710,7 +712,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -814,7 +816,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -851,7 +853,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -871,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +914,11 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>rotation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>*skills</t>
         </is>
       </c>
@@ -954,6 +961,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>固定旋转朝向(整格四向)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>技能标签ID列表</t>
         </is>
       </c>
@@ -996,6 +1008,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>DishRotation</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>list,string</t>
         </is>
       </c>
@@ -1022,6 +1039,11 @@
           <t>1,10</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Deg0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1047,6 +1069,11 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>t_fresh</t>
         </is>
       </c>
@@ -1075,6 +1102,11 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>t_lonely</t>
         </is>
       </c>
@@ -1103,6 +1135,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>t_fresh</t>
         </is>
       </c>
@@ -1131,6 +1168,11 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>t_hearty</t>
         </is>
       </c>
@@ -1159,6 +1201,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>t_hearty</t>
         </is>
       </c>
@@ -1187,6 +1234,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>t_spicy</t>
         </is>
       </c>
@@ -1215,6 +1267,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>t_sweet</t>
         </is>
       </c>
@@ -1243,6 +1300,11 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>t_sweet</t>
         </is>
       </c>
@@ -1272,6 +1334,495 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>40,70</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Deg0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>effectValue</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>effectParam</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>termId</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>标签ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>标签名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>标签描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>效果参数</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>关联术语ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TagEffectType</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>list,float</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t_fresh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>新鲜</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>结算时美味度 {0}。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>term_deliciousness</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t_sweet</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>香甜</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>结算时本菜品贡献的分数 ×{0}。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t_spicy</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>麻辣</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>每有一个相邻菜品，美味度 {0}。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PerAdjacentDish</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>term_adjacent</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t_lonely</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>孤食</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>棋盘上每有一个空位，美味度 {0}。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PerEmptyCell</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>term_empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t_hearty</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>扎实</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>本菜品每占用一格，美味度 {0}。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PerOccupiedCell</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>effectType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>effectValue</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>effectParam</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>termId</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>标签ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>标签名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>标签描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>效果参数</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>关联术语ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TagEffectType</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>list,float</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t_feast</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>盛宴</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>棋盘上每有一道菜，本菜品分数 ×1.1。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PerDishOnBoard</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t_golden</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>黄金</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>本菜品贡献的分数 ×{0}。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_rule" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>t_lonely</t>
+          <t>sk_neighbor</t>
         </is>
       </c>
     </row>
@@ -1239,7 +1240,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>t_spicy</t>
+          <t>sk_same</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1306,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>t_sweet</t>
+          <t>cake_layer_add</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1629,6 +1630,358 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sk_neighbor</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>邻里飘香</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>每有一个相邻菜品，美味度 +3。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sk_empty</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>空盘寂寞</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>棋盘上每有一个空位，美味度 +2。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sk_row_full</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>满行盛宴</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>本行被填满时，本菜品分数 ×2。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sk_edge</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>边缘料理</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>本菜品处于棋盘边缘时，美味度 +5。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sk_bigdish</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>大菜相伴</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>全场每有一个≥2格的菜，美味度 +2。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sk_same</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>同类共鸣</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>全场每有一个同种菜，分数 ×1.5。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sk_shape</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>小巧玲珑</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>全场每有一个 1x1 菜，美味度 +1。</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sk_step</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>丰盛阶梯</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>全场菜品达到 3 个时，美味度 +50。</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sk_transfer</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>分你一口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>把本菜 30% 加法分传递给相邻菜。</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sk_extra</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>回味无穷</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>每有一个相邻菜，本菜额外结算 1 次。</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sk_gold</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>财源广进</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>全场每有一个菜，获得 1 金币。</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>cake_layer_add</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>蛋糕叠层</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>上菜时层数 +1。</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>cake_layer_score</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>蛋糕层高</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>本菜每有一层，美味度 +3。</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sk_run_same</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>念念不忘</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>本局每结算过一次本种菜，美味度 +3。</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sk_recipe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>菜谱丰盈</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>菜谱内菜品达到 8 个时，分数 ×2。</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sk_share_skill</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>秘方相传</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>上菜时把自身技能传给相邻菜。</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1829,4 +2182,1313 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>skillId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>order</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>trigger</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>condType</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>condScope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>condUnit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>condMode</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>condCompare</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>condThreshold</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>condParam</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>actionType</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>actionScope</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>actionCount</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>actionValue</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>actionParam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>规则ID(主键)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>所属技能ID-&gt;TbSkill.id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>同技能内执行顺序</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>触发时机</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>前提类型(None=无前提)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>前提作用域</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>计数单位(个/种)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>计数模式</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>比较符</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>阈值</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>前提附加参数(如1x1/settled/self)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>行为类型</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>行为作用域(目标)</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>随机目标数(0=全部)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>行为数值</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>行为参数(如mult/keep_transfer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SkillTrigger</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SkillConditionType</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SkillScope</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CountUnit</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>CountMode</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CompareOp</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>SkillActionType</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SkillScope</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>list,float</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>rr_neighbor</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sk_neighbor</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>DishCount</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rr_empty</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sk_empty</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EmptyCell</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>rr_rowfull</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sk_row_full</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PositionFilled</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>rr_edge</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sk_edge</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>rr_bigdish</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sk_bigdish</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DishSize</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>rr_same</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sk_same</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SameDish</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>rr_shape</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sk_shape</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ShapeMatch</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>rr_step</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sk_step</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DishCount</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rr_transfer</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sk_transfer</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>TransferScore</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>rr_extra</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sk_extra</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DishCount</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ExtraSettlement</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>rr_gold</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sk_gold</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DishCount</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>GrantGold</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>rr_cake_add</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cake_layer_add</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OnServe</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>AddLayer</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>rr_cake_score</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cake_layer_add</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>LayerCount</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>rr_runsame</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sk_run_same</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SameKindInRun</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>rr_recipe</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sk_recipe</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RecipeCount</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>8</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rr_share</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sk_share_skill</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OnServe</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>TransferSkills</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Adjacent</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -457,6 +457,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>skills</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>*shapeRows</t>
         </is>
       </c>
@@ -494,6 +499,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>技能标签ID列表</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>菜品形状行列表</t>
         </is>
       </c>
@@ -534,6 +544,11 @@
           <t>list,string</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -559,7 +574,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -591,6 +606,11 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>t_fresh</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
@@ -621,6 +641,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>sk_neighbor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
@@ -651,6 +676,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>t_fresh</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>XXX</t>
         </is>
       </c>
@@ -681,12 +711,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>t_hearty</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>X.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -718,12 +753,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>t_hearty</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>.X</t>
         </is>
@@ -755,6 +795,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>sk_same</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>X</t>
         </is>
       </c>
@@ -785,12 +830,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>t_sweet</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>XX</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>XX</t>
         </is>
@@ -822,12 +872,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>cake_layer_add</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>XXX</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>.X.</t>
         </is>
@@ -857,7 +912,7 @@
           <t>false</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>XXXX</t>
         </is>
@@ -874,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,11 +973,6 @@
           <t>rotation</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>*skills</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -965,11 +1015,6 @@
           <t>固定旋转朝向(整格四向)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>技能标签ID列表</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1012,11 +1057,6 @@
           <t>DishRotation</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>list,string</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -1073,11 +1113,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>t_fresh</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -1106,11 +1141,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>sk_neighbor</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -1139,11 +1169,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>t_fresh</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1172,11 +1197,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>t_hearty</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1205,11 +1225,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>t_hearty</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1238,11 +1253,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>sk_same</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1271,11 +1281,6 @@
           <t>Deg0</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>t_sweet</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1302,11 +1307,6 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>Deg0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>cake_layer_add</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1380,21 +1380,6 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>effectType</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>effectValue</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>effectParam</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>termId</t>
         </is>
       </c>
@@ -1422,21 +1407,6 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>效果类型</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>效果数值</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>效果参数</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>关联术语ID</t>
         </is>
       </c>
@@ -1464,21 +1434,6 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TagEffectType</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>list,float</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>list,string</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>string</t>
         </is>
       </c>
@@ -1496,20 +1451,10 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>结算时美味度 {0}。</t>
+          <t>结算时美味度 +5。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
         <is>
           <t>term_deliciousness</t>
         </is>
@@ -1528,17 +1473,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>结算时本菜品贡献的分数 ×{0}。</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AddMult</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1.5</t>
+          <t>结算时本菜品贡献的分数 ×1.5。</t>
         </is>
       </c>
     </row>
@@ -1555,20 +1490,10 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>每有一个相邻菜品，美味度 {0}。</t>
+          <t>每有一个相邻菜品，美味度 +3。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
-        <is>
-          <t>PerAdjacentDish</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
         <is>
           <t>term_adjacent</t>
         </is>
@@ -1587,20 +1512,10 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>棋盘上每有一个空位，美味度 {0}。</t>
+          <t>棋盘上每有一个空位，美味度 +2。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
-        <is>
-          <t>PerEmptyCell</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
         <is>
           <t>term_empty</t>
         </is>
@@ -1619,17 +1534,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>本菜品每占用一格，美味度 {0}。</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PerOccupiedCell</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>本菜品每占用一格，美味度 +2。</t>
         </is>
       </c>
     </row>
@@ -1649,11 +1554,6 @@
           <t>每有一个相邻菜品，美味度 +3。</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1671,11 +1571,6 @@
           <t>棋盘上每有一个空位，美味度 +2。</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1693,11 +1588,6 @@
           <t>本行被填满时，本菜品分数 ×2。</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1715,11 +1605,6 @@
           <t>本菜品处于棋盘边缘时，美味度 +5。</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -1737,11 +1622,6 @@
           <t>全场每有一个≥2格的菜，美味度 +2。</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -1759,11 +1639,6 @@
           <t>全场每有一个同种菜，分数 ×1.5。</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -1781,11 +1656,6 @@
           <t>全场每有一个 1x1 菜，美味度 +1。</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -1803,11 +1673,6 @@
           <t>全场菜品达到 3 个时，美味度 +50。</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -1825,11 +1690,6 @@
           <t>把本菜 30% 加法分传递给相邻菜。</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
@@ -1847,11 +1707,6 @@
           <t>每有一个相邻菜，本菜额外结算 1 次。</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -1869,11 +1724,6 @@
           <t>全场每有一个菜，获得 1 金币。</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -1891,11 +1741,6 @@
           <t>上菜时层数 +1。</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -1913,11 +1758,6 @@
           <t>本菜每有一层，美味度 +3。</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
@@ -1935,11 +1775,6 @@
           <t>本局每结算过一次本种菜，美味度 +3。</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -1957,11 +1792,6 @@
           <t>菜谱内菜品达到 8 个时，分数 ×2。</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -1977,11 +1807,6 @@
       <c r="D24" t="inlineStr">
         <is>
           <t>上菜时把自身技能传给相邻菜。</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,12 +2282,12 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>rr_neighbor</t>
+          <t>rr_t_fresh</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sk_neighbor</t>
+          <t>t_fresh</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2475,12 +2300,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DishCount</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Adjacent</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2515,18 +2340,18 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>rr_empty</t>
+          <t>rr_t_sweet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sk_empty</t>
+          <t>t_sweet</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -2539,12 +2364,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EmptyCell</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2567,7 +2392,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>AddFlat</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2579,18 +2404,18 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>rr_rowfull</t>
+          <t>rr_t_spicy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sk_row_full</t>
+          <t>t_spicy</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -2603,12 +2428,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PositionFilled</t>
+          <t>DishCount</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Row</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2618,7 +2443,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Per</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2631,7 +2456,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2643,18 +2468,18 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>rr_edge</t>
+          <t>rr_t_lonely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sk_edge</t>
+          <t>t_lonely</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -2667,58 +2492,58 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Edge</t>
+          <t>EmptyCell</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Instances</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Gate</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>rr_bigdish</t>
+          <t>rr_t_hearty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sk_bigdish</t>
+          <t>t_hearty</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -2731,12 +2556,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>DishSize</t>
+          <t>OccupiedCell</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2751,11 +2576,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Gte</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2777,12 +2602,12 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>rr_same</t>
+          <t>rr_neighbor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sk_same</t>
+          <t>sk_neighbor</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -2795,12 +2620,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SameDish</t>
+          <t>DishCount</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2823,7 +2648,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2835,18 +2660,18 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>rr_shape</t>
+          <t>rr_empty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sk_shape</t>
+          <t>sk_empty</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -2859,7 +2684,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ShapeMatch</t>
+          <t>EmptyCell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2885,11 +2710,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1x1</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>AddFlat</t>
@@ -2904,18 +2724,18 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>rr_step</t>
+          <t>rr_rowfull</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sk_step</t>
+          <t>sk_row_full</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2928,12 +2748,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DishCount</t>
+          <t>PositionFilled</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Row</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2943,20 +2763,20 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Gate</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Gte</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>AddFlat</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2968,18 +2788,18 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>rr_transfer</t>
+          <t>rr_edge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sk_transfer</t>
+          <t>sk_edge</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2992,58 +2812,58 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Instances</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Per</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>TransferScore</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Adjacent</t>
-        </is>
-      </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>rr_extra</t>
+          <t>rr_bigdish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sk_extra</t>
+          <t>sk_bigdish</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -3056,12 +2876,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DishCount</t>
+          <t>DishSize</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Adjacent</t>
+          <t>All</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3076,15 +2896,15 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Gte</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>ExtraSettlement</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3096,18 +2916,18 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>rr_gold</t>
+          <t>rr_same</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sk_gold</t>
+          <t>sk_same</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -3120,7 +2940,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DishCount</t>
+          <t>SameDish</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3146,14 +2966,9 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>self</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>GrantGold</t>
+          <t>AddMult</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3165,18 +2980,18 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>rr_cake_add</t>
+          <t>rr_shape</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cake_layer_add</t>
+          <t>sk_shape</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -3184,40 +2999,45 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OnServe</t>
+          <t>OnSettle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>ShapeMatch</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Instances</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Per</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1x1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>AddLayer</t>
+          <t>AddFlat</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3235,16 +3055,16 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>rr_cake_score</t>
+          <t>rr_step</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cake_layer_add</t>
+          <t>sk_step</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -3253,58 +3073,58 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LayerCount</t>
+          <t>DishCount</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Reach</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Instances</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Per</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>AddFlat</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Self</t>
-        </is>
-      </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>rr_runsame</t>
+          <t>rr_transfer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sk_run_same</t>
+          <t>sk_transfer</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -3317,7 +3137,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SameKindInRun</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3345,30 +3165,30 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>AddFlat</t>
+          <t>TransferScore</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Self</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>rr_recipe</t>
+          <t>rr_extra</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sk_recipe</t>
+          <t>sk_extra</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -3381,12 +3201,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RecipeCount</t>
+          <t>DishCount</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Adjacent</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3396,20 +3216,20 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gate</t>
+          <t>Per</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Gte</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>AddMult</t>
+          <t>ExtraSettlement</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3421,70 +3241,395 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
+          <t>rr_gold</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sk_gold</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DishCount</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>GrantGold</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>rr_cake_add</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cake_layer_add</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>OnServe</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>AddLayer</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>rr_cake_score</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cake_layer_add</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>LayerCount</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>rr_runsame</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sk_run_same</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SameKindInRun</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>AddFlat</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>rr_recipe</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sk_recipe</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>RecipeCount</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Recipe</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Gate</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Gte</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>AddMult</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
           <t>rr_share</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>sk_share_skill</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>OnServe</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Self</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Instances</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Per</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>TransferSkills</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Adjacent</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>0</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="5"/>
+    <workbookView windowHeight="16760" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">sub_skill!$C$1:$C$69</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1199,7 +1212,7 @@
     <t>true</t>
   </si>
   <si>
-    <t>处在棋盘边缘时，{ascopes}倍率 {0}。</t>
+    <t>处在棋盘边缘时，{ascope}倍率 {0}。</t>
   </si>
   <si>
     <t>DishCount</t>
@@ -1214,7 +1227,7 @@
     <t>Per</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascopes}分数 {0}。</t>
+    <t>{cscope}每有 1 {unit}食物，{ascope}分数 {0}。</t>
   </si>
   <si>
     <t>None</t>
@@ -1226,19 +1239,19 @@
     <t>Row</t>
   </si>
   <si>
-    <t>甜蜜传递至{ascopes}食物</t>
+    <t>甜蜜传递至{ascope}食物</t>
   </si>
   <si>
     <t>EmptyCell</t>
   </si>
   <si>
-    <t>{cscope}每有 1 个空格，{ascopes}分数 {0}。</t>
+    <t>{cscope}每有 1 个空格，{ascope}分数 {0}。</t>
   </si>
   <si>
     <t>AddLayer</t>
   </si>
   <si>
-    <t>Cake</t>
+    <t>CakeBuff</t>
   </si>
   <si>
     <t>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层。</t>
@@ -1250,13 +1263,13 @@
     <t>PermanentAddFlat</t>
   </si>
   <si>
-    <t>结算时，{ascopes}分数永久 {0}。</t>
+    <t>结算时，{ascope}分数永久 {0}。</t>
   </si>
   <si>
     <t>ColumnAndSelf</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascopes}倍率 {0}。</t>
+    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</t>
   </si>
   <si>
     <t>RowAndSelf</t>
@@ -1265,7 +1278,7 @@
     <t>TagCount</t>
   </si>
   <si>
-    <t>结算每有1个技能，{ascopes}分数永久 {0}。</t>
+    <t>结算每有1个技能，{ascope}分数永久 {0}。</t>
   </si>
   <si>
     <t>RoundAndSelf</t>
@@ -1304,7 +1317,7 @@
     <t>AddCountAs</t>
   </si>
   <si>
-    <t>{ascopes}视为 {countas} 个食物。</t>
+    <t>{ascope}视为 {countas} 个食物。</t>
   </si>
   <si>
     <t>OnServe</t>
@@ -1325,13 +1338,13 @@
     <t>1x1</t>
   </si>
   <si>
-    <t>{cscope}有占 1 格的食物时，{ascopes}倍率 ×{0}。</t>
+    <t>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}。</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascopes}倍率 ×{0}。</t>
+    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}。</t>
   </si>
   <si>
     <t>CopySkill</t>
@@ -1343,16 +1356,16 @@
     <t>每有 1 个技能，欢乐蛋糕 {0} 层。</t>
   </si>
   <si>
-    <t>{ascopes}倍率 ×{0}。</t>
-  </si>
-  <si>
-    <t>{ascopes}分数永久 {0}。</t>
+    <t>{ascope}倍率 ×{0}。</t>
+  </si>
+  <si>
+    <t>{ascope}分数永久 {0}。</t>
   </si>
   <si>
     <t>All</t>
   </si>
   <si>
-    <t>{ascopes}倍率 {0}。</t>
+    <t>{ascope}倍率 {0}。</t>
   </si>
   <si>
     <t>ConsumeLayer</t>
@@ -1367,6 +1380,9 @@
     <t>欢乐蛋糕 ×{0} 层，至少 +{floor} 层。</t>
   </si>
   <si>
+    <t>除需要严格刨除自身时，才刨除</t>
+  </si>
+  <si>
     <t>Reach</t>
   </si>
   <si>
@@ -1376,13 +1392,13 @@
     <t>tiervals:1.5|2.5|5</t>
   </si>
   <si>
-    <t>{cscope}食物达 {tiers} 个时，{ascopes}倍率 ×{tiervals}。</t>
-  </si>
-  <si>
-    <t>若{cscope}被填满，{ascopes}额外视为 {0} 个食物。</t>
-  </si>
-  <si>
-    <t>{ascopes}额外视为 {0} 个食物。</t>
+    <t>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}。</t>
+  </si>
+  <si>
+    <t>若{cscope}被填满，{ascope}额外视为 {0} 个食物。</t>
+  </si>
+  <si>
+    <t>{ascope}额外视为 {0} 个食物。</t>
   </si>
   <si>
     <t>Category</t>
@@ -1394,7 +1410,7 @@
     <t>将分数加到所有{cat}上（每个{cat} {0} 分）。</t>
   </si>
   <si>
-    <t>{cscope}每有 1 个技能，{ascopes}倍率 {0}。</t>
+    <t>{cscope}每有 1 个技能，{ascope}倍率 {0}。</t>
   </si>
   <si>
     <t>将倍率 {0} 加到所有{cat}上。</t>
@@ -1433,13 +1449,10 @@
     <t>同行同列带甜蜜传递的食物，各执行一次它们的甜蜜传递。</t>
   </si>
   <si>
-    <t>{cscope}每有 1 个技能，{ascopes}倍率 ×{0}。</t>
-  </si>
-  <si>
-    <t>{ascopes}获得 {0} 种不同的{cat}技能。</t>
-  </si>
-  <si>
-    <t>除需要严格刨除自身时，才刨除</t>
+    <t>{cscope}每有 1 个技能，{ascope}倍率 ×{0}。</t>
+  </si>
+  <si>
+    <t>{ascope}获得 {0} 种不同的{cat}技能。</t>
   </si>
   <si>
     <t>菜品</t>
@@ -1970,7 +1983,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -3216,7 +3229,7 @@
       </c>
       <c r="O4" s="1" t="str">
         <f>IFERROR(VLOOKUP(M4,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>处在棋盘边缘时，{ascopes}倍率 {0}。</v>
+        <v>处在棋盘边缘时，{ascope}倍率 {0}。</v>
       </c>
       <c r="P4" s="1" t="str">
         <f>IFERROR(VLOOKUP(N4,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3264,11 +3277,11 @@
       </c>
       <c r="O5" s="1" t="str">
         <f>IFERROR(VLOOKUP(M5,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}分数 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}分数 {0}。</v>
       </c>
       <c r="P5" s="1" t="str">
         <f>IFERROR(VLOOKUP(N5,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -3309,7 +3322,7 @@
       </c>
       <c r="O6" s="1" t="str">
         <f>IFERROR(VLOOKUP(M6,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 个空格，{ascopes}分数 {0}。</v>
+        <v>{cscope}每有 1 个空格，{ascope}分数 {0}。</v>
       </c>
       <c r="P6" s="1" t="str">
         <f>IFERROR(VLOOKUP(N6,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3397,7 +3410,7 @@
       </c>
       <c r="O8" s="1" t="str">
         <f>IFERROR(VLOOKUP(M8,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>结算时，{ascopes}分数永久 {0}。</v>
+        <v>结算时，{ascope}分数永久 {0}。</v>
       </c>
       <c r="P8" s="1" t="str">
         <f>IFERROR(VLOOKUP(N8,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3440,7 +3453,7 @@
       </c>
       <c r="O9" s="1" t="str">
         <f>IFERROR(VLOOKUP(M9,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
       </c>
       <c r="P9" s="1" t="str">
         <f>IFERROR(VLOOKUP(N9,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3483,7 +3496,7 @@
       </c>
       <c r="O10" s="1" t="str">
         <f>IFERROR(VLOOKUP(M10,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}分数 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}分数 {0}。</v>
       </c>
       <c r="P10" s="1" t="str">
         <f>IFERROR(VLOOKUP(N10,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3526,7 +3539,7 @@
       </c>
       <c r="O11" s="1" t="str">
         <f>IFERROR(VLOOKUP(M11,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>结算每有1个技能，{ascopes}分数永久 {0}。</v>
+        <v>结算每有1个技能，{ascope}分数永久 {0}。</v>
       </c>
       <c r="P11" s="1" t="str">
         <f>IFERROR(VLOOKUP(N11,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3569,7 +3582,7 @@
       </c>
       <c r="O12" s="1" t="str">
         <f>IFERROR(VLOOKUP(M12,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
       </c>
       <c r="P12" s="1" t="str">
         <f>IFERROR(VLOOKUP(N12,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3662,7 +3675,7 @@
       </c>
       <c r="P14" s="1" t="str">
         <f>IFERROR(VLOOKUP(N14,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -3790,11 +3803,11 @@
       </c>
       <c r="O17" s="1" t="str">
         <f>IFERROR(VLOOKUP(M17,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
       </c>
       <c r="P17" s="1" t="str">
         <f>IFERROR(VLOOKUP(N17,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -3905,11 +3918,11 @@
       </c>
       <c r="O20" s="1" t="str">
         <f>IFERROR(VLOOKUP(M20,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}有占 1 格的食物时，{ascopes}倍率 ×{0}。</v>
+        <v>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P20" s="1" t="str">
         <f>IFERROR(VLOOKUP(N20,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="21" spans="2:16">
@@ -3953,11 +3966,11 @@
       </c>
       <c r="O21" s="1" t="str">
         <f>IFERROR(VLOOKUP(M21,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 ×{0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P21" s="1" t="str">
         <f>IFERROR(VLOOKUP(N21,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="22" spans="2:16">
@@ -4049,7 +4062,7 @@
       </c>
       <c r="O23" s="1" t="str">
         <f>IFERROR(VLOOKUP(M23,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P23" s="1" t="str">
         <f>IFERROR(VLOOKUP(N23,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4118,11 +4131,11 @@
       </c>
       <c r="O25" s="1" t="str">
         <f>IFERROR(VLOOKUP(M25,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}分数永久 {0}。</v>
+        <v>{ascope}分数永久 {0}。</v>
       </c>
       <c r="P25" s="1" t="str">
         <f>IFERROR(VLOOKUP(N25,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="26" spans="9:16">
@@ -4191,7 +4204,7 @@
       </c>
       <c r="P27" s="1" t="str">
         <f>IFERROR(VLOOKUP(N27,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="28" spans="9:16">
@@ -4254,11 +4267,11 @@
       </c>
       <c r="O29" s="1" t="str">
         <f>IFERROR(VLOOKUP(M29,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
       </c>
       <c r="P29" s="1" t="str">
         <f>IFERROR(VLOOKUP(N29,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -4300,11 +4313,11 @@
       </c>
       <c r="O30" s="1" t="str">
         <f>IFERROR(VLOOKUP(M30,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
       <c r="P30" s="1" t="str">
         <f>IFERROR(VLOOKUP(N30,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -4350,7 +4363,7 @@
       </c>
       <c r="P31" s="1" t="str">
         <f>IFERROR(VLOOKUP(N31,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
     </row>
     <row r="32" spans="9:16">
@@ -4436,11 +4449,11 @@
       </c>
       <c r="O34" s="1" t="str">
         <f>IFERROR(VLOOKUP(M34,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
       <c r="P34" s="1" t="str">
         <f>IFERROR(VLOOKUP(N34,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="35" spans="9:16">
@@ -4587,7 +4600,7 @@
       </c>
       <c r="O39" s="1" t="str">
         <f>IFERROR(VLOOKUP(M39,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}食物达 {tiers} 个时，{ascopes}倍率 ×{tiervals}。</v>
+        <v>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}。</v>
       </c>
       <c r="P39" s="1" t="str">
         <f>IFERROR(VLOOKUP(N39,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4660,7 +4673,7 @@
       </c>
       <c r="P41" s="1" t="str">
         <f>IFERROR(VLOOKUP(N41,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="42" spans="9:16">
@@ -4725,11 +4738,11 @@
       </c>
       <c r="O43" s="1" t="str">
         <f>IFERROR(VLOOKUP(M43,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P43" s="1" t="str">
         <f>IFERROR(VLOOKUP(N43,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>若{cscope}被填满，{ascopes}额外视为 {0} 个食物。</v>
+        <v>若{cscope}被填满，{ascope}额外视为 {0} 个食物。</v>
       </c>
     </row>
     <row r="44" spans="9:16">
@@ -4794,11 +4807,11 @@
       </c>
       <c r="O45" s="1" t="str">
         <f>IFERROR(VLOOKUP(M45,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}额外视为 {0} 个食物。</v>
+        <v>{ascope}额外视为 {0} 个食物。</v>
       </c>
       <c r="P45" s="1" t="str">
         <f>IFERROR(VLOOKUP(N45,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
     </row>
     <row r="46" spans="9:16">
@@ -4863,7 +4876,7 @@
       </c>
       <c r="O47" s="1" t="str">
         <f>IFERROR(VLOOKUP(M47,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}分数永久 {0}。</v>
+        <v>{ascope}分数永久 {0}。</v>
       </c>
       <c r="P47" s="1" t="str">
         <f>IFERROR(VLOOKUP(N47,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4934,7 +4947,7 @@
       </c>
       <c r="P49" s="1" t="str">
         <f>IFERROR(VLOOKUP(N49,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
     </row>
     <row r="50" spans="9:16">
@@ -4999,11 +5012,11 @@
       </c>
       <c r="O51" s="1" t="str">
         <f>IFERROR(VLOOKUP(M51,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 个技能，{ascopes}倍率 {0}。</v>
+        <v>{cscope}每有 1 个技能，{ascope}倍率 {0}。</v>
       </c>
       <c r="P51" s="1" t="str">
         <f>IFERROR(VLOOKUP(N51,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="52" spans="9:16">
@@ -5068,11 +5081,11 @@
       </c>
       <c r="O53" s="1" t="str">
         <f>IFERROR(VLOOKUP(M53,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 ×{0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P53" s="1" t="str">
         <f>IFERROR(VLOOKUP(N53,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="54" spans="9:16">
@@ -5137,11 +5150,11 @@
       </c>
       <c r="O55" s="1" t="str">
         <f>IFERROR(VLOOKUP(M55,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P55" s="1" t="str">
         <f>IFERROR(VLOOKUP(N55,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="56" spans="9:16">
@@ -5229,7 +5242,7 @@
       </c>
       <c r="P58" s="1" t="str">
         <f>IFERROR(VLOOKUP(N58,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
     </row>
     <row r="59" spans="9:16">
@@ -5319,7 +5332,7 @@
       </c>
       <c r="P61" s="1" t="str">
         <f>IFERROR(VLOOKUP(N61,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="62" spans="9:16">
@@ -5384,7 +5397,7 @@
       </c>
       <c r="O63" s="1" t="str">
         <f>IFERROR(VLOOKUP(M63,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}。</v>
       </c>
       <c r="P63" s="1" t="str">
         <f>IFERROR(VLOOKUP(N63,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5450,7 +5463,7 @@
       </c>
       <c r="O65" s="1" t="str">
         <f>IFERROR(VLOOKUP(M65,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascopes}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
       </c>
       <c r="P65" s="1" t="str">
         <f>IFERROR(VLOOKUP(N65,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5540,7 +5553,7 @@
       </c>
       <c r="O68" s="1" t="str">
         <f>IFERROR(VLOOKUP(M68,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P68" s="1" t="str">
         <f>IFERROR(VLOOKUP(N68,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5760,11 +5773,11 @@
       </c>
       <c r="O75" s="1" t="str">
         <f>IFERROR(VLOOKUP(M75,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P75" s="1" t="str">
         <f>IFERROR(VLOOKUP(N75,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物。</v>
       </c>
     </row>
     <row r="76" spans="9:16">
@@ -5829,11 +5842,11 @@
       </c>
       <c r="O77" s="1" t="str">
         <f>IFERROR(VLOOKUP(M77,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P77" s="1" t="str">
         <f>IFERROR(VLOOKUP(N77,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="78" spans="9:16">
@@ -6048,11 +6061,11 @@
       </c>
       <c r="O85" s="1" t="str">
         <f>IFERROR(VLOOKUP(M85,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 个技能，{ascopes}倍率 ×{0}。</v>
+        <v>{cscope}每有 1 个技能，{ascope}倍率 ×{0}。</v>
       </c>
       <c r="P85" s="1" t="str">
         <f>IFERROR(VLOOKUP(N85,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>甜蜜传递至{ascopes}食物</v>
+        <v>甜蜜传递至{ascope}食物</v>
       </c>
     </row>
     <row r="86" spans="9:16">
@@ -6135,7 +6148,7 @@
       </c>
       <c r="O88" s="1" t="str">
         <f>IFERROR(VLOOKUP(M88,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascopes}获得 {0} 种不同的{cat}技能。</v>
+        <v>{ascope}获得 {0} 种不同的{cat}技能。</v>
       </c>
       <c r="P88" s="1" t="str">
         <f>IFERROR(VLOOKUP(N88,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -8217,7 +8230,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R78"/>
+  <dimension ref="A1:R69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
@@ -8236,6 +8249,7 @@
     <col min="14" max="14" width="10.3076923076923" customWidth="1"/>
     <col min="15" max="15" width="12.7692307692308" customWidth="1"/>
     <col min="16" max="16" width="84.6153846153846" customWidth="1"/>
+    <col min="18" max="18" width="34.5384615384615" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -9891,7 +9905,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="36" spans="2:16">
+    <row r="36" spans="2:18">
       <c r="B36" t="s">
         <v>135</v>
       </c>
@@ -9935,8 +9949,11 @@
       <c r="P36" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="37" spans="2:16">
+      <c r="R36" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18">
       <c r="B37" t="s">
         <v>136</v>
       </c>
@@ -9982,8 +9999,11 @@
       <c r="P37" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="38" spans="2:16">
+      <c r="R37" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18">
       <c r="B38" t="s">
         <v>140</v>
       </c>
@@ -10029,8 +10049,11 @@
       <c r="P38" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="39" spans="2:16">
+      <c r="R38" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18">
       <c r="B39" t="s">
         <v>141</v>
       </c>
@@ -10076,8 +10099,11 @@
       <c r="P39" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="40" spans="2:16">
+      <c r="R39" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18">
       <c r="B40" t="s">
         <v>145</v>
       </c>
@@ -10122,6 +10148,9 @@
       </c>
       <c r="P40" t="s">
         <v>446</v>
+      </c>
+      <c r="R40" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="41" spans="2:16">
@@ -10141,10 +10170,10 @@
         <v>388</v>
       </c>
       <c r="G41" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H41" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="I41" t="s">
         <v>330</v>
@@ -10159,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N41" t="s">
         <v>27</v>
@@ -10168,7 +10197,7 @@
         <v>27</v>
       </c>
       <c r="P41" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="42" spans="2:16">
@@ -10309,7 +10338,7 @@
         <v>27</v>
       </c>
       <c r="P44" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="45" spans="2:16">
@@ -10356,7 +10385,7 @@
         <v>27</v>
       </c>
       <c r="P45" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="46" spans="2:16">
@@ -10432,7 +10461,7 @@
         <v>344</v>
       </c>
       <c r="J47" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -10441,7 +10470,7 @@
         <v>10</v>
       </c>
       <c r="M47" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s">
         <v>27</v>
@@ -10450,7 +10479,7 @@
         <v>390</v>
       </c>
       <c r="P47" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" spans="2:16">
@@ -10544,7 +10573,7 @@
         <v>390</v>
       </c>
       <c r="P49" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="50" spans="2:16">
@@ -10902,7 +10931,7 @@
         <v>347</v>
       </c>
       <c r="J57" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -10911,7 +10940,7 @@
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N57" t="s">
         <v>27</v>
@@ -10920,7 +10949,7 @@
         <v>390</v>
       </c>
       <c r="P57" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" spans="2:16">
@@ -11025,7 +11054,7 @@
         <v>385</v>
       </c>
       <c r="D60" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E60" t="s">
         <v>441</v>
@@ -11034,10 +11063,10 @@
         <v>388</v>
       </c>
       <c r="G60" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H60" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I60" t="s">
         <v>403</v>
@@ -11052,7 +11081,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N60" t="s">
         <v>27</v>
@@ -11061,7 +11090,7 @@
         <v>27</v>
       </c>
       <c r="P60" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61" spans="2:16">
@@ -11072,7 +11101,7 @@
         <v>385</v>
       </c>
       <c r="D61" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E61" t="s">
         <v>441</v>
@@ -11081,10 +11110,10 @@
         <v>394</v>
       </c>
       <c r="G61" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H61" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I61" t="s">
         <v>330</v>
@@ -11099,7 +11128,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N61" t="s">
         <v>27</v>
@@ -11108,7 +11137,7 @@
         <v>27</v>
       </c>
       <c r="P61" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62" spans="2:16">
@@ -11322,7 +11351,7 @@
         <v>29</v>
       </c>
       <c r="I66" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J66" t="s">
         <v>441</v>
@@ -11334,7 +11363,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N66" t="s">
         <v>27</v>
@@ -11343,7 +11372,7 @@
         <v>27</v>
       </c>
       <c r="P66" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="67" spans="2:16">
@@ -11390,7 +11419,7 @@
         <v>27</v>
       </c>
       <c r="P67" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="68" spans="2:16">
@@ -11475,7 +11504,7 @@
         <v>3</v>
       </c>
       <c r="M69" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N69" t="s">
         <v>27</v>
@@ -11484,36 +11513,11 @@
         <v>27</v>
       </c>
       <c r="P69" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="74" spans="6:6">
-      <c r="F74" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="75" spans="6:6">
-      <c r="F75" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="76" spans="6:6">
-      <c r="F76" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="77" spans="6:6">
-      <c r="F77" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="78" spans="6:6">
-      <c r="F78" t="s">
         <v>471</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C69">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C69" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -19,20 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">sub_skill!$C$1:$C$69</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
@@ -1212,7 +1199,7 @@
     <t>true</t>
   </si>
   <si>
-    <t>处在棋盘边缘时，{ascope}倍率 {0}。</t>
+    <t>处在棋盘边缘时，{ascope}倍率 {0}</t>
   </si>
   <si>
     <t>DishCount</t>
@@ -1227,7 +1214,7 @@
     <t>Per</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascope}分数 {0}。</t>
+    <t>{cscope}每有 1 {unit}食物，{ascope}分数 {0}</t>
   </si>
   <si>
     <t>None</t>
@@ -1245,7 +1232,7 @@
     <t>EmptyCell</t>
   </si>
   <si>
-    <t>{cscope}每有 1 个空格，{ascope}分数 {0}。</t>
+    <t>{cscope}每有 1 个空格，{ascope}分数 {0}</t>
   </si>
   <si>
     <t>AddLayer</t>
@@ -1254,7 +1241,7 @@
     <t>CakeBuff</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层。</t>
+    <t>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层</t>
   </si>
   <si>
     <t>SameKindInRun</t>
@@ -1263,13 +1250,13 @@
     <t>PermanentAddFlat</t>
   </si>
   <si>
-    <t>结算时，{ascope}分数永久 {0}。</t>
+    <t>结算时，{ascope}分数永久 {0}</t>
   </si>
   <si>
     <t>ColumnAndSelf</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</t>
+    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</t>
   </si>
   <si>
     <t>RowAndSelf</t>
@@ -1278,19 +1265,19 @@
     <t>TagCount</t>
   </si>
   <si>
-    <t>结算每有1个技能，{ascope}分数永久 {0}。</t>
+    <t>结算每有1个技能，{ascope}分数永久 {0}</t>
   </si>
   <si>
     <t>RoundAndSelf</t>
   </si>
   <si>
-    <t>欢乐蛋糕 {0} 层。</t>
+    <t>欢乐蛋糕 {0} 层</t>
   </si>
   <si>
     <t>ExtraSettlement</t>
   </si>
   <si>
-    <t>技能额外结算 {0} 次。</t>
+    <t>技能额外结算 {0} 次</t>
   </si>
   <si>
     <t>设计比较危险</t>
@@ -1305,19 +1292,19 @@
     <t>GrantGold</t>
   </si>
   <si>
-    <t>若{cscope}被填满，获得 {0} 金币。</t>
+    <t>若{cscope}被填满，获得 {0} 金币</t>
   </si>
   <si>
     <t>运营向的比较少</t>
   </si>
   <si>
-    <t>若{cscope}被填满，欢乐蛋糕 {0} 层。</t>
+    <t>若{cscope}被填满，欢乐蛋糕 {0} 层</t>
   </si>
   <si>
     <t>AddCountAs</t>
   </si>
   <si>
-    <t>{ascope}视为 {countas} 个食物。</t>
+    <t>{ascope}视为 {countas} 个食物</t>
   </si>
   <si>
     <t>OnServe</t>
@@ -1326,7 +1313,7 @@
     <t>TempCopyDish</t>
   </si>
   <si>
-    <t>复制本菜品至空格中。</t>
+    <t>复制本菜品至空格中</t>
   </si>
   <si>
     <t>需要立即结算</t>
@@ -1338,46 +1325,46 @@
     <t>1x1</t>
   </si>
   <si>
-    <t>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}。</t>
+    <t>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}。</t>
+    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}</t>
   </si>
   <si>
     <t>CopySkill</t>
   </si>
   <si>
-    <t>复制{ascope}食物的 {0} 个技能。</t>
-  </si>
-  <si>
-    <t>每有 1 个技能，欢乐蛋糕 {0} 层。</t>
-  </si>
-  <si>
-    <t>{ascope}倍率 ×{0}。</t>
-  </si>
-  <si>
-    <t>{ascope}分数永久 {0}。</t>
+    <t>复制{ascope}食物的 {0} 个技能</t>
+  </si>
+  <si>
+    <t>每有 1 个技能，欢乐蛋糕 {0} 层</t>
+  </si>
+  <si>
+    <t>{ascope}倍率 ×{0}</t>
+  </si>
+  <si>
+    <t>{ascope}分数永久 {0}</t>
   </si>
   <si>
     <t>All</t>
   </si>
   <si>
-    <t>{ascope}倍率 {0}。</t>
+    <t>{ascope}倍率 {0}</t>
   </si>
   <si>
     <t>ConsumeLayer</t>
   </si>
   <si>
-    <t>消耗 {0} 层欢乐蛋糕。</t>
+    <t>消耗 {0} 层欢乐蛋糕</t>
   </si>
   <si>
     <t>multfloor:5</t>
   </si>
   <si>
-    <t>欢乐蛋糕 ×{0} 层，至少 +{floor} 层。</t>
+    <t>欢乐蛋糕 ×{0} 层，至少 +{floor} 层</t>
   </si>
   <si>
     <t>除需要严格刨除自身时，才刨除</t>
@@ -1392,13 +1379,13 @@
     <t>tiervals:1.5|2.5|5</t>
   </si>
   <si>
-    <t>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}。</t>
-  </si>
-  <si>
-    <t>若{cscope}被填满，{ascope}额外视为 {0} 个食物。</t>
-  </si>
-  <si>
-    <t>{ascope}额外视为 {0} 个食物。</t>
+    <t>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}</t>
+  </si>
+  <si>
+    <t>若{cscope}被填满，{ascope}额外视为 {0} 个食物</t>
+  </si>
+  <si>
+    <t>{ascope}额外视为 {0} 个食物</t>
   </si>
   <si>
     <t>Category</t>
@@ -1407,13 +1394,13 @@
     <t>cat:cake</t>
   </si>
   <si>
-    <t>将分数加到所有{cat}上（每个{cat} {0} 分）。</t>
-  </si>
-  <si>
-    <t>{cscope}每有 1 个技能，{ascope}倍率 {0}。</t>
-  </si>
-  <si>
-    <t>将倍率 {0} 加到所有{cat}上。</t>
+    <t>将分数加到所有{cat}上（每个{cat} {0} 分）</t>
+  </si>
+  <si>
+    <t>{cscope}每有 1 个技能，{ascope}倍率 {0}</t>
+  </si>
+  <si>
+    <t>将倍率 {0} 加到所有{cat}上</t>
   </si>
   <si>
     <t>CategoryCount</t>
@@ -1425,7 +1412,7 @@
     <t>tiervals:10|20|40</t>
   </si>
   <si>
-    <t>蛋糕数量达 {tiers} 时，欢乐蛋糕 +{tiervals} 层。</t>
+    <t>蛋糕数量达 {tiers} 时，欢乐蛋糕 +{tiervals} 层</t>
   </si>
   <si>
     <t>SkillTypeCount</t>
@@ -1437,7 +1424,7 @@
     <t>tiervals:1.5|2.5|5;skilltype:TransferSkills</t>
   </si>
   <si>
-    <t>带甜蜜传递的食物达 {tiers} 种时，此类食物倍率 ×{tiervals}。</t>
+    <t>带甜蜜传递的食物达 {tiers} 种时，此类食物倍率 ×{tiervals}</t>
   </si>
   <si>
     <t>TriggerSweetTransfer</t>
@@ -1446,13 +1433,13 @@
     <t>axis:rowcol;skilltype:TransferSkills</t>
   </si>
   <si>
-    <t>同行同列带甜蜜传递的食物，各执行一次它们的甜蜜传递。</t>
-  </si>
-  <si>
-    <t>{cscope}每有 1 个技能，{ascope}倍率 ×{0}。</t>
-  </si>
-  <si>
-    <t>{ascope}获得 {0} 种不同的{cat}技能。</t>
+    <t>同行同列带甜蜜传递的食物，各执行一次它们的甜蜜传递</t>
+  </si>
+  <si>
+    <t>{cscope}每有 1 个技能，{ascope}倍率 ×{0}</t>
+  </si>
+  <si>
+    <t>{ascope}获得 {0} 种不同的{cat}技能</t>
   </si>
   <si>
     <t>菜品</t>
@@ -1983,7 +1970,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -3229,7 +3216,7 @@
       </c>
       <c r="O4" s="1" t="str">
         <f>IFERROR(VLOOKUP(M4,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>处在棋盘边缘时，{ascope}倍率 {0}。</v>
+        <v>处在棋盘边缘时，{ascope}倍率 {0}</v>
       </c>
       <c r="P4" s="1" t="str">
         <f>IFERROR(VLOOKUP(N4,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3277,7 +3264,7 @@
       </c>
       <c r="O5" s="1" t="str">
         <f>IFERROR(VLOOKUP(M5,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}分数 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}分数 {0}</v>
       </c>
       <c r="P5" s="1" t="str">
         <f>IFERROR(VLOOKUP(N5,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3322,7 +3309,7 @@
       </c>
       <c r="O6" s="1" t="str">
         <f>IFERROR(VLOOKUP(M6,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 个空格，{ascope}分数 {0}。</v>
+        <v>{cscope}每有 1 个空格，{ascope}分数 {0}</v>
       </c>
       <c r="P6" s="1" t="str">
         <f>IFERROR(VLOOKUP(N6,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3367,7 +3354,7 @@
       </c>
       <c r="O7" s="1" t="str">
         <f>IFERROR(VLOOKUP(M7,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层。</v>
+        <v>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P7" s="1" t="str">
         <f>IFERROR(VLOOKUP(N7,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3410,7 +3397,7 @@
       </c>
       <c r="O8" s="1" t="str">
         <f>IFERROR(VLOOKUP(M8,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>结算时，{ascope}分数永久 {0}。</v>
+        <v>结算时，{ascope}分数永久 {0}</v>
       </c>
       <c r="P8" s="1" t="str">
         <f>IFERROR(VLOOKUP(N8,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3453,7 +3440,7 @@
       </c>
       <c r="O9" s="1" t="str">
         <f>IFERROR(VLOOKUP(M9,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</v>
       </c>
       <c r="P9" s="1" t="str">
         <f>IFERROR(VLOOKUP(N9,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3496,7 +3483,7 @@
       </c>
       <c r="O10" s="1" t="str">
         <f>IFERROR(VLOOKUP(M10,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}分数 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}分数 {0}</v>
       </c>
       <c r="P10" s="1" t="str">
         <f>IFERROR(VLOOKUP(N10,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3539,7 +3526,7 @@
       </c>
       <c r="O11" s="1" t="str">
         <f>IFERROR(VLOOKUP(M11,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>结算每有1个技能，{ascope}分数永久 {0}。</v>
+        <v>结算每有1个技能，{ascope}分数永久 {0}</v>
       </c>
       <c r="P11" s="1" t="str">
         <f>IFERROR(VLOOKUP(N11,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3582,7 +3569,7 @@
       </c>
       <c r="O12" s="1" t="str">
         <f>IFERROR(VLOOKUP(M12,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</v>
       </c>
       <c r="P12" s="1" t="str">
         <f>IFERROR(VLOOKUP(N12,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3625,7 +3612,7 @@
       </c>
       <c r="O13" s="1" t="str">
         <f>IFERROR(VLOOKUP(M13,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>欢乐蛋糕 {0} 层。</v>
+        <v>欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P13" s="1" t="str">
         <f>IFERROR(VLOOKUP(N13,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3671,7 +3658,7 @@
       </c>
       <c r="O14" s="1" t="str">
         <f>IFERROR(VLOOKUP(M14,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>技能额外结算 {0} 次。</v>
+        <v>技能额外结算 {0} 次</v>
       </c>
       <c r="P14" s="1" t="str">
         <f>IFERROR(VLOOKUP(N14,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3714,7 +3701,7 @@
       </c>
       <c r="O15" s="1" t="str">
         <f>IFERROR(VLOOKUP(M15,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>若{cscope}被填满，获得 {0} 金币。</v>
+        <v>若{cscope}被填满，获得 {0} 金币</v>
       </c>
       <c r="P15" s="1" t="str">
         <f>IFERROR(VLOOKUP(N15,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3757,7 +3744,7 @@
       </c>
       <c r="O16" s="1" t="str">
         <f>IFERROR(VLOOKUP(M16,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>若{cscope}被填满，欢乐蛋糕 {0} 层。</v>
+        <v>若{cscope}被填满，欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P16" s="1" t="str">
         <f>IFERROR(VLOOKUP(N16,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3803,11 +3790,11 @@
       </c>
       <c r="O17" s="1" t="str">
         <f>IFERROR(VLOOKUP(M17,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</v>
       </c>
       <c r="P17" s="1" t="str">
         <f>IFERROR(VLOOKUP(N17,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="18" spans="2:16">
@@ -3849,11 +3836,11 @@
       </c>
       <c r="O18" s="1" t="str">
         <f>IFERROR(VLOOKUP(M18,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>欢乐蛋糕 {0} 层。</v>
+        <v>欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P18" s="1" t="str">
         <f>IFERROR(VLOOKUP(N18,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>复制本菜品至空格中。</v>
+        <v>复制本菜品至空格中</v>
       </c>
     </row>
     <row r="19" spans="9:16">
@@ -3918,7 +3905,7 @@
       </c>
       <c r="O20" s="1" t="str">
         <f>IFERROR(VLOOKUP(M20,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}。</v>
+        <v>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}</v>
       </c>
       <c r="P20" s="1" t="str">
         <f>IFERROR(VLOOKUP(N20,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -3966,7 +3953,7 @@
       </c>
       <c r="O21" s="1" t="str">
         <f>IFERROR(VLOOKUP(M21,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}</v>
       </c>
       <c r="P21" s="1" t="str">
         <f>IFERROR(VLOOKUP(N21,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4014,11 +4001,11 @@
       </c>
       <c r="O22" s="1" t="str">
         <f>IFERROR(VLOOKUP(M22,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>复制{ascope}食物的 {0} 个技能。</v>
+        <v>复制{ascope}食物的 {0} 个技能</v>
       </c>
       <c r="P22" s="1" t="str">
         <f>IFERROR(VLOOKUP(N22,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>每有 1 个技能，欢乐蛋糕 {0} 层。</v>
+        <v>每有 1 个技能，欢乐蛋糕 {0} 层</v>
       </c>
     </row>
     <row r="23" spans="2:16">
@@ -4062,11 +4049,11 @@
       </c>
       <c r="O23" s="1" t="str">
         <f>IFERROR(VLOOKUP(M23,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}</v>
       </c>
       <c r="P23" s="1" t="str">
         <f>IFERROR(VLOOKUP(N23,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>技能额外结算 {0} 次。</v>
+        <v>技能额外结算 {0} 次</v>
       </c>
     </row>
     <row r="24" spans="9:16">
@@ -4131,7 +4118,7 @@
       </c>
       <c r="O25" s="1" t="str">
         <f>IFERROR(VLOOKUP(M25,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}分数永久 {0}。</v>
+        <v>{ascope}分数永久 {0}</v>
       </c>
       <c r="P25" s="1" t="str">
         <f>IFERROR(VLOOKUP(N25,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4200,7 +4187,7 @@
       </c>
       <c r="O27" s="1" t="str">
         <f>IFERROR(VLOOKUP(M27,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>技能额外结算 {0} 次。</v>
+        <v>技能额外结算 {0} 次</v>
       </c>
       <c r="P27" s="1" t="str">
         <f>IFERROR(VLOOKUP(N27,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4267,11 +4254,11 @@
       </c>
       <c r="O29" s="1" t="str">
         <f>IFERROR(VLOOKUP(M29,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</v>
       </c>
       <c r="P29" s="1" t="str">
         <f>IFERROR(VLOOKUP(N29,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="30" spans="2:16">
@@ -4313,7 +4300,7 @@
       </c>
       <c r="O30" s="1" t="str">
         <f>IFERROR(VLOOKUP(M30,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
       <c r="P30" s="1" t="str">
         <f>IFERROR(VLOOKUP(N30,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4359,11 +4346,11 @@
       </c>
       <c r="O31" s="1" t="str">
         <f>IFERROR(VLOOKUP(M31,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>消耗 {0} 层欢乐蛋糕。</v>
+        <v>消耗 {0} 层欢乐蛋糕</v>
       </c>
       <c r="P31" s="1" t="str">
         <f>IFERROR(VLOOKUP(N31,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
     </row>
     <row r="32" spans="9:16">
@@ -4449,7 +4436,7 @@
       </c>
       <c r="O34" s="1" t="str">
         <f>IFERROR(VLOOKUP(M34,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
       <c r="P34" s="1" t="str">
         <f>IFERROR(VLOOKUP(N34,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4534,7 +4521,7 @@
       </c>
       <c r="O37" s="1" t="str">
         <f>IFERROR(VLOOKUP(M37,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>欢乐蛋糕 ×{0} 层，至少 +{floor} 层。</v>
+        <v>欢乐蛋糕 ×{0} 层，至少 +{floor} 层</v>
       </c>
       <c r="P37" s="1" t="str">
         <f>IFERROR(VLOOKUP(N37,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4600,7 +4587,7 @@
       </c>
       <c r="O39" s="1" t="str">
         <f>IFERROR(VLOOKUP(M39,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}。</v>
+        <v>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}</v>
       </c>
       <c r="P39" s="1" t="str">
         <f>IFERROR(VLOOKUP(N39,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -4669,11 +4656,11 @@
       </c>
       <c r="O41" s="1" t="str">
         <f>IFERROR(VLOOKUP(M41,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>复制{ascope}食物的 {0} 个技能。</v>
+        <v>复制{ascope}食物的 {0} 个技能</v>
       </c>
       <c r="P41" s="1" t="str">
         <f>IFERROR(VLOOKUP(N41,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="42" spans="9:16">
@@ -4738,11 +4725,11 @@
       </c>
       <c r="O43" s="1" t="str">
         <f>IFERROR(VLOOKUP(M43,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}</v>
       </c>
       <c r="P43" s="1" t="str">
         <f>IFERROR(VLOOKUP(N43,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>若{cscope}被填满，{ascope}额外视为 {0} 个食物。</v>
+        <v>若{cscope}被填满，{ascope}额外视为 {0} 个食物</v>
       </c>
     </row>
     <row r="44" spans="9:16">
@@ -4807,11 +4794,11 @@
       </c>
       <c r="O45" s="1" t="str">
         <f>IFERROR(VLOOKUP(M45,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}额外视为 {0} 个食物。</v>
+        <v>{ascope}额外视为 {0} 个食物</v>
       </c>
       <c r="P45" s="1" t="str">
         <f>IFERROR(VLOOKUP(N45,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
     </row>
     <row r="46" spans="9:16">
@@ -4876,11 +4863,11 @@
       </c>
       <c r="O47" s="1" t="str">
         <f>IFERROR(VLOOKUP(M47,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}分数永久 {0}。</v>
+        <v>{ascope}分数永久 {0}</v>
       </c>
       <c r="P47" s="1" t="str">
         <f>IFERROR(VLOOKUP(N47,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>将分数加到所有{cat}上（每个{cat} {0} 分）。</v>
+        <v>将分数加到所有{cat}上（每个{cat} {0} 分）</v>
       </c>
     </row>
     <row r="48" spans="9:16">
@@ -4943,11 +4930,11 @@
       </c>
       <c r="O49" s="1" t="str">
         <f>IFERROR(VLOOKUP(M49,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>欢乐蛋糕 {0} 层。</v>
+        <v>欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P49" s="1" t="str">
         <f>IFERROR(VLOOKUP(N49,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
     </row>
     <row r="50" spans="9:16">
@@ -5012,7 +4999,7 @@
       </c>
       <c r="O51" s="1" t="str">
         <f>IFERROR(VLOOKUP(M51,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 个技能，{ascope}倍率 {0}。</v>
+        <v>{cscope}每有 1 个技能，{ascope}倍率 {0}</v>
       </c>
       <c r="P51" s="1" t="str">
         <f>IFERROR(VLOOKUP(N51,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5081,11 +5068,11 @@
       </c>
       <c r="O53" s="1" t="str">
         <f>IFERROR(VLOOKUP(M53,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}</v>
       </c>
       <c r="P53" s="1" t="str">
         <f>IFERROR(VLOOKUP(N53,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="54" spans="9:16">
@@ -5150,11 +5137,11 @@
       </c>
       <c r="O55" s="1" t="str">
         <f>IFERROR(VLOOKUP(M55,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}</v>
       </c>
       <c r="P55" s="1" t="str">
         <f>IFERROR(VLOOKUP(N55,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="56" spans="9:16">
@@ -5238,11 +5225,11 @@
       </c>
       <c r="O58" s="1" t="str">
         <f>IFERROR(VLOOKUP(M58,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>欢乐蛋糕 {0} 层。</v>
+        <v>欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P58" s="1" t="str">
         <f>IFERROR(VLOOKUP(N58,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
     </row>
     <row r="59" spans="9:16">
@@ -5328,11 +5315,11 @@
       </c>
       <c r="O61" s="1" t="str">
         <f>IFERROR(VLOOKUP(M61,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>复制{ascope}食物的 {0} 个技能。</v>
+        <v>复制{ascope}食物的 {0} 个技能</v>
       </c>
       <c r="P61" s="1" t="str">
         <f>IFERROR(VLOOKUP(N61,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="62" spans="9:16">
@@ -5397,11 +5384,11 @@
       </c>
       <c r="O63" s="1" t="str">
         <f>IFERROR(VLOOKUP(M63,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 {0}。</v>
+        <v>{ascope}倍率 {0}</v>
       </c>
       <c r="P63" s="1" t="str">
         <f>IFERROR(VLOOKUP(N63,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>将倍率 {0} 加到所有{cat}上。</v>
+        <v>将倍率 {0} 加到所有{cat}上</v>
       </c>
     </row>
     <row r="64" spans="9:16">
@@ -5463,7 +5450,7 @@
       </c>
       <c r="O65" s="1" t="str">
         <f>IFERROR(VLOOKUP(M65,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}。</v>
+        <v>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</v>
       </c>
       <c r="P65" s="1" t="str">
         <f>IFERROR(VLOOKUP(N65,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5553,11 +5540,11 @@
       </c>
       <c r="O68" s="1" t="str">
         <f>IFERROR(VLOOKUP(M68,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}</v>
       </c>
       <c r="P68" s="1" t="str">
         <f>IFERROR(VLOOKUP(N68,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>蛋糕数量达 {tiers} 时，欢乐蛋糕 +{tiervals} 层。</v>
+        <v>蛋糕数量达 {tiers} 时，欢乐蛋糕 +{tiervals} 层</v>
       </c>
     </row>
     <row r="69" spans="9:16">
@@ -5640,7 +5627,7 @@
       </c>
       <c r="O71" s="1" t="str">
         <f>IFERROR(VLOOKUP(M71,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>带甜蜜传递的食物达 {tiers} 种时，此类食物倍率 ×{tiervals}。</v>
+        <v>带甜蜜传递的食物达 {tiers} 种时，此类食物倍率 ×{tiervals}</v>
       </c>
       <c r="P71" s="1" t="str">
         <f>IFERROR(VLOOKUP(N71,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5704,7 +5691,7 @@
       </c>
       <c r="O73" s="1" t="str">
         <f>IFERROR(VLOOKUP(M73,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层。</v>
+        <v>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层</v>
       </c>
       <c r="P73" s="1" t="str">
         <f>IFERROR(VLOOKUP(N73,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5773,11 +5760,11 @@
       </c>
       <c r="O75" s="1" t="str">
         <f>IFERROR(VLOOKUP(M75,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}</v>
       </c>
       <c r="P75" s="1" t="str">
         <f>IFERROR(VLOOKUP(N75,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}视为 {countas} 个食物。</v>
+        <v>{ascope}视为 {countas} 个食物</v>
       </c>
     </row>
     <row r="76" spans="9:16">
@@ -5842,7 +5829,7 @@
       </c>
       <c r="O77" s="1" t="str">
         <f>IFERROR(VLOOKUP(M77,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}倍率 ×{0}。</v>
+        <v>{ascope}倍率 ×{0}</v>
       </c>
       <c r="P77" s="1" t="str">
         <f>IFERROR(VLOOKUP(N77,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -5929,7 +5916,7 @@
       </c>
       <c r="O80" s="1" t="str">
         <f>IFERROR(VLOOKUP(M80,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>同行同列带甜蜜传递的食物，各执行一次它们的甜蜜传递。</v>
+        <v>同行同列带甜蜜传递的食物，各执行一次它们的甜蜜传递</v>
       </c>
       <c r="P80" s="1" t="str">
         <f>IFERROR(VLOOKUP(N80,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -6061,7 +6048,7 @@
       </c>
       <c r="O85" s="1" t="str">
         <f>IFERROR(VLOOKUP(M85,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{cscope}每有 1 个技能，{ascope}倍率 ×{0}。</v>
+        <v>{cscope}每有 1 个技能，{ascope}倍率 ×{0}</v>
       </c>
       <c r="P85" s="1" t="str">
         <f>IFERROR(VLOOKUP(N85,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -6148,7 +6135,7 @@
       </c>
       <c r="O88" s="1" t="str">
         <f>IFERROR(VLOOKUP(M88,sub_skill!$B:$R,15,FALSE),"")</f>
-        <v>{ascope}获得 {0} 种不同的{cat}技能。</v>
+        <v>{ascope}获得 {0} 种不同的{cat}技能</v>
       </c>
       <c r="P88" s="1" t="str">
         <f>IFERROR(VLOOKUP(N88,sub_skill!$B:$R,15,FALSE),"")</f>
@@ -9699,7 +9686,6 @@
       <c r="G31" t="s">
         <v>395</v>
       </c>
-      <c r="H31"/>
       <c r="I31" t="s">
         <v>398</v>
       </c>
@@ -9744,7 +9730,6 @@
       <c r="G32" t="s">
         <v>395</v>
       </c>
-      <c r="H32"/>
       <c r="I32" t="s">
         <v>347</v>
       </c>
@@ -9789,7 +9774,6 @@
       <c r="G33" t="s">
         <v>395</v>
       </c>
-      <c r="H33"/>
       <c r="I33" t="s">
         <v>425</v>
       </c>
@@ -9834,7 +9818,6 @@
       <c r="G34" t="s">
         <v>395</v>
       </c>
-      <c r="H34"/>
       <c r="I34" t="s">
         <v>347</v>
       </c>
@@ -9879,7 +9862,6 @@
       <c r="G35" t="s">
         <v>395</v>
       </c>
-      <c r="H35"/>
       <c r="I35" t="s">
         <v>398</v>
       </c>
@@ -9924,7 +9906,6 @@
       <c r="G36" t="s">
         <v>395</v>
       </c>
-      <c r="H36"/>
       <c r="I36" t="s">
         <v>443</v>
       </c>
@@ -11517,7 +11498,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C69" etc:filterBottomFollowUsedRange="0">
+  <autoFilter ref="C1:C69">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -3763,7 +3763,6 @@
           <t>cookie</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
         <v>120</v>
       </c>
@@ -3792,7 +3791,6 @@
           <t>macaron</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
         <v>120</v>
       </c>
@@ -3821,7 +3819,6 @@
           <t>pudding</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
         <v>120</v>
       </c>
@@ -3850,7 +3847,6 @@
           <t>puff</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
         <v>120</v>
       </c>
@@ -3879,7 +3875,6 @@
           <t>eggtart</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
         <v>120</v>
       </c>
@@ -3908,7 +3903,6 @@
           <t>mochi</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
         <v>90</v>
       </c>
@@ -3937,7 +3931,6 @@
           <t>daifuku</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
         <v>120</v>
       </c>
@@ -3966,7 +3959,6 @@
           <t>choco_candy</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
         <v>90</v>
       </c>
@@ -3995,7 +3987,6 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
         <v>120</v>
       </c>
@@ -4024,7 +4015,6 @@
           <t>cream_cell</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
         <v>120</v>
       </c>
@@ -4053,7 +4043,6 @@
           <t>sugarbean</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
         <v>60</v>
       </c>
@@ -4082,7 +4071,6 @@
           <t>gold_choco</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
         <v>90</v>
       </c>
@@ -4111,7 +4099,6 @@
           <t>milk_slice</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
         <v>90</v>
       </c>
@@ -4140,7 +4127,6 @@
           <t>sundae</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="n">
         <v>90</v>
       </c>
@@ -4169,7 +4155,6 @@
           <t>cone</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
         <v>90</v>
       </c>
@@ -4198,7 +4183,6 @@
           <t>lollipop</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>90</v>
       </c>
@@ -4227,7 +4211,6 @@
           <t>gummy</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
         <v>90</v>
       </c>
@@ -4256,7 +4239,6 @@
           <t>cupcake</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
         <v>60</v>
       </c>
@@ -4285,7 +4267,6 @@
           <t>mousse</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
         <v>60</v>
       </c>
@@ -4314,7 +4295,6 @@
           <t>toffee</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
         <v>90</v>
       </c>
@@ -4343,7 +4323,6 @@
           <t>nougat</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
         <v>90</v>
       </c>
@@ -4372,7 +4351,6 @@
           <t>eggroll</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
         <v>90</v>
       </c>
@@ -4401,7 +4379,6 @@
           <t>choco_bar</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
         <v>90</v>
       </c>
@@ -4430,7 +4407,6 @@
           <t>eclair</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
         <v>90</v>
       </c>
@@ -4459,7 +4435,6 @@
           <t>tanghulu</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
         <v>90</v>
       </c>
@@ -4488,7 +4463,6 @@
           <t>souffle</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="n">
         <v>90</v>
       </c>
@@ -4517,7 +4491,6 @@
           <t>taosu</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="n">
         <v>60</v>
       </c>
@@ -4546,7 +4519,6 @@
           <t>mooncake</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="n">
         <v>60</v>
       </c>
@@ -4575,7 +4547,6 @@
           <t>waffle</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="n">
         <v>60</v>
       </c>
@@ -4604,7 +4575,6 @@
           <t>dorayaki</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="n">
         <v>60</v>
       </c>
@@ -4633,7 +4603,6 @@
           <t>cream_cake</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="n">
         <v>60</v>
       </c>
@@ -4662,7 +4631,6 @@
           <t>donut</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
         <v>60</v>
       </c>
@@ -4691,7 +4659,6 @@
           <t>pengtang</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="n">
         <v>90</v>
       </c>
@@ -4720,7 +4687,6 @@
           <t>parfait</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="n">
         <v>60</v>
       </c>
@@ -4749,7 +4715,6 @@
           <t>sundae_big</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
         <v>60</v>
       </c>
@@ -4778,7 +4743,6 @@
           <t>swiss_roll</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
         <v>90</v>
       </c>
@@ -4807,7 +4771,6 @@
           <t>mango_sago</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
         <v>60</v>
       </c>
@@ -4836,7 +4799,6 @@
           <t>chiffon</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
         <v>60</v>
       </c>
@@ -4865,7 +4827,6 @@
           <t>apple_pie</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
         <v>90</v>
       </c>
@@ -4894,7 +4855,6 @@
           <t>fruit_cake</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
         <v>90</v>
       </c>
@@ -4923,7 +4883,6 @@
           <t>chocolate</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
         <v>60</v>
       </c>
@@ -4952,7 +4911,6 @@
           <t>croissant</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
         <v>90</v>
       </c>
@@ -4981,7 +4939,6 @@
           <t>palmier</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
         <v>90</v>
       </c>
@@ -5010,7 +4967,6 @@
           <t>candycane</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
         <v>60</v>
       </c>
@@ -5039,7 +4995,6 @@
           <t>big_lollipop</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
         <v>60</v>
       </c>
@@ -5068,7 +5023,6 @@
           <t>marshmallow</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
         <v>60</v>
       </c>
@@ -5097,7 +5051,6 @@
           <t>double_cake</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
         <v>60</v>
       </c>
@@ -5207,7 +5160,6 @@
           <t>sk_cookie</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>ss_edge_multflat_v3</t>
@@ -5237,7 +5189,6 @@
           <t>sk_pudding</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>ss_flat_per_empty_adj_vm2</t>
@@ -5250,7 +5201,6 @@
           <t>sk_puff</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>ss_layer_per_dish_adj_v2</t>
@@ -5263,7 +5213,6 @@
           <t>sk_eggtart</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>ss_flat_per_run_v6</t>
@@ -5276,7 +5225,6 @@
           <t>sk_mochi</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>ss_multflat_per_dish_col_v1</t>
@@ -5289,7 +5237,6 @@
           <t>sk_daifuku</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>ss_flat_per_dish_row_v10</t>
@@ -5302,7 +5249,6 @@
           <t>sk_choco_candy</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>ss_permflat_per_tag_v5</t>
@@ -5315,7 +5261,6 @@
           <t>sk_jelly</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>ss_multflat_per_dish_all_adj_v0p2</t>
@@ -5328,7 +5273,6 @@
           <t>sk_cream_cell</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>ss_layer_add_v5</t>
@@ -5358,7 +5302,6 @@
           <t>sk_gold_choco</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>ss_grant_gold_filled_adj_v30</t>
@@ -5371,7 +5314,6 @@
           <t>sk_milk_slice</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>ss_layer_filled_row_v10</t>
@@ -5384,7 +5326,6 @@
           <t>sk_sundae</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>ss_multflat_per_dish_row_v2|ss_count_as_base_v1</t>
@@ -5397,7 +5338,6 @@
           <t>sk_cone</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>ss_layer_add_v10|ss_temp_copy_v1</t>
@@ -5444,7 +5384,6 @@
           <t>sk_cupcake</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>ss_copy_skill_adj_v1|ss_layer_per_tag_v6</t>
@@ -5457,7 +5396,6 @@
           <t>sk_mousse</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>ss_mult_v1p5|ss_extra_settle_v1</t>
@@ -5504,7 +5442,6 @@
           <t>sk_eggroll</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>ss_multflat_per_dish_all_v0p2|ss_count_as_base_v3</t>
@@ -5534,7 +5471,6 @@
           <t>sk_eclair</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>ss_consume_layer_v10|ss_multflat_v5</t>
@@ -5564,7 +5500,6 @@
           <t>sk_souffle</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>ss_layer_mult_v1p5</t>
@@ -5577,7 +5512,6 @@
           <t>sk_taosu</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>ss_mult_tier_dishcount_row_row</t>
@@ -5590,7 +5524,6 @@
           <t>sk_mooncake</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>ss_copy_skill_adj_v1|ss_count_as_base_v4</t>
@@ -5603,7 +5536,6 @@
           <t>sk_waffle</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>ss_mult_v3|ss_count_as_filled_row_v9</t>
@@ -5616,7 +5548,6 @@
           <t>sk_dorayaki</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>ss_count_as_col_v2|ss_multflat_v4</t>
@@ -5629,7 +5560,6 @@
           <t>sk_cream_cake</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>ss_perm_flat_v10|ss_flat_category_cat_v10</t>
@@ -5642,7 +5572,6 @@
           <t>sk_donut</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>ss_layer_add_v15|ss_multflat_v5</t>
@@ -5672,7 +5601,6 @@
           <t>sk_parfait</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
           <t>ss_mult_per_dish_adj_v1p2|ss_count_as_base_v9</t>
@@ -5685,7 +5613,6 @@
           <t>sk_sundae_big</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>ss_mult_col_v2|ss_count_as_base_v4</t>
@@ -5698,7 +5625,6 @@
           <t>sk_swiss_roll</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>ss_layer_add_v20|ss_multflat_all_v0p5</t>
@@ -5711,7 +5637,6 @@
           <t>sk_mango_sago</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
           <t>ss_copy_skill_adj_v2|ss_count_as_base_v7</t>
@@ -5724,7 +5649,6 @@
           <t>sk_chiffon</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
           <t>ss_multflat_v5|ss_multflat_category_cat_v5</t>
@@ -5737,7 +5661,6 @@
           <t>sk_apple_pie</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>ss_multflat_per_dish_row_adj_v0p3</t>
@@ -5750,7 +5673,6 @@
           <t>sk_fruit_cake</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>ss_mult_v2|ss_layer_tier_all</t>
@@ -5763,7 +5685,6 @@
           <t>sk_chocolate</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
           <t>ss_mult_tier_skilltype_all_all</t>
@@ -5776,7 +5697,6 @@
           <t>sk_croissant</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>ss_layer_per_dish_adj_v2_2</t>
@@ -5789,7 +5709,6 @@
           <t>sk_palmier</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>ss_mult_adj_v1p5|ss_count_as_base_v3</t>
@@ -5853,7 +5772,6 @@
           <t>sk_double_cake</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>ss_copy_cat_skill_v3</t>
@@ -5871,7 +5789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
@@ -6142,6 +6060,87 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t_numb</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>麻</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>上菜时逆时针旋转 90 度（可叠加）。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Rotate</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t_sour</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>酸</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>整体结算末尾，若未上菜，则场上同菜谱食物倍率 ×1.5。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SourRecipeMult</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t_salty</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>咸</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>整体结算末尾，若未上菜，则场上每个同菜谱食物 +2 金币。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SaltyRecipeGold</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6687,6 @@
           <t>Gate</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -6705,7 +6703,6 @@
       <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>false</t>
@@ -6753,7 +6750,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>AddFlat</t>
@@ -6770,7 +6766,6 @@
       <c r="L5" t="n">
         <v>8</v>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>false</t>
@@ -6818,7 +6813,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -6835,7 +6829,6 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>false</t>
@@ -6883,7 +6876,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>AddFlat</t>
@@ -6900,7 +6892,6 @@
       <c r="L7" t="n">
         <v>-2</v>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>false</t>
@@ -6948,7 +6939,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -6965,7 +6955,6 @@
       <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>false</t>
@@ -7013,7 +7002,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>PermanentAddFlat</t>
@@ -7030,7 +7018,6 @@
       <c r="L9" t="n">
         <v>6</v>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>false</t>
@@ -7078,7 +7065,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -7095,7 +7081,6 @@
       <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>false</t>
@@ -7143,7 +7128,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>AddFlat</t>
@@ -7160,7 +7144,6 @@
       <c r="L11" t="n">
         <v>10</v>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>false</t>
@@ -7208,7 +7191,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>PermanentAddFlat</t>
@@ -7225,7 +7207,6 @@
       <c r="L12" t="n">
         <v>5</v>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>false</t>
@@ -7273,7 +7254,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -7290,7 +7270,6 @@
       <c r="L13" t="n">
         <v>0.2</v>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>false</t>
@@ -7338,7 +7317,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -7355,7 +7333,6 @@
       <c r="L14" t="n">
         <v>5</v>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>false</t>
@@ -7473,7 +7450,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -7490,7 +7466,6 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>false</t>
@@ -7538,7 +7513,6 @@
           <t>Gate</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>GrantGold</t>
@@ -7555,7 +7529,6 @@
       <c r="L17" t="n">
         <v>30</v>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>false</t>
@@ -7608,7 +7581,6 @@
           <t>Gate</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -7625,7 +7597,6 @@
       <c r="L18" t="n">
         <v>10</v>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>false</t>
@@ -7673,7 +7644,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -7690,7 +7660,6 @@
       <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>false</t>
@@ -7738,7 +7707,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>AddCountAs</t>
@@ -7755,7 +7723,6 @@
       <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>true</t>
@@ -7803,7 +7770,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -7820,7 +7786,6 @@
       <c r="L21" t="n">
         <v>10</v>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>false</t>
@@ -7959,7 +7924,6 @@
       <c r="L23" t="n">
         <v>1.5</v>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>false</t>
@@ -8007,7 +7971,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -8024,7 +7987,6 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>false</t>
@@ -8072,7 +8034,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -8089,7 +8050,6 @@
       <c r="L25" t="n">
         <v>1.2</v>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>false</t>
@@ -8137,7 +8097,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -8154,7 +8113,6 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>false</t>
@@ -8202,7 +8160,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>CopySkill</t>
@@ -8219,7 +8176,6 @@
       <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>false</t>
@@ -8267,7 +8223,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -8284,7 +8239,6 @@
       <c r="L28" t="n">
         <v>6</v>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>false</t>
@@ -8332,7 +8286,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -8349,7 +8302,6 @@
       <c r="L29" t="n">
         <v>1.5</v>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>false</t>
@@ -8397,7 +8349,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>PermanentAddFlat</t>
@@ -8414,7 +8365,6 @@
       <c r="L30" t="n">
         <v>10</v>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>false</t>
@@ -8478,7 +8428,6 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>false</t>
@@ -8542,7 +8491,6 @@
       <c r="L32" t="n">
         <v>0.2</v>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>false</t>
@@ -8606,7 +8554,6 @@
       <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>true</t>
@@ -8670,7 +8617,6 @@
       <c r="L34" t="n">
         <v>5</v>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>false</t>
@@ -8734,7 +8680,6 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>false</t>
@@ -8798,7 +8743,6 @@
       <c r="L36" t="n">
         <v>10</v>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>false</t>
@@ -8851,7 +8795,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -8868,7 +8811,6 @@
       <c r="L37" t="n">
         <v>5</v>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>false</t>
@@ -8921,7 +8863,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -8938,7 +8879,6 @@
       <c r="L38" t="n">
         <v>3</v>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>false</t>
@@ -8991,7 +8931,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -9008,7 +8947,6 @@
       <c r="L39" t="n">
         <v>0</v>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>false</t>
@@ -9061,7 +8999,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -9208,7 +9145,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>AddCountAs</t>
@@ -9225,7 +9161,6 @@
       <c r="L42" t="n">
         <v>4</v>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>true</t>
@@ -9273,7 +9208,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -9290,7 +9224,6 @@
       <c r="L43" t="n">
         <v>3</v>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>false</t>
@@ -9338,7 +9271,6 @@
           <t>Gate</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>AddCountAs</t>
@@ -9355,7 +9287,6 @@
       <c r="L44" t="n">
         <v>9</v>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>true</t>
@@ -9403,7 +9334,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>AddCountAs</t>
@@ -9420,7 +9350,6 @@
       <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>true</t>
@@ -9468,7 +9397,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -9485,7 +9413,6 @@
       <c r="L46" t="n">
         <v>4</v>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>false</t>
@@ -9533,7 +9460,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>AddFlat</t>
@@ -9602,7 +9528,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -9619,7 +9544,6 @@
       <c r="L48" t="n">
         <v>15</v>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>false</t>
@@ -9667,7 +9591,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -9684,7 +9607,6 @@
       <c r="L49" t="n">
         <v>5</v>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>false</t>
@@ -9732,7 +9654,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -9749,7 +9670,6 @@
       <c r="L50" t="n">
         <v>0</v>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>false</t>
@@ -9797,7 +9717,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>AddCountAs</t>
@@ -9814,7 +9733,6 @@
       <c r="L51" t="n">
         <v>9</v>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>true</t>
@@ -9862,7 +9780,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -9879,7 +9796,6 @@
       <c r="L52" t="n">
         <v>2</v>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>false</t>
@@ -9927,7 +9843,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -9944,7 +9859,6 @@
       <c r="L53" t="n">
         <v>20</v>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>false</t>
@@ -9992,7 +9906,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -10009,7 +9922,6 @@
       <c r="L54" t="n">
         <v>0.5</v>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>false</t>
@@ -10057,7 +9969,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>CopySkill</t>
@@ -10074,7 +9985,6 @@
       <c r="L55" t="n">
         <v>2</v>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>false</t>
@@ -10122,7 +10032,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>AddCountAs</t>
@@ -10139,7 +10048,6 @@
       <c r="L56" t="n">
         <v>7</v>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>true</t>
@@ -10187,7 +10095,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -10256,7 +10163,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>AddMultFlat</t>
@@ -10273,7 +10179,6 @@
       <c r="L58" t="n">
         <v>0.3</v>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>false</t>
@@ -10321,7 +10226,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -10338,7 +10242,6 @@
       <c r="L59" t="n">
         <v>2</v>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>false</t>
@@ -10532,7 +10435,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>AddLayer</t>
@@ -10549,7 +10451,6 @@
       <c r="L62" t="n">
         <v>2</v>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>false</t>
@@ -10597,7 +10498,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -10614,7 +10514,6 @@
       <c r="L63" t="n">
         <v>1.5</v>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>false</t>
@@ -10662,7 +10561,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -10679,7 +10577,6 @@
       <c r="L64" t="n">
         <v>1.4</v>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>false</t>
@@ -10727,7 +10624,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -10744,7 +10640,6 @@
       <c r="L65" t="n">
         <v>0</v>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>false</t>
@@ -10792,7 +10687,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>TriggerSweetTransfer</t>
@@ -10861,7 +10755,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>AddMult</t>
@@ -10878,7 +10771,6 @@
       <c r="L67" t="n">
         <v>1.5</v>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>false</t>
@@ -10926,7 +10818,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>TransferSkills</t>
@@ -10943,7 +10834,6 @@
       <c r="L68" t="n">
         <v>0</v>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>false</t>
@@ -10991,7 +10881,6 @@
           <t>Per</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>CopySkill</t>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -5909,7 +5909,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TagEffectType</t>
+          <t>FlavorEffectType</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="5"/>
+    <workbookView windowHeight="15200" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2035" uniqueCount="674">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="673">
   <si>
     <t>##var</t>
   </si>
@@ -701,7 +701,10 @@
     <t>ss_multflat_per_dish_row_v2|ss_count_as_base_v1</t>
   </si>
   <si>
-    <t>ss_layer_add_v10|ss_temp_copy_v1</t>
+    <t>ss_layer_add_v10</t>
+  </si>
+  <si>
+    <t>|ss_temp_copy_v1</t>
   </si>
   <si>
     <t>ss_shape_mult_adj_v1p5|ss_transfer_col_n2</t>
@@ -815,13 +818,13 @@
     <t>termId</t>
   </si>
   <si>
-    <t>标签ID</t>
-  </si>
-  <si>
-    <t>标签名称</t>
-  </si>
-  <si>
-    <t>标签描述</t>
+    <t>风味ID</t>
+  </si>
+  <si>
+    <t>风味名称</t>
+  </si>
+  <si>
+    <t>风味描述</t>
   </si>
   <si>
     <t>效果类型</t>
@@ -881,7 +884,8 @@
     <t>鲜</t>
   </si>
   <si>
-    <t>结算时，+5金币</t>
+    <t>结算时
++5金币</t>
   </si>
   <si>
     <t>GrantGold</t>
@@ -914,7 +918,8 @@
     <t>酸</t>
   </si>
   <si>
-    <t>结算时若未上菜，场上同菜谱食物倍率 ×1.5</t>
+    <t>结算时若未上菜
+场上同菜谱食物倍率 ×1.5</t>
   </si>
   <si>
     <t>SourRecipeMult</t>
@@ -932,7 +937,9 @@
     <t>咸</t>
   </si>
   <si>
-    <t>结算时若未上菜，场上每有一个同菜谱食物， +2 金币。</t>
+    <t>结算时若未上菜
+场上每有一个同菜谱食物
+ +2 金币</t>
   </si>
   <si>
     <t>SaltyRecipeGold</t>
@@ -1185,6 +1192,9 @@
 欢乐蛋糕 {0} 层</t>
   </si>
   <si>
+    <t>clb</t>
+  </si>
+  <si>
     <t>SameKindInRun</t>
   </si>
   <si>
@@ -1262,9 +1272,6 @@
     <t>{ascope}视为 {countas} 个食物</t>
   </si>
   <si>
-    <t>ss_layer_add_v10</t>
-  </si>
-  <si>
     <t>ss_temp_copy_v1</t>
   </si>
   <si>
@@ -1274,7 +1281,8 @@
     <t>TempCopyDish</t>
   </si>
   <si>
-    <t>复制至空格中，并立即结算此食物</t>
+    <t>复制至空格中
+并立即结算此食物</t>
   </si>
   <si>
     <t>需要立即结算</t>
@@ -1289,7 +1297,8 @@
     <t>1x1</t>
   </si>
   <si>
-    <t>{cscope}有占 1 格的食物时，{ascope}倍率 ×{0}</t>
+    <t>{cscope}有占 1 格的食物时
+{ascope}倍率 ×{0}</t>
   </si>
   <si>
     <t>ss_transfer_col_n2</t>
@@ -1301,7 +1310,8 @@
     <t>ss_mult_per_dish_adj_v1p2</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 ×{0}</t>
+    <t>{cscope}每有 1 {unit}食物
+{ascope}倍率 ×{0}</t>
   </si>
   <si>
     <t>ss_transfer_adj_n2</t>
@@ -1319,7 +1329,8 @@
     <t>ss_layer_per_tag_v6</t>
   </si>
   <si>
-    <t>每有 1 个技能，欢乐蛋糕 {0} 层</t>
+    <t>每有 1 个技能
+欢乐蛋糕 {0} 层</t>
   </si>
   <si>
     <t>ss_mult_v1p5</t>
@@ -1343,9 +1354,6 @@
     <t>All</t>
   </si>
   <si>
-    <t>{cscope}每有 1 {unit}食物，{ascope}倍率 {0}</t>
-  </si>
-  <si>
     <t>ss_count_as_base_v3</t>
   </si>
   <si>
@@ -1379,7 +1387,8 @@
     <t>multfloor:5</t>
   </si>
   <si>
-    <t>欢乐蛋糕 ×{0} 层，至少 +{floor} 层</t>
+    <t>欢乐蛋糕 ×{0} 层
+至少 +{floor} 层</t>
   </si>
   <si>
     <t>除需要严格刨除自身时，才刨除</t>
@@ -1394,7 +1403,8 @@
     <t>tiervals:1.5|2.5|5</t>
   </si>
   <si>
-    <t>{cscope}食物达 {tiers} 个时，{ascope}倍率 ×{tiervals}</t>
+    <t>{cscope}食物达 {tiers} 个时
+{ascope}倍率 ×{tiervals}</t>
   </si>
   <si>
     <t>ss_count_as_base_v4</t>
@@ -1406,7 +1416,8 @@
     <t>ss_count_as_filled_row_v9</t>
   </si>
   <si>
-    <t>若{cscope}被填满，{ascope}额外视为 {0} 个食物</t>
+    <t>若{cscope}被填满
+{ascope}额外视为 {0} 个食物</t>
   </si>
   <si>
     <t>ss_count_as_col_v2</t>
@@ -1427,7 +1438,8 @@
     <t>cat:cake</t>
   </si>
   <si>
-    <t>将分数加到所有{cat}上（每个{cat} {0} 分）</t>
+    <t>将分数加到所有{cat}上
+（每个{cat} {0} 分）</t>
   </si>
   <si>
     <t>ss_layer_add_v15</t>
@@ -1436,7 +1448,8 @@
     <t>ss_multflat_per_tag_v5</t>
   </si>
   <si>
-    <t>{cscope}每有 1 个技能，{ascope}倍率 {0}</t>
+    <t>{cscope}每有 1 个技能
+{ascope}倍率 {0}</t>
   </si>
   <si>
     <t>ss_transfer_col</t>
@@ -1481,7 +1494,8 @@
     <t>tiervals:10|20|40</t>
   </si>
   <si>
-    <t>蛋糕数量达 {tiers} 时，欢乐蛋糕 +{tiervals} 层</t>
+    <t>蛋糕数量达 {tiers} 时
+欢乐蛋糕 +{tiervals} 层</t>
   </si>
   <si>
     <t>SkillTypeCount</t>
@@ -1493,10 +1507,8 @@
     <t>tiervals:1.5|2.5|5;skilltype:TransferSkills</t>
   </si>
   <si>
-    <t>带甜蜜传递的食物达 {tiers} 种时，此类食物倍率 ×{tiervals}</t>
-  </si>
-  <si>
-    <t>{cscope}每有 1 {unit}食物，欢乐蛋糕 {0} 层</t>
+    <t>带甜蜜传递的食物达 {tiers} 种时
+此类食物倍率 ×{tiervals}</t>
   </si>
   <si>
     <t>ss_mult_adj_v1p5</t>
@@ -1514,13 +1526,15 @@
     <t>axis:rowcol;skilltype:TransferSkills</t>
   </si>
   <si>
-    <t>同行同列带甜蜜传递的食物，各执行一次它们的甜蜜传递</t>
+    <t>同行同列带甜蜜传递的食物
+各执行一次它们的甜蜜传递</t>
   </si>
   <si>
     <t>ss_mult_per_tag_v1p5</t>
   </si>
   <si>
-    <t>{cscope}每有 1 个技能，{ascope}倍率 ×{0}</t>
+    <t>{cscope}每有 1 个技能
+{ascope}倍率 ×{0}</t>
   </si>
   <si>
     <t>ss_transfer_row</t>
@@ -2742,7 +2756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2798,6 +2812,15 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3169,31 +3192,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="23" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="str">
@@ -3202,31 +3225,31 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="23" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="1" t="str">
@@ -3238,31 +3261,31 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="23" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="1" t="str">
@@ -3274,28 +3297,28 @@
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="23">
         <v>10</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="20" t="s">
+      <c r="E4" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="23">
         <v>1</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K4" s="1" t="str">
@@ -3304,28 +3327,28 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="23">
         <v>8</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="23">
         <v>1</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K5" s="1" t="str">
@@ -3334,28 +3357,28 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="23">
         <v>30</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="20" t="s">
+      <c r="E6" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="23">
         <v>1</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K6" s="1" t="str">
@@ -3364,28 +3387,28 @@
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="23">
         <v>8</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="20" t="s">
+      <c r="E7" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="23">
         <v>1</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="1" t="str">
@@ -3394,26 +3417,26 @@
       </c>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="23">
         <v>6</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="20" t="s">
+      <c r="E8" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23">
         <v>1</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="1" t="str">
@@ -3422,26 +3445,26 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="23">
         <v>10</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="20" t="s">
+      <c r="E9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20">
+      <c r="G9" s="23"/>
+      <c r="H9" s="23">
         <v>1</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K9" s="1" t="str">
@@ -3450,26 +3473,26 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="23">
         <v>6</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="20" t="s">
+      <c r="E10" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20">
+      <c r="G10" s="23"/>
+      <c r="H10" s="23">
         <v>1</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K10" s="1" t="str">
@@ -3478,26 +3501,26 @@
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="23">
         <v>10</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="20" t="s">
+      <c r="E11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="20">
+      <c r="G11" s="23"/>
+      <c r="H11" s="23">
         <v>1</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K11" s="1" t="str">
@@ -3506,26 +3529,26 @@
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="23">
         <v>4</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="20" t="s">
+      <c r="E12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20">
+      <c r="G12" s="23"/>
+      <c r="H12" s="23">
         <v>1</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K12" s="1" t="str">
@@ -3534,26 +3557,26 @@
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="23">
         <v>10</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="20" t="s">
+      <c r="E13" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="20"/>
-      <c r="H13" s="20">
+      <c r="G13" s="23"/>
+      <c r="H13" s="23">
         <v>1</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K13" s="1" t="str">
@@ -3562,26 +3585,26 @@
       </c>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="23">
         <v>10</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="20" t="s">
+      <c r="E14" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20">
+      <c r="G14" s="23"/>
+      <c r="H14" s="23">
         <v>1</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K14" s="1" t="str">
@@ -3590,26 +3613,26 @@
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="23">
         <v>6</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20">
+      <c r="G15" s="23"/>
+      <c r="H15" s="23">
         <v>1</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K15" s="1" t="str">
@@ -3618,26 +3641,26 @@
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="23">
         <v>8</v>
       </c>
-      <c r="E16" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="20" t="s">
+      <c r="E16" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20">
+      <c r="G16" s="23"/>
+      <c r="H16" s="23">
         <v>1</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K16" s="1" t="str">
@@ -3646,26 +3669,26 @@
       </c>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="23">
         <v>20</v>
       </c>
-      <c r="E17" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="20" t="s">
+      <c r="E17" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20">
+      <c r="G17" s="23"/>
+      <c r="H17" s="23">
         <v>1</v>
       </c>
-      <c r="I17" s="20" t="s">
+      <c r="I17" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="1" t="str">
@@ -3674,26 +3697,26 @@
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="23">
         <v>20</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="20" t="s">
+      <c r="E18" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20">
+      <c r="G18" s="23"/>
+      <c r="H18" s="23">
         <v>1</v>
       </c>
-      <c r="I18" s="20" t="s">
+      <c r="I18" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="1" t="str">
@@ -3702,7 +3725,7 @@
       </c>
     </row>
     <row r="19" spans="9:11">
-      <c r="I19" s="20" t="s">
+      <c r="I19" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K19" s="1" t="str">
@@ -3711,28 +3734,28 @@
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="23">
         <v>10</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="20" t="s">
+      <c r="E20" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="23">
         <v>1</v>
       </c>
-      <c r="I20" s="20" t="s">
+      <c r="I20" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K20" s="1" t="str">
@@ -3741,28 +3764,28 @@
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="23">
         <v>8</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="20" t="s">
+      <c r="E21" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="23">
         <v>1</v>
       </c>
-      <c r="I21" s="20" t="s">
+      <c r="I21" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K21" s="1" t="str">
@@ -3771,28 +3794,28 @@
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="23">
         <v>14</v>
       </c>
-      <c r="E22" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="20" t="s">
+      <c r="E22" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="23">
         <v>1</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K22" s="1" t="str">
@@ -3801,28 +3824,28 @@
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="23">
         <v>16</v>
       </c>
-      <c r="E23" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="20" t="s">
+      <c r="E23" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="23">
         <v>1</v>
       </c>
-      <c r="I23" s="20" t="s">
+      <c r="I23" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K23" s="1" t="str">
@@ -3831,7 +3854,7 @@
       </c>
     </row>
     <row r="24" spans="9:11">
-      <c r="I24" s="20" t="s">
+      <c r="I24" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K24" s="1" t="str">
@@ -3840,28 +3863,28 @@
       </c>
     </row>
     <row r="25" spans="2:11">
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="20" t="s">
+      <c r="C25" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="23">
         <v>15</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="20" t="s">
+      <c r="E25" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="23">
         <v>1</v>
       </c>
-      <c r="I25" s="20" t="s">
+      <c r="I25" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K25" s="1" t="str">
@@ -3870,7 +3893,7 @@
       </c>
     </row>
     <row r="26" spans="9:11">
-      <c r="I26" s="20" t="s">
+      <c r="I26" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K26" s="1" t="str">
@@ -3879,28 +3902,28 @@
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="23">
         <v>20</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="20" t="s">
+      <c r="E27" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="G27" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="23">
         <v>1</v>
       </c>
-      <c r="I27" s="20" t="s">
+      <c r="I27" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K27" s="1" t="str">
@@ -3909,7 +3932,7 @@
       </c>
     </row>
     <row r="28" spans="9:11">
-      <c r="I28" s="20" t="s">
+      <c r="I28" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K28" s="1" t="str">
@@ -3918,26 +3941,26 @@
       </c>
     </row>
     <row r="29" spans="2:11">
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="23">
         <v>30</v>
       </c>
-      <c r="E29" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="20" t="s">
+      <c r="E29" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20">
+      <c r="G29" s="23"/>
+      <c r="H29" s="23">
         <v>1</v>
       </c>
-      <c r="I29" s="20" t="s">
+      <c r="I29" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K29" s="1" t="str">
@@ -3946,26 +3969,26 @@
       </c>
     </row>
     <row r="30" spans="2:11">
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="23">
         <v>40</v>
       </c>
-      <c r="E30" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="20" t="s">
+      <c r="E30" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20">
+      <c r="G30" s="23"/>
+      <c r="H30" s="23">
         <v>1</v>
       </c>
-      <c r="I30" s="20" t="s">
+      <c r="I30" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K30" s="1" t="str">
@@ -3974,26 +3997,26 @@
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="23">
         <v>30</v>
       </c>
-      <c r="E31" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F31" s="20" t="s">
+      <c r="E31" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20">
+      <c r="G31" s="23"/>
+      <c r="H31" s="23">
         <v>1</v>
       </c>
-      <c r="I31" s="20" t="s">
+      <c r="I31" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K31" s="1" t="str">
@@ -4002,7 +4025,7 @@
       </c>
     </row>
     <row r="32" spans="9:11">
-      <c r="I32" s="20" t="s">
+      <c r="I32" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K32" s="1" t="str">
@@ -4011,7 +4034,7 @@
       </c>
     </row>
     <row r="33" spans="9:11">
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K33" s="1" t="str">
@@ -4020,28 +4043,28 @@
       </c>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="20" t="s">
+      <c r="B34" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="23">
         <v>20</v>
       </c>
-      <c r="E34" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="20" t="s">
+      <c r="E34" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="G34" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="23">
         <v>1</v>
       </c>
-      <c r="I34" s="20" t="s">
+      <c r="I34" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K34" s="1" t="str">
@@ -4050,7 +4073,7 @@
       </c>
     </row>
     <row r="35" spans="9:11">
-      <c r="I35" s="20" t="s">
+      <c r="I35" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K35" s="1" t="str">
@@ -4059,7 +4082,7 @@
       </c>
     </row>
     <row r="36" spans="9:11">
-      <c r="I36" s="20" t="s">
+      <c r="I36" s="23" t="s">
         <v>30</v>
       </c>
       <c r="K36" s="1" t="str">
@@ -4068,26 +4091,26 @@
       </c>
     </row>
     <row r="37" spans="2:11">
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="20">
+      <c r="D37" s="23">
         <v>30</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="20" t="s">
+      <c r="E37" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20">
+      <c r="G37" s="23"/>
+      <c r="H37" s="23">
         <v>1</v>
       </c>
-      <c r="I37" s="20" t="s">
+      <c r="I37" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K37" s="1" t="str">
@@ -4096,7 +4119,7 @@
       </c>
     </row>
     <row r="38" spans="9:11">
-      <c r="I38" s="20" t="s">
+      <c r="I38" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K38" s="1" t="str">
@@ -4105,28 +4128,28 @@
       </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="20">
+      <c r="D39" s="23">
         <v>20</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="20" t="s">
+      <c r="E39" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="23">
         <v>1</v>
       </c>
-      <c r="I39" s="20" t="s">
+      <c r="I39" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K39" s="1" t="str">
@@ -4135,7 +4158,7 @@
       </c>
     </row>
     <row r="40" spans="9:11">
-      <c r="I40" s="20" t="s">
+      <c r="I40" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K40" s="1" t="str">
@@ -4144,28 +4167,28 @@
       </c>
     </row>
     <row r="41" spans="2:11">
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="20">
+      <c r="D41" s="23">
         <v>25</v>
       </c>
-      <c r="E41" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="20" t="s">
+      <c r="E41" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="G41" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H41" s="20">
+      <c r="H41" s="23">
         <v>1</v>
       </c>
-      <c r="I41" s="20" t="s">
+      <c r="I41" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K41" s="1" t="str">
@@ -4174,7 +4197,7 @@
       </c>
     </row>
     <row r="42" spans="9:11">
-      <c r="I42" s="20" t="s">
+      <c r="I42" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K42" s="1" t="str">
@@ -4183,28 +4206,28 @@
       </c>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="20">
+      <c r="D43" s="23">
         <v>20</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" s="20" t="s">
+      <c r="E43" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="G43" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H43" s="20">
+      <c r="H43" s="23">
         <v>1</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="I43" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K43" s="1" t="str">
@@ -4213,7 +4236,7 @@
       </c>
     </row>
     <row r="44" spans="9:11">
-      <c r="I44" s="20" t="s">
+      <c r="I44" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K44" s="1" t="str">
@@ -4222,28 +4245,28 @@
       </c>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D45" s="20">
+      <c r="D45" s="23">
         <v>20</v>
       </c>
-      <c r="E45" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F45" s="20" t="s">
+      <c r="E45" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="G45" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H45" s="20">
+      <c r="H45" s="23">
         <v>1</v>
       </c>
-      <c r="I45" s="20" t="s">
+      <c r="I45" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K45" s="1" t="str">
@@ -4252,7 +4275,7 @@
       </c>
     </row>
     <row r="46" spans="9:11">
-      <c r="I46" s="20" t="s">
+      <c r="I46" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K46" s="1" t="str">
@@ -4261,28 +4284,28 @@
       </c>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="20" t="s">
+      <c r="B47" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="20" t="s">
+      <c r="C47" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="D47" s="20">
+      <c r="D47" s="23">
         <v>50</v>
       </c>
-      <c r="E47" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="20" t="s">
+      <c r="E47" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="G47" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H47" s="20">
+      <c r="H47" s="23">
         <v>1</v>
       </c>
-      <c r="I47" s="20" t="s">
+      <c r="I47" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K47" s="1" t="str">
@@ -4291,7 +4314,7 @@
       </c>
     </row>
     <row r="48" spans="9:11">
-      <c r="I48" s="20" t="s">
+      <c r="I48" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K48" s="1" t="str">
@@ -4300,26 +4323,26 @@
       </c>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="D49" s="20">
+      <c r="D49" s="23">
         <v>40</v>
       </c>
-      <c r="E49" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F49" s="20" t="s">
+      <c r="E49" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20">
+      <c r="G49" s="23"/>
+      <c r="H49" s="23">
         <v>1</v>
       </c>
-      <c r="I49" s="20" t="s">
+      <c r="I49" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K49" s="1" t="str">
@@ -4328,7 +4351,7 @@
       </c>
     </row>
     <row r="50" spans="9:11">
-      <c r="I50" s="20" t="s">
+      <c r="I50" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K50" s="1" t="str">
@@ -4337,28 +4360,28 @@
       </c>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="23">
         <v>30</v>
       </c>
-      <c r="E51" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" s="20" t="s">
+      <c r="E51" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="G51" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H51" s="20">
+      <c r="H51" s="23">
         <v>1</v>
       </c>
-      <c r="I51" s="20" t="s">
+      <c r="I51" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K51" s="1" t="str">
@@ -4367,7 +4390,7 @@
       </c>
     </row>
     <row r="52" spans="9:11">
-      <c r="I52" s="20" t="s">
+      <c r="I52" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K52" s="1" t="str">
@@ -4376,28 +4399,28 @@
       </c>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="23">
         <v>50</v>
       </c>
-      <c r="E53" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F53" s="20" t="s">
+      <c r="E53" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="G53" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H53" s="20">
+      <c r="H53" s="23">
         <v>1</v>
       </c>
-      <c r="I53" s="20" t="s">
+      <c r="I53" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K53" s="1" t="str">
@@ -4406,7 +4429,7 @@
       </c>
     </row>
     <row r="54" spans="9:11">
-      <c r="I54" s="20" t="s">
+      <c r="I54" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K54" s="1" t="str">
@@ -4415,28 +4438,28 @@
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="20">
+      <c r="D55" s="23">
         <v>40</v>
       </c>
-      <c r="E55" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="20" t="s">
+      <c r="E55" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="G55" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H55" s="20">
+      <c r="H55" s="23">
         <v>1</v>
       </c>
-      <c r="I55" s="20" t="s">
+      <c r="I55" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K55" s="1" t="str">
@@ -4445,7 +4468,7 @@
       </c>
     </row>
     <row r="56" spans="9:11">
-      <c r="I56" s="20" t="s">
+      <c r="I56" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K56" s="1" t="str">
@@ -4454,7 +4477,7 @@
       </c>
     </row>
     <row r="57" spans="9:11">
-      <c r="I57" s="20" t="s">
+      <c r="I57" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K57" s="1" t="str">
@@ -4463,26 +4486,26 @@
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="20" t="s">
+      <c r="B58" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="20">
+      <c r="D58" s="23">
         <v>30</v>
       </c>
-      <c r="E58" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" s="20" t="s">
+      <c r="E58" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20">
+      <c r="G58" s="23"/>
+      <c r="H58" s="23">
         <v>1</v>
       </c>
-      <c r="I58" s="20" t="s">
+      <c r="I58" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K58" s="1" t="str">
@@ -4491,7 +4514,7 @@
       </c>
     </row>
     <row r="59" spans="9:11">
-      <c r="I59" s="20" t="s">
+      <c r="I59" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K59" s="1" t="str">
@@ -4500,7 +4523,7 @@
       </c>
     </row>
     <row r="60" spans="9:11">
-      <c r="I60" s="20" t="s">
+      <c r="I60" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K60" s="1" t="str">
@@ -4509,28 +4532,28 @@
       </c>
     </row>
     <row r="61" spans="2:11">
-      <c r="B61" s="20" t="s">
+      <c r="B61" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="20" t="s">
+      <c r="C61" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="D61" s="20">
+      <c r="D61" s="23">
         <v>20</v>
       </c>
-      <c r="E61" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" s="20" t="s">
+      <c r="E61" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="G61" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H61" s="20">
+      <c r="H61" s="23">
         <v>1</v>
       </c>
-      <c r="I61" s="20" t="s">
+      <c r="I61" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K61" s="1" t="str">
@@ -4539,7 +4562,7 @@
       </c>
     </row>
     <row r="62" spans="9:11">
-      <c r="I62" s="20" t="s">
+      <c r="I62" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K62" s="1" t="str">
@@ -4548,28 +4571,28 @@
       </c>
     </row>
     <row r="63" spans="2:11">
-      <c r="B63" s="20" t="s">
+      <c r="B63" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="C63" s="20" t="s">
+      <c r="C63" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="20">
+      <c r="D63" s="23">
         <v>30</v>
       </c>
-      <c r="E63" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" s="20" t="s">
+      <c r="E63" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="G63" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H63" s="20">
+      <c r="H63" s="23">
         <v>1</v>
       </c>
-      <c r="I63" s="20" t="s">
+      <c r="I63" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K63" s="1" t="str">
@@ -4578,7 +4601,7 @@
       </c>
     </row>
     <row r="64" spans="9:11">
-      <c r="I64" s="20" t="s">
+      <c r="I64" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K64" s="1" t="str">
@@ -4587,28 +4610,28 @@
       </c>
     </row>
     <row r="65" spans="2:11">
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="20" t="s">
+      <c r="C65" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="D65" s="20">
+      <c r="D65" s="23">
         <v>50</v>
       </c>
-      <c r="E65" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" s="20" t="s">
+      <c r="E65" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G65" s="20" t="s">
+      <c r="G65" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H65" s="20">
+      <c r="H65" s="23">
         <v>1</v>
       </c>
-      <c r="I65" s="20" t="s">
+      <c r="I65" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K65" s="1" t="str">
@@ -4617,7 +4640,7 @@
       </c>
     </row>
     <row r="66" spans="9:11">
-      <c r="I66" s="20" t="s">
+      <c r="I66" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K66" s="1" t="str">
@@ -4626,7 +4649,7 @@
       </c>
     </row>
     <row r="67" spans="9:11">
-      <c r="I67" s="20" t="s">
+      <c r="I67" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K67" s="1" t="str">
@@ -4635,28 +4658,28 @@
       </c>
     </row>
     <row r="68" spans="2:11">
-      <c r="B68" s="20" t="s">
+      <c r="B68" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="C68" s="20" t="s">
+      <c r="C68" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="D68" s="20">
+      <c r="D68" s="23">
         <v>40</v>
       </c>
-      <c r="E68" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" s="20" t="s">
+      <c r="E68" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="G68" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H68" s="20">
+      <c r="H68" s="23">
         <v>1</v>
       </c>
-      <c r="I68" s="20" t="s">
+      <c r="I68" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K68" s="1" t="str">
@@ -4665,7 +4688,7 @@
       </c>
     </row>
     <row r="69" spans="9:11">
-      <c r="I69" s="20" t="s">
+      <c r="I69" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K69" s="1" t="str">
@@ -4674,7 +4697,7 @@
       </c>
     </row>
     <row r="70" spans="9:11">
-      <c r="I70" s="20" t="s">
+      <c r="I70" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K70" s="1" t="str">
@@ -4683,28 +4706,28 @@
       </c>
     </row>
     <row r="71" spans="2:11">
-      <c r="B71" s="20" t="s">
+      <c r="B71" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="20" t="s">
+      <c r="C71" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="D71" s="20">
+      <c r="D71" s="23">
         <v>30</v>
       </c>
-      <c r="E71" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" s="20" t="s">
+      <c r="E71" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="G71" s="20" t="s">
+      <c r="G71" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H71" s="20">
+      <c r="H71" s="23">
         <v>1</v>
       </c>
-      <c r="I71" s="20" t="s">
+      <c r="I71" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K71" s="1" t="str">
@@ -4713,7 +4736,7 @@
       </c>
     </row>
     <row r="72" spans="9:11">
-      <c r="I72" s="20" t="s">
+      <c r="I72" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K72" s="1" t="str">
@@ -4722,26 +4745,26 @@
       </c>
     </row>
     <row r="73" spans="2:11">
-      <c r="B73" s="20" t="s">
+      <c r="B73" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="C73" s="20" t="s">
+      <c r="C73" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="20">
+      <c r="D73" s="23">
         <v>20</v>
       </c>
-      <c r="E73" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F73" s="20" t="s">
+      <c r="E73" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20">
+      <c r="G73" s="23"/>
+      <c r="H73" s="23">
         <v>1</v>
       </c>
-      <c r="I73" s="20" t="s">
+      <c r="I73" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K73" s="1" t="str">
@@ -4750,7 +4773,7 @@
       </c>
     </row>
     <row r="74" spans="9:11">
-      <c r="I74" s="20" t="s">
+      <c r="I74" s="23" t="s">
         <v>156</v>
       </c>
       <c r="K74" s="1" t="str">
@@ -4759,28 +4782,28 @@
       </c>
     </row>
     <row r="75" spans="2:11">
-      <c r="B75" s="20" t="s">
+      <c r="B75" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C75" s="20" t="s">
+      <c r="C75" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="D75" s="20">
+      <c r="D75" s="23">
         <v>30</v>
       </c>
-      <c r="E75" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F75" s="20" t="s">
+      <c r="E75" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G75" s="20" t="s">
+      <c r="G75" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H75" s="20">
+      <c r="H75" s="23">
         <v>1</v>
       </c>
-      <c r="I75" s="20" t="s">
+      <c r="I75" s="23" t="s">
         <v>160</v>
       </c>
       <c r="K75" s="1" t="str">
@@ -4789,7 +4812,7 @@
       </c>
     </row>
     <row r="76" spans="9:11">
-      <c r="I76" s="20" t="s">
+      <c r="I76" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K76" s="1" t="str">
@@ -4798,28 +4821,28 @@
       </c>
     </row>
     <row r="77" spans="2:11">
-      <c r="B77" s="20" t="s">
+      <c r="B77" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="20" t="s">
+      <c r="C77" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="D77" s="20">
+      <c r="D77" s="23">
         <v>40</v>
       </c>
-      <c r="E77" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77" s="20" t="s">
+      <c r="E77" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="G77" s="20" t="s">
+      <c r="G77" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H77" s="20">
+      <c r="H77" s="23">
         <v>1</v>
       </c>
-      <c r="I77" s="20" t="s">
+      <c r="I77" s="23" t="s">
         <v>70</v>
       </c>
       <c r="K77" s="1" t="str">
@@ -4828,7 +4851,7 @@
       </c>
     </row>
     <row r="78" spans="9:11">
-      <c r="I78" s="20" t="s">
+      <c r="I78" s="23" t="s">
         <v>156</v>
       </c>
       <c r="K78" s="1" t="str">
@@ -4837,7 +4860,7 @@
       </c>
     </row>
     <row r="79" spans="9:11">
-      <c r="I79" s="20" t="s">
+      <c r="I79" s="23" t="s">
         <v>156</v>
       </c>
       <c r="K79" s="1" t="str">
@@ -4846,28 +4869,28 @@
       </c>
     </row>
     <row r="80" spans="2:11">
-      <c r="B80" s="20" t="s">
+      <c r="B80" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="20" t="s">
+      <c r="C80" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D80" s="20">
+      <c r="D80" s="23">
         <v>100</v>
       </c>
-      <c r="E80" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F80" s="20" t="s">
+      <c r="E80" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="G80" s="20" t="s">
+      <c r="G80" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H80" s="20">
+      <c r="H80" s="23">
         <v>1</v>
       </c>
-      <c r="I80" s="20" t="s">
+      <c r="I80" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K80" s="1" t="str">
@@ -4876,7 +4899,7 @@
       </c>
     </row>
     <row r="81" spans="9:11">
-      <c r="I81" s="20" t="s">
+      <c r="I81" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K81" s="1" t="str">
@@ -4885,7 +4908,7 @@
       </c>
     </row>
     <row r="82" spans="9:11">
-      <c r="I82" s="20" t="s">
+      <c r="I82" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K82" s="1" t="str">
@@ -4894,7 +4917,7 @@
       </c>
     </row>
     <row r="83" spans="9:11">
-      <c r="I83" s="20" t="s">
+      <c r="I83" s="23" t="s">
         <v>167</v>
       </c>
       <c r="K83" s="1" t="str">
@@ -4903,7 +4926,7 @@
       </c>
     </row>
     <row r="84" spans="9:11">
-      <c r="I84" s="20" t="s">
+      <c r="I84" s="23" t="s">
         <v>167</v>
       </c>
       <c r="K84" s="1" t="str">
@@ -4912,28 +4935,28 @@
       </c>
     </row>
     <row r="85" spans="2:11">
-      <c r="B85" s="20" t="s">
+      <c r="B85" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="20" t="s">
+      <c r="C85" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="D85" s="20">
+      <c r="D85" s="23">
         <v>80</v>
       </c>
-      <c r="E85" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85" s="20" t="s">
+      <c r="E85" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="G85" s="20" t="s">
+      <c r="G85" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="H85" s="20">
+      <c r="H85" s="23">
         <v>1</v>
       </c>
-      <c r="I85" s="20" t="s">
+      <c r="I85" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K85" s="1" t="str">
@@ -4942,7 +4965,7 @@
       </c>
     </row>
     <row r="86" spans="9:11">
-      <c r="I86" s="20" t="s">
+      <c r="I86" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K86" s="1" t="str">
@@ -4951,7 +4974,7 @@
       </c>
     </row>
     <row r="87" spans="9:11">
-      <c r="I87" s="20" t="s">
+      <c r="I87" s="23" t="s">
         <v>96</v>
       </c>
       <c r="K87" s="1" t="str">
@@ -4960,28 +4983,28 @@
       </c>
     </row>
     <row r="88" spans="2:11">
-      <c r="B88" s="20" t="s">
+      <c r="B88" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="C88" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="D88" s="20">
+      <c r="D88" s="23">
         <v>140</v>
       </c>
-      <c r="E88" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88" s="20" t="s">
+      <c r="E88" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="G88" s="20" t="s">
+      <c r="G88" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="H88" s="20">
+      <c r="H88" s="23">
         <v>1</v>
       </c>
-      <c r="I88" s="20" t="s">
+      <c r="I88" s="23" t="s">
         <v>174</v>
       </c>
       <c r="K88" s="1" t="str">
@@ -4990,17 +5013,17 @@
       </c>
     </row>
     <row r="89" spans="9:9">
-      <c r="I89" s="20" t="s">
+      <c r="I89" s="23" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="90" spans="9:9">
-      <c r="I90" s="20" t="s">
+      <c r="I90" s="23" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="91" spans="9:9">
-      <c r="I91" s="20" t="s">
+      <c r="I91" s="23" t="s">
         <v>175</v>
       </c>
     </row>
@@ -6053,8 +6076,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="2"/>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="23.2307692307692" customWidth="1"/>
@@ -6206,12 +6229,15 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="2:3">
+    <row r="18" spans="2:7">
       <c r="B18" t="s">
         <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>225</v>
+      </c>
+      <c r="G18" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="2:3">
@@ -6219,7 +6245,7 @@
         <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="2:3">
@@ -6227,7 +6253,7 @@
         <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="2:3">
@@ -6235,7 +6261,7 @@
         <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="2:3">
@@ -6243,7 +6269,7 @@
         <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="2:3">
@@ -6251,7 +6277,7 @@
         <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="2:3">
@@ -6259,7 +6285,7 @@
         <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="2:3">
@@ -6267,7 +6293,7 @@
         <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="2:3">
@@ -6275,7 +6301,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="2:3">
@@ -6283,7 +6309,7 @@
         <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="2:3">
@@ -6291,7 +6317,7 @@
         <v>105</v>
       </c>
       <c r="C28" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="2:3">
@@ -6299,7 +6325,7 @@
         <v>108</v>
       </c>
       <c r="C29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="2:3">
@@ -6307,7 +6333,7 @@
         <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="2:3">
@@ -6315,7 +6341,7 @@
         <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="2:3">
@@ -6323,7 +6349,7 @@
         <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="2:3">
@@ -6331,7 +6357,7 @@
         <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="2:3">
@@ -6339,7 +6365,7 @@
         <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="2:3">
@@ -6347,7 +6373,7 @@
         <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="2:3">
@@ -6355,7 +6381,7 @@
         <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="2:3">
@@ -6363,7 +6389,7 @@
         <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="2:3">
@@ -6371,7 +6397,7 @@
         <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="2:3">
@@ -6379,7 +6405,7 @@
         <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="2:3">
@@ -6387,7 +6413,7 @@
         <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="2:3">
@@ -6395,7 +6421,7 @@
         <v>143</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="2:3">
@@ -6403,7 +6429,7 @@
         <v>146</v>
       </c>
       <c r="C42" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="43" spans="2:3">
@@ -6411,7 +6437,7 @@
         <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="2:3">
@@ -6419,7 +6445,7 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="2:3">
@@ -6427,7 +6453,7 @@
         <v>155</v>
       </c>
       <c r="C45" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="2:3">
@@ -6435,7 +6461,7 @@
         <v>159</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="2:3">
@@ -6443,7 +6469,7 @@
         <v>163</v>
       </c>
       <c r="C47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="2:3">
@@ -6451,7 +6477,7 @@
         <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="2:3">
@@ -6459,7 +6485,7 @@
         <v>170</v>
       </c>
       <c r="C49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="50" spans="2:3">
@@ -6467,7 +6493,7 @@
         <v>173</v>
       </c>
       <c r="C50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -6482,212 +6508,214 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="9.30769230769231" customWidth="1"/>
-    <col min="3" max="3" width="10.3076923076923" customWidth="1"/>
-    <col min="4" max="4" width="65.1538461538462" customWidth="1"/>
-    <col min="5" max="5" width="17.8461538461538" customWidth="1"/>
-    <col min="6" max="6" width="11.9230769230769" customWidth="1"/>
-    <col min="7" max="7" width="12.6153846153846" customWidth="1"/>
-    <col min="8" max="8" width="13.0769230769231" customWidth="1"/>
+    <col min="1" max="1" width="13.0769230769231" style="21" customWidth="1"/>
+    <col min="2" max="2" width="9.30769230769231" style="21" customWidth="1"/>
+    <col min="3" max="3" width="10.3076923076923" style="21" customWidth="1"/>
+    <col min="4" max="4" width="65.1538461538462" style="21" customWidth="1"/>
+    <col min="5" max="5" width="17.8461538461538" style="21" customWidth="1"/>
+    <col min="6" max="6" width="11.9230769230769" style="21" customWidth="1"/>
+    <col min="7" max="7" width="12.6153846153846" style="21" customWidth="1"/>
+    <col min="8" max="8" width="14.25" style="21" customWidth="1"/>
+    <col min="9" max="9" width="58.6538461538462" style="21" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="21"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" s="21" t="s">
         <v>259</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="21" t="s">
         <v>262</v>
       </c>
+      <c r="H1" s="21" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" t="s">
+      <c r="A2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C2" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G2" s="21" t="s">
         <v>269</v>
       </c>
+      <c r="H2" s="21" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" t="s">
+      <c r="A3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>270</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="G3" t="s">
-        <v>271</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="G3" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="H3" s="21" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>272</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C4" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E4" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G4" s="21" t="s">
         <v>277</v>
       </c>
+      <c r="I4" s="21" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>278</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C5" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="E5" t="s">
-        <v>275</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="D5" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="I5" t="s">
+      <c r="E5" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
+      <c r="I5" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="6" ht="34" spans="2:9">
+      <c r="B6" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="D6" t="s">
+      <c r="C6" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D6" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="G6" t="s">
+      <c r="E6" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="I6" t="s">
+      <c r="G6" s="21" t="s">
         <v>288</v>
       </c>
+      <c r="I6" s="21" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B7" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="E7" t="s">
+      <c r="D7" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="G7" t="s">
-        <v>276</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="E7" s="21" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
+      <c r="G7" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="I7" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="8" ht="34" spans="2:9">
+      <c r="B8" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C8" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="E8" t="s">
+      <c r="D8" s="22" t="s">
         <v>297</v>
       </c>
-      <c r="G8" t="s">
+      <c r="E8" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="I8" t="s">
+      <c r="G8" s="21" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
+      <c r="I8" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="9" ht="51" spans="2:9">
+      <c r="B9" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C9" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="E9" t="s">
+      <c r="D9" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="G9" t="s">
+      <c r="E9" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="I9" t="s">
+      <c r="G9" s="21" t="s">
         <v>305</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -6701,6 +6729,16 @@
   <sheetPr/>
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="10.3076923076923" customWidth="1"/>
+    <col min="4" max="4" width="19.8461538461538" customWidth="1"/>
+    <col min="5" max="5" width="10.3076923076923" customWidth="1"/>
+    <col min="6" max="6" width="27.5384615384615" customWidth="1"/>
+    <col min="7" max="7" width="14.8461538461538" customWidth="1"/>
+    <col min="8" max="8" width="53.4615384615385" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
@@ -6710,22 +6748,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
       </c>
       <c r="F1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1" t="s">
         <v>259</v>
-      </c>
-      <c r="G1" t="s">
-        <v>308</v>
-      </c>
-      <c r="H1" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6733,25 +6771,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6771,7 +6809,7 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G3" t="s">
         <v>189</v>
@@ -6782,7 +6820,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6794,18 +6832,18 @@
         <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6817,18 +6855,18 @@
         <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G5">
         <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -6840,13 +6878,13 @@
         <v>83</v>
       </c>
       <c r="F6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G6">
         <v>0.02</v>
       </c>
       <c r="H6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -6877,6 +6915,7 @@
     <col min="14" max="14" width="10.3076923076923" customWidth="1"/>
     <col min="15" max="15" width="12.7692307692308" customWidth="1"/>
     <col min="16" max="16" width="84.6153846153846" customWidth="1"/>
+    <col min="17" max="17" width="20.6923076923077" customWidth="1"/>
     <col min="18" max="18" width="34.5384615384615" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6888,49 +6927,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="I1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -6938,52 +6977,52 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -6994,34 +7033,34 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G3" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -7044,25 +7083,25 @@
         <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F4" t="s">
+        <v>365</v>
+      </c>
+      <c r="G4" t="s">
+        <v>366</v>
+      </c>
+      <c r="I4" t="s">
+        <v>322</v>
+      </c>
+      <c r="J4" t="s">
         <v>364</v>
-      </c>
-      <c r="G4" t="s">
-        <v>365</v>
-      </c>
-      <c r="I4" t="s">
-        <v>321</v>
-      </c>
-      <c r="J4" t="s">
-        <v>363</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -7074,36 +7113,36 @@
         <v>27</v>
       </c>
       <c r="O4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" ht="34" spans="2:16">
       <c r="B5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -7115,36 +7154,36 @@
         <v>27</v>
       </c>
       <c r="O5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7159,10 +7198,10 @@
         <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" ht="34" spans="2:16">
@@ -7170,25 +7209,25 @@
         <v>213</v>
       </c>
       <c r="C7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F7" t="s">
+        <v>365</v>
+      </c>
+      <c r="G7" t="s">
+        <v>373</v>
+      </c>
+      <c r="I7" t="s">
+        <v>319</v>
+      </c>
+      <c r="J7" t="s">
         <v>364</v>
-      </c>
-      <c r="G7" t="s">
-        <v>372</v>
-      </c>
-      <c r="I7" t="s">
-        <v>318</v>
-      </c>
-      <c r="J7" t="s">
-        <v>363</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -7200,36 +7239,36 @@
         <v>27</v>
       </c>
       <c r="O7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="8" ht="34" spans="2:16">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="8" ht="34" spans="2:17">
       <c r="B8" t="s">
         <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G8" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -7241,10 +7280,13 @@
         <v>27</v>
       </c>
       <c r="O8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P8" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
+      </c>
+      <c r="Q8" s="21" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:16">
@@ -7252,25 +7294,25 @@
         <v>215</v>
       </c>
       <c r="C9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F9" t="s">
+        <v>365</v>
+      </c>
+      <c r="G9" t="s">
+        <v>373</v>
+      </c>
+      <c r="I9" t="s">
+        <v>388</v>
+      </c>
+      <c r="J9" t="s">
         <v>364</v>
-      </c>
-      <c r="G9" t="s">
-        <v>372</v>
-      </c>
-      <c r="I9" t="s">
-        <v>386</v>
-      </c>
-      <c r="J9" t="s">
-        <v>363</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -7282,10 +7324,10 @@
         <v>27</v>
       </c>
       <c r="O9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:16">
@@ -7293,25 +7335,25 @@
         <v>216</v>
       </c>
       <c r="C10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E10" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F10" t="s">
+        <v>365</v>
+      </c>
+      <c r="G10" t="s">
+        <v>373</v>
+      </c>
+      <c r="I10" t="s">
+        <v>322</v>
+      </c>
+      <c r="J10" t="s">
         <v>364</v>
-      </c>
-      <c r="G10" t="s">
-        <v>372</v>
-      </c>
-      <c r="I10" t="s">
-        <v>321</v>
-      </c>
-      <c r="J10" t="s">
-        <v>363</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7323,10 +7365,10 @@
         <v>27</v>
       </c>
       <c r="O10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" ht="34" spans="2:16">
@@ -7334,25 +7376,25 @@
         <v>217</v>
       </c>
       <c r="C11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F11" t="s">
+        <v>365</v>
+      </c>
+      <c r="G11" t="s">
+        <v>373</v>
+      </c>
+      <c r="I11" t="s">
+        <v>319</v>
+      </c>
+      <c r="J11" t="s">
         <v>364</v>
-      </c>
-      <c r="G11" t="s">
-        <v>372</v>
-      </c>
-      <c r="I11" t="s">
-        <v>318</v>
-      </c>
-      <c r="J11" t="s">
-        <v>363</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -7364,10 +7406,10 @@
         <v>27</v>
       </c>
       <c r="O11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" ht="34" spans="2:16">
@@ -7375,25 +7417,25 @@
         <v>218</v>
       </c>
       <c r="C12" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D12" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E12" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F12" t="s">
+        <v>365</v>
+      </c>
+      <c r="G12" t="s">
+        <v>373</v>
+      </c>
+      <c r="I12" t="s">
+        <v>388</v>
+      </c>
+      <c r="J12" t="s">
         <v>364</v>
-      </c>
-      <c r="G12" t="s">
-        <v>372</v>
-      </c>
-      <c r="I12" t="s">
-        <v>386</v>
-      </c>
-      <c r="J12" t="s">
-        <v>363</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -7405,10 +7447,10 @@
         <v>27</v>
       </c>
       <c r="O12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" ht="34" spans="2:16">
@@ -7416,25 +7458,25 @@
         <v>219</v>
       </c>
       <c r="C13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -7446,36 +7488,36 @@
         <v>27</v>
       </c>
       <c r="O13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17">
       <c r="B14" t="s">
         <v>220</v>
       </c>
       <c r="C14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I14" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J14" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -7487,39 +7529,42 @@
         <v>27</v>
       </c>
       <c r="O14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P14" t="s">
-        <v>394</v>
+        <v>396</v>
+      </c>
+      <c r="Q14" s="21" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="15" s="18" customFormat="1" spans="2:18">
       <c r="B15" s="18" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K15" s="18">
         <v>0</v>
@@ -7531,42 +7576,42 @@
         <v>29</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O15" s="18" t="s">
         <v>27</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="R15" s="18" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D16" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F16" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G16" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I16" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J16" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -7581,10 +7626,10 @@
         <v>27</v>
       </c>
       <c r="P16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q16" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" ht="34" spans="2:18">
@@ -7592,25 +7637,25 @@
         <v>222</v>
       </c>
       <c r="C17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D17" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E17" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F17" t="s">
+        <v>365</v>
+      </c>
+      <c r="G17" t="s">
+        <v>366</v>
+      </c>
+      <c r="I17" t="s">
+        <v>287</v>
+      </c>
+      <c r="J17" t="s">
         <v>364</v>
-      </c>
-      <c r="G17" t="s">
-        <v>365</v>
-      </c>
-      <c r="I17" t="s">
-        <v>286</v>
-      </c>
-      <c r="J17" t="s">
-        <v>363</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -7625,36 +7670,36 @@
         <v>27</v>
       </c>
       <c r="P17" s="19" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="R17" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="18" ht="34" spans="2:16">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" ht="34" spans="2:17">
       <c r="B18" t="s">
         <v>223</v>
       </c>
       <c r="C18" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E18" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G18" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J18" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -7666,36 +7711,39 @@
         <v>27</v>
       </c>
       <c r="O18" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P18" s="19" t="s">
-        <v>404</v>
+        <v>406</v>
+      </c>
+      <c r="Q18" s="21" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="19" ht="34" spans="2:16">
       <c r="B19" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E19" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F19" t="s">
+        <v>365</v>
+      </c>
+      <c r="G19" t="s">
+        <v>373</v>
+      </c>
+      <c r="I19" t="s">
+        <v>322</v>
+      </c>
+      <c r="J19" t="s">
         <v>364</v>
-      </c>
-      <c r="G19" t="s">
-        <v>372</v>
-      </c>
-      <c r="I19" t="s">
-        <v>321</v>
-      </c>
-      <c r="J19" t="s">
-        <v>363</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -7707,36 +7755,36 @@
         <v>27</v>
       </c>
       <c r="O19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C20" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F20" t="s">
+        <v>365</v>
+      </c>
+      <c r="G20" t="s">
+        <v>373</v>
+      </c>
+      <c r="I20" t="s">
+        <v>409</v>
+      </c>
+      <c r="J20" t="s">
         <v>364</v>
-      </c>
-      <c r="G20" t="s">
-        <v>372</v>
-      </c>
-      <c r="I20" t="s">
-        <v>407</v>
-      </c>
-      <c r="J20" t="s">
-        <v>363</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -7745,39 +7793,39 @@
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O20" t="s">
         <v>27</v>
       </c>
       <c r="P20" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
       <c r="B21" t="s">
-        <v>409</v>
+        <v>225</v>
       </c>
       <c r="C21" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D21" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F21" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I21" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J21" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -7789,39 +7837,42 @@
         <v>27</v>
       </c>
       <c r="O21" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P21" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="22" s="18" customFormat="1" spans="2:18">
+        <v>396</v>
+      </c>
+      <c r="Q21" s="21" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="22" s="18" customFormat="1" ht="34" spans="2:18">
       <c r="B22" s="18" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K22" s="18">
         <v>0</v>
@@ -7838,40 +7889,40 @@
       <c r="O22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="P22" s="18" t="s">
-        <v>413</v>
+      <c r="P22" s="20" t="s">
+        <v>414</v>
       </c>
       <c r="R22" s="18" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" ht="34" spans="2:16">
       <c r="B23" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C23" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D23" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E23" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F23" t="s">
+        <v>365</v>
+      </c>
+      <c r="G23" t="s">
+        <v>366</v>
+      </c>
+      <c r="H23" t="s">
+        <v>418</v>
+      </c>
+      <c r="I23" t="s">
+        <v>325</v>
+      </c>
+      <c r="J23" t="s">
         <v>364</v>
-      </c>
-      <c r="G23" t="s">
-        <v>365</v>
-      </c>
-      <c r="H23" t="s">
-        <v>417</v>
-      </c>
-      <c r="I23" t="s">
-        <v>324</v>
-      </c>
-      <c r="J23" t="s">
-        <v>363</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -7885,34 +7936,34 @@
       <c r="O23" t="s">
         <v>27</v>
       </c>
-      <c r="P23" t="s">
-        <v>418</v>
+      <c r="P23" s="19" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="2:17">
       <c r="B24" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C24" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E24" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F24" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G24" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I24" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J24" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K24">
         <v>2</v>
@@ -7927,36 +7978,36 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q24" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="25" ht="34" spans="2:16">
       <c r="B25" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D25" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E25" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F25" t="s">
+        <v>365</v>
+      </c>
+      <c r="G25" t="s">
+        <v>373</v>
+      </c>
+      <c r="I25" t="s">
+        <v>325</v>
+      </c>
+      <c r="J25" t="s">
         <v>364</v>
-      </c>
-      <c r="G25" t="s">
-        <v>372</v>
-      </c>
-      <c r="I25" t="s">
-        <v>324</v>
-      </c>
-      <c r="J25" t="s">
-        <v>363</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -7970,34 +8021,34 @@
       <c r="O25" t="s">
         <v>27</v>
       </c>
-      <c r="P25" t="s">
-        <v>422</v>
+      <c r="P25" s="19" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="26" spans="2:17">
       <c r="B26" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F26" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G26" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I26" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J26" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K26">
         <v>2</v>
@@ -8012,36 +8063,36 @@
         <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q26" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C27" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E27" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F27" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I27" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J27" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -8056,33 +8107,33 @@
         <v>27</v>
       </c>
       <c r="P27" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="28" ht="34" spans="2:17">
       <c r="B28" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D28" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E28" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F28" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G28" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I28" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J28" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -8094,36 +8145,39 @@
         <v>27</v>
       </c>
       <c r="O28" t="s">
-        <v>366</v>
-      </c>
-      <c r="P28" t="s">
-        <v>428</v>
+        <v>367</v>
+      </c>
+      <c r="P28" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="Q28" s="21" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D29" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E29" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F29" t="s">
+        <v>365</v>
+      </c>
+      <c r="G29" t="s">
+        <v>373</v>
+      </c>
+      <c r="I29" t="s">
+        <v>325</v>
+      </c>
+      <c r="J29" t="s">
         <v>364</v>
-      </c>
-      <c r="G29" t="s">
-        <v>372</v>
-      </c>
-      <c r="I29" t="s">
-        <v>324</v>
-      </c>
-      <c r="J29" t="s">
-        <v>363</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -8138,33 +8192,33 @@
         <v>27</v>
       </c>
       <c r="P29" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D30" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E30" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F30" t="s">
+        <v>365</v>
+      </c>
+      <c r="G30" t="s">
+        <v>373</v>
+      </c>
+      <c r="I30" t="s">
+        <v>388</v>
+      </c>
+      <c r="J30" t="s">
         <v>364</v>
-      </c>
-      <c r="G30" t="s">
-        <v>372</v>
-      </c>
-      <c r="I30" t="s">
-        <v>386</v>
-      </c>
-      <c r="J30" t="s">
-        <v>363</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -8176,36 +8230,36 @@
         <v>27</v>
       </c>
       <c r="O30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P30" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="31" spans="2:17">
       <c r="B31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D31" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E31" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F31" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G31" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I31" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J31" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K31">
         <v>2</v>
@@ -8220,36 +8274,36 @@
         <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q31" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="32" ht="34" spans="2:16">
       <c r="B32" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C32" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D32" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E32" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F32" t="s">
+        <v>365</v>
+      </c>
+      <c r="G32" t="s">
+        <v>373</v>
+      </c>
+      <c r="I32" t="s">
+        <v>322</v>
+      </c>
+      <c r="J32" t="s">
         <v>364</v>
-      </c>
-      <c r="G32" t="s">
-        <v>372</v>
-      </c>
-      <c r="I32" t="s">
-        <v>321</v>
-      </c>
-      <c r="J32" t="s">
-        <v>363</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -8261,10 +8315,10 @@
         <v>27</v>
       </c>
       <c r="O32" t="s">
-        <v>366</v>
-      </c>
-      <c r="P32" t="s">
-        <v>436</v>
+        <v>367</v>
+      </c>
+      <c r="P32" s="19" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="33" spans="2:16">
@@ -8272,25 +8326,25 @@
         <v>437</v>
       </c>
       <c r="C33" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D33" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F33" t="s">
+        <v>365</v>
+      </c>
+      <c r="G33" t="s">
+        <v>373</v>
+      </c>
+      <c r="I33" t="s">
+        <v>409</v>
+      </c>
+      <c r="J33" t="s">
         <v>364</v>
-      </c>
-      <c r="G33" t="s">
-        <v>372</v>
-      </c>
-      <c r="I33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J33" t="s">
-        <v>363</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -8299,13 +8353,13 @@
         <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="34" spans="2:16">
@@ -8313,25 +8367,25 @@
         <v>438</v>
       </c>
       <c r="C34" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D34" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E34" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G34" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J34" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -8343,7 +8397,7 @@
         <v>27</v>
       </c>
       <c r="O34" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P34" t="s">
         <v>439</v>
@@ -8354,25 +8408,25 @@
         <v>440</v>
       </c>
       <c r="C35" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D35" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E35" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F35" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G35" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I35" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J35" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -8387,10 +8441,10 @@
         <v>27</v>
       </c>
       <c r="P35" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q35" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="36" spans="2:18">
@@ -8398,25 +8452,25 @@
         <v>441</v>
       </c>
       <c r="C36" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D36" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E36" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F36" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G36" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I36" t="s">
         <v>442</v>
       </c>
       <c r="J36" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -8433,8 +8487,11 @@
       <c r="P36" t="s">
         <v>443</v>
       </c>
+      <c r="Q36" s="21" t="s">
+        <v>386</v>
+      </c>
       <c r="R36" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="37" spans="2:18">
@@ -8442,25 +8499,25 @@
         <v>444</v>
       </c>
       <c r="C37" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D37" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E37" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F37" t="s">
+        <v>365</v>
+      </c>
+      <c r="G37" t="s">
+        <v>373</v>
+      </c>
+      <c r="I37" t="s">
+        <v>322</v>
+      </c>
+      <c r="J37" t="s">
         <v>364</v>
-      </c>
-      <c r="G37" t="s">
-        <v>372</v>
-      </c>
-      <c r="I37" t="s">
-        <v>321</v>
-      </c>
-      <c r="J37" t="s">
-        <v>363</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -8472,13 +8529,13 @@
         <v>27</v>
       </c>
       <c r="O37" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P37" t="s">
         <v>439</v>
       </c>
       <c r="R37" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="38" spans="2:18">
@@ -8486,25 +8543,25 @@
         <v>445</v>
       </c>
       <c r="C38" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D38" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E38" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F38" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G38" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I38" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J38" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -8516,13 +8573,13 @@
         <v>27</v>
       </c>
       <c r="O38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P38" t="s">
         <v>439</v>
       </c>
       <c r="R38" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="39" spans="2:18">
@@ -8530,25 +8587,25 @@
         <v>446</v>
       </c>
       <c r="C39" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D39" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E39" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F39" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G39" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I39" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J39" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -8563,39 +8620,39 @@
         <v>27</v>
       </c>
       <c r="P39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q39" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="R39" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="40" spans="2:18">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="40" ht="34" spans="2:18">
       <c r="B40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C40" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D40" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E40" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F40" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G40" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I40" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J40" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -8612,28 +8669,31 @@
       <c r="O40" t="s">
         <v>27</v>
       </c>
-      <c r="P40" t="s">
+      <c r="P40" s="19" t="s">
         <v>448</v>
+      </c>
+      <c r="Q40" s="21" t="s">
+        <v>386</v>
       </c>
       <c r="R40" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="41" spans="2:16">
+    <row r="41" ht="34" spans="2:16">
       <c r="B41" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D41" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E41" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F41" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G41" t="s">
         <v>450</v>
@@ -8642,10 +8702,10 @@
         <v>451</v>
       </c>
       <c r="I41" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J41" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -8662,7 +8722,7 @@
       <c r="O41" t="s">
         <v>27</v>
       </c>
-      <c r="P41" t="s">
+      <c r="P41" s="19" t="s">
         <v>453</v>
       </c>
     </row>
@@ -8671,25 +8731,25 @@
         <v>454</v>
       </c>
       <c r="C42" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D42" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E42" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F42" t="s">
+        <v>365</v>
+      </c>
+      <c r="G42" t="s">
+        <v>373</v>
+      </c>
+      <c r="I42" t="s">
+        <v>409</v>
+      </c>
+      <c r="J42" t="s">
         <v>364</v>
-      </c>
-      <c r="G42" t="s">
-        <v>372</v>
-      </c>
-      <c r="I42" t="s">
-        <v>407</v>
-      </c>
-      <c r="J42" t="s">
-        <v>363</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -8698,13 +8758,13 @@
         <v>4</v>
       </c>
       <c r="N42" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O42" t="s">
         <v>27</v>
       </c>
       <c r="P42" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="43" spans="2:16">
@@ -8712,25 +8772,25 @@
         <v>455</v>
       </c>
       <c r="C43" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D43" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E43" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F43" t="s">
+        <v>365</v>
+      </c>
+      <c r="G43" t="s">
+        <v>373</v>
+      </c>
+      <c r="I43" t="s">
+        <v>325</v>
+      </c>
+      <c r="J43" t="s">
         <v>364</v>
-      </c>
-      <c r="G43" t="s">
-        <v>372</v>
-      </c>
-      <c r="I43" t="s">
-        <v>324</v>
-      </c>
-      <c r="J43" t="s">
-        <v>363</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -8745,33 +8805,33 @@
         <v>27</v>
       </c>
       <c r="P43" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="44" ht="34" spans="2:16">
       <c r="B44" t="s">
         <v>456</v>
       </c>
       <c r="C44" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D44" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E44" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F44" t="s">
+        <v>365</v>
+      </c>
+      <c r="G44" t="s">
+        <v>366</v>
+      </c>
+      <c r="I44" t="s">
+        <v>409</v>
+      </c>
+      <c r="J44" t="s">
         <v>364</v>
-      </c>
-      <c r="G44" t="s">
-        <v>365</v>
-      </c>
-      <c r="I44" t="s">
-        <v>407</v>
-      </c>
-      <c r="J44" t="s">
-        <v>363</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -8780,12 +8840,12 @@
         <v>9</v>
       </c>
       <c r="N44" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O44" t="s">
         <v>27</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="19" t="s">
         <v>457</v>
       </c>
     </row>
@@ -8794,25 +8854,25 @@
         <v>458</v>
       </c>
       <c r="C45" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D45" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E45" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F45" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G45" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I45" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J45" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -8821,7 +8881,7 @@
         <v>2</v>
       </c>
       <c r="N45" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O45" t="s">
         <v>27</v>
@@ -8835,25 +8895,25 @@
         <v>460</v>
       </c>
       <c r="C46" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D46" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E46" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F46" t="s">
+        <v>365</v>
+      </c>
+      <c r="G46" t="s">
+        <v>373</v>
+      </c>
+      <c r="I46" t="s">
+        <v>322</v>
+      </c>
+      <c r="J46" t="s">
         <v>364</v>
-      </c>
-      <c r="G46" t="s">
-        <v>372</v>
-      </c>
-      <c r="I46" t="s">
-        <v>321</v>
-      </c>
-      <c r="J46" t="s">
-        <v>363</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -8865,33 +8925,33 @@
         <v>27</v>
       </c>
       <c r="O46" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P46" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="47" spans="2:16">
+    <row r="47" ht="34" spans="2:16">
       <c r="B47" t="s">
         <v>461</v>
       </c>
       <c r="C47" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D47" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E47" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F47" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G47" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I47" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J47" t="s">
         <v>462</v>
@@ -8909,36 +8969,36 @@
         <v>27</v>
       </c>
       <c r="O47" t="s">
-        <v>366</v>
-      </c>
-      <c r="P47" t="s">
+        <v>367</v>
+      </c>
+      <c r="P47" s="19" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="48" spans="2:16">
+    <row r="48" spans="2:17">
       <c r="B48" t="s">
         <v>465</v>
       </c>
       <c r="C48" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D48" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F48" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G48" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I48" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J48" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -8950,36 +9010,39 @@
         <v>27</v>
       </c>
       <c r="O48" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P48" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16">
+        <v>396</v>
+      </c>
+      <c r="Q48" s="21" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="49" ht="34" spans="2:16">
       <c r="B49" t="s">
         <v>466</v>
       </c>
       <c r="C49" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D49" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E49" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F49" t="s">
+        <v>365</v>
+      </c>
+      <c r="G49" t="s">
+        <v>373</v>
+      </c>
+      <c r="I49" t="s">
+        <v>322</v>
+      </c>
+      <c r="J49" t="s">
         <v>364</v>
-      </c>
-      <c r="G49" t="s">
-        <v>372</v>
-      </c>
-      <c r="I49" t="s">
-        <v>321</v>
-      </c>
-      <c r="J49" t="s">
-        <v>363</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -8991,9 +9054,9 @@
         <v>27</v>
       </c>
       <c r="O49" t="s">
-        <v>366</v>
-      </c>
-      <c r="P49" t="s">
+        <v>367</v>
+      </c>
+      <c r="P49" s="19" t="s">
         <v>467</v>
       </c>
     </row>
@@ -9002,25 +9065,25 @@
         <v>468</v>
       </c>
       <c r="C50" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D50" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E50" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F50" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G50" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I50" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J50" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -9035,10 +9098,10 @@
         <v>27</v>
       </c>
       <c r="P50" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q50" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="51" spans="2:16">
@@ -9046,25 +9109,25 @@
         <v>469</v>
       </c>
       <c r="C51" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D51" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E51" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F51" t="s">
+        <v>365</v>
+      </c>
+      <c r="G51" t="s">
+        <v>373</v>
+      </c>
+      <c r="I51" t="s">
+        <v>409</v>
+      </c>
+      <c r="J51" t="s">
         <v>364</v>
-      </c>
-      <c r="G51" t="s">
-        <v>372</v>
-      </c>
-      <c r="I51" t="s">
-        <v>407</v>
-      </c>
-      <c r="J51" t="s">
-        <v>363</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -9073,13 +9136,13 @@
         <v>9</v>
       </c>
       <c r="N51" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O51" t="s">
         <v>27</v>
       </c>
       <c r="P51" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" spans="2:16">
@@ -9087,25 +9150,25 @@
         <v>470</v>
       </c>
       <c r="C52" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D52" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E52" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F52" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G52" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I52" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J52" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -9120,33 +9183,33 @@
         <v>27</v>
       </c>
       <c r="P52" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17">
       <c r="B53" t="s">
         <v>471</v>
       </c>
       <c r="C53" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D53" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E53" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F53" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G53" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I53" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J53" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -9158,10 +9221,13 @@
         <v>27</v>
       </c>
       <c r="O53" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P53" t="s">
-        <v>394</v>
+        <v>396</v>
+      </c>
+      <c r="Q53" s="21" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="2:16">
@@ -9169,25 +9235,25 @@
         <v>472</v>
       </c>
       <c r="C54" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E54" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F54" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G54" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I54" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J54" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -9199,7 +9265,7 @@
         <v>27</v>
       </c>
       <c r="O54" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P54" t="s">
         <v>439</v>
@@ -9210,25 +9276,25 @@
         <v>473</v>
       </c>
       <c r="C55" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D55" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E55" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F55" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G55" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I55" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J55" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -9243,7 +9309,7 @@
         <v>27</v>
       </c>
       <c r="P55" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="56" spans="2:16">
@@ -9251,25 +9317,25 @@
         <v>474</v>
       </c>
       <c r="C56" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D56" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E56" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F56" t="s">
+        <v>365</v>
+      </c>
+      <c r="G56" t="s">
+        <v>373</v>
+      </c>
+      <c r="I56" t="s">
+        <v>409</v>
+      </c>
+      <c r="J56" t="s">
         <v>364</v>
-      </c>
-      <c r="G56" t="s">
-        <v>372</v>
-      </c>
-      <c r="I56" t="s">
-        <v>407</v>
-      </c>
-      <c r="J56" t="s">
-        <v>363</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -9278,13 +9344,13 @@
         <v>7</v>
       </c>
       <c r="N56" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O56" t="s">
         <v>27</v>
       </c>
       <c r="P56" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="57" spans="2:16">
@@ -9292,22 +9358,22 @@
         <v>475</v>
       </c>
       <c r="C57" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D57" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E57" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F57" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G57" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I57" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J57" t="s">
         <v>462</v>
@@ -9325,36 +9391,36 @@
         <v>27</v>
       </c>
       <c r="O57" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P57" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="58" spans="2:16">
+    <row r="58" ht="34" spans="2:16">
       <c r="B58" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D58" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E58" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G58" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I58" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J58" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -9366,10 +9432,10 @@
         <v>27</v>
       </c>
       <c r="O58" t="s">
-        <v>366</v>
-      </c>
-      <c r="P58" t="s">
-        <v>436</v>
+        <v>367</v>
+      </c>
+      <c r="P58" s="19" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="59" spans="2:16">
@@ -9377,25 +9443,25 @@
         <v>477</v>
       </c>
       <c r="C59" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D59" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E59" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F59" t="s">
+        <v>365</v>
+      </c>
+      <c r="G59" t="s">
+        <v>373</v>
+      </c>
+      <c r="I59" t="s">
+        <v>325</v>
+      </c>
+      <c r="J59" t="s">
         <v>364</v>
-      </c>
-      <c r="G59" t="s">
-        <v>372</v>
-      </c>
-      <c r="I59" t="s">
-        <v>324</v>
-      </c>
-      <c r="J59" t="s">
-        <v>363</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -9410,24 +9476,24 @@
         <v>27</v>
       </c>
       <c r="P59" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="60" spans="2:16">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="60" ht="34" spans="2:17">
       <c r="B60" t="s">
         <v>478</v>
       </c>
       <c r="C60" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D60" t="s">
         <v>479</v>
       </c>
       <c r="E60" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F60" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G60" t="s">
         <v>450</v>
@@ -9436,10 +9502,10 @@
         <v>480</v>
       </c>
       <c r="I60" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J60" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -9456,25 +9522,28 @@
       <c r="O60" t="s">
         <v>27</v>
       </c>
-      <c r="P60" t="s">
+      <c r="P60" s="19" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="61" spans="2:16">
+      <c r="Q60" s="21" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="61" ht="34" spans="2:17">
       <c r="B61" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C61" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D61" t="s">
         <v>483</v>
       </c>
       <c r="E61" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F61" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G61" t="s">
         <v>450</v>
@@ -9483,10 +9552,10 @@
         <v>484</v>
       </c>
       <c r="I61" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J61" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -9503,34 +9572,37 @@
       <c r="O61" t="s">
         <v>27</v>
       </c>
-      <c r="P61" t="s">
+      <c r="P61" s="19" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="62" spans="2:16">
+      <c r="Q61" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="62" ht="34" spans="2:17">
       <c r="B62" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C62" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D62" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E62" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F62" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G62" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I62" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J62" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -9542,36 +9614,39 @@
         <v>27</v>
       </c>
       <c r="O62" t="s">
-        <v>366</v>
-      </c>
-      <c r="P62" t="s">
-        <v>487</v>
+        <v>367</v>
+      </c>
+      <c r="P62" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q62" s="21" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="63" spans="2:16">
       <c r="B63" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C63" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D63" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E63" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F63" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G63" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J63" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -9586,33 +9661,33 @@
         <v>27</v>
       </c>
       <c r="P63" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="64" spans="2:16">
       <c r="B64" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C64" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D64" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E64" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F64" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G64" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I64" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J64" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -9627,33 +9702,33 @@
         <v>27</v>
       </c>
       <c r="P64" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="65" spans="2:17">
       <c r="B65" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C65" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D65" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E65" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F65" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G65" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I65" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J65" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -9668,36 +9743,36 @@
         <v>27</v>
       </c>
       <c r="P65" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q65" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="66" spans="2:17">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="66" ht="34" spans="2:17">
       <c r="B66" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C66" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D66" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E66" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F66" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G66" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I66" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="J66" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -9706,45 +9781,45 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
+        <v>491</v>
+      </c>
+      <c r="N66" t="s">
+        <v>27</v>
+      </c>
+      <c r="O66" t="s">
+        <v>27</v>
+      </c>
+      <c r="P66" s="19" t="s">
         <v>492</v>
       </c>
-      <c r="N66" t="s">
-        <v>27</v>
-      </c>
-      <c r="O66" t="s">
-        <v>27</v>
-      </c>
-      <c r="P66" t="s">
+      <c r="Q66" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" ht="34" spans="2:16">
+      <c r="B67" t="s">
         <v>493</v>
       </c>
-      <c r="Q66" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16">
-      <c r="B67" t="s">
-        <v>494</v>
-      </c>
       <c r="C67" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D67" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E67" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F67" t="s">
+        <v>365</v>
+      </c>
+      <c r="G67" t="s">
+        <v>373</v>
+      </c>
+      <c r="I67" t="s">
+        <v>325</v>
+      </c>
+      <c r="J67" t="s">
         <v>364</v>
-      </c>
-      <c r="G67" t="s">
-        <v>372</v>
-      </c>
-      <c r="I67" t="s">
-        <v>324</v>
-      </c>
-      <c r="J67" t="s">
-        <v>363</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -9758,34 +9833,34 @@
       <c r="O67" t="s">
         <v>27</v>
       </c>
-      <c r="P67" t="s">
-        <v>495</v>
+      <c r="P67" s="19" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="68" spans="2:17">
       <c r="B68" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D68" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E68" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F68" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G68" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I68" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J68" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -9800,36 +9875,36 @@
         <v>27</v>
       </c>
       <c r="P68" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q68" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="69" spans="2:16">
       <c r="B69" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C69" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D69" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E69" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F69" t="s">
+        <v>365</v>
+      </c>
+      <c r="G69" t="s">
+        <v>373</v>
+      </c>
+      <c r="I69" t="s">
+        <v>426</v>
+      </c>
+      <c r="J69" t="s">
         <v>364</v>
-      </c>
-      <c r="G69" t="s">
-        <v>372</v>
-      </c>
-      <c r="I69" t="s">
-        <v>425</v>
-      </c>
-      <c r="J69" t="s">
-        <v>363</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -9847,7 +9922,7 @@
         <v>27</v>
       </c>
       <c r="P69" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -9885,34 +9960,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>505</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="M2" t="s">
         <v>506</v>
-      </c>
-      <c r="M2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="3" ht="17.6" customHeight="1" spans="1:15">
@@ -9929,22 +10004,22 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="M3" t="s">
         <v>511</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" s="6" t="s">
         <v>512</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="4" ht="17.6" customHeight="1" spans="1:13">
@@ -9961,19 +10036,19 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" t="s">
         <v>516</v>
-      </c>
-      <c r="M4" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="5" ht="17.6" customHeight="1" spans="1:13">
@@ -9990,22 +10065,22 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="M5" t="s">
         <v>519</v>
-      </c>
-      <c r="M5" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="6" ht="17.6" customHeight="1" spans="1:13">
@@ -10022,19 +10097,19 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="M6" t="s">
         <v>523</v>
-      </c>
-      <c r="M6" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="7" ht="17.6" customHeight="1" spans="1:13">
@@ -10051,19 +10126,19 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="M7" t="s">
         <v>525</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="M7" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="8" ht="17.6" customHeight="1" spans="1:9">
@@ -10080,16 +10155,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" ht="17.6" customHeight="1" spans="1:9">
@@ -10106,16 +10181,16 @@
         <v>6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="10" ht="17.6" customHeight="1" spans="1:14">
@@ -10132,19 +10207,19 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="N10" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="11" ht="17.6" customHeight="1" spans="1:9">
@@ -10161,16 +10236,16 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="12" ht="17.6" customHeight="1" spans="1:15">
@@ -10187,25 +10262,25 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M12" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="M12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="O12" s="6" t="s">
         <v>537</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="13" ht="17.6" customHeight="1" spans="1:15">
@@ -10222,28 +10297,28 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="J13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="O13" s="6" t="s">
         <v>544</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -10260,22 +10335,22 @@
         <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="H14" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="O14" s="6" t="s">
         <v>549</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -10292,22 +10367,22 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="N15" s="1" t="s">
+      <c r="O15" s="6" t="s">
         <v>552</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="16" ht="17.6" customHeight="1" spans="1:15">
@@ -10324,25 +10399,25 @@
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="M16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="O16" s="6" t="s">
         <v>557</v>
-      </c>
-      <c r="O16" s="6" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="17" ht="17.6" customHeight="1" spans="1:15">
@@ -10359,22 +10434,22 @@
         <v>20</v>
       </c>
       <c r="E17" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="N17" s="1" t="s">
+      <c r="O17" s="6" t="s">
         <v>560</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="18" spans="3:15">
@@ -10382,10 +10457,10 @@
         <v>30</v>
       </c>
       <c r="N18" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="O18" s="6" t="s">
         <v>562</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="19" ht="17.6" customHeight="1" spans="1:15">
@@ -10402,22 +10477,22 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="N19" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="N19" s="1" t="s">
+      <c r="O19" s="6" t="s">
         <v>565</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="20" ht="17.6" customHeight="1" spans="1:15">
@@ -10431,25 +10506,25 @@
         <v>70</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="M20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="O20" s="6" t="s">
         <v>569</v>
-      </c>
-      <c r="O20" s="6" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="21" ht="17.6" customHeight="1" spans="1:15">
@@ -10466,22 +10541,22 @@
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="N21" s="1" t="s">
+      <c r="O21" s="6" t="s">
         <v>573</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="22" ht="17.6" customHeight="1" spans="1:15">
@@ -10498,22 +10573,22 @@
         <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="N22" s="1" t="s">
+      <c r="O22" s="6" t="s">
         <v>576</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="23" spans="3:15">
@@ -10521,13 +10596,13 @@
         <v>30</v>
       </c>
       <c r="M23" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="N23" s="1" t="s">
         <v>578</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="O23" s="6" t="s">
         <v>579</v>
-      </c>
-      <c r="O23" s="6" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="24" ht="17.6" customHeight="1" spans="1:15">
@@ -10544,25 +10619,25 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="H24" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="N24" s="1" t="s">
+      <c r="O24" s="6" t="s">
         <v>583</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="25" spans="3:15">
@@ -10570,10 +10645,10 @@
         <v>30</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="26" ht="17.6" customHeight="1" spans="1:15">
@@ -10590,25 +10665,25 @@
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
+        <v>585</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="M26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="O26" s="6" t="s">
         <v>588</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="27" spans="3:15">
@@ -10616,10 +10691,10 @@
         <v>30</v>
       </c>
       <c r="N27" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="O27" s="6" t="s">
         <v>590</v>
-      </c>
-      <c r="O27" s="6" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="28" ht="17.6" customHeight="1" spans="1:15">
@@ -10636,25 +10711,25 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="M28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="O28" s="6" t="s">
         <v>594</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="29" ht="17.6" customHeight="1" spans="1:15">
@@ -10671,22 +10746,22 @@
         <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="H29" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="N29" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="H29" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="N29" s="1" t="s">
+      <c r="O29" s="6" t="s">
         <v>598</v>
-      </c>
-      <c r="O29" s="6" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="30" ht="17.6" customHeight="1" spans="1:15">
@@ -10703,25 +10778,25 @@
         <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="N30" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="G30" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="N30" s="1" t="s">
+      <c r="O30" s="6" t="s">
         <v>601</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="31" spans="3:15">
@@ -10729,10 +10804,10 @@
         <v>30</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="32" spans="3:15">
@@ -10740,10 +10815,10 @@
         <v>30</v>
       </c>
       <c r="N32" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="O32" s="13" t="s">
         <v>604</v>
-      </c>
-      <c r="O32" s="13" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="33" ht="17.6" customHeight="1" spans="1:15">
@@ -10760,25 +10835,25 @@
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="M33" s="1" t="s">
+      <c r="N33" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="O33" s="13" t="s">
         <v>608</v>
-      </c>
-      <c r="O33" s="13" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="34" spans="3:15">
@@ -10786,13 +10861,13 @@
         <v>30</v>
       </c>
       <c r="M34" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="N34" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="13" t="s">
         <v>611</v>
-      </c>
-      <c r="O34" s="13" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="35" spans="3:3">
@@ -10814,16 +10889,16 @@
         <v>30</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="37" spans="3:15">
@@ -10831,10 +10906,10 @@
         <v>70</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="38" ht="17.6" customHeight="1" spans="1:15">
@@ -10851,22 +10926,22 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N38" s="1" t="s">
         <v>614</v>
       </c>
-      <c r="G38" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="N38" s="1" t="s">
+      <c r="O38" s="6" t="s">
         <v>615</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="39" spans="3:15">
@@ -10874,10 +10949,10 @@
         <v>70</v>
       </c>
       <c r="N39" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="O39" s="6" t="s">
         <v>617</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="40" ht="17.6" customHeight="1" spans="1:15">
@@ -10894,22 +10969,22 @@
         <v>25</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N40" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="G40" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="N40" s="1" t="s">
+      <c r="O40" s="6" t="s">
         <v>620</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="41" ht="17.6" customHeight="1" spans="3:15">
@@ -10917,10 +10992,10 @@
         <v>70</v>
       </c>
       <c r="N41" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="O41" s="6" t="s">
         <v>622</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="42" ht="17.6" customHeight="1" spans="1:9">
@@ -10937,16 +11012,16 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="43" spans="3:15">
@@ -10954,10 +11029,10 @@
         <v>70</v>
       </c>
       <c r="N43" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="O43" s="6" t="s">
         <v>625</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="44" ht="17.6" customHeight="1" spans="1:15">
@@ -10974,22 +11049,22 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N44" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="N44" s="1" t="s">
+      <c r="O44" s="6" t="s">
         <v>628</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="45" spans="3:15">
@@ -10997,10 +11072,10 @@
         <v>70</v>
       </c>
       <c r="N45" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="O45" s="6" t="s">
         <v>630</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="46" ht="17.6" customHeight="1" spans="1:15">
@@ -11017,22 +11092,22 @@
         <v>50</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N46" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="G46" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="N46" s="1" t="s">
+      <c r="O46" s="6" t="s">
         <v>633</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="47" spans="3:15">
@@ -11040,10 +11115,10 @@
         <v>70</v>
       </c>
       <c r="N47" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="O47" s="6" t="s">
         <v>635</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="48" ht="17.6" customHeight="1" spans="1:15">
@@ -11060,22 +11135,22 @@
         <v>40</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="N48" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="G48" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="N48" s="1" t="s">
+      <c r="O48" s="6" t="s">
         <v>638</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -11083,10 +11158,10 @@
         <v>70</v>
       </c>
       <c r="N49" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="O49" s="6" t="s">
         <v>640</v>
-      </c>
-      <c r="O49" s="6" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="50" ht="17.6" customHeight="1" spans="1:15">
@@ -11103,22 +11178,22 @@
         <v>30</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="N50" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="G50" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="N50" s="1" t="s">
+      <c r="O50" s="6" t="s">
         <v>643</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="51" spans="3:15">
@@ -11126,10 +11201,10 @@
         <v>70</v>
       </c>
       <c r="N51" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="O51" s="6" t="s">
         <v>645</v>
-      </c>
-      <c r="O51" s="6" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="52" ht="17.6" customHeight="1" spans="1:15">
@@ -11146,22 +11221,22 @@
         <v>50</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H52" s="1" t="s">
+      <c r="I52" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="N52" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="N52" s="1" t="s">
+      <c r="O52" s="6" t="s">
         <v>649</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="53" spans="3:15">
@@ -11169,10 +11244,10 @@
         <v>96</v>
       </c>
       <c r="N53" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="O53" s="6" t="s">
         <v>651</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="54" ht="17.6" customHeight="1" spans="1:9">
@@ -11189,16 +11264,16 @@
         <v>40</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" spans="3:3">
@@ -11225,16 +11300,16 @@
         <v>30</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="58" spans="3:3">
@@ -11261,16 +11336,16 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="61" spans="3:3">
@@ -11292,16 +11367,16 @@
         <v>30</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="63" spans="3:3">
@@ -11323,16 +11398,16 @@
         <v>50</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65" spans="3:3">
@@ -11359,16 +11434,16 @@
         <v>40</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="G67" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I67" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="68" spans="3:3">
@@ -11395,16 +11470,16 @@
         <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="71" spans="3:3">
@@ -11426,16 +11501,16 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="G72" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="I72" s="1" t="s">
         <v>522</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="73" spans="3:3">
@@ -11457,16 +11532,16 @@
         <v>30</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="75" spans="3:3">
@@ -11488,16 +11563,16 @@
         <v>40</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J76" s="15"/>
       <c r="K76" s="17"/>
@@ -11530,16 +11605,16 @@
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="80" spans="3:3">
@@ -11583,16 +11658,16 @@
         <v>80</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
@@ -11628,16 +11703,16 @@
         <v>140</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
@@ -11679,16 +11754,16 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -11700,19 +11775,19 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -11720,85 +11795,85 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="N6" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="M6" s="4" t="s">
+      <c r="O6" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>671</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="8:18">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="8:18">
       <c r="H8" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="3" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="8:18">
@@ -11807,22 +11882,22 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="M9" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="Q9" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="R9" s="3"/>
     </row>
@@ -11833,16 +11908,16 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -11854,10 +11929,10 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -11871,10 +11946,10 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="3"/>
+    <workbookView windowHeight="15240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -2756,7 +2756,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2815,9 +2815,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3192,31 +3189,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="22" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="1" t="str">
@@ -3225,31 +3222,31 @@
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="22" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="1" t="str">
@@ -3261,31 +3258,31 @@
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="23" t="s">
+      <c r="F3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="23" t="s">
+      <c r="G3" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="22" t="s">
         <v>23</v>
       </c>
       <c r="K3" s="1" t="str">
@@ -3297,28 +3294,28 @@
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <v>10</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="23" t="s">
+      <c r="E4" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <v>1</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K4" s="1" t="str">
@@ -3327,28 +3324,28 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="22">
         <v>8</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="23" t="s">
+      <c r="E5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="23" t="s">
+      <c r="G5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="22">
         <v>1</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K5" s="1" t="str">
@@ -3357,28 +3354,28 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="22">
         <v>30</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="23" t="s">
+      <c r="E6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="23" t="s">
+      <c r="G6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="22">
         <v>1</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K6" s="1" t="str">
@@ -3387,28 +3384,28 @@
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="22">
         <v>8</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="23" t="s">
+      <c r="E7" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G7" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>1</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K7" s="1" t="str">
@@ -3417,26 +3414,26 @@
       </c>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="22">
         <v>6</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="23" t="s">
+      <c r="E8" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="23">
+      <c r="G8" s="22"/>
+      <c r="H8" s="22">
         <v>1</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="1" t="str">
@@ -3445,26 +3442,26 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="22">
         <v>10</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="23" t="s">
+      <c r="E9" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23">
+      <c r="G9" s="22"/>
+      <c r="H9" s="22">
         <v>1</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K9" s="1" t="str">
@@ -3473,26 +3470,26 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <v>6</v>
       </c>
-      <c r="E10" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="23" t="s">
+      <c r="E10" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23">
+      <c r="G10" s="22"/>
+      <c r="H10" s="22">
         <v>1</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K10" s="1" t="str">
@@ -3501,26 +3498,26 @@
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="22">
         <v>10</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="E11" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23">
+      <c r="G11" s="22"/>
+      <c r="H11" s="22">
         <v>1</v>
       </c>
-      <c r="I11" s="23" t="s">
+      <c r="I11" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K11" s="1" t="str">
@@ -3529,26 +3526,26 @@
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="22">
         <v>4</v>
       </c>
-      <c r="E12" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="23" t="s">
+      <c r="E12" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23">
+      <c r="G12" s="22"/>
+      <c r="H12" s="22">
         <v>1</v>
       </c>
-      <c r="I12" s="23" t="s">
+      <c r="I12" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K12" s="1" t="str">
@@ -3557,26 +3554,26 @@
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="22">
         <v>10</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="23" t="s">
+      <c r="E13" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23">
+      <c r="G13" s="22"/>
+      <c r="H13" s="22">
         <v>1</v>
       </c>
-      <c r="I13" s="23" t="s">
+      <c r="I13" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K13" s="1" t="str">
@@ -3585,26 +3582,26 @@
       </c>
     </row>
     <row r="14" spans="2:11">
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="22">
         <v>10</v>
       </c>
-      <c r="E14" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="23" t="s">
+      <c r="E14" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23">
+      <c r="G14" s="22"/>
+      <c r="H14" s="22">
         <v>1</v>
       </c>
-      <c r="I14" s="23" t="s">
+      <c r="I14" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K14" s="1" t="str">
@@ -3613,26 +3610,26 @@
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="22">
         <v>6</v>
       </c>
-      <c r="E15" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="23" t="s">
+      <c r="E15" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23">
+      <c r="G15" s="22"/>
+      <c r="H15" s="22">
         <v>1</v>
       </c>
-      <c r="I15" s="23" t="s">
+      <c r="I15" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K15" s="1" t="str">
@@ -3641,26 +3638,26 @@
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="22">
         <v>8</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="23" t="s">
+      <c r="E16" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23">
+      <c r="G16" s="22"/>
+      <c r="H16" s="22">
         <v>1</v>
       </c>
-      <c r="I16" s="23" t="s">
+      <c r="I16" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K16" s="1" t="str">
@@ -3669,26 +3666,26 @@
       </c>
     </row>
     <row r="17" spans="2:11">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="22">
         <v>20</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="23" t="s">
+      <c r="E17" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23">
+      <c r="G17" s="22"/>
+      <c r="H17" s="22">
         <v>1</v>
       </c>
-      <c r="I17" s="23" t="s">
+      <c r="I17" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K17" s="1" t="str">
@@ -3697,26 +3694,26 @@
       </c>
     </row>
     <row r="18" spans="2:11">
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="22">
         <v>20</v>
       </c>
-      <c r="E18" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F18" s="23" t="s">
+      <c r="E18" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="23">
+      <c r="G18" s="22"/>
+      <c r="H18" s="22">
         <v>1</v>
       </c>
-      <c r="I18" s="23" t="s">
+      <c r="I18" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="1" t="str">
@@ -3725,7 +3722,7 @@
       </c>
     </row>
     <row r="19" spans="9:11">
-      <c r="I19" s="23" t="s">
+      <c r="I19" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K19" s="1" t="str">
@@ -3734,28 +3731,28 @@
       </c>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="22">
         <v>10</v>
       </c>
-      <c r="E20" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F20" s="23" t="s">
+      <c r="E20" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="23" t="s">
+      <c r="G20" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="22">
         <v>1</v>
       </c>
-      <c r="I20" s="23" t="s">
+      <c r="I20" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K20" s="1" t="str">
@@ -3764,28 +3761,28 @@
       </c>
     </row>
     <row r="21" spans="2:11">
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="22">
         <v>8</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F21" s="23" t="s">
+      <c r="E21" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="22">
         <v>1</v>
       </c>
-      <c r="I21" s="23" t="s">
+      <c r="I21" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K21" s="1" t="str">
@@ -3794,28 +3791,28 @@
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="22">
         <v>14</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="23" t="s">
+      <c r="E22" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="22">
         <v>1</v>
       </c>
-      <c r="I22" s="23" t="s">
+      <c r="I22" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K22" s="1" t="str">
@@ -3824,28 +3821,28 @@
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="22">
         <v>16</v>
       </c>
-      <c r="E23" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="23" t="s">
+      <c r="E23" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="23" t="s">
+      <c r="G23" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="22">
         <v>1</v>
       </c>
-      <c r="I23" s="23" t="s">
+      <c r="I23" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K23" s="1" t="str">
@@ -3854,7 +3851,7 @@
       </c>
     </row>
     <row r="24" spans="9:11">
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K24" s="1" t="str">
@@ -3863,28 +3860,28 @@
       </c>
     </row>
     <row r="25" spans="2:11">
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="22">
         <v>15</v>
       </c>
-      <c r="E25" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="23" t="s">
+      <c r="E25" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="23" t="s">
+      <c r="G25" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="22">
         <v>1</v>
       </c>
-      <c r="I25" s="23" t="s">
+      <c r="I25" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K25" s="1" t="str">
@@ -3893,7 +3890,7 @@
       </c>
     </row>
     <row r="26" spans="9:11">
-      <c r="I26" s="23" t="s">
+      <c r="I26" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K26" s="1" t="str">
@@ -3902,28 +3899,28 @@
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="22">
         <v>20</v>
       </c>
-      <c r="E27" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="23" t="s">
+      <c r="E27" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="22">
         <v>1</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="I27" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K27" s="1" t="str">
@@ -3932,7 +3929,7 @@
       </c>
     </row>
     <row r="28" spans="9:11">
-      <c r="I28" s="23" t="s">
+      <c r="I28" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K28" s="1" t="str">
@@ -3941,26 +3938,26 @@
       </c>
     </row>
     <row r="29" spans="2:11">
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="22">
         <v>30</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F29" s="23" t="s">
+      <c r="E29" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23">
+      <c r="G29" s="22"/>
+      <c r="H29" s="22">
         <v>1</v>
       </c>
-      <c r="I29" s="23" t="s">
+      <c r="I29" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K29" s="1" t="str">
@@ -3969,26 +3966,26 @@
       </c>
     </row>
     <row r="30" spans="2:11">
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="D30" s="23">
+      <c r="D30" s="22">
         <v>40</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="23" t="s">
+      <c r="E30" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23">
+      <c r="G30" s="22"/>
+      <c r="H30" s="22">
         <v>1</v>
       </c>
-      <c r="I30" s="23" t="s">
+      <c r="I30" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K30" s="1" t="str">
@@ -3997,26 +3994,26 @@
       </c>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="22">
         <v>30</v>
       </c>
-      <c r="E31" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F31" s="23" t="s">
+      <c r="E31" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23">
+      <c r="G31" s="22"/>
+      <c r="H31" s="22">
         <v>1</v>
       </c>
-      <c r="I31" s="23" t="s">
+      <c r="I31" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K31" s="1" t="str">
@@ -4025,7 +4022,7 @@
       </c>
     </row>
     <row r="32" spans="9:11">
-      <c r="I32" s="23" t="s">
+      <c r="I32" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K32" s="1" t="str">
@@ -4034,7 +4031,7 @@
       </c>
     </row>
     <row r="33" spans="9:11">
-      <c r="I33" s="23" t="s">
+      <c r="I33" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K33" s="1" t="str">
@@ -4043,28 +4040,28 @@
       </c>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="22">
         <v>20</v>
       </c>
-      <c r="E34" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="23" t="s">
+      <c r="E34" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="G34" s="23" t="s">
+      <c r="G34" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="22">
         <v>1</v>
       </c>
-      <c r="I34" s="23" t="s">
+      <c r="I34" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K34" s="1" t="str">
@@ -4073,7 +4070,7 @@
       </c>
     </row>
     <row r="35" spans="9:11">
-      <c r="I35" s="23" t="s">
+      <c r="I35" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K35" s="1" t="str">
@@ -4082,7 +4079,7 @@
       </c>
     </row>
     <row r="36" spans="9:11">
-      <c r="I36" s="23" t="s">
+      <c r="I36" s="22" t="s">
         <v>30</v>
       </c>
       <c r="K36" s="1" t="str">
@@ -4091,26 +4088,26 @@
       </c>
     </row>
     <row r="37" spans="2:11">
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="22">
         <v>30</v>
       </c>
-      <c r="E37" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F37" s="23" t="s">
+      <c r="E37" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="23">
+      <c r="G37" s="22"/>
+      <c r="H37" s="22">
         <v>1</v>
       </c>
-      <c r="I37" s="23" t="s">
+      <c r="I37" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K37" s="1" t="str">
@@ -4119,7 +4116,7 @@
       </c>
     </row>
     <row r="38" spans="9:11">
-      <c r="I38" s="23" t="s">
+      <c r="I38" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K38" s="1" t="str">
@@ -4128,28 +4125,28 @@
       </c>
     </row>
     <row r="39" spans="2:11">
-      <c r="B39" s="23" t="s">
+      <c r="B39" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="22">
         <v>20</v>
       </c>
-      <c r="E39" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F39" s="23" t="s">
+      <c r="E39" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="G39" s="23" t="s">
+      <c r="G39" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="22">
         <v>1</v>
       </c>
-      <c r="I39" s="23" t="s">
+      <c r="I39" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K39" s="1" t="str">
@@ -4158,7 +4155,7 @@
       </c>
     </row>
     <row r="40" spans="9:11">
-      <c r="I40" s="23" t="s">
+      <c r="I40" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K40" s="1" t="str">
@@ -4167,28 +4164,28 @@
       </c>
     </row>
     <row r="41" spans="2:11">
-      <c r="B41" s="23" t="s">
+      <c r="B41" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="23" t="s">
+      <c r="C41" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="22">
         <v>25</v>
       </c>
-      <c r="E41" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F41" s="23" t="s">
+      <c r="E41" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="G41" s="23" t="s">
+      <c r="G41" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="22">
         <v>1</v>
       </c>
-      <c r="I41" s="23" t="s">
+      <c r="I41" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K41" s="1" t="str">
@@ -4197,7 +4194,7 @@
       </c>
     </row>
     <row r="42" spans="9:11">
-      <c r="I42" s="23" t="s">
+      <c r="I42" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K42" s="1" t="str">
@@ -4206,28 +4203,28 @@
       </c>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="23" t="s">
+      <c r="B43" s="22" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="23" t="s">
+      <c r="C43" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D43" s="23">
+      <c r="D43" s="22">
         <v>20</v>
       </c>
-      <c r="E43" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" s="23" t="s">
+      <c r="E43" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="G43" s="23" t="s">
+      <c r="G43" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H43" s="23">
+      <c r="H43" s="22">
         <v>1</v>
       </c>
-      <c r="I43" s="23" t="s">
+      <c r="I43" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K43" s="1" t="str">
@@ -4236,7 +4233,7 @@
       </c>
     </row>
     <row r="44" spans="9:11">
-      <c r="I44" s="23" t="s">
+      <c r="I44" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K44" s="1" t="str">
@@ -4245,28 +4242,28 @@
       </c>
     </row>
     <row r="45" spans="2:11">
-      <c r="B45" s="23" t="s">
+      <c r="B45" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="D45" s="23">
+      <c r="D45" s="22">
         <v>20</v>
       </c>
-      <c r="E45" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F45" s="23" t="s">
+      <c r="E45" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="G45" s="23" t="s">
+      <c r="G45" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H45" s="23">
+      <c r="H45" s="22">
         <v>1</v>
       </c>
-      <c r="I45" s="23" t="s">
+      <c r="I45" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K45" s="1" t="str">
@@ -4275,7 +4272,7 @@
       </c>
     </row>
     <row r="46" spans="9:11">
-      <c r="I46" s="23" t="s">
+      <c r="I46" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K46" s="1" t="str">
@@ -4284,28 +4281,28 @@
       </c>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="22">
         <v>50</v>
       </c>
-      <c r="E47" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="23" t="s">
+      <c r="E47" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>123</v>
       </c>
-      <c r="G47" s="23" t="s">
+      <c r="G47" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="22">
         <v>1</v>
       </c>
-      <c r="I47" s="23" t="s">
+      <c r="I47" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K47" s="1" t="str">
@@ -4314,7 +4311,7 @@
       </c>
     </row>
     <row r="48" spans="9:11">
-      <c r="I48" s="23" t="s">
+      <c r="I48" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K48" s="1" t="str">
@@ -4323,26 +4320,26 @@
       </c>
     </row>
     <row r="49" spans="2:11">
-      <c r="B49" s="23" t="s">
+      <c r="B49" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="22">
         <v>40</v>
       </c>
-      <c r="E49" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F49" s="23" t="s">
+      <c r="E49" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23">
+      <c r="G49" s="22"/>
+      <c r="H49" s="22">
         <v>1</v>
       </c>
-      <c r="I49" s="23" t="s">
+      <c r="I49" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K49" s="1" t="str">
@@ -4351,7 +4348,7 @@
       </c>
     </row>
     <row r="50" spans="9:11">
-      <c r="I50" s="23" t="s">
+      <c r="I50" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K50" s="1" t="str">
@@ -4360,28 +4357,28 @@
       </c>
     </row>
     <row r="51" spans="2:11">
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="22">
         <v>30</v>
       </c>
-      <c r="E51" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F51" s="23" t="s">
+      <c r="E51" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="G51" s="23" t="s">
+      <c r="G51" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="22">
         <v>1</v>
       </c>
-      <c r="I51" s="23" t="s">
+      <c r="I51" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K51" s="1" t="str">
@@ -4390,7 +4387,7 @@
       </c>
     </row>
     <row r="52" spans="9:11">
-      <c r="I52" s="23" t="s">
+      <c r="I52" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K52" s="1" t="str">
@@ -4399,28 +4396,28 @@
       </c>
     </row>
     <row r="53" spans="2:11">
-      <c r="B53" s="23" t="s">
+      <c r="B53" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="22">
         <v>50</v>
       </c>
-      <c r="E53" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F53" s="23" t="s">
+      <c r="E53" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="G53" s="23" t="s">
+      <c r="G53" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="22">
         <v>1</v>
       </c>
-      <c r="I53" s="23" t="s">
+      <c r="I53" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K53" s="1" t="str">
@@ -4429,7 +4426,7 @@
       </c>
     </row>
     <row r="54" spans="9:11">
-      <c r="I54" s="23" t="s">
+      <c r="I54" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K54" s="1" t="str">
@@ -4438,28 +4435,28 @@
       </c>
     </row>
     <row r="55" spans="2:11">
-      <c r="B55" s="23" t="s">
+      <c r="B55" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="22">
         <v>40</v>
       </c>
-      <c r="E55" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" s="23" t="s">
+      <c r="E55" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="G55" s="23" t="s">
+      <c r="G55" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="22">
         <v>1</v>
       </c>
-      <c r="I55" s="23" t="s">
+      <c r="I55" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K55" s="1" t="str">
@@ -4468,7 +4465,7 @@
       </c>
     </row>
     <row r="56" spans="9:11">
-      <c r="I56" s="23" t="s">
+      <c r="I56" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K56" s="1" t="str">
@@ -4477,7 +4474,7 @@
       </c>
     </row>
     <row r="57" spans="9:11">
-      <c r="I57" s="23" t="s">
+      <c r="I57" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K57" s="1" t="str">
@@ -4486,26 +4483,26 @@
       </c>
     </row>
     <row r="58" spans="2:11">
-      <c r="B58" s="23" t="s">
+      <c r="B58" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="23">
+      <c r="D58" s="22">
         <v>30</v>
       </c>
-      <c r="E58" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" s="23" t="s">
+      <c r="E58" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="G58" s="23"/>
-      <c r="H58" s="23">
+      <c r="G58" s="22"/>
+      <c r="H58" s="22">
         <v>1</v>
       </c>
-      <c r="I58" s="23" t="s">
+      <c r="I58" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K58" s="1" t="str">
@@ -4514,7 +4511,7 @@
       </c>
     </row>
     <row r="59" spans="9:11">
-      <c r="I59" s="23" t="s">
+      <c r="I59" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K59" s="1" t="str">
@@ -4523,7 +4520,7 @@
       </c>
     </row>
     <row r="60" spans="9:11">
-      <c r="I60" s="23" t="s">
+      <c r="I60" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K60" s="1" t="str">
@@ -4532,28 +4529,28 @@
       </c>
     </row>
     <row r="61" spans="2:11">
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="22">
         <v>20</v>
       </c>
-      <c r="E61" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" s="23" t="s">
+      <c r="E61" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="G61" s="23" t="s">
+      <c r="G61" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="22">
         <v>1</v>
       </c>
-      <c r="I61" s="23" t="s">
+      <c r="I61" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K61" s="1" t="str">
@@ -4562,7 +4559,7 @@
       </c>
     </row>
     <row r="62" spans="9:11">
-      <c r="I62" s="23" t="s">
+      <c r="I62" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K62" s="1" t="str">
@@ -4571,28 +4568,28 @@
       </c>
     </row>
     <row r="63" spans="2:11">
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="22">
         <v>30</v>
       </c>
-      <c r="E63" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" s="23" t="s">
+      <c r="E63" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="G63" s="23" t="s">
+      <c r="G63" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="22">
         <v>1</v>
       </c>
-      <c r="I63" s="23" t="s">
+      <c r="I63" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K63" s="1" t="str">
@@ -4601,7 +4598,7 @@
       </c>
     </row>
     <row r="64" spans="9:11">
-      <c r="I64" s="23" t="s">
+      <c r="I64" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K64" s="1" t="str">
@@ -4610,28 +4607,28 @@
       </c>
     </row>
     <row r="65" spans="2:11">
-      <c r="B65" s="23" t="s">
+      <c r="B65" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="22">
         <v>50</v>
       </c>
-      <c r="E65" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" s="23" t="s">
+      <c r="E65" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="G65" s="23" t="s">
+      <c r="G65" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="22">
         <v>1</v>
       </c>
-      <c r="I65" s="23" t="s">
+      <c r="I65" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K65" s="1" t="str">
@@ -4640,7 +4637,7 @@
       </c>
     </row>
     <row r="66" spans="9:11">
-      <c r="I66" s="23" t="s">
+      <c r="I66" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K66" s="1" t="str">
@@ -4649,7 +4646,7 @@
       </c>
     </row>
     <row r="67" spans="9:11">
-      <c r="I67" s="23" t="s">
+      <c r="I67" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K67" s="1" t="str">
@@ -4658,28 +4655,28 @@
       </c>
     </row>
     <row r="68" spans="2:11">
-      <c r="B68" s="23" t="s">
+      <c r="B68" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="D68" s="23">
+      <c r="D68" s="22">
         <v>40</v>
       </c>
-      <c r="E68" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" s="23" t="s">
+      <c r="E68" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="22">
         <v>1</v>
       </c>
-      <c r="I68" s="23" t="s">
+      <c r="I68" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K68" s="1" t="str">
@@ -4688,7 +4685,7 @@
       </c>
     </row>
     <row r="69" spans="9:11">
-      <c r="I69" s="23" t="s">
+      <c r="I69" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K69" s="1" t="str">
@@ -4697,7 +4694,7 @@
       </c>
     </row>
     <row r="70" spans="9:11">
-      <c r="I70" s="23" t="s">
+      <c r="I70" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K70" s="1" t="str">
@@ -4706,28 +4703,28 @@
       </c>
     </row>
     <row r="71" spans="2:11">
-      <c r="B71" s="23" t="s">
+      <c r="B71" s="22" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D71" s="22">
         <v>30</v>
       </c>
-      <c r="E71" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" s="23" t="s">
+      <c r="E71" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="G71" s="23" t="s">
+      <c r="G71" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H71" s="23">
+      <c r="H71" s="22">
         <v>1</v>
       </c>
-      <c r="I71" s="23" t="s">
+      <c r="I71" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K71" s="1" t="str">
@@ -4736,7 +4733,7 @@
       </c>
     </row>
     <row r="72" spans="9:11">
-      <c r="I72" s="23" t="s">
+      <c r="I72" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K72" s="1" t="str">
@@ -4745,26 +4742,26 @@
       </c>
     </row>
     <row r="73" spans="2:11">
-      <c r="B73" s="23" t="s">
+      <c r="B73" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D73" s="22">
         <v>20</v>
       </c>
-      <c r="E73" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F73" s="23" t="s">
+      <c r="E73" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="G73" s="23"/>
-      <c r="H73" s="23">
+      <c r="G73" s="22"/>
+      <c r="H73" s="22">
         <v>1</v>
       </c>
-      <c r="I73" s="23" t="s">
+      <c r="I73" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K73" s="1" t="str">
@@ -4773,7 +4770,7 @@
       </c>
     </row>
     <row r="74" spans="9:11">
-      <c r="I74" s="23" t="s">
+      <c r="I74" s="22" t="s">
         <v>156</v>
       </c>
       <c r="K74" s="1" t="str">
@@ -4782,28 +4779,28 @@
       </c>
     </row>
     <row r="75" spans="2:11">
-      <c r="B75" s="23" t="s">
+      <c r="B75" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="D75" s="23">
+      <c r="D75" s="22">
         <v>30</v>
       </c>
-      <c r="E75" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F75" s="23" t="s">
+      <c r="E75" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="G75" s="23" t="s">
+      <c r="G75" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H75" s="23">
+      <c r="H75" s="22">
         <v>1</v>
       </c>
-      <c r="I75" s="23" t="s">
+      <c r="I75" s="22" t="s">
         <v>160</v>
       </c>
       <c r="K75" s="1" t="str">
@@ -4812,7 +4809,7 @@
       </c>
     </row>
     <row r="76" spans="9:11">
-      <c r="I76" s="23" t="s">
+      <c r="I76" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K76" s="1" t="str">
@@ -4821,28 +4818,28 @@
       </c>
     </row>
     <row r="77" spans="2:11">
-      <c r="B77" s="23" t="s">
+      <c r="B77" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="D77" s="23">
+      <c r="D77" s="22">
         <v>40</v>
       </c>
-      <c r="E77" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F77" s="23" t="s">
+      <c r="E77" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="G77" s="23" t="s">
+      <c r="G77" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H77" s="23">
+      <c r="H77" s="22">
         <v>1</v>
       </c>
-      <c r="I77" s="23" t="s">
+      <c r="I77" s="22" t="s">
         <v>70</v>
       </c>
       <c r="K77" s="1" t="str">
@@ -4851,7 +4848,7 @@
       </c>
     </row>
     <row r="78" spans="9:11">
-      <c r="I78" s="23" t="s">
+      <c r="I78" s="22" t="s">
         <v>156</v>
       </c>
       <c r="K78" s="1" t="str">
@@ -4860,7 +4857,7 @@
       </c>
     </row>
     <row r="79" spans="9:11">
-      <c r="I79" s="23" t="s">
+      <c r="I79" s="22" t="s">
         <v>156</v>
       </c>
       <c r="K79" s="1" t="str">
@@ -4869,28 +4866,28 @@
       </c>
     </row>
     <row r="80" spans="2:11">
-      <c r="B80" s="23" t="s">
+      <c r="B80" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="D80" s="23">
+      <c r="D80" s="22">
         <v>100</v>
       </c>
-      <c r="E80" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F80" s="23" t="s">
+      <c r="E80" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="G80" s="23" t="s">
+      <c r="G80" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H80" s="23">
+      <c r="H80" s="22">
         <v>1</v>
       </c>
-      <c r="I80" s="23" t="s">
+      <c r="I80" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K80" s="1" t="str">
@@ -4899,7 +4896,7 @@
       </c>
     </row>
     <row r="81" spans="9:11">
-      <c r="I81" s="23" t="s">
+      <c r="I81" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K81" s="1" t="str">
@@ -4908,7 +4905,7 @@
       </c>
     </row>
     <row r="82" spans="9:11">
-      <c r="I82" s="23" t="s">
+      <c r="I82" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K82" s="1" t="str">
@@ -4917,7 +4914,7 @@
       </c>
     </row>
     <row r="83" spans="9:11">
-      <c r="I83" s="23" t="s">
+      <c r="I83" s="22" t="s">
         <v>167</v>
       </c>
       <c r="K83" s="1" t="str">
@@ -4926,7 +4923,7 @@
       </c>
     </row>
     <row r="84" spans="9:11">
-      <c r="I84" s="23" t="s">
+      <c r="I84" s="22" t="s">
         <v>167</v>
       </c>
       <c r="K84" s="1" t="str">
@@ -4935,28 +4932,28 @@
       </c>
     </row>
     <row r="85" spans="2:11">
-      <c r="B85" s="23" t="s">
+      <c r="B85" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="D85" s="23">
+      <c r="D85" s="22">
         <v>80</v>
       </c>
-      <c r="E85" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85" s="23" t="s">
+      <c r="E85" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="G85" s="23" t="s">
+      <c r="G85" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H85" s="23">
+      <c r="H85" s="22">
         <v>1</v>
       </c>
-      <c r="I85" s="23" t="s">
+      <c r="I85" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K85" s="1" t="str">
@@ -4965,7 +4962,7 @@
       </c>
     </row>
     <row r="86" spans="9:11">
-      <c r="I86" s="23" t="s">
+      <c r="I86" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K86" s="1" t="str">
@@ -4974,7 +4971,7 @@
       </c>
     </row>
     <row r="87" spans="9:11">
-      <c r="I87" s="23" t="s">
+      <c r="I87" s="22" t="s">
         <v>96</v>
       </c>
       <c r="K87" s="1" t="str">
@@ -4983,28 +4980,28 @@
       </c>
     </row>
     <row r="88" spans="2:11">
-      <c r="B88" s="23" t="s">
+      <c r="B88" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="D88" s="23">
+      <c r="D88" s="22">
         <v>140</v>
       </c>
-      <c r="E88" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88" s="23" t="s">
+      <c r="E88" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="F88" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="G88" s="23" t="s">
+      <c r="G88" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="H88" s="23">
+      <c r="H88" s="22">
         <v>1</v>
       </c>
-      <c r="I88" s="23" t="s">
+      <c r="I88" s="22" t="s">
         <v>174</v>
       </c>
       <c r="K88" s="1" t="str">
@@ -5013,17 +5010,17 @@
       </c>
     </row>
     <row r="89" spans="9:9">
-      <c r="I89" s="23" t="s">
+      <c r="I89" s="22" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="90" spans="9:9">
-      <c r="I90" s="23" t="s">
+      <c r="I90" s="22" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="91" spans="9:9">
-      <c r="I91" s="23" t="s">
+      <c r="I91" s="22" t="s">
         <v>175</v>
       </c>
     </row>
@@ -6508,213 +6505,213 @@
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="21" customWidth="1"/>
-    <col min="2" max="2" width="9.30769230769231" style="21" customWidth="1"/>
-    <col min="3" max="3" width="10.3076923076923" style="21" customWidth="1"/>
-    <col min="4" max="4" width="65.1538461538462" style="21" customWidth="1"/>
-    <col min="5" max="5" width="17.8461538461538" style="21" customWidth="1"/>
-    <col min="6" max="6" width="11.9230769230769" style="21" customWidth="1"/>
-    <col min="7" max="7" width="12.6153846153846" style="21" customWidth="1"/>
-    <col min="8" max="8" width="14.25" style="21" customWidth="1"/>
-    <col min="9" max="9" width="58.6538461538462" style="21" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="21"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.30769230769231" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3076923076923" style="1" customWidth="1"/>
+    <col min="4" max="4" width="65.1538461538462" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.8461538461538" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.9230769230769" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6153846153846" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="58.6538461538462" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="1" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="1" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="H3" s="21" t="s">
+      <c r="H3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="2:9">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="I4" s="1" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="1" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="6" ht="34" spans="2:9">
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="1" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="1" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:9">
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="1" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="9" ht="51" spans="2:9">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="1" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7285,7 +7282,7 @@
       <c r="P8" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="Q8" s="21" t="s">
+      <c r="Q8" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -7534,7 +7531,7 @@
       <c r="P14" t="s">
         <v>396</v>
       </c>
-      <c r="Q14" s="21" t="s">
+      <c r="Q14" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -7716,7 +7713,7 @@
       <c r="P18" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="Q18" s="21" t="s">
+      <c r="Q18" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -7842,7 +7839,7 @@
       <c r="P21" t="s">
         <v>396</v>
       </c>
-      <c r="Q21" s="21" t="s">
+      <c r="Q21" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -8150,7 +8147,7 @@
       <c r="P28" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="Q28" s="21" t="s">
+      <c r="Q28" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -8487,7 +8484,7 @@
       <c r="P36" t="s">
         <v>443</v>
       </c>
-      <c r="Q36" s="21" t="s">
+      <c r="Q36" s="1" t="s">
         <v>386</v>
       </c>
       <c r="R36" t="s">
@@ -8672,7 +8669,7 @@
       <c r="P40" s="19" t="s">
         <v>448</v>
       </c>
-      <c r="Q40" s="21" t="s">
+      <c r="Q40" s="1" t="s">
         <v>386</v>
       </c>
       <c r="R40" t="s">
@@ -9015,7 +9012,7 @@
       <c r="P48" t="s">
         <v>396</v>
       </c>
-      <c r="Q48" s="21" t="s">
+      <c r="Q48" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -9226,7 +9223,7 @@
       <c r="P53" t="s">
         <v>396</v>
       </c>
-      <c r="Q53" s="21" t="s">
+      <c r="Q53" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -9525,7 +9522,7 @@
       <c r="P60" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="Q60" s="21" t="s">
+      <c r="Q60" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -9619,7 +9616,7 @@
       <c r="P62" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="Q62" s="21" t="s">
+      <c r="Q62" s="1" t="s">
         <v>386</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="5"/>
+    <workbookView windowHeight="15200" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2053" uniqueCount="678">
   <si>
     <t>##var</t>
   </si>
@@ -128,6 +128,9 @@
     <t>sk_macaron</t>
   </si>
   <si>
+    <t>0周</t>
+  </si>
+  <si>
     <t>pudding</t>
   </si>
   <si>
@@ -137,6 +140,9 @@
     <t>sk_pudding</t>
   </si>
   <si>
+    <t>1周</t>
+  </si>
+  <si>
     <t>puff</t>
   </si>
   <si>
@@ -146,6 +152,9 @@
     <t>sk_puff</t>
   </si>
   <si>
+    <t>2周</t>
+  </si>
+  <si>
     <t>eggtart</t>
   </si>
   <si>
@@ -155,6 +164,9 @@
     <t>sk_eggtart</t>
   </si>
   <si>
+    <t>3周</t>
+  </si>
+  <si>
     <t>mochi</t>
   </si>
   <si>
@@ -162,6 +174,9 @@
   </si>
   <si>
     <t>sk_mochi</t>
+  </si>
+  <si>
+    <t>4周</t>
   </si>
   <si>
     <t>daifuku</t>
@@ -3168,7 +3183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:T91"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -3183,9 +3198,8 @@
     <col min="10" max="11" width="9" style="1" customWidth="1"/>
     <col min="12" max="12" width="11.6923076923077" style="1" customWidth="1"/>
     <col min="13" max="14" width="6.89423076923077" style="1" customWidth="1"/>
-    <col min="15" max="15" width="73.3076923076923" style="1" customWidth="1"/>
-    <col min="16" max="16" width="84.6153846153846" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="15" max="20" width="7.04807692307692" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -3323,7 +3337,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="2:20">
       <c r="B5" s="22" t="s">
         <v>31</v>
       </c>
@@ -3352,13 +3366,40 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="6" spans="2:11">
+      <c r="L5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="1">
+        <v>10</v>
+      </c>
+      <c r="N5" s="1">
+        <v>11</v>
+      </c>
+      <c r="O5" s="1">
+        <v>12</v>
+      </c>
+      <c r="P5" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>14</v>
+      </c>
+      <c r="R5" s="1">
+        <v>15</v>
+      </c>
+      <c r="S5" s="1">
+        <v>16</v>
+      </c>
+      <c r="T5" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20">
       <c r="B6" s="22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="22">
         <v>30</v>
@@ -3367,7 +3408,7 @@
         <v>27</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="22" t="s">
         <v>29</v>
@@ -3382,13 +3423,40 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="2:11">
+      <c r="L6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M6" s="1">
+        <v>20</v>
+      </c>
+      <c r="N6" s="1">
+        <v>21</v>
+      </c>
+      <c r="O6" s="1">
+        <v>22</v>
+      </c>
+      <c r="P6" s="1">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>24</v>
+      </c>
+      <c r="R6" s="1">
+        <v>25</v>
+      </c>
+      <c r="S6" s="1">
+        <v>26</v>
+      </c>
+      <c r="T6" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:20">
       <c r="B7" s="22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D7" s="22">
         <v>8</v>
@@ -3397,7 +3465,7 @@
         <v>27</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" s="22" t="s">
         <v>29</v>
@@ -3412,13 +3480,40 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="2:11">
+      <c r="L7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7" s="1">
+        <v>30</v>
+      </c>
+      <c r="N7" s="1">
+        <v>31</v>
+      </c>
+      <c r="O7" s="1">
+        <v>32</v>
+      </c>
+      <c r="P7" s="1">
+        <v>33</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>34</v>
+      </c>
+      <c r="R7" s="1">
+        <v>35</v>
+      </c>
+      <c r="S7" s="1">
+        <v>36</v>
+      </c>
+      <c r="T7" s="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="2:20">
       <c r="B8" s="22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D8" s="22">
         <v>6</v>
@@ -3427,7 +3522,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G8" s="22"/>
       <c r="H8" s="22">
@@ -3440,13 +3535,40 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="2:11">
+      <c r="L8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M8" s="1">
+        <v>40</v>
+      </c>
+      <c r="N8" s="1">
+        <v>41</v>
+      </c>
+      <c r="O8" s="1">
+        <v>42</v>
+      </c>
+      <c r="P8" s="1">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>44</v>
+      </c>
+      <c r="R8" s="1">
+        <v>45</v>
+      </c>
+      <c r="S8" s="1">
+        <v>46</v>
+      </c>
+      <c r="T8" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="2:20">
       <c r="B9" s="22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D9" s="22">
         <v>10</v>
@@ -3455,7 +3577,7 @@
         <v>27</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="22">
@@ -3468,13 +3590,40 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
+      <c r="L9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="1">
+        <v>50</v>
+      </c>
+      <c r="N9" s="1">
+        <v>51</v>
+      </c>
+      <c r="O9" s="1">
+        <v>52</v>
+      </c>
+      <c r="P9" s="1">
+        <v>53</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>54</v>
+      </c>
+      <c r="R9" s="1">
+        <v>55</v>
+      </c>
+      <c r="S9" s="1">
+        <v>56</v>
+      </c>
+      <c r="T9" s="1">
+        <v>57</v>
+      </c>
     </row>
     <row r="10" spans="2:11">
       <c r="B10" s="22" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D10" s="22">
         <v>6</v>
@@ -3483,7 +3632,7 @@
         <v>27</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="22">
@@ -3499,10 +3648,10 @@
     </row>
     <row r="11" spans="2:11">
       <c r="B11" s="22" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D11" s="22">
         <v>10</v>
@@ -3511,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="22">
@@ -3527,10 +3676,10 @@
     </row>
     <row r="12" spans="2:11">
       <c r="B12" s="22" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D12" s="22">
         <v>4</v>
@@ -3539,7 +3688,7 @@
         <v>27</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G12" s="22"/>
       <c r="H12" s="22">
@@ -3555,10 +3704,10 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="22" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D13" s="22">
         <v>10</v>
@@ -3567,7 +3716,7 @@
         <v>27</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G13" s="22"/>
       <c r="H13" s="22">
@@ -3583,10 +3732,10 @@
     </row>
     <row r="14" spans="2:11">
       <c r="B14" s="22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D14" s="22">
         <v>10</v>
@@ -3595,7 +3744,7 @@
         <v>27</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G14" s="22"/>
       <c r="H14" s="22">
@@ -3611,10 +3760,10 @@
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="22" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D15" s="22">
         <v>6</v>
@@ -3623,7 +3772,7 @@
         <v>27</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G15" s="22"/>
       <c r="H15" s="22">
@@ -3639,10 +3788,10 @@
     </row>
     <row r="16" spans="2:11">
       <c r="B16" s="22" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D16" s="22">
         <v>8</v>
@@ -3651,7 +3800,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G16" s="22"/>
       <c r="H16" s="22">
@@ -3667,10 +3816,10 @@
     </row>
     <row r="17" spans="2:11">
       <c r="B17" s="22" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D17" s="22">
         <v>20</v>
@@ -3679,14 +3828,14 @@
         <v>27</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G17" s="22"/>
       <c r="H17" s="22">
         <v>1</v>
       </c>
       <c r="I17" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K17" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3695,10 +3844,10 @@
     </row>
     <row r="18" spans="2:11">
       <c r="B18" s="22" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D18" s="22">
         <v>20</v>
@@ -3707,7 +3856,7 @@
         <v>27</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="G18" s="22"/>
       <c r="H18" s="22">
@@ -3732,10 +3881,10 @@
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="22" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D20" s="22">
         <v>10</v>
@@ -3744,7 +3893,7 @@
         <v>27</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G20" s="22" t="s">
         <v>29</v>
@@ -3753,7 +3902,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K20" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3762,10 +3911,10 @@
     </row>
     <row r="21" spans="2:11">
       <c r="B21" s="22" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D21" s="22">
         <v>8</v>
@@ -3774,7 +3923,7 @@
         <v>27</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G21" s="22" t="s">
         <v>29</v>
@@ -3783,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K21" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3792,10 +3941,10 @@
     </row>
     <row r="22" spans="2:11">
       <c r="B22" s="22" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D22" s="22">
         <v>14</v>
@@ -3804,16 +3953,16 @@
         <v>27</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H22" s="22">
         <v>1</v>
       </c>
       <c r="I22" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K22" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3822,10 +3971,10 @@
     </row>
     <row r="23" spans="2:11">
       <c r="B23" s="22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D23" s="22">
         <v>16</v>
@@ -3834,10 +3983,10 @@
         <v>27</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H23" s="22">
         <v>1</v>
@@ -3861,10 +4010,10 @@
     </row>
     <row r="25" spans="2:11">
       <c r="B25" s="22" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D25" s="22">
         <v>15</v>
@@ -3873,7 +4022,7 @@
         <v>27</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G25" s="22" t="s">
         <v>29</v>
@@ -3900,10 +4049,10 @@
     </row>
     <row r="27" spans="2:11">
       <c r="B27" s="22" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D27" s="22">
         <v>20</v>
@@ -3912,7 +4061,7 @@
         <v>27</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="G27" s="22" t="s">
         <v>29</v>
@@ -3939,10 +4088,10 @@
     </row>
     <row r="29" spans="2:11">
       <c r="B29" s="22" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D29" s="22">
         <v>30</v>
@@ -3951,14 +4100,14 @@
         <v>27</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G29" s="22"/>
       <c r="H29" s="22">
         <v>1</v>
       </c>
       <c r="I29" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K29" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3967,10 +4116,10 @@
     </row>
     <row r="30" spans="2:11">
       <c r="B30" s="22" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D30" s="22">
         <v>40</v>
@@ -3979,14 +4128,14 @@
         <v>27</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G30" s="22"/>
       <c r="H30" s="22">
         <v>1</v>
       </c>
       <c r="I30" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K30" s="1" t="str">
         <f t="shared" si="0"/>
@@ -3995,10 +4144,10 @@
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="22" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D31" s="22">
         <v>30</v>
@@ -4007,7 +4156,7 @@
         <v>27</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G31" s="22"/>
       <c r="H31" s="22">
@@ -4041,10 +4190,10 @@
     </row>
     <row r="34" spans="2:11">
       <c r="B34" s="22" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D34" s="22">
         <v>20</v>
@@ -4053,7 +4202,7 @@
         <v>27</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G34" s="22" t="s">
         <v>29</v>
@@ -4089,10 +4238,10 @@
     </row>
     <row r="37" spans="2:11">
       <c r="B37" s="22" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D37" s="22">
         <v>30</v>
@@ -4101,14 +4250,14 @@
         <v>27</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G37" s="22"/>
       <c r="H37" s="22">
         <v>1</v>
       </c>
       <c r="I37" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K37" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4117,7 +4266,7 @@
     </row>
     <row r="38" spans="9:11">
       <c r="I38" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K38" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4126,10 +4275,10 @@
     </row>
     <row r="39" spans="2:11">
       <c r="B39" s="22" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C39" s="22" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D39" s="22">
         <v>20</v>
@@ -4138,7 +4287,7 @@
         <v>27</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G39" s="22" t="s">
         <v>29</v>
@@ -4147,7 +4296,7 @@
         <v>1</v>
       </c>
       <c r="I39" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K39" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4156,7 +4305,7 @@
     </row>
     <row r="40" spans="9:11">
       <c r="I40" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K40" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4165,10 +4314,10 @@
     </row>
     <row r="41" spans="2:11">
       <c r="B41" s="22" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C41" s="22" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D41" s="22">
         <v>25</v>
@@ -4177,7 +4326,7 @@
         <v>27</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G41" s="22" t="s">
         <v>29</v>
@@ -4186,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="I41" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K41" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4195,7 +4344,7 @@
     </row>
     <row r="42" spans="9:11">
       <c r="I42" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K42" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4204,10 +4353,10 @@
     </row>
     <row r="43" spans="2:11">
       <c r="B43" s="22" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C43" s="22" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D43" s="22">
         <v>20</v>
@@ -4216,7 +4365,7 @@
         <v>27</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G43" s="22" t="s">
         <v>29</v>
@@ -4225,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="I43" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K43" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4234,7 +4383,7 @@
     </row>
     <row r="44" spans="9:11">
       <c r="I44" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K44" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4243,10 +4392,10 @@
     </row>
     <row r="45" spans="2:11">
       <c r="B45" s="22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C45" s="22" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D45" s="22">
         <v>20</v>
@@ -4255,7 +4404,7 @@
         <v>27</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G45" s="22" t="s">
         <v>29</v>
@@ -4264,7 +4413,7 @@
         <v>1</v>
       </c>
       <c r="I45" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K45" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4273,7 +4422,7 @@
     </row>
     <row r="46" spans="9:11">
       <c r="I46" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K46" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4282,10 +4431,10 @@
     </row>
     <row r="47" spans="2:11">
       <c r="B47" s="22" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C47" s="22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D47" s="22">
         <v>50</v>
@@ -4294,16 +4443,16 @@
         <v>27</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H47" s="22">
         <v>1</v>
       </c>
       <c r="I47" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K47" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4312,7 +4461,7 @@
     </row>
     <row r="48" spans="9:11">
       <c r="I48" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K48" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4321,10 +4470,10 @@
     </row>
     <row r="49" spans="2:11">
       <c r="B49" s="22" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C49" s="22" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D49" s="22">
         <v>40</v>
@@ -4333,14 +4482,14 @@
         <v>27</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G49" s="22"/>
       <c r="H49" s="22">
         <v>1</v>
       </c>
       <c r="I49" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K49" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4349,7 +4498,7 @@
     </row>
     <row r="50" spans="9:11">
       <c r="I50" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K50" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4358,10 +4507,10 @@
     </row>
     <row r="51" spans="2:11">
       <c r="B51" s="22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C51" s="22" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D51" s="22">
         <v>30</v>
@@ -4370,7 +4519,7 @@
         <v>27</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G51" s="22" t="s">
         <v>29</v>
@@ -4379,7 +4528,7 @@
         <v>1</v>
       </c>
       <c r="I51" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K51" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4388,7 +4537,7 @@
     </row>
     <row r="52" spans="9:11">
       <c r="I52" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K52" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4397,10 +4546,10 @@
     </row>
     <row r="53" spans="2:11">
       <c r="B53" s="22" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C53" s="22" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D53" s="22">
         <v>50</v>
@@ -4409,7 +4558,7 @@
         <v>27</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G53" s="22" t="s">
         <v>29</v>
@@ -4418,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K53" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4427,7 +4576,7 @@
     </row>
     <row r="54" spans="9:11">
       <c r="I54" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K54" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4436,10 +4585,10 @@
     </row>
     <row r="55" spans="2:11">
       <c r="B55" s="22" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C55" s="22" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D55" s="22">
         <v>40</v>
@@ -4448,7 +4597,7 @@
         <v>27</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G55" s="22" t="s">
         <v>29</v>
@@ -4457,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K55" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4466,7 +4615,7 @@
     </row>
     <row r="56" spans="9:11">
       <c r="I56" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K56" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4475,7 +4624,7 @@
     </row>
     <row r="57" spans="9:11">
       <c r="I57" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K57" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4484,10 +4633,10 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" s="22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C58" s="22" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D58" s="22">
         <v>30</v>
@@ -4496,14 +4645,14 @@
         <v>27</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G58" s="22"/>
       <c r="H58" s="22">
         <v>1</v>
       </c>
       <c r="I58" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K58" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4512,7 +4661,7 @@
     </row>
     <row r="59" spans="9:11">
       <c r="I59" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K59" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4521,7 +4670,7 @@
     </row>
     <row r="60" spans="9:11">
       <c r="I60" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K60" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4530,10 +4679,10 @@
     </row>
     <row r="61" spans="2:11">
       <c r="B61" s="22" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C61" s="22" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D61" s="22">
         <v>20</v>
@@ -4542,7 +4691,7 @@
         <v>27</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G61" s="22" t="s">
         <v>29</v>
@@ -4551,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="I61" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K61" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4560,7 +4709,7 @@
     </row>
     <row r="62" spans="9:11">
       <c r="I62" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K62" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4569,10 +4718,10 @@
     </row>
     <row r="63" spans="2:11">
       <c r="B63" s="22" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C63" s="22" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D63" s="22">
         <v>30</v>
@@ -4581,16 +4730,16 @@
         <v>27</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G63" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H63" s="22">
         <v>1</v>
       </c>
       <c r="I63" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K63" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4599,7 +4748,7 @@
     </row>
     <row r="64" spans="9:11">
       <c r="I64" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K64" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4608,10 +4757,10 @@
     </row>
     <row r="65" spans="2:11">
       <c r="B65" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C65" s="22" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D65" s="22">
         <v>50</v>
@@ -4620,7 +4769,7 @@
         <v>27</v>
       </c>
       <c r="F65" s="22" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G65" s="22" t="s">
         <v>29</v>
@@ -4629,7 +4778,7 @@
         <v>1</v>
       </c>
       <c r="I65" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K65" s="1" t="str">
         <f t="shared" ref="K65:K88" si="1">""</f>
@@ -4638,7 +4787,7 @@
     </row>
     <row r="66" spans="9:11">
       <c r="I66" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K66" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4647,7 +4796,7 @@
     </row>
     <row r="67" spans="9:11">
       <c r="I67" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K67" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4656,10 +4805,10 @@
     </row>
     <row r="68" spans="2:11">
       <c r="B68" s="22" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="D68" s="22">
         <v>40</v>
@@ -4668,16 +4817,16 @@
         <v>27</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H68" s="22">
         <v>1</v>
       </c>
       <c r="I68" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K68" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4686,7 +4835,7 @@
     </row>
     <row r="69" spans="9:11">
       <c r="I69" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K69" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4695,7 +4844,7 @@
     </row>
     <row r="70" spans="9:11">
       <c r="I70" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K70" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4704,10 +4853,10 @@
     </row>
     <row r="71" spans="2:11">
       <c r="B71" s="22" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D71" s="22">
         <v>30</v>
@@ -4716,7 +4865,7 @@
         <v>27</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G71" s="22" t="s">
         <v>29</v>
@@ -4725,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K71" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4734,7 +4883,7 @@
     </row>
     <row r="72" spans="9:11">
       <c r="I72" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K72" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4743,10 +4892,10 @@
     </row>
     <row r="73" spans="2:11">
       <c r="B73" s="22" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="D73" s="22">
         <v>20</v>
@@ -4755,14 +4904,14 @@
         <v>27</v>
       </c>
       <c r="F73" s="22" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G73" s="22"/>
       <c r="H73" s="22">
         <v>1</v>
       </c>
       <c r="I73" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K73" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4771,7 +4920,7 @@
     </row>
     <row r="74" spans="9:11">
       <c r="I74" s="22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K74" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4780,10 +4929,10 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" s="22" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D75" s="22">
         <v>30</v>
@@ -4792,7 +4941,7 @@
         <v>27</v>
       </c>
       <c r="F75" s="22" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G75" s="22" t="s">
         <v>29</v>
@@ -4801,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="I75" s="22" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K75" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4810,7 +4959,7 @@
     </row>
     <row r="76" spans="9:11">
       <c r="I76" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K76" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4819,10 +4968,10 @@
     </row>
     <row r="77" spans="2:11">
       <c r="B77" s="22" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D77" s="22">
         <v>40</v>
@@ -4831,7 +4980,7 @@
         <v>27</v>
       </c>
       <c r="F77" s="22" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G77" s="22" t="s">
         <v>29</v>
@@ -4840,7 +4989,7 @@
         <v>1</v>
       </c>
       <c r="I77" s="22" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K77" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4849,7 +4998,7 @@
     </row>
     <row r="78" spans="9:11">
       <c r="I78" s="22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K78" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4858,7 +5007,7 @@
     </row>
     <row r="79" spans="9:11">
       <c r="I79" s="22" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K79" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4867,10 +5016,10 @@
     </row>
     <row r="80" spans="2:11">
       <c r="B80" s="22" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C80" s="22" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="D80" s="22">
         <v>100</v>
@@ -4879,7 +5028,7 @@
         <v>27</v>
       </c>
       <c r="F80" s="22" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="G80" s="22" t="s">
         <v>29</v>
@@ -4888,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="I80" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K80" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4897,7 +5046,7 @@
     </row>
     <row r="81" spans="9:11">
       <c r="I81" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K81" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4906,7 +5055,7 @@
     </row>
     <row r="82" spans="9:11">
       <c r="I82" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K82" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4915,7 +5064,7 @@
     </row>
     <row r="83" spans="9:11">
       <c r="I83" s="22" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K83" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4924,7 +5073,7 @@
     </row>
     <row r="84" spans="9:11">
       <c r="I84" s="22" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K84" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4933,10 +5082,10 @@
     </row>
     <row r="85" spans="2:11">
       <c r="B85" s="22" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C85" s="22" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="D85" s="22">
         <v>80</v>
@@ -4945,7 +5094,7 @@
         <v>27</v>
       </c>
       <c r="F85" s="22" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G85" s="22" t="s">
         <v>29</v>
@@ -4954,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K85" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4963,7 +5112,7 @@
     </row>
     <row r="86" spans="9:11">
       <c r="I86" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K86" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4972,7 +5121,7 @@
     </row>
     <row r="87" spans="9:11">
       <c r="I87" s="22" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K87" s="1" t="str">
         <f t="shared" si="1"/>
@@ -4981,10 +5130,10 @@
     </row>
     <row r="88" spans="2:11">
       <c r="B88" s="22" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C88" s="22" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D88" s="22">
         <v>140</v>
@@ -4993,16 +5142,16 @@
         <v>27</v>
       </c>
       <c r="F88" s="22" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H88" s="22">
         <v>1</v>
       </c>
       <c r="I88" s="22" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K88" s="1" t="str">
         <f t="shared" si="1"/>
@@ -5011,17 +5160,17 @@
     </row>
     <row r="89" spans="9:9">
       <c r="I89" s="22" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="90" spans="9:9">
       <c r="I90" s="22" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="91" spans="9:9">
       <c r="I91" s="22" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -5054,22 +5203,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5077,25 +5226,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D2" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F2" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G2" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="H2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -5112,16 +5261,16 @@
         <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F3" t="s">
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="2:8">
@@ -5138,10 +5287,10 @@
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H4" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -5158,18 +5307,18 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H5" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -5178,18 +5327,18 @@
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7">
         <v>120</v>
@@ -5198,18 +5347,18 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E8">
         <v>120</v>
@@ -5218,18 +5367,18 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H8" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>90</v>
@@ -5238,18 +5387,18 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H9" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>120</v>
@@ -5258,18 +5407,18 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E11">
         <v>90</v>
@@ -5278,18 +5427,18 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H11" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E12">
         <v>120</v>
@@ -5298,18 +5447,18 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E13">
         <v>120</v>
@@ -5318,18 +5467,18 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E14">
         <v>60</v>
@@ -5338,18 +5487,18 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H14" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E15">
         <v>90</v>
@@ -5358,18 +5507,18 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="H15" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E16">
         <v>90</v>
@@ -5378,18 +5527,18 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="2:8">
       <c r="B17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E17">
         <v>90</v>
@@ -5398,18 +5547,18 @@
         <v>3</v>
       </c>
       <c r="G17" t="s">
+        <v>203</v>
+      </c>
+      <c r="H17" t="s">
         <v>198</v>
-      </c>
-      <c r="H17" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="18" spans="2:8">
       <c r="B18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E18">
         <v>90</v>
@@ -5418,18 +5567,18 @@
         <v>3</v>
       </c>
       <c r="G18" t="s">
+        <v>203</v>
+      </c>
+      <c r="H18" t="s">
         <v>198</v>
-      </c>
-      <c r="H18" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:8">
       <c r="B19" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E19">
         <v>90</v>
@@ -5438,18 +5587,18 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H19" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="2:8">
       <c r="B20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E20">
         <v>90</v>
@@ -5458,18 +5607,18 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E21">
         <v>60</v>
@@ -5478,18 +5627,18 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="H21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="2:8">
       <c r="B22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E22">
         <v>60</v>
@@ -5498,18 +5647,18 @@
         <v>3</v>
       </c>
       <c r="G22" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="H22" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="23" spans="2:8">
       <c r="B23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E23">
         <v>90</v>
@@ -5518,18 +5667,18 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="H23" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24" spans="2:8">
       <c r="B24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E24">
         <v>90</v>
@@ -5538,18 +5687,18 @@
         <v>3</v>
       </c>
       <c r="G24" t="s">
+        <v>203</v>
+      </c>
+      <c r="H24" t="s">
         <v>198</v>
-      </c>
-      <c r="H24" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E25">
         <v>90</v>
@@ -5558,18 +5707,18 @@
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H25" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="26" spans="2:8">
       <c r="B26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E26">
         <v>90</v>
@@ -5578,18 +5727,18 @@
         <v>7</v>
       </c>
       <c r="G26" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H26" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="27" spans="2:8">
       <c r="B27" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E27">
         <v>90</v>
@@ -5598,18 +5747,18 @@
         <v>5</v>
       </c>
       <c r="G27" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H27" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E28">
         <v>90</v>
@@ -5618,18 +5767,18 @@
         <v>3</v>
       </c>
       <c r="G28" t="s">
+        <v>203</v>
+      </c>
+      <c r="H28" t="s">
         <v>198</v>
-      </c>
-      <c r="H28" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E29">
         <v>90</v>
@@ -5638,18 +5787,18 @@
         <v>5</v>
       </c>
       <c r="G29" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H29" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="2:8">
       <c r="B30" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E30">
         <v>60</v>
@@ -5658,18 +5807,18 @@
         <v>3</v>
       </c>
       <c r="G30" t="s">
+        <v>203</v>
+      </c>
+      <c r="H30" t="s">
         <v>198</v>
-      </c>
-      <c r="H30" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E31">
         <v>60</v>
@@ -5678,18 +5827,18 @@
         <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H31" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="32" spans="2:8">
       <c r="B32" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E32">
         <v>60</v>
@@ -5698,18 +5847,18 @@
         <v>3</v>
       </c>
       <c r="G32" t="s">
+        <v>203</v>
+      </c>
+      <c r="H32" t="s">
         <v>198</v>
-      </c>
-      <c r="H32" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E33">
         <v>60</v>
@@ -5718,18 +5867,18 @@
         <v>3</v>
       </c>
       <c r="G33" t="s">
+        <v>203</v>
+      </c>
+      <c r="H33" t="s">
         <v>198</v>
-      </c>
-      <c r="H33" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E34">
         <v>60</v>
@@ -5738,18 +5887,18 @@
         <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H34" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E35">
         <v>60</v>
@@ -5758,18 +5907,18 @@
         <v>7</v>
       </c>
       <c r="G35" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H35" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="E36">
         <v>90</v>
@@ -5778,18 +5927,18 @@
         <v>5</v>
       </c>
       <c r="G36" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H36" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E37">
         <v>60</v>
@@ -5798,18 +5947,18 @@
         <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H37" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E38">
         <v>60</v>
@@ -5818,18 +5967,18 @@
         <v>7</v>
       </c>
       <c r="G38" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H38" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E39">
         <v>90</v>
@@ -5838,18 +5987,18 @@
         <v>5</v>
       </c>
       <c r="G39" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H39" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E40">
         <v>60</v>
@@ -5858,18 +6007,18 @@
         <v>3</v>
       </c>
       <c r="G40" t="s">
+        <v>203</v>
+      </c>
+      <c r="H40" t="s">
         <v>198</v>
-      </c>
-      <c r="H40" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E41">
         <v>60</v>
@@ -5878,18 +6027,18 @@
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H41" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E42">
         <v>90</v>
@@ -5898,18 +6047,18 @@
         <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="H42" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E43">
         <v>90</v>
@@ -5918,18 +6067,18 @@
         <v>7</v>
       </c>
       <c r="G43" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H43" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C44" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E44">
         <v>60</v>
@@ -5938,18 +6087,18 @@
         <v>5</v>
       </c>
       <c r="G44" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H44" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C45" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E45">
         <v>90</v>
@@ -5958,18 +6107,18 @@
         <v>3</v>
       </c>
       <c r="G45" t="s">
+        <v>203</v>
+      </c>
+      <c r="H45" t="s">
         <v>198</v>
-      </c>
-      <c r="H45" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C46" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E46">
         <v>90</v>
@@ -5978,18 +6127,18 @@
         <v>5</v>
       </c>
       <c r="G46" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="H46" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C47" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E47">
         <v>60</v>
@@ -5998,18 +6147,18 @@
         <v>7</v>
       </c>
       <c r="G47" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H47" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E48">
         <v>60</v>
@@ -6018,18 +6167,18 @@
         <v>17</v>
       </c>
       <c r="G48" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="H48" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E49">
         <v>60</v>
@@ -6038,18 +6187,18 @@
         <v>13</v>
       </c>
       <c r="G49" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H49" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C50" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E50">
         <v>60</v>
@@ -6058,10 +6207,10 @@
         <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="H50" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -6089,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6097,10 +6246,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6119,7 +6268,7 @@
         <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="2:3">
@@ -6127,370 +6276,370 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="B6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="B7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="B10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="B11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="B12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="B14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" spans="2:7">
       <c r="B18" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G18" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="B19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="B22" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="B23" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="B24" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="B25" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="B27" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C27" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="B28" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C28" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="B30" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="B31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="B34" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C34" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="B35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="B36" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C36" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C37" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="B38" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C38" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="B39" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C39" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="B41" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="B42" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C42" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="B43" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C43" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="B44" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="B45" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="B46" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C46" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="B47" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C47" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="B48" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="B50" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C50" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -6528,19 +6677,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6548,25 +6697,25 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6583,13 +6732,13 @@
         <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>20</v>
@@ -6597,122 +6746,122 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" ht="34" spans="2:9">
       <c r="B6" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:9">
       <c r="B8" s="1" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" ht="51" spans="2:9">
       <c r="B9" s="1" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -6745,22 +6894,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="D1" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
       </c>
       <c r="F1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G1" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="H1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6768,25 +6917,25 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="C2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="E2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6806,10 +6955,10 @@
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="G3" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
@@ -6817,7 +6966,7 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6826,21 +6975,21 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
       <c r="H4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6849,21 +6998,21 @@
         <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G5">
         <v>0.1</v>
       </c>
       <c r="H5" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -6872,16 +7021,16 @@
         <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G6">
         <v>0.02</v>
       </c>
       <c r="H6" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -6924,49 +7073,49 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="D1" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E1" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="F1" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="G1" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="H1" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="I1" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J1" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K1" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="L1" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="M1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="N1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="O1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="P1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="Q1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:17">
@@ -6974,52 +7123,52 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="G2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="H2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="K2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="L2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="N2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="O2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="P2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="Q2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -7030,34 +7179,34 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D3" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="E3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="F3" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="G3" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="H3" t="s">
         <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K3" t="s">
         <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -7077,28 +7226,28 @@
     </row>
     <row r="4" ht="34" spans="2:16">
       <c r="B4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="C4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D4" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="E4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J4" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -7110,36 +7259,36 @@
         <v>27</v>
       </c>
       <c r="O4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P4" s="19" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="34" spans="2:16">
       <c r="B5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F5" t="s">
+        <v>377</v>
+      </c>
+      <c r="G5" t="s">
+        <v>378</v>
+      </c>
+      <c r="I5" t="s">
+        <v>324</v>
+      </c>
+      <c r="J5" t="s">
         <v>369</v>
-      </c>
-      <c r="C5" t="s">
-        <v>362</v>
-      </c>
-      <c r="D5" t="s">
-        <v>370</v>
-      </c>
-      <c r="E5" t="s">
-        <v>371</v>
-      </c>
-      <c r="F5" t="s">
-        <v>372</v>
-      </c>
-      <c r="G5" t="s">
-        <v>373</v>
-      </c>
-      <c r="I5" t="s">
-        <v>319</v>
-      </c>
-      <c r="J5" t="s">
-        <v>364</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -7151,36 +7300,36 @@
         <v>27</v>
       </c>
       <c r="O5" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="2:17">
       <c r="B6" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E6" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F6" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G6" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I6" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J6" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7195,36 +7344,36 @@
         <v>27</v>
       </c>
       <c r="P6" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" ht="34" spans="2:16">
       <c r="B7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E7" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F7" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G7" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I7" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J7" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -7236,36 +7385,36 @@
         <v>27</v>
       </c>
       <c r="O7" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P7" s="19" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" ht="34" spans="2:17">
       <c r="B8" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E8" t="s">
+        <v>376</v>
+      </c>
+      <c r="F8" t="s">
         <v>370</v>
       </c>
-      <c r="E8" t="s">
-        <v>371</v>
-      </c>
-      <c r="F8" t="s">
-        <v>365</v>
-      </c>
       <c r="G8" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I8" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J8" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -7277,39 +7426,39 @@
         <v>27</v>
       </c>
       <c r="O8" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P8" s="19" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9" ht="34" spans="2:16">
       <c r="B9" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C9" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D9" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E9" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F9" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G9" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I9" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J9" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -7321,36 +7470,36 @@
         <v>27</v>
       </c>
       <c r="O9" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P9" s="19" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" ht="34" spans="2:16">
       <c r="B10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D10" t="s">
+        <v>375</v>
+      </c>
+      <c r="E10" t="s">
+        <v>395</v>
+      </c>
+      <c r="F10" t="s">
         <v>370</v>
       </c>
-      <c r="E10" t="s">
-        <v>390</v>
-      </c>
-      <c r="F10" t="s">
-        <v>365</v>
-      </c>
       <c r="G10" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I10" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J10" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -7362,36 +7511,36 @@
         <v>27</v>
       </c>
       <c r="O10" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P10" s="19" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="11" ht="34" spans="2:16">
       <c r="B11" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C11" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D11" t="s">
+        <v>375</v>
+      </c>
+      <c r="E11" t="s">
+        <v>397</v>
+      </c>
+      <c r="F11" t="s">
         <v>370</v>
       </c>
-      <c r="E11" t="s">
-        <v>392</v>
-      </c>
-      <c r="F11" t="s">
-        <v>365</v>
-      </c>
       <c r="G11" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I11" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J11" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -7403,36 +7552,36 @@
         <v>27</v>
       </c>
       <c r="O11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P11" s="19" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12" ht="34" spans="2:16">
       <c r="B12" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C12" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D12" t="s">
+        <v>398</v>
+      </c>
+      <c r="E12" t="s">
+        <v>369</v>
+      </c>
+      <c r="F12" t="s">
+        <v>370</v>
+      </c>
+      <c r="G12" t="s">
+        <v>378</v>
+      </c>
+      <c r="I12" t="s">
         <v>393</v>
       </c>
-      <c r="E12" t="s">
-        <v>364</v>
-      </c>
-      <c r="F12" t="s">
-        <v>365</v>
-      </c>
-      <c r="G12" t="s">
-        <v>373</v>
-      </c>
-      <c r="I12" t="s">
-        <v>388</v>
-      </c>
       <c r="J12" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -7444,36 +7593,36 @@
         <v>27</v>
       </c>
       <c r="O12" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" ht="34" spans="2:16">
       <c r="B13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C13" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D13" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E13" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F13" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G13" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I13" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J13" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -7485,36 +7634,36 @@
         <v>27</v>
       </c>
       <c r="O13" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" spans="2:17">
       <c r="B14" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C14" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D14" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F14" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G14" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I14" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J14" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -7526,42 +7675,42 @@
         <v>27</v>
       </c>
       <c r="O14" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P14" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" s="18" customFormat="1" spans="2:18">
       <c r="B15" s="18" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K15" s="18">
         <v>0</v>
@@ -7573,42 +7722,42 @@
         <v>29</v>
       </c>
       <c r="N15" s="18" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O15" s="18" t="s">
         <v>27</v>
       </c>
       <c r="P15" s="18" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="R15" s="18" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="2:17">
       <c r="B16" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="C16" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D16" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E16" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F16" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G16" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I16" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J16" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -7623,36 +7772,36 @@
         <v>27</v>
       </c>
       <c r="P16" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q16" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="17" ht="34" spans="2:18">
       <c r="B17" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C17" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D17" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E17" t="s">
+        <v>376</v>
+      </c>
+      <c r="F17" t="s">
+        <v>370</v>
+      </c>
+      <c r="G17" t="s">
         <v>371</v>
       </c>
-      <c r="F17" t="s">
-        <v>365</v>
-      </c>
-      <c r="G17" t="s">
-        <v>366</v>
-      </c>
       <c r="I17" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J17" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -7667,36 +7816,36 @@
         <v>27</v>
       </c>
       <c r="P17" s="19" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="R17" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" ht="34" spans="2:17">
       <c r="B18" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C18" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D18" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E18" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F18" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G18" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I18" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J18" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -7708,39 +7857,39 @@
         <v>27</v>
       </c>
       <c r="O18" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P18" s="19" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" ht="34" spans="2:16">
       <c r="B19" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="C19" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D19" t="s">
+        <v>375</v>
+      </c>
+      <c r="E19" t="s">
+        <v>397</v>
+      </c>
+      <c r="F19" t="s">
         <v>370</v>
       </c>
-      <c r="E19" t="s">
-        <v>392</v>
-      </c>
-      <c r="F19" t="s">
-        <v>365</v>
-      </c>
       <c r="G19" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I19" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J19" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -7752,36 +7901,36 @@
         <v>27</v>
       </c>
       <c r="O19" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="C20" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E20" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F20" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G20" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I20" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J20" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -7790,39 +7939,39 @@
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O20" t="s">
         <v>27</v>
       </c>
       <c r="P20" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="2:17">
       <c r="B21" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C21" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D21" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E21" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F21" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G21" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I21" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J21" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -7834,42 +7983,42 @@
         <v>27</v>
       </c>
       <c r="O21" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P21" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" s="18" customFormat="1" ht="34" spans="2:18">
       <c r="B22" s="18" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="H22" s="18" t="s">
         <v>29</v>
       </c>
       <c r="I22" s="18" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J22" s="18" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K22" s="18">
         <v>0</v>
@@ -7887,39 +8036,39 @@
         <v>27</v>
       </c>
       <c r="P22" s="20" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="R22" s="18" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="23" ht="34" spans="2:16">
       <c r="B23" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C23" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D23" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E23" t="s">
+        <v>376</v>
+      </c>
+      <c r="F23" t="s">
+        <v>370</v>
+      </c>
+      <c r="G23" t="s">
         <v>371</v>
       </c>
-      <c r="F23" t="s">
-        <v>365</v>
-      </c>
-      <c r="G23" t="s">
-        <v>366</v>
-      </c>
       <c r="H23" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="I23" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J23" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -7934,33 +8083,33 @@
         <v>27</v>
       </c>
       <c r="P23" s="19" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="24" spans="2:17">
       <c r="B24" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="C24" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D24" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E24" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F24" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G24" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I24" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J24" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K24">
         <v>2</v>
@@ -7975,36 +8124,36 @@
         <v>27</v>
       </c>
       <c r="P24" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q24" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" ht="34" spans="2:16">
       <c r="B25" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C25" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D25" t="s">
+        <v>375</v>
+      </c>
+      <c r="E25" t="s">
+        <v>376</v>
+      </c>
+      <c r="F25" t="s">
         <v>370</v>
       </c>
-      <c r="E25" t="s">
-        <v>371</v>
-      </c>
-      <c r="F25" t="s">
-        <v>365</v>
-      </c>
       <c r="G25" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J25" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -8019,33 +8168,33 @@
         <v>27</v>
       </c>
       <c r="P25" s="19" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="2:17">
       <c r="B26" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="C26" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D26" t="s">
+        <v>381</v>
+      </c>
+      <c r="E26" t="s">
+        <v>369</v>
+      </c>
+      <c r="F26" t="s">
+        <v>370</v>
+      </c>
+      <c r="G26" t="s">
+        <v>378</v>
+      </c>
+      <c r="I26" t="s">
+        <v>382</v>
+      </c>
+      <c r="J26" t="s">
         <v>376</v>
-      </c>
-      <c r="E26" t="s">
-        <v>364</v>
-      </c>
-      <c r="F26" t="s">
-        <v>365</v>
-      </c>
-      <c r="G26" t="s">
-        <v>373</v>
-      </c>
-      <c r="I26" t="s">
-        <v>377</v>
-      </c>
-      <c r="J26" t="s">
-        <v>371</v>
       </c>
       <c r="K26">
         <v>2</v>
@@ -8060,36 +8209,36 @@
         <v>27</v>
       </c>
       <c r="P26" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q26" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="C27" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D27" t="s">
+        <v>381</v>
+      </c>
+      <c r="E27" t="s">
+        <v>369</v>
+      </c>
+      <c r="F27" t="s">
+        <v>370</v>
+      </c>
+      <c r="G27" t="s">
+        <v>378</v>
+      </c>
+      <c r="I27" t="s">
+        <v>431</v>
+      </c>
+      <c r="J27" t="s">
         <v>376</v>
-      </c>
-      <c r="E27" t="s">
-        <v>364</v>
-      </c>
-      <c r="F27" t="s">
-        <v>365</v>
-      </c>
-      <c r="G27" t="s">
-        <v>373</v>
-      </c>
-      <c r="I27" t="s">
-        <v>426</v>
-      </c>
-      <c r="J27" t="s">
-        <v>371</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -8104,33 +8253,33 @@
         <v>27</v>
       </c>
       <c r="P27" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" ht="34" spans="2:17">
       <c r="B28" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C28" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D28" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E28" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F28" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G28" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I28" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J28" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -8142,39 +8291,39 @@
         <v>27</v>
       </c>
       <c r="O28" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P28" s="19" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C29" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D29" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E29" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F29" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G29" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I29" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J29" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -8189,33 +8338,33 @@
         <v>27</v>
       </c>
       <c r="P29" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="C30" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D30" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E30" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F30" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G30" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I30" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="J30" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -8227,36 +8376,36 @@
         <v>27</v>
       </c>
       <c r="O30" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P30" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="31" spans="2:17">
       <c r="B31" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C31" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D31" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E31" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F31" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G31" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I31" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J31" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K31">
         <v>2</v>
@@ -8271,36 +8420,36 @@
         <v>27</v>
       </c>
       <c r="P31" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q31" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="32" ht="34" spans="2:16">
       <c r="B32" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="C32" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D32" t="s">
+        <v>375</v>
+      </c>
+      <c r="E32" t="s">
+        <v>441</v>
+      </c>
+      <c r="F32" t="s">
         <v>370</v>
       </c>
-      <c r="E32" t="s">
-        <v>436</v>
-      </c>
-      <c r="F32" t="s">
-        <v>365</v>
-      </c>
       <c r="G32" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I32" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J32" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -8312,36 +8461,36 @@
         <v>27</v>
       </c>
       <c r="O32" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P32" s="19" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="33" spans="2:16">
       <c r="B33" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="C33" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D33" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E33" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F33" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G33" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I33" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J33" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -8350,39 +8499,39 @@
         <v>3</v>
       </c>
       <c r="N33" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O33" t="s">
         <v>27</v>
       </c>
       <c r="P33" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="34" spans="2:16">
       <c r="B34" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C34" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D34" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E34" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F34" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G34" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I34" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J34" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -8394,36 +8543,36 @@
         <v>27</v>
       </c>
       <c r="O34" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P34" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="35" spans="2:17">
       <c r="B35" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="C35" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D35" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E35" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F35" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G35" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I35" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J35" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -8438,36 +8587,36 @@
         <v>27</v>
       </c>
       <c r="P35" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q35" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="36" spans="2:18">
       <c r="B36" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="C36" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D36" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E36" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F36" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G36" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I36" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="J36" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -8482,39 +8631,39 @@
         <v>27</v>
       </c>
       <c r="P36" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="R36" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="37" spans="2:18">
       <c r="B37" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="C37" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D37" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E37" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F37" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G37" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I37" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J37" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -8526,39 +8675,39 @@
         <v>27</v>
       </c>
       <c r="O37" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P37" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="R37" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38" spans="2:18">
       <c r="B38" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C38" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D38" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E38" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F38" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G38" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I38" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J38" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -8570,39 +8719,39 @@
         <v>27</v>
       </c>
       <c r="O38" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P38" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="R38" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="39" spans="2:18">
       <c r="B39" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="C39" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D39" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E39" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F39" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G39" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I39" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J39" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K39">
         <v>3</v>
@@ -8617,39 +8766,39 @@
         <v>27</v>
       </c>
       <c r="P39" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q39" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="R39" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="40" ht="34" spans="2:18">
       <c r="B40" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="C40" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D40" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E40" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F40" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G40" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I40" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J40" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -8658,7 +8807,7 @@
         <v>1.5</v>
       </c>
       <c r="M40" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="N40" t="s">
         <v>27</v>
@@ -8667,42 +8816,42 @@
         <v>27</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="R40" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="41" ht="34" spans="2:16">
       <c r="B41" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C41" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D41" t="s">
+        <v>375</v>
+      </c>
+      <c r="E41" t="s">
+        <v>397</v>
+      </c>
+      <c r="F41" t="s">
         <v>370</v>
       </c>
-      <c r="E41" t="s">
-        <v>392</v>
-      </c>
-      <c r="F41" t="s">
-        <v>365</v>
-      </c>
       <c r="G41" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="H41" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="I41" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J41" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -8711,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="N41" t="s">
         <v>27</v>
@@ -8720,33 +8869,33 @@
         <v>27</v>
       </c>
       <c r="P41" s="19" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="42" spans="2:16">
       <c r="B42" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="C42" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D42" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E42" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F42" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G42" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I42" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J42" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -8755,39 +8904,39 @@
         <v>4</v>
       </c>
       <c r="N42" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O42" t="s">
         <v>27</v>
       </c>
       <c r="P42" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43" spans="2:16">
       <c r="B43" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="C43" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D43" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E43" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F43" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G43" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I43" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J43" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -8802,33 +8951,33 @@
         <v>27</v>
       </c>
       <c r="P43" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="44" ht="34" spans="2:16">
       <c r="B44" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="C44" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D44" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E44" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F44" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G44" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I44" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J44" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -8837,39 +8986,39 @@
         <v>9</v>
       </c>
       <c r="N44" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O44" t="s">
         <v>27</v>
       </c>
       <c r="P44" s="19" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="45" spans="2:16">
       <c r="B45" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="C45" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D45" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E45" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F45" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G45" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I45" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J45" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -8878,39 +9027,39 @@
         <v>2</v>
       </c>
       <c r="N45" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O45" t="s">
         <v>27</v>
       </c>
       <c r="P45" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="46" spans="2:16">
       <c r="B46" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C46" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D46" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E46" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F46" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G46" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I46" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J46" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -8922,36 +9071,36 @@
         <v>27</v>
       </c>
       <c r="O46" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P46" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="47" ht="34" spans="2:16">
       <c r="B47" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="C47" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D47" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E47" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F47" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G47" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I47" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J47" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -8960,42 +9109,42 @@
         <v>10</v>
       </c>
       <c r="M47" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N47" t="s">
         <v>27</v>
       </c>
       <c r="O47" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P47" s="19" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="48" spans="2:17">
       <c r="B48" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="C48" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D48" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E48" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F48" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G48" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I48" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J48" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -9007,39 +9156,39 @@
         <v>27</v>
       </c>
       <c r="O48" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P48" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="49" ht="34" spans="2:16">
       <c r="B49" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="C49" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D49" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E49" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F49" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G49" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I49" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J49" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -9051,36 +9200,36 @@
         <v>27</v>
       </c>
       <c r="O49" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P49" s="19" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" spans="2:17">
       <c r="B50" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C50" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D50" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E50" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F50" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G50" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I50" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J50" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -9095,36 +9244,36 @@
         <v>27</v>
       </c>
       <c r="P50" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q50" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" spans="2:16">
       <c r="B51" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C51" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D51" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E51" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F51" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G51" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I51" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J51" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -9133,39 +9282,39 @@
         <v>9</v>
       </c>
       <c r="N51" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O51" t="s">
         <v>27</v>
       </c>
       <c r="P51" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="52" spans="2:16">
       <c r="B52" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="C52" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D52" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E52" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F52" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G52" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I52" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J52" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -9180,33 +9329,33 @@
         <v>27</v>
       </c>
       <c r="P52" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="53" spans="2:17">
       <c r="B53" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="C53" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D53" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E53" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F53" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G53" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I53" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J53" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K53">
         <v>0</v>
@@ -9218,39 +9367,39 @@
         <v>27</v>
       </c>
       <c r="O53" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P53" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="54" spans="2:16">
       <c r="B54" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C54" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D54" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E54" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F54" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G54" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I54" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J54" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K54">
         <v>0</v>
@@ -9262,36 +9411,36 @@
         <v>27</v>
       </c>
       <c r="O54" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P54" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="55" spans="2:16">
       <c r="B55" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="C55" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D55" t="s">
+        <v>381</v>
+      </c>
+      <c r="E55" t="s">
+        <v>369</v>
+      </c>
+      <c r="F55" t="s">
+        <v>370</v>
+      </c>
+      <c r="G55" t="s">
+        <v>378</v>
+      </c>
+      <c r="I55" t="s">
+        <v>431</v>
+      </c>
+      <c r="J55" t="s">
         <v>376</v>
-      </c>
-      <c r="E55" t="s">
-        <v>364</v>
-      </c>
-      <c r="F55" t="s">
-        <v>365</v>
-      </c>
-      <c r="G55" t="s">
-        <v>373</v>
-      </c>
-      <c r="I55" t="s">
-        <v>426</v>
-      </c>
-      <c r="J55" t="s">
-        <v>371</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -9306,33 +9455,33 @@
         <v>27</v>
       </c>
       <c r="P55" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="56" spans="2:16">
       <c r="B56" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C56" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D56" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E56" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F56" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G56" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I56" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="J56" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -9341,39 +9490,39 @@
         <v>7</v>
       </c>
       <c r="N56" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O56" t="s">
         <v>27</v>
       </c>
       <c r="P56" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="57" spans="2:16">
       <c r="B57" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="C57" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D57" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E57" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F57" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G57" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I57" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J57" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -9382,42 +9531,42 @@
         <v>5</v>
       </c>
       <c r="M57" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N57" t="s">
         <v>27</v>
       </c>
       <c r="O57" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P57" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="58" ht="34" spans="2:16">
       <c r="B58" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C58" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D58" t="s">
+        <v>375</v>
+      </c>
+      <c r="E58" t="s">
+        <v>397</v>
+      </c>
+      <c r="F58" t="s">
         <v>370</v>
       </c>
-      <c r="E58" t="s">
-        <v>392</v>
-      </c>
-      <c r="F58" t="s">
-        <v>365</v>
-      </c>
       <c r="G58" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I58" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J58" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -9429,36 +9578,36 @@
         <v>27</v>
       </c>
       <c r="O58" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P58" s="19" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="2:16">
       <c r="B59" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C59" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D59" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E59" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F59" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G59" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I59" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J59" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -9473,36 +9622,36 @@
         <v>27</v>
       </c>
       <c r="P59" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" ht="34" spans="2:17">
       <c r="B60" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="C60" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D60" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="E60" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F60" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G60" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="H60" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="I60" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J60" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -9511,7 +9660,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="N60" t="s">
         <v>27</v>
@@ -9520,39 +9669,39 @@
         <v>27</v>
       </c>
       <c r="P60" s="19" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="61" ht="34" spans="2:17">
       <c r="B61" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C61" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D61" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="E61" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F61" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G61" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="H61" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="I61" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J61" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -9561,7 +9710,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="N61" t="s">
         <v>27</v>
@@ -9570,36 +9719,36 @@
         <v>27</v>
       </c>
       <c r="P61" s="19" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="Q61" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="62" ht="34" spans="2:17">
       <c r="B62" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C62" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D62" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E62" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F62" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="G62" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I62" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J62" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -9611,39 +9760,39 @@
         <v>27</v>
       </c>
       <c r="O62" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P62" s="19" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="63" spans="2:16">
       <c r="B63" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="C63" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D63" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E63" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F63" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G63" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I63" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J63" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -9658,33 +9807,33 @@
         <v>27</v>
       </c>
       <c r="P63" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" spans="2:16">
       <c r="B64" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C64" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D64" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E64" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F64" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G64" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I64" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J64" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -9699,33 +9848,33 @@
         <v>27</v>
       </c>
       <c r="P64" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="65" spans="2:17">
       <c r="B65" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C65" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D65" t="s">
+        <v>381</v>
+      </c>
+      <c r="E65" t="s">
+        <v>369</v>
+      </c>
+      <c r="F65" t="s">
+        <v>370</v>
+      </c>
+      <c r="G65" t="s">
+        <v>378</v>
+      </c>
+      <c r="I65" t="s">
+        <v>382</v>
+      </c>
+      <c r="J65" t="s">
         <v>376</v>
-      </c>
-      <c r="E65" t="s">
-        <v>364</v>
-      </c>
-      <c r="F65" t="s">
-        <v>365</v>
-      </c>
-      <c r="G65" t="s">
-        <v>373</v>
-      </c>
-      <c r="I65" t="s">
-        <v>377</v>
-      </c>
-      <c r="J65" t="s">
-        <v>371</v>
       </c>
       <c r="K65">
         <v>0</v>
@@ -9740,36 +9889,36 @@
         <v>27</v>
       </c>
       <c r="P65" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q65" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="66" ht="34" spans="2:17">
       <c r="B66" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C66" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D66" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E66" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F66" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G66" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I66" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="J66" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -9778,7 +9927,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="N66" t="s">
         <v>27</v>
@@ -9787,36 +9936,36 @@
         <v>27</v>
       </c>
       <c r="P66" s="19" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="Q66" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="67" ht="34" spans="2:16">
       <c r="B67" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="C67" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D67" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E67" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F67" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G67" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I67" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J67" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -9831,33 +9980,33 @@
         <v>27</v>
       </c>
       <c r="P67" s="19" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="68" spans="2:17">
       <c r="B68" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C68" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D68" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E68" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F68" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G68" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I68" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J68" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -9872,36 +10021,36 @@
         <v>27</v>
       </c>
       <c r="P68" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="Q68" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="69" spans="2:16">
       <c r="B69" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C69" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D69" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="E69" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F69" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G69" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I69" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="J69" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -9910,7 +10059,7 @@
         <v>3</v>
       </c>
       <c r="M69" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="N69" t="s">
         <v>27</v>
@@ -9919,7 +10068,7 @@
         <v>27</v>
       </c>
       <c r="P69" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -9957,34 +10106,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="M2" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" ht="17.6" customHeight="1" spans="1:15">
@@ -10001,22 +10150,22 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="M3" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" ht="17.6" customHeight="1" spans="1:13">
@@ -10033,19 +10182,19 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M4" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" ht="17.6" customHeight="1" spans="1:13">
@@ -10053,7 +10202,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
@@ -10062,22 +10211,22 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="I5" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="M5" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" ht="17.6" customHeight="1" spans="1:13">
@@ -10085,7 +10234,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
@@ -10094,19 +10243,19 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M6" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" ht="17.6" customHeight="1" spans="1:13">
@@ -10114,7 +10263,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
@@ -10123,19 +10272,19 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="I7" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="M7" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" ht="17.6" customHeight="1" spans="1:9">
@@ -10143,7 +10292,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
@@ -10152,16 +10301,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" ht="17.6" customHeight="1" spans="1:9">
@@ -10169,7 +10318,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>30</v>
@@ -10178,16 +10327,16 @@
         <v>6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="I9" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" ht="17.6" customHeight="1" spans="1:14">
@@ -10195,7 +10344,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
@@ -10204,19 +10353,19 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" ht="17.6" customHeight="1" spans="1:9">
@@ -10224,7 +10373,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -10233,16 +10382,16 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="12" ht="17.6" customHeight="1" spans="1:15">
@@ -10250,7 +10399,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>30</v>
@@ -10259,25 +10408,25 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="13" ht="17.6" customHeight="1" spans="1:15">
@@ -10285,7 +10434,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>30</v>
@@ -10294,28 +10443,28 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -10323,7 +10472,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>30</v>
@@ -10332,22 +10481,22 @@
         <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -10355,7 +10504,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>30</v>
@@ -10364,22 +10513,22 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="16" ht="17.6" customHeight="1" spans="1:15">
@@ -10387,34 +10536,34 @@
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D16" s="1">
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="17" ht="17.6" customHeight="1" spans="1:15">
@@ -10422,7 +10571,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -10431,22 +10580,22 @@
         <v>20</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="18" spans="3:15">
@@ -10454,10 +10603,10 @@
         <v>30</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="19" ht="17.6" customHeight="1" spans="1:15">
@@ -10465,31 +10614,31 @@
         <v>16</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="D19" s="1">
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
     </row>
     <row r="20" ht="17.6" customHeight="1" spans="1:15">
@@ -10497,31 +10646,31 @@
         <v>17</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="21" ht="17.6" customHeight="1" spans="1:15">
@@ -10529,31 +10678,31 @@
         <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D21" s="1">
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="22" ht="17.6" customHeight="1" spans="1:15">
@@ -10561,7 +10710,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>30</v>
@@ -10570,22 +10719,22 @@
         <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="N22" s="1" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" spans="3:15">
@@ -10593,13 +10742,13 @@
         <v>30</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="24" ht="17.6" customHeight="1" spans="1:15">
@@ -10607,7 +10756,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>30</v>
@@ -10616,25 +10765,25 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="25" spans="3:15">
@@ -10642,10 +10791,10 @@
         <v>30</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" ht="17.6" customHeight="1" spans="1:15">
@@ -10653,7 +10802,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>30</v>
@@ -10662,25 +10811,25 @@
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="3:15">
@@ -10688,10 +10837,10 @@
         <v>30</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
     </row>
     <row r="28" ht="17.6" customHeight="1" spans="1:15">
@@ -10699,34 +10848,34 @@
         <v>22</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D28" s="1">
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" ht="17.6" customHeight="1" spans="1:15">
@@ -10734,31 +10883,31 @@
         <v>23</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D29" s="1">
         <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="30" ht="17.6" customHeight="1" spans="1:15">
@@ -10766,7 +10915,7 @@
         <v>24</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>30</v>
@@ -10775,25 +10924,25 @@
         <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="31" spans="3:15">
@@ -10801,10 +10950,10 @@
         <v>30</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="32" spans="3:15">
@@ -10812,10 +10961,10 @@
         <v>30</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="O32" s="13" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="33" ht="17.6" customHeight="1" spans="1:15">
@@ -10823,7 +10972,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>30</v>
@@ -10832,25 +10981,25 @@
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="O33" s="13" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" spans="3:15">
@@ -10858,13 +11007,13 @@
         <v>30</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="O34" s="13" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="35" spans="3:3">
@@ -10877,36 +11026,36 @@
         <v>26</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D36" s="1">
         <v>30</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" spans="3:15">
       <c r="C37" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="38" ht="17.6" customHeight="1" spans="1:15">
@@ -10914,42 +11063,42 @@
         <v>27</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D38" s="1">
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>615</v>
+        <v>620</v>
       </c>
     </row>
     <row r="39" spans="3:15">
       <c r="C39" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>617</v>
+        <v>622</v>
       </c>
     </row>
     <row r="40" ht="17.6" customHeight="1" spans="1:15">
@@ -10957,42 +11106,42 @@
         <v>28</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D40" s="1">
         <v>25</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="41" ht="17.6" customHeight="1" spans="3:15">
       <c r="C41" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>622</v>
+        <v>627</v>
       </c>
     </row>
     <row r="42" ht="17.6" customHeight="1" spans="1:9">
@@ -11000,36 +11149,36 @@
         <v>29</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D42" s="1">
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="43" spans="3:15">
       <c r="C43" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>625</v>
+        <v>630</v>
       </c>
     </row>
     <row r="44" ht="17.6" customHeight="1" spans="1:15">
@@ -11037,42 +11186,42 @@
         <v>30</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D44" s="1">
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>628</v>
+        <v>633</v>
       </c>
     </row>
     <row r="45" spans="3:15">
       <c r="C45" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>630</v>
+        <v>635</v>
       </c>
     </row>
     <row r="46" ht="17.6" customHeight="1" spans="1:15">
@@ -11080,42 +11229,42 @@
         <v>31</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D46" s="1">
         <v>50</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
     </row>
     <row r="47" spans="3:15">
       <c r="C47" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>635</v>
+        <v>640</v>
       </c>
     </row>
     <row r="48" ht="17.6" customHeight="1" spans="1:15">
@@ -11123,42 +11272,42 @@
         <v>32</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D48" s="1">
         <v>40</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>638</v>
+        <v>643</v>
       </c>
     </row>
     <row r="49" spans="3:15">
       <c r="C49" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>640</v>
+        <v>645</v>
       </c>
     </row>
     <row r="50" ht="17.6" customHeight="1" spans="1:15">
@@ -11166,42 +11315,42 @@
         <v>33</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D50" s="1">
         <v>30</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>643</v>
+        <v>648</v>
       </c>
     </row>
     <row r="51" spans="3:15">
       <c r="C51" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>645</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52" ht="17.6" customHeight="1" spans="1:15">
@@ -11209,42 +11358,42 @@
         <v>34</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D52" s="1">
         <v>50</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>646</v>
+        <v>651</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
     </row>
     <row r="53" spans="3:15">
       <c r="C53" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
     </row>
     <row r="54" ht="17.6" customHeight="1" spans="1:9">
@@ -11252,35 +11401,35 @@
         <v>35</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D54" s="1">
         <v>40</v>
       </c>
       <c r="E54" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H54" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>647</v>
-      </c>
       <c r="I54" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="55" spans="3:3">
       <c r="C55" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="56" spans="3:3">
       <c r="C56" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57" ht="17.6" customHeight="1" spans="1:9">
@@ -11288,35 +11437,35 @@
         <v>36</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D57" s="1">
         <v>30</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="58" spans="3:3">
       <c r="C58" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="59" spans="3:3">
       <c r="C59" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" ht="17.6" customHeight="1" spans="1:9">
@@ -11324,30 +11473,30 @@
         <v>37</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D60" s="1">
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="62" ht="17.6" customHeight="1" spans="1:9">
@@ -11355,30 +11504,30 @@
         <v>38</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D62" s="1">
         <v>30</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="63" spans="3:3">
       <c r="C63" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64" ht="17.6" customHeight="1" spans="1:9">
@@ -11386,35 +11535,35 @@
         <v>39</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D64" s="1">
         <v>50</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="3:3">
       <c r="C66" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67" ht="17.6" customHeight="1" spans="1:9">
@@ -11422,35 +11571,35 @@
         <v>40</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D67" s="1">
         <v>40</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="68" spans="3:3">
       <c r="C68" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="3:3">
       <c r="C69" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" ht="17.6" customHeight="1" spans="1:9">
@@ -11458,30 +11607,30 @@
         <v>41</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D70" s="1">
         <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>658</v>
+        <v>663</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="72" ht="17.6" customHeight="1" spans="1:9">
@@ -11489,30 +11638,30 @@
         <v>42</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D72" s="1">
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>659</v>
+        <v>664</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="74" ht="17.6" customHeight="1" spans="1:9">
@@ -11520,30 +11669,30 @@
         <v>43</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D74" s="1">
         <v>30</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="75" spans="3:3">
       <c r="C75" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="76" ht="17.6" customHeight="1" spans="1:12">
@@ -11551,25 +11700,25 @@
         <v>44</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D76" s="1">
         <v>40</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>661</v>
+        <v>666</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="J76" s="15"/>
       <c r="K76" s="17"/>
@@ -11577,13 +11726,13 @@
     </row>
     <row r="77" ht="17.6" customHeight="1" spans="3:11">
       <c r="C77" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K77" s="17"/>
     </row>
     <row r="78" ht="17.6" customHeight="1" spans="3:12">
       <c r="C78" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K78" s="17"/>
       <c r="L78" s="17"/>
@@ -11593,41 +11742,41 @@
         <v>45</v>
       </c>
       <c r="B79" s="16" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D79" s="1">
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>662</v>
+        <v>667</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" spans="3:3">
       <c r="C80" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" ht="17.6" customHeight="1" spans="3:11">
       <c r="C81" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="K81" s="17"/>
     </row>
     <row r="82" ht="17.6" customHeight="1" spans="3:12">
       <c r="C82" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
@@ -11635,7 +11784,7 @@
     </row>
     <row r="83" ht="17.6" customHeight="1" spans="3:12">
       <c r="C83" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
@@ -11646,25 +11795,25 @@
         <v>46</v>
       </c>
       <c r="B84" s="16" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D84" s="1">
         <v>80</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>663</v>
+        <v>668</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="J84" s="17"/>
       <c r="K84" s="17"/>
@@ -11672,7 +11821,7 @@
     </row>
     <row r="85" ht="17.6" customHeight="1" spans="3:12">
       <c r="C85" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J85" s="17"/>
       <c r="K85" s="17"/>
@@ -11680,7 +11829,7 @@
     </row>
     <row r="86" ht="17.6" customHeight="1" spans="3:12">
       <c r="C86" s="1" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J86" s="17"/>
       <c r="K86" s="17"/>
@@ -11691,42 +11840,42 @@
         <v>47</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D87" s="1">
         <v>140</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>664</v>
+        <v>669</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="K87" s="17"/>
       <c r="L87" s="17"/>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="89" spans="3:3">
       <c r="C89" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -11751,16 +11900,16 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -11772,19 +11921,19 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -11792,85 +11941,85 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="3" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="8:18">
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="3" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="8:18">
       <c r="H8" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="3" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="8:18">
@@ -11879,22 +12028,22 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>666</v>
+        <v>671</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>667</v>
+        <v>672</v>
       </c>
       <c r="R9" s="3"/>
     </row>
@@ -11905,16 +12054,16 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -11926,10 +12075,10 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -11943,10 +12092,10 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>665</v>
+        <v>670</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -6634,7 +6634,7 @@
         <v>23</v>
       </c>
       <c r="E4" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F4" s="1">
         <f>VLOOKUP(C4,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6657,7 +6657,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1">
         <f>VLOOKUP(C5,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6680,7 +6680,7 @@
         <v>32</v>
       </c>
       <c r="E6" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1">
         <f>VLOOKUP(C6,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6703,7 +6703,7 @@
         <v>35</v>
       </c>
       <c r="E7" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1">
         <f>VLOOKUP(C7,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6726,7 +6726,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1">
         <f>VLOOKUP(C8,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6749,7 +6749,7 @@
         <v>41</v>
       </c>
       <c r="E9" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
         <f>VLOOKUP(C9,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6772,7 +6772,7 @@
         <v>44</v>
       </c>
       <c r="E10" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <f>VLOOKUP(C10,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6795,7 +6795,7 @@
         <v>47</v>
       </c>
       <c r="E11" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F11" s="1">
         <f>VLOOKUP(C11,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6818,7 +6818,7 @@
         <v>50</v>
       </c>
       <c r="E12" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F12" s="1">
         <f>VLOOKUP(C12,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6841,7 +6841,7 @@
         <v>54</v>
       </c>
       <c r="E13" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F13" s="1">
         <f>VLOOKUP(C13,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6864,7 +6864,7 @@
         <v>58</v>
       </c>
       <c r="E14" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F14" s="1">
         <f>VLOOKUP(C14,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6887,7 +6887,7 @@
         <v>62</v>
       </c>
       <c r="E15" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F15" s="1">
         <f>VLOOKUP(C15,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6910,7 +6910,7 @@
         <v>66</v>
       </c>
       <c r="E16" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1">
         <f>VLOOKUP(C16,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6933,7 +6933,7 @@
         <v>70</v>
       </c>
       <c r="E17" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1">
         <f>VLOOKUP(C17,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6956,7 +6956,7 @@
         <v>74</v>
       </c>
       <c r="E18" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F18" s="1">
         <f>VLOOKUP(C18,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -6979,7 +6979,7 @@
         <v>77</v>
       </c>
       <c r="E19" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F19" s="1">
         <f>VLOOKUP(C19,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7002,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="E20" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F20" s="1">
         <f>VLOOKUP(C20,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7025,7 +7025,7 @@
         <v>83</v>
       </c>
       <c r="E21" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1">
         <f>VLOOKUP(C21,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7048,7 +7048,7 @@
         <v>87</v>
       </c>
       <c r="E22" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F22" s="1">
         <f>VLOOKUP(C22,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7071,7 +7071,7 @@
         <v>94</v>
       </c>
       <c r="E23" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F23" s="1">
         <f>VLOOKUP(C23,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7094,7 +7094,7 @@
         <v>101</v>
       </c>
       <c r="E24" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F24" s="1">
         <f>VLOOKUP(C24,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7117,7 +7117,7 @@
         <v>107</v>
       </c>
       <c r="E25" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F25" s="1">
         <f>VLOOKUP(C25,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7140,7 +7140,7 @@
         <v>113</v>
       </c>
       <c r="E26" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F26" s="1">
         <f>VLOOKUP(C26,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7163,7 +7163,7 @@
         <v>116</v>
       </c>
       <c r="E27" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F27" s="1">
         <f>VLOOKUP(C27,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7186,7 +7186,7 @@
         <v>119</v>
       </c>
       <c r="E28" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F28" s="1">
         <f>VLOOKUP(C28,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7209,7 +7209,7 @@
         <v>122</v>
       </c>
       <c r="E29" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F29" s="1">
         <f>VLOOKUP(C29,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7232,7 +7232,7 @@
         <v>125</v>
       </c>
       <c r="E30" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F30" s="1">
         <f>VLOOKUP(C30,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7255,7 +7255,7 @@
         <v>128</v>
       </c>
       <c r="E31" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F31" s="1">
         <f>VLOOKUP(C31,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7278,7 +7278,7 @@
         <v>131</v>
       </c>
       <c r="E32" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F32" s="1">
         <f>VLOOKUP(C32,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7301,7 +7301,7 @@
         <v>134</v>
       </c>
       <c r="E33" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1">
         <f>VLOOKUP(C33,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7324,7 +7324,7 @@
         <v>137</v>
       </c>
       <c r="E34" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F34" s="1">
         <f>VLOOKUP(C34,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7347,7 +7347,7 @@
         <v>140</v>
       </c>
       <c r="E35" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F35" s="1">
         <f>VLOOKUP(C35,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7370,7 +7370,7 @@
         <v>143</v>
       </c>
       <c r="E36" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F36" s="1">
         <f>VLOOKUP(C36,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7393,7 +7393,7 @@
         <v>146</v>
       </c>
       <c r="E37" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F37" s="1">
         <f>VLOOKUP(C37,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7416,7 +7416,7 @@
         <v>149</v>
       </c>
       <c r="E38" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F38" s="1">
         <f>VLOOKUP(C38,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7439,7 +7439,7 @@
         <v>151</v>
       </c>
       <c r="E39" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F39" s="1">
         <f>VLOOKUP(C39,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7462,7 +7462,7 @@
         <v>154</v>
       </c>
       <c r="E40" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F40" s="1">
         <f>VLOOKUP(C40,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7485,7 +7485,7 @@
         <v>157</v>
       </c>
       <c r="E41" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F41" s="1">
         <f>VLOOKUP(C41,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7508,7 +7508,7 @@
         <v>160</v>
       </c>
       <c r="E42" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F42" s="1">
         <f>VLOOKUP(C42,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7531,7 +7531,7 @@
         <v>163</v>
       </c>
       <c r="E43" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F43" s="1">
         <f>VLOOKUP(C43,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7554,7 +7554,7 @@
         <v>166</v>
       </c>
       <c r="E44" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F44" s="1">
         <f>VLOOKUP(C44,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7577,7 +7577,7 @@
         <v>169</v>
       </c>
       <c r="E45" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F45" s="1">
         <f>VLOOKUP(C45,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7600,7 +7600,7 @@
         <v>173</v>
       </c>
       <c r="E46" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F46" s="1">
         <f>VLOOKUP(C46,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7623,7 +7623,7 @@
         <v>177</v>
       </c>
       <c r="E47" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F47" s="1">
         <f>VLOOKUP(C47,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7646,7 +7646,7 @@
         <v>180</v>
       </c>
       <c r="E48" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F48" s="1">
         <f>VLOOKUP(C48,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7669,7 +7669,7 @@
         <v>184</v>
       </c>
       <c r="E49" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F49" s="1">
         <f>VLOOKUP(C49,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7692,7 +7692,7 @@
         <v>187</v>
       </c>
       <c r="E50" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F50" s="1">
         <f>VLOOKUP(C50,dish_base!$B$4:$O$92,13,FALSE)</f>
@@ -7718,7 +7718,7 @@
         <v>209</v>
       </c>
       <c r="E51" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F51" s="1">
         <f>VLOOKUP(C51,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7744,7 +7744,7 @@
         <v>209</v>
       </c>
       <c r="E52" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F52" s="1">
         <f>VLOOKUP(C52,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7770,7 +7770,7 @@
         <v>209</v>
       </c>
       <c r="E53" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F53" s="1">
         <f>VLOOKUP(C53,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7796,7 +7796,7 @@
         <v>209</v>
       </c>
       <c r="E54" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F54" s="1">
         <f>VLOOKUP(C54,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7822,7 +7822,7 @@
         <v>209</v>
       </c>
       <c r="E55" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F55" s="1">
         <f>VLOOKUP(C55,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7848,7 +7848,7 @@
         <v>209</v>
       </c>
       <c r="E56" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F56" s="1">
         <f>VLOOKUP(C56,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7874,7 +7874,7 @@
         <v>209</v>
       </c>
       <c r="E57" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F57" s="1">
         <f>VLOOKUP(C57,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7900,7 +7900,7 @@
         <v>209</v>
       </c>
       <c r="E58" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F58" s="1">
         <f>VLOOKUP(C58,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7926,7 +7926,7 @@
         <v>209</v>
       </c>
       <c r="E59" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F59" s="1">
         <f>VLOOKUP(C59,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7952,7 +7952,7 @@
         <v>209</v>
       </c>
       <c r="E60" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F60" s="1">
         <f>VLOOKUP(C60,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -7978,7 +7978,7 @@
         <v>209</v>
       </c>
       <c r="E61" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F61" s="1">
         <f>VLOOKUP(C61,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8004,7 +8004,7 @@
         <v>209</v>
       </c>
       <c r="E62" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F62" s="1">
         <f>VLOOKUP(C62,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8030,7 +8030,7 @@
         <v>209</v>
       </c>
       <c r="E63" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F63" s="1">
         <f>VLOOKUP(C63,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8056,7 +8056,7 @@
         <v>209</v>
       </c>
       <c r="E64" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F64" s="1">
         <f>VLOOKUP(C64,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8082,7 +8082,7 @@
         <v>209</v>
       </c>
       <c r="E65" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F65" s="1">
         <f>VLOOKUP(C65,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8108,7 +8108,7 @@
         <v>209</v>
       </c>
       <c r="E66" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F66" s="1">
         <f>VLOOKUP(C66,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8134,7 +8134,7 @@
         <v>209</v>
       </c>
       <c r="E67" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F67" s="1">
         <f>VLOOKUP(C67,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8160,7 +8160,7 @@
         <v>209</v>
       </c>
       <c r="E68" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F68" s="1">
         <f>VLOOKUP(C68,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8186,7 +8186,7 @@
         <v>209</v>
       </c>
       <c r="E69" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F69" s="1">
         <f>VLOOKUP(C69,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8212,7 +8212,7 @@
         <v>209</v>
       </c>
       <c r="E70" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F70" s="1">
         <f>VLOOKUP(C70,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8238,7 +8238,7 @@
         <v>209</v>
       </c>
       <c r="E71" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F71" s="1">
         <f>VLOOKUP(C71,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8264,7 +8264,7 @@
         <v>209</v>
       </c>
       <c r="E72" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F72" s="1">
         <f>VLOOKUP(C72,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8290,7 +8290,7 @@
         <v>209</v>
       </c>
       <c r="E73" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F73" s="1">
         <f>VLOOKUP(C73,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8316,7 +8316,7 @@
         <v>209</v>
       </c>
       <c r="E74" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F74" s="1">
         <f>VLOOKUP(C74,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8342,7 +8342,7 @@
         <v>209</v>
       </c>
       <c r="E75" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F75" s="1">
         <f>VLOOKUP(C75,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8368,7 +8368,7 @@
         <v>209</v>
       </c>
       <c r="E76" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F76" s="1">
         <f>VLOOKUP(C76,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8394,7 +8394,7 @@
         <v>209</v>
       </c>
       <c r="E77" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F77" s="1">
         <f>VLOOKUP(C77,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8420,7 +8420,7 @@
         <v>209</v>
       </c>
       <c r="E78" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F78" s="1">
         <f>VLOOKUP(C78,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8446,7 +8446,7 @@
         <v>209</v>
       </c>
       <c r="E79" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F79" s="1">
         <f>VLOOKUP(C79,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8472,7 +8472,7 @@
         <v>209</v>
       </c>
       <c r="E80" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F80" s="1">
         <f>VLOOKUP(C80,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8498,7 +8498,7 @@
         <v>209</v>
       </c>
       <c r="E81" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F81" s="1">
         <f>VLOOKUP(C81,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8524,7 +8524,7 @@
         <v>209</v>
       </c>
       <c r="E82" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F82" s="1">
         <f>VLOOKUP(C82,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8550,7 +8550,7 @@
         <v>209</v>
       </c>
       <c r="E83" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F83" s="1">
         <f>VLOOKUP(C83,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8576,7 +8576,7 @@
         <v>209</v>
       </c>
       <c r="E84" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F84" s="1">
         <f>VLOOKUP(C84,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8602,7 +8602,7 @@
         <v>209</v>
       </c>
       <c r="E85" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F85" s="1">
         <f>VLOOKUP(C85,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8628,7 +8628,7 @@
         <v>209</v>
       </c>
       <c r="E86" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F86" s="1">
         <f>VLOOKUP(C86,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8654,7 +8654,7 @@
         <v>209</v>
       </c>
       <c r="E87" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F87" s="1">
         <f>VLOOKUP(C87,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8680,7 +8680,7 @@
         <v>209</v>
       </c>
       <c r="E88" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F88" s="1">
         <f>VLOOKUP(C88,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8706,7 +8706,7 @@
         <v>209</v>
       </c>
       <c r="E89" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F89" s="1">
         <f>VLOOKUP(C89,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8732,7 +8732,7 @@
         <v>209</v>
       </c>
       <c r="E90" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F90" s="1">
         <f>VLOOKUP(C90,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8758,7 +8758,7 @@
         <v>209</v>
       </c>
       <c r="E91" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F91" s="1">
         <f>VLOOKUP(C91,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8784,7 +8784,7 @@
         <v>209</v>
       </c>
       <c r="E92" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F92" s="1">
         <f>VLOOKUP(C92,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8810,7 +8810,7 @@
         <v>209</v>
       </c>
       <c r="E93" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F93" s="1">
         <f>VLOOKUP(C93,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8836,7 +8836,7 @@
         <v>209</v>
       </c>
       <c r="E94" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F94" s="1">
         <f>VLOOKUP(C94,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8862,7 +8862,7 @@
         <v>209</v>
       </c>
       <c r="E95" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F95" s="1">
         <f>VLOOKUP(C95,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8888,7 +8888,7 @@
         <v>209</v>
       </c>
       <c r="E96" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F96" s="1">
         <f>VLOOKUP(C96,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8914,7 +8914,7 @@
         <v>209</v>
       </c>
       <c r="E97" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F97" s="1">
         <f>VLOOKUP(C97,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8940,7 +8940,7 @@
         <v>210</v>
       </c>
       <c r="E98" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F98" s="1">
         <f>VLOOKUP(C98,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8966,7 +8966,7 @@
         <v>210</v>
       </c>
       <c r="E99" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F99" s="1">
         <f>VLOOKUP(C99,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -8992,7 +8992,7 @@
         <v>210</v>
       </c>
       <c r="E100" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F100" s="1">
         <f>VLOOKUP(C100,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9018,7 +9018,7 @@
         <v>210</v>
       </c>
       <c r="E101" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F101" s="1">
         <f>VLOOKUP(C101,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9044,7 +9044,7 @@
         <v>210</v>
       </c>
       <c r="E102" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F102" s="1">
         <f>VLOOKUP(C102,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9070,7 +9070,7 @@
         <v>210</v>
       </c>
       <c r="E103" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F103" s="1">
         <f>VLOOKUP(C103,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9096,7 +9096,7 @@
         <v>210</v>
       </c>
       <c r="E104" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F104" s="1">
         <f>VLOOKUP(C104,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9122,7 +9122,7 @@
         <v>210</v>
       </c>
       <c r="E105" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F105" s="1">
         <f>VLOOKUP(C105,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9148,7 +9148,7 @@
         <v>210</v>
       </c>
       <c r="E106" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F106" s="1">
         <f>VLOOKUP(C106,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9174,7 +9174,7 @@
         <v>210</v>
       </c>
       <c r="E107" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F107" s="1">
         <f>VLOOKUP(C107,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9200,7 +9200,7 @@
         <v>210</v>
       </c>
       <c r="E108" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F108" s="1">
         <f>VLOOKUP(C108,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9226,7 +9226,7 @@
         <v>210</v>
       </c>
       <c r="E109" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F109" s="1">
         <f>VLOOKUP(C109,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9252,7 +9252,7 @@
         <v>210</v>
       </c>
       <c r="E110" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F110" s="1">
         <f>VLOOKUP(C110,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9278,7 +9278,7 @@
         <v>210</v>
       </c>
       <c r="E111" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F111" s="1">
         <f>VLOOKUP(C111,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9304,7 +9304,7 @@
         <v>210</v>
       </c>
       <c r="E112" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F112" s="1">
         <f>VLOOKUP(C112,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9330,7 +9330,7 @@
         <v>210</v>
       </c>
       <c r="E113" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F113" s="1">
         <f>VLOOKUP(C113,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9356,7 +9356,7 @@
         <v>210</v>
       </c>
       <c r="E114" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F114" s="1">
         <f>VLOOKUP(C114,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9382,7 +9382,7 @@
         <v>210</v>
       </c>
       <c r="E115" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F115" s="1">
         <f>VLOOKUP(C115,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9408,7 +9408,7 @@
         <v>210</v>
       </c>
       <c r="E116" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F116" s="1">
         <f>VLOOKUP(C116,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9434,7 +9434,7 @@
         <v>210</v>
       </c>
       <c r="E117" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F117" s="1">
         <f>VLOOKUP(C117,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9460,7 +9460,7 @@
         <v>210</v>
       </c>
       <c r="E118" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F118" s="1">
         <f>VLOOKUP(C118,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9486,7 +9486,7 @@
         <v>210</v>
       </c>
       <c r="E119" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F119" s="1">
         <f>VLOOKUP(C119,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9512,7 +9512,7 @@
         <v>210</v>
       </c>
       <c r="E120" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F120" s="1">
         <f>VLOOKUP(C120,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9538,7 +9538,7 @@
         <v>210</v>
       </c>
       <c r="E121" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F121" s="1">
         <f>VLOOKUP(C121,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9564,7 +9564,7 @@
         <v>210</v>
       </c>
       <c r="E122" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F122" s="1">
         <f>VLOOKUP(C122,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9590,7 +9590,7 @@
         <v>210</v>
       </c>
       <c r="E123" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F123" s="1">
         <f>VLOOKUP(C123,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9616,7 +9616,7 @@
         <v>210</v>
       </c>
       <c r="E124" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F124" s="1">
         <f>VLOOKUP(C124,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9642,7 +9642,7 @@
         <v>210</v>
       </c>
       <c r="E125" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F125" s="1">
         <f>VLOOKUP(C125,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9668,7 +9668,7 @@
         <v>210</v>
       </c>
       <c r="E126" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F126" s="1">
         <f>VLOOKUP(C126,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9694,7 +9694,7 @@
         <v>210</v>
       </c>
       <c r="E127" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F127" s="1">
         <f>VLOOKUP(C127,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9720,7 +9720,7 @@
         <v>210</v>
       </c>
       <c r="E128" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F128" s="1">
         <f>VLOOKUP(C128,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9746,7 +9746,7 @@
         <v>210</v>
       </c>
       <c r="E129" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F129" s="1">
         <f>VLOOKUP(C129,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9772,7 +9772,7 @@
         <v>210</v>
       </c>
       <c r="E130" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F130" s="1">
         <f>VLOOKUP(C130,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9798,7 +9798,7 @@
         <v>210</v>
       </c>
       <c r="E131" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F131" s="1">
         <f>VLOOKUP(C131,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9824,7 +9824,7 @@
         <v>210</v>
       </c>
       <c r="E132" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F132" s="1">
         <f>VLOOKUP(C132,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9850,7 +9850,7 @@
         <v>210</v>
       </c>
       <c r="E133" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F133" s="1">
         <f>VLOOKUP(C133,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9876,7 +9876,7 @@
         <v>210</v>
       </c>
       <c r="E134" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F134" s="1">
         <f>VLOOKUP(C134,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9902,7 +9902,7 @@
         <v>210</v>
       </c>
       <c r="E135" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F135" s="1">
         <f>VLOOKUP(C135,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9928,7 +9928,7 @@
         <v>210</v>
       </c>
       <c r="E136" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F136" s="1">
         <f>VLOOKUP(C136,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9954,7 +9954,7 @@
         <v>210</v>
       </c>
       <c r="E137" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F137" s="1">
         <f>VLOOKUP(C137,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -9980,7 +9980,7 @@
         <v>210</v>
       </c>
       <c r="E138" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F138" s="1">
         <f>VLOOKUP(C138,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10006,7 +10006,7 @@
         <v>210</v>
       </c>
       <c r="E139" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F139" s="1">
         <f>VLOOKUP(C139,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10032,7 +10032,7 @@
         <v>210</v>
       </c>
       <c r="E140" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F140" s="1">
         <f>VLOOKUP(C140,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10058,7 +10058,7 @@
         <v>210</v>
       </c>
       <c r="E141" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F141" s="1">
         <f>VLOOKUP(C141,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10084,7 +10084,7 @@
         <v>210</v>
       </c>
       <c r="E142" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F142" s="1">
         <f>VLOOKUP(C142,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10110,7 +10110,7 @@
         <v>210</v>
       </c>
       <c r="E143" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F143" s="1">
         <f>VLOOKUP(C143,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10136,7 +10136,7 @@
         <v>210</v>
       </c>
       <c r="E144" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F144" s="1">
         <f>VLOOKUP(C144,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10162,7 +10162,7 @@
         <v>211</v>
       </c>
       <c r="E145" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F145" s="1">
         <f>VLOOKUP(C145,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10188,7 +10188,7 @@
         <v>211</v>
       </c>
       <c r="E146" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F146" s="1">
         <f>VLOOKUP(C146,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10214,7 +10214,7 @@
         <v>211</v>
       </c>
       <c r="E147" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F147" s="1">
         <f>VLOOKUP(C147,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10240,7 +10240,7 @@
         <v>211</v>
       </c>
       <c r="E148" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F148" s="1">
         <f>VLOOKUP(C148,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10266,7 +10266,7 @@
         <v>211</v>
       </c>
       <c r="E149" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F149" s="1">
         <f>VLOOKUP(C149,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10292,7 +10292,7 @@
         <v>211</v>
       </c>
       <c r="E150" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F150" s="1">
         <f>VLOOKUP(C150,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10318,7 +10318,7 @@
         <v>211</v>
       </c>
       <c r="E151" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F151" s="1">
         <f>VLOOKUP(C151,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10344,7 +10344,7 @@
         <v>211</v>
       </c>
       <c r="E152" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F152" s="1">
         <f>VLOOKUP(C152,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10370,7 +10370,7 @@
         <v>211</v>
       </c>
       <c r="E153" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F153" s="1">
         <f>VLOOKUP(C153,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10396,7 +10396,7 @@
         <v>211</v>
       </c>
       <c r="E154" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F154" s="1">
         <f>VLOOKUP(C154,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10422,7 +10422,7 @@
         <v>211</v>
       </c>
       <c r="E155" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F155" s="1">
         <f>VLOOKUP(C155,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10448,7 +10448,7 @@
         <v>211</v>
       </c>
       <c r="E156" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F156" s="1">
         <f>VLOOKUP(C156,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10474,7 +10474,7 @@
         <v>211</v>
       </c>
       <c r="E157" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F157" s="1">
         <f>VLOOKUP(C157,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10500,7 +10500,7 @@
         <v>211</v>
       </c>
       <c r="E158" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F158" s="1">
         <f>VLOOKUP(C158,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10526,7 +10526,7 @@
         <v>211</v>
       </c>
       <c r="E159" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F159" s="1">
         <f>VLOOKUP(C159,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10552,7 +10552,7 @@
         <v>211</v>
       </c>
       <c r="E160" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F160" s="1">
         <f>VLOOKUP(C160,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10578,7 +10578,7 @@
         <v>211</v>
       </c>
       <c r="E161" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F161" s="1">
         <f>VLOOKUP(C161,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10604,7 +10604,7 @@
         <v>211</v>
       </c>
       <c r="E162" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F162" s="1">
         <f>VLOOKUP(C162,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10630,7 +10630,7 @@
         <v>211</v>
       </c>
       <c r="E163" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F163" s="1">
         <f>VLOOKUP(C163,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10656,7 +10656,7 @@
         <v>211</v>
       </c>
       <c r="E164" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F164" s="1">
         <f>VLOOKUP(C164,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10682,7 +10682,7 @@
         <v>211</v>
       </c>
       <c r="E165" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F165" s="1">
         <f>VLOOKUP(C165,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10708,7 +10708,7 @@
         <v>211</v>
       </c>
       <c r="E166" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F166" s="1">
         <f>VLOOKUP(C166,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10734,7 +10734,7 @@
         <v>211</v>
       </c>
       <c r="E167" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F167" s="1">
         <f>VLOOKUP(C167,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10760,7 +10760,7 @@
         <v>211</v>
       </c>
       <c r="E168" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F168" s="1">
         <f>VLOOKUP(C168,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10786,7 +10786,7 @@
         <v>211</v>
       </c>
       <c r="E169" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F169" s="1">
         <f>VLOOKUP(C169,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10812,7 +10812,7 @@
         <v>211</v>
       </c>
       <c r="E170" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F170" s="1">
         <f>VLOOKUP(C170,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10838,7 +10838,7 @@
         <v>211</v>
       </c>
       <c r="E171" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F171" s="1">
         <f>VLOOKUP(C171,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10864,7 +10864,7 @@
         <v>211</v>
       </c>
       <c r="E172" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F172" s="1">
         <f>VLOOKUP(C172,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10890,7 +10890,7 @@
         <v>211</v>
       </c>
       <c r="E173" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F173" s="1">
         <f>VLOOKUP(C173,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10916,7 +10916,7 @@
         <v>211</v>
       </c>
       <c r="E174" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F174" s="1">
         <f>VLOOKUP(C174,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10942,7 +10942,7 @@
         <v>211</v>
       </c>
       <c r="E175" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F175" s="1">
         <f>VLOOKUP(C175,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10968,7 +10968,7 @@
         <v>211</v>
       </c>
       <c r="E176" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F176" s="1">
         <f>VLOOKUP(C176,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -10994,7 +10994,7 @@
         <v>211</v>
       </c>
       <c r="E177" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F177" s="1">
         <f>VLOOKUP(C177,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11020,7 +11020,7 @@
         <v>211</v>
       </c>
       <c r="E178" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F178" s="1">
         <f>VLOOKUP(C178,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11046,7 +11046,7 @@
         <v>211</v>
       </c>
       <c r="E179" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F179" s="1">
         <f>VLOOKUP(C179,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11072,7 +11072,7 @@
         <v>211</v>
       </c>
       <c r="E180" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F180" s="1">
         <f>VLOOKUP(C180,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11098,7 +11098,7 @@
         <v>211</v>
       </c>
       <c r="E181" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F181" s="1">
         <f>VLOOKUP(C181,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11124,7 +11124,7 @@
         <v>211</v>
       </c>
       <c r="E182" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F182" s="1">
         <f>VLOOKUP(C182,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11150,7 +11150,7 @@
         <v>211</v>
       </c>
       <c r="E183" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F183" s="1">
         <f>VLOOKUP(C183,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11176,7 +11176,7 @@
         <v>211</v>
       </c>
       <c r="E184" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F184" s="1">
         <f>VLOOKUP(C184,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11202,7 +11202,7 @@
         <v>211</v>
       </c>
       <c r="E185" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F185" s="1">
         <f>VLOOKUP(C185,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11228,7 +11228,7 @@
         <v>211</v>
       </c>
       <c r="E186" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F186" s="1">
         <f>VLOOKUP(C186,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11254,7 +11254,7 @@
         <v>211</v>
       </c>
       <c r="E187" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F187" s="1">
         <f>VLOOKUP(C187,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11280,7 +11280,7 @@
         <v>211</v>
       </c>
       <c r="E188" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F188" s="1">
         <f>VLOOKUP(C188,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11306,7 +11306,7 @@
         <v>211</v>
       </c>
       <c r="E189" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F189" s="1">
         <f>VLOOKUP(C189,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11332,7 +11332,7 @@
         <v>211</v>
       </c>
       <c r="E190" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F190" s="1">
         <f>VLOOKUP(C190,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11358,7 +11358,7 @@
         <v>211</v>
       </c>
       <c r="E191" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F191" s="1">
         <f>VLOOKUP(C191,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11384,7 +11384,7 @@
         <v>212</v>
       </c>
       <c r="E192" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F192" s="1">
         <f>VLOOKUP(C192,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11410,7 +11410,7 @@
         <v>212</v>
       </c>
       <c r="E193" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F193" s="1">
         <f>VLOOKUP(C193,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11436,7 +11436,7 @@
         <v>212</v>
       </c>
       <c r="E194" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F194" s="1">
         <f>VLOOKUP(C194,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11462,7 +11462,7 @@
         <v>212</v>
       </c>
       <c r="E195" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F195" s="1">
         <f>VLOOKUP(C195,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11488,7 +11488,7 @@
         <v>212</v>
       </c>
       <c r="E196" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F196" s="1">
         <f>VLOOKUP(C196,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11514,7 +11514,7 @@
         <v>212</v>
       </c>
       <c r="E197" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F197" s="1">
         <f>VLOOKUP(C197,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11540,7 +11540,7 @@
         <v>212</v>
       </c>
       <c r="E198" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F198" s="1">
         <f>VLOOKUP(C198,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11566,7 +11566,7 @@
         <v>212</v>
       </c>
       <c r="E199" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F199" s="1">
         <f>VLOOKUP(C199,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11592,7 +11592,7 @@
         <v>212</v>
       </c>
       <c r="E200" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F200" s="1">
         <f>VLOOKUP(C200,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11618,7 +11618,7 @@
         <v>212</v>
       </c>
       <c r="E201" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F201" s="1">
         <f>VLOOKUP(C201,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11644,7 +11644,7 @@
         <v>212</v>
       </c>
       <c r="E202" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F202" s="1">
         <f>VLOOKUP(C202,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11670,7 +11670,7 @@
         <v>212</v>
       </c>
       <c r="E203" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F203" s="1">
         <f>VLOOKUP(C203,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11696,7 +11696,7 @@
         <v>212</v>
       </c>
       <c r="E204" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F204" s="1">
         <f>VLOOKUP(C204,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11722,7 +11722,7 @@
         <v>212</v>
       </c>
       <c r="E205" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F205" s="1">
         <f>VLOOKUP(C205,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11748,7 +11748,7 @@
         <v>212</v>
       </c>
       <c r="E206" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F206" s="1">
         <f>VLOOKUP(C206,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11774,7 +11774,7 @@
         <v>212</v>
       </c>
       <c r="E207" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F207" s="1">
         <f>VLOOKUP(C207,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11800,7 +11800,7 @@
         <v>212</v>
       </c>
       <c r="E208" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F208" s="1">
         <f>VLOOKUP(C208,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11826,7 +11826,7 @@
         <v>212</v>
       </c>
       <c r="E209" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F209" s="1">
         <f>VLOOKUP(C209,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11852,7 +11852,7 @@
         <v>212</v>
       </c>
       <c r="E210" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F210" s="1">
         <f>VLOOKUP(C210,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11878,7 +11878,7 @@
         <v>212</v>
       </c>
       <c r="E211" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F211" s="1">
         <f>VLOOKUP(C211,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11904,7 +11904,7 @@
         <v>212</v>
       </c>
       <c r="E212" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F212" s="1">
         <f>VLOOKUP(C212,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11930,7 +11930,7 @@
         <v>212</v>
       </c>
       <c r="E213" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F213" s="1">
         <f>VLOOKUP(C213,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11956,7 +11956,7 @@
         <v>212</v>
       </c>
       <c r="E214" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F214" s="1">
         <f>VLOOKUP(C214,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -11982,7 +11982,7 @@
         <v>212</v>
       </c>
       <c r="E215" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F215" s="1">
         <f>VLOOKUP(C215,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12008,7 +12008,7 @@
         <v>212</v>
       </c>
       <c r="E216" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F216" s="1">
         <f>VLOOKUP(C216,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12034,7 +12034,7 @@
         <v>212</v>
       </c>
       <c r="E217" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F217" s="1">
         <f>VLOOKUP(C217,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12060,7 +12060,7 @@
         <v>212</v>
       </c>
       <c r="E218" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F218" s="1">
         <f>VLOOKUP(C218,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12086,7 +12086,7 @@
         <v>212</v>
       </c>
       <c r="E219" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F219" s="1">
         <f>VLOOKUP(C219,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12112,7 +12112,7 @@
         <v>212</v>
       </c>
       <c r="E220" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F220" s="1">
         <f>VLOOKUP(C220,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12138,7 +12138,7 @@
         <v>212</v>
       </c>
       <c r="E221" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F221" s="1">
         <f>VLOOKUP(C221,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12164,7 +12164,7 @@
         <v>212</v>
       </c>
       <c r="E222" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F222" s="1">
         <f>VLOOKUP(C222,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12190,7 +12190,7 @@
         <v>212</v>
       </c>
       <c r="E223" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F223" s="1">
         <f>VLOOKUP(C223,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12216,7 +12216,7 @@
         <v>212</v>
       </c>
       <c r="E224" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F224" s="1">
         <f>VLOOKUP(C224,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12242,7 +12242,7 @@
         <v>212</v>
       </c>
       <c r="E225" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F225" s="1">
         <f>VLOOKUP(C225,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12268,7 +12268,7 @@
         <v>212</v>
       </c>
       <c r="E226" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F226" s="1">
         <f>VLOOKUP(C226,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12294,7 +12294,7 @@
         <v>212</v>
       </c>
       <c r="E227" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F227" s="1">
         <f>VLOOKUP(C227,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12320,7 +12320,7 @@
         <v>212</v>
       </c>
       <c r="E228" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F228" s="1">
         <f>VLOOKUP(C228,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12346,7 +12346,7 @@
         <v>212</v>
       </c>
       <c r="E229" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F229" s="1">
         <f>VLOOKUP(C229,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12372,7 +12372,7 @@
         <v>212</v>
       </c>
       <c r="E230" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F230" s="1">
         <f>VLOOKUP(C230,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12398,7 +12398,7 @@
         <v>212</v>
       </c>
       <c r="E231" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F231" s="1">
         <f>VLOOKUP(C231,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12424,7 +12424,7 @@
         <v>212</v>
       </c>
       <c r="E232" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F232" s="1">
         <f>VLOOKUP(C232,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12450,7 +12450,7 @@
         <v>212</v>
       </c>
       <c r="E233" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F233" s="1">
         <f>VLOOKUP(C233,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12476,7 +12476,7 @@
         <v>212</v>
       </c>
       <c r="E234" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F234" s="1">
         <f>VLOOKUP(C234,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12502,7 +12502,7 @@
         <v>212</v>
       </c>
       <c r="E235" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F235" s="1">
         <f>VLOOKUP(C235,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12528,7 +12528,7 @@
         <v>212</v>
       </c>
       <c r="E236" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F236" s="1">
         <f>VLOOKUP(C236,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12554,7 +12554,7 @@
         <v>212</v>
       </c>
       <c r="E237" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F237" s="1">
         <f>VLOOKUP(C237,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12580,7 +12580,7 @@
         <v>212</v>
       </c>
       <c r="E238" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F238" s="1">
         <f>VLOOKUP(C238,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12606,7 +12606,7 @@
         <v>213</v>
       </c>
       <c r="E239" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F239" s="1">
         <f>VLOOKUP(C239,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12632,7 +12632,7 @@
         <v>213</v>
       </c>
       <c r="E240" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F240" s="1">
         <f>VLOOKUP(C240,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12658,7 +12658,7 @@
         <v>213</v>
       </c>
       <c r="E241" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F241" s="1">
         <f>VLOOKUP(C241,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12684,7 +12684,7 @@
         <v>213</v>
       </c>
       <c r="E242" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F242" s="1">
         <f>VLOOKUP(C242,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12713,7 +12713,7 @@
         <v>213</v>
       </c>
       <c r="E243" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F243" s="1">
         <f>VLOOKUP(C243,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12739,7 +12739,7 @@
         <v>213</v>
       </c>
       <c r="E244" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F244" s="1">
         <f>VLOOKUP(C244,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12765,7 +12765,7 @@
         <v>213</v>
       </c>
       <c r="E245" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F245" s="1">
         <f>VLOOKUP(C245,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12791,7 +12791,7 @@
         <v>213</v>
       </c>
       <c r="E246" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F246" s="1">
         <f>VLOOKUP(C246,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12817,7 +12817,7 @@
         <v>213</v>
       </c>
       <c r="E247" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F247" s="1">
         <f>VLOOKUP(C247,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12843,7 +12843,7 @@
         <v>213</v>
       </c>
       <c r="E248" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F248" s="1">
         <f>VLOOKUP(C248,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12869,7 +12869,7 @@
         <v>213</v>
       </c>
       <c r="E249" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F249" s="1">
         <f>VLOOKUP(C249,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12895,7 +12895,7 @@
         <v>213</v>
       </c>
       <c r="E250" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F250" s="1">
         <f>VLOOKUP(C250,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12921,7 +12921,7 @@
         <v>213</v>
       </c>
       <c r="E251" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F251" s="1">
         <f>VLOOKUP(C251,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12947,7 +12947,7 @@
         <v>213</v>
       </c>
       <c r="E252" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F252" s="1">
         <f>VLOOKUP(C252,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12973,7 +12973,7 @@
         <v>213</v>
       </c>
       <c r="E253" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F253" s="1">
         <f>VLOOKUP(C253,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -12999,7 +12999,7 @@
         <v>213</v>
       </c>
       <c r="E254" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F254" s="1">
         <f>VLOOKUP(C254,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13025,7 +13025,7 @@
         <v>213</v>
       </c>
       <c r="E255" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F255" s="1">
         <f>VLOOKUP(C255,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13051,7 +13051,7 @@
         <v>213</v>
       </c>
       <c r="E256" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F256" s="1">
         <f>VLOOKUP(C256,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13077,7 +13077,7 @@
         <v>213</v>
       </c>
       <c r="E257" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F257" s="1">
         <f>VLOOKUP(C257,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13103,7 +13103,7 @@
         <v>213</v>
       </c>
       <c r="E258" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F258" s="1">
         <f>VLOOKUP(C258,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13129,7 +13129,7 @@
         <v>213</v>
       </c>
       <c r="E259" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F259" s="1">
         <f>VLOOKUP(C259,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13155,7 +13155,7 @@
         <v>213</v>
       </c>
       <c r="E260" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F260" s="1">
         <f>VLOOKUP(C260,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13181,7 +13181,7 @@
         <v>213</v>
       </c>
       <c r="E261" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F261" s="1">
         <f>VLOOKUP(C261,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13207,7 +13207,7 @@
         <v>213</v>
       </c>
       <c r="E262" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F262" s="1">
         <f>VLOOKUP(C262,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13233,7 +13233,7 @@
         <v>213</v>
       </c>
       <c r="E263" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F263" s="1">
         <f>VLOOKUP(C263,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13259,7 +13259,7 @@
         <v>213</v>
       </c>
       <c r="E264" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F264" s="1">
         <f>VLOOKUP(C264,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13285,7 +13285,7 @@
         <v>213</v>
       </c>
       <c r="E265" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F265" s="1">
         <f>VLOOKUP(C265,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13311,7 +13311,7 @@
         <v>213</v>
       </c>
       <c r="E266" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F266" s="1">
         <f>VLOOKUP(C266,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13337,7 +13337,7 @@
         <v>213</v>
       </c>
       <c r="E267" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F267" s="1">
         <f>VLOOKUP(C267,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13363,7 +13363,7 @@
         <v>213</v>
       </c>
       <c r="E268" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F268" s="1">
         <f>VLOOKUP(C268,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13389,7 +13389,7 @@
         <v>213</v>
       </c>
       <c r="E269" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F269" s="1">
         <f>VLOOKUP(C269,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13415,7 +13415,7 @@
         <v>213</v>
       </c>
       <c r="E270" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F270" s="1">
         <f>VLOOKUP(C270,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13441,7 +13441,7 @@
         <v>213</v>
       </c>
       <c r="E271" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F271" s="1">
         <f>VLOOKUP(C271,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13467,7 +13467,7 @@
         <v>213</v>
       </c>
       <c r="E272" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F272" s="1">
         <f>VLOOKUP(C272,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13493,7 +13493,7 @@
         <v>213</v>
       </c>
       <c r="E273" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F273" s="1">
         <f>VLOOKUP(C273,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13519,7 +13519,7 @@
         <v>213</v>
       </c>
       <c r="E274" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F274" s="1">
         <f>VLOOKUP(C274,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13545,7 +13545,7 @@
         <v>213</v>
       </c>
       <c r="E275" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F275" s="1">
         <f>VLOOKUP(C275,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13571,7 +13571,7 @@
         <v>213</v>
       </c>
       <c r="E276" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F276" s="1">
         <f>VLOOKUP(C276,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13597,7 +13597,7 @@
         <v>213</v>
       </c>
       <c r="E277" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F277" s="1">
         <f>VLOOKUP(C277,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13623,7 +13623,7 @@
         <v>213</v>
       </c>
       <c r="E278" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F278" s="1">
         <f>VLOOKUP(C278,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13649,7 +13649,7 @@
         <v>213</v>
       </c>
       <c r="E279" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F279" s="1">
         <f>VLOOKUP(C279,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13675,7 +13675,7 @@
         <v>213</v>
       </c>
       <c r="E280" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F280" s="1">
         <f>VLOOKUP(C280,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13701,7 +13701,7 @@
         <v>213</v>
       </c>
       <c r="E281" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F281" s="1">
         <f>VLOOKUP(C281,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13727,7 +13727,7 @@
         <v>213</v>
       </c>
       <c r="E282" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F282" s="1">
         <f>VLOOKUP(C282,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13753,7 +13753,7 @@
         <v>213</v>
       </c>
       <c r="E283" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F283" s="1">
         <f>VLOOKUP(C283,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13779,7 +13779,7 @@
         <v>213</v>
       </c>
       <c r="E284" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F284" s="1">
         <f>VLOOKUP(C284,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13805,7 +13805,7 @@
         <v>213</v>
       </c>
       <c r="E285" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F285" s="1">
         <f>VLOOKUP(C285,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13831,7 +13831,7 @@
         <v>214</v>
       </c>
       <c r="E286" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F286" s="1">
         <f>VLOOKUP(C286,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13857,7 +13857,7 @@
         <v>214</v>
       </c>
       <c r="E287" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F287" s="1">
         <f>VLOOKUP(C287,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13883,7 +13883,7 @@
         <v>214</v>
       </c>
       <c r="E288" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F288" s="1">
         <f>VLOOKUP(C288,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13909,7 +13909,7 @@
         <v>214</v>
       </c>
       <c r="E289" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F289" s="1">
         <f>VLOOKUP(C289,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13935,7 +13935,7 @@
         <v>214</v>
       </c>
       <c r="E290" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F290" s="1">
         <f>VLOOKUP(C290,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13961,7 +13961,7 @@
         <v>214</v>
       </c>
       <c r="E291" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F291" s="1">
         <f>VLOOKUP(C291,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -13987,7 +13987,7 @@
         <v>214</v>
       </c>
       <c r="E292" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F292" s="1">
         <f>VLOOKUP(C292,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14013,7 +14013,7 @@
         <v>214</v>
       </c>
       <c r="E293" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F293" s="1">
         <f>VLOOKUP(C293,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14039,7 +14039,7 @@
         <v>214</v>
       </c>
       <c r="E294" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F294" s="1">
         <f>VLOOKUP(C294,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14065,7 +14065,7 @@
         <v>214</v>
       </c>
       <c r="E295" s="1">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F295" s="1">
         <f>VLOOKUP(C295,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14091,7 +14091,7 @@
         <v>214</v>
       </c>
       <c r="E296" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F296" s="1">
         <f>VLOOKUP(C296,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14117,7 +14117,7 @@
         <v>214</v>
       </c>
       <c r="E297" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F297" s="1">
         <f>VLOOKUP(C297,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14143,7 +14143,7 @@
         <v>214</v>
       </c>
       <c r="E298" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F298" s="1">
         <f>VLOOKUP(C298,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14169,7 +14169,7 @@
         <v>214</v>
       </c>
       <c r="E299" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F299" s="1">
         <f>VLOOKUP(C299,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14195,7 +14195,7 @@
         <v>214</v>
       </c>
       <c r="E300" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F300" s="1">
         <f>VLOOKUP(C300,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14221,7 +14221,7 @@
         <v>214</v>
       </c>
       <c r="E301" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F301" s="1">
         <f>VLOOKUP(C301,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14247,7 +14247,7 @@
         <v>214</v>
       </c>
       <c r="E302" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F302" s="1">
         <f>VLOOKUP(C302,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14273,7 +14273,7 @@
         <v>214</v>
       </c>
       <c r="E303" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F303" s="1">
         <f>VLOOKUP(C303,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14299,7 +14299,7 @@
         <v>214</v>
       </c>
       <c r="E304" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F304" s="1">
         <f>VLOOKUP(C304,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14325,7 +14325,7 @@
         <v>214</v>
       </c>
       <c r="E305" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F305" s="1">
         <f>VLOOKUP(C305,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14351,7 +14351,7 @@
         <v>214</v>
       </c>
       <c r="E306" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F306" s="1">
         <f>VLOOKUP(C306,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14377,7 +14377,7 @@
         <v>214</v>
       </c>
       <c r="E307" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F307" s="1">
         <f>VLOOKUP(C307,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14403,7 +14403,7 @@
         <v>214</v>
       </c>
       <c r="E308" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F308" s="1">
         <f>VLOOKUP(C308,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14429,7 +14429,7 @@
         <v>214</v>
       </c>
       <c r="E309" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F309" s="1">
         <f>VLOOKUP(C309,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14455,7 +14455,7 @@
         <v>214</v>
       </c>
       <c r="E310" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F310" s="1">
         <f>VLOOKUP(C310,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14481,7 +14481,7 @@
         <v>214</v>
       </c>
       <c r="E311" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F311" s="1">
         <f>VLOOKUP(C311,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14507,7 +14507,7 @@
         <v>214</v>
       </c>
       <c r="E312" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F312" s="1">
         <f>VLOOKUP(C312,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14533,7 +14533,7 @@
         <v>214</v>
       </c>
       <c r="E313" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F313" s="1">
         <f>VLOOKUP(C313,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14559,7 +14559,7 @@
         <v>214</v>
       </c>
       <c r="E314" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F314" s="1">
         <f>VLOOKUP(C314,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14585,7 +14585,7 @@
         <v>214</v>
       </c>
       <c r="E315" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F315" s="1">
         <f>VLOOKUP(C315,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14611,7 +14611,7 @@
         <v>214</v>
       </c>
       <c r="E316" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F316" s="1">
         <f>VLOOKUP(C316,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14637,7 +14637,7 @@
         <v>214</v>
       </c>
       <c r="E317" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F317" s="1">
         <f>VLOOKUP(C317,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14663,7 +14663,7 @@
         <v>214</v>
       </c>
       <c r="E318" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F318" s="1">
         <f>VLOOKUP(C318,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14689,7 +14689,7 @@
         <v>214</v>
       </c>
       <c r="E319" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F319" s="1">
         <f>VLOOKUP(C319,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14715,7 +14715,7 @@
         <v>214</v>
       </c>
       <c r="E320" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F320" s="1">
         <f>VLOOKUP(C320,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14741,7 +14741,7 @@
         <v>214</v>
       </c>
       <c r="E321" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F321" s="1">
         <f>VLOOKUP(C321,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14767,7 +14767,7 @@
         <v>214</v>
       </c>
       <c r="E322" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F322" s="1">
         <f>VLOOKUP(C322,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14793,7 +14793,7 @@
         <v>214</v>
       </c>
       <c r="E323" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F323" s="1">
         <f>VLOOKUP(C323,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14819,7 +14819,7 @@
         <v>214</v>
       </c>
       <c r="E324" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F324" s="1">
         <f>VLOOKUP(C324,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14845,7 +14845,7 @@
         <v>214</v>
       </c>
       <c r="E325" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F325" s="1">
         <f>VLOOKUP(C325,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14871,7 +14871,7 @@
         <v>214</v>
       </c>
       <c r="E326" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F326" s="1">
         <f>VLOOKUP(C326,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14897,7 +14897,7 @@
         <v>214</v>
       </c>
       <c r="E327" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F327" s="1">
         <f>VLOOKUP(C327,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14923,7 +14923,7 @@
         <v>214</v>
       </c>
       <c r="E328" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="F328" s="1">
         <f>VLOOKUP(C328,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14949,7 +14949,7 @@
         <v>214</v>
       </c>
       <c r="E329" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F329" s="1">
         <f>VLOOKUP(C329,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -14975,7 +14975,7 @@
         <v>214</v>
       </c>
       <c r="E330" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F330" s="1">
         <f>VLOOKUP(C330,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -15001,7 +15001,7 @@
         <v>214</v>
       </c>
       <c r="E331" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F331" s="1">
         <f>VLOOKUP(C331,dish_base!$B$4:$O$92,14,FALSE)</f>
@@ -15027,7 +15027,7 @@
         <v>214</v>
       </c>
       <c r="E332" s="1">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F332" s="1">
         <f>VLOOKUP(C332,dish_base!$B$4:$O$92,14,FALSE)</f>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="5"/>
+    <workbookView windowHeight="15200" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -16403,7 +16403,7 @@
     <col min="7" max="7" width="12.3076923076923" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.3076923076923" style="1" customWidth="1"/>
     <col min="9" max="9" width="21.8461538461538" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7692307692308" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.3846153846154" style="1" customWidth="1"/>
     <col min="11" max="11" width="21.7692307692308" style="1" customWidth="1"/>
     <col min="12" max="12" width="12.7692307692308" style="1" customWidth="1"/>
     <col min="13" max="13" width="40.3076923076923" style="1" customWidth="1"/>
@@ -16609,7 +16609,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>25</v>
@@ -17067,7 +17067,7 @@
       <c r="P13" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="S13" s="1" t="str">
+      <c r="S13" s="22" t="str">
         <f>IFERROR(VLOOKUP(B13,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>果冻</v>
       </c>
@@ -17371,7 +17371,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>25</v>
@@ -17382,11 +17382,11 @@
       <c r="P19" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="S19" s="1" t="str">
+      <c r="S19" s="22" t="str">
         <f>IFERROR(VLOOKUP(B19,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>圣代</v>
       </c>
-      <c r="T19" s="1" t="str">
+      <c r="T19" s="22" t="str">
         <f>IFERROR(VLOOKUP(B19,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17431,11 +17431,11 @@
       <c r="P20" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="S20" s="1" t="str">
+      <c r="S20" s="22" t="str">
         <f>IFERROR(VLOOKUP(B20,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T20" s="1" t="str">
+      <c r="T20" s="22" t="str">
         <f>IFERROR(VLOOKUP(B20,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>圣代</v>
       </c>
@@ -17928,13 +17928,13 @@
         <v>433</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>412</v>
+        <v>440</v>
       </c>
       <c r="K30" s="1">
         <v>0</v>
       </c>
       <c r="L30" s="1">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N30" s="1" t="s">
         <v>25</v>
@@ -17945,11 +17945,11 @@
       <c r="P30" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="S30" s="1" t="str">
+      <c r="S30" s="22" t="str">
         <f>IFERROR(VLOOKUP(B30,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>太妃糖</v>
       </c>
-      <c r="T30" s="1" t="str">
+      <c r="T30" s="22" t="str">
         <f>IFERROR(VLOOKUP(B30,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17980,7 +17980,7 @@
         <v>445</v>
       </c>
       <c r="K31" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -17997,11 +17997,11 @@
       <c r="Q31" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S31" s="1" t="str">
+      <c r="S31" s="22" t="str">
         <f>IFERROR(VLOOKUP(B31,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T31" s="1" t="str">
+      <c r="T31" s="22" t="str">
         <f>IFERROR(VLOOKUP(B31,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>太妃糖</v>
       </c>
@@ -18251,11 +18251,11 @@
       <c r="R36" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="S36" s="1" t="str">
+      <c r="S36" s="22" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>闪电泡芙</v>
       </c>
-      <c r="T36" s="1" t="str">
+      <c r="T36" s="22" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18303,11 +18303,11 @@
       <c r="R37" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="S37" s="1" t="str">
+      <c r="S37" s="22" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T37" s="1" t="str">
+      <c r="T37" s="22" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>闪电泡芙</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="5"/>
+    <workbookView windowHeight="15300" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -19637,7 +19637,7 @@
       <c r="P63" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="S63" s="1" t="str">
+      <c r="S63" s="22" t="str">
         <f>IFERROR(VLOOKUP(B63,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>蝴蝶酥</v>
       </c>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300" activeTab="5"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -3356,7 +3356,7 @@
         <v>30</v>
       </c>
       <c r="D5" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>25</v>
@@ -3446,7 +3446,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>25</v>
@@ -3491,7 +3491,7 @@
         <v>39</v>
       </c>
       <c r="D8" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>25</v>
@@ -3575,7 +3575,7 @@
         <v>45</v>
       </c>
       <c r="D10" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>25</v>
@@ -3659,7 +3659,7 @@
         <v>51</v>
       </c>
       <c r="D12" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>25</v>
@@ -3866,7 +3866,7 @@
         <v>63</v>
       </c>
       <c r="D15" s="1">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>25</v>
@@ -3935,7 +3935,7 @@
         <v>67</v>
       </c>
       <c r="D16" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>25</v>
@@ -4112,7 +4112,7 @@
         <v>78</v>
       </c>
       <c r="D20" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>25</v>
@@ -4157,7 +4157,7 @@
         <v>81</v>
       </c>
       <c r="D21" s="1">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>25</v>
@@ -4202,7 +4202,7 @@
         <v>84</v>
       </c>
       <c r="D22" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>25</v>
@@ -4247,7 +4247,7 @@
         <v>88</v>
       </c>
       <c r="D23" s="1">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>25</v>
@@ -4331,7 +4331,7 @@
         <v>95</v>
       </c>
       <c r="D25" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>25</v>
@@ -4556,7 +4556,7 @@
         <v>114</v>
       </c>
       <c r="D30" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>25</v>
@@ -4688,7 +4688,7 @@
         <v>120</v>
       </c>
       <c r="D34" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>25</v>
@@ -4781,7 +4781,7 @@
         <v>123</v>
       </c>
       <c r="D37" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>25</v>
@@ -4847,7 +4847,7 @@
         <v>126</v>
       </c>
       <c r="D39" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>25</v>
@@ -4916,7 +4916,7 @@
         <v>129</v>
       </c>
       <c r="D41" s="1">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>25</v>
@@ -4985,7 +4985,7 @@
         <v>132</v>
       </c>
       <c r="D43" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E43" s="1" t="s">
         <v>25</v>
@@ -5054,7 +5054,7 @@
         <v>135</v>
       </c>
       <c r="D45" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>25</v>
@@ -5123,7 +5123,7 @@
         <v>138</v>
       </c>
       <c r="D47" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>25</v>
@@ -5258,7 +5258,7 @@
         <v>144</v>
       </c>
       <c r="D51" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>25</v>
@@ -5327,7 +5327,7 @@
         <v>147</v>
       </c>
       <c r="D53" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>25</v>
@@ -5396,7 +5396,7 @@
         <v>71</v>
       </c>
       <c r="D55" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>25</v>
@@ -5489,7 +5489,7 @@
         <v>152</v>
       </c>
       <c r="D58" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>25</v>
@@ -5579,7 +5579,7 @@
         <v>155</v>
       </c>
       <c r="D61" s="1">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>25</v>
@@ -5648,7 +5648,7 @@
         <v>158</v>
       </c>
       <c r="D63" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>25</v>
@@ -5717,7 +5717,7 @@
         <v>161</v>
       </c>
       <c r="D65" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>25</v>
@@ -5810,7 +5810,7 @@
         <v>164</v>
       </c>
       <c r="D68" s="1">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>25</v>
@@ -5903,7 +5903,7 @@
         <v>167</v>
       </c>
       <c r="D71" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>25</v>
@@ -5972,7 +5972,7 @@
         <v>170</v>
       </c>
       <c r="D73" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>25</v>
@@ -6200,7 +6200,7 @@
         <v>181</v>
       </c>
       <c r="D80" s="1">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>25</v>
@@ -6331,7 +6331,7 @@
         <v>185</v>
       </c>
       <c r="D85" s="1">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>25</v>
@@ -6418,7 +6418,7 @@
         <v>188</v>
       </c>
       <c r="D88" s="1">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>25</v>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300"/>
+    <workbookView windowHeight="15240" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -17371,7 +17371,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>25</v>
@@ -17582,7 +17582,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>25</v>
@@ -17593,11 +17593,11 @@
       <c r="P23" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="S23" s="1" t="str">
+      <c r="S23" s="22" t="str">
         <f>IFERROR(VLOOKUP(B23,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>棒棒糖</v>
       </c>
-      <c r="T23" s="1" t="str">
+      <c r="T23" s="22" t="str">
         <f>IFERROR(VLOOKUP(B23,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17645,11 +17645,11 @@
       <c r="Q24" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S24" s="1" t="str">
+      <c r="S24" s="22" t="str">
         <f>IFERROR(VLOOKUP(B24,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T24" s="1" t="str">
+      <c r="T24" s="22" t="str">
         <f>IFERROR(VLOOKUP(B24,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>棒棒糖</v>
       </c>
@@ -19626,7 +19626,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>25</v>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="5"/>
+    <workbookView windowHeight="15200" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -17,14 +17,14 @@
     <sheet name="定义" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">sub_skill!$C$1:$C$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">sub_skill!$C$1:$C$70</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3026" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3038" uniqueCount="678">
   <si>
     <t>##var</t>
   </si>
@@ -932,7 +932,7 @@
     <t>ss_layer_per_dish_adj_v2_2</t>
   </si>
   <si>
-    <t>ss_mult_adj_v1p5|ss_count_as_base_v3</t>
+    <t>ss_mult_adj_v1p5|ss_count_as_base_v3_1</t>
   </si>
   <si>
     <t>ss_mult_adj_v1p5</t>
@@ -1441,7 +1441,8 @@
     <t>{ascope}倍率 ×{0}</t>
   </si>
   <si>
-    <t>{ascope}分数永久 {0}</t>
+    <t>{ascope}
+分数永久 {0}</t>
   </si>
   <si>
     <t>All</t>
@@ -1479,10 +1480,6 @@
 {ascope}倍率 ×{tiervals}</t>
   </si>
   <si>
-    <t>若{cscope}被填满
-{ascope}额外视为 {0} 个食物</t>
-  </si>
-  <si>
     <t>{ascope}额外视为 {0} 个食物</t>
   </si>
   <si>
@@ -1527,6 +1524,12 @@
   <si>
     <t>带甜蜜传递的食物达 {tiers} 种时
 此类食物倍率 ×{tiervals}</t>
+  </si>
+  <si>
+    <t>ss_count_as_base_v3_1</t>
+  </si>
+  <si>
+    <t>蝴蝶肃</t>
   </si>
   <si>
     <t>TriggerSweetTransfer</t>
@@ -16391,7 +16394,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T69"/>
+  <dimension ref="A1:T70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -17356,7 +17359,7 @@
         <v>437</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>420</v>
@@ -17371,7 +17374,7 @@
         <v>0</v>
       </c>
       <c r="L19" s="1">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>25</v>
@@ -17905,7 +17908,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="2:20">
+    <row r="30" ht="34" spans="2:20">
       <c r="B30" s="1" t="s">
         <v>251</v>
       </c>
@@ -17942,7 +17945,7 @@
       <c r="O30" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="P30" s="20" t="s">
         <v>466</v>
       </c>
       <c r="S30" s="22" t="str">
@@ -18234,7 +18237,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>25</v>
@@ -18289,7 +18292,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>25</v>
@@ -18581,7 +18584,7 @@
         <v>月饼</v>
       </c>
     </row>
-    <row r="43" spans="2:20">
+    <row r="43" ht="34" spans="2:20">
       <c r="B43" s="1" t="s">
         <v>271</v>
       </c>
@@ -18589,13 +18592,13 @@
         <v>410</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>420</v>
@@ -18610,7 +18613,7 @@
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>25</v>
@@ -18618,19 +18621,19 @@
       <c r="O43" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="S43" s="1" t="str">
+      <c r="P43" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="S43" s="22" t="str">
         <f>IFERROR(VLOOKUP(B43,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>华夫饼</v>
       </c>
-      <c r="T43" s="1" t="str">
+      <c r="T43" s="22" t="str">
         <f>IFERROR(VLOOKUP(B43,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="34" spans="2:20">
+    <row r="44" ht="17" spans="2:20">
       <c r="B44" s="1" t="s">
         <v>272</v>
       </c>
@@ -18670,11 +18673,11 @@
       <c r="P44" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="S44" s="1" t="str">
+      <c r="S44" s="22" t="str">
         <f>IFERROR(VLOOKUP(B44,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T44" s="1" t="str">
+      <c r="T44" s="22" t="str">
         <f>IFERROR(VLOOKUP(B44,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>华夫饼</v>
       </c>
@@ -18717,7 +18720,7 @@
         <v>25</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S45" s="1" t="str">
         <f>IFERROR(VLOOKUP(B45,skill!$G$4:$K$50,5,FALSE),"")</f>
@@ -18800,7 +18803,7 @@
         <v>366</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -18809,7 +18812,7 @@
         <v>10</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>25</v>
@@ -18818,7 +18821,7 @@
         <v>415</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S47" s="1" t="str">
         <f>IFERROR(VLOOKUP(B47,skill!$G$4:$K$50,5,FALSE),"")</f>
@@ -18919,7 +18922,7 @@
         <v>415</v>
       </c>
       <c r="P49" s="20" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="S49" s="1" t="str">
         <f>IFERROR(VLOOKUP(B49,skill!$G$4:$K$50,5,FALSE),"")</f>
@@ -19302,7 +19305,7 @@
         <v>369</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -19311,7 +19314,7 @@
         <v>5</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>25</v>
@@ -19320,7 +19323,7 @@
         <v>415</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S57" s="1" t="str">
         <f>IFERROR(VLOOKUP(B57,skill!$G$4:$K$50,5,FALSE),"")</f>
@@ -19437,7 +19440,7 @@
         <v>410</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>467</v>
@@ -19449,7 +19452,7 @@
         <v>474</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>429</v>
@@ -19464,7 +19467,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>25</v>
@@ -19473,7 +19476,7 @@
         <v>25</v>
       </c>
       <c r="P60" s="20" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q60" s="1" t="s">
         <v>432</v>
@@ -19495,7 +19498,7 @@
         <v>410</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>467</v>
@@ -19507,7 +19510,7 @@
         <v>474</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>372</v>
@@ -19522,7 +19525,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>25</v>
@@ -19531,7 +19534,7 @@
         <v>25</v>
       </c>
       <c r="P61" s="20" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q61" s="1" t="s">
         <v>426</v>
@@ -19626,7 +19629,7 @@
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N63" s="1" t="s">
         <v>25</v>
@@ -19648,7 +19651,7 @@
     </row>
     <row r="64" spans="2:20">
       <c r="B64" s="1" t="s">
-        <v>305</v>
+        <v>492</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>410</v>
@@ -19666,38 +19669,37 @@
         <v>420</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>372</v>
+        <v>450</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>435</v>
+        <v>412</v>
       </c>
       <c r="K64" s="1">
         <v>0</v>
       </c>
       <c r="L64" s="1">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>25</v>
+        <v>415</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="S64" s="1" t="str">
         <f>IFERROR(VLOOKUP(B64,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>拐杖糖</v>
-      </c>
-      <c r="T64" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B64,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="65" spans="2:20">
       <c r="B65" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>410</v>
@@ -19715,16 +19717,16 @@
         <v>420</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>25</v>
@@ -19733,23 +19735,20 @@
         <v>25</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>426</v>
+        <v>465</v>
       </c>
       <c r="S65" s="1" t="str">
         <f>IFERROR(VLOOKUP(B65,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v/>
+        <v>拐杖糖</v>
       </c>
       <c r="T65" s="1" t="str">
         <f>IFERROR(VLOOKUP(B65,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>拐杖糖</v>
-      </c>
-    </row>
-    <row r="66" ht="34" spans="2:20">
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="2:20">
       <c r="B66" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>410</v>
@@ -19767,10 +19766,10 @@
         <v>420</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>467</v>
+        <v>418</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
@@ -19778,39 +19777,36 @@
       <c r="L66" s="1">
         <v>0</v>
       </c>
-      <c r="M66" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="N66" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P66" s="20" t="s">
-        <v>495</v>
+      <c r="P66" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="Q66" s="1" t="s">
         <v>426</v>
       </c>
       <c r="S66" s="1" t="str">
         <f>IFERROR(VLOOKUP(B66,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>大棒棒糖</v>
+        <v/>
       </c>
       <c r="T66" s="1" t="str">
         <f>IFERROR(VLOOKUP(B66,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v/>
+        <v>拐杖糖</v>
       </c>
     </row>
     <row r="67" ht="34" spans="2:20">
       <c r="B67" s="1" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>410</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>412</v>
@@ -19822,16 +19818,19 @@
         <v>420</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>372</v>
+        <v>494</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>412</v>
+        <v>467</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>25</v>
@@ -19842,24 +19841,27 @@
       <c r="P67" s="20" t="s">
         <v>496</v>
       </c>
+      <c r="Q67" s="1" t="s">
+        <v>426</v>
+      </c>
       <c r="S67" s="1" t="str">
         <f>IFERROR(VLOOKUP(B67,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>棉花糖</v>
+        <v>大棒棒糖</v>
       </c>
       <c r="T67" s="1" t="str">
         <f>IFERROR(VLOOKUP(B67,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="2:20">
+    <row r="68" ht="34" spans="2:20">
       <c r="B68" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>410</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>412</v>
@@ -19871,16 +19873,16 @@
         <v>420</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>25</v>
@@ -19888,24 +19890,21 @@
       <c r="O68" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>426</v>
+      <c r="P68" s="20" t="s">
+        <v>497</v>
       </c>
       <c r="S68" s="1" t="str">
         <f>IFERROR(VLOOKUP(B68,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v/>
+        <v>棉花糖</v>
       </c>
       <c r="T68" s="1" t="str">
         <f>IFERROR(VLOOKUP(B68,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>棉花糖</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="2:20">
       <c r="B69" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>410</v>
@@ -19923,19 +19922,16 @@
         <v>420</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>462</v>
+        <v>423</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
       </c>
       <c r="L69" s="1">
-        <v>3</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>481</v>
+        <v>0</v>
       </c>
       <c r="N69" s="1" t="s">
         <v>25</v>
@@ -19944,15 +19940,70 @@
         <v>25</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>497</v>
+        <v>425</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="S69" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B69,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T69" s="1" t="str">
         <f>IFERROR(VLOOKUP(B69,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <v>棉花糖</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20">
+      <c r="B70" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K70" s="1">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1">
+        <v>3</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="T70" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B70,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C69">
+  <autoFilter ref="C1:C70">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19986,34 +20037,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" ht="17.6" customHeight="1" spans="1:15">
@@ -20030,22 +20081,22 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" ht="17.6" customHeight="1" spans="1:13">
@@ -20062,19 +20113,19 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" ht="17.6" customHeight="1" spans="1:13">
@@ -20091,22 +20142,22 @@
         <v>30</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" ht="17.6" customHeight="1" spans="1:13">
@@ -20123,19 +20174,19 @@
         <v>8</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M6" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" ht="17.6" customHeight="1" spans="1:13">
@@ -20152,19 +20203,19 @@
         <v>6</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M7" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" ht="17.6" customHeight="1" spans="1:9">
@@ -20181,16 +20232,16 @@
         <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" ht="17.6" customHeight="1" spans="1:9">
@@ -20207,16 +20258,16 @@
         <v>6</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" ht="17.6" customHeight="1" spans="1:14">
@@ -20233,19 +20284,19 @@
         <v>10</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" ht="17.6" customHeight="1" spans="1:9">
@@ -20262,16 +20313,16 @@
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="12" ht="17.6" customHeight="1" spans="1:15">
@@ -20288,25 +20339,25 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="13" ht="17.6" customHeight="1" spans="1:15">
@@ -20323,28 +20374,28 @@
         <v>10</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -20361,22 +20412,22 @@
         <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -20393,22 +20444,22 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16" ht="17.6" customHeight="1" spans="1:15">
@@ -20425,25 +20476,25 @@
         <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" ht="17.6" customHeight="1" spans="1:15">
@@ -20460,22 +20511,22 @@
         <v>20</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="18" spans="3:15">
@@ -20483,10 +20534,10 @@
         <v>28</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" ht="17.6" customHeight="1" spans="1:15">
@@ -20503,22 +20554,22 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O19" s="8" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" ht="17.6" customHeight="1" spans="1:15">
@@ -20532,25 +20583,25 @@
         <v>73</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="21" ht="17.6" customHeight="1" spans="1:15">
@@ -20567,22 +20618,22 @@
         <v>14</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="22" ht="17.6" customHeight="1" spans="1:15">
@@ -20599,22 +20650,22 @@
         <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="3:15">
@@ -20622,13 +20673,13 @@
         <v>28</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O23" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="24" ht="17.6" customHeight="1" spans="1:15">
@@ -20645,25 +20696,25 @@
         <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="25" spans="3:15">
@@ -20671,10 +20722,10 @@
         <v>28</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O25" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="26" ht="17.6" customHeight="1" spans="1:15">
@@ -20691,25 +20742,25 @@
         <v>20</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="27" spans="3:15">
@@ -20717,10 +20768,10 @@
         <v>28</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="O27" s="8" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="28" ht="17.6" customHeight="1" spans="1:15">
@@ -20737,25 +20788,25 @@
         <v>30</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O28" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="29" ht="17.6" customHeight="1" spans="1:15">
@@ -20772,22 +20823,22 @@
         <v>40</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O29" s="8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" ht="17.6" customHeight="1" spans="1:15">
@@ -20804,25 +20855,25 @@
         <v>30</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O30" s="8" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="31" spans="3:15">
@@ -20830,10 +20881,10 @@
         <v>28</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O31" s="8" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="32" spans="3:15">
@@ -20841,10 +20892,10 @@
         <v>28</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O32" s="15" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" ht="17.6" customHeight="1" spans="1:15">
@@ -20861,25 +20912,25 @@
         <v>20</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O33" s="15" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="34" spans="3:15">
@@ -20887,13 +20938,13 @@
         <v>28</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="O34" s="15" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="35" spans="3:3">
@@ -20915,16 +20966,16 @@
         <v>30</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="37" spans="3:15">
@@ -20932,10 +20983,10 @@
         <v>73</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="38" ht="17.6" customHeight="1" spans="1:15">
@@ -20952,22 +21003,22 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O38" s="8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="39" spans="3:15">
@@ -20975,10 +21026,10 @@
         <v>73</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O39" s="8" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="40" ht="17.6" customHeight="1" spans="1:15">
@@ -20995,22 +21046,22 @@
         <v>25</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="O40" s="8" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="41" ht="17.6" customHeight="1" spans="3:15">
@@ -21018,10 +21069,10 @@
         <v>73</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O41" s="8" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="42" ht="17.6" customHeight="1" spans="1:9">
@@ -21038,16 +21089,16 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="43" spans="3:15">
@@ -21055,10 +21106,10 @@
         <v>73</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O43" s="8" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="44" ht="17.6" customHeight="1" spans="1:15">
@@ -21075,22 +21126,22 @@
         <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O44" s="8" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="45" spans="3:15">
@@ -21098,10 +21149,10 @@
         <v>73</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O45" s="8" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="46" ht="17.6" customHeight="1" spans="1:15">
@@ -21118,22 +21169,22 @@
         <v>50</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O46" s="8" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="47" spans="3:15">
@@ -21141,10 +21192,10 @@
         <v>73</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O47" s="8" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="48" ht="17.6" customHeight="1" spans="1:15">
@@ -21161,22 +21212,22 @@
         <v>40</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -21184,10 +21235,10 @@
         <v>73</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="50" ht="17.6" customHeight="1" spans="1:15">
@@ -21204,22 +21255,22 @@
         <v>30</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="51" spans="3:15">
@@ -21227,10 +21278,10 @@
         <v>73</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="52" ht="17.6" customHeight="1" spans="1:15">
@@ -21247,22 +21298,22 @@
         <v>50</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="O52" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="53" spans="3:15">
@@ -21270,10 +21321,10 @@
         <v>110</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O53" s="8" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="54" ht="17.6" customHeight="1" spans="1:9">
@@ -21290,16 +21341,16 @@
         <v>40</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="55" spans="3:3">
@@ -21326,16 +21377,16 @@
         <v>30</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="58" spans="3:3">
@@ -21362,16 +21413,16 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="61" spans="3:3">
@@ -21393,16 +21444,16 @@
         <v>30</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="63" spans="3:3">
@@ -21424,16 +21475,16 @@
         <v>50</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="65" spans="3:3">
@@ -21460,16 +21511,16 @@
         <v>40</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="68" spans="3:3">
@@ -21496,16 +21547,16 @@
         <v>30</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="71" spans="3:3">
@@ -21527,16 +21578,16 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="73" spans="3:3">
@@ -21558,16 +21609,16 @@
         <v>30</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="75" spans="3:3">
@@ -21589,16 +21640,16 @@
         <v>40</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J76" s="17"/>
       <c r="K76" s="19"/>
@@ -21631,16 +21682,16 @@
         <v>100</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="80" spans="3:3">
@@ -21684,16 +21735,16 @@
         <v>80</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J84" s="19"/>
       <c r="K84" s="19"/>
@@ -21729,16 +21780,16 @@
         <v>140</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K87" s="19"/>
       <c r="L87" s="19"/>
@@ -21780,16 +21831,16 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -21819,19 +21870,19 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="R5" s="3"/>
       <c r="V5" s="6"/>
@@ -21857,29 +21908,29 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
@@ -21904,29 +21955,29 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
@@ -21949,29 +22000,29 @@
     </row>
     <row r="8" customHeight="1" spans="8:41">
       <c r="H8" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="3" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
@@ -21998,35 +22049,35 @@
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="M9" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>667</v>
-      </c>
       <c r="N9" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="R9" s="3"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
       <c r="Y9" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
@@ -22035,13 +22086,13 @@
       <c r="AH9" s="6"/>
       <c r="AI9" s="6"/>
       <c r="AJ9" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
@@ -22054,16 +22105,16 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -22080,13 +22131,13 @@
       <c r="AH10" s="6"/>
       <c r="AI10" s="6"/>
       <c r="AJ10" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
@@ -22099,10 +22150,10 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -22121,13 +22172,13 @@
       <c r="AH11" s="6"/>
       <c r="AI11" s="6"/>
       <c r="AJ11" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
@@ -22140,10 +22191,10 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15200" activeTab="5"/>
+    <workbookView windowHeight="15280" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3038" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3097" uniqueCount="712">
   <si>
     <t>##var</t>
   </si>
@@ -1561,9 +1561,6 @@
     <t>技能</t>
   </si>
   <si>
-    <t>作用范围</t>
-  </si>
-  <si>
     <t>作用乘区</t>
   </si>
   <si>
@@ -1573,13 +1570,17 @@
     <t>所属build</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>技能列举</t>
-  </si>
-  <si>
-    <t>处在边缘时，倍率+3</t>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>分析</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>处在棋盘边缘时
+倍率 +3</t>
   </si>
   <si>
     <t>加倍率</t>
@@ -1591,13 +1592,15 @@
     <t>小而多</t>
   </si>
   <si>
-    <t>行为</t>
-  </si>
-  <si>
-    <t>甜蜜传递：使目标食物获得并结算此技能</t>
-  </si>
-  <si>
-    <t>周围每有一种食物，分数+8。甜蜜传递至同行1个食物</t>
+    <t>自己</t>
+  </si>
+  <si>
+    <t>有条件（前期易达成），自身加倍率</t>
+  </si>
+  <si>
+    <t>周围每有 1 种食物
+分数 +5
+甜蜜传递至同行 1 个食物</t>
   </si>
   <si>
     <t>分数</t>
@@ -1606,214 +1609,321 @@
     <t>传递</t>
   </si>
   <si>
-    <t>前提+行为</t>
-  </si>
-  <si>
-    <t>周围每有1个空格，分数-2</t>
-  </si>
-  <si>
-    <t>本食物默认不写</t>
-  </si>
-  <si>
-    <t>行为+行为</t>
-  </si>
-  <si>
-    <t>周围每有1个食物，蛋糕+2层</t>
+    <t>自己与另一</t>
+  </si>
+  <si>
+    <t>前期更易，自身和另一个同行的加分数</t>
+  </si>
+  <si>
+    <t>周围每有1个空格
+分数-2</t>
+  </si>
+  <si>
+    <t>保证空格少</t>
+  </si>
+  <si>
+    <t>周围每有 1 个食物
+欢乐蛋糕 +2层</t>
   </si>
   <si>
     <t>buff</t>
   </si>
   <si>
-    <t>多辅一</t>
-  </si>
-  <si>
-    <t>前提+行为+行为</t>
-  </si>
-  <si>
-    <t>结算时，分数永久+6</t>
-  </si>
-  <si>
-    <t>行为+行为+行为</t>
-  </si>
-  <si>
-    <t>本列每有1个食物，倍率+1</t>
+    <t>前中后</t>
+  </si>
+  <si>
+    <t>攒Buff/小而多</t>
+  </si>
+  <si>
+    <t>都适用，加层4～8+</t>
+  </si>
+  <si>
+    <t>结算时
+分数永久+8</t>
+  </si>
+  <si>
+    <t>自身永久加分数</t>
+  </si>
+  <si>
+    <t>4回合回本</t>
+  </si>
+  <si>
+    <t>本列每有1个食物
+倍率+0.4</t>
+  </si>
+  <si>
+    <t>前中</t>
+  </si>
+  <si>
+    <t>列检测数量，加倍率</t>
+  </si>
+  <si>
+    <t>本行每有1个食物
+分数+8</t>
+  </si>
+  <si>
+    <t>行检测数量，加分数</t>
+  </si>
+  <si>
+    <t>每有1个技能
+分数永久+5</t>
+  </si>
+  <si>
+    <t>永久加分数</t>
+  </si>
+  <si>
+    <t>技能检测数量，永久加分数</t>
+  </si>
+  <si>
+    <t>前提</t>
+  </si>
+  <si>
+    <t>本行每有1种食物
+周围及自身
+倍率+0.15</t>
+  </si>
+  <si>
+    <t>自己及周围</t>
+  </si>
+  <si>
+    <t>行检测种数，范围加倍率</t>
+  </si>
+  <si>
+    <t>欢乐蛋糕+8层</t>
+  </si>
+  <si>
+    <t>攒Buff</t>
+  </si>
+  <si>
+    <t>加层数</t>
+  </si>
+  <si>
+    <t>类别</t>
+  </si>
+  <si>
+    <t>技能机制</t>
+  </si>
+  <si>
+    <t>技能详情</t>
+  </si>
+  <si>
+    <t>周围每有1个食物
+倍率+0.2
+甜蜜传递至周围1个食物</t>
+  </si>
+  <si>
+    <t>周围检测数量，加倍率，传递到周围</t>
+  </si>
+  <si>
+    <t>空间</t>
+  </si>
+  <si>
+    <t>位置检测</t>
+  </si>
+  <si>
+    <t>如果（同行/同列/周围/全部）被填满</t>
+  </si>
+  <si>
+    <t>若周围被填满
+获得10个金币</t>
+  </si>
+  <si>
+    <t>金币</t>
+  </si>
+  <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>加钱</t>
   </si>
   <si>
     <t>乘倍率</t>
   </si>
   <si>
-    <t>前中</t>
-  </si>
-  <si>
-    <t>本行每有一个食物，分数+10</t>
-  </si>
-  <si>
-    <t>每有1个技能，分数永久+5</t>
-  </si>
-  <si>
-    <t>永久加分数</t>
-  </si>
-  <si>
-    <t>前提</t>
-  </si>
-  <si>
-    <t>本行每有1种食物，周围及自身食物倍率+0.2</t>
-  </si>
-  <si>
-    <t>蛋糕+5层</t>
-  </si>
-  <si>
-    <t>类别</t>
-  </si>
-  <si>
-    <t>技能机制</t>
-  </si>
-  <si>
-    <t>技能详情</t>
-  </si>
-  <si>
-    <t>技能额外结算1次。甜蜜传递至1个食物</t>
+    <t>空格检测</t>
+  </si>
+  <si>
+    <t>（周围/同列/同行/空）每有1个空格</t>
+  </si>
+  <si>
+    <t>若本行被填满
+欢乐蛋糕+10层</t>
+  </si>
+  <si>
+    <t>有条件加层数</t>
+  </si>
+  <si>
+    <t>1格</t>
+  </si>
+  <si>
+    <t>边缘检测</t>
+  </si>
+  <si>
+    <t>若本食物处在边缘</t>
+  </si>
+  <si>
+    <t>本行每有 1 个食物
+倍率 +1
+视为 2 个食物</t>
+  </si>
+  <si>
+    <t>中</t>
+  </si>
+  <si>
+    <t>行检测数量，加自身倍率</t>
+  </si>
+  <si>
+    <t>2格</t>
+  </si>
+  <si>
+    <t>数量</t>
+  </si>
+  <si>
+    <t>检测数量</t>
+  </si>
+  <si>
+    <t>（周围/同列/同行/空）每有1（种/个）食物</t>
+  </si>
+  <si>
+    <t>蛋糕+15层
+视为3个食物</t>
+  </si>
+  <si>
+    <t>加层数，过度</t>
+  </si>
+  <si>
+    <t>3格</t>
+  </si>
+  <si>
+    <t>阶梯数量</t>
+  </si>
+  <si>
+    <t>（周围/同列/同行/空）食物数量达到[2/5/10]时</t>
+  </si>
+  <si>
+    <t>4格</t>
+  </si>
+  <si>
+    <t>大小检测</t>
+  </si>
+  <si>
+    <t>（周围/同列/同行/空）每有1（种/个）（大于等于/小于等于）3格的食物</t>
+  </si>
+  <si>
+    <t>周围有占1格的食物时
+倍率x1.5
+甜蜜传递至同行2个食物</t>
+  </si>
+  <si>
+    <t>传递/小而多</t>
+  </si>
+  <si>
+    <t>自己与另二</t>
+  </si>
+  <si>
+    <t>周围检测，同列传递</t>
+  </si>
+  <si>
+    <t>顺序检测</t>
+  </si>
+  <si>
+    <t>（前面/后面）每有1个食物</t>
+  </si>
+  <si>
+    <t>本行食物
+分数+10
+甜蜜传递至同列1个食物</t>
+  </si>
+  <si>
+    <t>加分数</t>
+  </si>
+  <si>
+    <t>中后</t>
+  </si>
+  <si>
+    <t>本行</t>
+  </si>
+  <si>
+    <t>种类</t>
+  </si>
+  <si>
+    <t>空间相同检测</t>
+  </si>
+  <si>
+    <t>（周围/同列/同行/空）每有1（种/个）相同的食物</t>
+  </si>
+  <si>
+    <t>糖霜蛋糕</t>
+  </si>
+  <si>
+    <t>每有1个技能
+欢乐蛋糕+6层
+甜蜜传递至同行1个食物</t>
+  </si>
+  <si>
+    <t>buff/传递</t>
+  </si>
+  <si>
+    <t>技能转层数</t>
+  </si>
+  <si>
+    <t>大局相同检测</t>
+  </si>
+  <si>
+    <t>本局每结算过一次本种菜品</t>
+  </si>
+  <si>
+    <t>蛋糕食物
+倍率x1.2
+欢乐蛋糕+5层</t>
+  </si>
+  <si>
+    <t>蛋糕</t>
+  </si>
+  <si>
+    <t>一类乘倍率，加buff</t>
+  </si>
+  <si>
+    <t>小局相同检测</t>
+  </si>
+  <si>
+    <t>本次美食品鉴，每（结算过一次/有一个）本种菜品</t>
+  </si>
+  <si>
+    <t>标签</t>
+  </si>
+  <si>
+    <t>标签检测</t>
+  </si>
+  <si>
+    <t>本食物每有1（种/个）技能</t>
+  </si>
+  <si>
+    <t>分数永久+10
+甜蜜传递至本列2个食物</t>
+  </si>
+  <si>
+    <t>分数永久加</t>
+  </si>
+  <si>
+    <t>形状检测</t>
+  </si>
+  <si>
+    <t>（周围/同列/同行/空）每有1（种/个）1*1的食物</t>
+  </si>
+  <si>
+    <t>若（周围/全部）存在xx形状的空格</t>
+  </si>
+  <si>
+    <t>周围及自身
+分数+10
+甜蜜传递至同行2个食物</t>
   </si>
   <si>
     <t>结算</t>
   </si>
   <si>
-    <t>前中后</t>
-  </si>
-  <si>
-    <t>让一个未结算的食物，再次结算一次技能</t>
-  </si>
-  <si>
-    <t>空间</t>
-  </si>
-  <si>
-    <t>位置检测</t>
-  </si>
-  <si>
-    <t>如果（同行/同列/周围/全部）被填满</t>
-  </si>
-  <si>
-    <t>若周围被填满，获得30个金币</t>
-  </si>
-  <si>
-    <t>金币</t>
-  </si>
-  <si>
-    <t>通用</t>
-  </si>
-  <si>
-    <t>空格检测</t>
-  </si>
-  <si>
-    <t>（周围/同列/同行/空）每有1个空格</t>
-  </si>
-  <si>
-    <t>若同行被填满，蛋糕+10层</t>
-  </si>
-  <si>
-    <t>边缘检测</t>
-  </si>
-  <si>
-    <t>若本食物处在边缘</t>
-  </si>
-  <si>
-    <t>视为2个食物，本行每有1个食物，倍率+2</t>
-  </si>
-  <si>
-    <t>中</t>
-  </si>
-  <si>
-    <t>数量</t>
-  </si>
-  <si>
-    <t>检测数量</t>
-  </si>
-  <si>
-    <t>（周围/同列/同行/空）每有1（种/个）食物</t>
-  </si>
-  <si>
-    <t>蛋糕+10层，复制本菜品至空格中</t>
-  </si>
-  <si>
-    <t>阶梯数量</t>
-  </si>
-  <si>
-    <t>（周围/同列/同行/空）食物数量达到[2/5/10]时</t>
-  </si>
-  <si>
-    <t>大小检测</t>
-  </si>
-  <si>
-    <t>（周围/同列/同行/空）每有1（种/个）（大于等于/小于等于）3格的食物</t>
-  </si>
-  <si>
-    <t>周围有占1格的食物时，倍率x1.5。甜蜜传递至同列2个食物</t>
-  </si>
-  <si>
-    <t>顺序检测</t>
-  </si>
-  <si>
-    <t>（前面/后面）每有1个食物</t>
-  </si>
-  <si>
-    <t>周围每有1个食物，倍率x1.2。甜蜜传递至周围2个食物</t>
-  </si>
-  <si>
-    <t>种类</t>
-  </si>
-  <si>
-    <t>空间相同检测</t>
-  </si>
-  <si>
-    <t>（周围/同列/同行/空）每有1（种/个）相同的食物</t>
-  </si>
-  <si>
-    <t>获得周围食物的1个技能。每有1个技能，使蛋糕+6层</t>
-  </si>
-  <si>
-    <t>中后</t>
-  </si>
-  <si>
-    <t>大局相同检测</t>
-  </si>
-  <si>
-    <t>本局每结算过一次本种菜品</t>
-  </si>
-  <si>
-    <t>倍率x1.5。技能额外结算1次</t>
-  </si>
-  <si>
-    <t>小局相同检测</t>
-  </si>
-  <si>
-    <t>本次美食品鉴，每（结算过一次/有一个）本种菜品</t>
-  </si>
-  <si>
-    <t>标签</t>
-  </si>
-  <si>
-    <t>标签检测</t>
-  </si>
-  <si>
-    <t>本食物每有1（种/个）技能</t>
-  </si>
-  <si>
-    <t>分数永久+10。甜蜜传递至2个食物</t>
-  </si>
-  <si>
-    <t>永久乘分数</t>
-  </si>
-  <si>
-    <t>形状检测</t>
-  </si>
-  <si>
-    <t>（周围/同列/同行/空）每有1（种/个）1*1的食物</t>
-  </si>
-  <si>
-    <t>若（周围/全部）存在xx形状的空格</t>
-  </si>
-  <si>
-    <t>技能额外结算1次。甜蜜传递至2个周围食物</t>
+    <t>周围加，同行传</t>
   </si>
   <si>
     <t>上菜</t>
@@ -1831,7 +1941,12 @@
     <t>上菜时</t>
   </si>
   <si>
-    <t>视为4个食物，每有1个食物，倍率+0.2</t>
+    <t>视为4个食物
+全场每有1个食物
+倍率+0.2</t>
+  </si>
+  <si>
+    <t>全场检测加自身倍率</t>
   </si>
   <si>
     <t>菜谱</t>
@@ -1843,19 +1958,29 @@
     <t>菜谱中食物（大于等于/小于等于）3（种/个）时</t>
   </si>
   <si>
-    <t>周围食物倍率+5。甜蜜传递至3个食物</t>
+    <t>周围及自身
+倍率+1.5
+甜蜜传递1个食物</t>
   </si>
   <si>
     <t>倍率</t>
   </si>
   <si>
+    <t>周围加倍率，随机传</t>
+  </si>
+  <si>
     <t>特定种类检测</t>
   </si>
   <si>
     <t>带有“蛋糕”的食物数量达到4（种/个）时</t>
   </si>
   <si>
-    <t>消耗10层欢乐蛋糕，倍率+5</t>
+    <t>最多消耗5层欢乐蛋糕
+每消耗一层
+本行倍率+0.8</t>
+  </si>
+  <si>
+    <t>本行倍率加</t>
   </si>
   <si>
     <t>传递检测</t>
@@ -1873,10 +1998,15 @@
     <t>本局传递次数达到10次时</t>
   </si>
   <si>
-    <t>同列食物倍率+3。甜蜜传递至同行3个食物</t>
-  </si>
-  <si>
-    <t>蛋糕</t>
+    <t>本列食物
+倍率+1
+甜蜜传递至同行2个食物</t>
+  </si>
+  <si>
+    <t>本列</t>
+  </si>
+  <si>
+    <t>本列倍率加</t>
   </si>
   <si>
     <t>层数检测</t>
@@ -1894,10 +2024,18 @@
     <t>（周围/同列/同行/空）有n个（失效/消耗）的食物时</t>
   </si>
   <si>
-    <t>蛋糕x1.5层，至少+5层</t>
-  </si>
-  <si>
-    <t>同行食物达「5/15/25」个时，同行食物倍率x「1.5/2.5/5」</t>
+    <t>欢乐蛋糕x1.5层
+至少+10层</t>
+  </si>
+  <si>
+    <t>枫糖</t>
+  </si>
+  <si>
+    <t>使1个带有甜蜜传递的食物
+额外结算1次甜蜜传递</t>
+  </si>
+  <si>
+    <t>本行倍率乘</t>
   </si>
   <si>
     <t>层数消耗</t>
@@ -1912,7 +2050,12 @@
     <t>每10层使（周围/同列/同行/空/下一个结算）（全部/随机两个）食物分数（x1.5/+10）</t>
   </si>
   <si>
-    <t>视为5个食物，复制周围食物的1个技能</t>
+    <t>视为6个食物
+本行食物达「10/18/25」个时
+本行倍率x「2/3/4」</t>
+  </si>
+  <si>
+    <t>周围倍率乘</t>
   </si>
   <si>
     <t>层数转化结算</t>
@@ -1927,7 +2070,12 @@
     <t>欢乐蛋糕层数（x1.5/+10）</t>
   </si>
   <si>
-    <t>倍率x3。同行被填满时，视为10个食物</t>
+    <t>视为5个食物
+周围及自身
+倍率x2.5</t>
+  </si>
+  <si>
+    <t>周围倍率加</t>
   </si>
   <si>
     <t>多次结算</t>
@@ -1936,7 +2084,9 @@
     <t>（周围/同列/同行/全部/本/下一个结算）（随机2个/空）食物，（周围/同列/同行/全部/本）（随机2个/空）额外结算1次</t>
   </si>
   <si>
-    <t>同列食物额外被视为2个食物，倍率+4</t>
+    <t>视为8个食物
+周围及自身
+倍率+5</t>
   </si>
   <si>
     <t>分数增加</t>
@@ -1951,7 +2101,9 @@
     <t>将（所有/1个）（周围/同列/同行/任意/下一个结算）食物分数（的1/3），加至（本/n个/所有）（同列/周围/同行/任意/下一个结算）食物上</t>
   </si>
   <si>
-    <t>分数永久+10，将分数加到所有蛋糕上</t>
+    <t>本列食物
+额外被视为2个食物
+本列食物分数+50</t>
   </si>
   <si>
     <t>经济运营</t>
@@ -1966,7 +2118,8 @@
     <t>临时复制（周围/同列/同行/空/下一个结算）（全部/随机两个）食物的到空格中</t>
   </si>
   <si>
-    <t>蛋糕层数+15，倍率+5</t>
+    <t>分数永久+10
+将本食物的分数加至蛋糕食物</t>
   </si>
   <si>
     <t>分数永久增长</t>
@@ -1981,7 +2134,10 @@
     <t>消耗（周围/同列/同行/全部/本/下一个结算）（随机2个/空）食物</t>
   </si>
   <si>
-    <t>每有1个技能，倍率+5。甜蜜传递至同列食物</t>
+    <t>蛋糕层数+40</t>
+  </si>
+  <si>
+    <t>自身</t>
   </si>
   <si>
     <t>技能复制</t>
@@ -1996,7 +2152,9 @@
     <t>（周围/同列/同行/全部/本/下一个结算）（随机2个/空）食物获得技能</t>
   </si>
   <si>
-    <t>视为10个食物，周围每有1个食物，倍率x1.2</t>
+    <t>自身每有1个技能
+倍率+3
+甜蜜传递至同列3个食物</t>
   </si>
   <si>
     <t>后</t>
@@ -2014,40 +2172,60 @@
     <t>本菜视为2种菜</t>
   </si>
   <si>
-    <t>视为5个食物，同列食物倍率x2</t>
-  </si>
-  <si>
-    <t>蛋糕层数+20，所有食物倍率+0.5</t>
-  </si>
-  <si>
-    <t>视为8个食物，复制周围的两个技能</t>
-  </si>
-  <si>
-    <t>倍率+5，将倍率加到所有蛋糕上</t>
-  </si>
-  <si>
-    <t>同行每有1个食物，周围食物倍率+0.3</t>
-  </si>
-  <si>
-    <t>倍率x2。蛋糕数量达3/5/8时，蛋糕层数+10/20/40</t>
-  </si>
-  <si>
-    <t>带有甜蜜传递的食物达「3/5/8」种，此类食物倍率x「1.5/2.5/5」</t>
-  </si>
-  <si>
-    <t>周围每有1种食物，蛋糕层数+2层</t>
-  </si>
-  <si>
-    <t>视为4个食物，周围食物倍率x1.5</t>
-  </si>
-  <si>
-    <t>同列食物倍率x1.4。甜蜜传递至周围食物</t>
-  </si>
-  <si>
-    <t>同行同列带有甜蜜传递的食物，执行一次它们的甜蜜传递</t>
-  </si>
-  <si>
-    <t>每有1个技能，倍率x1.5。甜蜜传递至同行食物</t>
+    <t>视为10个食物
+周围每有1个食物
+周围及自身倍率x1.2</t>
+  </si>
+  <si>
+    <t>视为5个食物
+同行倍率x3</t>
+  </si>
+  <si>
+    <t>蛋糕层数+20
+所有食物倍率+1</t>
+  </si>
+  <si>
+    <t>视为8个食物
+将所有占1格食物的倍率
+添加到自身</t>
+  </si>
+  <si>
+    <t>倍率+8
+将倍率加到蛋糕食物上</t>
+  </si>
+  <si>
+    <t>同行每有1个食物
+周围食物倍率+0.5</t>
+  </si>
+  <si>
+    <t>蛋糕食物倍率x2
+蛋糕数量达3/5/8时
+蛋糕层数+30/50/80</t>
+  </si>
+  <si>
+    <t>甜蜜传递食物达「3/5/8」种
+此类食物倍率x「2/3/4」</t>
+  </si>
+  <si>
+    <t>周围每有1种食物
+蛋糕层数+10层</t>
+  </si>
+  <si>
+    <t>视为4个食物
+周围及自身倍率x1.5</t>
+  </si>
+  <si>
+    <t>同列食物倍率x1.3
+甜蜜传递至周围1个食物</t>
+  </si>
+  <si>
+    <t>同行同列带有甜蜜传递的食物
+执行一次它们的甜蜜传递</t>
+  </si>
+  <si>
+    <t>每有1个技能
+倍率x2
+甜蜜传递至同行食物</t>
   </si>
   <si>
     <t>获得3种不同的蛋糕技能</t>
@@ -2059,9 +2237,6 @@
     <t>周围/同列</t>
   </si>
   <si>
-    <t>周围</t>
-  </si>
-  <si>
     <t>同行</t>
   </si>
   <si>
@@ -2072,12 +2247,6 @@
   </si>
   <si>
     <t>周围/同行</t>
-  </si>
-  <si>
-    <t>同行/周围</t>
-  </si>
-  <si>
-    <t>下侧</t>
   </si>
   <si>
     <t>下侧所有/下侧</t>
@@ -2096,7 +2265,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2112,6 +2281,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF101418"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.25"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2266,7 +2441,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2305,7 +2480,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2641,16 +2828,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
@@ -2659,58 +2843,55 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="5">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="5">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
@@ -2719,10 +2900,10 @@
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
@@ -2731,10 +2912,10 @@
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
@@ -2743,10 +2924,10 @@
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
@@ -2755,10 +2936,10 @@
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="37" borderId="0">
@@ -2767,11 +2948,17 @@
     <xf numFmtId="0" fontId="22" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2791,11 +2978,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2809,32 +3002,50 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3307,7 +3518,7 @@
       </c>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -3352,7 +3563,7 @@
       </c>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="30" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -4463,7 +4674,7 @@
       <c r="T27" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U27" s="23" t="s">
+      <c r="U27" s="31" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4496,7 +4707,7 @@
       <c r="T28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="U28" s="23" t="s">
+      <c r="U28" s="31" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4547,12 +4758,12 @@
       <c r="T29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="U29" s="23" t="s">
+      <c r="U29" s="31" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="30" t="s">
         <v>113</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -6226,7 +6437,7 @@
       <c r="L80" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M80" s="23" t="s">
+      <c r="M80" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N80" s="1">
@@ -6248,7 +6459,7 @@
       <c r="L81" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M81" s="23" t="s">
+      <c r="M81" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N81" s="1">
@@ -6270,7 +6481,7 @@
       <c r="L82" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M82" s="23" t="s">
+      <c r="M82" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N82" s="1">
@@ -6292,7 +6503,7 @@
       <c r="L83" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M83" s="23" t="s">
+      <c r="M83" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N83" s="1">
@@ -6314,7 +6525,7 @@
       <c r="L84" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M84" s="23" t="s">
+      <c r="M84" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N84" s="1">
@@ -6357,7 +6568,7 @@
       <c r="L85" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M85" s="23" t="s">
+      <c r="M85" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N85" s="1">
@@ -6379,7 +6590,7 @@
       <c r="L86" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M86" s="23" t="s">
+      <c r="M86" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N86" s="1">
@@ -6401,7 +6612,7 @@
       <c r="L87" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M87" s="23" t="s">
+      <c r="M87" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N87" s="1">
@@ -6444,7 +6655,7 @@
       <c r="L88" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M88" s="23" t="s">
+      <c r="M88" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N88" s="1">
@@ -6466,7 +6677,7 @@
       <c r="L89" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M89" s="23" t="s">
+      <c r="M89" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N89" s="1">
@@ -6488,7 +6699,7 @@
       <c r="L90" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M90" s="23" t="s">
+      <c r="M90" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N90" s="1">
@@ -6510,7 +6721,7 @@
       <c r="L91" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M91" s="23" t="s">
+      <c r="M91" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N91" s="1">
@@ -6529,7 +6740,7 @@
       <c r="L92" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M92" s="23" t="s">
+      <c r="M92" s="31" t="s">
         <v>112</v>
       </c>
       <c r="N92" s="1">
@@ -8365,7 +8576,7 @@
         <f>VLOOKUP(C75,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G75" s="23" t="str">
+      <c r="G75" s="31" t="str">
         <f>VLOOKUP(C75,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -8391,7 +8602,7 @@
         <f>VLOOKUP(C76,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G76" s="23" t="str">
+      <c r="G76" s="31" t="str">
         <f>VLOOKUP(C76,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8417,7 +8628,7 @@
         <f>VLOOKUP(C77,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G77" s="23" t="str">
+      <c r="G77" s="31" t="str">
         <f>VLOOKUP(C77,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8443,7 +8654,7 @@
         <f>VLOOKUP(C78,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G78" s="23" t="str">
+      <c r="G78" s="31" t="str">
         <f>VLOOKUP(C78,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8469,7 +8680,7 @@
         <f>VLOOKUP(C79,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G79" s="23" t="str">
+      <c r="G79" s="31" t="str">
         <f>VLOOKUP(C79,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8495,7 +8706,7 @@
         <f>VLOOKUP(C80,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G80" s="23" t="str">
+      <c r="G80" s="31" t="str">
         <f>VLOOKUP(C80,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8521,7 +8732,7 @@
         <f>VLOOKUP(C81,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G81" s="23" t="str">
+      <c r="G81" s="31" t="str">
         <f>VLOOKUP(C81,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8547,7 +8758,7 @@
         <f>VLOOKUP(C82,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G82" s="23" t="str">
+      <c r="G82" s="31" t="str">
         <f>VLOOKUP(C82,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8573,7 +8784,7 @@
         <f>VLOOKUP(C83,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G83" s="23" t="str">
+      <c r="G83" s="31" t="str">
         <f>VLOOKUP(C83,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8599,7 +8810,7 @@
         <f>VLOOKUP(C84,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G84" s="23" t="str">
+      <c r="G84" s="31" t="str">
         <f>VLOOKUP(C84,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8625,7 +8836,7 @@
         <f>VLOOKUP(C85,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G85" s="23" t="str">
+      <c r="G85" s="31" t="str">
         <f>VLOOKUP(C85,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8651,7 +8862,7 @@
         <f>VLOOKUP(C86,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G86" s="23" t="str">
+      <c r="G86" s="31" t="str">
         <f>VLOOKUP(C86,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8677,7 +8888,7 @@
         <f>VLOOKUP(C87,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G87" s="23" t="str">
+      <c r="G87" s="31" t="str">
         <f>VLOOKUP(C87,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8703,7 +8914,7 @@
         <f>VLOOKUP(C88,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G88" s="23" t="str">
+      <c r="G88" s="31" t="str">
         <f>VLOOKUP(C88,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8729,7 +8940,7 @@
         <f>VLOOKUP(C89,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G89" s="23" t="str">
+      <c r="G89" s="31" t="str">
         <f>VLOOKUP(C89,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8755,7 +8966,7 @@
         <f>VLOOKUP(C90,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G90" s="23" t="str">
+      <c r="G90" s="31" t="str">
         <f>VLOOKUP(C90,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8781,7 +8992,7 @@
         <f>VLOOKUP(C91,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G91" s="23" t="str">
+      <c r="G91" s="31" t="str">
         <f>VLOOKUP(C91,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -8807,7 +9018,7 @@
         <f>VLOOKUP(C92,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G92" s="23" t="str">
+      <c r="G92" s="31" t="str">
         <f>VLOOKUP(C92,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -8833,7 +9044,7 @@
         <f>VLOOKUP(C93,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G93" s="23" t="str">
+      <c r="G93" s="31" t="str">
         <f>VLOOKUP(C93,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -8859,7 +9070,7 @@
         <f>VLOOKUP(C94,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G94" s="23" t="str">
+      <c r="G94" s="31" t="str">
         <f>VLOOKUP(C94,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -8885,7 +9096,7 @@
         <f>VLOOKUP(C95,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>190</v>
       </c>
-      <c r="G95" s="23" t="str">
+      <c r="G95" s="31" t="str">
         <f>VLOOKUP(C95,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -8911,7 +9122,7 @@
         <f>VLOOKUP(C96,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G96" s="23" t="str">
+      <c r="G96" s="31" t="str">
         <f>VLOOKUP(C96,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -8937,7 +9148,7 @@
         <f>VLOOKUP(C97,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>260</v>
       </c>
-      <c r="G97" s="23" t="str">
+      <c r="G97" s="31" t="str">
         <f>VLOOKUP(C97,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -9587,7 +9798,7 @@
         <f>VLOOKUP(C122,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G122" s="23" t="str">
+      <c r="G122" s="31" t="str">
         <f>VLOOKUP(C122,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -9613,7 +9824,7 @@
         <f>VLOOKUP(C123,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G123" s="23" t="str">
+      <c r="G123" s="31" t="str">
         <f>VLOOKUP(C123,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9639,7 +9850,7 @@
         <f>VLOOKUP(C124,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G124" s="23" t="str">
+      <c r="G124" s="31" t="str">
         <f>VLOOKUP(C124,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9665,7 +9876,7 @@
         <f>VLOOKUP(C125,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G125" s="23" t="str">
+      <c r="G125" s="31" t="str">
         <f>VLOOKUP(C125,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9691,7 +9902,7 @@
         <f>VLOOKUP(C126,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G126" s="23" t="str">
+      <c r="G126" s="31" t="str">
         <f>VLOOKUP(C126,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9717,7 +9928,7 @@
         <f>VLOOKUP(C127,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G127" s="23" t="str">
+      <c r="G127" s="31" t="str">
         <f>VLOOKUP(C127,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9743,7 +9954,7 @@
         <f>VLOOKUP(C128,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G128" s="23" t="str">
+      <c r="G128" s="31" t="str">
         <f>VLOOKUP(C128,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9769,7 +9980,7 @@
         <f>VLOOKUP(C129,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G129" s="23" t="str">
+      <c r="G129" s="31" t="str">
         <f>VLOOKUP(C129,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9795,7 +10006,7 @@
         <f>VLOOKUP(C130,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G130" s="23" t="str">
+      <c r="G130" s="31" t="str">
         <f>VLOOKUP(C130,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9821,7 +10032,7 @@
         <f>VLOOKUP(C131,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G131" s="23" t="str">
+      <c r="G131" s="31" t="str">
         <f>VLOOKUP(C131,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9847,7 +10058,7 @@
         <f>VLOOKUP(C132,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G132" s="23" t="str">
+      <c r="G132" s="31" t="str">
         <f>VLOOKUP(C132,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9873,7 +10084,7 @@
         <f>VLOOKUP(C133,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G133" s="23" t="str">
+      <c r="G133" s="31" t="str">
         <f>VLOOKUP(C133,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9899,7 +10110,7 @@
         <f>VLOOKUP(C134,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G134" s="23" t="str">
+      <c r="G134" s="31" t="str">
         <f>VLOOKUP(C134,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9925,7 +10136,7 @@
         <f>VLOOKUP(C135,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G135" s="23" t="str">
+      <c r="G135" s="31" t="str">
         <f>VLOOKUP(C135,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9951,7 +10162,7 @@
         <f>VLOOKUP(C136,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G136" s="23" t="str">
+      <c r="G136" s="31" t="str">
         <f>VLOOKUP(C136,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9977,7 +10188,7 @@
         <f>VLOOKUP(C137,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G137" s="23" t="str">
+      <c r="G137" s="31" t="str">
         <f>VLOOKUP(C137,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10003,7 +10214,7 @@
         <f>VLOOKUP(C138,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G138" s="23" t="str">
+      <c r="G138" s="31" t="str">
         <f>VLOOKUP(C138,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10029,7 +10240,7 @@
         <f>VLOOKUP(C139,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G139" s="23" t="str">
+      <c r="G139" s="31" t="str">
         <f>VLOOKUP(C139,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -10055,7 +10266,7 @@
         <f>VLOOKUP(C140,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G140" s="23" t="str">
+      <c r="G140" s="31" t="str">
         <f>VLOOKUP(C140,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -10081,7 +10292,7 @@
         <f>VLOOKUP(C141,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G141" s="23" t="str">
+      <c r="G141" s="31" t="str">
         <f>VLOOKUP(C141,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10107,7 +10318,7 @@
         <f>VLOOKUP(C142,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>190</v>
       </c>
-      <c r="G142" s="23" t="str">
+      <c r="G142" s="31" t="str">
         <f>VLOOKUP(C142,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -10133,7 +10344,7 @@
         <f>VLOOKUP(C143,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G143" s="23" t="str">
+      <c r="G143" s="31" t="str">
         <f>VLOOKUP(C143,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -10159,7 +10370,7 @@
         <f>VLOOKUP(C144,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>260</v>
       </c>
-      <c r="G144" s="23" t="str">
+      <c r="G144" s="31" t="str">
         <f>VLOOKUP(C144,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -10809,7 +11020,7 @@
         <f>VLOOKUP(C169,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G169" s="23" t="str">
+      <c r="G169" s="31" t="str">
         <f>VLOOKUP(C169,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -10835,7 +11046,7 @@
         <f>VLOOKUP(C170,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G170" s="23" t="str">
+      <c r="G170" s="31" t="str">
         <f>VLOOKUP(C170,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10861,7 +11072,7 @@
         <f>VLOOKUP(C171,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G171" s="23" t="str">
+      <c r="G171" s="31" t="str">
         <f>VLOOKUP(C171,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10887,7 +11098,7 @@
         <f>VLOOKUP(C172,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G172" s="23" t="str">
+      <c r="G172" s="31" t="str">
         <f>VLOOKUP(C172,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10913,7 +11124,7 @@
         <f>VLOOKUP(C173,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G173" s="23" t="str">
+      <c r="G173" s="31" t="str">
         <f>VLOOKUP(C173,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10939,7 +11150,7 @@
         <f>VLOOKUP(C174,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G174" s="23" t="str">
+      <c r="G174" s="31" t="str">
         <f>VLOOKUP(C174,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10965,7 +11176,7 @@
         <f>VLOOKUP(C175,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G175" s="23" t="str">
+      <c r="G175" s="31" t="str">
         <f>VLOOKUP(C175,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10991,7 +11202,7 @@
         <f>VLOOKUP(C176,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G176" s="23" t="str">
+      <c r="G176" s="31" t="str">
         <f>VLOOKUP(C176,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11017,7 +11228,7 @@
         <f>VLOOKUP(C177,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G177" s="23" t="str">
+      <c r="G177" s="31" t="str">
         <f>VLOOKUP(C177,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11043,7 +11254,7 @@
         <f>VLOOKUP(C178,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G178" s="23" t="str">
+      <c r="G178" s="31" t="str">
         <f>VLOOKUP(C178,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11069,7 +11280,7 @@
         <f>VLOOKUP(C179,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G179" s="23" t="str">
+      <c r="G179" s="31" t="str">
         <f>VLOOKUP(C179,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11095,7 +11306,7 @@
         <f>VLOOKUP(C180,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G180" s="23" t="str">
+      <c r="G180" s="31" t="str">
         <f>VLOOKUP(C180,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11121,7 +11332,7 @@
         <f>VLOOKUP(C181,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G181" s="23" t="str">
+      <c r="G181" s="31" t="str">
         <f>VLOOKUP(C181,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11147,7 +11358,7 @@
         <f>VLOOKUP(C182,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G182" s="23" t="str">
+      <c r="G182" s="31" t="str">
         <f>VLOOKUP(C182,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11173,7 +11384,7 @@
         <f>VLOOKUP(C183,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G183" s="23" t="str">
+      <c r="G183" s="31" t="str">
         <f>VLOOKUP(C183,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11199,7 +11410,7 @@
         <f>VLOOKUP(C184,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G184" s="23" t="str">
+      <c r="G184" s="31" t="str">
         <f>VLOOKUP(C184,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11225,7 +11436,7 @@
         <f>VLOOKUP(C185,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G185" s="23" t="str">
+      <c r="G185" s="31" t="str">
         <f>VLOOKUP(C185,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11251,7 +11462,7 @@
         <f>VLOOKUP(C186,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G186" s="23" t="str">
+      <c r="G186" s="31" t="str">
         <f>VLOOKUP(C186,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -11277,7 +11488,7 @@
         <f>VLOOKUP(C187,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G187" s="23" t="str">
+      <c r="G187" s="31" t="str">
         <f>VLOOKUP(C187,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -11303,7 +11514,7 @@
         <f>VLOOKUP(C188,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G188" s="23" t="str">
+      <c r="G188" s="31" t="str">
         <f>VLOOKUP(C188,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11329,7 +11540,7 @@
         <f>VLOOKUP(C189,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>190</v>
       </c>
-      <c r="G189" s="23" t="str">
+      <c r="G189" s="31" t="str">
         <f>VLOOKUP(C189,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -11355,7 +11566,7 @@
         <f>VLOOKUP(C190,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G190" s="23" t="str">
+      <c r="G190" s="31" t="str">
         <f>VLOOKUP(C190,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -11381,7 +11592,7 @@
         <f>VLOOKUP(C191,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>260</v>
       </c>
-      <c r="G191" s="23" t="str">
+      <c r="G191" s="31" t="str">
         <f>VLOOKUP(C191,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -12031,7 +12242,7 @@
         <f>VLOOKUP(C216,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G216" s="23" t="str">
+      <c r="G216" s="31" t="str">
         <f>VLOOKUP(C216,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -12057,7 +12268,7 @@
         <f>VLOOKUP(C217,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G217" s="23" t="str">
+      <c r="G217" s="31" t="str">
         <f>VLOOKUP(C217,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12083,7 +12294,7 @@
         <f>VLOOKUP(C218,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G218" s="23" t="str">
+      <c r="G218" s="31" t="str">
         <f>VLOOKUP(C218,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12109,7 +12320,7 @@
         <f>VLOOKUP(C219,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G219" s="23" t="str">
+      <c r="G219" s="31" t="str">
         <f>VLOOKUP(C219,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12135,7 +12346,7 @@
         <f>VLOOKUP(C220,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G220" s="23" t="str">
+      <c r="G220" s="31" t="str">
         <f>VLOOKUP(C220,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12161,7 +12372,7 @@
         <f>VLOOKUP(C221,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G221" s="23" t="str">
+      <c r="G221" s="31" t="str">
         <f>VLOOKUP(C221,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12187,7 +12398,7 @@
         <f>VLOOKUP(C222,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G222" s="23" t="str">
+      <c r="G222" s="31" t="str">
         <f>VLOOKUP(C222,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12213,7 +12424,7 @@
         <f>VLOOKUP(C223,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G223" s="23" t="str">
+      <c r="G223" s="31" t="str">
         <f>VLOOKUP(C223,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12239,7 +12450,7 @@
         <f>VLOOKUP(C224,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G224" s="23" t="str">
+      <c r="G224" s="31" t="str">
         <f>VLOOKUP(C224,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12265,7 +12476,7 @@
         <f>VLOOKUP(C225,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G225" s="23" t="str">
+      <c r="G225" s="31" t="str">
         <f>VLOOKUP(C225,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12291,7 +12502,7 @@
         <f>VLOOKUP(C226,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G226" s="23" t="str">
+      <c r="G226" s="31" t="str">
         <f>VLOOKUP(C226,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12317,7 +12528,7 @@
         <f>VLOOKUP(C227,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G227" s="23" t="str">
+      <c r="G227" s="31" t="str">
         <f>VLOOKUP(C227,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12343,7 +12554,7 @@
         <f>VLOOKUP(C228,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G228" s="23" t="str">
+      <c r="G228" s="31" t="str">
         <f>VLOOKUP(C228,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12369,7 +12580,7 @@
         <f>VLOOKUP(C229,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G229" s="23" t="str">
+      <c r="G229" s="31" t="str">
         <f>VLOOKUP(C229,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12395,7 +12606,7 @@
         <f>VLOOKUP(C230,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G230" s="23" t="str">
+      <c r="G230" s="31" t="str">
         <f>VLOOKUP(C230,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12421,7 +12632,7 @@
         <f>VLOOKUP(C231,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G231" s="23" t="str">
+      <c r="G231" s="31" t="str">
         <f>VLOOKUP(C231,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12447,7 +12658,7 @@
         <f>VLOOKUP(C232,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G232" s="23" t="str">
+      <c r="G232" s="31" t="str">
         <f>VLOOKUP(C232,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12473,7 +12684,7 @@
         <f>VLOOKUP(C233,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G233" s="23" t="str">
+      <c r="G233" s="31" t="str">
         <f>VLOOKUP(C233,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -12499,7 +12710,7 @@
         <f>VLOOKUP(C234,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G234" s="23" t="str">
+      <c r="G234" s="31" t="str">
         <f>VLOOKUP(C234,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -12525,7 +12736,7 @@
         <f>VLOOKUP(C235,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G235" s="23" t="str">
+      <c r="G235" s="31" t="str">
         <f>VLOOKUP(C235,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12551,7 +12762,7 @@
         <f>VLOOKUP(C236,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>190</v>
       </c>
-      <c r="G236" s="23" t="str">
+      <c r="G236" s="31" t="str">
         <f>VLOOKUP(C236,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -12577,7 +12788,7 @@
         <f>VLOOKUP(C237,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G237" s="23" t="str">
+      <c r="G237" s="31" t="str">
         <f>VLOOKUP(C237,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -12603,7 +12814,7 @@
         <f>VLOOKUP(C238,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>260</v>
       </c>
-      <c r="G238" s="23" t="str">
+      <c r="G238" s="31" t="str">
         <f>VLOOKUP(C238,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -13256,7 +13467,7 @@
         <f>VLOOKUP(C263,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G263" s="23" t="str">
+      <c r="G263" s="31" t="str">
         <f>VLOOKUP(C263,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -13282,7 +13493,7 @@
         <f>VLOOKUP(C264,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G264" s="23" t="str">
+      <c r="G264" s="31" t="str">
         <f>VLOOKUP(C264,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13308,7 +13519,7 @@
         <f>VLOOKUP(C265,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G265" s="23" t="str">
+      <c r="G265" s="31" t="str">
         <f>VLOOKUP(C265,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13334,7 +13545,7 @@
         <f>VLOOKUP(C266,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G266" s="23" t="str">
+      <c r="G266" s="31" t="str">
         <f>VLOOKUP(C266,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13360,7 +13571,7 @@
         <f>VLOOKUP(C267,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G267" s="23" t="str">
+      <c r="G267" s="31" t="str">
         <f>VLOOKUP(C267,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13386,7 +13597,7 @@
         <f>VLOOKUP(C268,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G268" s="23" t="str">
+      <c r="G268" s="31" t="str">
         <f>VLOOKUP(C268,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13412,7 +13623,7 @@
         <f>VLOOKUP(C269,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G269" s="23" t="str">
+      <c r="G269" s="31" t="str">
         <f>VLOOKUP(C269,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13438,7 +13649,7 @@
         <f>VLOOKUP(C270,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G270" s="23" t="str">
+      <c r="G270" s="31" t="str">
         <f>VLOOKUP(C270,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13464,7 +13675,7 @@
         <f>VLOOKUP(C271,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G271" s="23" t="str">
+      <c r="G271" s="31" t="str">
         <f>VLOOKUP(C271,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13490,7 +13701,7 @@
         <f>VLOOKUP(C272,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G272" s="23" t="str">
+      <c r="G272" s="31" t="str">
         <f>VLOOKUP(C272,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13516,7 +13727,7 @@
         <f>VLOOKUP(C273,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G273" s="23" t="str">
+      <c r="G273" s="31" t="str">
         <f>VLOOKUP(C273,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13542,7 +13753,7 @@
         <f>VLOOKUP(C274,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G274" s="23" t="str">
+      <c r="G274" s="31" t="str">
         <f>VLOOKUP(C274,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13568,7 +13779,7 @@
         <f>VLOOKUP(C275,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G275" s="23" t="str">
+      <c r="G275" s="31" t="str">
         <f>VLOOKUP(C275,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13594,7 +13805,7 @@
         <f>VLOOKUP(C276,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G276" s="23" t="str">
+      <c r="G276" s="31" t="str">
         <f>VLOOKUP(C276,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13620,7 +13831,7 @@
         <f>VLOOKUP(C277,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G277" s="23" t="str">
+      <c r="G277" s="31" t="str">
         <f>VLOOKUP(C277,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13646,7 +13857,7 @@
         <f>VLOOKUP(C278,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G278" s="23" t="str">
+      <c r="G278" s="31" t="str">
         <f>VLOOKUP(C278,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13672,7 +13883,7 @@
         <f>VLOOKUP(C279,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G279" s="23" t="str">
+      <c r="G279" s="31" t="str">
         <f>VLOOKUP(C279,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13698,7 +13909,7 @@
         <f>VLOOKUP(C280,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G280" s="23" t="str">
+      <c r="G280" s="31" t="str">
         <f>VLOOKUP(C280,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -13724,7 +13935,7 @@
         <f>VLOOKUP(C281,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G281" s="23" t="str">
+      <c r="G281" s="31" t="str">
         <f>VLOOKUP(C281,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -13750,7 +13961,7 @@
         <f>VLOOKUP(C282,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G282" s="23" t="str">
+      <c r="G282" s="31" t="str">
         <f>VLOOKUP(C282,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13776,7 +13987,7 @@
         <f>VLOOKUP(C283,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>190</v>
       </c>
-      <c r="G283" s="23" t="str">
+      <c r="G283" s="31" t="str">
         <f>VLOOKUP(C283,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -13802,7 +14013,7 @@
         <f>VLOOKUP(C284,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G284" s="23" t="str">
+      <c r="G284" s="31" t="str">
         <f>VLOOKUP(C284,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -13828,7 +14039,7 @@
         <f>VLOOKUP(C285,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>260</v>
       </c>
-      <c r="G285" s="23" t="str">
+      <c r="G285" s="31" t="str">
         <f>VLOOKUP(C285,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -14478,7 +14689,7 @@
         <f>VLOOKUP(C310,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G310" s="23" t="str">
+      <c r="G310" s="31" t="str">
         <f>VLOOKUP(C310,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -14504,7 +14715,7 @@
         <f>VLOOKUP(C311,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G311" s="23" t="str">
+      <c r="G311" s="31" t="str">
         <f>VLOOKUP(C311,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14530,7 +14741,7 @@
         <f>VLOOKUP(C312,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G312" s="23" t="str">
+      <c r="G312" s="31" t="str">
         <f>VLOOKUP(C312,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14556,7 +14767,7 @@
         <f>VLOOKUP(C313,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G313" s="23" t="str">
+      <c r="G313" s="31" t="str">
         <f>VLOOKUP(C313,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14582,7 +14793,7 @@
         <f>VLOOKUP(C314,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G314" s="23" t="str">
+      <c r="G314" s="31" t="str">
         <f>VLOOKUP(C314,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14608,7 +14819,7 @@
         <f>VLOOKUP(C315,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G315" s="23" t="str">
+      <c r="G315" s="31" t="str">
         <f>VLOOKUP(C315,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14634,7 +14845,7 @@
         <f>VLOOKUP(C316,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G316" s="23" t="str">
+      <c r="G316" s="31" t="str">
         <f>VLOOKUP(C316,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14660,7 +14871,7 @@
         <f>VLOOKUP(C317,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G317" s="23" t="str">
+      <c r="G317" s="31" t="str">
         <f>VLOOKUP(C317,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14686,7 +14897,7 @@
         <f>VLOOKUP(C318,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G318" s="23" t="str">
+      <c r="G318" s="31" t="str">
         <f>VLOOKUP(C318,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14712,7 +14923,7 @@
         <f>VLOOKUP(C319,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G319" s="23" t="str">
+      <c r="G319" s="31" t="str">
         <f>VLOOKUP(C319,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14738,7 +14949,7 @@
         <f>VLOOKUP(C320,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G320" s="23" t="str">
+      <c r="G320" s="31" t="str">
         <f>VLOOKUP(C320,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14764,7 +14975,7 @@
         <f>VLOOKUP(C321,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G321" s="23" t="str">
+      <c r="G321" s="31" t="str">
         <f>VLOOKUP(C321,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14790,7 +15001,7 @@
         <f>VLOOKUP(C322,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G322" s="23" t="str">
+      <c r="G322" s="31" t="str">
         <f>VLOOKUP(C322,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14816,7 +15027,7 @@
         <f>VLOOKUP(C323,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G323" s="23" t="str">
+      <c r="G323" s="31" t="str">
         <f>VLOOKUP(C323,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14842,7 +15053,7 @@
         <f>VLOOKUP(C324,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G324" s="23" t="str">
+      <c r="G324" s="31" t="str">
         <f>VLOOKUP(C324,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14868,7 +15079,7 @@
         <f>VLOOKUP(C325,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G325" s="23" t="str">
+      <c r="G325" s="31" t="str">
         <f>VLOOKUP(C325,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14894,7 +15105,7 @@
         <f>VLOOKUP(C326,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G326" s="23" t="str">
+      <c r="G326" s="31" t="str">
         <f>VLOOKUP(C326,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14920,7 +15131,7 @@
         <f>VLOOKUP(C327,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G327" s="23" t="str">
+      <c r="G327" s="31" t="str">
         <f>VLOOKUP(C327,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -14946,7 +15157,7 @@
         <f>VLOOKUP(C328,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G328" s="23" t="str">
+      <c r="G328" s="31" t="str">
         <f>VLOOKUP(C328,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -14972,7 +15183,7 @@
         <f>VLOOKUP(C329,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>90</v>
       </c>
-      <c r="G329" s="23" t="str">
+      <c r="G329" s="31" t="str">
         <f>VLOOKUP(C329,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14998,7 +15209,7 @@
         <f>VLOOKUP(C330,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>190</v>
       </c>
-      <c r="G330" s="23" t="str">
+      <c r="G330" s="31" t="str">
         <f>VLOOKUP(C330,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -15024,7 +15235,7 @@
         <f>VLOOKUP(C331,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G331" s="23" t="str">
+      <c r="G331" s="31" t="str">
         <f>VLOOKUP(C331,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -15050,7 +15261,7 @@
         <f>VLOOKUP(C332,dish_base!$B$4:$O$92,14,FALSE)</f>
         <v>260</v>
       </c>
-      <c r="G332" s="23" t="str">
+      <c r="G332" s="31" t="str">
         <f>VLOOKUP(C332,dish_base!$B$4:$M$92,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -16623,7 +16834,7 @@
       <c r="P4" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="S4" s="22" t="str">
+      <c r="S4" s="30" t="str">
         <f>IFERROR(VLOOKUP(B4,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>曲奇</v>
       </c>
@@ -16672,11 +16883,11 @@
       <c r="P5" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="S5" s="22" t="str">
+      <c r="S5" s="30" t="str">
         <f>IFERROR(VLOOKUP(B5,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>马卡龙</v>
       </c>
-      <c r="T5" s="22" t="str">
+      <c r="T5" s="30" t="str">
         <f>IFERROR(VLOOKUP(B5,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -16724,11 +16935,11 @@
       <c r="Q6" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S6" s="22" t="str">
+      <c r="S6" s="30" t="str">
         <f>IFERROR(VLOOKUP(B6,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T6" s="22" t="str">
+      <c r="T6" s="30" t="str">
         <f>IFERROR(VLOOKUP(B6,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>马卡龙</v>
       </c>
@@ -16874,7 +17085,7 @@
       <c r="P9" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="S9" s="22" t="str">
+      <c r="S9" s="30" t="str">
         <f>IFERROR(VLOOKUP(B9,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>蛋挞</v>
       </c>
@@ -17070,7 +17281,7 @@
       <c r="P13" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="S13" s="22" t="str">
+      <c r="S13" s="30" t="str">
         <f>IFERROR(VLOOKUP(B13,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>果冻</v>
       </c>
@@ -17131,53 +17342,53 @@
         <v/>
       </c>
     </row>
-    <row r="15" s="14" customFormat="1" spans="2:20">
-      <c r="B15" s="14" t="s">
+    <row r="15" s="29" customFormat="1" spans="2:20">
+      <c r="B15" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="29" t="s">
         <v>420</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="K15" s="14">
+      <c r="K15" s="29">
         <v>0</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="29">
         <v>1</v>
       </c>
-      <c r="M15" s="14" t="s">
+      <c r="M15" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="N15" s="14" t="s">
+      <c r="N15" s="29" t="s">
         <v>415</v>
       </c>
-      <c r="O15" s="14" t="s">
+      <c r="O15" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="P15" s="14" t="s">
+      <c r="P15" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="R15" s="14" t="s">
+      <c r="R15" s="29" t="s">
         <v>444</v>
       </c>
       <c r="S15" s="1" t="str">
@@ -17385,11 +17596,11 @@
       <c r="P19" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="S19" s="22" t="str">
+      <c r="S19" s="30" t="str">
         <f>IFERROR(VLOOKUP(B19,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>圣代</v>
       </c>
-      <c r="T19" s="22" t="str">
+      <c r="T19" s="30" t="str">
         <f>IFERROR(VLOOKUP(B19,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17434,11 +17645,11 @@
       <c r="P20" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="S20" s="22" t="str">
+      <c r="S20" s="30" t="str">
         <f>IFERROR(VLOOKUP(B20,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T20" s="22" t="str">
+      <c r="T20" s="30" t="str">
         <f>IFERROR(VLOOKUP(B20,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>圣代</v>
       </c>
@@ -17495,53 +17706,53 @@
         <v/>
       </c>
     </row>
-    <row r="22" s="14" customFormat="1" ht="34" spans="2:20">
-      <c r="B22" s="14" t="s">
+    <row r="22" s="29" customFormat="1" ht="34" spans="2:20">
+      <c r="B22" s="29" t="s">
         <v>452</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="29" t="s">
         <v>453</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="29" t="s">
         <v>420</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="29" t="s">
         <v>454</v>
       </c>
-      <c r="J22" s="14" t="s">
+      <c r="J22" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="K22" s="14">
+      <c r="K22" s="29">
         <v>0</v>
       </c>
-      <c r="L22" s="14">
+      <c r="L22" s="29">
         <v>1</v>
       </c>
-      <c r="M22" s="14" t="s">
+      <c r="M22" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="N22" s="14" t="s">
+      <c r="N22" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="O22" s="14" t="s">
+      <c r="O22" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="P22" s="21" t="s">
+      <c r="P22" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="R22" s="14" t="s">
+      <c r="R22" s="29" t="s">
         <v>456</v>
       </c>
       <c r="S22" s="1" t="str">
@@ -17596,11 +17807,11 @@
       <c r="P23" s="20" t="s">
         <v>459</v>
       </c>
-      <c r="S23" s="22" t="str">
+      <c r="S23" s="30" t="str">
         <f>IFERROR(VLOOKUP(B23,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>棒棒糖</v>
       </c>
-      <c r="T23" s="22" t="str">
+      <c r="T23" s="30" t="str">
         <f>IFERROR(VLOOKUP(B23,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17648,11 +17859,11 @@
       <c r="Q24" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S24" s="22" t="str">
+      <c r="S24" s="30" t="str">
         <f>IFERROR(VLOOKUP(B24,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T24" s="22" t="str">
+      <c r="T24" s="30" t="str">
         <f>IFERROR(VLOOKUP(B24,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>棒棒糖</v>
       </c>
@@ -17888,7 +18099,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>25</v>
@@ -17899,7 +18110,7 @@
       <c r="P29" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="S29" s="1" t="str">
+      <c r="S29" s="30" t="str">
         <f>IFERROR(VLOOKUP(B29,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>慕斯蛋糕</v>
       </c>
@@ -17948,11 +18159,11 @@
       <c r="P30" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="S30" s="22" t="str">
+      <c r="S30" s="30" t="str">
         <f>IFERROR(VLOOKUP(B30,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>太妃糖</v>
       </c>
-      <c r="T30" s="22" t="str">
+      <c r="T30" s="30" t="str">
         <f>IFERROR(VLOOKUP(B30,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18000,11 +18211,11 @@
       <c r="Q31" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S31" s="22" t="str">
+      <c r="S31" s="30" t="str">
         <f>IFERROR(VLOOKUP(B31,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T31" s="22" t="str">
+      <c r="T31" s="30" t="str">
         <f>IFERROR(VLOOKUP(B31,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>太妃糖</v>
       </c>
@@ -18147,11 +18358,11 @@
       <c r="P34" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="S34" s="22" t="str">
+      <c r="S34" s="30" t="str">
         <f>IFERROR(VLOOKUP(B34,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>巧克力棒</v>
       </c>
-      <c r="T34" s="22" t="str">
+      <c r="T34" s="30" t="str">
         <f>IFERROR(VLOOKUP(B34,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18199,11 +18410,11 @@
       <c r="Q35" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="S35" s="22" t="str">
+      <c r="S35" s="30" t="str">
         <f>IFERROR(VLOOKUP(B35,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T35" s="22" t="str">
+      <c r="T35" s="30" t="str">
         <f>IFERROR(VLOOKUP(B35,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>巧克力棒</v>
       </c>
@@ -18254,11 +18465,11 @@
       <c r="R36" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="S36" s="22" t="str">
+      <c r="S36" s="30" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>闪电泡芙</v>
       </c>
-      <c r="T36" s="22" t="str">
+      <c r="T36" s="30" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18306,11 +18517,11 @@
       <c r="R37" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="S37" s="22" t="str">
+      <c r="S37" s="30" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T37" s="22" t="str">
+      <c r="T37" s="30" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>闪电泡芙</v>
       </c>
@@ -18624,11 +18835,11 @@
       <c r="P43" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="S43" s="22" t="str">
+      <c r="S43" s="30" t="str">
         <f>IFERROR(VLOOKUP(B43,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>华夫饼</v>
       </c>
-      <c r="T43" s="22" t="str">
+      <c r="T43" s="30" t="str">
         <f>IFERROR(VLOOKUP(B43,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18673,11 +18884,11 @@
       <c r="P44" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="S44" s="22" t="str">
+      <c r="S44" s="30" t="str">
         <f>IFERROR(VLOOKUP(B44,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T44" s="22" t="str">
+      <c r="T44" s="30" t="str">
         <f>IFERROR(VLOOKUP(B44,skill!$H$4:$K$50,4,FALSE),"")</f>
         <v>华夫饼</v>
       </c>
@@ -19640,7 +19851,7 @@
       <c r="P63" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="S63" s="22" t="str">
+      <c r="S63" s="30" t="str">
         <f>IFERROR(VLOOKUP(B63,skill!$G$4:$K$50,5,FALSE),"")</f>
         <v>蝴蝶酥</v>
       </c>
@@ -20014,64 +20225,73 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:O90"/>
+  <dimension ref="A2:Y92"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="9.23076923076923" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5384615384615" style="1" customWidth="1"/>
     <col min="3" max="3" width="22.7596153846154" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.4807692307692" style="1" customWidth="1"/>
-    <col min="5" max="5" width="62.6923076923077" style="1" customWidth="1"/>
-    <col min="6" max="7" width="21.0576923076923" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.0673076923077" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.2307692307692" style="1" customWidth="1"/>
-    <col min="10" max="10" width="46.4711538461538" style="1" customWidth="1"/>
-    <col min="11" max="13" width="9.23076923076923" style="1" customWidth="1"/>
-    <col min="14" max="14" width="20.9903846153846" style="1" customWidth="1"/>
-    <col min="15" max="15" width="106.134615384615" style="8" customWidth="1"/>
-    <col min="16" max="16384" width="9.23076923076923" style="1" customWidth="1"/>
+    <col min="5" max="5" width="28.8461538461538" style="1" customWidth="1"/>
+    <col min="6" max="10" width="28.8461538461538" style="10" customWidth="1"/>
+    <col min="11" max="11" width="21.0576923076923" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.0673076923077" style="1" customWidth="1"/>
+    <col min="13" max="14" width="16.3846153846154" style="1" customWidth="1"/>
+    <col min="15" max="15" width="46.4711538461538" style="1" customWidth="1"/>
+    <col min="16" max="17" width="9.23076923076923" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.4615384615385" style="1" customWidth="1"/>
+    <col min="19" max="23" width="9.23076923076923" style="1" customWidth="1"/>
+    <col min="24" max="24" width="20.9903846153846" style="1" customWidth="1"/>
+    <col min="25" max="25" width="106.134615384615" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.23076923076923" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="18" customHeight="1" spans="1:13">
+    <row r="2" ht="18" customHeight="1" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="L2" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="M2" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="N2" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="O2" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="M2" t="s">
+      <c r="P2" s="1" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="3" ht="17.6" customHeight="1" spans="1:15">
+      <c r="W2" s="26"/>
+    </row>
+    <row r="3" ht="34" spans="1:17">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -20080,149 +20300,218 @@
       <c r="D3" s="1">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="1" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="4" ht="17.6" customHeight="1" spans="1:13">
+      <c r="P3" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="1">
+        <f>P3*10</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" ht="51" spans="1:17">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="1">
-        <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="20" t="s">
         <v>515</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" s="1" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="5" ht="17.6" customHeight="1" spans="1:13">
+      <c r="O4" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="P4" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>P4*3*2</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="34" spans="1:23">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>33</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D5" s="1">
+        <v>40</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>520</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1">
         <v>30</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="M5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="6" ht="17.6" customHeight="1" spans="1:13">
+      <c r="W5" s="26"/>
+    </row>
+    <row r="6" ht="34" spans="1:23">
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="1">
-        <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" s="1" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="7" ht="17.6" customHeight="1" spans="1:13">
+      <c r="N6" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="P6" s="1">
+        <v>2</v>
+      </c>
+      <c r="W6" s="26"/>
+    </row>
+    <row r="7" ht="34" spans="1:21">
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="1">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="G7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>527</v>
+      </c>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="M7" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="8" ht="17.6" customHeight="1" spans="1:9">
+      <c r="N7" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="P7" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>8</v>
+      </c>
+      <c r="R7" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="S7" s="26"/>
+      <c r="T7" s="26"/>
+      <c r="U7" s="26"/>
+    </row>
+    <row r="8" ht="34" spans="1:17">
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -20231,50 +20520,84 @@
       <c r="D8" s="1">
         <v>10</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="E8" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="9" ht="17.6" customHeight="1" spans="1:9">
+      <c r="N8" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="P8" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="1:17">
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="11" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D9" s="1">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>533</v>
+      </c>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="I9" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="10" ht="17.6" customHeight="1" spans="1:14">
+      <c r="N9" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="P9" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="34" spans="1:24">
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -20283,53 +20606,88 @@
       <c r="D10" s="1">
         <v>10</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="I10" s="1" t="s">
+      <c r="E10" s="20" t="s">
+        <v>535</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="M10" s="1" t="s">
         <v>517</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="11" ht="17.6" customHeight="1" spans="1:9">
+        <v>513</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="P10" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>5</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="11" ht="51" spans="1:17">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D11" s="1">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="M11" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="12" ht="17.6" customHeight="1" spans="1:15">
+      <c r="N11" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="P11" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="Q11" s="1">
+        <f>P11*3*5</f>
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="12" ht="17.6" customHeight="1" spans="1:25">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -20339,32 +20697,41 @@
         <v>10</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="G12" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="M12" s="1" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="13" ht="17.6" customHeight="1" spans="1:15">
+        <v>523</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="P12" s="1">
+        <v>8</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="13" ht="51" spans="1:25">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="12" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -20373,32 +20740,47 @@
       <c r="D13" s="1">
         <v>10</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="I13" s="1" t="s">
+      <c r="E13" s="22" t="s">
+        <v>548</v>
+      </c>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="M13" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="N13" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>518</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="P13" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q13" s="1">
+        <f>2*5*0.2</f>
+        <v>2</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="Y13" s="1" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="14" ht="34" spans="1:25">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -20409,64 +20791,104 @@
         <v>28</v>
       </c>
       <c r="D14" s="1">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>549</v>
+        <v>10</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+        <v>554</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="Y14" s="1" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="15" ht="34" spans="1:25">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="14" t="s">
         <v>67</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="1">
-        <v>8</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="G15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>560</v>
+      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>524</v>
+      <c r="L15" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="16" ht="17.6" customHeight="1" spans="1:15">
+        <v>523</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="S15" s="26">
+        <v>30</v>
+      </c>
+      <c r="T15" s="26">
+        <v>2</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16" ht="51" spans="1:25">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="11" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -20475,33 +20897,63 @@
       <c r="D16" s="1">
         <v>20</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="G16" s="1" t="s">
+      <c r="E16" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="L16" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="N16" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="17" ht="17.6" customHeight="1" spans="1:15">
+        <v>513</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="1">
+        <f>6*P16</f>
+        <v>6</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="S16" s="1">
+        <v>90</v>
+      </c>
+      <c r="T16" s="1">
+        <v>6</v>
+      </c>
+      <c r="U16" s="1">
+        <v>2</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="17" ht="34" spans="1:25">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -20510,229 +20962,348 @@
       <c r="D17" s="1">
         <v>20</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>560</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="E17" s="24" t="s">
+        <v>572</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>524</v>
+      <c r="L17" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>525</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>561</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="18" spans="3:15">
+        <v>523</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="S17" s="1">
+        <v>150</v>
+      </c>
+      <c r="T17" s="1">
+        <v>12</v>
+      </c>
+      <c r="U17" s="1">
+        <v>4</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25">
       <c r="C18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N18" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="19" ht="17.6" customHeight="1" spans="1:15">
+      <c r="R18" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="S18" s="1">
+        <v>240</v>
+      </c>
+      <c r="T18" s="1">
+        <v>18</v>
+      </c>
+      <c r="U18" s="1">
+        <v>7</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="19" ht="51" spans="1:25">
       <c r="A19" s="1">
         <v>16</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="12" t="s">
         <v>78</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D19" s="1">
-        <v>10</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>517</v>
+        <v>20</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>580</v>
+      </c>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="20" ht="17.6" customHeight="1" spans="1:15">
+        <v>582</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q19" s="1">
+        <f>3*P19*0.6</f>
+        <v>2.7</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="20" ht="51" spans="1:25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="12" t="s">
         <v>81</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="D20" s="1">
+        <v>20</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>586</v>
+      </c>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M20" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="N20" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="21" ht="17.6" customHeight="1" spans="1:15">
+        <v>589</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q20" s="1">
+        <f>P20*2*5</f>
+        <v>100</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="21" ht="51" spans="1:25">
       <c r="A21" s="1">
         <v>18</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>84</v>
+      <c r="B21" s="15" t="s">
+        <v>593</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D21" s="1">
-        <v>14</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="G21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>594</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="22" ht="17.6" customHeight="1" spans="1:15">
+      <c r="O21" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="22" ht="51" spans="1:25">
       <c r="A22" s="1">
         <v>19</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D22" s="1">
-        <v>16</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>524</v>
+        <v>20</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="23" spans="3:15">
+        <v>600</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="Q22" s="1">
+        <f>P22*3*30*0.2</f>
+        <v>21.6</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25">
       <c r="C23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="24" ht="17.6" customHeight="1" spans="1:15">
+      <c r="W23" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="24" ht="34" spans="1:25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="12" t="s">
         <v>95</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D24" s="1">
-        <v>15</v>
-      </c>
-      <c r="E24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>607</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="N24" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>583</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="M24" s="1" t="s">
+      <c r="O24" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="P24" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="1">
+        <f>P24*3</f>
+        <v>30</v>
+      </c>
+      <c r="W24" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="25" spans="3:15">
+      <c r="X24" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25">
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="O25" s="8" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="26" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X25" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="26" ht="51" spans="1:25">
       <c r="A26" s="1">
         <v>21</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="12" t="s">
         <v>102</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -20741,44 +21312,62 @@
       <c r="D26" s="1">
         <v>20</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I26" s="1" t="s">
+      <c r="E26" s="20" t="s">
+        <v>612</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M26" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="N26" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="27" spans="3:15">
+        <v>540</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="P26" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="1">
+        <f>P26*5*3</f>
+        <v>150</v>
+      </c>
+      <c r="W26" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y26" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25">
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>591</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="28" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X27" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="Y27" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1" spans="1:25">
       <c r="A28" s="1">
         <v>22</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="11" t="s">
         <v>108</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -20787,65 +21376,101 @@
       <c r="D28" s="1">
         <v>30</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="G28" s="1" t="s">
+      <c r="E28" s="20" t="s">
+        <v>620</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I28" s="1" t="s">
+      <c r="L28" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>594</v>
-      </c>
       <c r="N28" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="29" ht="17.6" customHeight="1" spans="1:15">
+        <v>513</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q28" s="1">
+        <f>P28*D28</f>
+        <v>6</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="Y28" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="29" ht="51" spans="1:25">
       <c r="A29" s="1">
         <v>23</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="12" t="s">
         <v>114</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D29" s="1">
-        <v>40</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>597</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>598</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>625</v>
+      </c>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M29" s="1" t="s">
         <v>517</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>599</v>
-      </c>
-      <c r="O29" s="8" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="30" ht="17.6" customHeight="1" spans="1:15">
+        <v>540</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="Q29" s="1">
+        <f>P29*2*4</f>
+        <v>12</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="Y29" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="30" ht="51" spans="1:25">
       <c r="A30" s="1">
         <v>24</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="13" t="s">
         <v>117</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -20854,97 +21479,132 @@
       <c r="D30" s="1">
         <v>30</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>524</v>
+      <c r="E30" s="22" t="s">
+        <v>630</v>
+      </c>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>566</v>
       </c>
       <c r="M30" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="P30" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="Q30" s="1">
+        <f>P30*5*5</f>
+        <v>20</v>
+      </c>
+      <c r="W30" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="N30" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="O30" s="8" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="31" spans="3:15">
+      <c r="X30" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="Y30" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25">
       <c r="C31" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="32" spans="3:15">
+      <c r="X31" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="Y31" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25">
       <c r="C32" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N32" s="1" t="s">
-        <v>605</v>
-      </c>
-      <c r="O32" s="15" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="33" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X32" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="Y32" s="27" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="33" ht="51" spans="1:25">
       <c r="A33" s="1">
         <v>25</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="12" t="s">
         <v>120</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="1">
-        <v>20</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="G33" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>637</v>
+      </c>
+      <c r="F33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="L33" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M33" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>608</v>
-      </c>
       <c r="N33" s="1" t="s">
-        <v>609</v>
-      </c>
-      <c r="O33" s="15" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="34" spans="3:15">
+        <v>638</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="P33" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="1">
+        <f>P33*4*3</f>
+        <v>12</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="Y33" s="27" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="34" spans="3:25">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>611</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="O34" s="15" t="s">
-        <v>613</v>
+      <c r="W34" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="Y34" s="27" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="35" spans="3:3">
@@ -20952,258 +21612,326 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" ht="17.6" customHeight="1" spans="1:9">
+    <row r="36" ht="34" spans="1:15">
       <c r="A36" s="1">
         <v>26</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="13" t="s">
         <v>123</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D36" s="1">
-        <v>30</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>614</v>
-      </c>
-      <c r="G36" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>645</v>
+      </c>
+      <c r="F36" s="21"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21"/>
+      <c r="K36" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="37" spans="3:15">
+      <c r="L36" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25">
       <c r="C37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="O37" s="8" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="38" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X37" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="38" ht="34" spans="1:25">
       <c r="A38" s="1">
         <v>27</v>
       </c>
-      <c r="B38" s="9" t="s">
-        <v>126</v>
+      <c r="B38" s="15" t="s">
+        <v>646</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D38" s="1">
-        <v>20</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>647</v>
+      </c>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
+      <c r="K38" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M38" s="1" t="s">
         <v>512</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="O38" s="8" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="39" spans="3:15">
+        <v>589</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="Q38" s="1">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="X38" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="Y38" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="39" spans="3:25">
       <c r="C39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N39" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="O39" s="8" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="40" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X39" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="Y39" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="40" ht="51" spans="1:25">
       <c r="A40" s="1">
-        <v>28</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>129</v>
+        <v>27</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>126</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D40" s="1">
-        <v>25</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I40" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>653</v>
+      </c>
+      <c r="F40" s="21"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="21"/>
+      <c r="J40" s="21"/>
+      <c r="K40" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M40" s="1" t="s">
         <v>512</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="O40" s="8" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="41" ht="17.6" customHeight="1" spans="3:15">
+        <v>540</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q40" s="1">
+        <f>2*5</f>
+        <v>10</v>
+      </c>
+      <c r="X40" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="Y40" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="41" ht="17.6" customHeight="1" spans="3:25">
       <c r="C41" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="O41" s="8" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="42" ht="17.6" customHeight="1" spans="1:9">
+      <c r="X41" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="Y41" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="42" ht="51" spans="1:15">
       <c r="A42" s="1">
-        <v>29</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>132</v>
+        <v>28</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>129</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D42" s="1">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I42" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>659</v>
+      </c>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M42" s="1" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="43" spans="3:15">
+      <c r="N42" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="43" spans="3:25">
       <c r="C43" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N43" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="44" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X43" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="44" ht="51" spans="1:25">
       <c r="A44" s="1">
-        <v>30</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>135</v>
+        <v>29</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>132</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D44" s="1">
-        <v>20</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I44" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="F44" s="21"/>
+      <c r="G44" s="21"/>
+      <c r="H44" s="21"/>
+      <c r="I44" s="21"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M44" s="1" t="s">
         <v>512</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="O44" s="8" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="45" spans="3:15">
+        <v>638</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="Y44" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="45" spans="3:25">
       <c r="C45" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N45" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="O45" s="8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="46" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X45" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="46" ht="51" spans="1:25">
       <c r="A46" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D46" s="1">
-        <v>50</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>524</v>
+        <v>40</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>668</v>
+      </c>
+      <c r="F46" s="21"/>
+      <c r="G46" s="21"/>
+      <c r="H46" s="21"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="O46" s="8" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="47" spans="3:15">
+        <v>600</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="Y46" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="47" spans="3:25">
       <c r="C47" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N47" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="O47" s="8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="48" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X47" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="Y47" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="48" ht="17.6" customHeight="1" spans="1:25">
       <c r="A48" s="1">
-        <v>32</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>141</v>
+        <v>31</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>73</v>
@@ -21211,182 +21939,212 @@
       <c r="D48" s="1">
         <v>40</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="G48" s="1" t="s">
+      <c r="E48" s="20" t="s">
+        <v>673</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>524</v>
+      <c r="L48" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="O48" s="8" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="49" spans="3:15">
+        <v>600</v>
+      </c>
+      <c r="X48" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="Y48" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25">
       <c r="C49" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N49" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="O49" s="8" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="50" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X49" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="Y49" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="50" ht="17.6" spans="1:25">
       <c r="A50" s="1">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D50" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="G50" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I50" s="1" t="s">
+      <c r="L50" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M50" s="1" t="s">
         <v>517</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>644</v>
-      </c>
-      <c r="O50" s="8" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="51" spans="3:15">
+        <v>679</v>
+      </c>
+      <c r="Q50" s="1">
+        <f>4*6</f>
+        <v>24</v>
+      </c>
+      <c r="X50" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="Y50" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25">
       <c r="C51" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>646</v>
-      </c>
-      <c r="O51" s="8" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="52" ht="17.6" customHeight="1" spans="1:15">
+      <c r="X51" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="Y51" s="1" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="52" ht="51" spans="1:25">
       <c r="A52" s="1">
+        <v>33</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D52" s="1">
+        <v>40</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>684</v>
+      </c>
+      <c r="F52" s="21"/>
+      <c r="G52" s="21"/>
+      <c r="H52" s="21"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="Y52" s="1" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25">
+      <c r="C53" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="Y53" s="1" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="54" ht="51" spans="1:13">
+      <c r="A54" s="1">
         <v>34</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="B54" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="1">
-        <v>50</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>648</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="O52" s="8" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="53" spans="3:15">
-      <c r="C53" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="O53" s="8" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="54" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A54" s="1">
-        <v>35</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="D54" s="1">
-        <v>40</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="I54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>690</v>
+      </c>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M54" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="55" spans="3:3">
       <c r="C55" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="3:3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" ht="34" spans="1:5">
+      <c r="A56" s="1">
+        <v>35</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>71</v>
+      </c>
       <c r="C56" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="57" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A57" s="1">
-        <v>36</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>152</v>
-      </c>
+      <c r="D56" s="1">
+        <v>60</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="57" spans="3:13">
       <c r="C57" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D57" s="1">
-        <v>30</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="G57" s="1" t="s">
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H57" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>524</v>
+      <c r="L57" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="58" spans="3:3">
@@ -21394,66 +22152,76 @@
         <v>73</v>
       </c>
     </row>
-    <row r="59" spans="3:3">
+    <row r="59" ht="34" spans="1:5">
+      <c r="A59" s="1">
+        <v>36</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>152</v>
+      </c>
       <c r="C59" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="60" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A60" s="1">
-        <v>37</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>155</v>
-      </c>
+      <c r="D59" s="1">
+        <v>60</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13">
       <c r="C60" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" s="1">
-        <v>20</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>656</v>
-      </c>
-      <c r="G60" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I60" s="1" t="s">
+      <c r="L60" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M60" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="61" spans="3:3">
       <c r="C61" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="62" ht="17.6" customHeight="1" spans="1:9">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" ht="51" spans="1:13">
       <c r="A62" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>110</v>
       </c>
       <c r="D62" s="1">
-        <v>30</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>657</v>
-      </c>
-      <c r="G62" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>693</v>
+      </c>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>524</v>
+      <c r="L62" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="63" spans="3:3">
@@ -21461,66 +22229,76 @@
         <v>110</v>
       </c>
     </row>
-    <row r="64" ht="17.6" customHeight="1" spans="1:9">
+    <row r="64" ht="34" spans="1:13">
       <c r="A64" s="1">
-        <v>39</v>
-      </c>
-      <c r="B64" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>158</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="D64" s="1">
-        <v>50</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="G64" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>694</v>
+      </c>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I64" s="1" t="s">
+      <c r="L64" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M64" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="65" spans="3:3">
       <c r="C65" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="66" spans="3:3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" ht="34" spans="1:5">
+      <c r="A66" s="1">
+        <v>39</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>161</v>
+      </c>
       <c r="C66" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="67" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A67" s="1">
-        <v>40</v>
-      </c>
-      <c r="B67" s="11" t="s">
-        <v>164</v>
-      </c>
+      <c r="D66" s="1">
+        <v>60</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="67" spans="3:13">
       <c r="C67" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D67" s="1">
-        <v>40</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="G67" s="1" t="s">
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H67" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>524</v>
+      <c r="L67" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="68" spans="3:3">
@@ -21528,284 +22306,376 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" spans="3:3">
+    <row r="69" ht="51" spans="1:5">
+      <c r="A69" s="1">
+        <v>40</v>
+      </c>
+      <c r="B69" s="13" t="s">
+        <v>164</v>
+      </c>
       <c r="C69" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="70" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A70" s="1">
-        <v>41</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>167</v>
-      </c>
+      <c r="D69" s="1">
+        <v>60</v>
+      </c>
+      <c r="E69" s="20" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="70" spans="3:13">
       <c r="C70" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D70" s="1">
-        <v>30</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I70" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
+      <c r="K70" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M70" s="1" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="71" spans="3:3">
       <c r="C71" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" ht="34" spans="1:13">
+      <c r="A72" s="1">
+        <v>41</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="72" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A72" s="1">
-        <v>42</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="D72" s="1">
-        <v>20</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="G72" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E72" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
+      <c r="K72" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>524</v>
+      <c r="L72" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="73" spans="3:3">
       <c r="C73" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="74" ht="17.6" customHeight="1" spans="1:9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" ht="34" spans="1:13">
       <c r="A74" s="1">
-        <v>43</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>174</v>
+        <v>42</v>
+      </c>
+      <c r="B74" s="13" t="s">
+        <v>170</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>176</v>
+        <v>73</v>
       </c>
       <c r="D74" s="1">
         <v>30</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="I74" s="1" t="s">
+      <c r="E74" s="20" t="s">
+        <v>698</v>
+      </c>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="M74" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="75" spans="3:3">
       <c r="C75" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="76" ht="34" spans="1:22">
+      <c r="A76" s="1">
+        <v>43</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D76" s="1">
+        <v>30</v>
+      </c>
+      <c r="E76" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="F76" s="21"/>
+      <c r="G76" s="21"/>
+      <c r="H76" s="21"/>
+      <c r="I76" s="21"/>
+      <c r="J76" s="21"/>
+      <c r="K76" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="O76" s="11"/>
+      <c r="P76" s="28"/>
+      <c r="Q76" s="28"/>
+      <c r="R76" s="28"/>
+      <c r="S76" s="28"/>
+      <c r="T76" s="28"/>
+      <c r="U76" s="28"/>
+      <c r="V76" s="28"/>
+    </row>
+    <row r="77" ht="17.6" customHeight="1" spans="3:16">
+      <c r="C77" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="76" ht="17.6" customHeight="1" spans="1:12">
-      <c r="A76" s="1">
+      <c r="P77" s="28"/>
+    </row>
+    <row r="78" ht="17.6" customHeight="1" spans="1:22">
+      <c r="A78" s="1">
         <v>44</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="B78" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C78" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D76" s="1">
+      <c r="D78" s="1">
         <v>40</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>663</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="J76" s="17"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="19"/>
-    </row>
-    <row r="77" ht="17.6" customHeight="1" spans="3:11">
-      <c r="C77" s="1" t="s">
+      <c r="E78" s="20" t="s">
+        <v>700</v>
+      </c>
+      <c r="P78" s="28"/>
+      <c r="Q78" s="28"/>
+      <c r="R78" s="28"/>
+      <c r="S78" s="28"/>
+      <c r="T78" s="28"/>
+      <c r="U78" s="28"/>
+      <c r="V78" s="28"/>
+    </row>
+    <row r="79" spans="3:13">
+      <c r="C79" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="K77" s="19"/>
-    </row>
-    <row r="78" ht="17.6" customHeight="1" spans="3:12">
-      <c r="C78" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="K78" s="19"/>
-      <c r="L78" s="19"/>
-    </row>
-    <row r="79" ht="17.6" customHeight="1" spans="1:9">
-      <c r="A79" s="1">
-        <v>45</v>
-      </c>
-      <c r="B79" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D79" s="1">
-        <v>100</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="G79" s="1" t="s">
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
+      <c r="H79" s="21"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="21"/>
+      <c r="K79" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="H79" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="I79" s="1" t="s">
+      <c r="L79" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M79" s="1" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="80" spans="3:3">
       <c r="C80" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="81" ht="17.6" customHeight="1" spans="3:11">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="81" ht="17.6" customHeight="1" spans="1:16">
+      <c r="A81" s="1">
+        <v>45</v>
+      </c>
+      <c r="B81" s="12" t="s">
+        <v>181</v>
+      </c>
       <c r="C81" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="K81" s="19"/>
-    </row>
-    <row r="82" ht="17.6" customHeight="1" spans="3:12">
+      <c r="D81" s="1">
+        <v>110</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>701</v>
+      </c>
+      <c r="P81" s="28"/>
+    </row>
+    <row r="82" ht="17.6" customHeight="1" spans="3:22">
       <c r="C82" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O82" s="28"/>
+      <c r="P82" s="28"/>
+      <c r="Q82" s="28"/>
+      <c r="R82" s="28"/>
+      <c r="S82" s="28"/>
+      <c r="T82" s="28"/>
+      <c r="U82" s="28"/>
+      <c r="V82" s="28"/>
+    </row>
+    <row r="83" ht="17.6" customHeight="1" spans="3:22">
+      <c r="C83" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O83" s="28"/>
+      <c r="P83" s="28"/>
+      <c r="Q83" s="28"/>
+      <c r="R83" s="28"/>
+      <c r="S83" s="28"/>
+      <c r="T83" s="28"/>
+      <c r="U83" s="28"/>
+      <c r="V83" s="28"/>
+    </row>
+    <row r="84" ht="17.6" spans="3:22">
+      <c r="C84" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J82" s="19"/>
-      <c r="K82" s="19"/>
-      <c r="L82" s="19"/>
-    </row>
-    <row r="83" ht="17.6" customHeight="1" spans="3:12">
-      <c r="C83" s="1" t="s">
+      <c r="F84" s="21"/>
+      <c r="G84" s="21"/>
+      <c r="H84" s="21"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="21"/>
+      <c r="K84" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="O84" s="28"/>
+      <c r="P84" s="28"/>
+      <c r="Q84" s="28"/>
+      <c r="R84" s="28"/>
+      <c r="S84" s="28"/>
+      <c r="T84" s="28"/>
+      <c r="U84" s="28"/>
+      <c r="V84" s="28"/>
+    </row>
+    <row r="85" ht="17.6" customHeight="1" spans="3:22">
+      <c r="C85" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J83" s="19"/>
-      <c r="K83" s="19"/>
-      <c r="L83" s="19"/>
-    </row>
-    <row r="84" ht="17.6" customHeight="1" spans="1:12">
-      <c r="A84" s="1">
+      <c r="O85" s="28"/>
+      <c r="P85" s="28"/>
+      <c r="Q85" s="28"/>
+      <c r="R85" s="28"/>
+      <c r="S85" s="28"/>
+      <c r="T85" s="28"/>
+      <c r="U85" s="28"/>
+      <c r="V85" s="28"/>
+    </row>
+    <row r="86" ht="17.6" customHeight="1" spans="1:22">
+      <c r="A86" s="1">
         <v>46</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B86" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D84" s="1">
-        <v>80</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="J84" s="19"/>
-      <c r="K84" s="19"/>
-      <c r="L84" s="19"/>
-    </row>
-    <row r="85" ht="17.6" customHeight="1" spans="3:12">
-      <c r="C85" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J85" s="19"/>
-      <c r="K85" s="19"/>
-      <c r="L85" s="19"/>
-    </row>
-    <row r="86" ht="17.6" customHeight="1" spans="3:12">
       <c r="C86" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J86" s="19"/>
-      <c r="K86" s="19"/>
-      <c r="L86" s="19"/>
-    </row>
-    <row r="87" ht="17.6" customHeight="1" spans="1:12">
-      <c r="A87" s="1">
-        <v>47</v>
-      </c>
-      <c r="B87" s="16" t="s">
-        <v>188</v>
-      </c>
+      <c r="D86" s="1">
+        <v>90</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>702</v>
+      </c>
+      <c r="O86" s="28"/>
+      <c r="P86" s="28"/>
+      <c r="Q86" s="28"/>
+      <c r="R86" s="28"/>
+      <c r="S86" s="28"/>
+      <c r="T86" s="28"/>
+      <c r="U86" s="28"/>
+      <c r="V86" s="28"/>
+    </row>
+    <row r="87" ht="17.6" customHeight="1" spans="3:22">
       <c r="C87" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D87" s="1">
-        <v>140</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>666</v>
-      </c>
-      <c r="G87" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="K87" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="I87" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="K87" s="19"/>
-      <c r="L87" s="19"/>
+      <c r="L87" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="P87" s="28"/>
+      <c r="Q87" s="28"/>
+      <c r="R87" s="28"/>
+      <c r="S87" s="28"/>
+      <c r="T87" s="28"/>
+      <c r="U87" s="28"/>
+      <c r="V87" s="28"/>
     </row>
     <row r="88" spans="3:3">
       <c r="C88" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="89" ht="17.6" spans="1:5">
+      <c r="A89" s="1">
+        <v>47</v>
+      </c>
+      <c r="B89" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="89" spans="3:3">
-      <c r="C89" s="1" t="s">
-        <v>191</v>
+      <c r="D89" s="1">
+        <v>160</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="90" spans="3:3">
       <c r="C90" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="91" spans="3:3">
+      <c r="C91" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="92" spans="3:3">
+      <c r="C92" s="1" t="s">
         <v>191</v>
       </c>
     </row>
@@ -21831,16 +22701,16 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -21870,20 +22740,18 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>668</v>
+        <v>704</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>669</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="V5" s="6"/>
       <c r="W5" s="6"/>
@@ -21908,45 +22776,51 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>671</v>
+        <v>707</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>671</v>
+        <v>707</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="3" t="s">
-        <v>673</v>
+        <v>709</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="6"/>
+      <c r="Y6" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="7">
+        <v>3</v>
+      </c>
+      <c r="AB6" s="8"/>
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
       <c r="AI6" s="6"/>
-      <c r="AJ6" s="7"/>
-      <c r="AK6" s="7"/>
-      <c r="AL6" s="7"/>
+      <c r="AJ6" s="9"/>
+      <c r="AK6" s="9"/>
+      <c r="AL6" s="9"/>
       <c r="AM6" s="6"/>
       <c r="AN6" s="6"/>
       <c r="AO6" s="6"/>
@@ -21955,90 +22829,102 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>674</v>
+        <v>706</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>672</v>
+        <v>708</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="3" t="s">
-        <v>673</v>
+        <v>709</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="V7" s="6"/>
       <c r="W7" s="6"/>
       <c r="X7" s="6"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="6"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="6"/>
+      <c r="Y7" s="7">
+        <v>4</v>
+      </c>
+      <c r="Z7" s="8">
+        <v>5</v>
+      </c>
+      <c r="AA7" s="7">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="8"/>
       <c r="AC7" s="6"/>
       <c r="AD7" s="6"/>
       <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
       <c r="AI7" s="6"/>
-      <c r="AJ7" s="7"/>
+      <c r="AJ7" s="9"/>
       <c r="AK7" s="6"/>
-      <c r="AL7" s="7"/>
+      <c r="AL7" s="9"/>
       <c r="AM7" s="6"/>
       <c r="AN7" s="6"/>
       <c r="AO7" s="6"/>
     </row>
     <row r="8" customHeight="1" spans="8:41">
       <c r="H8" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>673</v>
+        <v>709</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="3" t="s">
-        <v>673</v>
+        <v>709</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>670</v>
+        <v>706</v>
       </c>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
       <c r="X8" s="6"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="6"/>
+      <c r="Y8" s="7">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="7">
+        <v>9</v>
+      </c>
+      <c r="AB8" s="8"/>
       <c r="AC8" s="6"/>
       <c r="AD8" s="6"/>
       <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
       <c r="AI8" s="6"/>
-      <c r="AJ8" s="7"/>
-      <c r="AK8" s="7"/>
-      <c r="AL8" s="7"/>
+      <c r="AJ8" s="9"/>
+      <c r="AK8" s="9"/>
+      <c r="AL8" s="9"/>
       <c r="AM8" s="6"/>
       <c r="AN8" s="6"/>
       <c r="AO8" s="6"/>
@@ -22048,37 +22934,27 @@
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
-      <c r="L9" s="3" t="s">
-        <v>669</v>
-      </c>
+      <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>669</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
-      <c r="Y9" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="Z9" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="AA9" s="6" t="s">
-        <v>675</v>
-      </c>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
@@ -22086,13 +22962,13 @@
       <c r="AH9" s="6"/>
       <c r="AI9" s="6"/>
       <c r="AJ9" s="2" t="s">
-        <v>676</v>
+        <v>710</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>676</v>
+        <v>710</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>676</v>
+        <v>710</v>
       </c>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
@@ -22105,16 +22981,16 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -22131,13 +23007,13 @@
       <c r="AH10" s="6"/>
       <c r="AI10" s="6"/>
       <c r="AJ10" s="2" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
@@ -22150,10 +23026,10 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -22172,13 +23048,13 @@
       <c r="AH11" s="6"/>
       <c r="AI11" s="6"/>
       <c r="AJ11" s="2" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
@@ -22191,10 +23067,10 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="727">
   <si>
     <t>##var</t>
   </si>
@@ -987,7 +987,7 @@
     <t>ss_copy_cat_skill_v3</t>
   </si>
   <si>
-    <t>ss_trigger_transfer_n1</t>
+    <t>ss_extra_transfer_n1</t>
   </si>
   <si>
     <t>desc</t>
@@ -2311,6 +2311,9 @@
   </si>
   <si>
     <t>下侧所有</t>
+  </si>
+  <si>
+    <t>ExtraSweetTransfer</t>
   </si>
 </sst>
 </file>
@@ -20559,7 +20562,7 @@
         <v>425</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>499</v>
+        <v>726</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>472</v>
@@ -20568,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="L77" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" s="1" t="s">
         <v>25</v>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -17,7 +17,7 @@
     <sheet name="定义" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">sub_skill!$C$1:$C$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">sub_skill!$C$1:$C$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="727">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="833">
   <si>
     <t>##var</t>
   </si>
@@ -2314,6 +2314,324 @@
   </si>
   <si>
     <t>ExtraSweetTransfer</t>
+  </si>
+  <si>
+    <t>本技能独占的有序子技能ID列表（| 分隔，命名为 skillId_序号）</t>
+  </si>
+  <si>
+    <t>sk_cookie_1</t>
+  </si>
+  <si>
+    <t>sk_macaron_1|sk_macaron_2</t>
+  </si>
+  <si>
+    <t>sk_macaron_1</t>
+  </si>
+  <si>
+    <t>sk_macaron_2</t>
+  </si>
+  <si>
+    <t>sk_pudding_1</t>
+  </si>
+  <si>
+    <t>sk_puff_1</t>
+  </si>
+  <si>
+    <t>sk_eggtart_1</t>
+  </si>
+  <si>
+    <t>sk_mochi_1</t>
+  </si>
+  <si>
+    <t>sk_daifuku_1</t>
+  </si>
+  <si>
+    <t>sk_choco_candy_1</t>
+  </si>
+  <si>
+    <t>sk_jelly_1</t>
+  </si>
+  <si>
+    <t>sk_cream_cell_1</t>
+  </si>
+  <si>
+    <t>sk_sugarbean_1|sk_sugarbean_2</t>
+  </si>
+  <si>
+    <t>sk_sugarbean_1</t>
+  </si>
+  <si>
+    <t>sk_sugarbean_2</t>
+  </si>
+  <si>
+    <t>sk_gold_choco_1</t>
+  </si>
+  <si>
+    <t>sk_milk_slice_1</t>
+  </si>
+  <si>
+    <t>sk_sundae_1|sk_sundae_2</t>
+  </si>
+  <si>
+    <t>sk_sundae_1</t>
+  </si>
+  <si>
+    <t>sk_sundae_2</t>
+  </si>
+  <si>
+    <t>sk_cone_1</t>
+  </si>
+  <si>
+    <t>sk_lollipop_1|sk_lollipop_2</t>
+  </si>
+  <si>
+    <t>sk_lollipop_1</t>
+  </si>
+  <si>
+    <t>sk_lollipop_2</t>
+  </si>
+  <si>
+    <t>sk_gummy_1|sk_gummy_2</t>
+  </si>
+  <si>
+    <t>sk_gummy_1</t>
+  </si>
+  <si>
+    <t>sk_gummy_2</t>
+  </si>
+  <si>
+    <t>sk_cupcake_1|sk_cupcake_2</t>
+  </si>
+  <si>
+    <t>sk_cupcake_1</t>
+  </si>
+  <si>
+    <t>sk_cupcake_2</t>
+  </si>
+  <si>
+    <t>sk_mousse_1|sk_mousse_2</t>
+  </si>
+  <si>
+    <t>sk_mousse_1</t>
+  </si>
+  <si>
+    <t>sk_mousse_2</t>
+  </si>
+  <si>
+    <t>sk_toffee_1|sk_toffee_2</t>
+  </si>
+  <si>
+    <t>sk_toffee_1</t>
+  </si>
+  <si>
+    <t>sk_toffee_2</t>
+  </si>
+  <si>
+    <t>sk_nougat_1|sk_nougat_2</t>
+  </si>
+  <si>
+    <t>sk_nougat_1</t>
+  </si>
+  <si>
+    <t>sk_nougat_2</t>
+  </si>
+  <si>
+    <t>sk_eggroll_1|sk_eggroll_2</t>
+  </si>
+  <si>
+    <t>sk_eggroll_1</t>
+  </si>
+  <si>
+    <t>sk_eggroll_2</t>
+  </si>
+  <si>
+    <t>sk_choco_bar_1|sk_choco_bar_2</t>
+  </si>
+  <si>
+    <t>sk_choco_bar_1</t>
+  </si>
+  <si>
+    <t>sk_choco_bar_2</t>
+  </si>
+  <si>
+    <t>sk_eclair_1|sk_eclair_2</t>
+  </si>
+  <si>
+    <t>sk_eclair_1</t>
+  </si>
+  <si>
+    <t>sk_eclair_2</t>
+  </si>
+  <si>
+    <t>sk_tanghulu_1|sk_tanghulu_2</t>
+  </si>
+  <si>
+    <t>sk_tanghulu_1</t>
+  </si>
+  <si>
+    <t>sk_tanghulu_2</t>
+  </si>
+  <si>
+    <t>sk_souffle_1</t>
+  </si>
+  <si>
+    <t>sk_taosu_1</t>
+  </si>
+  <si>
+    <t>sk_mooncake_1|sk_mooncake_2</t>
+  </si>
+  <si>
+    <t>sk_mooncake_1</t>
+  </si>
+  <si>
+    <t>sk_mooncake_2</t>
+  </si>
+  <si>
+    <t>sk_waffle_1|sk_waffle_2</t>
+  </si>
+  <si>
+    <t>sk_waffle_1</t>
+  </si>
+  <si>
+    <t>sk_waffle_2</t>
+  </si>
+  <si>
+    <t>sk_dorayaki_1|sk_dorayaki_2</t>
+  </si>
+  <si>
+    <t>sk_dorayaki_1</t>
+  </si>
+  <si>
+    <t>sk_dorayaki_2</t>
+  </si>
+  <si>
+    <t>sk_cream_cake_1|sk_cream_cake_2</t>
+  </si>
+  <si>
+    <t>sk_cream_cake_1</t>
+  </si>
+  <si>
+    <t>sk_cream_cake_2</t>
+  </si>
+  <si>
+    <t>sk_donut_1|sk_donut_2</t>
+  </si>
+  <si>
+    <t>sk_donut_1</t>
+  </si>
+  <si>
+    <t>sk_donut_2</t>
+  </si>
+  <si>
+    <t>sk_pengtang_1|sk_pengtang_2</t>
+  </si>
+  <si>
+    <t>sk_pengtang_1</t>
+  </si>
+  <si>
+    <t>sk_pengtang_2</t>
+  </si>
+  <si>
+    <t>sk_parfait_1|sk_parfait_2</t>
+  </si>
+  <si>
+    <t>sk_parfait_1</t>
+  </si>
+  <si>
+    <t>sk_parfait_2</t>
+  </si>
+  <si>
+    <t>sk_sundae_big_1|sk_sundae_big_2</t>
+  </si>
+  <si>
+    <t>sk_sundae_big_1</t>
+  </si>
+  <si>
+    <t>sk_sundae_big_2</t>
+  </si>
+  <si>
+    <t>sk_swiss_roll_1|sk_swiss_roll_2</t>
+  </si>
+  <si>
+    <t>sk_swiss_roll_1</t>
+  </si>
+  <si>
+    <t>sk_swiss_roll_2</t>
+  </si>
+  <si>
+    <t>sk_mango_sago_1|sk_mango_sago_2</t>
+  </si>
+  <si>
+    <t>sk_mango_sago_1</t>
+  </si>
+  <si>
+    <t>sk_mango_sago_2</t>
+  </si>
+  <si>
+    <t>sk_chiffon_1|sk_chiffon_2</t>
+  </si>
+  <si>
+    <t>sk_chiffon_1</t>
+  </si>
+  <si>
+    <t>sk_chiffon_2</t>
+  </si>
+  <si>
+    <t>sk_apple_pie_1</t>
+  </si>
+  <si>
+    <t>sk_fruit_cake_1|sk_fruit_cake_2</t>
+  </si>
+  <si>
+    <t>sk_fruit_cake_1</t>
+  </si>
+  <si>
+    <t>sk_fruit_cake_2</t>
+  </si>
+  <si>
+    <t>sk_chocolate_1</t>
+  </si>
+  <si>
+    <t>sk_croissant_1</t>
+  </si>
+  <si>
+    <t>sk_palmier_1|sk_palmier_2</t>
+  </si>
+  <si>
+    <t>sk_palmier_1</t>
+  </si>
+  <si>
+    <t>sk_palmier_2</t>
+  </si>
+  <si>
+    <t>sk_candycane_1|sk_candycane_2</t>
+  </si>
+  <si>
+    <t>sk_candycane_1</t>
+  </si>
+  <si>
+    <t>sk_candycane_2</t>
+  </si>
+  <si>
+    <t>sk_big_lollipop_1</t>
+  </si>
+  <si>
+    <t>sk_marshmallow_1|sk_marshmallow_2</t>
+  </si>
+  <si>
+    <t>sk_marshmallow_1</t>
+  </si>
+  <si>
+    <t>sk_marshmallow_2</t>
+  </si>
+  <si>
+    <t>sk_double_cake_1</t>
+  </si>
+  <si>
+    <t>sk_maple_sugar_1</t>
+  </si>
+  <si>
+    <t>子技能ID（skillId_序号；每次关联独立一行，不复用）</t>
   </si>
 </sst>
 </file>
@@ -15374,7 +15692,7 @@
         <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>220</v>
+        <v>727</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -15393,10 +15711,10 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>221</v>
+        <v>728</v>
       </c>
       <c r="G4" t="s">
-        <v>221</v>
+        <v>728</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
@@ -15410,13 +15728,13 @@
         <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>222</v>
+        <v>729</v>
       </c>
       <c r="G5" t="s">
-        <v>223</v>
+        <v>730</v>
       </c>
       <c r="H5" t="s">
-        <v>224</v>
+        <v>731</v>
       </c>
       <c r="J5" t="s">
         <v>29</v>
@@ -15430,10 +15748,10 @@
         <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>732</v>
       </c>
       <c r="G6" t="s">
-        <v>225</v>
+        <v>732</v>
       </c>
       <c r="J6" t="s">
         <v>32</v>
@@ -15447,10 +15765,10 @@
         <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>733</v>
       </c>
       <c r="G7" t="s">
-        <v>226</v>
+        <v>733</v>
       </c>
       <c r="J7" t="s">
         <v>35</v>
@@ -15464,10 +15782,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>227</v>
+        <v>734</v>
       </c>
       <c r="G8" t="s">
-        <v>227</v>
+        <v>734</v>
       </c>
       <c r="J8" t="s">
         <v>38</v>
@@ -15481,10 +15799,10 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>228</v>
+        <v>735</v>
       </c>
       <c r="G9" t="s">
-        <v>228</v>
+        <v>735</v>
       </c>
       <c r="J9" t="s">
         <v>41</v>
@@ -15498,10 +15816,10 @@
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>229</v>
+        <v>736</v>
       </c>
       <c r="G10" t="s">
-        <v>229</v>
+        <v>736</v>
       </c>
       <c r="J10" t="s">
         <v>44</v>
@@ -15515,10 +15833,10 @@
         <v>49</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>737</v>
       </c>
       <c r="G11" t="s">
-        <v>230</v>
+        <v>737</v>
       </c>
       <c r="J11" t="s">
         <v>47</v>
@@ -15532,10 +15850,10 @@
         <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>738</v>
       </c>
       <c r="G12" t="s">
-        <v>231</v>
+        <v>738</v>
       </c>
       <c r="J12" t="s">
         <v>50</v>
@@ -15549,10 +15867,10 @@
         <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>232</v>
+        <v>739</v>
       </c>
       <c r="G13" t="s">
-        <v>232</v>
+        <v>739</v>
       </c>
       <c r="J13" t="s">
         <v>54</v>
@@ -15566,13 +15884,13 @@
         <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>233</v>
+        <v>740</v>
       </c>
       <c r="G14" t="s">
-        <v>234</v>
+        <v>741</v>
       </c>
       <c r="H14" t="s">
-        <v>235</v>
+        <v>742</v>
       </c>
       <c r="J14" t="s">
         <v>58</v>
@@ -15586,10 +15904,10 @@
         <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>236</v>
+        <v>743</v>
       </c>
       <c r="G15" t="s">
-        <v>236</v>
+        <v>743</v>
       </c>
       <c r="J15" t="s">
         <v>62</v>
@@ -15603,10 +15921,10 @@
         <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>237</v>
+        <v>744</v>
       </c>
       <c r="G16" t="s">
-        <v>237</v>
+        <v>744</v>
       </c>
       <c r="J16" t="s">
         <v>66</v>
@@ -15620,13 +15938,13 @@
         <v>72</v>
       </c>
       <c r="C17" t="s">
-        <v>238</v>
+        <v>745</v>
       </c>
       <c r="G17" t="s">
-        <v>239</v>
+        <v>746</v>
       </c>
       <c r="H17" t="s">
-        <v>240</v>
+        <v>747</v>
       </c>
       <c r="J17" t="s">
         <v>70</v>
@@ -15640,10 +15958,10 @@
         <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>241</v>
+        <v>748</v>
       </c>
       <c r="G18" t="s">
-        <v>241</v>
+        <v>748</v>
       </c>
       <c r="J18" t="s">
         <v>74</v>
@@ -15657,13 +15975,13 @@
         <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>242</v>
+        <v>749</v>
       </c>
       <c r="G19" t="s">
-        <v>243</v>
+        <v>750</v>
       </c>
       <c r="H19" t="s">
-        <v>244</v>
+        <v>751</v>
       </c>
       <c r="J19" t="s">
         <v>77</v>
@@ -15677,13 +15995,13 @@
         <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>245</v>
+        <v>752</v>
       </c>
       <c r="G20" t="s">
-        <v>246</v>
+        <v>753</v>
       </c>
       <c r="H20" t="s">
-        <v>247</v>
+        <v>754</v>
       </c>
       <c r="J20" t="s">
         <v>80</v>
@@ -15697,13 +16015,13 @@
         <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>248</v>
+        <v>755</v>
       </c>
       <c r="G21" t="s">
-        <v>249</v>
+        <v>756</v>
       </c>
       <c r="H21" t="s">
-        <v>250</v>
+        <v>757</v>
       </c>
       <c r="J21" t="s">
         <v>83</v>
@@ -15717,13 +16035,13 @@
         <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>252</v>
+        <v>758</v>
       </c>
       <c r="G22" t="s">
-        <v>253</v>
+        <v>759</v>
       </c>
       <c r="H22" t="s">
-        <v>234</v>
+        <v>760</v>
       </c>
       <c r="J22" t="s">
         <v>87</v>
@@ -15737,13 +16055,13 @@
         <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>761</v>
       </c>
       <c r="G23" t="s">
-        <v>255</v>
+        <v>762</v>
       </c>
       <c r="H23" t="s">
-        <v>256</v>
+        <v>763</v>
       </c>
       <c r="J23" t="s">
         <v>94</v>
@@ -15757,13 +16075,13 @@
         <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>257</v>
+        <v>764</v>
       </c>
       <c r="G24" t="s">
-        <v>234</v>
+        <v>765</v>
       </c>
       <c r="H24" t="s">
-        <v>247</v>
+        <v>766</v>
       </c>
       <c r="J24" t="s">
         <v>101</v>
@@ -15777,13 +16095,13 @@
         <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>258</v>
+        <v>767</v>
       </c>
       <c r="G25" t="s">
-        <v>259</v>
+        <v>768</v>
       </c>
       <c r="H25" t="s">
-        <v>260</v>
+        <v>769</v>
       </c>
       <c r="J25" t="s">
         <v>107</v>
@@ -15797,13 +16115,13 @@
         <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>261</v>
+        <v>770</v>
       </c>
       <c r="G26" t="s">
-        <v>262</v>
+        <v>771</v>
       </c>
       <c r="H26" t="s">
-        <v>263</v>
+        <v>772</v>
       </c>
       <c r="J26" t="s">
         <v>113</v>
@@ -15817,13 +16135,13 @@
         <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>264</v>
+        <v>773</v>
       </c>
       <c r="G27" t="s">
-        <v>265</v>
+        <v>774</v>
       </c>
       <c r="H27" t="s">
-        <v>266</v>
+        <v>775</v>
       </c>
       <c r="J27" t="s">
         <v>116</v>
@@ -15837,13 +16155,13 @@
         <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>267</v>
+        <v>776</v>
       </c>
       <c r="G28" t="s">
-        <v>268</v>
+        <v>777</v>
       </c>
       <c r="H28" t="s">
-        <v>269</v>
+        <v>778</v>
       </c>
       <c r="J28" t="s">
         <v>119</v>
@@ -15857,10 +16175,10 @@
         <v>124</v>
       </c>
       <c r="C29" t="s">
-        <v>270</v>
+        <v>779</v>
       </c>
       <c r="G29" t="s">
-        <v>270</v>
+        <v>779</v>
       </c>
       <c r="J29" t="s">
         <v>122</v>
@@ -15874,10 +16192,10 @@
         <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>271</v>
+        <v>780</v>
       </c>
       <c r="G30" t="s">
-        <v>271</v>
+        <v>780</v>
       </c>
       <c r="J30" t="s">
         <v>128</v>
@@ -15891,13 +16209,13 @@
         <v>133</v>
       </c>
       <c r="C31" t="s">
-        <v>272</v>
+        <v>781</v>
       </c>
       <c r="G31" t="s">
-        <v>249</v>
+        <v>782</v>
       </c>
       <c r="H31" t="s">
-        <v>273</v>
+        <v>783</v>
       </c>
       <c r="J31" t="s">
         <v>131</v>
@@ -15911,13 +16229,13 @@
         <v>136</v>
       </c>
       <c r="C32" t="s">
-        <v>274</v>
+        <v>784</v>
       </c>
       <c r="G32" t="s">
-        <v>275</v>
+        <v>785</v>
       </c>
       <c r="H32" t="s">
-        <v>276</v>
+        <v>786</v>
       </c>
       <c r="J32" t="s">
         <v>134</v>
@@ -15931,13 +16249,13 @@
         <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>277</v>
+        <v>787</v>
       </c>
       <c r="G33" t="s">
-        <v>278</v>
+        <v>788</v>
       </c>
       <c r="H33" t="s">
-        <v>279</v>
+        <v>789</v>
       </c>
       <c r="J33" t="s">
         <v>137</v>
@@ -15951,13 +16269,13 @@
         <v>142</v>
       </c>
       <c r="C34" t="s">
-        <v>280</v>
+        <v>790</v>
       </c>
       <c r="G34" t="s">
-        <v>255</v>
+        <v>791</v>
       </c>
       <c r="H34" t="s">
-        <v>281</v>
+        <v>792</v>
       </c>
       <c r="J34" t="s">
         <v>140</v>
@@ -15971,13 +16289,13 @@
         <v>145</v>
       </c>
       <c r="C35" t="s">
-        <v>282</v>
+        <v>793</v>
       </c>
       <c r="G35" t="s">
-        <v>283</v>
+        <v>794</v>
       </c>
       <c r="H35" t="s">
-        <v>266</v>
+        <v>795</v>
       </c>
       <c r="J35" t="s">
         <v>143</v>
@@ -15991,13 +16309,13 @@
         <v>148</v>
       </c>
       <c r="C36" t="s">
-        <v>284</v>
+        <v>796</v>
       </c>
       <c r="G36" t="s">
-        <v>285</v>
+        <v>797</v>
       </c>
       <c r="H36" t="s">
-        <v>286</v>
+        <v>798</v>
       </c>
       <c r="J36" t="s">
         <v>146</v>
@@ -16011,13 +16329,13 @@
         <v>151</v>
       </c>
       <c r="C37" t="s">
-        <v>287</v>
+        <v>799</v>
       </c>
       <c r="G37" t="s">
-        <v>246</v>
+        <v>800</v>
       </c>
       <c r="H37" t="s">
-        <v>288</v>
+        <v>801</v>
       </c>
       <c r="J37" t="s">
         <v>149</v>
@@ -16031,13 +16349,13 @@
         <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>289</v>
+        <v>802</v>
       </c>
       <c r="G38" t="s">
-        <v>290</v>
+        <v>803</v>
       </c>
       <c r="H38" t="s">
-        <v>273</v>
+        <v>804</v>
       </c>
       <c r="J38" t="s">
         <v>152</v>
@@ -16051,13 +16369,13 @@
         <v>156</v>
       </c>
       <c r="C39" t="s">
-        <v>291</v>
+        <v>805</v>
       </c>
       <c r="G39" t="s">
-        <v>292</v>
+        <v>806</v>
       </c>
       <c r="H39" t="s">
-        <v>293</v>
+        <v>807</v>
       </c>
       <c r="J39" t="s">
         <v>154</v>
@@ -16071,13 +16389,13 @@
         <v>159</v>
       </c>
       <c r="C40" t="s">
-        <v>294</v>
+        <v>808</v>
       </c>
       <c r="G40" t="s">
-        <v>295</v>
+        <v>809</v>
       </c>
       <c r="H40" t="s">
-        <v>296</v>
+        <v>810</v>
       </c>
       <c r="J40" t="s">
         <v>157</v>
@@ -16091,13 +16409,13 @@
         <v>162</v>
       </c>
       <c r="C41" t="s">
-        <v>297</v>
+        <v>811</v>
       </c>
       <c r="G41" t="s">
-        <v>266</v>
+        <v>812</v>
       </c>
       <c r="H41" t="s">
-        <v>298</v>
+        <v>813</v>
       </c>
       <c r="J41" t="s">
         <v>299</v>
@@ -16111,10 +16429,10 @@
         <v>165</v>
       </c>
       <c r="C42" t="s">
-        <v>300</v>
+        <v>814</v>
       </c>
       <c r="G42" t="s">
-        <v>300</v>
+        <v>814</v>
       </c>
       <c r="J42" t="s">
         <v>163</v>
@@ -16128,13 +16446,13 @@
         <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>301</v>
+        <v>815</v>
       </c>
       <c r="G43" t="s">
-        <v>302</v>
+        <v>816</v>
       </c>
       <c r="H43" t="s">
-        <v>303</v>
+        <v>817</v>
       </c>
       <c r="J43" t="s">
         <v>166</v>
@@ -16148,10 +16466,10 @@
         <v>171</v>
       </c>
       <c r="C44" t="s">
-        <v>304</v>
+        <v>818</v>
       </c>
       <c r="G44" t="s">
-        <v>304</v>
+        <v>818</v>
       </c>
       <c r="J44" t="s">
         <v>169</v>
@@ -16165,10 +16483,10 @@
         <v>174</v>
       </c>
       <c r="C45" t="s">
-        <v>305</v>
+        <v>819</v>
       </c>
       <c r="G45" t="s">
-        <v>305</v>
+        <v>819</v>
       </c>
       <c r="J45" t="s">
         <v>172</v>
@@ -16182,13 +16500,13 @@
         <v>178</v>
       </c>
       <c r="C46" t="s">
-        <v>306</v>
+        <v>820</v>
       </c>
       <c r="G46" t="s">
-        <v>307</v>
+        <v>821</v>
       </c>
       <c r="H46" t="s">
-        <v>260</v>
+        <v>822</v>
       </c>
       <c r="J46" t="s">
         <v>176</v>
@@ -16202,13 +16520,13 @@
         <v>182</v>
       </c>
       <c r="C47" t="s">
-        <v>308</v>
+        <v>823</v>
       </c>
       <c r="G47" t="s">
-        <v>309</v>
+        <v>824</v>
       </c>
       <c r="H47" t="s">
-        <v>310</v>
+        <v>825</v>
       </c>
       <c r="J47" t="s">
         <v>180</v>
@@ -16222,10 +16540,10 @@
         <v>185</v>
       </c>
       <c r="C48" t="s">
-        <v>311</v>
+        <v>826</v>
       </c>
       <c r="G48" t="s">
-        <v>311</v>
+        <v>826</v>
       </c>
       <c r="J48" t="s">
         <v>183</v>
@@ -16239,13 +16557,13 @@
         <v>189</v>
       </c>
       <c r="C49" t="s">
-        <v>312</v>
+        <v>827</v>
       </c>
       <c r="G49" t="s">
-        <v>313</v>
+        <v>828</v>
       </c>
       <c r="H49" t="s">
-        <v>314</v>
+        <v>829</v>
       </c>
       <c r="J49" t="s">
         <v>187</v>
@@ -16259,10 +16577,10 @@
         <v>192</v>
       </c>
       <c r="C50" t="s">
-        <v>315</v>
+        <v>830</v>
       </c>
       <c r="G50" t="s">
-        <v>315</v>
+        <v>830</v>
       </c>
       <c r="J50" t="s">
         <v>190</v>
@@ -16276,7 +16594,10 @@
         <v>127</v>
       </c>
       <c r="C51" t="s">
-        <v>316</v>
+        <v>831</v>
+      </c>
+      <c r="G51" t="s">
+        <v>831</v>
       </c>
     </row>
   </sheetData>
@@ -16679,7 +17000,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T77"/>
+  <dimension ref="A1:T79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -16761,7 +17082,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>393</v>
+        <v>832</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>394</v>
@@ -16870,7 +17191,7 @@
     </row>
     <row r="4" ht="34" spans="2:20">
       <c r="B4" s="1" t="s">
-        <v>221</v>
+        <v>728</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>415</v>
@@ -16909,17 +17230,17 @@
         <v>421</v>
       </c>
       <c r="S4" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B4,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>曲奇</v>
+        <f>IFERROR(VLOOKUP(B4,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T4" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B4,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B4,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" ht="34" spans="2:20">
       <c r="B5" s="1" t="s">
-        <v>223</v>
+        <v>730</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>415</v>
@@ -16958,17 +17279,17 @@
         <v>426</v>
       </c>
       <c r="S5" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B5,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>马卡龙</v>
+        <f>IFERROR(VLOOKUP(B5,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T5" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B5,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B5,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="6" spans="2:20">
       <c r="B6" s="1" t="s">
-        <v>224</v>
+        <v>731</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>415</v>
@@ -17010,17 +17331,17 @@
         <v>431</v>
       </c>
       <c r="S6" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B6,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B6,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T6" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B6,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>马卡龙</v>
+        <f>IFERROR(VLOOKUP(B6,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="34" spans="2:20">
       <c r="B7" s="1" t="s">
-        <v>225</v>
+        <v>732</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>415</v>
@@ -17059,17 +17380,17 @@
         <v>433</v>
       </c>
       <c r="S7" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B7,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>布丁</v>
+        <f>IFERROR(VLOOKUP(B7,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T7" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B7,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B7,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="34" spans="2:20">
       <c r="B8" s="1" t="s">
-        <v>226</v>
+        <v>733</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>415</v>
@@ -17111,17 +17432,17 @@
         <v>437</v>
       </c>
       <c r="S8" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B8,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>泡芙</v>
+        <f>IFERROR(VLOOKUP(B8,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T8" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B8,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B8,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="34" spans="2:20">
       <c r="B9" s="1" t="s">
-        <v>227</v>
+        <v>734</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>415</v>
@@ -17160,17 +17481,17 @@
         <v>439</v>
       </c>
       <c r="S9" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B9,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>蛋挞</v>
+        <f>IFERROR(VLOOKUP(B9,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T9" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B9,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B9,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="34" spans="2:20">
       <c r="B10" s="1" t="s">
-        <v>228</v>
+        <v>735</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>415</v>
@@ -17209,17 +17530,17 @@
         <v>441</v>
       </c>
       <c r="S10" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B10,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>麻薯</v>
+        <f>IFERROR(VLOOKUP(B10,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T10" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B10,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B10,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="34" spans="2:20">
       <c r="B11" s="1" t="s">
-        <v>229</v>
+        <v>736</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>415</v>
@@ -17258,17 +17579,17 @@
         <v>426</v>
       </c>
       <c r="S11" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B11,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>大福</v>
+        <f>IFERROR(VLOOKUP(B11,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T11" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B11,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B11,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="34" spans="2:20">
       <c r="B12" s="1" t="s">
-        <v>230</v>
+        <v>737</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>415</v>
@@ -17307,17 +17628,17 @@
         <v>444</v>
       </c>
       <c r="S12" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B12,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>巧克力糖</v>
+        <f>IFERROR(VLOOKUP(B12,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T12" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B12,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B12,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="34" spans="2:20">
       <c r="B13" s="1" t="s">
-        <v>231</v>
+        <v>738</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>415</v>
@@ -17356,17 +17677,17 @@
         <v>441</v>
       </c>
       <c r="S13" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B13,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>果冻</v>
+        <f>IFERROR(VLOOKUP(B13,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T13" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B13,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B13,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="2:20">
       <c r="B14" s="1" t="s">
-        <v>232</v>
+        <v>739</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>415</v>
@@ -17408,75 +17729,66 @@
         <v>437</v>
       </c>
       <c r="S14" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B14,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>奶油小格</v>
+        <f>IFERROR(VLOOKUP(B14,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T14" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B14,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B14,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" s="25" customFormat="1" spans="2:20">
-      <c r="B15" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="C15" s="25" t="s">
+    <row r="15" ht="34" spans="2:16">
+      <c r="B15" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D15" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="E15" s="25" t="s">
+      <c r="D15" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F15" s="25" t="s">
-        <v>418</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>425</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="25" t="s">
-        <v>447</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="K15" s="25">
+      <c r="K15" s="1">
         <v>0</v>
       </c>
-      <c r="L15" s="25">
-        <v>1</v>
-      </c>
-      <c r="M15" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="25" t="s">
+      <c r="L15" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="O15" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="P15" s="25" t="s">
-        <v>448</v>
-      </c>
-      <c r="R15" s="25" t="s">
-        <v>449</v>
-      </c>
-      <c r="S15" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B15,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>糖豆</v>
+      <c r="P15" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="S15" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B15,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T15" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B15,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>慕斯蛋糕</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20">
+        <f>IFERROR(VLOOKUP(B15,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:17">
       <c r="B16" s="1" t="s">
-        <v>235</v>
+        <v>742</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>415</v>
@@ -17497,7 +17809,7 @@
         <v>428</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="K16" s="1">
         <v>1</v>
@@ -17517,18 +17829,18 @@
       <c r="Q16" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="S16" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B16,skill!$G$4:$K$50,5,FALSE),"")</f>
+      <c r="S16" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B16,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T16" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B16,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>糖豆</v>
+        <f>IFERROR(VLOOKUP(B16,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="34" spans="2:20">
       <c r="B17" s="1" t="s">
-        <v>236</v>
+        <v>743</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>415</v>
@@ -17570,17 +17882,17 @@
         <v>453</v>
       </c>
       <c r="S17" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B17,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>金巧克力</v>
+        <f>IFERROR(VLOOKUP(B17,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T17" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B17,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B17,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="34" spans="2:20">
       <c r="B18" s="1" t="s">
-        <v>237</v>
+        <v>744</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>415</v>
@@ -17622,17 +17934,17 @@
         <v>437</v>
       </c>
       <c r="S18" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B18,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>奶片</v>
+        <f>IFERROR(VLOOKUP(B18,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T18" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B18,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B18,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="34" spans="2:20">
       <c r="B19" s="1" t="s">
-        <v>239</v>
+        <v>746</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>415</v>
@@ -17671,17 +17983,17 @@
         <v>441</v>
       </c>
       <c r="S19" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B19,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>圣代</v>
+        <f>IFERROR(VLOOKUP(B19,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T19" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B19,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B19,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="2:20">
       <c r="B20" s="1" t="s">
-        <v>240</v>
+        <v>747</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>415</v>
@@ -17720,17 +18032,17 @@
         <v>456</v>
       </c>
       <c r="S20" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B20,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B20,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T20" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B20,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>圣代</v>
+        <f>IFERROR(VLOOKUP(B20,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="21" spans="2:20">
       <c r="B21" s="1" t="s">
-        <v>241</v>
+        <v>748</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>415</v>
@@ -17772,105 +18084,96 @@
         <v>437</v>
       </c>
       <c r="S21" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B21,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>甜筒</v>
+        <f>IFERROR(VLOOKUP(B21,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T21" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B21,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B21,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" s="25" customFormat="1" ht="34" spans="2:20">
-      <c r="B22" s="25" t="s">
-        <v>457</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>458</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>427</v>
-      </c>
-      <c r="E22" s="25" t="s">
+    <row r="22" ht="34" spans="2:20">
+      <c r="B22" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F22" s="25" t="s">
-        <v>418</v>
-      </c>
-      <c r="G22" s="25" t="s">
-        <v>425</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="I22" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>417</v>
-      </c>
-      <c r="K22" s="25">
+      <c r="K22" s="1">
         <v>0</v>
       </c>
-      <c r="L22" s="25">
-        <v>1</v>
-      </c>
-      <c r="M22" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="N22" s="25" t="s">
+      <c r="L22" s="1">
+        <v>2</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O22" s="25" t="s">
+      <c r="O22" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P22" s="22" t="s">
-        <v>460</v>
-      </c>
-      <c r="R22" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="S22" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B22,skill!$G$4:$K$50,5,FALSE),"")</f>
+      <c r="P22" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="S22" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B22,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T22" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B22,skill!$H$4:$K$50,4,FALSE),"")</f>
+      <c r="T22" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B22,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="34" spans="2:20">
+    <row r="23" spans="2:20">
       <c r="B23" s="1" t="s">
-        <v>243</v>
+        <v>751</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>462</v>
+        <v>427</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>418</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>463</v>
+        <v>425</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="K23" s="1">
+        <v>2</v>
+      </c>
+      <c r="L23" s="1">
         <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>2</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>25</v>
@@ -17878,21 +18181,24 @@
       <c r="O23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P23" s="19" t="s">
-        <v>464</v>
+      <c r="P23" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="S23" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B23,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>棒棒糖</v>
+        <f>IFERROR(VLOOKUP(B23,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T23" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B23,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B23,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="2:20">
+    <row r="24" ht="34" spans="2:16">
       <c r="B24" s="1" t="s">
-        <v>244</v>
+        <v>753</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>415</v>
@@ -17910,50 +18216,47 @@
         <v>425</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>428</v>
+        <v>371</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="K24" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
+      </c>
+      <c r="P24" s="19" t="s">
+        <v>507</v>
       </c>
       <c r="S24" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B24,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B24,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T24" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B24,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>棒棒糖</v>
-      </c>
-    </row>
-    <row r="25" ht="34" spans="2:20">
+      <c r="T24" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B24,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="1" t="s">
-        <v>246</v>
+        <v>754</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>418</v>
@@ -17962,16 +18265,16 @@
         <v>425</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
         <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>1.2</v>
       </c>
       <c r="N25" s="1" t="s">
         <v>25</v>
@@ -17979,27 +18282,30 @@
       <c r="O25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P25" s="19" t="s">
-        <v>466</v>
-      </c>
-      <c r="S25" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B25,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>软糖</v>
+      <c r="P25" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="S25" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B25,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T25" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B25,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B25,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:20">
+    <row r="26" ht="34" spans="2:20">
       <c r="B26" s="1" t="s">
-        <v>247</v>
+        <v>756</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>417</v>
@@ -18011,41 +18317,41 @@
         <v>425</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="K26" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N26" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>430</v>
+        <v>420</v>
+      </c>
+      <c r="P26" s="19" t="s">
+        <v>469</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="S26" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B26,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B26,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T26" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B26,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>软糖</v>
+        <f>IFERROR(VLOOKUP(B26,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="27" spans="2:20">
       <c r="B27" s="1" t="s">
-        <v>249</v>
+        <v>757</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>415</v>
@@ -18063,16 +18369,16 @@
         <v>425</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
         <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>1</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>25</v>
@@ -18081,26 +18387,29 @@
         <v>25</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="S27" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B27,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>杯子蛋糕</v>
-      </c>
-      <c r="T27" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B27,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <v>430</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="S27" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B27,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="28" ht="34" spans="2:20">
+      <c r="T27" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B27,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="2:16">
       <c r="B28" s="1" t="s">
-        <v>250</v>
+        <v>759</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>417</v>
@@ -18112,41 +18421,41 @@
         <v>425</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>434</v>
+        <v>377</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>435</v>
+        <v>484</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
       </c>
       <c r="L28" s="1">
-        <v>6</v>
+        <v>1.2</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P28" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="S28" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B28,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>25</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="S28" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B28,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T28" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B28,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>杯子蛋糕</v>
+        <f>IFERROR(VLOOKUP(B28,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="29" spans="2:20">
       <c r="B29" s="1" t="s">
-        <v>253</v>
+        <v>760</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>415</v>
@@ -18164,38 +18473,41 @@
         <v>425</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N29" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="S29" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B29,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>慕斯蛋糕</v>
+        <v>446</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="S29" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B29,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T29" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B29,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B29,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="34" spans="2:20">
       <c r="B30" s="1" t="s">
-        <v>255</v>
+        <v>762</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>415</v>
@@ -18234,17 +18546,17 @@
         <v>471</v>
       </c>
       <c r="S30" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B30,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>太妃糖</v>
+        <f>IFERROR(VLOOKUP(B30,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T30" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B30,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B30,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="2:20">
       <c r="B31" s="1" t="s">
-        <v>256</v>
+        <v>763</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>415</v>
@@ -18286,66 +18598,75 @@
         <v>431</v>
       </c>
       <c r="S31" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B31,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B31,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T31" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B31,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>太妃糖</v>
-      </c>
-    </row>
-    <row r="32" ht="34" spans="2:20">
-      <c r="B32" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C32" s="1" t="s">
+        <f>IFERROR(VLOOKUP(B31,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" s="25" customFormat="1" spans="2:20">
+      <c r="B32" s="25" t="s">
+        <v>765</v>
+      </c>
+      <c r="C32" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="F32" s="1" t="s">
+      <c r="D32" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="25" t="s">
         <v>425</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="J32" s="1" t="s">
+      <c r="H32" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I32" s="25" t="s">
+        <v>447</v>
+      </c>
+      <c r="J32" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="K32" s="1">
+      <c r="K32" s="25">
         <v>0</v>
       </c>
-      <c r="L32" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="N32" s="1" t="s">
+      <c r="L32" s="25">
+        <v>1</v>
+      </c>
+      <c r="M32" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="N32" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="O32" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P32" s="19" t="s">
-        <v>441</v>
+      <c r="P32" s="25" t="s">
+        <v>448</v>
+      </c>
+      <c r="R32" s="25" t="s">
+        <v>449</v>
       </c>
       <c r="S32" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B32,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>蛋卷</v>
+        <f>IFERROR(VLOOKUP(B32,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T32" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B32,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B32,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="2:20">
       <c r="B33" s="1" t="s">
-        <v>260</v>
+        <v>766</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>415</v>
@@ -18363,47 +18684,50 @@
         <v>425</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>455</v>
+        <v>428</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="K33" s="1">
+        <v>2</v>
+      </c>
+      <c r="L33" s="1">
         <v>0</v>
       </c>
-      <c r="L33" s="1">
-        <v>3</v>
-      </c>
       <c r="N33" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>456</v>
+        <v>430</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="S33" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B33,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B33,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T33" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B33,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>蛋卷</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20">
+        <f>IFERROR(VLOOKUP(B33,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="34" spans="2:20">
       <c r="B34" s="1" t="s">
-        <v>262</v>
+        <v>768</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>418</v>
@@ -18415,13 +18739,13 @@
         <v>374</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="K34" s="1">
         <v>0</v>
       </c>
       <c r="L34" s="1">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="N34" s="1" t="s">
         <v>25</v>
@@ -18429,21 +18753,21 @@
       <c r="O34" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="P34" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="S34" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B34,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>巧克力棒</v>
-      </c>
-      <c r="T34" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B34,skill!$H$4:$K$50,4,FALSE),"")</f>
+      <c r="P34" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="S34" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B34,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T34" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B34,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="2:20">
       <c r="B35" s="1" t="s">
-        <v>263</v>
+        <v>769</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>415</v>
@@ -18461,41 +18785,38 @@
         <v>425</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>450</v>
+        <v>417</v>
       </c>
       <c r="K35" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="O35" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="S35" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B35,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>456</v>
+      </c>
+      <c r="S35" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B35,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T35" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B35,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>巧克力棒</v>
+      <c r="T35" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B35,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="36" spans="2:20">
       <c r="B36" s="1" t="s">
-        <v>265</v>
+        <v>771</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>415</v>
@@ -18513,44 +18834,38 @@
         <v>425</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>440</v>
+        <v>473</v>
       </c>
       <c r="S36" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B36,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>闪电泡芙</v>
+        <f>IFERROR(VLOOKUP(B36,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T36" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B36,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B36,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="37" spans="2:20">
       <c r="B37" s="1" t="s">
-        <v>266</v>
+        <v>772</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>415</v>
@@ -18568,41 +18883,41 @@
         <v>425</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>374</v>
+        <v>428</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="K37" s="1">
+        <v>2</v>
+      </c>
+      <c r="L37" s="1">
         <v>0</v>
-      </c>
-      <c r="L37" s="1">
-        <v>3</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>445</v>
+        <v>430</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="S37" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B37,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B37,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T37" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B37,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>闪电泡芙</v>
+        <f>IFERROR(VLOOKUP(B37,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="38" spans="2:20">
       <c r="B38" s="1" t="s">
-        <v>268</v>
+        <v>774</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>415</v>
@@ -18620,47 +18935,50 @@
         <v>425</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>374</v>
+        <v>474</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="K38" s="1">
         <v>0</v>
       </c>
       <c r="L38" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N38" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="S38" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B38,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>糖葫芦</v>
-      </c>
-      <c r="T38" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B38,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <v>440</v>
+      </c>
+      <c r="S38" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B38,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="2:20">
+      <c r="T38" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B38,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="34" spans="2:16">
       <c r="B39" s="1" t="s">
-        <v>269</v>
+        <v>775</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>427</v>
+        <v>512</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>417</v>
@@ -18672,44 +18990,38 @@
         <v>425</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="K39" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L39" s="1">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="S39" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B39,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>420</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="S39" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B39,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T39" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B39,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>糖葫芦</v>
-      </c>
-    </row>
-    <row r="40" ht="34" spans="2:20">
+        <f>IFERROR(VLOOKUP(B39,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="2:20">
       <c r="B40" s="1" t="s">
-        <v>270</v>
+        <v>777</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>415</v>
@@ -18727,102 +19039,96 @@
         <v>425</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K40" s="1">
         <v>0</v>
       </c>
       <c r="L40" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>476</v>
+        <v>3</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P40" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>437</v>
+        <v>420</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="S40" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B40,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>舒芙蕾</v>
+        <f>IFERROR(VLOOKUP(B40,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T40" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B40,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B40,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="41" ht="34" spans="2:20">
+    <row r="41" spans="2:20">
       <c r="B41" s="1" t="s">
-        <v>271</v>
+        <v>778</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>418</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>377</v>
+        <v>428</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="K41" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
       </c>
-      <c r="M41" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="N41" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P41" s="19" t="s">
-        <v>482</v>
+      <c r="P41" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="S41" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B41,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>桃酥</v>
+        <f>IFERROR(VLOOKUP(B41,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T41" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B41,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B41,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:20">
+    <row r="42" ht="34" spans="2:20">
       <c r="B42" s="1" t="s">
-        <v>273</v>
+        <v>779</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>415</v>
@@ -18840,38 +19146,47 @@
         <v>425</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>4</v>
+        <v>1.5</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P42" s="1" t="s">
-        <v>456</v>
+      <c r="P42" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="S42" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B42,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B42,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T42" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B42,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>月饼</v>
+        <f>IFERROR(VLOOKUP(B42,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="43" ht="34" spans="2:20">
       <c r="B43" s="1" t="s">
-        <v>275</v>
+        <v>780</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>415</v>
@@ -18880,25 +19195,31 @@
         <v>422</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>425</v>
+        <v>479</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>377</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="K43" s="1">
         <v>0</v>
       </c>
       <c r="L43" s="1">
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>481</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>25</v>
@@ -18907,69 +19228,69 @@
         <v>25</v>
       </c>
       <c r="P43" s="19" t="s">
-        <v>441</v>
-      </c>
-      <c r="S43" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B43,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>华夫饼</v>
-      </c>
-      <c r="T43" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B43,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <v>482</v>
+      </c>
+      <c r="S43" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B43,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="44" ht="17" spans="2:20">
+      <c r="T43" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B43,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="2:20">
       <c r="B44" s="1" t="s">
-        <v>276</v>
+        <v>782</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>418</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
       </c>
       <c r="L44" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P44" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="S44" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B44,skill!$G$4:$K$50,5,FALSE),"")</f>
+      <c r="P44" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="S44" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B44,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T44" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B44,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>华夫饼</v>
+      <c r="T44" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B44,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="45" spans="2:20">
       <c r="B45" s="1" t="s">
-        <v>278</v>
+        <v>783</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>415</v>
@@ -18990,13 +19311,13 @@
         <v>455</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
       </c>
       <c r="L45" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>420</v>
@@ -19005,38 +19326,38 @@
         <v>25</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="S45" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B45,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>铜锣烧</v>
+        <f>IFERROR(VLOOKUP(B45,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T45" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B45,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B45,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:20">
+    <row r="46" ht="34" spans="2:20">
       <c r="B46" s="1" t="s">
-        <v>279</v>
+        <v>785</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>425</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>417</v>
@@ -19045,81 +19366,78 @@
         <v>0</v>
       </c>
       <c r="L46" s="1">
-        <v>4</v>
+        <v>0.4</v>
       </c>
       <c r="N46" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="S46" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B46,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>25</v>
+      </c>
+      <c r="P46" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="S46" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B46,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T46" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B46,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>铜锣烧</v>
-      </c>
-    </row>
-    <row r="47" ht="34" spans="2:20">
+      <c r="T46" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B46,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="17" spans="2:20">
       <c r="B47" s="1" t="s">
-        <v>281</v>
+        <v>786</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>418</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>371</v>
+        <v>455</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>484</v>
+        <v>417</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
       </c>
       <c r="L47" s="1">
-        <v>10</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>485</v>
+        <v>9</v>
       </c>
       <c r="N47" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O47" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="P47" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="S47" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B47,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>483</v>
+      </c>
+      <c r="S47" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B47,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T47" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B47,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>奶油蛋糕</v>
+      <c r="T47" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B47,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="48" spans="2:20">
       <c r="B48" s="1" t="s">
-        <v>283</v>
+        <v>788</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>415</v>
@@ -19137,47 +19455,44 @@
         <v>425</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K48" s="1">
         <v>0</v>
       </c>
       <c r="L48" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N48" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O48" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O48" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="P48" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>437</v>
+        <v>483</v>
       </c>
       <c r="S48" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B48,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>甜甜圈</v>
+        <f>IFERROR(VLOOKUP(B48,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T48" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B48,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B48,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="34" spans="2:20">
+    <row r="49" spans="2:20">
       <c r="B49" s="1" t="s">
-        <v>285</v>
+        <v>789</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>417</v>
@@ -19198,7 +19513,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>25</v>
@@ -19206,21 +19521,21 @@
       <c r="O49" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="P49" s="19" t="s">
-        <v>487</v>
+      <c r="P49" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="S49" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B49,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>椪糖</v>
+        <f>IFERROR(VLOOKUP(B49,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T49" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B49,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B49,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:20">
+    <row r="50" ht="34" spans="2:20">
       <c r="B50" s="1" t="s">
-        <v>286</v>
+        <v>791</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>415</v>
@@ -19238,41 +19553,38 @@
         <v>425</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="K50" s="1">
         <v>0</v>
       </c>
       <c r="L50" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="S50" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B50,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>420</v>
+      </c>
+      <c r="P50" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="S50" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B50,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T50" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B50,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>椪糖</v>
-      </c>
-    </row>
-    <row r="51" spans="2:20">
+      <c r="T50" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B50,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="34" spans="2:20">
       <c r="B51" s="1" t="s">
-        <v>288</v>
+        <v>792</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>415</v>
@@ -19290,38 +19602,41 @@
         <v>425</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>455</v>
+        <v>371</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>417</v>
+        <v>484</v>
       </c>
       <c r="K51" s="1">
         <v>0</v>
       </c>
       <c r="L51" s="1">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="N51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O51" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="O51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>456</v>
+      <c r="P51" s="19" t="s">
+        <v>486</v>
       </c>
       <c r="S51" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B51,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B51,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T51" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B51,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>芭菲</v>
+        <f>IFERROR(VLOOKUP(B51,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="52" spans="2:20">
       <c r="B52" s="1" t="s">
-        <v>290</v>
+        <v>794</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>415</v>
@@ -19339,38 +19654,41 @@
         <v>425</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="K52" s="1">
         <v>0</v>
       </c>
       <c r="L52" s="1">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>470</v>
+        <v>446</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="S52" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B52,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>圣代</v>
+        <f>IFERROR(VLOOKUP(B52,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T52" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B52,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B52,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" spans="2:20">
       <c r="B53" s="1" t="s">
-        <v>292</v>
+        <v>795</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>415</v>
@@ -19388,16 +19706,16 @@
         <v>425</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>434</v>
+        <v>374</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="K53" s="1">
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>25</v>
@@ -19406,29 +19724,29 @@
         <v>420</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="S53" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B53,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>瑞士卷</v>
-      </c>
-      <c r="T53" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B53,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <v>473</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="S53" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B53,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-    </row>
-    <row r="54" spans="2:20">
+      <c r="T53" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B53,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="34" spans="2:20">
       <c r="B54" s="1" t="s">
-        <v>293</v>
+        <v>797</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>417</v>
@@ -19443,13 +19761,13 @@
         <v>374</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
       </c>
       <c r="L54" s="1">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>25</v>
@@ -19457,21 +19775,21 @@
       <c r="O54" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>473</v>
+      <c r="P54" s="19" t="s">
+        <v>487</v>
       </c>
       <c r="S54" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B54,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B54,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T54" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B54,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>瑞士卷</v>
+        <f>IFERROR(VLOOKUP(B54,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="55" spans="2:20">
       <c r="B55" s="1" t="s">
-        <v>295</v>
+        <v>798</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>415</v>
@@ -19489,16 +19807,16 @@
         <v>425</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>467</v>
+        <v>428</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>423</v>
+        <v>465</v>
       </c>
       <c r="K55" s="1">
         <v>0</v>
       </c>
       <c r="L55" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>25</v>
@@ -19507,29 +19825,32 @@
         <v>25</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>468</v>
+        <v>430</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="S55" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B55,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>杨枝甘露</v>
+        <f>IFERROR(VLOOKUP(B55,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T55" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B55,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B55,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:20">
+    <row r="56" ht="34" spans="2:20">
       <c r="B56" s="1" t="s">
-        <v>296</v>
+        <v>800</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>418</v>
@@ -19538,7 +19859,7 @@
         <v>425</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>455</v>
+        <v>377</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>417</v>
@@ -19547,29 +19868,29 @@
         <v>0</v>
       </c>
       <c r="L56" s="1">
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>456</v>
+      <c r="P56" s="19" t="s">
+        <v>466</v>
       </c>
       <c r="S56" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B56,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B56,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T56" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B56,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>杨枝甘露</v>
+        <f>IFERROR(VLOOKUP(B56,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="57" spans="2:20">
       <c r="B57" s="1" t="s">
-        <v>298</v>
+        <v>801</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>415</v>
@@ -19587,50 +19908,47 @@
         <v>425</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>374</v>
+        <v>455</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>484</v>
+        <v>417</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
       </c>
       <c r="L57" s="1">
-        <v>5</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>485</v>
+        <v>9</v>
       </c>
       <c r="N57" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="O57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O57" s="1" t="s">
-        <v>420</v>
-      </c>
       <c r="P57" s="1" t="s">
-        <v>488</v>
+        <v>456</v>
       </c>
       <c r="S57" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B57,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B57,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T57" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B57,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B57,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="58" ht="34" spans="2:20">
+    <row r="58" spans="2:20">
       <c r="B58" s="1" t="s">
-        <v>300</v>
+        <v>803</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>418</v>
@@ -19639,38 +19957,38 @@
         <v>425</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
       </c>
       <c r="L58" s="1">
-        <v>0.3</v>
+        <v>2</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P58" s="19" t="s">
-        <v>441</v>
+        <v>25</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="S58" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B58,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>苹果派</v>
+        <f>IFERROR(VLOOKUP(B58,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T58" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B58,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B58,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="59" spans="2:20">
       <c r="B59" s="1" t="s">
-        <v>302</v>
+        <v>804</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>415</v>
@@ -19688,7 +20006,7 @@
         <v>425</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>377</v>
+        <v>455</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>417</v>
@@ -19697,47 +20015,44 @@
         <v>0</v>
       </c>
       <c r="L59" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="O59" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="S59" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B59,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>水果蛋糕</v>
+        <f>IFERROR(VLOOKUP(B59,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T59" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B59,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B59,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="60" ht="34" spans="2:20">
+    <row r="60" spans="2:20">
       <c r="B60" s="1" t="s">
-        <v>303</v>
+        <v>806</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>489</v>
+        <v>427</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>418</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>490</v>
+        <v>425</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>434</v>
@@ -19749,56 +20064,50 @@
         <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>0</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>491</v>
+        <v>20</v>
       </c>
       <c r="N60" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P60" s="19" t="s">
-        <v>492</v>
+        <v>420</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="Q60" s="1" t="s">
         <v>437</v>
       </c>
       <c r="S60" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B60,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B60,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T60" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B60,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>水果蛋糕</v>
-      </c>
-    </row>
-    <row r="61" ht="34" spans="2:20">
+        <f>IFERROR(VLOOKUP(B60,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="2:20">
       <c r="B61" s="1" t="s">
-        <v>304</v>
+        <v>807</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>494</v>
+        <v>425</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>472</v>
@@ -19807,56 +20116,50 @@
         <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>0</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>495</v>
+        <v>0.5</v>
       </c>
       <c r="N61" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P61" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="S61" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B61,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>巧克力</v>
+        <f>IFERROR(VLOOKUP(B61,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T61" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B61,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B61,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="62" ht="34" spans="2:20">
+    <row r="62" spans="2:20">
       <c r="B62" s="1" t="s">
-        <v>305</v>
+        <v>809</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>425</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="K62" s="1">
         <v>0</v>
@@ -19868,26 +20171,23 @@
         <v>25</v>
       </c>
       <c r="O62" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P62" s="19" t="s">
-        <v>436</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>437</v>
+        <v>25</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="S62" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B62,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>牛角包</v>
+        <f>IFERROR(VLOOKUP(B62,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T62" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B62,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B62,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="63" spans="2:20">
       <c r="B63" s="1" t="s">
-        <v>307</v>
+        <v>810</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>415</v>
@@ -19905,38 +20205,38 @@
         <v>425</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>377</v>
+        <v>455</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>445</v>
+        <v>417</v>
       </c>
       <c r="K63" s="1">
         <v>0</v>
       </c>
       <c r="L63" s="1">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="O63" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="S63" s="26" t="str">
-        <f>IFERROR(VLOOKUP(B63,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>蝴蝶酥</v>
+        <v>456</v>
+      </c>
+      <c r="S63" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B63,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T63" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B63,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B63,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="64" spans="2:20">
       <c r="B64" s="1" t="s">
-        <v>497</v>
+        <v>812</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>415</v>
@@ -19954,7 +20254,7 @@
         <v>425</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>455</v>
+        <v>374</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>417</v>
@@ -19966,25 +20266,29 @@
         <v>3</v>
       </c>
       <c r="N64" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="P64" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="S64" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B64,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <v>473</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="S64" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B64,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T64" s="1" t="s">
-        <v>498</v>
+      <c r="T64" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B64,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
       </c>
     </row>
     <row r="65" spans="2:20">
       <c r="B65" s="1" t="s">
-        <v>309</v>
+        <v>813</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>415</v>
@@ -20002,47 +20306,50 @@
         <v>425</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>440</v>
+        <v>484</v>
       </c>
       <c r="K65" s="1">
         <v>0</v>
       </c>
       <c r="L65" s="1">
-        <v>1.4</v>
+        <v>5</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="S65" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B65,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>拐杖糖</v>
+        <f>IFERROR(VLOOKUP(B65,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T65" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B65,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B65,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="2:20">
+    <row r="66" ht="34" spans="2:20">
       <c r="B66" s="1" t="s">
-        <v>310</v>
+        <v>814</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>417</v>
+        <v>442</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>418</v>
@@ -20051,41 +20358,38 @@
         <v>425</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>428</v>
+        <v>374</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="K66" s="1">
         <v>0</v>
       </c>
       <c r="L66" s="1">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N66" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
+      </c>
+      <c r="P66" s="19" t="s">
+        <v>441</v>
       </c>
       <c r="S66" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B66,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B66,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T66" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B66,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>拐杖糖</v>
-      </c>
-    </row>
-    <row r="67" ht="34" spans="2:20">
+        <f>IFERROR(VLOOKUP(B66,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="2:20">
       <c r="B67" s="1" t="s">
-        <v>311</v>
+        <v>816</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>415</v>
@@ -20103,19 +20407,16 @@
         <v>425</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>499</v>
+        <v>377</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>472</v>
+        <v>417</v>
       </c>
       <c r="K67" s="1">
         <v>0</v>
       </c>
       <c r="L67" s="1">
-        <v>0</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>500</v>
+        <v>2</v>
       </c>
       <c r="N67" s="1" t="s">
         <v>25</v>
@@ -20123,51 +20424,54 @@
       <c r="O67" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P67" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>431</v>
+      <c r="P67" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="S67" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B67,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>大棒棒糖</v>
+        <f>IFERROR(VLOOKUP(B67,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T67" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B67,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B67,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="34" spans="2:20">
       <c r="B68" s="1" t="s">
-        <v>313</v>
+        <v>817</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>443</v>
+        <v>489</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>418</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>425</v>
+        <v>479</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>490</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="K68" s="1">
         <v>0</v>
       </c>
       <c r="L68" s="1">
-        <v>1.5</v>
+        <v>0</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>25</v>
@@ -20176,41 +20480,47 @@
         <v>25</v>
       </c>
       <c r="P68" s="19" t="s">
-        <v>502</v>
+        <v>492</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="S68" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B68,skill!$G$4:$K$50,5,FALSE),"")</f>
-        <v>棉花糖</v>
+        <f>IFERROR(VLOOKUP(B68,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T68" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B68,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B68,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:20">
+    <row r="69" ht="34" spans="2:20">
       <c r="B69" s="1" t="s">
-        <v>314</v>
+        <v>818</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>417</v>
+        <v>472</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>425</v>
+        <v>479</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>429</v>
+        <v>472</v>
       </c>
       <c r="K69" s="1">
         <v>0</v>
@@ -20218,87 +20528,94 @@
       <c r="L69" s="1">
         <v>0</v>
       </c>
+      <c r="M69" s="1" t="s">
+        <v>495</v>
+      </c>
       <c r="N69" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>430</v>
+      <c r="P69" s="19" t="s">
+        <v>496</v>
       </c>
       <c r="Q69" s="1" t="s">
         <v>431</v>
       </c>
       <c r="S69" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B69,skill!$G$4:$K$50,5,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B69,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
       <c r="T69" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B69,skill!$H$4:$K$50,4,FALSE),"")</f>
-        <v>棉花糖</v>
-      </c>
-    </row>
-    <row r="70" spans="2:20">
+        <f>IFERROR(VLOOKUP(B69,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" ht="34" spans="2:20">
       <c r="B70" s="1" t="s">
-        <v>315</v>
+        <v>819</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>425</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>467</v>
+        <v>434</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="K70" s="1">
         <v>0</v>
       </c>
       <c r="L70" s="1">
-        <v>3</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>485</v>
+        <v>2</v>
       </c>
       <c r="N70" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>503</v>
+        <v>420</v>
+      </c>
+      <c r="P70" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="S70" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B70,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
       </c>
       <c r="T70" s="1" t="str">
-        <f>IFERROR(VLOOKUP(B70,skill!$H$4:$K$50,4,FALSE),"")</f>
+        <f>IFERROR(VLOOKUP(B70,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
-    <row r="71" ht="34" spans="2:16">
+    <row r="71" spans="2:20">
       <c r="B71" s="1" t="s">
-        <v>504</v>
+        <v>821</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>418</v>
@@ -20307,30 +20624,38 @@
         <v>425</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>417</v>
+        <v>445</v>
       </c>
       <c r="K71" s="1">
         <v>0</v>
       </c>
       <c r="L71" s="1">
-        <v>0.2</v>
+        <v>2.5</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P71" s="19" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="72" spans="2:17">
+        <v>25</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="S71" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B71,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T71" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B71,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="2:20">
       <c r="B72" s="1" t="s">
-        <v>505</v>
+        <v>822</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>415</v>
@@ -20348,33 +20673,38 @@
         <v>425</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K72" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>25</v>
+        <v>420</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="73" ht="34" spans="2:16">
+        <v>456</v>
+      </c>
+      <c r="S72" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B72,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T72" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B72,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="2:20">
       <c r="B73" s="1" t="s">
-        <v>506</v>
+        <v>824</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>415</v>
@@ -20392,30 +20722,38 @@
         <v>425</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="K73" s="1">
         <v>0</v>
       </c>
       <c r="L73" s="1">
-        <v>10</v>
+        <v>1.4</v>
       </c>
       <c r="N73" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="P73" s="19" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="74" spans="2:17">
+        <v>25</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="S73" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B73,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T73" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B73,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="2:20">
       <c r="B74" s="1" t="s">
-        <v>508</v>
+        <v>825</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>415</v>
@@ -20436,10 +20774,10 @@
         <v>428</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>465</v>
+        <v>423</v>
       </c>
       <c r="K74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>
@@ -20456,10 +20794,18 @@
       <c r="Q74" s="1" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="75" spans="2:16">
+      <c r="S74" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B74,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T74" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B74,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" ht="34" spans="2:20">
       <c r="B75" s="1" t="s">
-        <v>509</v>
+        <v>826</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>415</v>
@@ -20477,19 +20823,19 @@
         <v>425</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>377</v>
+        <v>499</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="K75" s="1">
         <v>0</v>
       </c>
       <c r="L75" s="1">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M75" s="1" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
       <c r="N75" s="1" t="s">
         <v>25</v>
@@ -20497,19 +20843,30 @@
       <c r="O75" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="76" ht="34" spans="2:16">
+      <c r="P75" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="S75" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B75,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T75" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B75,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="34" spans="2:20">
       <c r="B76" s="1" t="s">
-        <v>511</v>
+        <v>828</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>415</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>512</v>
+        <v>443</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>417</v>
@@ -20521,30 +20878,38 @@
         <v>425</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>442</v>
+        <v>417</v>
       </c>
       <c r="K76" s="1">
         <v>0</v>
       </c>
       <c r="L76" s="1">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="N76" s="1" t="s">
         <v>25</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="P76" s="19" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="77" ht="34" spans="2:17">
+        <v>502</v>
+      </c>
+      <c r="S76" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B76,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T76" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B76,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="2:20">
       <c r="B77" s="1" t="s">
-        <v>316</v>
+        <v>829</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>415</v>
@@ -20562,16 +20927,16 @@
         <v>425</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>726</v>
+        <v>428</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>472</v>
+        <v>429</v>
       </c>
       <c r="K77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N77" s="1" t="s">
         <v>25</v>
@@ -20579,15 +20944,127 @@
       <c r="O77" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="P77" s="19" t="s">
-        <v>514</v>
+      <c r="P77" s="1" t="s">
+        <v>430</v>
       </c>
       <c r="Q77" s="1" t="s">
         <v>431</v>
       </c>
+      <c r="S77" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B77,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T77" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B77,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="2:20">
+      <c r="B78" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="K78" s="1">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1">
+        <v>3</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P78" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="S78" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B78,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T78" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B78,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="34" spans="2:17">
+      <c r="B79" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="K79" s="1">
+        <v>1</v>
+      </c>
+      <c r="L79" s="1">
+        <v>1</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P79" s="19" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="S79" s="26" t="str">
+        <f>IFERROR(VLOOKUP(B79,skill!$G$4:$K$51,5,FALSE),"")</f>
+        <v/>
+      </c>
+      <c r="T79" s="1" t="str">
+        <f>IFERROR(VLOOKUP(B79,skill!$H$4:$K$51,4,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C70" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="C1:C79" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -19791,21 +19791,74 @@
       </c>
     </row>
     <row r="63" spans="2:20">
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="26"/>
+      <c r="B63" s="26" t="inlineStr">
+        <is>
+          <t>sk_mango_sago_2</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="D63" s="26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E63" s="26" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F63" s="26" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="G63" s="26" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
       <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
-      <c r="M63" s="26"/>
-      <c r="N63" s="26"/>
-      <c r="O63" s="26"/>
-      <c r="P63" s="26"/>
+      <c r="I63" s="26" t="inlineStr">
+        <is>
+          <t>AddCurrentMult</t>
+        </is>
+      </c>
+      <c r="J63" s="26" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="K63" s="26">
+        <v>0</v>
+      </c>
+      <c r="L63" s="26">
+        <v>0</v>
+      </c>
+      <c r="M63" s="26" t="inlineStr">
+        <is>
+          <t>source:one-cell</t>
+        </is>
+      </c>
+      <c r="N63" s="26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O63" s="26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P63" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所有占 1 格食物的倍率
+添加到自身</t>
+        </is>
+      </c>
       <c r="S63" s="27" t="str">
         <f>IFERROR(VLOOKUP(B63,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
@@ -19914,21 +19967,73 @@
       </c>
     </row>
     <row r="66" spans="2:20">
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>sk_chiffon_2</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="inlineStr">
+        <is>
+          <t>OnSettle</t>
+        </is>
+      </c>
+      <c r="D66" s="25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E66" s="25" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="F66" s="25" t="inlineStr">
+        <is>
+          <t>Instances</t>
+        </is>
+      </c>
+      <c r="G66" s="25" t="inlineStr">
+        <is>
+          <t>Per</t>
+        </is>
+      </c>
       <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="25"/>
-      <c r="K66" s="25"/>
-      <c r="L66" s="25"/>
-      <c r="M66" s="25"/>
-      <c r="N66" s="25"/>
-      <c r="O66" s="25"/>
-      <c r="P66" s="25"/>
+      <c r="I66" s="25" t="inlineStr">
+        <is>
+          <t>AddCurrentMult</t>
+        </is>
+      </c>
+      <c r="J66" s="25" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="K66" s="25">
+        <v>0</v>
+      </c>
+      <c r="L66" s="25">
+        <v>0</v>
+      </c>
+      <c r="M66" s="25" t="inlineStr">
+        <is>
+          <t>cat:cake</t>
+        </is>
+      </c>
+      <c r="N66" s="25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="O66" s="25" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="P66" s="25" t="inlineStr">
+        <is>
+          <t>将自身倍率添加到所有{cat}食物</t>
+        </is>
+      </c>
       <c r="S66" s="27" t="str">
         <f>IFERROR(VLOOKUP(B66,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -19085,14 +19085,78 @@
         <x:f>IFERROR(VLOOKUP(B52,skill!$H$4:$K$51,4,FALSE),"")</x:f>
       </x:c>
     </x:row>
-    <x:row r="53">
-      <x:c r="P53" s="19"/>
+    <x:row r="53" ht="34">
+      <x:c r="B53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>sk_cream_cake_2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>OnSettle</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Self</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Instances</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Per</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>AddCurrentScore</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K53" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>cat:cake</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>false</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O53" s="1" t="inlineStr">
+        <x:is>
+          <x:t>false</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P53" s="19" t="inlineStr">
+        <x:is>
+          <x:t>将自身当前分数添加到所有{cat}食物</x:t>
+        </x:is>
+      </x:c>
       <x:c r="S53" s="27" t="str">
         <x:f>IFERROR(VLOOKUP(B53,skill!$G$4:$K$51,5,FALSE),"")</x:f>
       </x:c>
       <x:c r="T53" s="27" t="str">
         <x:f>IFERROR(VLOOKUP(B53,skill!$H$4:$K$51,4,FALSE),"")</x:f>
-        <x:v>曲奇</x:v>
       </x:c>
     </x:row>
     <x:row r="54">

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240" activeTab="1"/>
+    <workbookView windowHeight="15300" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3230" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3219" uniqueCount="732">
   <si>
     <t>##var</t>
   </si>
@@ -1185,7 +1185,7 @@
     <t>AddFlat</t>
   </si>
   <si>
-    <t>欢乐蛋糕≥1层：所有蛋糕基础分 +5×层数。</t>
+    <t>欢乐蛋糕≥1层：所有蛋糕基础分 +3×层数。</t>
   </si>
   <si>
     <t>clb_multflat</t>
@@ -1194,7 +1194,7 @@
     <t>AddMultFlat</t>
   </si>
   <si>
-    <t>欢乐蛋糕≥50层：所有蛋糕倍率 +0.1×层数。</t>
+    <t>欢乐蛋糕≥50层：所有蛋糕倍率 +0.05×层数。</t>
   </si>
   <si>
     <t>clb_mult</t>
@@ -1475,9 +1475,6 @@
     <t>All</t>
   </si>
   <si>
-    <t>{ascope}视为 {countas} 个食物</t>
-  </si>
-  <si>
     <t>{ascope}倍率 {0}</t>
   </si>
   <si>
@@ -1520,6 +1517,9 @@
 {ascope}倍率 ×{tiervals}</t>
   </si>
   <si>
+    <t>{ascope}倍率 ×{0}</t>
+  </si>
+  <si>
     <t>{ascope}额外视为 {0} 个食物</t>
   </si>
   <si>
@@ -1545,7 +1545,7 @@
 {ascope}倍率 ×{0}</t>
   </si>
   <si>
-    <t>{ascope}倍率 ×{0}</t>
+    <t>{ascope}视为 {countas} 个食物</t>
   </si>
   <si>
     <t>{ascope}食物倍率 {0}</t>
@@ -1814,7 +1814,7 @@
     <t>（周围/同列/同行/空）每有1个空格</t>
   </si>
   <si>
-    <t>若本行被填满
+    <t>若本列被填满
 欢乐蛋糕+10层</t>
   </si>
   <si>
@@ -1898,8 +1898,7 @@
     <t>（前面/后面）每有1个食物</t>
   </si>
   <si>
-    <t>本行食物
-分数+10
+    <t>本行食物分数+10
 甜蜜传递至同列1个食物</t>
   </si>
   <si>
@@ -1980,8 +1979,7 @@
     <t>若（周围/全部）存在xx形状的空格</t>
   </si>
   <si>
-    <t>周围及自身
-分数+10
+    <t>周围及自身分数+10
 甜蜜传递至同行2个食物</t>
   </si>
   <si>
@@ -2023,8 +2021,7 @@
     <t>菜谱中食物（大于等于/小于等于）3（种/个）时</t>
   </si>
   <si>
-    <t>周围及自身
-倍率+1.5
+    <t>周围及自身倍率+1.5
 甜蜜传递1个食物</t>
   </si>
   <si>
@@ -2113,8 +2110,8 @@
   </si>
   <si>
     <t>额外视为5个食物
-本行食物达「10/18/25」个时
-本行倍率x「2/3/4」</t>
+本列食物达「10/18/25」个时
+本列倍率x「2/3/4」</t>
   </si>
   <si>
     <t>周围倍率乘</t>
@@ -2146,8 +2143,8 @@
   </si>
   <si>
     <t>额外视为7个食物
-周围及自身
-倍率+5</t>
+本行每有1个食物
+周围及自身倍率+0.3</t>
   </si>
   <si>
     <t>分数增加</t>
@@ -2239,7 +2236,8 @@
   </si>
   <si>
     <t>额外视为4个食物
-本行倍率x3</t>
+本列倍率×N
+（N=1+周围食物个数×0.2）</t>
   </si>
   <si>
     <t>蛋糕层数+20
@@ -2256,8 +2254,7 @@
   </si>
   <si>
     <t>本行每有1个食物
-周围及自身
-倍率+0.5</t>
+周围及自身倍率+0.5</t>
   </si>
   <si>
     <t>蛋糕食物倍率x2
@@ -2274,7 +2271,8 @@
   </si>
   <si>
     <t>额外视为3个食物
-周围及自身倍率x1.5</t>
+周围及自身倍率×N
+（N=1+本列食物个数×0.05）</t>
   </si>
   <si>
     <t>本列食物倍率x1.3
@@ -2990,7 +2988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3034,10 +3032,10 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3071,12 +3069,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -3768,11 +3760,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="1" t="str">
-        <f t="shared" ref="L5:L38" si="0">VLOOKUP(K5,$R$24:$U$29,3,FALSE)</f>
+        <f t="shared" ref="L5:L40" si="0">VLOOKUP(K5,$R$24:$U$29,3,FALSE)</f>
         <v>10,40</v>
       </c>
       <c r="M5" s="1" t="str">
-        <f t="shared" ref="M5:M38" si="1">VLOOKUP(K5,$R$24:$U$29,4,FALSE)</f>
+        <f t="shared" ref="M5:M40" si="1">VLOOKUP(K5,$R$24:$U$29,4,FALSE)</f>
         <v>40,80</v>
       </c>
       <c r="N5" s="1">
@@ -3780,7 +3772,7 @@
         <v>15</v>
       </c>
       <c r="O5" s="1">
-        <f t="shared" ref="O5:O38" si="3">ROUNDUP(N5*1.4+30,-1)</f>
+        <f t="shared" ref="O5:O40" si="3">ROUNDUP(N5*1.4+30,-1)</f>
         <v>60</v>
       </c>
     </row>
@@ -4865,7 +4857,7 @@
       <c r="T27" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="U27" s="30" t="s">
+      <c r="U27" s="28" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4899,7 +4891,7 @@
       <c r="T28" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="U28" s="30" t="s">
+      <c r="U28" s="28" t="s">
         <v>107</v>
       </c>
     </row>
@@ -4948,10 +4940,10 @@
       <c r="R29" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="T29" s="31">
+      <c r="T29" s="29">
         <v>45100</v>
       </c>
-      <c r="U29" s="30" t="s">
+      <c r="U29" s="28" t="s">
         <v>113</v>
       </c>
     </row>
@@ -5281,11 +5273,11 @@
         <v>4</v>
       </c>
       <c r="L39" s="1" t="str">
-        <f>VLOOKUP(K39,$R$24:$U$29,3,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>30,75</v>
       </c>
       <c r="M39" s="1" t="str">
-        <f>VLOOKUP(K39,$R$24:$U$29,4,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>55,100</v>
       </c>
       <c r="N39" s="1">
@@ -5293,7 +5285,7 @@
         <v>60</v>
       </c>
       <c r="O39" s="1">
-        <f>ROUNDUP(N39*1.4+30,-1)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
     </row>
@@ -5306,11 +5298,11 @@
         <v>4</v>
       </c>
       <c r="L40" s="1" t="str">
-        <f>VLOOKUP(K40,$R$24:$U$29,3,FALSE)</f>
+        <f t="shared" si="0"/>
         <v>30,75</v>
       </c>
       <c r="M40" s="1" t="str">
-        <f>VLOOKUP(K40,$R$24:$U$29,4,FALSE)</f>
+        <f t="shared" si="1"/>
         <v>55,100</v>
       </c>
       <c r="N40" s="1">
@@ -5318,7 +5310,7 @@
         <v>60</v>
       </c>
       <c r="O40" s="1">
-        <f>ROUNDUP(N40*1.4+30,-1)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
     </row>
@@ -6732,7 +6724,7 @@
       <c r="L82" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M82" s="30" t="s">
+      <c r="M82" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N82" s="1">
@@ -6755,7 +6747,7 @@
       <c r="L83" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M83" s="30" t="s">
+      <c r="M83" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N83" s="1">
@@ -6778,7 +6770,7 @@
       <c r="L84" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M84" s="30" t="s">
+      <c r="M84" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N84" s="1">
@@ -6801,7 +6793,7 @@
       <c r="L85" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M85" s="30" t="s">
+      <c r="M85" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N85" s="1">
@@ -6824,7 +6816,7 @@
       <c r="L86" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M86" s="30" t="s">
+      <c r="M86" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N86" s="1">
@@ -6867,7 +6859,7 @@
       <c r="L87" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M87" s="30" t="s">
+      <c r="M87" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N87" s="1">
@@ -6890,7 +6882,7 @@
       <c r="L88" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M88" s="30" t="s">
+      <c r="M88" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N88" s="1">
@@ -6913,7 +6905,7 @@
       <c r="L89" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M89" s="30" t="s">
+      <c r="M89" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N89" s="1">
@@ -6956,7 +6948,7 @@
       <c r="L90" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M90" s="30" t="s">
+      <c r="M90" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N90" s="1">
@@ -6979,7 +6971,7 @@
       <c r="L91" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M91" s="30" t="s">
+      <c r="M91" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N91" s="1">
@@ -7002,7 +6994,7 @@
       <c r="L92" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M92" s="30" t="s">
+      <c r="M92" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N92" s="1">
@@ -7025,7 +7017,7 @@
       <c r="L93" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M93" s="30" t="s">
+      <c r="M93" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N93" s="1">
@@ -7045,7 +7037,7 @@
       <c r="L94" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="M94" s="30" t="s">
+      <c r="M94" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N94" s="1">
@@ -8325,7 +8317,6 @@
       <c r="C51" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D51" s="1"/>
       <c r="E51" s="1">
         <v>100</v>
       </c>
@@ -8346,7 +8337,7 @@
         <f t="shared" si="1"/>
         <v>cookiet_sweet</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -8372,7 +8363,7 @@
         <f t="shared" si="1"/>
         <v>macaront_sweet</v>
       </c>
-      <c r="C53" s="28" t="s">
+      <c r="C53" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -8398,7 +8389,7 @@
         <f t="shared" si="1"/>
         <v>puddingt_sweet</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -8424,7 +8415,7 @@
         <f t="shared" si="1"/>
         <v>pufft_sweet</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -8450,7 +8441,7 @@
         <f t="shared" si="1"/>
         <v>eggtartt_sweet</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -8476,7 +8467,7 @@
         <f t="shared" si="1"/>
         <v>mochit_sweet</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -8502,7 +8493,7 @@
         <f t="shared" si="1"/>
         <v>daifukut_sweet</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -8528,7 +8519,7 @@
         <f t="shared" si="1"/>
         <v>choco_candyt_sweet</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -8554,7 +8545,7 @@
         <f t="shared" si="1"/>
         <v>jellyt_sweet</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -8580,7 +8571,7 @@
         <f t="shared" si="1"/>
         <v>cream_cellt_sweet</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -8606,7 +8597,7 @@
         <f t="shared" si="1"/>
         <v>sugarbeant_sweet</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -8632,7 +8623,7 @@
         <f t="shared" si="1"/>
         <v>gold_chocot_sweet</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -8658,7 +8649,7 @@
         <f t="shared" si="1"/>
         <v>milk_slicet_sweet</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -8684,7 +8675,7 @@
         <f t="shared" si="1"/>
         <v>sundaet_sweet</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -8710,7 +8701,7 @@
         <f t="shared" si="1"/>
         <v>conet_sweet</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -8736,7 +8727,7 @@
         <f t="shared" si="1"/>
         <v>lollipopt_sweet</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -8762,7 +8753,7 @@
         <f t="shared" si="1"/>
         <v>gummyt_sweet</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -8788,7 +8779,7 @@
         <f t="shared" ref="B69:B132" si="2">C69&amp;D69</f>
         <v>cupcaket_sweet</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -8814,7 +8805,7 @@
         <f t="shared" si="2"/>
         <v>mousset_sweet</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -8840,7 +8831,7 @@
         <f t="shared" si="2"/>
         <v>toffeet_sweet</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -8866,7 +8857,7 @@
         <f t="shared" si="2"/>
         <v>nougatt_sweet</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -8892,7 +8883,7 @@
         <f t="shared" si="2"/>
         <v>eggrollt_sweet</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -8918,7 +8909,7 @@
         <f t="shared" si="2"/>
         <v>choco_bart_sweet</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C74" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -8944,7 +8935,7 @@
         <f t="shared" si="2"/>
         <v>eclairt_sweet</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -8957,7 +8948,7 @@
         <f>VLOOKUP(C75,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G75" s="30" t="str">
+      <c r="G75" s="28" t="str">
         <f>VLOOKUP(C75,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -8970,7 +8961,7 @@
         <f t="shared" si="2"/>
         <v>tanghulut_sweet</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -8983,7 +8974,7 @@
         <f>VLOOKUP(C76,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G76" s="30" t="str">
+      <c r="G76" s="28" t="str">
         <f>VLOOKUP(C76,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9009,7 +9000,7 @@
         <f>VLOOKUP(C77,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G77" s="30" t="str">
+      <c r="G77" s="28" t="str">
         <f>VLOOKUP(C77,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9035,7 +9026,7 @@
         <f>VLOOKUP(C78,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G78" s="30" t="str">
+      <c r="G78" s="28" t="str">
         <f>VLOOKUP(C78,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9061,7 +9052,7 @@
         <f>VLOOKUP(C79,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G79" s="30" t="str">
+      <c r="G79" s="28" t="str">
         <f>VLOOKUP(C79,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9087,7 +9078,7 @@
         <f>VLOOKUP(C80,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G80" s="30" t="str">
+      <c r="G80" s="28" t="str">
         <f>VLOOKUP(C80,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9113,7 +9104,7 @@
         <f>VLOOKUP(C81,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G81" s="30" t="str">
+      <c r="G81" s="28" t="str">
         <f>VLOOKUP(C81,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9139,7 +9130,7 @@
         <f>VLOOKUP(C82,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G82" s="30" t="str">
+      <c r="G82" s="28" t="str">
         <f>VLOOKUP(C82,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9165,7 +9156,7 @@
         <f>VLOOKUP(C83,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G83" s="30" t="str">
+      <c r="G83" s="28" t="str">
         <f>VLOOKUP(C83,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9191,7 +9182,7 @@
         <f>VLOOKUP(C84,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G84" s="30" t="str">
+      <c r="G84" s="28" t="str">
         <f>VLOOKUP(C84,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9217,7 +9208,7 @@
         <f>VLOOKUP(C85,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G85" s="30" t="str">
+      <c r="G85" s="28" t="str">
         <f>VLOOKUP(C85,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9243,7 +9234,7 @@
         <f>VLOOKUP(C86,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G86" s="30" t="str">
+      <c r="G86" s="28" t="str">
         <f>VLOOKUP(C86,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9269,7 +9260,7 @@
         <f>VLOOKUP(C87,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G87" s="30" t="str">
+      <c r="G87" s="28" t="str">
         <f>VLOOKUP(C87,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9295,7 +9286,7 @@
         <f>VLOOKUP(C88,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G88" s="30" t="str">
+      <c r="G88" s="28" t="str">
         <f>VLOOKUP(C88,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9321,7 +9312,7 @@
         <f>VLOOKUP(C89,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G89" s="30" t="str">
+      <c r="G89" s="28" t="str">
         <f>VLOOKUP(C89,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9347,7 +9338,7 @@
         <f>VLOOKUP(C90,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G90" s="30" t="str">
+      <c r="G90" s="28" t="str">
         <f>VLOOKUP(C90,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9373,7 +9364,7 @@
         <f>VLOOKUP(C91,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G91" s="30" t="str">
+      <c r="G91" s="28" t="str">
         <f>VLOOKUP(C91,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9399,7 +9390,7 @@
         <f>VLOOKUP(C92,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G92" s="30" t="str">
+      <c r="G92" s="28" t="str">
         <f>VLOOKUP(C92,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9425,7 +9416,7 @@
         <f>VLOOKUP(C93,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G93" s="30" t="str">
+      <c r="G93" s="28" t="str">
         <f>VLOOKUP(C93,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9451,7 +9442,7 @@
         <f>VLOOKUP(C94,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G94" s="30" t="str">
+      <c r="G94" s="28" t="str">
         <f>VLOOKUP(C94,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9477,7 +9468,7 @@
         <f>VLOOKUP(C95,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G95" s="30" t="str">
+      <c r="G95" s="28" t="str">
         <f>VLOOKUP(C95,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9503,7 +9494,7 @@
         <f>VLOOKUP(C96,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G96" s="30" t="str">
+      <c r="G96" s="28" t="str">
         <f>VLOOKUP(C96,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9529,7 +9520,7 @@
         <f>VLOOKUP(C97,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>270</v>
       </c>
-      <c r="G97" s="30" t="str">
+      <c r="G97" s="28" t="str">
         <f>VLOOKUP(C97,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -9594,7 +9585,7 @@
         <f t="shared" si="2"/>
         <v>cookiet_bitter</v>
       </c>
-      <c r="C100" s="28" t="s">
+      <c r="C100" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -9620,7 +9611,7 @@
         <f t="shared" si="2"/>
         <v>macaront_bitter</v>
       </c>
-      <c r="C101" s="28" t="s">
+      <c r="C101" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -9646,7 +9637,7 @@
         <f t="shared" si="2"/>
         <v>puddingt_bitter</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -9672,7 +9663,7 @@
         <f t="shared" si="2"/>
         <v>pufft_bitter</v>
       </c>
-      <c r="C103" s="29" t="s">
+      <c r="C103" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -9698,7 +9689,7 @@
         <f t="shared" si="2"/>
         <v>eggtartt_bitter</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -9724,7 +9715,7 @@
         <f t="shared" si="2"/>
         <v>mochit_bitter</v>
       </c>
-      <c r="C105" s="29" t="s">
+      <c r="C105" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -9750,7 +9741,7 @@
         <f t="shared" si="2"/>
         <v>daifukut_bitter</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -9776,7 +9767,7 @@
         <f t="shared" si="2"/>
         <v>choco_candyt_bitter</v>
       </c>
-      <c r="C107" s="29" t="s">
+      <c r="C107" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -9802,7 +9793,7 @@
         <f t="shared" si="2"/>
         <v>jellyt_bitter</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -9828,7 +9819,7 @@
         <f t="shared" si="2"/>
         <v>cream_cellt_bitter</v>
       </c>
-      <c r="C109" s="29" t="s">
+      <c r="C109" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -9854,7 +9845,7 @@
         <f t="shared" si="2"/>
         <v>sugarbeant_bitter</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C110" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -9880,7 +9871,7 @@
         <f t="shared" si="2"/>
         <v>gold_chocot_bitter</v>
       </c>
-      <c r="C111" s="29" t="s">
+      <c r="C111" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -9906,7 +9897,7 @@
         <f t="shared" si="2"/>
         <v>milk_slicet_bitter</v>
       </c>
-      <c r="C112" s="29" t="s">
+      <c r="C112" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -9932,7 +9923,7 @@
         <f t="shared" si="2"/>
         <v>sundaet_bitter</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C113" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -9958,7 +9949,7 @@
         <f t="shared" si="2"/>
         <v>conet_bitter</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -9984,7 +9975,7 @@
         <f t="shared" si="2"/>
         <v>lollipopt_bitter</v>
       </c>
-      <c r="C115" s="29" t="s">
+      <c r="C115" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -10010,7 +10001,7 @@
         <f t="shared" si="2"/>
         <v>gummyt_bitter</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="C116" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -10036,7 +10027,7 @@
         <f t="shared" si="2"/>
         <v>cupcaket_bitter</v>
       </c>
-      <c r="C117" s="29" t="s">
+      <c r="C117" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -10062,7 +10053,7 @@
         <f t="shared" si="2"/>
         <v>mousset_bitter</v>
       </c>
-      <c r="C118" s="29" t="s">
+      <c r="C118" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -10088,7 +10079,7 @@
         <f t="shared" si="2"/>
         <v>toffeet_bitter</v>
       </c>
-      <c r="C119" s="29" t="s">
+      <c r="C119" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -10114,7 +10105,7 @@
         <f t="shared" si="2"/>
         <v>nougatt_bitter</v>
       </c>
-      <c r="C120" s="29" t="s">
+      <c r="C120" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -10140,7 +10131,7 @@
         <f t="shared" si="2"/>
         <v>eggrollt_bitter</v>
       </c>
-      <c r="C121" s="29" t="s">
+      <c r="C121" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -10166,7 +10157,7 @@
         <f t="shared" si="2"/>
         <v>choco_bart_bitter</v>
       </c>
-      <c r="C122" s="28" t="s">
+      <c r="C122" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -10179,7 +10170,7 @@
         <f>VLOOKUP(C122,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G122" s="30" t="str">
+      <c r="G122" s="28" t="str">
         <f>VLOOKUP(C122,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10192,7 +10183,7 @@
         <f t="shared" si="2"/>
         <v>eclairt_bitter</v>
       </c>
-      <c r="C123" s="29" t="s">
+      <c r="C123" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -10205,7 +10196,7 @@
         <f>VLOOKUP(C123,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G123" s="30" t="str">
+      <c r="G123" s="28" t="str">
         <f>VLOOKUP(C123,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10218,7 +10209,7 @@
         <f t="shared" si="2"/>
         <v>tanghulut_bitter</v>
       </c>
-      <c r="C124" s="29" t="s">
+      <c r="C124" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -10231,7 +10222,7 @@
         <f>VLOOKUP(C124,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G124" s="30" t="str">
+      <c r="G124" s="28" t="str">
         <f>VLOOKUP(C124,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10257,7 +10248,7 @@
         <f>VLOOKUP(C125,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G125" s="30" t="str">
+      <c r="G125" s="28" t="str">
         <f>VLOOKUP(C125,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10283,7 +10274,7 @@
         <f>VLOOKUP(C126,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G126" s="30" t="str">
+      <c r="G126" s="28" t="str">
         <f>VLOOKUP(C126,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10309,7 +10300,7 @@
         <f>VLOOKUP(C127,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G127" s="30" t="str">
+      <c r="G127" s="28" t="str">
         <f>VLOOKUP(C127,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10335,7 +10326,7 @@
         <f>VLOOKUP(C128,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G128" s="30" t="str">
+      <c r="G128" s="28" t="str">
         <f>VLOOKUP(C128,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10361,7 +10352,7 @@
         <f>VLOOKUP(C129,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G129" s="30" t="str">
+      <c r="G129" s="28" t="str">
         <f>VLOOKUP(C129,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10387,7 +10378,7 @@
         <f>VLOOKUP(C130,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G130" s="30" t="str">
+      <c r="G130" s="28" t="str">
         <f>VLOOKUP(C130,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10413,7 +10404,7 @@
         <f>VLOOKUP(C131,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G131" s="30" t="str">
+      <c r="G131" s="28" t="str">
         <f>VLOOKUP(C131,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10439,7 +10430,7 @@
         <f>VLOOKUP(C132,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G132" s="30" t="str">
+      <c r="G132" s="28" t="str">
         <f>VLOOKUP(C132,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10465,7 +10456,7 @@
         <f>VLOOKUP(C133,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G133" s="30" t="str">
+      <c r="G133" s="28" t="str">
         <f>VLOOKUP(C133,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10491,7 +10482,7 @@
         <f>VLOOKUP(C134,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G134" s="30" t="str">
+      <c r="G134" s="28" t="str">
         <f>VLOOKUP(C134,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10517,7 +10508,7 @@
         <f>VLOOKUP(C135,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G135" s="30" t="str">
+      <c r="G135" s="28" t="str">
         <f>VLOOKUP(C135,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10543,7 +10534,7 @@
         <f>VLOOKUP(C136,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G136" s="30" t="str">
+      <c r="G136" s="28" t="str">
         <f>VLOOKUP(C136,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10569,7 +10560,7 @@
         <f>VLOOKUP(C137,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G137" s="30" t="str">
+      <c r="G137" s="28" t="str">
         <f>VLOOKUP(C137,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10595,7 +10586,7 @@
         <f>VLOOKUP(C138,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G138" s="30" t="str">
+      <c r="G138" s="28" t="str">
         <f>VLOOKUP(C138,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10621,7 +10612,7 @@
         <f>VLOOKUP(C139,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G139" s="30" t="str">
+      <c r="G139" s="28" t="str">
         <f>VLOOKUP(C139,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10647,7 +10638,7 @@
         <f>VLOOKUP(C140,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G140" s="30" t="str">
+      <c r="G140" s="28" t="str">
         <f>VLOOKUP(C140,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10673,7 +10664,7 @@
         <f>VLOOKUP(C141,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G141" s="30" t="str">
+      <c r="G141" s="28" t="str">
         <f>VLOOKUP(C141,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10699,7 +10690,7 @@
         <f>VLOOKUP(C142,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G142" s="30" t="str">
+      <c r="G142" s="28" t="str">
         <f>VLOOKUP(C142,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10725,7 +10716,7 @@
         <f>VLOOKUP(C143,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G143" s="30" t="str">
+      <c r="G143" s="28" t="str">
         <f>VLOOKUP(C143,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10751,7 +10742,7 @@
         <f>VLOOKUP(C144,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G144" s="30" t="str">
+      <c r="G144" s="28" t="str">
         <f>VLOOKUP(C144,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10842,7 +10833,7 @@
         <f t="shared" si="3"/>
         <v>cookiet_rust</v>
       </c>
-      <c r="C148" s="28" t="s">
+      <c r="C148" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -10868,7 +10859,7 @@
         <f t="shared" si="3"/>
         <v>macaront_rust</v>
       </c>
-      <c r="C149" s="28" t="s">
+      <c r="C149" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -10894,7 +10885,7 @@
         <f t="shared" si="3"/>
         <v>puddingt_rust</v>
       </c>
-      <c r="C150" s="29" t="s">
+      <c r="C150" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D150" s="1" t="s">
@@ -10920,7 +10911,7 @@
         <f t="shared" si="3"/>
         <v>pufft_rust</v>
       </c>
-      <c r="C151" s="29" t="s">
+      <c r="C151" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -10946,7 +10937,7 @@
         <f t="shared" si="3"/>
         <v>eggtartt_rust</v>
       </c>
-      <c r="C152" s="29" t="s">
+      <c r="C152" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D152" s="1" t="s">
@@ -10972,7 +10963,7 @@
         <f t="shared" si="3"/>
         <v>mochit_rust</v>
       </c>
-      <c r="C153" s="29" t="s">
+      <c r="C153" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -10998,7 +10989,7 @@
         <f t="shared" si="3"/>
         <v>daifukut_rust</v>
       </c>
-      <c r="C154" s="29" t="s">
+      <c r="C154" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D154" s="1" t="s">
@@ -11024,7 +11015,7 @@
         <f t="shared" si="3"/>
         <v>choco_candyt_rust</v>
       </c>
-      <c r="C155" s="29" t="s">
+      <c r="C155" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D155" s="1" t="s">
@@ -11050,7 +11041,7 @@
         <f t="shared" si="3"/>
         <v>jellyt_rust</v>
       </c>
-      <c r="C156" s="29" t="s">
+      <c r="C156" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D156" s="1" t="s">
@@ -11076,7 +11067,7 @@
         <f t="shared" si="3"/>
         <v>cream_cellt_rust</v>
       </c>
-      <c r="C157" s="29" t="s">
+      <c r="C157" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D157" s="1" t="s">
@@ -11102,7 +11093,7 @@
         <f t="shared" si="3"/>
         <v>sugarbeant_rust</v>
       </c>
-      <c r="C158" s="29" t="s">
+      <c r="C158" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -11128,7 +11119,7 @@
         <f t="shared" si="3"/>
         <v>gold_chocot_rust</v>
       </c>
-      <c r="C159" s="29" t="s">
+      <c r="C159" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D159" s="1" t="s">
@@ -11154,7 +11145,7 @@
         <f t="shared" si="3"/>
         <v>milk_slicet_rust</v>
       </c>
-      <c r="C160" s="29" t="s">
+      <c r="C160" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D160" s="1" t="s">
@@ -11180,7 +11171,7 @@
         <f t="shared" si="3"/>
         <v>sundaet_rust</v>
       </c>
-      <c r="C161" s="29" t="s">
+      <c r="C161" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D161" s="1" t="s">
@@ -11206,7 +11197,7 @@
         <f t="shared" si="3"/>
         <v>conet_rust</v>
       </c>
-      <c r="C162" s="29" t="s">
+      <c r="C162" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D162" s="1" t="s">
@@ -11232,7 +11223,7 @@
         <f t="shared" si="3"/>
         <v>lollipopt_rust</v>
       </c>
-      <c r="C163" s="29" t="s">
+      <c r="C163" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D163" s="1" t="s">
@@ -11258,7 +11249,7 @@
         <f t="shared" si="3"/>
         <v>gummyt_rust</v>
       </c>
-      <c r="C164" s="29" t="s">
+      <c r="C164" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D164" s="1" t="s">
@@ -11284,7 +11275,7 @@
         <f t="shared" si="3"/>
         <v>cupcaket_rust</v>
       </c>
-      <c r="C165" s="29" t="s">
+      <c r="C165" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -11310,7 +11301,7 @@
         <f t="shared" si="3"/>
         <v>mousset_rust</v>
       </c>
-      <c r="C166" s="29" t="s">
+      <c r="C166" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D166" s="1" t="s">
@@ -11336,7 +11327,7 @@
         <f t="shared" si="3"/>
         <v>toffeet_rust</v>
       </c>
-      <c r="C167" s="29" t="s">
+      <c r="C167" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -11362,7 +11353,7 @@
         <f t="shared" si="3"/>
         <v>nougatt_rust</v>
       </c>
-      <c r="C168" s="29" t="s">
+      <c r="C168" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -11388,7 +11379,7 @@
         <f t="shared" si="3"/>
         <v>eggrollt_rust</v>
       </c>
-      <c r="C169" s="29" t="s">
+      <c r="C169" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -11401,7 +11392,7 @@
         <f>VLOOKUP(C169,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G169" s="30" t="str">
+      <c r="G169" s="28" t="str">
         <f>VLOOKUP(C169,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11414,7 +11405,7 @@
         <f t="shared" si="3"/>
         <v>choco_bart_rust</v>
       </c>
-      <c r="C170" s="28" t="s">
+      <c r="C170" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D170" s="1" t="s">
@@ -11427,7 +11418,7 @@
         <f>VLOOKUP(C170,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G170" s="30" t="str">
+      <c r="G170" s="28" t="str">
         <f>VLOOKUP(C170,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11440,7 +11431,7 @@
         <f t="shared" si="3"/>
         <v>eclairt_rust</v>
       </c>
-      <c r="C171" s="29" t="s">
+      <c r="C171" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D171" s="1" t="s">
@@ -11453,7 +11444,7 @@
         <f>VLOOKUP(C171,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G171" s="30" t="str">
+      <c r="G171" s="28" t="str">
         <f>VLOOKUP(C171,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11466,7 +11457,7 @@
         <f t="shared" si="3"/>
         <v>tanghulut_rust</v>
       </c>
-      <c r="C172" s="29" t="s">
+      <c r="C172" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -11479,7 +11470,7 @@
         <f>VLOOKUP(C172,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G172" s="30" t="str">
+      <c r="G172" s="28" t="str">
         <f>VLOOKUP(C172,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11505,7 +11496,7 @@
         <f>VLOOKUP(C173,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G173" s="30" t="str">
+      <c r="G173" s="28" t="str">
         <f>VLOOKUP(C173,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11531,7 +11522,7 @@
         <f>VLOOKUP(C174,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G174" s="30" t="str">
+      <c r="G174" s="28" t="str">
         <f>VLOOKUP(C174,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11557,7 +11548,7 @@
         <f>VLOOKUP(C175,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G175" s="30" t="str">
+      <c r="G175" s="28" t="str">
         <f>VLOOKUP(C175,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11583,7 +11574,7 @@
         <f>VLOOKUP(C176,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G176" s="30" t="str">
+      <c r="G176" s="28" t="str">
         <f>VLOOKUP(C176,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11609,7 +11600,7 @@
         <f>VLOOKUP(C177,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G177" s="30" t="str">
+      <c r="G177" s="28" t="str">
         <f>VLOOKUP(C177,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11635,7 +11626,7 @@
         <f>VLOOKUP(C178,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G178" s="30" t="str">
+      <c r="G178" s="28" t="str">
         <f>VLOOKUP(C178,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11661,7 +11652,7 @@
         <f>VLOOKUP(C179,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G179" s="30" t="str">
+      <c r="G179" s="28" t="str">
         <f>VLOOKUP(C179,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11687,7 +11678,7 @@
         <f>VLOOKUP(C180,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G180" s="30" t="str">
+      <c r="G180" s="28" t="str">
         <f>VLOOKUP(C180,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11713,7 +11704,7 @@
         <f>VLOOKUP(C181,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G181" s="30" t="str">
+      <c r="G181" s="28" t="str">
         <f>VLOOKUP(C181,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11739,7 +11730,7 @@
         <f>VLOOKUP(C182,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G182" s="30" t="str">
+      <c r="G182" s="28" t="str">
         <f>VLOOKUP(C182,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11765,7 +11756,7 @@
         <f>VLOOKUP(C183,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G183" s="30" t="str">
+      <c r="G183" s="28" t="str">
         <f>VLOOKUP(C183,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11791,7 +11782,7 @@
         <f>VLOOKUP(C184,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G184" s="30" t="str">
+      <c r="G184" s="28" t="str">
         <f>VLOOKUP(C184,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11817,7 +11808,7 @@
         <f>VLOOKUP(C185,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G185" s="30" t="str">
+      <c r="G185" s="28" t="str">
         <f>VLOOKUP(C185,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11843,7 +11834,7 @@
         <f>VLOOKUP(C186,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G186" s="30" t="str">
+      <c r="G186" s="28" t="str">
         <f>VLOOKUP(C186,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11869,7 +11860,7 @@
         <f>VLOOKUP(C187,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G187" s="30" t="str">
+      <c r="G187" s="28" t="str">
         <f>VLOOKUP(C187,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11895,7 +11886,7 @@
         <f>VLOOKUP(C188,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G188" s="30" t="str">
+      <c r="G188" s="28" t="str">
         <f>VLOOKUP(C188,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11921,7 +11912,7 @@
         <f>VLOOKUP(C189,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G189" s="30" t="str">
+      <c r="G189" s="28" t="str">
         <f>VLOOKUP(C189,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11947,7 +11938,7 @@
         <f>VLOOKUP(C190,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G190" s="30" t="str">
+      <c r="G190" s="28" t="str">
         <f>VLOOKUP(C190,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11973,7 +11964,7 @@
         <f>VLOOKUP(C191,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G191" s="30" t="str">
+      <c r="G191" s="28" t="str">
         <f>VLOOKUP(C191,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -12090,7 +12081,7 @@
         <f t="shared" si="3"/>
         <v>cookiet_numb</v>
       </c>
-      <c r="C196" s="28" t="s">
+      <c r="C196" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D196" s="1" t="s">
@@ -12116,7 +12107,7 @@
         <f t="shared" si="3"/>
         <v>macaront_numb</v>
       </c>
-      <c r="C197" s="28" t="s">
+      <c r="C197" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D197" s="1" t="s">
@@ -12142,7 +12133,7 @@
         <f t="shared" ref="B198:B261" si="4">C198&amp;D198</f>
         <v>puddingt_numb</v>
       </c>
-      <c r="C198" s="29" t="s">
+      <c r="C198" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -12168,7 +12159,7 @@
         <f t="shared" si="4"/>
         <v>pufft_numb</v>
       </c>
-      <c r="C199" s="29" t="s">
+      <c r="C199" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D199" s="1" t="s">
@@ -12194,7 +12185,7 @@
         <f t="shared" si="4"/>
         <v>eggtartt_numb</v>
       </c>
-      <c r="C200" s="29" t="s">
+      <c r="C200" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D200" s="1" t="s">
@@ -12220,7 +12211,7 @@
         <f t="shared" si="4"/>
         <v>mochit_numb</v>
       </c>
-      <c r="C201" s="29" t="s">
+      <c r="C201" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -12246,7 +12237,7 @@
         <f t="shared" si="4"/>
         <v>daifukut_numb</v>
       </c>
-      <c r="C202" s="29" t="s">
+      <c r="C202" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D202" s="1" t="s">
@@ -12272,7 +12263,7 @@
         <f t="shared" si="4"/>
         <v>choco_candyt_numb</v>
       </c>
-      <c r="C203" s="29" t="s">
+      <c r="C203" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D203" s="1" t="s">
@@ -12298,7 +12289,7 @@
         <f t="shared" si="4"/>
         <v>jellyt_numb</v>
       </c>
-      <c r="C204" s="29" t="s">
+      <c r="C204" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D204" s="1" t="s">
@@ -12324,7 +12315,7 @@
         <f t="shared" si="4"/>
         <v>cream_cellt_numb</v>
       </c>
-      <c r="C205" s="29" t="s">
+      <c r="C205" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D205" s="1" t="s">
@@ -12350,7 +12341,7 @@
         <f t="shared" si="4"/>
         <v>sugarbeant_numb</v>
       </c>
-      <c r="C206" s="29" t="s">
+      <c r="C206" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D206" s="1" t="s">
@@ -12376,7 +12367,7 @@
         <f t="shared" si="4"/>
         <v>gold_chocot_numb</v>
       </c>
-      <c r="C207" s="29" t="s">
+      <c r="C207" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D207" s="1" t="s">
@@ -12402,7 +12393,7 @@
         <f t="shared" si="4"/>
         <v>milk_slicet_numb</v>
       </c>
-      <c r="C208" s="29" t="s">
+      <c r="C208" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D208" s="1" t="s">
@@ -12428,7 +12419,7 @@
         <f t="shared" si="4"/>
         <v>sundaet_numb</v>
       </c>
-      <c r="C209" s="29" t="s">
+      <c r="C209" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D209" s="1" t="s">
@@ -12454,7 +12445,7 @@
         <f t="shared" si="4"/>
         <v>conet_numb</v>
       </c>
-      <c r="C210" s="29" t="s">
+      <c r="C210" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D210" s="1" t="s">
@@ -12480,7 +12471,7 @@
         <f t="shared" si="4"/>
         <v>lollipopt_numb</v>
       </c>
-      <c r="C211" s="29" t="s">
+      <c r="C211" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D211" s="1" t="s">
@@ -12506,7 +12497,7 @@
         <f t="shared" si="4"/>
         <v>gummyt_numb</v>
       </c>
-      <c r="C212" s="29" t="s">
+      <c r="C212" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D212" s="1" t="s">
@@ -12532,7 +12523,7 @@
         <f t="shared" si="4"/>
         <v>cupcaket_numb</v>
       </c>
-      <c r="C213" s="29" t="s">
+      <c r="C213" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D213" s="1" t="s">
@@ -12558,7 +12549,7 @@
         <f t="shared" si="4"/>
         <v>mousset_numb</v>
       </c>
-      <c r="C214" s="29" t="s">
+      <c r="C214" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D214" s="1" t="s">
@@ -12584,7 +12575,7 @@
         <f t="shared" si="4"/>
         <v>toffeet_numb</v>
       </c>
-      <c r="C215" s="29" t="s">
+      <c r="C215" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D215" s="1" t="s">
@@ -12610,7 +12601,7 @@
         <f t="shared" si="4"/>
         <v>nougatt_numb</v>
       </c>
-      <c r="C216" s="29" t="s">
+      <c r="C216" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D216" s="1" t="s">
@@ -12623,7 +12614,7 @@
         <f>VLOOKUP(C216,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G216" s="30" t="str">
+      <c r="G216" s="28" t="str">
         <f>VLOOKUP(C216,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -12636,7 +12627,7 @@
         <f t="shared" si="4"/>
         <v>eggrollt_numb</v>
       </c>
-      <c r="C217" s="29" t="s">
+      <c r="C217" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D217" s="1" t="s">
@@ -12649,7 +12640,7 @@
         <f>VLOOKUP(C217,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G217" s="30" t="str">
+      <c r="G217" s="28" t="str">
         <f>VLOOKUP(C217,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -12662,7 +12653,7 @@
         <f t="shared" si="4"/>
         <v>choco_bart_numb</v>
       </c>
-      <c r="C218" s="28" t="s">
+      <c r="C218" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D218" s="1" t="s">
@@ -12675,7 +12666,7 @@
         <f>VLOOKUP(C218,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G218" s="30" t="str">
+      <c r="G218" s="28" t="str">
         <f>VLOOKUP(C218,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -12688,7 +12679,7 @@
         <f t="shared" si="4"/>
         <v>eclairt_numb</v>
       </c>
-      <c r="C219" s="29" t="s">
+      <c r="C219" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D219" s="1" t="s">
@@ -12701,7 +12692,7 @@
         <f>VLOOKUP(C219,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G219" s="30" t="str">
+      <c r="G219" s="28" t="str">
         <f>VLOOKUP(C219,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -12714,7 +12705,7 @@
         <f t="shared" si="4"/>
         <v>tanghulut_numb</v>
       </c>
-      <c r="C220" s="29" t="s">
+      <c r="C220" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D220" s="1" t="s">
@@ -12727,7 +12718,7 @@
         <f>VLOOKUP(C220,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G220" s="30" t="str">
+      <c r="G220" s="28" t="str">
         <f>VLOOKUP(C220,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -12753,7 +12744,7 @@
         <f>VLOOKUP(C221,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G221" s="30" t="str">
+      <c r="G221" s="28" t="str">
         <f>VLOOKUP(C221,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12779,7 +12770,7 @@
         <f>VLOOKUP(C222,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G222" s="30" t="str">
+      <c r="G222" s="28" t="str">
         <f>VLOOKUP(C222,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12805,7 +12796,7 @@
         <f>VLOOKUP(C223,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G223" s="30" t="str">
+      <c r="G223" s="28" t="str">
         <f>VLOOKUP(C223,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12831,7 +12822,7 @@
         <f>VLOOKUP(C224,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G224" s="30" t="str">
+      <c r="G224" s="28" t="str">
         <f>VLOOKUP(C224,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12857,7 +12848,7 @@
         <f>VLOOKUP(C225,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G225" s="30" t="str">
+      <c r="G225" s="28" t="str">
         <f>VLOOKUP(C225,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12883,7 +12874,7 @@
         <f>VLOOKUP(C226,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G226" s="30" t="str">
+      <c r="G226" s="28" t="str">
         <f>VLOOKUP(C226,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12909,7 +12900,7 @@
         <f>VLOOKUP(C227,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G227" s="30" t="str">
+      <c r="G227" s="28" t="str">
         <f>VLOOKUP(C227,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12935,7 +12926,7 @@
         <f>VLOOKUP(C228,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G228" s="30" t="str">
+      <c r="G228" s="28" t="str">
         <f>VLOOKUP(C228,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12961,7 +12952,7 @@
         <f>VLOOKUP(C229,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G229" s="30" t="str">
+      <c r="G229" s="28" t="str">
         <f>VLOOKUP(C229,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12987,7 +12978,7 @@
         <f>VLOOKUP(C230,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G230" s="30" t="str">
+      <c r="G230" s="28" t="str">
         <f>VLOOKUP(C230,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13013,7 +13004,7 @@
         <f>VLOOKUP(C231,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G231" s="30" t="str">
+      <c r="G231" s="28" t="str">
         <f>VLOOKUP(C231,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13039,7 +13030,7 @@
         <f>VLOOKUP(C232,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G232" s="30" t="str">
+      <c r="G232" s="28" t="str">
         <f>VLOOKUP(C232,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13065,7 +13056,7 @@
         <f>VLOOKUP(C233,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G233" s="30" t="str">
+      <c r="G233" s="28" t="str">
         <f>VLOOKUP(C233,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13091,7 +13082,7 @@
         <f>VLOOKUP(C234,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G234" s="30" t="str">
+      <c r="G234" s="28" t="str">
         <f>VLOOKUP(C234,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13117,7 +13108,7 @@
         <f>VLOOKUP(C235,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G235" s="30" t="str">
+      <c r="G235" s="28" t="str">
         <f>VLOOKUP(C235,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13143,7 +13134,7 @@
         <f>VLOOKUP(C236,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G236" s="30" t="str">
+      <c r="G236" s="28" t="str">
         <f>VLOOKUP(C236,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13169,7 +13160,7 @@
         <f>VLOOKUP(C237,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G237" s="30" t="str">
+      <c r="G237" s="28" t="str">
         <f>VLOOKUP(C237,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13195,7 +13186,7 @@
         <f>VLOOKUP(C238,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G238" s="30" t="str">
+      <c r="G238" s="28" t="str">
         <f>VLOOKUP(C238,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13341,7 +13332,7 @@
         <f t="shared" si="4"/>
         <v>cookiet_sour</v>
       </c>
-      <c r="C244" s="28" t="s">
+      <c r="C244" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D244" s="1" t="s">
@@ -13367,7 +13358,7 @@
         <f t="shared" si="4"/>
         <v>macaront_sour</v>
       </c>
-      <c r="C245" s="28" t="s">
+      <c r="C245" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D245" s="1" t="s">
@@ -13393,7 +13384,7 @@
         <f t="shared" si="4"/>
         <v>puddingt_sour</v>
       </c>
-      <c r="C246" s="29" t="s">
+      <c r="C246" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D246" s="1" t="s">
@@ -13419,7 +13410,7 @@
         <f t="shared" si="4"/>
         <v>pufft_sour</v>
       </c>
-      <c r="C247" s="29" t="s">
+      <c r="C247" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D247" s="1" t="s">
@@ -13445,7 +13436,7 @@
         <f t="shared" si="4"/>
         <v>eggtartt_sour</v>
       </c>
-      <c r="C248" s="29" t="s">
+      <c r="C248" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D248" s="1" t="s">
@@ -13471,7 +13462,7 @@
         <f t="shared" si="4"/>
         <v>mochit_sour</v>
       </c>
-      <c r="C249" s="29" t="s">
+      <c r="C249" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D249" s="1" t="s">
@@ -13497,7 +13488,7 @@
         <f t="shared" si="4"/>
         <v>daifukut_sour</v>
       </c>
-      <c r="C250" s="29" t="s">
+      <c r="C250" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D250" s="1" t="s">
@@ -13523,7 +13514,7 @@
         <f t="shared" si="4"/>
         <v>choco_candyt_sour</v>
       </c>
-      <c r="C251" s="29" t="s">
+      <c r="C251" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D251" s="1" t="s">
@@ -13549,7 +13540,7 @@
         <f t="shared" si="4"/>
         <v>jellyt_sour</v>
       </c>
-      <c r="C252" s="29" t="s">
+      <c r="C252" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D252" s="1" t="s">
@@ -13575,7 +13566,7 @@
         <f t="shared" si="4"/>
         <v>cream_cellt_sour</v>
       </c>
-      <c r="C253" s="29" t="s">
+      <c r="C253" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D253" s="1" t="s">
@@ -13601,7 +13592,7 @@
         <f t="shared" si="4"/>
         <v>sugarbeant_sour</v>
       </c>
-      <c r="C254" s="29" t="s">
+      <c r="C254" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D254" s="1" t="s">
@@ -13627,7 +13618,7 @@
         <f t="shared" si="4"/>
         <v>gold_chocot_sour</v>
       </c>
-      <c r="C255" s="29" t="s">
+      <c r="C255" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D255" s="1" t="s">
@@ -13653,7 +13644,7 @@
         <f t="shared" si="4"/>
         <v>milk_slicet_sour</v>
       </c>
-      <c r="C256" s="29" t="s">
+      <c r="C256" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D256" s="1" t="s">
@@ -13679,7 +13670,7 @@
         <f t="shared" si="4"/>
         <v>sundaet_sour</v>
       </c>
-      <c r="C257" s="29" t="s">
+      <c r="C257" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D257" s="1" t="s">
@@ -13705,7 +13696,7 @@
         <f t="shared" si="4"/>
         <v>conet_sour</v>
       </c>
-      <c r="C258" s="29" t="s">
+      <c r="C258" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D258" s="1" t="s">
@@ -13731,7 +13722,7 @@
         <f t="shared" si="4"/>
         <v>lollipopt_sour</v>
       </c>
-      <c r="C259" s="29" t="s">
+      <c r="C259" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D259" s="1" t="s">
@@ -13757,7 +13748,7 @@
         <f t="shared" si="4"/>
         <v>gummyt_sour</v>
       </c>
-      <c r="C260" s="29" t="s">
+      <c r="C260" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D260" s="1" t="s">
@@ -13783,7 +13774,7 @@
         <f t="shared" si="4"/>
         <v>cupcaket_sour</v>
       </c>
-      <c r="C261" s="29" t="s">
+      <c r="C261" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D261" s="1" t="s">
@@ -13809,7 +13800,7 @@
         <f t="shared" ref="B262:B325" si="5">C262&amp;D262</f>
         <v>mousset_sour</v>
       </c>
-      <c r="C262" s="29" t="s">
+      <c r="C262" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D262" s="1" t="s">
@@ -13835,7 +13826,7 @@
         <f t="shared" si="5"/>
         <v>toffeet_sour</v>
       </c>
-      <c r="C263" s="29" t="s">
+      <c r="C263" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D263" s="1" t="s">
@@ -13848,7 +13839,7 @@
         <f>VLOOKUP(C263,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G263" s="30" t="str">
+      <c r="G263" s="28" t="str">
         <f>VLOOKUP(C263,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -13861,7 +13852,7 @@
         <f t="shared" si="5"/>
         <v>nougatt_sour</v>
       </c>
-      <c r="C264" s="29" t="s">
+      <c r="C264" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D264" s="1" t="s">
@@ -13874,7 +13865,7 @@
         <f>VLOOKUP(C264,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G264" s="30" t="str">
+      <c r="G264" s="28" t="str">
         <f>VLOOKUP(C264,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -13887,7 +13878,7 @@
         <f t="shared" si="5"/>
         <v>eggrollt_sour</v>
       </c>
-      <c r="C265" s="29" t="s">
+      <c r="C265" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D265" s="1" t="s">
@@ -13900,7 +13891,7 @@
         <f>VLOOKUP(C265,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G265" s="30" t="str">
+      <c r="G265" s="28" t="str">
         <f>VLOOKUP(C265,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13913,7 +13904,7 @@
         <f t="shared" si="5"/>
         <v>choco_bart_sour</v>
       </c>
-      <c r="C266" s="28" t="s">
+      <c r="C266" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D266" s="1" t="s">
@@ -13926,7 +13917,7 @@
         <f>VLOOKUP(C266,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G266" s="30" t="str">
+      <c r="G266" s="28" t="str">
         <f>VLOOKUP(C266,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13939,7 +13930,7 @@
         <f t="shared" si="5"/>
         <v>eclairt_sour</v>
       </c>
-      <c r="C267" s="29" t="s">
+      <c r="C267" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D267" s="1" t="s">
@@ -13952,7 +13943,7 @@
         <f>VLOOKUP(C267,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G267" s="30" t="str">
+      <c r="G267" s="28" t="str">
         <f>VLOOKUP(C267,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13965,7 +13956,7 @@
         <f t="shared" si="5"/>
         <v>tanghulut_sour</v>
       </c>
-      <c r="C268" s="29" t="s">
+      <c r="C268" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D268" s="1" t="s">
@@ -13978,7 +13969,7 @@
         <f>VLOOKUP(C268,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G268" s="30" t="str">
+      <c r="G268" s="28" t="str">
         <f>VLOOKUP(C268,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -14004,7 +13995,7 @@
         <f>VLOOKUP(C269,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G269" s="30" t="str">
+      <c r="G269" s="28" t="str">
         <f>VLOOKUP(C269,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14030,7 +14021,7 @@
         <f>VLOOKUP(C270,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G270" s="30" t="str">
+      <c r="G270" s="28" t="str">
         <f>VLOOKUP(C270,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14056,7 +14047,7 @@
         <f>VLOOKUP(C271,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G271" s="30" t="str">
+      <c r="G271" s="28" t="str">
         <f>VLOOKUP(C271,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14082,7 +14073,7 @@
         <f>VLOOKUP(C272,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G272" s="30" t="str">
+      <c r="G272" s="28" t="str">
         <f>VLOOKUP(C272,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14108,7 +14099,7 @@
         <f>VLOOKUP(C273,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G273" s="30" t="str">
+      <c r="G273" s="28" t="str">
         <f>VLOOKUP(C273,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14134,7 +14125,7 @@
         <f>VLOOKUP(C274,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G274" s="30" t="str">
+      <c r="G274" s="28" t="str">
         <f>VLOOKUP(C274,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14160,7 +14151,7 @@
         <f>VLOOKUP(C275,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G275" s="30" t="str">
+      <c r="G275" s="28" t="str">
         <f>VLOOKUP(C275,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14186,7 +14177,7 @@
         <f>VLOOKUP(C276,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G276" s="30" t="str">
+      <c r="G276" s="28" t="str">
         <f>VLOOKUP(C276,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14212,7 +14203,7 @@
         <f>VLOOKUP(C277,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G277" s="30" t="str">
+      <c r="G277" s="28" t="str">
         <f>VLOOKUP(C277,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14238,7 +14229,7 @@
         <f>VLOOKUP(C278,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G278" s="30" t="str">
+      <c r="G278" s="28" t="str">
         <f>VLOOKUP(C278,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14264,7 +14255,7 @@
         <f>VLOOKUP(C279,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G279" s="30" t="str">
+      <c r="G279" s="28" t="str">
         <f>VLOOKUP(C279,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14290,7 +14281,7 @@
         <f>VLOOKUP(C280,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G280" s="30" t="str">
+      <c r="G280" s="28" t="str">
         <f>VLOOKUP(C280,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14316,7 +14307,7 @@
         <f>VLOOKUP(C281,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G281" s="30" t="str">
+      <c r="G281" s="28" t="str">
         <f>VLOOKUP(C281,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14342,7 +14333,7 @@
         <f>VLOOKUP(C282,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G282" s="30" t="str">
+      <c r="G282" s="28" t="str">
         <f>VLOOKUP(C282,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14368,7 +14359,7 @@
         <f>VLOOKUP(C283,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G283" s="30" t="str">
+      <c r="G283" s="28" t="str">
         <f>VLOOKUP(C283,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14394,7 +14385,7 @@
         <f>VLOOKUP(C284,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G284" s="30" t="str">
+      <c r="G284" s="28" t="str">
         <f>VLOOKUP(C284,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14420,7 +14411,7 @@
         <f>VLOOKUP(C285,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G285" s="30" t="str">
+      <c r="G285" s="28" t="str">
         <f>VLOOKUP(C285,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14589,7 +14580,7 @@
         <f t="shared" si="5"/>
         <v>cookiet_salty</v>
       </c>
-      <c r="C292" s="28" t="s">
+      <c r="C292" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D292" s="1" t="s">
@@ -14615,7 +14606,7 @@
         <f t="shared" si="5"/>
         <v>macaront_salty</v>
       </c>
-      <c r="C293" s="28" t="s">
+      <c r="C293" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D293" s="1" t="s">
@@ -14641,7 +14632,7 @@
         <f t="shared" si="5"/>
         <v>puddingt_salty</v>
       </c>
-      <c r="C294" s="29" t="s">
+      <c r="C294" s="9" t="s">
         <v>32</v>
       </c>
       <c r="D294" s="1" t="s">
@@ -14667,7 +14658,7 @@
         <f t="shared" si="5"/>
         <v>pufft_salty</v>
       </c>
-      <c r="C295" s="29" t="s">
+      <c r="C295" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D295" s="1" t="s">
@@ -14693,7 +14684,7 @@
         <f t="shared" si="5"/>
         <v>eggtartt_salty</v>
       </c>
-      <c r="C296" s="29" t="s">
+      <c r="C296" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D296" s="1" t="s">
@@ -14719,7 +14710,7 @@
         <f t="shared" si="5"/>
         <v>mochit_salty</v>
       </c>
-      <c r="C297" s="29" t="s">
+      <c r="C297" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D297" s="1" t="s">
@@ -14745,7 +14736,7 @@
         <f t="shared" si="5"/>
         <v>daifukut_salty</v>
       </c>
-      <c r="C298" s="29" t="s">
+      <c r="C298" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D298" s="1" t="s">
@@ -14771,7 +14762,7 @@
         <f t="shared" si="5"/>
         <v>choco_candyt_salty</v>
       </c>
-      <c r="C299" s="29" t="s">
+      <c r="C299" s="9" t="s">
         <v>47</v>
       </c>
       <c r="D299" s="1" t="s">
@@ -14797,7 +14788,7 @@
         <f t="shared" si="5"/>
         <v>jellyt_salty</v>
       </c>
-      <c r="C300" s="29" t="s">
+      <c r="C300" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D300" s="1" t="s">
@@ -14823,7 +14814,7 @@
         <f t="shared" si="5"/>
         <v>cream_cellt_salty</v>
       </c>
-      <c r="C301" s="29" t="s">
+      <c r="C301" s="9" t="s">
         <v>54</v>
       </c>
       <c r="D301" s="1" t="s">
@@ -14849,7 +14840,7 @@
         <f t="shared" si="5"/>
         <v>sugarbeant_salty</v>
       </c>
-      <c r="C302" s="29" t="s">
+      <c r="C302" s="9" t="s">
         <v>58</v>
       </c>
       <c r="D302" s="1" t="s">
@@ -14875,7 +14866,7 @@
         <f t="shared" si="5"/>
         <v>gold_chocot_salty</v>
       </c>
-      <c r="C303" s="29" t="s">
+      <c r="C303" s="9" t="s">
         <v>62</v>
       </c>
       <c r="D303" s="1" t="s">
@@ -14901,7 +14892,7 @@
         <f t="shared" si="5"/>
         <v>milk_slicet_salty</v>
       </c>
-      <c r="C304" s="29" t="s">
+      <c r="C304" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D304" s="1" t="s">
@@ -14927,7 +14918,7 @@
         <f t="shared" si="5"/>
         <v>sundaet_salty</v>
       </c>
-      <c r="C305" s="29" t="s">
+      <c r="C305" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D305" s="1" t="s">
@@ -14953,7 +14944,7 @@
         <f t="shared" si="5"/>
         <v>conet_salty</v>
       </c>
-      <c r="C306" s="29" t="s">
+      <c r="C306" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D306" s="1" t="s">
@@ -14979,7 +14970,7 @@
         <f t="shared" si="5"/>
         <v>lollipopt_salty</v>
       </c>
-      <c r="C307" s="29" t="s">
+      <c r="C307" s="9" t="s">
         <v>77</v>
       </c>
       <c r="D307" s="1" t="s">
@@ -15005,7 +14996,7 @@
         <f t="shared" si="5"/>
         <v>gummyt_salty</v>
       </c>
-      <c r="C308" s="29" t="s">
+      <c r="C308" s="9" t="s">
         <v>80</v>
       </c>
       <c r="D308" s="1" t="s">
@@ -15031,7 +15022,7 @@
         <f t="shared" si="5"/>
         <v>cupcaket_salty</v>
       </c>
-      <c r="C309" s="29" t="s">
+      <c r="C309" s="9" t="s">
         <v>83</v>
       </c>
       <c r="D309" s="1" t="s">
@@ -15057,7 +15048,7 @@
         <f t="shared" si="5"/>
         <v>mousset_salty</v>
       </c>
-      <c r="C310" s="29" t="s">
+      <c r="C310" s="9" t="s">
         <v>87</v>
       </c>
       <c r="D310" s="1" t="s">
@@ -15070,7 +15061,7 @@
         <f>VLOOKUP(C310,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G310" s="30" t="str">
+      <c r="G310" s="28" t="str">
         <f>VLOOKUP(C310,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -15083,7 +15074,7 @@
         <f t="shared" si="5"/>
         <v>toffeet_salty</v>
       </c>
-      <c r="C311" s="29" t="s">
+      <c r="C311" s="9" t="s">
         <v>94</v>
       </c>
       <c r="D311" s="1" t="s">
@@ -15096,7 +15087,7 @@
         <f>VLOOKUP(C311,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G311" s="30" t="str">
+      <c r="G311" s="28" t="str">
         <f>VLOOKUP(C311,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -15109,7 +15100,7 @@
         <f t="shared" si="5"/>
         <v>nougatt_salty</v>
       </c>
-      <c r="C312" s="29" t="s">
+      <c r="C312" s="9" t="s">
         <v>101</v>
       </c>
       <c r="D312" s="1" t="s">
@@ -15122,7 +15113,7 @@
         <f>VLOOKUP(C312,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G312" s="30" t="str">
+      <c r="G312" s="28" t="str">
         <f>VLOOKUP(C312,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -15135,7 +15126,7 @@
         <f t="shared" si="5"/>
         <v>eggrollt_salty</v>
       </c>
-      <c r="C313" s="29" t="s">
+      <c r="C313" s="9" t="s">
         <v>108</v>
       </c>
       <c r="D313" s="1" t="s">
@@ -15148,7 +15139,7 @@
         <f>VLOOKUP(C313,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G313" s="30" t="str">
+      <c r="G313" s="28" t="str">
         <f>VLOOKUP(C313,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15161,7 +15152,7 @@
         <f t="shared" si="5"/>
         <v>choco_bart_salty</v>
       </c>
-      <c r="C314" s="28" t="s">
+      <c r="C314" s="9" t="s">
         <v>114</v>
       </c>
       <c r="D314" s="1" t="s">
@@ -15174,7 +15165,7 @@
         <f>VLOOKUP(C314,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G314" s="30" t="str">
+      <c r="G314" s="28" t="str">
         <f>VLOOKUP(C314,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15187,7 +15178,7 @@
         <f t="shared" si="5"/>
         <v>eclairt_salty</v>
       </c>
-      <c r="C315" s="29" t="s">
+      <c r="C315" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D315" s="1" t="s">
@@ -15200,7 +15191,7 @@
         <f>VLOOKUP(C315,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G315" s="30" t="str">
+      <c r="G315" s="28" t="str">
         <f>VLOOKUP(C315,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15213,7 +15204,7 @@
         <f t="shared" si="5"/>
         <v>tanghulut_salty</v>
       </c>
-      <c r="C316" s="29" t="s">
+      <c r="C316" s="9" t="s">
         <v>120</v>
       </c>
       <c r="D316" s="1" t="s">
@@ -15226,7 +15217,7 @@
         <f>VLOOKUP(C316,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G316" s="30" t="str">
+      <c r="G316" s="28" t="str">
         <f>VLOOKUP(C316,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15252,7 +15243,7 @@
         <f>VLOOKUP(C317,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G317" s="30" t="str">
+      <c r="G317" s="28" t="str">
         <f>VLOOKUP(C317,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15278,7 +15269,7 @@
         <f>VLOOKUP(C318,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G318" s="30" t="str">
+      <c r="G318" s="28" t="str">
         <f>VLOOKUP(C318,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15304,7 +15295,7 @@
         <f>VLOOKUP(C319,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G319" s="30" t="str">
+      <c r="G319" s="28" t="str">
         <f>VLOOKUP(C319,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15330,7 +15321,7 @@
         <f>VLOOKUP(C320,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G320" s="30" t="str">
+      <c r="G320" s="28" t="str">
         <f>VLOOKUP(C320,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15356,7 +15347,7 @@
         <f>VLOOKUP(C321,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G321" s="30" t="str">
+      <c r="G321" s="28" t="str">
         <f>VLOOKUP(C321,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15382,7 +15373,7 @@
         <f>VLOOKUP(C322,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G322" s="30" t="str">
+      <c r="G322" s="28" t="str">
         <f>VLOOKUP(C322,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15408,7 +15399,7 @@
         <f>VLOOKUP(C323,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G323" s="30" t="str">
+      <c r="G323" s="28" t="str">
         <f>VLOOKUP(C323,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15434,7 +15425,7 @@
         <f>VLOOKUP(C324,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G324" s="30" t="str">
+      <c r="G324" s="28" t="str">
         <f>VLOOKUP(C324,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15460,7 +15451,7 @@
         <f>VLOOKUP(C325,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G325" s="30" t="str">
+      <c r="G325" s="28" t="str">
         <f>VLOOKUP(C325,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15486,7 +15477,7 @@
         <f>VLOOKUP(C326,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G326" s="30" t="str">
+      <c r="G326" s="28" t="str">
         <f>VLOOKUP(C326,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15512,7 +15503,7 @@
         <f>VLOOKUP(C327,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G327" s="30" t="str">
+      <c r="G327" s="28" t="str">
         <f>VLOOKUP(C327,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15538,7 +15529,7 @@
         <f>VLOOKUP(C328,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G328" s="30" t="str">
+      <c r="G328" s="28" t="str">
         <f>VLOOKUP(C328,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15564,7 +15555,7 @@
         <f>VLOOKUP(C329,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G329" s="30" t="str">
+      <c r="G329" s="28" t="str">
         <f>VLOOKUP(C329,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15590,7 +15581,7 @@
         <f>VLOOKUP(C330,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G330" s="30" t="str">
+      <c r="G330" s="28" t="str">
         <f>VLOOKUP(C330,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15616,7 +15607,7 @@
         <f>VLOOKUP(C331,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G331" s="30" t="str">
+      <c r="G331" s="28" t="str">
         <f>VLOOKUP(C331,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15642,7 +15633,7 @@
         <f>VLOOKUP(C332,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G332" s="30" t="str">
+      <c r="G332" s="28" t="str">
         <f>VLOOKUP(C332,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15668,7 +15659,7 @@
         <f>VLOOKUP(C333,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G333" s="30" t="str">
+      <c r="G333" s="28" t="str">
         <f>VLOOKUP(C333,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15694,7 +15685,7 @@
         <f>VLOOKUP(C334,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G334" s="30" t="str">
+      <c r="G334" s="28" t="str">
         <f>VLOOKUP(C334,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15720,7 +15711,7 @@
         <f>VLOOKUP(C335,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G335" s="30" t="str">
+      <c r="G335" s="28" t="str">
         <f>VLOOKUP(C335,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15746,7 +15737,7 @@
         <f>VLOOKUP(C336,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G336" s="30" t="str">
+      <c r="G336" s="28" t="str">
         <f>VLOOKUP(C336,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15772,7 +15763,7 @@
         <f>VLOOKUP(C337,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>270</v>
       </c>
-      <c r="G337" s="30" t="str">
+      <c r="G337" s="28" t="str">
         <f>VLOOKUP(C337,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -15798,7 +15789,7 @@
         <f>VLOOKUP(C338,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>220</v>
       </c>
-      <c r="G338" s="30" t="str">
+      <c r="G338" s="28" t="str">
         <f>VLOOKUP(C338,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -15824,7 +15815,7 @@
         <f>VLOOKUP(C339,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>370</v>
       </c>
-      <c r="G339" s="30" t="str">
+      <c r="G339" s="28" t="str">
         <f>VLOOKUP(C339,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -17010,8 +17001,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -17118,13 +17109,13 @@
         <v>384</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H4" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:13">
       <c r="B5" t="s">
         <v>386</v>
       </c>
@@ -17141,10 +17132,16 @@
         <v>387</v>
       </c>
       <c r="G5">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H5" t="s">
         <v>388</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
+      <c r="M5">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -18077,7 +18074,7 @@
         <v>460</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>431</v>
@@ -19013,7 +19010,7 @@
         <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>433</v>
@@ -19022,7 +19019,7 @@
         <v>25</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="S36" s="27" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -19071,7 +19068,7 @@
         <v>433</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S37" s="27" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -19105,7 +19102,7 @@
         <v>441</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
@@ -19154,7 +19151,7 @@
         <v>438</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J39" s="1" t="s">
         <v>448</v>
@@ -19172,7 +19169,7 @@
         <v>25</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q39" s="1" t="s">
         <v>450</v>
@@ -19194,7 +19191,7 @@
         <v>428</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>430</v>
@@ -19224,7 +19221,7 @@
         <v>433</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="S40" s="27" t="str">
         <f>IFERROR(VLOOKUP(B40,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -19273,7 +19270,7 @@
         <v>433</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S41" s="27" t="str">
         <f>IFERROR(VLOOKUP(B41,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -19368,7 +19365,7 @@
         <v>1.5</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="N43" s="1" t="s">
         <v>25</v>
@@ -19377,7 +19374,7 @@
         <v>25</v>
       </c>
       <c r="P43" s="19" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q43" s="1" t="s">
         <v>450</v>
@@ -19442,7 +19439,7 @@
     </row>
     <row r="45" ht="34" spans="2:20">
       <c r="B45" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>428</v>
@@ -19451,22 +19448,22 @@
         <v>435</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>431</v>
       </c>
       <c r="G45" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="H45" s="1" t="s">
         <v>488</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>489</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>390</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K45" s="1">
         <v>0</v>
@@ -19475,7 +19472,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>25</v>
@@ -19484,7 +19481,7 @@
         <v>25</v>
       </c>
       <c r="P45" s="19" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="S45" s="27" t="str">
         <f>IFERROR(VLOOKUP(B45,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -19579,10 +19576,10 @@
         <v>25</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>433</v>
+        <v>25</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="S47" s="27" t="str">
         <f>IFERROR(VLOOKUP(B47,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -19593,7 +19590,7 @@
         <v>月饼</v>
       </c>
     </row>
-    <row r="48" ht="17" spans="2:20">
+    <row r="48" ht="34" spans="2:20">
       <c r="B48" s="1" t="s">
         <v>284</v>
       </c>
@@ -19604,10 +19601,10 @@
         <v>435</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>438</v>
@@ -19622,7 +19619,7 @@
         <v>0</v>
       </c>
       <c r="L48" s="1">
-        <v>5</v>
+        <v>0.3</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>25</v>
@@ -19631,7 +19628,7 @@
         <v>433</v>
       </c>
       <c r="P48" s="19" t="s">
-        <v>479</v>
+        <v>454</v>
       </c>
       <c r="S48" s="27" t="str">
         <f>IFERROR(VLOOKUP(B48,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -20130,7 +20127,7 @@
         <v>25</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="S58" s="27" t="str">
         <f>IFERROR(VLOOKUP(B58,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -20179,7 +20176,7 @@
         <v>25</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="S59" s="27" t="str">
         <f>IFERROR(VLOOKUP(B59,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -20431,7 +20428,7 @@
         <v>25</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>478</v>
+        <v>499</v>
       </c>
       <c r="S64" s="27" t="str">
         <f>IFERROR(VLOOKUP(B64,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -20480,7 +20477,7 @@
         <v>433</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="S65" s="27" t="str">
         <f>IFERROR(VLOOKUP(B65,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -20662,7 +20659,7 @@
         <v>431</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>506</v>
@@ -20720,7 +20717,7 @@
         <v>437</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>510</v>
@@ -20815,7 +20812,7 @@
     </row>
     <row r="72" spans="2:20">
       <c r="B72" s="1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>428</v>
@@ -20833,78 +20830,39 @@
         <v>438</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>390</v>
+        <v>463</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>458</v>
+        <v>430</v>
       </c>
       <c r="K72" s="1">
         <v>0</v>
       </c>
       <c r="L72" s="1">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>25</v>
+        <v>433</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>25</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="S72" s="27" t="str">
         <f>IFERROR(VLOOKUP(B72,skill!$G$4:$K$51,5,FALSE),"")</f>
-        <v/>
+        <v>蝴蝶酥</v>
       </c>
       <c r="T72" s="27" t="str">
         <f>IFERROR(VLOOKUP(B72,skill!$H$4:$K$51,4,FALSE),"")</f>
-        <v>蝴蝶酥</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20">
-      <c r="B73" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="K73" s="1">
-        <v>0</v>
-      </c>
-      <c r="L73" s="1">
-        <v>3</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>464</v>
-      </c>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="19:20">
       <c r="S73" s="27" t="str">
         <f>IFERROR(VLOOKUP(B73,skill!$G$4:$K$51,5,FALSE),"")</f>
-        <v>蝴蝶酥</v>
+        <v/>
       </c>
       <c r="T73" s="27" t="str">
         <f>IFERROR(VLOOKUP(B73,skill!$H$4:$K$51,4,FALSE),"")</f>
@@ -20949,7 +20907,7 @@
         <v>25</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="S74" s="27" t="str">
         <f>IFERROR(VLOOKUP(B74,skill!$G$4:$K$51,5,FALSE),"")</f>
@@ -21318,11 +21276,11 @@
       <c r="E2" s="10" t="s">
         <v>524</v>
       </c>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
       <c r="K2" s="10" t="s">
         <v>525</v>
       </c>
@@ -21949,9 +21907,7 @@
       <c r="E16" s="19" t="s">
         <v>587</v>
       </c>
-      <c r="F16" s="20">
-        <v>1</v>
-      </c>
+      <c r="F16" s="20"/>
       <c r="G16" s="20"/>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
@@ -22016,9 +21972,7 @@
       <c r="E17" s="22" t="s">
         <v>594</v>
       </c>
-      <c r="F17" s="20">
-        <v>1</v>
-      </c>
+      <c r="F17" s="20"/>
       <c r="G17" s="20"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -22130,7 +22084,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="20" ht="51" spans="1:25">
+    <row r="20" ht="34" spans="1:25">
       <c r="A20" s="1">
         <v>17</v>
       </c>
@@ -22143,12 +22097,10 @@
       <c r="D20" s="1">
         <v>20</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="20" t="s">
         <v>608</v>
       </c>
-      <c r="F20" s="20">
-        <v>1</v>
-      </c>
+      <c r="F20" s="20"/>
       <c r="G20" s="20"/>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
@@ -22195,7 +22147,7 @@
       <c r="D21" s="1">
         <v>20</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="20" t="s">
         <v>615</v>
       </c>
       <c r="F21" s="20"/>
@@ -22238,7 +22190,7 @@
       <c r="D22" s="1">
         <v>20</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="20" t="s">
         <v>620</v>
       </c>
       <c r="F22" s="20"/>
@@ -22279,6 +22231,7 @@
       <c r="C23" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E23" s="9"/>
       <c r="W23" s="1" t="s">
         <v>625</v>
       </c>
@@ -22302,7 +22255,7 @@
       <c r="D24" s="1">
         <v>20</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="20" t="s">
         <v>628</v>
       </c>
       <c r="F24" s="20"/>
@@ -22346,6 +22299,7 @@
       <c r="C25" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E25" s="9"/>
       <c r="X25" s="1" t="s">
         <v>630</v>
       </c>
@@ -22353,7 +22307,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="26" ht="51" spans="1:25">
+    <row r="26" ht="34" spans="1:25">
       <c r="A26" s="1">
         <v>21</v>
       </c>
@@ -22366,12 +22320,10 @@
       <c r="D26" s="1">
         <v>20</v>
       </c>
-      <c r="E26" s="19" t="s">
+      <c r="E26" s="20" t="s">
         <v>633</v>
       </c>
-      <c r="F26" s="20">
-        <v>1</v>
-      </c>
+      <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
@@ -22412,6 +22364,7 @@
       <c r="C27" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E27" s="9"/>
       <c r="X27" s="1" t="s">
         <v>639</v>
       </c>
@@ -22432,7 +22385,7 @@
       <c r="D28" s="1">
         <v>30</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="20" t="s">
         <v>641</v>
       </c>
       <c r="F28" s="20">
@@ -22474,7 +22427,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="29" ht="51" spans="1:25">
+    <row r="29" ht="34" spans="1:25">
       <c r="A29" s="1">
         <v>23</v>
       </c>
@@ -22487,12 +22440,10 @@
       <c r="D29" s="1">
         <v>30</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="20" t="s">
         <v>646</v>
       </c>
-      <c r="F29" s="20">
-        <v>1</v>
-      </c>
+      <c r="F29" s="20"/>
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
       <c r="I29" s="20"/>
@@ -22539,7 +22490,7 @@
       <c r="D30" s="1">
         <v>30</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="20" t="s">
         <v>651</v>
       </c>
       <c r="F30" s="20"/>
@@ -22583,6 +22534,7 @@
       <c r="C31" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E31" s="9"/>
       <c r="X31" s="1" t="s">
         <v>653</v>
       </c>
@@ -22594,6 +22546,7 @@
       <c r="C32" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E32" s="9"/>
       <c r="X32" s="1" t="s">
         <v>656</v>
       </c>
@@ -22614,7 +22567,7 @@
       <c r="D33" s="1">
         <v>30</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="E33" s="20" t="s">
         <v>658</v>
       </c>
       <c r="F33" s="20"/>
@@ -22657,6 +22610,7 @@
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E34" s="9"/>
       <c r="W34" s="1" t="s">
         <v>663</v>
       </c>
@@ -22667,10 +22621,11 @@
         <v>665</v>
       </c>
     </row>
-    <row r="35" spans="3:3">
+    <row r="35" spans="3:5">
       <c r="C35" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="E35" s="9"/>
     </row>
     <row r="36" ht="34" spans="1:15">
       <c r="A36" s="1">
@@ -22685,7 +22640,7 @@
       <c r="D36" s="1">
         <v>40</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="20" t="s">
         <v>666</v>
       </c>
       <c r="F36" s="20"/>
@@ -22713,6 +22668,7 @@
       <c r="C37" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="E37" s="9"/>
       <c r="X37" s="1" t="s">
         <v>567</v>
       </c>
@@ -22724,7 +22680,7 @@
       <c r="A38" s="1">
         <v>27</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="15" t="s">
         <v>127</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -22733,7 +22689,7 @@
       <c r="D38" s="1">
         <v>40</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="20" t="s">
         <v>667</v>
       </c>
       <c r="F38" s="20"/>
@@ -22771,6 +22727,7 @@
       <c r="C39" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="E39" s="9"/>
       <c r="X39" s="1" t="s">
         <v>671</v>
       </c>
@@ -22791,12 +22748,10 @@
       <c r="D40" s="1">
         <v>40</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="20" t="s">
         <v>673</v>
       </c>
-      <c r="F40" s="20">
-        <v>1</v>
-      </c>
+      <c r="F40" s="20"/>
       <c r="G40" s="20"/>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
@@ -22831,6 +22786,7 @@
       <c r="C41" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="E41" s="9"/>
       <c r="X41" s="1" t="s">
         <v>677</v>
       </c>
@@ -22851,7 +22807,7 @@
       <c r="D42" s="1">
         <v>40</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="20" t="s">
         <v>679</v>
       </c>
       <c r="F42" s="20">
@@ -22881,6 +22837,7 @@
       <c r="C43" s="1" t="s">
         <v>73</v>
       </c>
+      <c r="E43" s="9"/>
       <c r="X43" s="1" t="s">
         <v>681</v>
       </c>
@@ -22901,7 +22858,7 @@
       <c r="D44" s="1">
         <v>40</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="E44" s="20" t="s">
         <v>683</v>
       </c>
       <c r="F44" s="20">
@@ -22957,9 +22914,7 @@
       <c r="E46" s="19" t="s">
         <v>688</v>
       </c>
-      <c r="F46" s="20">
-        <v>1</v>
-      </c>
+      <c r="F46" s="20"/>
       <c r="G46" s="20"/>
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
@@ -23099,7 +23054,7 @@
       <c r="A52" s="1">
         <v>33</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="16" t="s">
         <v>148</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -23179,7 +23134,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="34" spans="1:6">
+    <row r="56" ht="51" spans="1:5">
       <c r="A56" s="1">
         <v>35</v>
       </c>
@@ -23194,9 +23149,6 @@
       </c>
       <c r="E56" s="19" t="s">
         <v>711</v>
-      </c>
-      <c r="F56" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="57" spans="3:13">
@@ -23223,7 +23175,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="59" ht="34" spans="1:6">
+    <row r="59" ht="34" spans="1:5">
       <c r="A59" s="1">
         <v>36</v>
       </c>
@@ -23238,9 +23190,6 @@
       </c>
       <c r="E59" s="19" t="s">
         <v>712</v>
-      </c>
-      <c r="F59" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="60" spans="3:13">
@@ -23283,9 +23232,7 @@
       <c r="E62" s="19" t="s">
         <v>713</v>
       </c>
-      <c r="F62" s="20">
-        <v>1</v>
-      </c>
+      <c r="F62" s="20"/>
       <c r="G62" s="20"/>
       <c r="H62" s="20"/>
       <c r="I62" s="20"/>
@@ -23321,9 +23268,7 @@
       <c r="E64" s="19" t="s">
         <v>714</v>
       </c>
-      <c r="F64" s="20">
-        <v>1</v>
-      </c>
+      <c r="F64" s="20"/>
       <c r="G64" s="20"/>
       <c r="H64" s="20"/>
       <c r="I64" s="20"/>
@@ -23343,7 +23288,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="66" ht="51" spans="1:5">
+    <row r="66" ht="34" spans="1:5">
       <c r="A66" s="1">
         <v>39</v>
       </c>
@@ -23384,7 +23329,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="69" ht="51" spans="1:6">
+    <row r="69" ht="51" spans="1:5">
       <c r="A69" s="1">
         <v>40</v>
       </c>
@@ -23399,9 +23344,6 @@
       </c>
       <c r="E69" s="19" t="s">
         <v>716</v>
-      </c>
-      <c r="F69" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="70" spans="3:13">
@@ -23432,7 +23374,7 @@
       <c r="A72" s="1">
         <v>41</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="16" t="s">
         <v>172</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -23500,7 +23442,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="76" ht="34" spans="1:22">
+    <row r="76" ht="68" spans="1:22">
       <c r="A76" s="1">
         <v>43</v>
       </c>
@@ -23513,10 +23455,12 @@
       <c r="D76" s="1">
         <v>30</v>
       </c>
-      <c r="E76" s="19" t="s">
+      <c r="E76" s="21" t="s">
         <v>719</v>
       </c>
-      <c r="F76" s="20"/>
+      <c r="F76" s="20">
+        <v>1</v>
+      </c>
       <c r="G76" s="20"/>
       <c r="H76" s="20"/>
       <c r="I76" s="20"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -20859,14 +20859,79 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="19:20">
+    <row r="73" spans="2:20" ht="34" customHeight="1">
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sk_palmier_2</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OnSettle</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DishCount</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ColumnAndSelf</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Instances</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AddMult</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RoundAndSelf</t>
+        </is>
+      </c>
+      <c r="K73" s="1">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="M73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">linear</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="O73" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">false</t>
+        </is>
+      </c>
+      <c r="P73" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{ascope}倍率 ×N
+（N=1+{cscope}食物个数×{0}）</t>
+        </is>
+      </c>
       <c r="S73" s="27" t="str">
         <f>IFERROR(VLOOKUP(B73,skill!$G$4:$K$51,5,FALSE),"")</f>
-        <v/>
       </c>
       <c r="T73" s="27" t="str">
         <f>IFERROR(VLOOKUP(B73,skill!$H$4:$K$51,4,FALSE),"")</f>
-        <v/>
       </c>
     </row>
     <row r="74" spans="2:20">

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300" firstSheet="3" activeTab="8"/>
+    <workbookView windowHeight="16760" firstSheet="3" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -15,12 +15,25 @@
     <sheet name="sub_skill" sheetId="6" r:id="rId6"/>
     <sheet name="食物设计" sheetId="7" r:id="rId7"/>
     <sheet name="位置" sheetId="8" r:id="rId8"/>
-    <sheet name="Sheet1" sheetId="9" r:id="rId9"/>
+    <sheet name="食物设计新" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dish_base!$B$1:$B$101</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2695,7 +2708,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -3371,7 +3384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3406,12 +3419,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3419,9 +3426,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3458,9 +3462,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4103,7 +4104,7 @@
       </c>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="34" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
@@ -4148,7 +4149,7 @@
       </c>
     </row>
     <row r="5" spans="2:15">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="34" t="s">
         <v>29</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -5273,7 +5274,7 @@
       <c r="T27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="U27" s="39" t="s">
+      <c r="U27" s="35" t="s">
         <v>105</v>
       </c>
     </row>
@@ -5307,7 +5308,7 @@
       <c r="T28" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="U28" s="39" t="s">
+      <c r="U28" s="35" t="s">
         <v>107</v>
       </c>
     </row>
@@ -5356,15 +5357,15 @@
       <c r="R29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="T29" s="40">
+      <c r="T29" s="36">
         <v>45100</v>
       </c>
-      <c r="U29" s="39" t="s">
+      <c r="U29" s="35" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="30" spans="2:15">
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="34" t="s">
         <v>114</v>
       </c>
       <c r="C30" s="2" t="s">
@@ -7140,7 +7141,7 @@
       <c r="L82" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M82" s="39" t="s">
+      <c r="M82" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N82" s="2">
@@ -7163,7 +7164,7 @@
       <c r="L83" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M83" s="39" t="s">
+      <c r="M83" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N83" s="2">
@@ -7186,7 +7187,7 @@
       <c r="L84" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M84" s="39" t="s">
+      <c r="M84" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N84" s="2">
@@ -7209,7 +7210,7 @@
       <c r="L85" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M85" s="39" t="s">
+      <c r="M85" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N85" s="2">
@@ -7232,7 +7233,7 @@
       <c r="L86" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M86" s="39" t="s">
+      <c r="M86" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N86" s="2">
@@ -7275,7 +7276,7 @@
       <c r="L87" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M87" s="39" t="s">
+      <c r="M87" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N87" s="2">
@@ -7298,7 +7299,7 @@
       <c r="L88" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M88" s="39" t="s">
+      <c r="M88" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N88" s="2">
@@ -7321,7 +7322,7 @@
       <c r="L89" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M89" s="39" t="s">
+      <c r="M89" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N89" s="2">
@@ -7364,7 +7365,7 @@
       <c r="L90" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M90" s="39" t="s">
+      <c r="M90" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N90" s="2">
@@ -7387,7 +7388,7 @@
       <c r="L91" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M91" s="39" t="s">
+      <c r="M91" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N91" s="2">
@@ -7410,7 +7411,7 @@
       <c r="L92" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M92" s="39" t="s">
+      <c r="M92" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N92" s="2">
@@ -7433,7 +7434,7 @@
       <c r="L93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M93" s="39" t="s">
+      <c r="M93" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N93" s="2">
@@ -7453,7 +7454,7 @@
       <c r="L94" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="M94" s="39" t="s">
+      <c r="M94" s="35" t="s">
         <v>113</v>
       </c>
       <c r="N94" s="2">
@@ -7487,7 +7488,7 @@
       <c r="G101"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B101">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:B101" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
       <filters>
         <filter val="croissant"/>
@@ -7649,7 +7650,7 @@
         <f>C4&amp;D4</f>
         <v>cookie</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="34" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="2">
@@ -7672,7 +7673,7 @@
         <f t="shared" ref="B5:B36" si="0">C5&amp;D5</f>
         <v>macaron</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="34" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="2">
@@ -8155,7 +8156,7 @@
         <f t="shared" si="0"/>
         <v>choco_bar</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="34" t="s">
         <v>114</v>
       </c>
       <c r="E26" s="2">
@@ -9364,7 +9365,7 @@
         <f>VLOOKUP(C75,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G75" s="39" t="str">
+      <c r="G75" s="35" t="str">
         <f>VLOOKUP(C75,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9390,7 +9391,7 @@
         <f>VLOOKUP(C76,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G76" s="39" t="str">
+      <c r="G76" s="35" t="str">
         <f>VLOOKUP(C76,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9416,7 +9417,7 @@
         <f>VLOOKUP(C77,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G77" s="39" t="str">
+      <c r="G77" s="35" t="str">
         <f>VLOOKUP(C77,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9442,7 +9443,7 @@
         <f>VLOOKUP(C78,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G78" s="39" t="str">
+      <c r="G78" s="35" t="str">
         <f>VLOOKUP(C78,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9468,7 +9469,7 @@
         <f>VLOOKUP(C79,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G79" s="39" t="str">
+      <c r="G79" s="35" t="str">
         <f>VLOOKUP(C79,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9494,7 +9495,7 @@
         <f>VLOOKUP(C80,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G80" s="39" t="str">
+      <c r="G80" s="35" t="str">
         <f>VLOOKUP(C80,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9520,7 +9521,7 @@
         <f>VLOOKUP(C81,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G81" s="39" t="str">
+      <c r="G81" s="35" t="str">
         <f>VLOOKUP(C81,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9546,7 +9547,7 @@
         <f>VLOOKUP(C82,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G82" s="39" t="str">
+      <c r="G82" s="35" t="str">
         <f>VLOOKUP(C82,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9572,7 +9573,7 @@
         <f>VLOOKUP(C83,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G83" s="39" t="str">
+      <c r="G83" s="35" t="str">
         <f>VLOOKUP(C83,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9598,7 +9599,7 @@
         <f>VLOOKUP(C84,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G84" s="39" t="str">
+      <c r="G84" s="35" t="str">
         <f>VLOOKUP(C84,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9624,7 +9625,7 @@
         <f>VLOOKUP(C85,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G85" s="39" t="str">
+      <c r="G85" s="35" t="str">
         <f>VLOOKUP(C85,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9650,7 +9651,7 @@
         <f>VLOOKUP(C86,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G86" s="39" t="str">
+      <c r="G86" s="35" t="str">
         <f>VLOOKUP(C86,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9676,7 +9677,7 @@
         <f>VLOOKUP(C87,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G87" s="39" t="str">
+      <c r="G87" s="35" t="str">
         <f>VLOOKUP(C87,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9702,7 +9703,7 @@
         <f>VLOOKUP(C88,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G88" s="39" t="str">
+      <c r="G88" s="35" t="str">
         <f>VLOOKUP(C88,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9728,7 +9729,7 @@
         <f>VLOOKUP(C89,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G89" s="39" t="str">
+      <c r="G89" s="35" t="str">
         <f>VLOOKUP(C89,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9754,7 +9755,7 @@
         <f>VLOOKUP(C90,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G90" s="39" t="str">
+      <c r="G90" s="35" t="str">
         <f>VLOOKUP(C90,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9780,7 +9781,7 @@
         <f>VLOOKUP(C91,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G91" s="39" t="str">
+      <c r="G91" s="35" t="str">
         <f>VLOOKUP(C91,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9806,7 +9807,7 @@
         <f>VLOOKUP(C92,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G92" s="39" t="str">
+      <c r="G92" s="35" t="str">
         <f>VLOOKUP(C92,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9832,7 +9833,7 @@
         <f>VLOOKUP(C93,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G93" s="39" t="str">
+      <c r="G93" s="35" t="str">
         <f>VLOOKUP(C93,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -9858,7 +9859,7 @@
         <f>VLOOKUP(C94,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G94" s="39" t="str">
+      <c r="G94" s="35" t="str">
         <f>VLOOKUP(C94,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9884,7 +9885,7 @@
         <f>VLOOKUP(C95,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G95" s="39" t="str">
+      <c r="G95" s="35" t="str">
         <f>VLOOKUP(C95,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -9910,7 +9911,7 @@
         <f>VLOOKUP(C96,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G96" s="39" t="str">
+      <c r="G96" s="35" t="str">
         <f>VLOOKUP(C96,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -9936,7 +9937,7 @@
         <f>VLOOKUP(C97,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>270</v>
       </c>
-      <c r="G97" s="39" t="str">
+      <c r="G97" s="35" t="str">
         <f>VLOOKUP(C97,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -10586,7 +10587,7 @@
         <f>VLOOKUP(C122,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G122" s="39" t="str">
+      <c r="G122" s="35" t="str">
         <f>VLOOKUP(C122,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10612,7 +10613,7 @@
         <f>VLOOKUP(C123,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G123" s="39" t="str">
+      <c r="G123" s="35" t="str">
         <f>VLOOKUP(C123,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10638,7 +10639,7 @@
         <f>VLOOKUP(C124,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G124" s="39" t="str">
+      <c r="G124" s="35" t="str">
         <f>VLOOKUP(C124,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -10664,7 +10665,7 @@
         <f>VLOOKUP(C125,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G125" s="39" t="str">
+      <c r="G125" s="35" t="str">
         <f>VLOOKUP(C125,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10690,7 +10691,7 @@
         <f>VLOOKUP(C126,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G126" s="39" t="str">
+      <c r="G126" s="35" t="str">
         <f>VLOOKUP(C126,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10716,7 +10717,7 @@
         <f>VLOOKUP(C127,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G127" s="39" t="str">
+      <c r="G127" s="35" t="str">
         <f>VLOOKUP(C127,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10742,7 +10743,7 @@
         <f>VLOOKUP(C128,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G128" s="39" t="str">
+      <c r="G128" s="35" t="str">
         <f>VLOOKUP(C128,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10768,7 +10769,7 @@
         <f>VLOOKUP(C129,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G129" s="39" t="str">
+      <c r="G129" s="35" t="str">
         <f>VLOOKUP(C129,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10794,7 +10795,7 @@
         <f>VLOOKUP(C130,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G130" s="39" t="str">
+      <c r="G130" s="35" t="str">
         <f>VLOOKUP(C130,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10820,7 +10821,7 @@
         <f>VLOOKUP(C131,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G131" s="39" t="str">
+      <c r="G131" s="35" t="str">
         <f>VLOOKUP(C131,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10846,7 +10847,7 @@
         <f>VLOOKUP(C132,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G132" s="39" t="str">
+      <c r="G132" s="35" t="str">
         <f>VLOOKUP(C132,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10872,7 +10873,7 @@
         <f>VLOOKUP(C133,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G133" s="39" t="str">
+      <c r="G133" s="35" t="str">
         <f>VLOOKUP(C133,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -10898,7 +10899,7 @@
         <f>VLOOKUP(C134,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G134" s="39" t="str">
+      <c r="G134" s="35" t="str">
         <f>VLOOKUP(C134,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10924,7 +10925,7 @@
         <f>VLOOKUP(C135,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G135" s="39" t="str">
+      <c r="G135" s="35" t="str">
         <f>VLOOKUP(C135,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10950,7 +10951,7 @@
         <f>VLOOKUP(C136,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G136" s="39" t="str">
+      <c r="G136" s="35" t="str">
         <f>VLOOKUP(C136,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -10976,7 +10977,7 @@
         <f>VLOOKUP(C137,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G137" s="39" t="str">
+      <c r="G137" s="35" t="str">
         <f>VLOOKUP(C137,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11002,7 +11003,7 @@
         <f>VLOOKUP(C138,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G138" s="39" t="str">
+      <c r="G138" s="35" t="str">
         <f>VLOOKUP(C138,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11028,7 +11029,7 @@
         <f>VLOOKUP(C139,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G139" s="39" t="str">
+      <c r="G139" s="35" t="str">
         <f>VLOOKUP(C139,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11054,7 +11055,7 @@
         <f>VLOOKUP(C140,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G140" s="39" t="str">
+      <c r="G140" s="35" t="str">
         <f>VLOOKUP(C140,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11080,7 +11081,7 @@
         <f>VLOOKUP(C141,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G141" s="39" t="str">
+      <c r="G141" s="35" t="str">
         <f>VLOOKUP(C141,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -11106,7 +11107,7 @@
         <f>VLOOKUP(C142,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G142" s="39" t="str">
+      <c r="G142" s="35" t="str">
         <f>VLOOKUP(C142,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11132,7 +11133,7 @@
         <f>VLOOKUP(C143,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G143" s="39" t="str">
+      <c r="G143" s="35" t="str">
         <f>VLOOKUP(C143,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11158,7 +11159,7 @@
         <f>VLOOKUP(C144,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G144" s="39" t="str">
+      <c r="G144" s="35" t="str">
         <f>VLOOKUP(C144,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11808,7 +11809,7 @@
         <f>VLOOKUP(C169,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G169" s="39" t="str">
+      <c r="G169" s="35" t="str">
         <f>VLOOKUP(C169,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11834,7 +11835,7 @@
         <f>VLOOKUP(C170,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G170" s="39" t="str">
+      <c r="G170" s="35" t="str">
         <f>VLOOKUP(C170,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11860,7 +11861,7 @@
         <f>VLOOKUP(C171,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G171" s="39" t="str">
+      <c r="G171" s="35" t="str">
         <f>VLOOKUP(C171,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11886,7 +11887,7 @@
         <f>VLOOKUP(C172,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G172" s="39" t="str">
+      <c r="G172" s="35" t="str">
         <f>VLOOKUP(C172,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -11912,7 +11913,7 @@
         <f>VLOOKUP(C173,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G173" s="39" t="str">
+      <c r="G173" s="35" t="str">
         <f>VLOOKUP(C173,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11938,7 +11939,7 @@
         <f>VLOOKUP(C174,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G174" s="39" t="str">
+      <c r="G174" s="35" t="str">
         <f>VLOOKUP(C174,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11964,7 +11965,7 @@
         <f>VLOOKUP(C175,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G175" s="39" t="str">
+      <c r="G175" s="35" t="str">
         <f>VLOOKUP(C175,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -11990,7 +11991,7 @@
         <f>VLOOKUP(C176,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G176" s="39" t="str">
+      <c r="G176" s="35" t="str">
         <f>VLOOKUP(C176,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12016,7 +12017,7 @@
         <f>VLOOKUP(C177,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G177" s="39" t="str">
+      <c r="G177" s="35" t="str">
         <f>VLOOKUP(C177,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12042,7 +12043,7 @@
         <f>VLOOKUP(C178,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G178" s="39" t="str">
+      <c r="G178" s="35" t="str">
         <f>VLOOKUP(C178,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12068,7 +12069,7 @@
         <f>VLOOKUP(C179,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G179" s="39" t="str">
+      <c r="G179" s="35" t="str">
         <f>VLOOKUP(C179,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12094,7 +12095,7 @@
         <f>VLOOKUP(C180,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G180" s="39" t="str">
+      <c r="G180" s="35" t="str">
         <f>VLOOKUP(C180,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12120,7 +12121,7 @@
         <f>VLOOKUP(C181,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G181" s="39" t="str">
+      <c r="G181" s="35" t="str">
         <f>VLOOKUP(C181,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -12146,7 +12147,7 @@
         <f>VLOOKUP(C182,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G182" s="39" t="str">
+      <c r="G182" s="35" t="str">
         <f>VLOOKUP(C182,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12172,7 +12173,7 @@
         <f>VLOOKUP(C183,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G183" s="39" t="str">
+      <c r="G183" s="35" t="str">
         <f>VLOOKUP(C183,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12198,7 +12199,7 @@
         <f>VLOOKUP(C184,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G184" s="39" t="str">
+      <c r="G184" s="35" t="str">
         <f>VLOOKUP(C184,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12224,7 +12225,7 @@
         <f>VLOOKUP(C185,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G185" s="39" t="str">
+      <c r="G185" s="35" t="str">
         <f>VLOOKUP(C185,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12250,7 +12251,7 @@
         <f>VLOOKUP(C186,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G186" s="39" t="str">
+      <c r="G186" s="35" t="str">
         <f>VLOOKUP(C186,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12276,7 +12277,7 @@
         <f>VLOOKUP(C187,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G187" s="39" t="str">
+      <c r="G187" s="35" t="str">
         <f>VLOOKUP(C187,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12302,7 +12303,7 @@
         <f>VLOOKUP(C188,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G188" s="39" t="str">
+      <c r="G188" s="35" t="str">
         <f>VLOOKUP(C188,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12328,7 +12329,7 @@
         <f>VLOOKUP(C189,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G189" s="39" t="str">
+      <c r="G189" s="35" t="str">
         <f>VLOOKUP(C189,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -12354,7 +12355,7 @@
         <f>VLOOKUP(C190,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G190" s="39" t="str">
+      <c r="G190" s="35" t="str">
         <f>VLOOKUP(C190,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -12380,7 +12381,7 @@
         <f>VLOOKUP(C191,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G191" s="39" t="str">
+      <c r="G191" s="35" t="str">
         <f>VLOOKUP(C191,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13030,7 +13031,7 @@
         <f>VLOOKUP(C216,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G216" s="39" t="str">
+      <c r="G216" s="35" t="str">
         <f>VLOOKUP(C216,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -13056,7 +13057,7 @@
         <f>VLOOKUP(C217,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G217" s="39" t="str">
+      <c r="G217" s="35" t="str">
         <f>VLOOKUP(C217,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13082,7 +13083,7 @@
         <f>VLOOKUP(C218,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G218" s="39" t="str">
+      <c r="G218" s="35" t="str">
         <f>VLOOKUP(C218,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13108,7 +13109,7 @@
         <f>VLOOKUP(C219,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G219" s="39" t="str">
+      <c r="G219" s="35" t="str">
         <f>VLOOKUP(C219,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13134,7 +13135,7 @@
         <f>VLOOKUP(C220,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G220" s="39" t="str">
+      <c r="G220" s="35" t="str">
         <f>VLOOKUP(C220,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -13160,7 +13161,7 @@
         <f>VLOOKUP(C221,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G221" s="39" t="str">
+      <c r="G221" s="35" t="str">
         <f>VLOOKUP(C221,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13186,7 +13187,7 @@
         <f>VLOOKUP(C222,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G222" s="39" t="str">
+      <c r="G222" s="35" t="str">
         <f>VLOOKUP(C222,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13212,7 +13213,7 @@
         <f>VLOOKUP(C223,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G223" s="39" t="str">
+      <c r="G223" s="35" t="str">
         <f>VLOOKUP(C223,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13238,7 +13239,7 @@
         <f>VLOOKUP(C224,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G224" s="39" t="str">
+      <c r="G224" s="35" t="str">
         <f>VLOOKUP(C224,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13264,7 +13265,7 @@
         <f>VLOOKUP(C225,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G225" s="39" t="str">
+      <c r="G225" s="35" t="str">
         <f>VLOOKUP(C225,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13290,7 +13291,7 @@
         <f>VLOOKUP(C226,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G226" s="39" t="str">
+      <c r="G226" s="35" t="str">
         <f>VLOOKUP(C226,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13316,7 +13317,7 @@
         <f>VLOOKUP(C227,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G227" s="39" t="str">
+      <c r="G227" s="35" t="str">
         <f>VLOOKUP(C227,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13342,7 +13343,7 @@
         <f>VLOOKUP(C228,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G228" s="39" t="str">
+      <c r="G228" s="35" t="str">
         <f>VLOOKUP(C228,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13368,7 +13369,7 @@
         <f>VLOOKUP(C229,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G229" s="39" t="str">
+      <c r="G229" s="35" t="str">
         <f>VLOOKUP(C229,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -13394,7 +13395,7 @@
         <f>VLOOKUP(C230,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G230" s="39" t="str">
+      <c r="G230" s="35" t="str">
         <f>VLOOKUP(C230,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13420,7 +13421,7 @@
         <f>VLOOKUP(C231,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G231" s="39" t="str">
+      <c r="G231" s="35" t="str">
         <f>VLOOKUP(C231,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13446,7 +13447,7 @@
         <f>VLOOKUP(C232,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G232" s="39" t="str">
+      <c r="G232" s="35" t="str">
         <f>VLOOKUP(C232,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13472,7 +13473,7 @@
         <f>VLOOKUP(C233,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G233" s="39" t="str">
+      <c r="G233" s="35" t="str">
         <f>VLOOKUP(C233,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13498,7 +13499,7 @@
         <f>VLOOKUP(C234,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G234" s="39" t="str">
+      <c r="G234" s="35" t="str">
         <f>VLOOKUP(C234,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13524,7 +13525,7 @@
         <f>VLOOKUP(C235,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G235" s="39" t="str">
+      <c r="G235" s="35" t="str">
         <f>VLOOKUP(C235,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13550,7 +13551,7 @@
         <f>VLOOKUP(C236,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G236" s="39" t="str">
+      <c r="G236" s="35" t="str">
         <f>VLOOKUP(C236,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13576,7 +13577,7 @@
         <f>VLOOKUP(C237,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G237" s="39" t="str">
+      <c r="G237" s="35" t="str">
         <f>VLOOKUP(C237,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -13602,7 +13603,7 @@
         <f>VLOOKUP(C238,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G238" s="39" t="str">
+      <c r="G238" s="35" t="str">
         <f>VLOOKUP(C238,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -14255,7 +14256,7 @@
         <f>VLOOKUP(C263,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G263" s="39" t="str">
+      <c r="G263" s="35" t="str">
         <f>VLOOKUP(C263,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -14281,7 +14282,7 @@
         <f>VLOOKUP(C264,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G264" s="39" t="str">
+      <c r="G264" s="35" t="str">
         <f>VLOOKUP(C264,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -14307,7 +14308,7 @@
         <f>VLOOKUP(C265,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G265" s="39" t="str">
+      <c r="G265" s="35" t="str">
         <f>VLOOKUP(C265,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -14333,7 +14334,7 @@
         <f>VLOOKUP(C266,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G266" s="39" t="str">
+      <c r="G266" s="35" t="str">
         <f>VLOOKUP(C266,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -14359,7 +14360,7 @@
         <f>VLOOKUP(C267,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G267" s="39" t="str">
+      <c r="G267" s="35" t="str">
         <f>VLOOKUP(C267,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -14385,7 +14386,7 @@
         <f>VLOOKUP(C268,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G268" s="39" t="str">
+      <c r="G268" s="35" t="str">
         <f>VLOOKUP(C268,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -14411,7 +14412,7 @@
         <f>VLOOKUP(C269,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G269" s="39" t="str">
+      <c r="G269" s="35" t="str">
         <f>VLOOKUP(C269,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14437,7 +14438,7 @@
         <f>VLOOKUP(C270,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G270" s="39" t="str">
+      <c r="G270" s="35" t="str">
         <f>VLOOKUP(C270,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14463,7 +14464,7 @@
         <f>VLOOKUP(C271,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G271" s="39" t="str">
+      <c r="G271" s="35" t="str">
         <f>VLOOKUP(C271,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14489,7 +14490,7 @@
         <f>VLOOKUP(C272,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G272" s="39" t="str">
+      <c r="G272" s="35" t="str">
         <f>VLOOKUP(C272,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14515,7 +14516,7 @@
         <f>VLOOKUP(C273,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G273" s="39" t="str">
+      <c r="G273" s="35" t="str">
         <f>VLOOKUP(C273,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14541,7 +14542,7 @@
         <f>VLOOKUP(C274,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G274" s="39" t="str">
+      <c r="G274" s="35" t="str">
         <f>VLOOKUP(C274,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14567,7 +14568,7 @@
         <f>VLOOKUP(C275,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G275" s="39" t="str">
+      <c r="G275" s="35" t="str">
         <f>VLOOKUP(C275,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14593,7 +14594,7 @@
         <f>VLOOKUP(C276,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G276" s="39" t="str">
+      <c r="G276" s="35" t="str">
         <f>VLOOKUP(C276,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14619,7 +14620,7 @@
         <f>VLOOKUP(C277,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G277" s="39" t="str">
+      <c r="G277" s="35" t="str">
         <f>VLOOKUP(C277,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -14645,7 +14646,7 @@
         <f>VLOOKUP(C278,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G278" s="39" t="str">
+      <c r="G278" s="35" t="str">
         <f>VLOOKUP(C278,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14671,7 +14672,7 @@
         <f>VLOOKUP(C279,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G279" s="39" t="str">
+      <c r="G279" s="35" t="str">
         <f>VLOOKUP(C279,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14697,7 +14698,7 @@
         <f>VLOOKUP(C280,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G280" s="39" t="str">
+      <c r="G280" s="35" t="str">
         <f>VLOOKUP(C280,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14723,7 +14724,7 @@
         <f>VLOOKUP(C281,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G281" s="39" t="str">
+      <c r="G281" s="35" t="str">
         <f>VLOOKUP(C281,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14749,7 +14750,7 @@
         <f>VLOOKUP(C282,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G282" s="39" t="str">
+      <c r="G282" s="35" t="str">
         <f>VLOOKUP(C282,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14775,7 +14776,7 @@
         <f>VLOOKUP(C283,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G283" s="39" t="str">
+      <c r="G283" s="35" t="str">
         <f>VLOOKUP(C283,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14801,7 +14802,7 @@
         <f>VLOOKUP(C284,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G284" s="39" t="str">
+      <c r="G284" s="35" t="str">
         <f>VLOOKUP(C284,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -14827,7 +14828,7 @@
         <f>VLOOKUP(C285,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G285" s="39" t="str">
+      <c r="G285" s="35" t="str">
         <f>VLOOKUP(C285,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15477,7 +15478,7 @@
         <f>VLOOKUP(C310,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G310" s="39" t="str">
+      <c r="G310" s="35" t="str">
         <f>VLOOKUP(C310,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -15503,7 +15504,7 @@
         <f>VLOOKUP(C311,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G311" s="39" t="str">
+      <c r="G311" s="35" t="str">
         <f>VLOOKUP(C311,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -15529,7 +15530,7 @@
         <f>VLOOKUP(C312,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>80</v>
       </c>
-      <c r="G312" s="39" t="str">
+      <c r="G312" s="35" t="str">
         <f>VLOOKUP(C312,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>45,80</v>
       </c>
@@ -15555,7 +15556,7 @@
         <f>VLOOKUP(C313,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G313" s="39" t="str">
+      <c r="G313" s="35" t="str">
         <f>VLOOKUP(C313,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15581,7 +15582,7 @@
         <f>VLOOKUP(C314,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G314" s="39" t="str">
+      <c r="G314" s="35" t="str">
         <f>VLOOKUP(C314,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15607,7 +15608,7 @@
         <f>VLOOKUP(C315,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G315" s="39" t="str">
+      <c r="G315" s="35" t="str">
         <f>VLOOKUP(C315,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15633,7 +15634,7 @@
         <f>VLOOKUP(C316,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G316" s="39" t="str">
+      <c r="G316" s="35" t="str">
         <f>VLOOKUP(C316,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -15659,7 +15660,7 @@
         <f>VLOOKUP(C317,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G317" s="39" t="str">
+      <c r="G317" s="35" t="str">
         <f>VLOOKUP(C317,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15685,7 +15686,7 @@
         <f>VLOOKUP(C318,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G318" s="39" t="str">
+      <c r="G318" s="35" t="str">
         <f>VLOOKUP(C318,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15711,7 +15712,7 @@
         <f>VLOOKUP(C319,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G319" s="39" t="str">
+      <c r="G319" s="35" t="str">
         <f>VLOOKUP(C319,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15737,7 +15738,7 @@
         <f>VLOOKUP(C320,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G320" s="39" t="str">
+      <c r="G320" s="35" t="str">
         <f>VLOOKUP(C320,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15763,7 +15764,7 @@
         <f>VLOOKUP(C321,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G321" s="39" t="str">
+      <c r="G321" s="35" t="str">
         <f>VLOOKUP(C321,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15789,7 +15790,7 @@
         <f>VLOOKUP(C322,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G322" s="39" t="str">
+      <c r="G322" s="35" t="str">
         <f>VLOOKUP(C322,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15815,7 +15816,7 @@
         <f>VLOOKUP(C323,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G323" s="39" t="str">
+      <c r="G323" s="35" t="str">
         <f>VLOOKUP(C323,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15841,7 +15842,7 @@
         <f>VLOOKUP(C324,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G324" s="39" t="str">
+      <c r="G324" s="35" t="str">
         <f>VLOOKUP(C324,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15867,7 +15868,7 @@
         <f>VLOOKUP(C325,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G325" s="39" t="str">
+      <c r="G325" s="35" t="str">
         <f>VLOOKUP(C325,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -15893,7 +15894,7 @@
         <f>VLOOKUP(C326,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G326" s="39" t="str">
+      <c r="G326" s="35" t="str">
         <f>VLOOKUP(C326,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15919,7 +15920,7 @@
         <f>VLOOKUP(C327,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G327" s="39" t="str">
+      <c r="G327" s="35" t="str">
         <f>VLOOKUP(C327,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15945,7 +15946,7 @@
         <f>VLOOKUP(C328,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G328" s="39" t="str">
+      <c r="G328" s="35" t="str">
         <f>VLOOKUP(C328,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15971,7 +15972,7 @@
         <f>VLOOKUP(C329,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G329" s="39" t="str">
+      <c r="G329" s="35" t="str">
         <f>VLOOKUP(C329,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -15997,7 +15998,7 @@
         <f>VLOOKUP(C330,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G330" s="39" t="str">
+      <c r="G330" s="35" t="str">
         <f>VLOOKUP(C330,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -16023,7 +16024,7 @@
         <f>VLOOKUP(C331,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G331" s="39" t="str">
+      <c r="G331" s="35" t="str">
         <f>VLOOKUP(C331,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -16049,7 +16050,7 @@
         <f>VLOOKUP(C332,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G332" s="39" t="str">
+      <c r="G332" s="35" t="str">
         <f>VLOOKUP(C332,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -16075,7 +16076,7 @@
         <f>VLOOKUP(C333,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>160</v>
       </c>
-      <c r="G333" s="39" t="str">
+      <c r="G333" s="35" t="str">
         <f>VLOOKUP(C333,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>70,120</v>
       </c>
@@ -16101,7 +16102,7 @@
         <f>VLOOKUP(C334,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G334" s="39" t="str">
+      <c r="G334" s="35" t="str">
         <f>VLOOKUP(C334,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -16127,7 +16128,7 @@
         <f>VLOOKUP(C335,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>100</v>
       </c>
-      <c r="G335" s="39" t="str">
+      <c r="G335" s="35" t="str">
         <f>VLOOKUP(C335,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>50,90</v>
       </c>
@@ -16153,7 +16154,7 @@
         <f>VLOOKUP(C336,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>120</v>
       </c>
-      <c r="G336" s="39" t="str">
+      <c r="G336" s="35" t="str">
         <f>VLOOKUP(C336,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>55,100</v>
       </c>
@@ -16179,7 +16180,7 @@
         <f>VLOOKUP(C337,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>270</v>
       </c>
-      <c r="G337" s="39" t="str">
+      <c r="G337" s="35" t="str">
         <f>VLOOKUP(C337,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -16205,7 +16206,7 @@
         <f>VLOOKUP(C338,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>220</v>
       </c>
-      <c r="G338" s="39" t="str">
+      <c r="G338" s="35" t="str">
         <f>VLOOKUP(C338,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -16231,7 +16232,7 @@
         <f>VLOOKUP(C339,dish_base!$B$4:$O$94,14,FALSE)</f>
         <v>370</v>
       </c>
-      <c r="G339" s="39" t="str">
+      <c r="G339" s="35" t="str">
         <f>VLOOKUP(C339,dish_base!$B$4:$M$94,12,FALSE)</f>
         <v>80,130</v>
       </c>
@@ -17335,7 +17336,7 @@
       <c r="C6" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="15" t="s">
         <v>354</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -17375,7 +17376,7 @@
       <c r="C8" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="15" t="s">
         <v>363</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -17395,7 +17396,7 @@
       <c r="C9" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="15" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -17818,14 +17819,14 @@
       <c r="O4" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P4" s="18" t="s">
+      <c r="P4" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="S4" s="38" t="str">
+      <c r="S4" s="34" t="str">
         <f>IFERROR(VLOOKUP(B4,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>曲奇</v>
       </c>
-      <c r="T4" s="38" t="str">
+      <c r="T4" s="34" t="str">
         <f>IFERROR(VLOOKUP(B4,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17867,14 +17868,14 @@
       <c r="O5" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P5" s="18" t="s">
+      <c r="P5" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="S5" s="38" t="str">
+      <c r="S5" s="34" t="str">
         <f>IFERROR(VLOOKUP(B5,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>马卡龙</v>
       </c>
-      <c r="T5" s="38" t="str">
+      <c r="T5" s="34" t="str">
         <f>IFERROR(VLOOKUP(B5,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -17922,11 +17923,11 @@
       <c r="Q6" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S6" s="38" t="str">
+      <c r="S6" s="34" t="str">
         <f>IFERROR(VLOOKUP(B6,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T6" s="38" t="str">
+      <c r="T6" s="34" t="str">
         <f>IFERROR(VLOOKUP(B6,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>马卡龙</v>
       </c>
@@ -17968,14 +17969,14 @@
       <c r="O7" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P7" s="18" t="s">
+      <c r="P7" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="S7" s="38" t="str">
+      <c r="S7" s="34" t="str">
         <f>IFERROR(VLOOKUP(B7,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>布丁</v>
       </c>
-      <c r="T7" s="38" t="str">
+      <c r="T7" s="34" t="str">
         <f>IFERROR(VLOOKUP(B7,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18017,17 +18018,17 @@
       <c r="O8" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P8" s="18" t="s">
+      <c r="P8" s="15" t="s">
         <v>449</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S8" s="38" t="str">
+      <c r="S8" s="34" t="str">
         <f>IFERROR(VLOOKUP(B8,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>泡芙</v>
       </c>
-      <c r="T8" s="38" t="str">
+      <c r="T8" s="34" t="str">
         <f>IFERROR(VLOOKUP(B8,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18069,14 +18070,14 @@
       <c r="O9" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P9" s="18" t="s">
+      <c r="P9" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="S9" s="38" t="str">
+      <c r="S9" s="34" t="str">
         <f>IFERROR(VLOOKUP(B9,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>蛋挞</v>
       </c>
-      <c r="T9" s="38" t="str">
+      <c r="T9" s="34" t="str">
         <f>IFERROR(VLOOKUP(B9,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18118,14 +18119,14 @@
       <c r="O10" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P10" s="18" t="s">
+      <c r="P10" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S10" s="38" t="str">
+      <c r="S10" s="34" t="str">
         <f>IFERROR(VLOOKUP(B10,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>麻薯</v>
       </c>
-      <c r="T10" s="38" t="str">
+      <c r="T10" s="34" t="str">
         <f>IFERROR(VLOOKUP(B10,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18167,14 +18168,14 @@
       <c r="O11" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P11" s="18" t="s">
+      <c r="P11" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="S11" s="38" t="str">
+      <c r="S11" s="34" t="str">
         <f>IFERROR(VLOOKUP(B11,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>大福</v>
       </c>
-      <c r="T11" s="38" t="str">
+      <c r="T11" s="34" t="str">
         <f>IFERROR(VLOOKUP(B11,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18216,14 +18217,14 @@
       <c r="O12" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P12" s="18" t="s">
+      <c r="P12" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="S12" s="38" t="str">
+      <c r="S12" s="34" t="str">
         <f>IFERROR(VLOOKUP(B12,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>巧克力糖</v>
       </c>
-      <c r="T12" s="38" t="str">
+      <c r="T12" s="34" t="str">
         <f>IFERROR(VLOOKUP(B12,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18265,14 +18266,14 @@
       <c r="O13" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P13" s="18" t="s">
+      <c r="P13" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S13" s="38" t="str">
+      <c r="S13" s="34" t="str">
         <f>IFERROR(VLOOKUP(B13,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>果冻</v>
       </c>
-      <c r="T13" s="38" t="str">
+      <c r="T13" s="34" t="str">
         <f>IFERROR(VLOOKUP(B13,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18320,11 +18321,11 @@
       <c r="Q14" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S14" s="38" t="str">
+      <c r="S14" s="34" t="str">
         <f>IFERROR(VLOOKUP(B14,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>奶油小格</v>
       </c>
-      <c r="T14" s="38" t="str">
+      <c r="T14" s="34" t="str">
         <f>IFERROR(VLOOKUP(B14,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18366,14 +18367,14 @@
       <c r="O15" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="P15" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S15" s="38" t="str">
+      <c r="S15" s="34" t="str">
         <f>IFERROR(VLOOKUP(B15,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>糖豆</v>
       </c>
-      <c r="T15" s="38" t="str">
+      <c r="T15" s="34" t="str">
         <f>IFERROR(VLOOKUP(B15,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18421,11 +18422,11 @@
       <c r="Q16" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S16" s="38" t="str">
+      <c r="S16" s="34" t="str">
         <f>IFERROR(VLOOKUP(B16,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T16" s="38" t="str">
+      <c r="T16" s="34" t="str">
         <f>IFERROR(VLOOKUP(B16,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>糖豆</v>
       </c>
@@ -18467,14 +18468,14 @@
       <c r="O17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P17" s="18" t="s">
+      <c r="P17" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="S17" s="38" t="str">
+      <c r="S17" s="34" t="str">
         <f>IFERROR(VLOOKUP(B17,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>金巧克力</v>
       </c>
-      <c r="T17" s="38" t="str">
+      <c r="T17" s="34" t="str">
         <f>IFERROR(VLOOKUP(B17,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18516,17 +18517,17 @@
       <c r="O18" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P18" s="18" t="s">
+      <c r="P18" s="15" t="s">
         <v>462</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S18" s="38" t="str">
+      <c r="S18" s="34" t="str">
         <f>IFERROR(VLOOKUP(B18,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>奶片</v>
       </c>
-      <c r="T18" s="38" t="str">
+      <c r="T18" s="34" t="str">
         <f>IFERROR(VLOOKUP(B18,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18568,14 +18569,14 @@
       <c r="O19" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P19" s="18" t="s">
+      <c r="P19" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S19" s="38" t="str">
+      <c r="S19" s="34" t="str">
         <f>IFERROR(VLOOKUP(B19,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T19" s="38" t="str">
+      <c r="T19" s="34" t="str">
         <f>IFERROR(VLOOKUP(B19,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>圣代</v>
       </c>
@@ -18620,11 +18621,11 @@
       <c r="P20" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S20" s="38" t="str">
+      <c r="S20" s="34" t="str">
         <f>IFERROR(VLOOKUP(B20,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>圣代</v>
       </c>
-      <c r="T20" s="38" t="str">
+      <c r="T20" s="34" t="str">
         <f>IFERROR(VLOOKUP(B20,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18672,11 +18673,11 @@
       <c r="Q21" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S21" s="38" t="str">
+      <c r="S21" s="34" t="str">
         <f>IFERROR(VLOOKUP(B21,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T21" s="38" t="str">
+      <c r="T21" s="34" t="str">
         <f>IFERROR(VLOOKUP(B21,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18721,11 +18722,11 @@
       <c r="P22" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S22" s="38" t="str">
+      <c r="S22" s="34" t="str">
         <f>IFERROR(VLOOKUP(B22,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>甜筒</v>
       </c>
-      <c r="T22" s="38" t="str">
+      <c r="T22" s="34" t="str">
         <f>IFERROR(VLOOKUP(B22,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18770,14 +18771,14 @@
       <c r="O23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P23" s="18" t="s">
+      <c r="P23" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="S23" s="38" t="str">
+      <c r="S23" s="34" t="str">
         <f>IFERROR(VLOOKUP(B23,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>棒棒糖</v>
       </c>
-      <c r="T23" s="38" t="str">
+      <c r="T23" s="34" t="str">
         <f>IFERROR(VLOOKUP(B23,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18825,11 +18826,11 @@
       <c r="Q24" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S24" s="38" t="str">
+      <c r="S24" s="34" t="str">
         <f>IFERROR(VLOOKUP(B24,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T24" s="38" t="str">
+      <c r="T24" s="34" t="str">
         <f>IFERROR(VLOOKUP(B24,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>棒棒糖</v>
       </c>
@@ -18871,14 +18872,14 @@
       <c r="O25" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P25" s="18" t="s">
+      <c r="P25" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="S25" s="38" t="str">
+      <c r="S25" s="34" t="str">
         <f>IFERROR(VLOOKUP(B25,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>软糖</v>
       </c>
-      <c r="T25" s="38" t="str">
+      <c r="T25" s="34" t="str">
         <f>IFERROR(VLOOKUP(B25,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -18926,11 +18927,11 @@
       <c r="Q26" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S26" s="38" t="str">
+      <c r="S26" s="34" t="str">
         <f>IFERROR(VLOOKUP(B26,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T26" s="38" t="str">
+      <c r="T26" s="34" t="str">
         <f>IFERROR(VLOOKUP(B26,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>软糖</v>
       </c>
@@ -18972,17 +18973,17 @@
       <c r="O27" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P27" s="18" t="s">
+      <c r="P27" s="15" t="s">
         <v>471</v>
       </c>
       <c r="Q27" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S27" s="38" t="str">
+      <c r="S27" s="34" t="str">
         <f>IFERROR(VLOOKUP(B27,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>杯子蛋糕</v>
       </c>
-      <c r="T27" s="38" t="str">
+      <c r="T27" s="34" t="str">
         <f>IFERROR(VLOOKUP(B27,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19030,11 +19031,11 @@
       <c r="Q28" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S28" s="38" t="str">
+      <c r="S28" s="34" t="str">
         <f>IFERROR(VLOOKUP(B28,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T28" s="38" t="str">
+      <c r="T28" s="34" t="str">
         <f>IFERROR(VLOOKUP(B28,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>杯子蛋糕</v>
       </c>
@@ -19082,11 +19083,11 @@
       <c r="P29" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="S29" s="38" t="str">
+      <c r="S29" s="34" t="str">
         <f>IFERROR(VLOOKUP(B29,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>慕斯蛋糕</v>
       </c>
-      <c r="T29" s="38" t="str">
+      <c r="T29" s="34" t="str">
         <f>IFERROR(VLOOKUP(B29,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19134,11 +19135,11 @@
       <c r="Q30" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S30" s="38" t="str">
+      <c r="S30" s="34" t="str">
         <f>IFERROR(VLOOKUP(B30,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T30" s="38" t="str">
+      <c r="T30" s="34" t="str">
         <f>IFERROR(VLOOKUP(B30,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>慕斯蛋糕</v>
       </c>
@@ -19180,14 +19181,14 @@
       <c r="O31" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P31" s="18" t="s">
+      <c r="P31" s="15" t="s">
         <v>475</v>
       </c>
-      <c r="S31" s="38" t="str">
+      <c r="S31" s="34" t="str">
         <f>IFERROR(VLOOKUP(B31,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>太妃糖</v>
       </c>
-      <c r="T31" s="38" t="str">
+      <c r="T31" s="34" t="str">
         <f>IFERROR(VLOOKUP(B31,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19235,16 +19236,16 @@
       <c r="Q32" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S32" s="38" t="str">
+      <c r="S32" s="34" t="str">
         <f>IFERROR(VLOOKUP(B32,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T32" s="38" t="str">
+      <c r="T32" s="34" t="str">
         <f>IFERROR(VLOOKUP(B32,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>太妃糖</v>
       </c>
     </row>
-    <row r="33" s="36" customFormat="1" ht="17" spans="1:20">
+    <row r="33" s="32" customFormat="1" ht="17" spans="1:20">
       <c r="A33" s="1"/>
       <c r="B33" s="1" t="s">
         <v>262</v>
@@ -19284,14 +19285,14 @@
       <c r="O33" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P33" s="18" t="s">
+      <c r="P33" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="S33" s="38" t="str">
+      <c r="S33" s="34" t="str">
         <f>IFERROR(VLOOKUP(B33,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>牛轧糖</v>
       </c>
-      <c r="T33" s="38" t="str">
+      <c r="T33" s="34" t="str">
         <f>IFERROR(VLOOKUP(B33,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19339,11 +19340,11 @@
       <c r="Q34" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S34" s="38" t="str">
+      <c r="S34" s="34" t="str">
         <f>IFERROR(VLOOKUP(B34,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T34" s="38" t="str">
+      <c r="T34" s="34" t="str">
         <f>IFERROR(VLOOKUP(B34,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>牛轧糖</v>
       </c>
@@ -19385,14 +19386,14 @@
       <c r="O35" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P35" s="18" t="s">
+      <c r="P35" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S35" s="38" t="str">
+      <c r="S35" s="34" t="str">
         <f>IFERROR(VLOOKUP(B35,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T35" s="38" t="str">
+      <c r="T35" s="34" t="str">
         <f>IFERROR(VLOOKUP(B35,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>蛋卷</v>
       </c>
@@ -19437,11 +19438,11 @@
       <c r="P36" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S36" s="38" t="str">
+      <c r="S36" s="34" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>蛋卷</v>
       </c>
-      <c r="T36" s="38" t="str">
+      <c r="T36" s="34" t="str">
         <f>IFERROR(VLOOKUP(B36,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19486,11 +19487,11 @@
       <c r="P37" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="S37" s="38" t="str">
+      <c r="S37" s="34" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>巧克力棒</v>
       </c>
-      <c r="T37" s="38" t="str">
+      <c r="T37" s="34" t="str">
         <f>IFERROR(VLOOKUP(B37,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19538,11 +19539,11 @@
       <c r="Q38" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S38" s="38" t="str">
+      <c r="S38" s="34" t="str">
         <f>IFERROR(VLOOKUP(B38,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T38" s="38" t="str">
+      <c r="T38" s="34" t="str">
         <f>IFERROR(VLOOKUP(B38,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>巧克力棒</v>
       </c>
@@ -19590,11 +19591,11 @@
       <c r="Q39" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S39" s="38" t="str">
+      <c r="S39" s="34" t="str">
         <f>IFERROR(VLOOKUP(B39,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>闪电泡芙</v>
       </c>
-      <c r="T39" s="38" t="str">
+      <c r="T39" s="34" t="str">
         <f>IFERROR(VLOOKUP(B39,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19636,14 +19637,14 @@
       <c r="O40" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P40" s="18" t="s">
+      <c r="P40" s="15" t="s">
         <v>483</v>
       </c>
-      <c r="S40" s="38" t="str">
+      <c r="S40" s="34" t="str">
         <f>IFERROR(VLOOKUP(B40,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T40" s="38" t="str">
+      <c r="T40" s="34" t="str">
         <f>IFERROR(VLOOKUP(B40,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>闪电泡芙</v>
       </c>
@@ -19688,11 +19689,11 @@
       <c r="P41" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="S41" s="38" t="str">
+      <c r="S41" s="34" t="str">
         <f>IFERROR(VLOOKUP(B41,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>糖葫芦</v>
       </c>
-      <c r="T41" s="38" t="str">
+      <c r="T41" s="34" t="str">
         <f>IFERROR(VLOOKUP(B41,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19740,11 +19741,11 @@
       <c r="Q42" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S42" s="38" t="str">
+      <c r="S42" s="34" t="str">
         <f>IFERROR(VLOOKUP(B42,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T42" s="38" t="str">
+      <c r="T42" s="34" t="str">
         <f>IFERROR(VLOOKUP(B42,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>糖葫芦</v>
       </c>
@@ -19789,17 +19790,17 @@
       <c r="O43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P43" s="18" t="s">
+      <c r="P43" s="15" t="s">
         <v>485</v>
       </c>
       <c r="Q43" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S43" s="38" t="str">
+      <c r="S43" s="34" t="str">
         <f>IFERROR(VLOOKUP(B43,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>舒芙蕾</v>
       </c>
-      <c r="T43" s="38" t="str">
+      <c r="T43" s="34" t="str">
         <f>IFERROR(VLOOKUP(B43,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19844,11 +19845,11 @@
       <c r="P44" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S44" s="38" t="str">
+      <c r="S44" s="34" t="str">
         <f>IFERROR(VLOOKUP(B44,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>桃酥</v>
       </c>
-      <c r="T44" s="38" t="str">
+      <c r="T44" s="34" t="str">
         <f>IFERROR(VLOOKUP(B44,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19896,14 +19897,14 @@
       <c r="O45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P45" s="18" t="s">
+      <c r="P45" s="15" t="s">
         <v>490</v>
       </c>
-      <c r="S45" s="38" t="str">
+      <c r="S45" s="34" t="str">
         <f>IFERROR(VLOOKUP(B45,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T45" s="38" t="str">
+      <c r="T45" s="34" t="str">
         <f>IFERROR(VLOOKUP(B45,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19948,11 +19949,11 @@
       <c r="P46" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S46" s="38" t="str">
+      <c r="S46" s="34" t="str">
         <f>IFERROR(VLOOKUP(B46,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>月饼</v>
       </c>
-      <c r="T46" s="38" t="str">
+      <c r="T46" s="34" t="str">
         <f>IFERROR(VLOOKUP(B46,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -19997,11 +19998,11 @@
       <c r="P47" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="S47" s="38" t="str">
+      <c r="S47" s="34" t="str">
         <f>IFERROR(VLOOKUP(B47,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T47" s="38" t="str">
+      <c r="T47" s="34" t="str">
         <f>IFERROR(VLOOKUP(B47,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>月饼</v>
       </c>
@@ -20043,14 +20044,14 @@
       <c r="O48" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P48" s="18" t="s">
+      <c r="P48" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S48" s="38" t="str">
+      <c r="S48" s="34" t="str">
         <f>IFERROR(VLOOKUP(B48,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T48" s="38" t="str">
+      <c r="T48" s="34" t="str">
         <f>IFERROR(VLOOKUP(B48,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>华夫饼</v>
       </c>
@@ -20092,14 +20093,14 @@
       <c r="O49" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P49" s="18" t="s">
+      <c r="P49" s="15" t="s">
         <v>492</v>
       </c>
-      <c r="S49" s="38" t="str">
+      <c r="S49" s="34" t="str">
         <f>IFERROR(VLOOKUP(B49,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>华夫饼</v>
       </c>
-      <c r="T49" s="38" t="str">
+      <c r="T49" s="34" t="str">
         <f>IFERROR(VLOOKUP(B49,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20141,14 +20142,14 @@
       <c r="O50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P50" s="18" t="s">
+      <c r="P50" s="15" t="s">
         <v>493</v>
       </c>
-      <c r="S50" s="38" t="str">
+      <c r="S50" s="34" t="str">
         <f>IFERROR(VLOOKUP(B50,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>铜锣烧</v>
       </c>
-      <c r="T50" s="38" t="str">
+      <c r="T50" s="34" t="str">
         <f>IFERROR(VLOOKUP(B50,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20190,14 +20191,14 @@
       <c r="O51" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P51" s="18" t="s">
+      <c r="P51" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="S51" s="38" t="str">
+      <c r="S51" s="34" t="str">
         <f>IFERROR(VLOOKUP(B51,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T51" s="38" t="str">
+      <c r="T51" s="34" t="str">
         <f>IFERROR(VLOOKUP(B51,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>铜锣烧</v>
       </c>
@@ -20239,14 +20240,14 @@
       <c r="O52" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P52" s="18" t="s">
+      <c r="P52" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="S52" s="38" t="str">
+      <c r="S52" s="34" t="str">
         <f>IFERROR(VLOOKUP(B52,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>奶油蛋糕</v>
       </c>
-      <c r="T52" s="38" t="str">
+      <c r="T52" s="34" t="str">
         <f>IFERROR(VLOOKUP(B52,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20291,14 +20292,14 @@
       <c r="O53" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P53" s="18" t="s">
+      <c r="P53" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="S53" s="38" t="str">
+      <c r="S53" s="34" t="str">
         <f>IFERROR(VLOOKUP(B53,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T53" s="38" t="str">
+      <c r="T53" s="34" t="str">
         <f>IFERROR(VLOOKUP(B53,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>奶油蛋糕</v>
       </c>
@@ -20346,11 +20347,11 @@
       <c r="Q54" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S54" s="38" t="str">
+      <c r="S54" s="34" t="str">
         <f>IFERROR(VLOOKUP(B54,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>甜甜圈</v>
       </c>
-      <c r="T54" s="38" t="str">
+      <c r="T54" s="34" t="str">
         <f>IFERROR(VLOOKUP(B54,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20392,14 +20393,14 @@
       <c r="O55" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P55" s="18" t="s">
+      <c r="P55" s="15" t="s">
         <v>497</v>
       </c>
-      <c r="S55" s="38" t="str">
+      <c r="S55" s="34" t="str">
         <f>IFERROR(VLOOKUP(B55,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>椪糖</v>
       </c>
-      <c r="T55" s="38" t="str">
+      <c r="T55" s="34" t="str">
         <f>IFERROR(VLOOKUP(B55,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20447,11 +20448,11 @@
       <c r="Q56" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S56" s="38" t="str">
+      <c r="S56" s="34" t="str">
         <f>IFERROR(VLOOKUP(B56,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T56" s="38" t="str">
+      <c r="T56" s="34" t="str">
         <f>IFERROR(VLOOKUP(B56,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>椪糖</v>
       </c>
@@ -20493,14 +20494,14 @@
       <c r="O57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P57" s="18" t="s">
+      <c r="P57" s="15" t="s">
         <v>498</v>
       </c>
-      <c r="S57" s="38" t="str">
+      <c r="S57" s="34" t="str">
         <f>IFERROR(VLOOKUP(B57,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T57" s="38" t="str">
+      <c r="T57" s="34" t="str">
         <f>IFERROR(VLOOKUP(B57,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>芭菲</v>
       </c>
@@ -20545,11 +20546,11 @@
       <c r="P58" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="S58" s="38" t="str">
+      <c r="S58" s="34" t="str">
         <f>IFERROR(VLOOKUP(B58,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>芭菲</v>
       </c>
-      <c r="T58" s="38" t="str">
+      <c r="T58" s="34" t="str">
         <f>IFERROR(VLOOKUP(B58,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20594,11 +20595,11 @@
       <c r="P59" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="S59" s="38" t="str">
+      <c r="S59" s="34" t="str">
         <f>IFERROR(VLOOKUP(B59,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T59" s="38" t="str">
+      <c r="T59" s="34" t="str">
         <f>IFERROR(VLOOKUP(B59,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>圣代</v>
       </c>
@@ -20643,11 +20644,11 @@
       <c r="P60" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S60" s="38" t="str">
+      <c r="S60" s="34" t="str">
         <f>IFERROR(VLOOKUP(B60,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>圣代</v>
       </c>
-      <c r="T60" s="38" t="str">
+      <c r="T60" s="34" t="str">
         <f>IFERROR(VLOOKUP(B60,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20695,11 +20696,11 @@
       <c r="Q61" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S61" s="38" t="str">
+      <c r="S61" s="34" t="str">
         <f>IFERROR(VLOOKUP(B61,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>瑞士卷</v>
       </c>
-      <c r="T61" s="38" t="str">
+      <c r="T61" s="34" t="str">
         <f>IFERROR(VLOOKUP(B61,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20744,64 +20745,64 @@
       <c r="P62" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="S62" s="38" t="str">
+      <c r="S62" s="34" t="str">
         <f>IFERROR(VLOOKUP(B62,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T62" s="38" t="str">
+      <c r="T62" s="34" t="str">
         <f>IFERROR(VLOOKUP(B62,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>瑞士卷</v>
       </c>
     </row>
     <row r="63" spans="2:20">
-      <c r="B63" s="37" t="s">
+      <c r="B63" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="C63" s="37" t="s">
+      <c r="C63" s="33" t="s">
         <v>428</v>
       </c>
-      <c r="D63" s="37" t="s">
+      <c r="D63" s="33" t="s">
         <v>440</v>
       </c>
-      <c r="E63" s="37" t="s">
+      <c r="E63" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="F63" s="37" t="s">
+      <c r="F63" s="33" t="s">
         <v>431</v>
       </c>
-      <c r="G63" s="37" t="s">
+      <c r="G63" s="33" t="s">
         <v>438</v>
       </c>
-      <c r="H63" s="37"/>
-      <c r="I63" s="37" t="s">
+      <c r="H63" s="33"/>
+      <c r="I63" s="33" t="s">
         <v>501</v>
       </c>
-      <c r="J63" s="37" t="s">
+      <c r="J63" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="K63" s="37">
+      <c r="K63" s="33">
         <v>0</v>
       </c>
-      <c r="L63" s="37">
+      <c r="L63" s="33">
         <v>0</v>
       </c>
-      <c r="M63" s="37" t="s">
+      <c r="M63" s="33" t="s">
         <v>502</v>
       </c>
-      <c r="N63" s="37" t="s">
+      <c r="N63" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="O63" s="37" t="s">
+      <c r="O63" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="P63" s="37" t="s">
+      <c r="P63" s="33" t="s">
         <v>503</v>
       </c>
-      <c r="S63" s="38" t="str">
+      <c r="S63" s="34" t="str">
         <f>IFERROR(VLOOKUP(B63,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T63" s="38" t="str">
+      <c r="T63" s="34" t="str">
         <f>IFERROR(VLOOKUP(B63,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>杨枝甘露</v>
       </c>
@@ -20846,11 +20847,11 @@
       <c r="P64" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="S64" s="38" t="str">
+      <c r="S64" s="34" t="str">
         <f>IFERROR(VLOOKUP(B64,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>杨枝甘露</v>
       </c>
-      <c r="T64" s="38" t="str">
+      <c r="T64" s="34" t="str">
         <f>IFERROR(VLOOKUP(B64,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20895,64 +20896,64 @@
       <c r="P65" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="S65" s="38" t="str">
+      <c r="S65" s="34" t="str">
         <f>IFERROR(VLOOKUP(B65,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T65" s="38" t="str">
+      <c r="T65" s="34" t="str">
         <f>IFERROR(VLOOKUP(B65,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
     </row>
     <row r="66" spans="2:20">
-      <c r="B66" s="36" t="s">
+      <c r="B66" s="32" t="s">
         <v>310</v>
       </c>
-      <c r="C66" s="36" t="s">
+      <c r="C66" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="D66" s="36" t="s">
+      <c r="D66" s="32" t="s">
         <v>440</v>
       </c>
-      <c r="E66" s="36" t="s">
+      <c r="E66" s="32" t="s">
         <v>430</v>
       </c>
-      <c r="F66" s="36" t="s">
+      <c r="F66" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="G66" s="36" t="s">
+      <c r="G66" s="32" t="s">
         <v>438</v>
       </c>
-      <c r="H66" s="36"/>
-      <c r="I66" s="36" t="s">
+      <c r="H66" s="32"/>
+      <c r="I66" s="32" t="s">
         <v>501</v>
       </c>
-      <c r="J66" s="36" t="s">
+      <c r="J66" s="32" t="s">
         <v>472</v>
       </c>
-      <c r="K66" s="36">
+      <c r="K66" s="32">
         <v>0</v>
       </c>
-      <c r="L66" s="36">
+      <c r="L66" s="32">
         <v>0</v>
       </c>
-      <c r="M66" s="36" t="s">
+      <c r="M66" s="32" t="s">
         <v>473</v>
       </c>
-      <c r="N66" s="36" t="s">
+      <c r="N66" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="O66" s="36" t="s">
+      <c r="O66" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="P66" s="36" t="s">
+      <c r="P66" s="32" t="s">
         <v>504</v>
       </c>
-      <c r="S66" s="38" t="str">
+      <c r="S66" s="34" t="str">
         <f>IFERROR(VLOOKUP(B66,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T66" s="38" t="str">
+      <c r="T66" s="34" t="str">
         <f>IFERROR(VLOOKUP(B66,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -20994,14 +20995,14 @@
       <c r="O67" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P67" s="18" t="s">
+      <c r="P67" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="S67" s="38" t="str">
+      <c r="S67" s="34" t="str">
         <f>IFERROR(VLOOKUP(B67,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>苹果派</v>
       </c>
-      <c r="T67" s="38" t="str">
+      <c r="T67" s="34" t="str">
         <f>IFERROR(VLOOKUP(B67,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21049,11 +21050,11 @@
       <c r="P68" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="S68" s="38" t="str">
+      <c r="S68" s="34" t="str">
         <f>IFERROR(VLOOKUP(B68,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>水果蛋糕</v>
       </c>
-      <c r="T68" s="38" t="str">
+      <c r="T68" s="34" t="str">
         <f>IFERROR(VLOOKUP(B68,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21101,17 +21102,17 @@
       <c r="O69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P69" s="18" t="s">
+      <c r="P69" s="15" t="s">
         <v>508</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S69" s="38" t="str">
+      <c r="S69" s="34" t="str">
         <f>IFERROR(VLOOKUP(B69,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T69" s="38" t="str">
+      <c r="T69" s="34" t="str">
         <f>IFERROR(VLOOKUP(B69,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>水果蛋糕</v>
       </c>
@@ -21159,17 +21160,17 @@
       <c r="O70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P70" s="18" t="s">
+      <c r="P70" s="15" t="s">
         <v>512</v>
       </c>
       <c r="Q70" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S70" s="38" t="str">
+      <c r="S70" s="34" t="str">
         <f>IFERROR(VLOOKUP(B70,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>巧克力</v>
       </c>
-      <c r="T70" s="38" t="str">
+      <c r="T70" s="34" t="str">
         <f>IFERROR(VLOOKUP(B70,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21211,17 +21212,17 @@
       <c r="O71" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="P71" s="18" t="s">
+      <c r="P71" s="15" t="s">
         <v>449</v>
       </c>
       <c r="Q71" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="S71" s="38" t="str">
+      <c r="S71" s="34" t="str">
         <f>IFERROR(VLOOKUP(B71,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>牛角包</v>
       </c>
-      <c r="T71" s="38" t="str">
+      <c r="T71" s="34" t="str">
         <f>IFERROR(VLOOKUP(B71,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21266,11 +21267,11 @@
       <c r="P72" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="S72" s="38" t="str">
+      <c r="S72" s="34" t="str">
         <f>IFERROR(VLOOKUP(B72,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>蝴蝶酥</v>
       </c>
-      <c r="T72" s="38" t="str">
+      <c r="T72" s="34" t="str">
         <f>IFERROR(VLOOKUP(B72,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21315,16 +21316,16 @@
       <c r="O73" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P73" s="18" t="s">
+      <c r="P73" s="15" t="s">
         <v>514</v>
       </c>
-      <c r="S73" s="38" t="str">
+      <c r="S73" s="34" t="str">
         <f>IFERROR(VLOOKUP(B73,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T73" s="38" t="str">
+      <c r="T73" s="34" t="str">
         <f>IFERROR(VLOOKUP(B73,skill!$H$4:$K$51,4,FALSE),"")</f>
-        <v/>
+        <v>蝴蝶酥</v>
       </c>
     </row>
     <row r="74" spans="2:20">
@@ -21367,11 +21368,11 @@
       <c r="P74" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="S74" s="38" t="str">
+      <c r="S74" s="34" t="str">
         <f>IFERROR(VLOOKUP(B74,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>拐杖糖</v>
       </c>
-      <c r="T74" s="38" t="str">
+      <c r="T74" s="34" t="str">
         <f>IFERROR(VLOOKUP(B74,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21419,11 +21420,11 @@
       <c r="Q75" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S75" s="38" t="str">
+      <c r="S75" s="34" t="str">
         <f>IFERROR(VLOOKUP(B75,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T75" s="38" t="str">
+      <c r="T75" s="34" t="str">
         <f>IFERROR(VLOOKUP(B75,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>拐杖糖</v>
       </c>
@@ -21468,17 +21469,17 @@
       <c r="O76" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P76" s="18" t="s">
+      <c r="P76" s="15" t="s">
         <v>517</v>
       </c>
       <c r="Q76" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S76" s="38" t="str">
+      <c r="S76" s="34" t="str">
         <f>IFERROR(VLOOKUP(B76,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>大棒棒糖</v>
       </c>
-      <c r="T76" s="38" t="str">
+      <c r="T76" s="34" t="str">
         <f>IFERROR(VLOOKUP(B76,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21520,14 +21521,14 @@
       <c r="O77" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P77" s="18" t="s">
+      <c r="P77" s="15" t="s">
         <v>518</v>
       </c>
-      <c r="S77" s="38" t="str">
+      <c r="S77" s="34" t="str">
         <f>IFERROR(VLOOKUP(B77,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>棉花糖</v>
       </c>
-      <c r="T77" s="38" t="str">
+      <c r="T77" s="34" t="str">
         <f>IFERROR(VLOOKUP(B77,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21575,11 +21576,11 @@
       <c r="Q78" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S78" s="38" t="str">
+      <c r="S78" s="34" t="str">
         <f>IFERROR(VLOOKUP(B78,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v/>
       </c>
-      <c r="T78" s="38" t="str">
+      <c r="T78" s="34" t="str">
         <f>IFERROR(VLOOKUP(B78,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v>棉花糖</v>
       </c>
@@ -21627,11 +21628,11 @@
       <c r="P79" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="S79" s="38" t="str">
+      <c r="S79" s="34" t="str">
         <f>IFERROR(VLOOKUP(B79,skill!$G$4:$K$51,5,FALSE),"")</f>
         <v>双层蛋糕</v>
       </c>
-      <c r="T79" s="38" t="str">
+      <c r="T79" s="34" t="str">
         <f>IFERROR(VLOOKUP(B79,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21676,14 +21677,14 @@
       <c r="O80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P80" s="18" t="s">
+      <c r="P80" s="15" t="s">
         <v>522</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="S80" s="38"/>
-      <c r="T80" s="38" t="str">
+      <c r="S80" s="34"/>
+      <c r="T80" s="34" t="str">
         <f>IFERROR(VLOOKUP(B80,skill!$H$4:$K$51,4,FALSE),"")</f>
         <v/>
       </c>
@@ -21726,7 +21727,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="134" customHeight="1" spans="1:1">
-      <c r="A1" s="25"/>
+      <c r="A1" s="22"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="3:22">
       <c r="C4" s="2" t="s">
@@ -21744,8 +21745,8 @@
       <c r="G4" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="11"/>
       <c r="J4" s="2" t="s">
         <v>1</v>
       </c>
@@ -21762,7 +21763,7 @@
       <c r="O4" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="P4" s="30"/>
+      <c r="P4" s="11"/>
       <c r="Q4" s="3" t="s">
         <v>527</v>
       </c>
@@ -21795,7 +21796,7 @@
       <c r="F5" s="2">
         <v>10</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="14" t="s">
         <v>533</v>
       </c>
       <c r="H5" s="5"/>
@@ -21844,7 +21845,7 @@
       <c r="C6" s="2">
         <v>2</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="23" t="s">
         <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -21853,7 +21854,7 @@
       <c r="F6" s="2">
         <v>10</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="15" t="s">
         <v>542</v>
       </c>
       <c r="H6" s="9"/>
@@ -21909,7 +21910,7 @@
       <c r="F7" s="2">
         <v>40</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="15" t="s">
         <v>549</v>
       </c>
       <c r="H7" s="9"/>
@@ -21952,7 +21953,7 @@
       <c r="C8" s="2">
         <v>4</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="24" t="s">
         <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -21961,7 +21962,7 @@
       <c r="F8" s="2">
         <v>10</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="15" t="s">
         <v>553</v>
       </c>
       <c r="H8" s="9"/>
@@ -22006,7 +22007,7 @@
       <c r="F9" s="2">
         <v>10</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="15" t="s">
         <v>558</v>
       </c>
       <c r="H9" s="9"/>
@@ -22064,7 +22065,7 @@
       <c r="F10" s="2">
         <v>10</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="15" t="s">
         <v>563</v>
       </c>
       <c r="H10" s="9"/>
@@ -22111,7 +22112,7 @@
       <c r="F11" s="2">
         <v>10</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="15" t="s">
         <v>566</v>
       </c>
       <c r="H11" s="9"/>
@@ -22129,7 +22130,7 @@
       <c r="N11" s="1">
         <v>20</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="O11" s="14" t="s">
         <v>568</v>
       </c>
       <c r="P11" s="9"/>
@@ -22159,7 +22160,7 @@
       <c r="C12" s="2">
         <v>8</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="23" t="s">
         <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -22168,7 +22169,7 @@
       <c r="F12" s="2">
         <v>10</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="G12" s="15" t="s">
         <v>570</v>
       </c>
       <c r="H12" s="9"/>
@@ -22224,7 +22225,7 @@
       <c r="F13" s="2">
         <v>10</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="15" t="s">
         <v>575</v>
       </c>
       <c r="I13" s="1">
@@ -22274,7 +22275,7 @@
       <c r="C14" s="2">
         <v>10</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="24" t="s">
         <v>55</v>
       </c>
       <c r="E14" s="2" t="s">
@@ -22338,7 +22339,7 @@
       <c r="C15" s="2">
         <v>11</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="23" t="s">
         <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
@@ -22347,7 +22348,7 @@
       <c r="F15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="28" t="s">
         <v>586</v>
       </c>
       <c r="H15" s="9"/>
@@ -22416,7 +22417,7 @@
       <c r="F16" s="2">
         <v>10</v>
       </c>
-      <c r="G16" s="18" t="s">
+      <c r="G16" s="15" t="s">
         <v>593</v>
       </c>
       <c r="H16" s="9"/>
@@ -22471,7 +22472,7 @@
       <c r="C17" s="2">
         <v>13</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="25" t="s">
         <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
@@ -22480,7 +22481,7 @@
       <c r="F17" s="2">
         <v>10</v>
       </c>
-      <c r="G17" s="18" t="s">
+      <c r="G17" s="15" t="s">
         <v>601</v>
       </c>
       <c r="H17" s="9"/>
@@ -22544,7 +22545,7 @@
       <c r="F18" s="2">
         <v>20</v>
       </c>
-      <c r="G18" s="18" t="s">
+      <c r="G18" s="15" t="s">
         <v>608</v>
       </c>
       <c r="H18" s="9"/>
@@ -22605,7 +22606,7 @@
       <c r="C19" s="2">
         <v>15</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="24" t="s">
         <v>75</v>
       </c>
       <c r="E19" s="2" t="s">
@@ -22614,7 +22615,7 @@
       <c r="F19" s="2">
         <v>20</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="29" t="s">
         <v>615</v>
       </c>
       <c r="H19" s="9"/>
@@ -22701,7 +22702,7 @@
       <c r="C21" s="2">
         <v>16</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="23" t="s">
         <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -22710,7 +22711,7 @@
       <c r="F21" s="2">
         <v>20</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="15" t="s">
         <v>624</v>
       </c>
       <c r="H21" s="9"/>
@@ -22763,7 +22764,7 @@
       <c r="C22" s="2">
         <v>17</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="23" t="s">
         <v>81</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -22817,7 +22818,7 @@
       <c r="C23" s="2">
         <v>18</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="26" t="s">
         <v>84</v>
       </c>
       <c r="E23" s="2" t="s">
@@ -22872,7 +22873,7 @@
       <c r="C24" s="2">
         <v>19</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="24" t="s">
         <v>88</v>
       </c>
       <c r="E24" s="2" t="s">
@@ -22955,7 +22956,7 @@
       <c r="C26" s="2">
         <v>20</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="23" t="s">
         <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
@@ -23026,7 +23027,7 @@
       <c r="C28" s="2">
         <v>21</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="23" t="s">
         <v>102</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -23163,7 +23164,7 @@
       <c r="C31" s="2">
         <v>23</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="23" t="s">
         <v>115</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -23218,7 +23219,7 @@
       <c r="C32" s="2">
         <v>24</v>
       </c>
-      <c r="D32" s="27" t="s">
+      <c r="D32" s="24" t="s">
         <v>118</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -23281,7 +23282,7 @@
       <c r="L33" s="1">
         <v>1</v>
       </c>
-      <c r="M33" s="18" t="s">
+      <c r="M33" s="15" t="s">
         <v>73</v>
       </c>
       <c r="AD33" s="2" t="s">
@@ -23302,7 +23303,7 @@
       <c r="AD34" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="AE34" s="34" t="s">
+      <c r="AE34" s="30" t="s">
         <v>683</v>
       </c>
     </row>
@@ -23310,7 +23311,7 @@
       <c r="C35" s="2">
         <v>25</v>
       </c>
-      <c r="D35" s="26" t="s">
+      <c r="D35" s="23" t="s">
         <v>121</v>
       </c>
       <c r="E35" s="2" t="s">
@@ -23363,7 +23364,7 @@
       <c r="AD35" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="AE35" s="34" t="s">
+      <c r="AE35" s="30" t="s">
         <v>688</v>
       </c>
     </row>
@@ -23382,7 +23383,7 @@
       <c r="AD36" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="AE36" s="34" t="s">
+      <c r="AE36" s="30" t="s">
         <v>691</v>
       </c>
     </row>
@@ -23402,7 +23403,7 @@
       <c r="C38" s="2">
         <v>26</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="24" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="2" t="s">
@@ -23463,7 +23464,7 @@
       <c r="C40" s="2">
         <v>27</v>
       </c>
-      <c r="D40" s="30" t="s">
+      <c r="D40" s="11" t="s">
         <v>127</v>
       </c>
       <c r="E40" s="2" t="s">
@@ -23480,7 +23481,7 @@
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
-      <c r="M40" s="18" t="s">
+      <c r="M40" s="15" t="s">
         <v>73</v>
       </c>
       <c r="N40" s="9"/>
@@ -23710,7 +23711,7 @@
       <c r="F48" s="2">
         <v>40</v>
       </c>
-      <c r="G48" s="18" t="s">
+      <c r="G48" s="15" t="s">
         <v>714</v>
       </c>
       <c r="H48" s="9"/>
@@ -23756,7 +23757,7 @@
       <c r="C50" s="2">
         <v>31</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="24" t="s">
         <v>142</v>
       </c>
       <c r="E50" s="2" t="s">
@@ -23765,7 +23766,7 @@
       <c r="F50" s="2">
         <v>40</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G50" s="15" t="s">
         <v>719</v>
       </c>
       <c r="Q50" s="2" t="s">
@@ -23802,7 +23803,7 @@
       <c r="C52" s="2">
         <v>32</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" s="24" t="s">
         <v>145</v>
       </c>
       <c r="E52" s="2" t="s">
@@ -23861,7 +23862,7 @@
       <c r="C54" s="2">
         <v>33</v>
       </c>
-      <c r="D54" s="31" t="s">
+      <c r="D54" s="27" t="s">
         <v>148</v>
       </c>
       <c r="E54" s="2" t="s">
@@ -23870,7 +23871,7 @@
       <c r="F54" s="2">
         <v>40</v>
       </c>
-      <c r="G54" s="18" t="s">
+      <c r="G54" s="15" t="s">
         <v>730</v>
       </c>
       <c r="H54" s="9"/>
@@ -23922,7 +23923,7 @@
       <c r="F56" s="2">
         <v>60</v>
       </c>
-      <c r="G56" s="18" t="s">
+      <c r="G56" s="15" t="s">
         <v>736</v>
       </c>
       <c r="H56" s="9"/>
@@ -23962,7 +23963,7 @@
       <c r="F58" s="2">
         <v>60</v>
       </c>
-      <c r="G58" s="18" t="s">
+      <c r="G58" s="15" t="s">
         <v>737</v>
       </c>
     </row>
@@ -23998,7 +23999,7 @@
       <c r="C61" s="2">
         <v>36</v>
       </c>
-      <c r="D61" s="27" t="s">
+      <c r="D61" s="24" t="s">
         <v>157</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -24007,7 +24008,7 @@
       <c r="F61" s="2">
         <v>60</v>
       </c>
-      <c r="G61" s="18" t="s">
+      <c r="G61" s="15" t="s">
         <v>738</v>
       </c>
     </row>
@@ -24052,7 +24053,7 @@
       <c r="F64" s="2">
         <v>60</v>
       </c>
-      <c r="G64" s="18" t="s">
+      <c r="G64" s="15" t="s">
         <v>739</v>
       </c>
       <c r="H64" s="9"/>
@@ -24083,7 +24084,7 @@
       <c r="C66" s="2">
         <v>38</v>
       </c>
-      <c r="D66" s="27" t="s">
+      <c r="D66" s="24" t="s">
         <v>163</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -24092,7 +24093,7 @@
       <c r="F66" s="2">
         <v>60</v>
       </c>
-      <c r="G66" s="18" t="s">
+      <c r="G66" s="15" t="s">
         <v>740</v>
       </c>
       <c r="H66" s="9"/>
@@ -24132,7 +24133,7 @@
       <c r="F68" s="2">
         <v>60</v>
       </c>
-      <c r="G68" s="18" t="s">
+      <c r="G68" s="15" t="s">
         <v>741</v>
       </c>
     </row>
@@ -24168,7 +24169,7 @@
       <c r="C71" s="2">
         <v>40</v>
       </c>
-      <c r="D71" s="27" t="s">
+      <c r="D71" s="24" t="s">
         <v>169</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -24177,7 +24178,7 @@
       <c r="F71" s="2">
         <v>60</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="15" t="s">
         <v>742</v>
       </c>
     </row>
@@ -24213,7 +24214,7 @@
       <c r="C74" s="2">
         <v>41</v>
       </c>
-      <c r="D74" s="31" t="s">
+      <c r="D74" s="27" t="s">
         <v>172</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -24222,7 +24223,7 @@
       <c r="F74" s="2">
         <v>60</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G74" s="15" t="s">
         <v>743</v>
       </c>
       <c r="H74" s="9"/>
@@ -24253,7 +24254,7 @@
       <c r="C76" s="2">
         <v>42</v>
       </c>
-      <c r="D76" s="27" t="s">
+      <c r="D76" s="24" t="s">
         <v>175</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -24262,7 +24263,7 @@
       <c r="F76" s="2">
         <v>30</v>
       </c>
-      <c r="G76" s="18" t="s">
+      <c r="G76" s="15" t="s">
         <v>744</v>
       </c>
       <c r="H76" s="9"/>
@@ -24302,7 +24303,7 @@
       <c r="F78" s="2">
         <v>30</v>
       </c>
-      <c r="G78" s="32" t="s">
+      <c r="G78" s="28" t="s">
         <v>745</v>
       </c>
       <c r="H78" s="9"/>
@@ -24324,25 +24325,25 @@
         <v>546</v>
       </c>
       <c r="U78" s="3"/>
-      <c r="V78" s="35"/>
-      <c r="W78" s="35"/>
-      <c r="X78" s="35"/>
-      <c r="Y78" s="35"/>
-      <c r="Z78" s="35"/>
-      <c r="AA78" s="35"/>
-      <c r="AB78" s="35"/>
+      <c r="V78" s="31"/>
+      <c r="W78" s="31"/>
+      <c r="X78" s="31"/>
+      <c r="Y78" s="31"/>
+      <c r="Z78" s="31"/>
+      <c r="AA78" s="31"/>
+      <c r="AB78" s="31"/>
     </row>
     <row r="79" ht="17.6" customHeight="1" spans="5:22">
       <c r="E79" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="V79" s="35"/>
+      <c r="V79" s="31"/>
     </row>
     <row r="80" ht="34" spans="3:28">
       <c r="C80" s="2">
         <v>44</v>
       </c>
-      <c r="D80" s="26" t="s">
+      <c r="D80" s="23" t="s">
         <v>183</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -24351,16 +24352,16 @@
       <c r="F80" s="2">
         <v>40</v>
       </c>
-      <c r="G80" s="18" t="s">
+      <c r="G80" s="15" t="s">
         <v>746</v>
       </c>
-      <c r="V80" s="35"/>
-      <c r="W80" s="35"/>
-      <c r="X80" s="35"/>
-      <c r="Y80" s="35"/>
-      <c r="Z80" s="35"/>
-      <c r="AA80" s="35"/>
-      <c r="AB80" s="35"/>
+      <c r="V80" s="31"/>
+      <c r="W80" s="31"/>
+      <c r="X80" s="31"/>
+      <c r="Y80" s="31"/>
+      <c r="Z80" s="31"/>
+      <c r="AA80" s="31"/>
+      <c r="AB80" s="31"/>
     </row>
     <row r="81" spans="5:19">
       <c r="E81" s="2" t="s">
@@ -24394,7 +24395,7 @@
       <c r="C83" s="2">
         <v>45</v>
       </c>
-      <c r="D83" s="26" t="s">
+      <c r="D83" s="23" t="s">
         <v>186</v>
       </c>
       <c r="E83" s="2" t="s">
@@ -24403,36 +24404,36 @@
       <c r="F83" s="2">
         <v>110</v>
       </c>
-      <c r="G83" s="18" t="s">
+      <c r="G83" s="15" t="s">
         <v>747</v>
       </c>
-      <c r="V83" s="35"/>
+      <c r="V83" s="31"/>
     </row>
     <row r="84" ht="17.6" customHeight="1" spans="5:28">
       <c r="E84" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="U84" s="35"/>
-      <c r="V84" s="35"/>
-      <c r="W84" s="35"/>
-      <c r="X84" s="35"/>
-      <c r="Y84" s="35"/>
-      <c r="Z84" s="35"/>
-      <c r="AA84" s="35"/>
-      <c r="AB84" s="35"/>
+      <c r="U84" s="31"/>
+      <c r="V84" s="31"/>
+      <c r="W84" s="31"/>
+      <c r="X84" s="31"/>
+      <c r="Y84" s="31"/>
+      <c r="Z84" s="31"/>
+      <c r="AA84" s="31"/>
+      <c r="AB84" s="31"/>
     </row>
     <row r="85" ht="17.6" customHeight="1" spans="5:28">
       <c r="E85" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="U85" s="35"/>
-      <c r="V85" s="35"/>
-      <c r="W85" s="35"/>
-      <c r="X85" s="35"/>
-      <c r="Y85" s="35"/>
-      <c r="Z85" s="35"/>
-      <c r="AA85" s="35"/>
-      <c r="AB85" s="35"/>
+      <c r="U85" s="31"/>
+      <c r="V85" s="31"/>
+      <c r="W85" s="31"/>
+      <c r="X85" s="31"/>
+      <c r="Y85" s="31"/>
+      <c r="Z85" s="31"/>
+      <c r="AA85" s="31"/>
+      <c r="AB85" s="31"/>
     </row>
     <row r="86" ht="17.6" spans="5:28">
       <c r="E86" s="2" t="s">
@@ -24456,33 +24457,33 @@
       <c r="S86" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="U86" s="35"/>
-      <c r="V86" s="35"/>
-      <c r="W86" s="35"/>
-      <c r="X86" s="35"/>
-      <c r="Y86" s="35"/>
-      <c r="Z86" s="35"/>
-      <c r="AA86" s="35"/>
-      <c r="AB86" s="35"/>
+      <c r="U86" s="31"/>
+      <c r="V86" s="31"/>
+      <c r="W86" s="31"/>
+      <c r="X86" s="31"/>
+      <c r="Y86" s="31"/>
+      <c r="Z86" s="31"/>
+      <c r="AA86" s="31"/>
+      <c r="AB86" s="31"/>
     </row>
     <row r="87" ht="17.6" customHeight="1" spans="5:28">
       <c r="E87" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="U87" s="35"/>
-      <c r="V87" s="35"/>
-      <c r="W87" s="35"/>
-      <c r="X87" s="35"/>
-      <c r="Y87" s="35"/>
-      <c r="Z87" s="35"/>
-      <c r="AA87" s="35"/>
-      <c r="AB87" s="35"/>
+      <c r="U87" s="31"/>
+      <c r="V87" s="31"/>
+      <c r="W87" s="31"/>
+      <c r="X87" s="31"/>
+      <c r="Y87" s="31"/>
+      <c r="Z87" s="31"/>
+      <c r="AA87" s="31"/>
+      <c r="AB87" s="31"/>
     </row>
     <row r="88" ht="51" spans="3:28">
       <c r="C88" s="2">
         <v>46</v>
       </c>
-      <c r="D88" s="26" t="s">
+      <c r="D88" s="23" t="s">
         <v>190</v>
       </c>
       <c r="E88" s="2" t="s">
@@ -24491,17 +24492,17 @@
       <c r="F88" s="2">
         <v>90</v>
       </c>
-      <c r="G88" s="18" t="s">
+      <c r="G88" s="15" t="s">
         <v>748</v>
       </c>
-      <c r="U88" s="35"/>
-      <c r="V88" s="35"/>
-      <c r="W88" s="35"/>
-      <c r="X88" s="35"/>
-      <c r="Y88" s="35"/>
-      <c r="Z88" s="35"/>
-      <c r="AA88" s="35"/>
-      <c r="AB88" s="35"/>
+      <c r="U88" s="31"/>
+      <c r="V88" s="31"/>
+      <c r="W88" s="31"/>
+      <c r="X88" s="31"/>
+      <c r="Y88" s="31"/>
+      <c r="Z88" s="31"/>
+      <c r="AA88" s="31"/>
+      <c r="AB88" s="31"/>
     </row>
     <row r="89" ht="17.6" spans="5:28">
       <c r="E89" s="2" t="s">
@@ -24516,13 +24517,13 @@
       <c r="S89" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="V89" s="35"/>
-      <c r="W89" s="35"/>
-      <c r="X89" s="35"/>
-      <c r="Y89" s="35"/>
-      <c r="Z89" s="35"/>
-      <c r="AA89" s="35"/>
-      <c r="AB89" s="35"/>
+      <c r="V89" s="31"/>
+      <c r="W89" s="31"/>
+      <c r="X89" s="31"/>
+      <c r="Y89" s="31"/>
+      <c r="Z89" s="31"/>
+      <c r="AA89" s="31"/>
+      <c r="AB89" s="31"/>
     </row>
     <row r="90" spans="5:5">
       <c r="E90" s="2" t="s">
@@ -24533,7 +24534,7 @@
       <c r="C91" s="2">
         <v>47</v>
       </c>
-      <c r="D91" s="27" t="s">
+      <c r="D91" s="24" t="s">
         <v>193</v>
       </c>
       <c r="E91" s="2" t="s">
@@ -24581,474 +24582,474 @@
   </cols>
   <sheetData>
     <row r="4" ht="45" customHeight="1" spans="8:41">
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20" t="s">
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="N4" s="20" t="s">
+      <c r="N4" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="P4" s="20" t="s">
+      <c r="P4" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="20"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="20"/>
-      <c r="AA4" s="20" t="s">
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="V4" s="16"/>
+      <c r="W4" s="16"/>
+      <c r="X4" s="17"/>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="17"/>
+      <c r="AA4" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AB4" s="20" t="s">
+      <c r="AB4" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AC4" s="20" t="s">
+      <c r="AC4" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AD4" s="20" t="s">
+      <c r="AD4" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AE4" s="20"/>
-      <c r="AF4" s="20"/>
-      <c r="AG4" s="23"/>
-      <c r="AH4" s="23"/>
-      <c r="AI4" s="23"/>
-      <c r="AJ4" s="23"/>
-      <c r="AK4" s="23"/>
-      <c r="AL4" s="23"/>
-      <c r="AM4" s="23"/>
-      <c r="AN4" s="23"/>
-      <c r="AO4" s="23"/>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="17"/>
+      <c r="AG4" s="20"/>
+      <c r="AH4" s="20"/>
+      <c r="AI4" s="20"/>
+      <c r="AJ4" s="20"/>
+      <c r="AK4" s="20"/>
+      <c r="AL4" s="20"/>
+      <c r="AM4" s="20"/>
+      <c r="AN4" s="20"/>
+      <c r="AO4" s="20"/>
     </row>
     <row r="5" ht="45" customHeight="1" spans="8:41">
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="N5" s="20" t="s">
+      <c r="N5" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="O5" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="P5" s="20" t="s">
+      <c r="P5" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="V5" s="19"/>
-      <c r="W5" s="19"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20" t="s">
+      <c r="Q5" s="17"/>
+      <c r="R5" s="17"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="17"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AB5" s="20" t="s">
+      <c r="AB5" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AC5" s="20" t="s">
+      <c r="AC5" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AD5" s="20" t="s">
+      <c r="AD5" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AE5" s="20"/>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="23"/>
-      <c r="AH5" s="23"/>
-      <c r="AI5" s="23"/>
-      <c r="AJ5" s="23"/>
-      <c r="AK5" s="23"/>
-      <c r="AL5" s="23"/>
-      <c r="AM5" s="23"/>
-      <c r="AN5" s="23"/>
-      <c r="AO5" s="23"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="17"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="20"/>
+      <c r="AK5" s="20"/>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="20"/>
+      <c r="AO5" s="20"/>
     </row>
     <row r="6" ht="45" customHeight="1" spans="8:41">
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="20" t="s">
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="M6" s="18" t="s">
         <v>754</v>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="20" t="s">
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="R6" s="20" t="s">
+      <c r="R6" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="V6" s="19"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="20" t="s">
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="Y6" s="20" t="s">
+      <c r="Y6" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="Z6" s="20" t="s">
+      <c r="Z6" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="AA6" s="20" t="s">
+      <c r="AA6" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="AB6" s="20" t="s">
+      <c r="AB6" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="AC6" s="20" t="s">
+      <c r="AC6" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="20" t="s">
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="AF6" s="20" t="s">
+      <c r="AF6" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="AG6" s="23"/>
-      <c r="AH6" s="23"/>
-      <c r="AI6" s="23"/>
-      <c r="AJ6" s="24"/>
-      <c r="AK6" s="24"/>
-      <c r="AL6" s="24"/>
-      <c r="AM6" s="23"/>
-      <c r="AN6" s="23"/>
-      <c r="AO6" s="23"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="20"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="21"/>
+      <c r="AL6" s="21"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="20"/>
+      <c r="AO6" s="20"/>
     </row>
     <row r="7" ht="45" customHeight="1" spans="8:41">
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="20" t="s">
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="L7" s="20" t="s">
+      <c r="L7" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="M7" s="21" t="s">
+      <c r="M7" s="18" t="s">
         <v>759</v>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="21" t="s">
+      <c r="N7" s="19"/>
+      <c r="O7" s="18" t="s">
         <v>759</v>
       </c>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="20" t="s">
+      <c r="P7" s="19"/>
+      <c r="Q7" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="R7" s="20" t="s">
+      <c r="R7" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="20" t="s">
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="Y7" s="20" t="s">
+      <c r="Y7" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="Z7" s="20" t="s">
+      <c r="Z7" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="AA7" s="20" t="s">
+      <c r="AA7" s="17" t="s">
         <v>757</v>
       </c>
-      <c r="AB7" s="22"/>
-      <c r="AC7" s="20" t="s">
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="AD7" s="22"/>
-      <c r="AE7" s="20" t="s">
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="AF7" s="20" t="s">
+      <c r="AF7" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="AG7" s="23"/>
-      <c r="AH7" s="23"/>
-      <c r="AI7" s="23"/>
-      <c r="AJ7" s="24"/>
-      <c r="AK7" s="23"/>
-      <c r="AL7" s="24"/>
-      <c r="AM7" s="23"/>
-      <c r="AN7" s="23"/>
-      <c r="AO7" s="23"/>
+      <c r="AG7" s="20"/>
+      <c r="AH7" s="20"/>
+      <c r="AI7" s="20"/>
+      <c r="AJ7" s="21"/>
+      <c r="AK7" s="20"/>
+      <c r="AL7" s="21"/>
+      <c r="AM7" s="20"/>
+      <c r="AN7" s="20"/>
+      <c r="AO7" s="20"/>
     </row>
     <row r="8" ht="45" customHeight="1" spans="8:41">
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="J8" s="20" t="s">
+      <c r="J8" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="L8" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="20" t="s">
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="R8" s="20" t="s">
+      <c r="R8" s="17" t="s">
         <v>753</v>
       </c>
-      <c r="V8" s="20" t="s">
+      <c r="V8" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="W8" s="20" t="s">
+      <c r="W8" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="X8" s="20" t="s">
+      <c r="X8" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="Y8" s="20" t="s">
+      <c r="Y8" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="Z8" s="20" t="s">
+      <c r="Z8" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="AA8" s="22"/>
-      <c r="AB8" s="22"/>
-      <c r="AC8" s="22"/>
-      <c r="AD8" s="22"/>
-      <c r="AE8" s="20" t="s">
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="AF8" s="20" t="s">
+      <c r="AF8" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="AG8" s="23"/>
-      <c r="AH8" s="23"/>
-      <c r="AI8" s="23"/>
-      <c r="AJ8" s="24"/>
-      <c r="AK8" s="24"/>
-      <c r="AL8" s="24"/>
-      <c r="AM8" s="23"/>
-      <c r="AN8" s="23"/>
-      <c r="AO8" s="23"/>
+      <c r="AG8" s="20"/>
+      <c r="AH8" s="20"/>
+      <c r="AI8" s="20"/>
+      <c r="AJ8" s="21"/>
+      <c r="AK8" s="21"/>
+      <c r="AL8" s="21"/>
+      <c r="AM8" s="20"/>
+      <c r="AN8" s="20"/>
+      <c r="AO8" s="20"/>
     </row>
     <row r="9" ht="45" customHeight="1" spans="8:41">
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20" t="s">
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="N9" s="20" t="s">
+      <c r="N9" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="O9" s="20" t="s">
+      <c r="O9" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="P9" s="20" t="s">
+      <c r="P9" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="V9" s="20"/>
-      <c r="W9" s="20"/>
-      <c r="X9" s="20"/>
-      <c r="Y9" s="20"/>
-      <c r="Z9" s="20"/>
-      <c r="AA9" s="20" t="s">
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AB9" s="20" t="s">
+      <c r="AB9" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AC9" s="20" t="s">
+      <c r="AC9" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AD9" s="20" t="s">
+      <c r="AD9" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AE9" s="20"/>
-      <c r="AF9" s="20"/>
-      <c r="AG9" s="23"/>
-      <c r="AH9" s="23"/>
-      <c r="AI9" s="23"/>
-      <c r="AJ9" s="19" t="s">
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="20"/>
+      <c r="AH9" s="20"/>
+      <c r="AI9" s="20"/>
+      <c r="AJ9" s="16" t="s">
         <v>761</v>
       </c>
-      <c r="AK9" s="19" t="s">
+      <c r="AK9" s="16" t="s">
         <v>761</v>
       </c>
-      <c r="AL9" s="19" t="s">
+      <c r="AL9" s="16" t="s">
         <v>761</v>
       </c>
-      <c r="AM9" s="23"/>
-      <c r="AN9" s="23"/>
-      <c r="AO9" s="23"/>
+      <c r="AM9" s="20"/>
+      <c r="AN9" s="20"/>
+      <c r="AO9" s="20"/>
     </row>
     <row r="10" ht="45" customHeight="1" spans="8:41">
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20" t="s">
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="O10" s="20" t="s">
+      <c r="O10" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="P10" s="20" t="s">
+      <c r="P10" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="X10" s="20"/>
-      <c r="Y10" s="20"/>
-      <c r="Z10" s="20"/>
-      <c r="AA10" s="20" t="s">
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="V10" s="17"/>
+      <c r="W10" s="17"/>
+      <c r="X10" s="17"/>
+      <c r="Y10" s="17"/>
+      <c r="Z10" s="17"/>
+      <c r="AA10" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AB10" s="20" t="s">
+      <c r="AB10" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AC10" s="20" t="s">
+      <c r="AC10" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AD10" s="20" t="s">
+      <c r="AD10" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AE10" s="20"/>
-      <c r="AF10" s="20"/>
-      <c r="AG10" s="23"/>
-      <c r="AH10" s="23"/>
-      <c r="AI10" s="23"/>
-      <c r="AJ10" s="19" t="s">
+      <c r="AE10" s="17"/>
+      <c r="AF10" s="17"/>
+      <c r="AG10" s="20"/>
+      <c r="AH10" s="20"/>
+      <c r="AI10" s="20"/>
+      <c r="AJ10" s="16" t="s">
         <v>762</v>
       </c>
-      <c r="AK10" s="19" t="s">
+      <c r="AK10" s="16" t="s">
         <v>762</v>
       </c>
-      <c r="AL10" s="19" t="s">
+      <c r="AL10" s="16" t="s">
         <v>762</v>
       </c>
-      <c r="AM10" s="23"/>
-      <c r="AN10" s="23"/>
-      <c r="AO10" s="23"/>
+      <c r="AM10" s="20"/>
+      <c r="AN10" s="20"/>
+      <c r="AO10" s="20"/>
     </row>
     <row r="11" ht="45" customHeight="1" spans="8:41">
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20" t="s">
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="N11" s="20" t="s">
+      <c r="N11" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="19"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="19"/>
-      <c r="Z11" s="19"/>
-      <c r="AA11" s="20" t="s">
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AB11" s="20" t="s">
+      <c r="AB11" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AC11" s="19"/>
-      <c r="AD11" s="19"/>
-      <c r="AE11" s="19"/>
-      <c r="AF11" s="19"/>
-      <c r="AG11" s="23"/>
-      <c r="AH11" s="23"/>
-      <c r="AI11" s="23"/>
-      <c r="AJ11" s="19" t="s">
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="16" t="s">
         <v>762</v>
       </c>
-      <c r="AK11" s="19" t="s">
+      <c r="AK11" s="16" t="s">
         <v>762</v>
       </c>
-      <c r="AL11" s="19" t="s">
+      <c r="AL11" s="16" t="s">
         <v>762</v>
       </c>
-      <c r="AM11" s="23"/>
-      <c r="AN11" s="23"/>
-      <c r="AO11" s="23"/>
+      <c r="AM11" s="20"/>
+      <c r="AN11" s="20"/>
+      <c r="AO11" s="20"/>
     </row>
     <row r="12" ht="45" customHeight="1" spans="8:32">
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="20" t="s">
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="N12" s="20" t="s">
+      <c r="N12" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="19"/>
-      <c r="Y12" s="19"/>
-      <c r="Z12" s="19"/>
-      <c r="AA12" s="20" t="s">
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AB12" s="20" t="s">
+      <c r="AB12" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="AC12" s="19"/>
-      <c r="AD12" s="19"/>
-      <c r="AE12" s="19"/>
-      <c r="AF12" s="19"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
     </row>
     <row r="14" spans="13:13">
       <c r="M14" s="2" t="s">
@@ -25244,7 +25245,7 @@
       <c r="F11" s="1">
         <v>20</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="14" t="s">
         <v>772</v>
       </c>
       <c r="I11" t="s">
@@ -25571,7 +25572,7 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="18"/>
+      <c r="W24" s="15"/>
     </row>
     <row r="25" ht="34" spans="3:23">
       <c r="C25" s="6"/>
@@ -25746,7 +25747,7 @@
         <v>773</v>
       </c>
       <c r="V31" s="9"/>
-      <c r="W31" s="18"/>
+      <c r="W31" s="15"/>
     </row>
     <row r="32" ht="51" spans="3:11">
       <c r="C32" s="8"/>
@@ -25930,13 +25931,13 @@
       <c r="D46" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="1">
         <v>40</v>
       </c>
-      <c r="G46" s="17" t="s">
+      <c r="G46" s="9" t="s">
         <v>812</v>
       </c>
       <c r="I46" t="s">
@@ -25955,54 +25956,50 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="3:7">
+    <row r="47" spans="3:5">
       <c r="C47" s="10"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12" t="s">
+      <c r="D47" s="1"/>
+      <c r="E47" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
     </row>
     <row r="48" ht="34" spans="3:9">
       <c r="C48" s="10"/>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="12" t="s">
+      <c r="E48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="1">
         <v>40</v>
       </c>
-      <c r="G48" s="17" t="s">
+      <c r="G48" s="9" t="s">
         <v>813</v>
       </c>
       <c r="I48" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="49" spans="3:7">
+    <row r="49" spans="3:5">
       <c r="C49" s="10"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12" t="s">
+      <c r="D49" s="1"/>
+      <c r="E49" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
     </row>
     <row r="50" ht="51" spans="3:11">
       <c r="C50" s="10"/>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="1">
         <v>40</v>
       </c>
-      <c r="G50" s="17" t="s">
+      <c r="G50" s="9" t="s">
         <v>814</v>
       </c>
       <c r="I50" t="s">
@@ -26015,27 +26012,25 @@
         <v>797</v>
       </c>
     </row>
-    <row r="51" spans="3:7">
+    <row r="51" spans="3:5">
       <c r="C51" s="10"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12" t="s">
+      <c r="D51" s="1"/>
+      <c r="E51" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
     </row>
     <row r="52" ht="51" spans="3:11">
       <c r="C52" s="10"/>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="1">
         <v>40</v>
       </c>
-      <c r="G52" s="17" t="s">
+      <c r="G52" s="9" t="s">
         <v>815</v>
       </c>
       <c r="I52" t="s">
@@ -26050,25 +26045,25 @@
     </row>
     <row r="53" ht="17.6" spans="3:7">
       <c r="C53" s="10"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="12" t="s">
+      <c r="D53" s="11"/>
+      <c r="E53" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F53" s="12"/>
-      <c r="G53" s="17"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="9"/>
     </row>
     <row r="54" ht="51" spans="3:11">
       <c r="C54" s="10"/>
       <c r="D54" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="E54" s="12" t="s">
+      <c r="E54" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="1">
         <v>40</v>
       </c>
-      <c r="G54" s="17" t="s">
+      <c r="G54" s="9" t="s">
         <v>816</v>
       </c>
       <c r="I54" t="s">
@@ -26081,41 +26076,37 @@
         <v>787</v>
       </c>
     </row>
-    <row r="55" spans="3:7">
+    <row r="55" spans="3:5">
       <c r="C55" s="10"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12" t="s">
+      <c r="D55" s="1"/>
+      <c r="E55" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
     </row>
     <row r="56" ht="51" spans="3:9">
       <c r="C56" s="10"/>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="E56" s="12" t="s">
+      <c r="E56" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="1">
         <v>40</v>
       </c>
-      <c r="G56" s="17" t="s">
+      <c r="G56" s="9" t="s">
         <v>817</v>
       </c>
       <c r="I56" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="57" spans="3:7">
+    <row r="57" spans="3:5">
       <c r="C57" s="10"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12" t="s">
+      <c r="D57" s="1"/>
+      <c r="E57" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
     </row>
     <row r="58" spans="3:5">
       <c r="C58" s="10"/>
@@ -26124,7 +26115,7 @@
       </c>
     </row>
     <row r="59" ht="68" spans="3:19">
-      <c r="C59" s="15" t="s">
+      <c r="C59" s="13" t="s">
         <v>818</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -26136,7 +26127,7 @@
       <c r="F59" s="1">
         <v>60</v>
       </c>
-      <c r="G59" s="18" t="s">
+      <c r="G59" s="15" t="s">
         <v>820</v>
       </c>
       <c r="I59" t="s">
@@ -26162,15 +26153,15 @@
       </c>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="15"/>
-      <c r="D60" s="12"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="1"/>
       <c r="E60" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="61" ht="51" spans="3:11">
-      <c r="C61" s="15"/>
-      <c r="D61" s="14" t="s">
+      <c r="C61" s="13"/>
+      <c r="D61" s="12" t="s">
         <v>821</v>
       </c>
       <c r="E61" s="2" t="s">
@@ -26193,22 +26184,22 @@
       </c>
     </row>
     <row r="62" spans="3:5">
-      <c r="C62" s="15"/>
-      <c r="D62" s="12"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="1"/>
       <c r="E62" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="63" ht="51" spans="3:11">
-      <c r="C63" s="15"/>
-      <c r="D63" s="13" t="s">
+      <c r="C63" s="13"/>
+      <c r="D63" s="11" t="s">
         <v>160</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F63" s="1"/>
-      <c r="G63" s="18" t="s">
+      <c r="G63" s="15" t="s">
         <v>823</v>
       </c>
       <c r="I63" t="s">
@@ -26222,8 +26213,8 @@
       </c>
     </row>
     <row r="64" spans="3:7">
-      <c r="C64" s="15"/>
-      <c r="D64" s="12"/>
+      <c r="C64" s="13"/>
+      <c r="D64" s="1"/>
       <c r="E64" s="2" t="s">
         <v>111</v>
       </c>
@@ -26231,7 +26222,7 @@
       <c r="G64" s="2"/>
     </row>
     <row r="65" ht="68" spans="3:11">
-      <c r="C65" s="15"/>
+      <c r="C65" s="13"/>
       <c r="D65" s="11" t="s">
         <v>169</v>
       </c>
@@ -26239,7 +26230,7 @@
         <v>73</v>
       </c>
       <c r="F65" s="1"/>
-      <c r="G65" s="18" t="s">
+      <c r="G65" s="15" t="s">
         <v>824</v>
       </c>
       <c r="I65" t="s">
@@ -26253,18 +26244,18 @@
       </c>
     </row>
     <row r="66" spans="3:11">
-      <c r="C66" s="15"/>
-      <c r="D66" s="12"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="1"/>
       <c r="E66" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="2"/>
-      <c r="K66" s="18"/>
+      <c r="K66" s="15"/>
     </row>
     <row r="67" spans="3:11">
-      <c r="C67" s="15"/>
-      <c r="D67" s="12"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="1"/>
       <c r="E67" s="2" t="s">
         <v>73</v>
       </c>
@@ -26273,24 +26264,24 @@
       <c r="K67" s="2"/>
     </row>
     <row r="68" ht="34" spans="3:11">
-      <c r="C68" s="15"/>
-      <c r="D68" s="13" t="s">
+      <c r="C68" s="13"/>
+      <c r="D68" s="11" t="s">
         <v>151</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F68" s="1"/>
-      <c r="G68" s="18" t="s">
+      <c r="G68" s="15" t="s">
         <v>825</v>
       </c>
       <c r="I68" t="s">
         <v>777</v>
       </c>
-      <c r="K68" s="18"/>
+      <c r="K68" s="15"/>
     </row>
     <row r="69" spans="3:7">
-      <c r="C69" s="15"/>
+      <c r="C69" s="13"/>
       <c r="D69" s="2"/>
       <c r="E69" s="2" t="s">
         <v>73</v>
@@ -26299,16 +26290,16 @@
       <c r="G69" s="2"/>
     </row>
     <row r="70" spans="3:7">
-      <c r="C70" s="15"/>
+      <c r="C70" s="13"/>
       <c r="D70" s="2"/>
       <c r="E70" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F70" s="9"/>
-      <c r="G70" s="18"/>
+      <c r="G70" s="15"/>
     </row>
     <row r="71" ht="34" spans="3:9">
-      <c r="C71" s="15"/>
+      <c r="C71" s="13"/>
       <c r="D71" s="1" t="s">
         <v>190</v>
       </c>
@@ -26316,7 +26307,7 @@
         <v>73</v>
       </c>
       <c r="F71" s="1"/>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="15" t="s">
         <v>826</v>
       </c>
       <c r="I71" t="s">
@@ -26324,16 +26315,16 @@
       </c>
     </row>
     <row r="72" spans="3:7">
-      <c r="C72" s="15"/>
+      <c r="C72" s="13"/>
       <c r="D72" s="2"/>
       <c r="E72" s="2" t="s">
         <v>73</v>
       </c>
       <c r="F72" s="9"/>
-      <c r="G72" s="18"/>
+      <c r="G72" s="15"/>
     </row>
     <row r="73" spans="3:7">
-      <c r="C73" s="15"/>
+      <c r="C73" s="13"/>
       <c r="E73" s="2" t="s">
         <v>73</v>
       </c>
@@ -26353,22 +26344,22 @@
       <c r="F74" s="2">
         <v>110</v>
       </c>
-      <c r="G74" s="18" t="s">
+      <c r="G74" s="15" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="75" spans="3:7">
       <c r="C75" s="9"/>
-      <c r="D75" s="12"/>
+      <c r="D75" s="1"/>
       <c r="E75" s="2" t="s">
         <v>111</v>
       </c>
       <c r="F75" s="2"/>
-      <c r="G75" s="18"/>
+      <c r="G75" s="15"/>
     </row>
     <row r="76" spans="3:7">
       <c r="C76" s="9"/>
-      <c r="D76" s="12"/>
+      <c r="D76" s="1"/>
       <c r="E76" s="2" t="s">
         <v>111</v>
       </c>
@@ -26392,7 +26383,7 @@
     </row>
     <row r="78" spans="3:7">
       <c r="C78" s="9"/>
-      <c r="D78" s="12"/>
+      <c r="D78" s="1"/>
       <c r="E78" s="2" t="s">
         <v>111</v>
       </c>
@@ -26401,7 +26392,7 @@
     </row>
     <row r="79" spans="3:7">
       <c r="C79" s="9"/>
-      <c r="D79" s="12"/>
+      <c r="D79" s="1"/>
       <c r="E79" s="2" t="s">
         <v>111</v>
       </c>
@@ -26449,7 +26440,7 @@
       <c r="G83" s="2"/>
     </row>
     <row r="88" ht="51" spans="7:7">
-      <c r="G88" s="18" t="s">
+      <c r="G88" s="15" t="s">
         <v>748</v>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280"/>
+    <workbookView windowHeight="15280" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="785">
   <si>
     <t>##var</t>
   </si>
@@ -6377,9 +6377,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.4615384615385" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.9230769230769" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.3846153846154" style="1" customWidth="1"/>
-    <col min="4" max="4" width="38" style="1" customWidth="1"/>
+    <col min="4" max="4" width="54.1538461538462" style="1" customWidth="1"/>
     <col min="5" max="5" width="15.1538461538462" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.3076923076923" style="1" customWidth="1"/>
     <col min="7" max="7" width="23" style="36" customWidth="1"/>
@@ -6537,9 +6537,8 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5"/>
-      <c r="B5" s="1" t="str">
-        <f t="shared" ref="B5:B12" si="0">C5&amp;D5</f>
-        <v>arrow_cookie_2</v>
+      <c r="B5" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
@@ -6574,9 +6573,8 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6"/>
-      <c r="B6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>arrow_cookie_3</v>
+      <c r="B6" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>33</v>
@@ -6611,9 +6609,8 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7"/>
-      <c r="B7" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>arrow_cookie_4</v>
+      <c r="B7" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>37</v>
@@ -6648,9 +6645,8 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8"/>
-      <c r="B8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>jellyt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B8" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>40</v>
@@ -6685,9 +6681,8 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9"/>
-      <c r="B9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>cupcaket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>43</v>
@@ -6722,9 +6717,8 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10"/>
-      <c r="B10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>eggtartt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -6759,9 +6753,8 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11"/>
-      <c r="B11" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>sugarbeant_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B11" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>50</v>
@@ -6796,9 +6789,8 @@
     </row>
     <row r="12" spans="1:12">
       <c r="A12"/>
-      <c r="B12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>cheesecaket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B12" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>53</v>
@@ -6833,9 +6825,8 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13"/>
-      <c r="B13" s="1" t="str">
-        <f t="shared" ref="B13:B44" si="1">C13&amp;D13</f>
-        <v>mousset_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B13" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
@@ -6870,9 +6861,8 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14"/>
-      <c r="B14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>fruit_candyt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B14" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>61</v>
@@ -6907,9 +6897,8 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15"/>
-      <c r="B15" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>choco_bart_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B15" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>66</v>
@@ -6944,9 +6933,8 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16"/>
-      <c r="B16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>mochit_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B16" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>70</v>
@@ -6981,9 +6969,8 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17"/>
-      <c r="B17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cup_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B17" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>73</v>
@@ -7018,9 +7005,8 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18"/>
-      <c r="B18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>creamt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B18" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>76</v>
@@ -7055,9 +7041,8 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19"/>
-      <c r="B19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>eggrollt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B19" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>81</v>
@@ -7092,9 +7077,8 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20"/>
-      <c r="B20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>baguettet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B20" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>87</v>
@@ -7129,9 +7113,8 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21"/>
-      <c r="B21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>tanghulut_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B21" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>92</v>
@@ -7166,9 +7149,8 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22"/>
-      <c r="B22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cake_slicet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B22" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>97</v>
@@ -7203,9 +7185,8 @@
     </row>
     <row r="23" spans="1:12">
       <c r="A23"/>
-      <c r="B23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>long_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B23" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>102</v>
@@ -7240,9 +7221,8 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24"/>
-      <c r="B24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>eclairt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B24" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>107</v>
@@ -7277,9 +7257,8 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25"/>
-      <c r="B25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>gummyt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B25" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>113</v>
@@ -7314,9 +7293,8 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26"/>
-      <c r="B26" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>chocolate_stript_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B26" s="1" t="s">
+        <v>116</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>116</v>
@@ -7351,9 +7329,8 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27"/>
-      <c r="B27" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cake_rollt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B27" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>119</v>
@@ -7388,9 +7365,8 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28"/>
-      <c r="B28" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>palmiert_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B28" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>122</v>
@@ -7425,9 +7401,8 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29"/>
-      <c r="B29" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>chiffiont_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B29" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>126</v>
@@ -7462,9 +7437,8 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30"/>
-      <c r="B30" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>maple_sugart_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B30" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>129</v>
@@ -7499,9 +7473,8 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31"/>
-      <c r="B31" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>taosut_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B31" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>132</v>
@@ -7536,9 +7509,8 @@
     </row>
     <row r="32" spans="1:12">
       <c r="A32"/>
-      <c r="B32" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>wafflet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B32" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>135</v>
@@ -7573,9 +7545,8 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33"/>
-      <c r="B33" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cream_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B33" s="1" t="s">
+        <v>138</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>138</v>
@@ -7610,9 +7581,8 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34"/>
-      <c r="B34" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>candycanet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B34" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>141</v>
@@ -7647,9 +7617,8 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35"/>
-      <c r="B35" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>black_forest_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B35" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>144</v>
@@ -7684,9 +7653,8 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36"/>
-      <c r="B36" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>chocolate_saucet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B36" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>147</v>
@@ -7721,9 +7689,8 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37"/>
-      <c r="B37" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>mango_sagot_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B37" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>150</v>
@@ -7758,9 +7725,8 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38"/>
-      <c r="B38" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>fruit_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B38" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>153</v>
@@ -7795,9 +7761,8 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39"/>
-      <c r="B39" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>parfaitt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B39" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>156</v>
@@ -7832,9 +7797,8 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40"/>
-      <c r="B40" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>marshmallowt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B40" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>159</v>
@@ -7869,9 +7833,8 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41"/>
-      <c r="B41" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>big_lollipopt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B41" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>162</v>
@@ -7906,9 +7869,8 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42"/>
-      <c r="B42" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>apple_piet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B42" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>165</v>
@@ -7943,9 +7905,8 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43"/>
-      <c r="B43" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>double_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+      <c r="B43" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>168</v>
@@ -7980,9 +7941,8 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44"/>
-      <c r="B44" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+      <c r="B44" t="s">
+        <v>196</v>
       </c>
       <c r="C44" s="8"/>
       <c r="I44"/>
@@ -7991,7 +7951,7 @@
     <row r="45" spans="1:10">
       <c r="A45"/>
       <c r="B45" s="1" t="str">
-        <f t="shared" ref="B45:B108" si="2">C45&amp;D45</f>
+        <f t="shared" ref="B45:B108" si="0">C45&amp;D45</f>
         <v/>
       </c>
       <c r="C45" s="8"/>
@@ -8001,7 +7961,7 @@
     <row r="46" spans="1:10">
       <c r="A46"/>
       <c r="B46" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C46" s="8"/>
@@ -8011,7 +7971,7 @@
     <row r="47" spans="1:10">
       <c r="A47"/>
       <c r="B47" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C47" s="8"/>
@@ -8021,7 +7981,7 @@
     <row r="48" spans="1:10">
       <c r="A48"/>
       <c r="B48" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C48" s="8"/>
@@ -8031,7 +7991,7 @@
     <row r="49" spans="1:10">
       <c r="A49"/>
       <c r="B49" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C49" s="8"/>
@@ -8041,7 +8001,7 @@
     <row r="50" spans="1:10">
       <c r="A50"/>
       <c r="B50" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C50" s="8"/>
@@ -8051,7 +8011,7 @@
     <row r="51" spans="1:10">
       <c r="A51"/>
       <c r="B51" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C51" s="8"/>
@@ -8061,7 +8021,7 @@
     <row r="52" spans="1:10">
       <c r="A52"/>
       <c r="B52" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C52" s="8"/>
@@ -8071,7 +8031,7 @@
     <row r="53" spans="1:10">
       <c r="A53"/>
       <c r="B53" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I53"/>
@@ -8080,7 +8040,7 @@
     <row r="54" spans="1:10">
       <c r="A54"/>
       <c r="B54" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I54"/>
@@ -8089,7 +8049,7 @@
     <row r="55" spans="1:10">
       <c r="A55"/>
       <c r="B55" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I55"/>
@@ -8098,7 +8058,7 @@
     <row r="56" spans="1:10">
       <c r="A56"/>
       <c r="B56" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I56"/>
@@ -8107,7 +8067,7 @@
     <row r="57" spans="1:10">
       <c r="A57"/>
       <c r="B57" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I57"/>
@@ -8116,7 +8076,7 @@
     <row r="58" spans="1:10">
       <c r="A58"/>
       <c r="B58" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I58"/>
@@ -8125,7 +8085,7 @@
     <row r="59" spans="1:10">
       <c r="A59"/>
       <c r="B59" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I59"/>
@@ -8134,7 +8094,7 @@
     <row r="60" spans="1:10">
       <c r="A60"/>
       <c r="B60" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I60"/>
@@ -8143,7 +8103,7 @@
     <row r="61" spans="1:10">
       <c r="A61"/>
       <c r="B61" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I61"/>
@@ -8152,7 +8112,7 @@
     <row r="62" spans="1:10">
       <c r="A62"/>
       <c r="B62" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I62"/>
@@ -8161,7 +8121,7 @@
     <row r="63" spans="1:10">
       <c r="A63"/>
       <c r="B63" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I63"/>
@@ -8170,7 +8130,7 @@
     <row r="64" spans="1:10">
       <c r="A64"/>
       <c r="B64" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I64"/>
@@ -8179,7 +8139,7 @@
     <row r="65" spans="1:10">
       <c r="A65"/>
       <c r="B65" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I65"/>
@@ -8188,7 +8148,7 @@
     <row r="66" spans="1:10">
       <c r="A66"/>
       <c r="B66" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I66"/>
@@ -8197,7 +8157,7 @@
     <row r="67" spans="1:10">
       <c r="A67"/>
       <c r="B67" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I67"/>
@@ -8206,7 +8166,7 @@
     <row r="68" spans="1:10">
       <c r="A68"/>
       <c r="B68" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I68"/>
@@ -8215,7 +8175,7 @@
     <row r="69" spans="1:10">
       <c r="A69"/>
       <c r="B69" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I69"/>
@@ -8224,7 +8184,7 @@
     <row r="70" spans="1:10">
       <c r="A70"/>
       <c r="B70" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I70"/>
@@ -8233,7 +8193,7 @@
     <row r="71" spans="1:10">
       <c r="A71"/>
       <c r="B71" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I71"/>
@@ -8242,7 +8202,7 @@
     <row r="72" spans="1:10">
       <c r="A72"/>
       <c r="B72" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I72"/>
@@ -8251,7 +8211,7 @@
     <row r="73" spans="1:10">
       <c r="A73"/>
       <c r="B73" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I73"/>
@@ -8260,7 +8220,7 @@
     <row r="74" spans="1:10">
       <c r="A74"/>
       <c r="B74" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I74"/>
@@ -8269,7 +8229,7 @@
     <row r="75" spans="1:10">
       <c r="A75"/>
       <c r="B75" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I75"/>
@@ -8278,7 +8238,7 @@
     <row r="76" spans="1:10">
       <c r="A76"/>
       <c r="B76" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C76" s="8"/>
@@ -8288,7 +8248,7 @@
     <row r="77" spans="1:10">
       <c r="A77"/>
       <c r="B77" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C77" s="8"/>
@@ -8298,7 +8258,7 @@
     <row r="78" spans="1:10">
       <c r="A78"/>
       <c r="B78" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C78" s="8"/>
@@ -8308,7 +8268,7 @@
     <row r="79" spans="1:10">
       <c r="A79"/>
       <c r="B79" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C79" s="8"/>
@@ -8318,7 +8278,7 @@
     <row r="80" spans="1:10">
       <c r="A80"/>
       <c r="B80" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C80" s="8"/>
@@ -8328,7 +8288,7 @@
     <row r="81" spans="1:10">
       <c r="A81"/>
       <c r="B81" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C81" s="8"/>
@@ -8338,7 +8298,7 @@
     <row r="82" spans="1:10">
       <c r="A82"/>
       <c r="B82" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C82" s="8"/>
@@ -8348,7 +8308,7 @@
     <row r="83" spans="1:10">
       <c r="A83"/>
       <c r="B83" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C83" s="8"/>
@@ -8358,7 +8318,7 @@
     <row r="84" spans="1:10">
       <c r="A84"/>
       <c r="B84" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C84" s="8"/>
@@ -8368,7 +8328,7 @@
     <row r="85" spans="1:10">
       <c r="A85"/>
       <c r="B85" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C85" s="8"/>
@@ -8378,7 +8338,7 @@
     <row r="86" spans="1:10">
       <c r="A86"/>
       <c r="B86" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C86" s="8"/>
@@ -8388,7 +8348,7 @@
     <row r="87" spans="1:10">
       <c r="A87"/>
       <c r="B87" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C87" s="8"/>
@@ -8398,7 +8358,7 @@
     <row r="88" spans="1:10">
       <c r="A88"/>
       <c r="B88" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C88" s="8"/>
@@ -8408,7 +8368,7 @@
     <row r="89" spans="1:10">
       <c r="A89"/>
       <c r="B89" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C89" s="8"/>
@@ -8418,7 +8378,7 @@
     <row r="90" spans="1:10">
       <c r="A90"/>
       <c r="B90" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C90" s="8"/>
@@ -8428,7 +8388,7 @@
     <row r="91" spans="1:10">
       <c r="A91"/>
       <c r="B91" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C91" s="8"/>
@@ -8438,7 +8398,7 @@
     <row r="92" spans="1:10">
       <c r="A92"/>
       <c r="B92" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C92" s="8"/>
@@ -8448,7 +8408,7 @@
     <row r="93" spans="1:10">
       <c r="A93"/>
       <c r="B93" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C93" s="8"/>
@@ -8458,7 +8418,7 @@
     <row r="94" spans="1:10">
       <c r="A94"/>
       <c r="B94" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C94" s="8"/>
@@ -8468,7 +8428,7 @@
     <row r="95" spans="1:10">
       <c r="A95"/>
       <c r="B95" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C95" s="8"/>
@@ -8478,7 +8438,7 @@
     <row r="96" spans="1:10">
       <c r="A96"/>
       <c r="B96" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C96" s="8"/>
@@ -8488,7 +8448,7 @@
     <row r="97" spans="1:10">
       <c r="A97"/>
       <c r="B97" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C97" s="8"/>
@@ -8498,7 +8458,7 @@
     <row r="98" spans="1:10">
       <c r="A98"/>
       <c r="B98" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C98" s="8"/>
@@ -8508,7 +8468,7 @@
     <row r="99" spans="1:10">
       <c r="A99"/>
       <c r="B99" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C99" s="8"/>
@@ -8518,7 +8478,7 @@
     <row r="100" spans="1:10">
       <c r="A100"/>
       <c r="B100" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="C100" s="8"/>
@@ -8528,7 +8488,7 @@
     <row r="101" spans="1:10">
       <c r="A101"/>
       <c r="B101" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I101"/>
@@ -8537,7 +8497,7 @@
     <row r="102" spans="1:10">
       <c r="A102"/>
       <c r="B102" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I102"/>
@@ -8546,7 +8506,7 @@
     <row r="103" spans="1:10">
       <c r="A103"/>
       <c r="B103" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I103"/>
@@ -8555,7 +8515,7 @@
     <row r="104" spans="1:10">
       <c r="A104"/>
       <c r="B104" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I104"/>
@@ -8564,7 +8524,7 @@
     <row r="105" spans="1:10">
       <c r="A105"/>
       <c r="B105" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I105"/>
@@ -8573,7 +8533,7 @@
     <row r="106" spans="1:10">
       <c r="A106"/>
       <c r="B106" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I106"/>
@@ -8582,7 +8542,7 @@
     <row r="107" spans="1:10">
       <c r="A107"/>
       <c r="B107" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I107"/>
@@ -8591,7 +8551,7 @@
     <row r="108" spans="1:10">
       <c r="A108"/>
       <c r="B108" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="I108"/>
@@ -8600,7 +8560,7 @@
     <row r="109" spans="1:10">
       <c r="A109"/>
       <c r="B109" s="1" t="str">
-        <f t="shared" ref="B109:B173" si="3">C109&amp;D109</f>
+        <f t="shared" ref="B109:B173" si="1">C109&amp;D109</f>
         <v/>
       </c>
       <c r="I109"/>
@@ -8609,7 +8569,7 @@
     <row r="110" spans="1:10">
       <c r="A110"/>
       <c r="B110" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I110"/>
@@ -8618,7 +8578,7 @@
     <row r="111" spans="1:10">
       <c r="A111"/>
       <c r="B111" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I111"/>
@@ -8627,7 +8587,7 @@
     <row r="112" spans="1:10">
       <c r="A112"/>
       <c r="B112" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I112"/>
@@ -8636,7 +8596,7 @@
     <row r="113" spans="1:10">
       <c r="A113"/>
       <c r="B113" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I113"/>
@@ -8645,7 +8605,7 @@
     <row r="114" spans="1:10">
       <c r="A114"/>
       <c r="B114" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I114"/>
@@ -8654,7 +8614,7 @@
     <row r="115" spans="1:10">
       <c r="A115"/>
       <c r="B115" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I115"/>
@@ -8663,7 +8623,7 @@
     <row r="116" spans="1:10">
       <c r="A116"/>
       <c r="B116" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I116"/>
@@ -8672,7 +8632,7 @@
     <row r="117" spans="1:10">
       <c r="A117"/>
       <c r="B117" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I117"/>
@@ -8681,7 +8641,7 @@
     <row r="118" spans="1:10">
       <c r="A118"/>
       <c r="B118" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I118"/>
@@ -8690,7 +8650,7 @@
     <row r="119" spans="1:10">
       <c r="A119"/>
       <c r="B119" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I119"/>
@@ -8699,7 +8659,7 @@
     <row r="120" spans="1:10">
       <c r="A120"/>
       <c r="B120" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I120"/>
@@ -8708,7 +8668,7 @@
     <row r="121" spans="1:10">
       <c r="A121"/>
       <c r="B121" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I121"/>
@@ -8717,7 +8677,7 @@
     <row r="122" spans="1:10">
       <c r="A122"/>
       <c r="B122" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I122"/>
@@ -8726,7 +8686,7 @@
     <row r="123" spans="1:10">
       <c r="A123"/>
       <c r="B123" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I123"/>
@@ -8735,7 +8695,7 @@
     <row r="124" spans="1:10">
       <c r="A124"/>
       <c r="B124" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C124" s="8"/>
@@ -8745,7 +8705,7 @@
     <row r="125" spans="1:10">
       <c r="A125"/>
       <c r="B125" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C125" s="8"/>
@@ -8755,7 +8715,7 @@
     <row r="126" spans="1:10">
       <c r="A126"/>
       <c r="B126" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C126" s="8"/>
@@ -8765,7 +8725,7 @@
     <row r="127" spans="1:10">
       <c r="A127"/>
       <c r="B127" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C127" s="8"/>
@@ -8775,7 +8735,7 @@
     <row r="128" spans="1:10">
       <c r="A128"/>
       <c r="B128" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C128" s="8"/>
@@ -8785,7 +8745,7 @@
     <row r="129" spans="1:10">
       <c r="A129"/>
       <c r="B129" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C129" s="8"/>
@@ -8795,7 +8755,7 @@
     <row r="130" spans="1:10">
       <c r="A130"/>
       <c r="B130" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C130" s="8"/>
@@ -8805,7 +8765,7 @@
     <row r="131" spans="1:10">
       <c r="A131"/>
       <c r="B131" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C131" s="8"/>
@@ -8815,7 +8775,7 @@
     <row r="132" spans="1:10">
       <c r="A132"/>
       <c r="B132" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C132" s="8"/>
@@ -8825,7 +8785,7 @@
     <row r="133" spans="1:10">
       <c r="A133"/>
       <c r="B133" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C133" s="8"/>
@@ -8835,7 +8795,7 @@
     <row r="134" spans="1:10">
       <c r="A134"/>
       <c r="B134" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C134" s="8"/>
@@ -8845,7 +8805,7 @@
     <row r="135" spans="1:10">
       <c r="A135"/>
       <c r="B135" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C135" s="8"/>
@@ -8855,7 +8815,7 @@
     <row r="136" spans="1:10">
       <c r="A136"/>
       <c r="B136" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C136" s="8"/>
@@ -8865,7 +8825,7 @@
     <row r="137" spans="1:10">
       <c r="A137"/>
       <c r="B137" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C137" s="8"/>
@@ -8875,7 +8835,7 @@
     <row r="138" spans="1:10">
       <c r="A138"/>
       <c r="B138" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C138" s="8"/>
@@ -8885,7 +8845,7 @@
     <row r="139" spans="1:10">
       <c r="A139"/>
       <c r="B139" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C139" s="8"/>
@@ -8895,7 +8855,7 @@
     <row r="140" spans="1:10">
       <c r="A140"/>
       <c r="B140" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C140" s="8"/>
@@ -8905,7 +8865,7 @@
     <row r="141" spans="1:10">
       <c r="A141"/>
       <c r="B141" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C141" s="8"/>
@@ -8915,7 +8875,7 @@
     <row r="142" spans="1:10">
       <c r="A142"/>
       <c r="B142" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C142" s="8"/>
@@ -8925,7 +8885,7 @@
     <row r="143" spans="1:10">
       <c r="A143"/>
       <c r="B143" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C143" s="8"/>
@@ -8935,7 +8895,7 @@
     <row r="144" spans="1:10">
       <c r="A144"/>
       <c r="B144" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C144" s="8"/>
@@ -8945,7 +8905,7 @@
     <row r="145" spans="1:10">
       <c r="A145"/>
       <c r="B145" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C145" s="8"/>
@@ -8955,7 +8915,7 @@
     <row r="146" spans="1:10">
       <c r="A146"/>
       <c r="B146" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C146" s="8"/>
@@ -8965,7 +8925,7 @@
     <row r="147" spans="1:10">
       <c r="A147"/>
       <c r="B147" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C147" s="8"/>
@@ -8975,7 +8935,7 @@
     <row r="148" spans="1:10">
       <c r="A148"/>
       <c r="B148" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C148" s="8"/>
@@ -8985,7 +8945,7 @@
     <row r="149" spans="1:10">
       <c r="A149"/>
       <c r="B149" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I149"/>
@@ -8994,7 +8954,7 @@
     <row r="150" spans="1:10">
       <c r="A150"/>
       <c r="B150" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I150"/>
@@ -9003,7 +8963,7 @@
     <row r="151" spans="1:10">
       <c r="A151"/>
       <c r="B151" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I151"/>
@@ -9012,7 +8972,7 @@
     <row r="152" spans="1:10">
       <c r="A152"/>
       <c r="B152" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I152"/>
@@ -9021,7 +8981,7 @@
     <row r="153" spans="1:10">
       <c r="A153"/>
       <c r="B153" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I153"/>
@@ -9030,7 +8990,7 @@
     <row r="154" spans="1:10">
       <c r="A154"/>
       <c r="B154" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I154"/>
@@ -9039,7 +8999,7 @@
     <row r="155" spans="1:10">
       <c r="A155"/>
       <c r="B155" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I155"/>
@@ -9048,7 +9008,7 @@
     <row r="156" spans="1:10">
       <c r="A156"/>
       <c r="B156" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I156"/>
@@ -9057,7 +9017,7 @@
     <row r="157" spans="1:10">
       <c r="A157"/>
       <c r="B157" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I157"/>
@@ -9066,7 +9026,7 @@
     <row r="158" spans="1:10">
       <c r="A158"/>
       <c r="B158" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I158"/>
@@ -9075,7 +9035,7 @@
     <row r="159" spans="1:10">
       <c r="A159"/>
       <c r="B159" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I159"/>
@@ -9084,7 +9044,7 @@
     <row r="160" spans="1:10">
       <c r="A160"/>
       <c r="B160" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I160"/>
@@ -9093,7 +9053,7 @@
     <row r="161" spans="1:10">
       <c r="A161"/>
       <c r="B161" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I161"/>
@@ -9102,7 +9062,7 @@
     <row r="162" spans="1:10">
       <c r="A162"/>
       <c r="B162" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I162"/>
@@ -9111,7 +9071,7 @@
     <row r="163" spans="1:10">
       <c r="A163"/>
       <c r="B163" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I163"/>
@@ -9120,7 +9080,7 @@
     <row r="164" spans="1:10">
       <c r="A164"/>
       <c r="B164" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I164"/>
@@ -9129,7 +9089,7 @@
     <row r="165" spans="1:10">
       <c r="A165"/>
       <c r="B165" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I165"/>
@@ -9138,7 +9098,7 @@
     <row r="166" spans="1:10">
       <c r="A166"/>
       <c r="B166" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I166"/>
@@ -9147,7 +9107,7 @@
     <row r="167" spans="1:10">
       <c r="A167"/>
       <c r="B167" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I167"/>
@@ -9156,7 +9116,7 @@
     <row r="168" spans="1:10">
       <c r="A168"/>
       <c r="B168" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I168"/>
@@ -9165,7 +9125,7 @@
     <row r="169" spans="1:10">
       <c r="A169"/>
       <c r="B169" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I169"/>
@@ -9174,7 +9134,7 @@
     <row r="170" spans="1:10">
       <c r="A170"/>
       <c r="B170" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I170"/>
@@ -9183,7 +9143,7 @@
     <row r="171" spans="1:10">
       <c r="A171"/>
       <c r="B171" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="I171"/>
@@ -9192,7 +9152,7 @@
     <row r="172" spans="1:10">
       <c r="A172"/>
       <c r="B172" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C172" s="8"/>
@@ -9202,7 +9162,7 @@
     <row r="173" spans="1:10">
       <c r="A173"/>
       <c r="B173" s="1" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="C173" s="8"/>
@@ -9212,7 +9172,7 @@
     <row r="174" spans="1:10">
       <c r="A174"/>
       <c r="B174" s="1" t="str">
-        <f t="shared" ref="B174:B237" si="4">C174&amp;D174</f>
+        <f t="shared" ref="B174:B237" si="2">C174&amp;D174</f>
         <v/>
       </c>
       <c r="C174" s="8"/>
@@ -9222,7 +9182,7 @@
     <row r="175" spans="1:10">
       <c r="A175"/>
       <c r="B175" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C175" s="8"/>
@@ -9232,7 +9192,7 @@
     <row r="176" spans="1:10">
       <c r="A176"/>
       <c r="B176" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C176" s="8"/>
@@ -9242,7 +9202,7 @@
     <row r="177" spans="1:10">
       <c r="A177"/>
       <c r="B177" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C177" s="8"/>
@@ -9252,7 +9212,7 @@
     <row r="178" spans="1:10">
       <c r="A178"/>
       <c r="B178" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C178" s="8"/>
@@ -9262,7 +9222,7 @@
     <row r="179" spans="1:10">
       <c r="A179"/>
       <c r="B179" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C179" s="8"/>
@@ -9272,7 +9232,7 @@
     <row r="180" spans="1:10">
       <c r="A180"/>
       <c r="B180" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C180" s="8"/>
@@ -9282,7 +9242,7 @@
     <row r="181" spans="1:10">
       <c r="A181"/>
       <c r="B181" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C181" s="8"/>
@@ -9292,7 +9252,7 @@
     <row r="182" spans="1:10">
       <c r="A182"/>
       <c r="B182" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C182" s="8"/>
@@ -9302,7 +9262,7 @@
     <row r="183" spans="1:10">
       <c r="A183"/>
       <c r="B183" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C183" s="8"/>
@@ -9312,7 +9272,7 @@
     <row r="184" spans="1:10">
       <c r="A184"/>
       <c r="B184" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C184" s="8"/>
@@ -9322,7 +9282,7 @@
     <row r="185" spans="1:10">
       <c r="A185"/>
       <c r="B185" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C185" s="8"/>
@@ -9332,7 +9292,7 @@
     <row r="186" spans="1:10">
       <c r="A186"/>
       <c r="B186" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C186" s="8"/>
@@ -9342,7 +9302,7 @@
     <row r="187" spans="1:10">
       <c r="A187"/>
       <c r="B187" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C187" s="8"/>
@@ -9352,7 +9312,7 @@
     <row r="188" spans="1:10">
       <c r="A188"/>
       <c r="B188" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C188" s="8"/>
@@ -9362,7 +9322,7 @@
     <row r="189" spans="1:10">
       <c r="A189"/>
       <c r="B189" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C189" s="8"/>
@@ -9372,7 +9332,7 @@
     <row r="190" spans="1:10">
       <c r="A190"/>
       <c r="B190" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C190" s="8"/>
@@ -9382,7 +9342,7 @@
     <row r="191" spans="1:10">
       <c r="A191"/>
       <c r="B191" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C191" s="8"/>
@@ -9392,7 +9352,7 @@
     <row r="192" spans="1:10">
       <c r="A192"/>
       <c r="B192" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C192" s="8"/>
@@ -9402,7 +9362,7 @@
     <row r="193" spans="1:10">
       <c r="A193"/>
       <c r="B193" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C193" s="8"/>
@@ -9412,7 +9372,7 @@
     <row r="194" spans="1:10">
       <c r="A194"/>
       <c r="B194" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C194" s="8"/>
@@ -9422,7 +9382,7 @@
     <row r="195" spans="1:10">
       <c r="A195"/>
       <c r="B195" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C195" s="8"/>
@@ -9432,7 +9392,7 @@
     <row r="196" spans="1:10">
       <c r="A196"/>
       <c r="B196" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C196" s="8"/>
@@ -9442,7 +9402,7 @@
     <row r="197" spans="1:10">
       <c r="A197"/>
       <c r="B197" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I197"/>
@@ -9451,7 +9411,7 @@
     <row r="198" spans="1:10">
       <c r="A198"/>
       <c r="B198" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I198"/>
@@ -9460,7 +9420,7 @@
     <row r="199" spans="1:10">
       <c r="A199"/>
       <c r="B199" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I199"/>
@@ -9469,7 +9429,7 @@
     <row r="200" spans="1:10">
       <c r="A200"/>
       <c r="B200" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I200"/>
@@ -9478,7 +9438,7 @@
     <row r="201" spans="1:10">
       <c r="A201"/>
       <c r="B201" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I201"/>
@@ -9487,7 +9447,7 @@
     <row r="202" spans="1:10">
       <c r="A202"/>
       <c r="B202" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I202"/>
@@ -9496,7 +9456,7 @@
     <row r="203" spans="1:10">
       <c r="A203"/>
       <c r="B203" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I203"/>
@@ -9505,7 +9465,7 @@
     <row r="204" spans="1:10">
       <c r="A204"/>
       <c r="B204" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I204"/>
@@ -9514,7 +9474,7 @@
     <row r="205" spans="1:10">
       <c r="A205"/>
       <c r="B205" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I205"/>
@@ -9523,7 +9483,7 @@
     <row r="206" spans="1:10">
       <c r="A206"/>
       <c r="B206" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I206"/>
@@ -9532,7 +9492,7 @@
     <row r="207" spans="1:10">
       <c r="A207"/>
       <c r="B207" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I207"/>
@@ -9541,7 +9501,7 @@
     <row r="208" spans="1:10">
       <c r="A208"/>
       <c r="B208" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I208"/>
@@ -9550,7 +9510,7 @@
     <row r="209" spans="1:10">
       <c r="A209"/>
       <c r="B209" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I209"/>
@@ -9559,7 +9519,7 @@
     <row r="210" spans="1:10">
       <c r="A210"/>
       <c r="B210" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I210"/>
@@ -9568,7 +9528,7 @@
     <row r="211" spans="1:10">
       <c r="A211"/>
       <c r="B211" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I211"/>
@@ -9577,7 +9537,7 @@
     <row r="212" spans="1:10">
       <c r="A212"/>
       <c r="B212" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I212"/>
@@ -9586,7 +9546,7 @@
     <row r="213" spans="1:10">
       <c r="A213"/>
       <c r="B213" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I213"/>
@@ -9595,7 +9555,7 @@
     <row r="214" spans="1:10">
       <c r="A214"/>
       <c r="B214" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I214"/>
@@ -9604,7 +9564,7 @@
     <row r="215" spans="1:10">
       <c r="A215"/>
       <c r="B215" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I215"/>
@@ -9613,7 +9573,7 @@
     <row r="216" spans="1:10">
       <c r="A216"/>
       <c r="B216" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I216"/>
@@ -9622,7 +9582,7 @@
     <row r="217" spans="1:10">
       <c r="A217"/>
       <c r="B217" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I217"/>
@@ -9631,7 +9591,7 @@
     <row r="218" spans="1:9">
       <c r="A218"/>
       <c r="B218" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I218"/>
@@ -9639,7 +9599,7 @@
     <row r="219" spans="1:10">
       <c r="A219"/>
       <c r="B219" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I219"/>
@@ -9648,7 +9608,7 @@
     <row r="220" spans="1:10">
       <c r="A220"/>
       <c r="B220" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C220" s="8"/>
@@ -9658,7 +9618,7 @@
     <row r="221" spans="1:10">
       <c r="A221"/>
       <c r="B221" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C221" s="8"/>
@@ -9668,7 +9628,7 @@
     <row r="222" spans="1:10">
       <c r="A222"/>
       <c r="B222" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C222" s="8"/>
@@ -9678,7 +9638,7 @@
     <row r="223" spans="1:10">
       <c r="A223"/>
       <c r="B223" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C223" s="8"/>
@@ -9688,7 +9648,7 @@
     <row r="224" spans="1:10">
       <c r="A224"/>
       <c r="B224" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C224" s="8"/>
@@ -9698,7 +9658,7 @@
     <row r="225" spans="1:10">
       <c r="A225"/>
       <c r="B225" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C225" s="8"/>
@@ -9708,7 +9668,7 @@
     <row r="226" spans="1:10">
       <c r="A226"/>
       <c r="B226" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C226" s="8"/>
@@ -9718,7 +9678,7 @@
     <row r="227" spans="1:10">
       <c r="A227"/>
       <c r="B227" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C227" s="8"/>
@@ -9728,7 +9688,7 @@
     <row r="228" spans="1:10">
       <c r="A228"/>
       <c r="B228" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C228" s="8"/>
@@ -9738,7 +9698,7 @@
     <row r="229" spans="1:10">
       <c r="A229"/>
       <c r="B229" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C229" s="8"/>
@@ -9748,7 +9708,7 @@
     <row r="230" spans="1:10">
       <c r="A230"/>
       <c r="B230" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C230" s="8"/>
@@ -9758,7 +9718,7 @@
     <row r="231" spans="1:10">
       <c r="A231"/>
       <c r="B231" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C231" s="8"/>
@@ -9768,7 +9728,7 @@
     <row r="232" spans="1:10">
       <c r="A232"/>
       <c r="B232" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C232" s="8"/>
@@ -9778,7 +9738,7 @@
     <row r="233" spans="1:10">
       <c r="A233"/>
       <c r="B233" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C233" s="8"/>
@@ -9788,7 +9748,7 @@
     <row r="234" spans="1:10">
       <c r="A234"/>
       <c r="B234" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C234" s="8"/>
@@ -9798,7 +9758,7 @@
     <row r="235" spans="1:10">
       <c r="A235"/>
       <c r="B235" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C235" s="8"/>
@@ -9808,7 +9768,7 @@
     <row r="236" spans="1:10">
       <c r="A236"/>
       <c r="B236" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C236" s="8"/>
@@ -9818,7 +9778,7 @@
     <row r="237" spans="1:10">
       <c r="A237"/>
       <c r="B237" s="1" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="C237" s="8"/>
@@ -9828,7 +9788,7 @@
     <row r="238" spans="1:10">
       <c r="A238"/>
       <c r="B238" s="1" t="str">
-        <f t="shared" ref="B238:B301" si="5">C238&amp;D238</f>
+        <f t="shared" ref="B238:B301" si="3">C238&amp;D238</f>
         <v/>
       </c>
       <c r="C238" s="8"/>
@@ -9838,7 +9798,7 @@
     <row r="239" spans="1:10">
       <c r="A239"/>
       <c r="B239" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C239" s="8"/>
@@ -9848,7 +9808,7 @@
     <row r="240" spans="1:10">
       <c r="A240"/>
       <c r="B240" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C240" s="8"/>
@@ -9858,7 +9818,7 @@
     <row r="241" spans="1:10">
       <c r="A241"/>
       <c r="B241" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C241" s="8"/>
@@ -9868,7 +9828,7 @@
     <row r="242" spans="1:10">
       <c r="A242"/>
       <c r="B242" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C242" s="8"/>
@@ -9878,7 +9838,7 @@
     <row r="243" spans="1:10">
       <c r="A243"/>
       <c r="B243" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C243" s="8"/>
@@ -9888,7 +9848,7 @@
     <row r="244" spans="1:10">
       <c r="A244"/>
       <c r="B244" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C244" s="8"/>
@@ -9898,7 +9858,7 @@
     <row r="245" spans="1:10">
       <c r="A245"/>
       <c r="B245" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I245"/>
@@ -9907,7 +9867,7 @@
     <row r="246" spans="1:10">
       <c r="A246"/>
       <c r="B246" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I246"/>
@@ -9916,7 +9876,7 @@
     <row r="247" spans="1:10">
       <c r="A247"/>
       <c r="B247" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I247"/>
@@ -9925,7 +9885,7 @@
     <row r="248" spans="1:10">
       <c r="A248"/>
       <c r="B248" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I248"/>
@@ -9934,7 +9894,7 @@
     <row r="249" spans="1:10">
       <c r="A249"/>
       <c r="B249" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I249"/>
@@ -9943,7 +9903,7 @@
     <row r="250" spans="1:10">
       <c r="A250"/>
       <c r="B250" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I250"/>
@@ -9952,7 +9912,7 @@
     <row r="251" spans="1:10">
       <c r="A251"/>
       <c r="B251" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I251"/>
@@ -9961,7 +9921,7 @@
     <row r="252" spans="1:10">
       <c r="A252"/>
       <c r="B252" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I252"/>
@@ -9970,7 +9930,7 @@
     <row r="253" spans="1:10">
       <c r="A253"/>
       <c r="B253" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I253"/>
@@ -9979,7 +9939,7 @@
     <row r="254" spans="1:10">
       <c r="A254"/>
       <c r="B254" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I254"/>
@@ -9988,7 +9948,7 @@
     <row r="255" spans="1:10">
       <c r="A255"/>
       <c r="B255" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I255"/>
@@ -9997,7 +9957,7 @@
     <row r="256" spans="1:10">
       <c r="A256"/>
       <c r="B256" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I256"/>
@@ -10006,7 +9966,7 @@
     <row r="257" spans="1:10">
       <c r="A257"/>
       <c r="B257" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I257"/>
@@ -10015,7 +9975,7 @@
     <row r="258" spans="1:10">
       <c r="A258"/>
       <c r="B258" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I258"/>
@@ -10024,7 +9984,7 @@
     <row r="259" spans="1:10">
       <c r="A259"/>
       <c r="B259" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="I259"/>
@@ -10032,362 +9992,362 @@
     </row>
     <row r="260" spans="2:2">
       <c r="B260" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="261" spans="2:2">
       <c r="B261" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="262" spans="2:2">
       <c r="B262" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="263" spans="2:2">
       <c r="B263" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="264" spans="2:2">
       <c r="B264" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="265" spans="2:2">
       <c r="B265" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="266" spans="2:2">
       <c r="B266" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="267" spans="2:2">
       <c r="B267" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="268" spans="2:3">
       <c r="B268" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C268" s="8"/>
     </row>
     <row r="269" spans="2:3">
       <c r="B269" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C269" s="8"/>
     </row>
     <row r="270" spans="2:3">
       <c r="B270" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C270" s="8"/>
     </row>
     <row r="271" spans="2:3">
       <c r="B271" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C271" s="8"/>
     </row>
     <row r="272" spans="2:3">
       <c r="B272" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C272" s="8"/>
     </row>
     <row r="273" spans="2:3">
       <c r="B273" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C273" s="8"/>
     </row>
     <row r="274" spans="2:3">
       <c r="B274" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C274" s="8"/>
     </row>
     <row r="275" spans="2:3">
       <c r="B275" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C275" s="8"/>
     </row>
     <row r="276" spans="2:3">
       <c r="B276" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C276" s="8"/>
     </row>
     <row r="277" spans="2:3">
       <c r="B277" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C277" s="8"/>
     </row>
     <row r="278" spans="2:3">
       <c r="B278" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C278" s="8"/>
     </row>
     <row r="279" spans="2:3">
       <c r="B279" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C279" s="8"/>
     </row>
     <row r="280" spans="2:3">
       <c r="B280" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C280" s="8"/>
     </row>
     <row r="281" spans="2:3">
       <c r="B281" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C281" s="8"/>
     </row>
     <row r="282" spans="2:3">
       <c r="B282" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C282" s="8"/>
     </row>
     <row r="283" spans="2:3">
       <c r="B283" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C283" s="8"/>
     </row>
     <row r="284" spans="2:3">
       <c r="B284" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C284" s="8"/>
     </row>
     <row r="285" spans="2:3">
       <c r="B285" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C285" s="8"/>
     </row>
     <row r="286" spans="2:3">
       <c r="B286" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C286" s="8"/>
     </row>
     <row r="287" spans="2:3">
       <c r="B287" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C287" s="8"/>
     </row>
     <row r="288" spans="2:3">
       <c r="B288" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C288" s="8"/>
     </row>
     <row r="289" spans="2:3">
       <c r="B289" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C289" s="8"/>
     </row>
     <row r="290" spans="2:3">
       <c r="B290" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C290" s="8"/>
     </row>
     <row r="291" spans="2:3">
       <c r="B291" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C291" s="8"/>
     </row>
     <row r="292" spans="2:3">
       <c r="B292" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="C292" s="8"/>
     </row>
     <row r="293" spans="2:2">
       <c r="B293" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="294" spans="2:2">
       <c r="B294" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="295" spans="2:2">
       <c r="B295" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="296" spans="2:2">
       <c r="B296" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="297" spans="2:2">
       <c r="B297" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="298" spans="2:2">
       <c r="B298" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="299" spans="2:2">
       <c r="B299" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="300" spans="2:2">
       <c r="B300" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="301" spans="2:2">
       <c r="B301" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
     <row r="302" spans="2:2">
       <c r="B302" s="1" t="str">
-        <f t="shared" ref="B302:B308" si="6">C302&amp;D302</f>
+        <f t="shared" ref="B302:B308" si="4">C302&amp;D302</f>
         <v/>
       </c>
     </row>
     <row r="303" spans="2:2">
       <c r="B303" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="304" spans="2:2">
       <c r="B304" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="305" spans="2:2">
       <c r="B305" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="306" spans="2:2">
       <c r="B306" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="307" spans="2:2">
       <c r="B307" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="308" spans="2:2">
       <c r="B308" s="1" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="309" spans="2:2">
       <c r="B309" s="1" t="str">
-        <f t="shared" ref="B309:B315" si="7">C309&amp;D309</f>
+        <f t="shared" ref="B309:B315" si="5">C309&amp;D309</f>
         <v/>
       </c>
     </row>
     <row r="310" spans="2:2">
       <c r="B310" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="311" spans="2:2">
       <c r="B311" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="312" spans="2:2">
       <c r="B312" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="313" spans="2:2">
       <c r="B313" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="314" spans="2:2">
       <c r="B314" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="315" spans="2:2">
       <c r="B315" s="1" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280" activeTab="1"/>
+    <workbookView windowHeight="15280" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -13446,7 +13446,7 @@
         <v>338</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280" activeTab="5"/>
+    <workbookView windowHeight="15280" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -934,7 +934,7 @@
   </si>
   <si>
     <t>结算时
-+10金币</t>
++8金币</t>
   </si>
   <si>
     <t>GrantGold</t>
@@ -964,7 +964,7 @@
     <t>酸</t>
   </si>
   <si>
-    <t>结算开始时，若未上菜
+    <t>结算开始时，若在菜谱中
 场上食物倍率 ×1.5</t>
   </si>
   <si>
@@ -980,7 +980,7 @@
     <t>咸</t>
   </si>
   <si>
-    <t>结算开始时，若未上菜
+    <t>结算开始时，若在菜谱中
 场上食物基础分+20</t>
   </si>
   <si>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15280" activeTab="3"/>
+    <workbookView windowHeight="15360" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="783">
   <si>
     <t>##var</t>
   </si>
@@ -1477,7 +1477,7 @@
   </si>
   <si>
     <t>右侧及自身
-分数+15</t>
+分数+10</t>
   </si>
   <si>
     <t>左侧及自身
@@ -1485,7 +1485,7 @@
   </si>
   <si>
     <t>下侧及自身
-分数+15</t>
+分数+10</t>
   </si>
   <si>
     <t>上侧及自身
@@ -1766,10 +1766,6 @@
 倍率 +3</t>
   </si>
   <si>
-    <t>右侧及自身
-分数+10</t>
-  </si>
-  <si>
     <t>前</t>
   </si>
   <si>
@@ -1801,10 +1797,6 @@
   <si>
     <t>周围每有1个空格
 分数-2</t>
-  </si>
-  <si>
-    <t>下侧及自身
-分数+10</t>
   </si>
   <si>
     <t>保证空格少</t>
@@ -3963,7 +3955,7 @@
         <v>26</v>
       </c>
       <c r="D4" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>27</v>
@@ -4008,7 +4000,7 @@
         <v>31</v>
       </c>
       <c r="D5" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>27</v>
@@ -4053,7 +4045,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>27</v>
@@ -4104,7 +4096,7 @@
         <v>38</v>
       </c>
       <c r="D8" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>27</v>
@@ -11920,7 +11912,7 @@
         <v>0</v>
       </c>
       <c r="L4" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M4"/>
       <c r="N4" s="1" t="s">
@@ -12024,7 +12016,7 @@
         <v>0</v>
       </c>
       <c r="L6" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M6"/>
       <c r="N6" s="1" t="s">
@@ -16726,23 +16718,23 @@
         <v>20</v>
       </c>
       <c r="O5" s="18" t="s">
-        <v>550</v>
+        <v>475</v>
       </c>
       <c r="P5" s="18"/>
       <c r="Q5" s="1" t="s">
         <v>471</v>
       </c>
       <c r="R5" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="T5" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="U5" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>554</v>
       </c>
       <c r="V5" s="1">
         <v>3</v>
@@ -16757,7 +16749,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>36</v>
@@ -16766,7 +16758,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
@@ -16789,16 +16781,16 @@
         <v>494</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T6" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>558</v>
       </c>
       <c r="V6" s="1">
         <v>5</v>
@@ -16813,7 +16805,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
@@ -16822,7 +16814,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
@@ -16838,23 +16830,23 @@
         <v>20</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>561</v>
+        <v>477</v>
       </c>
       <c r="P7" s="20"/>
       <c r="Q7" s="1" t="s">
         <v>494</v>
       </c>
       <c r="R7" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="S7" s="1" t="s">
+      <c r="T7" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T7" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="U7" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="W7" s="1">
         <v>30</v>
@@ -16865,7 +16857,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>36</v>
@@ -16874,7 +16866,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
@@ -16890,16 +16882,16 @@
         <v>488</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="T8" s="1" t="s">
         <v>488</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="V8" s="1">
         <v>2</v>
@@ -16919,7 +16911,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
@@ -16942,16 +16934,16 @@
         <v>494</v>
       </c>
       <c r="R9" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="S9" s="1" t="s">
+      <c r="T9" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T9" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="U9" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="V9" s="1">
         <v>8</v>
@@ -16960,7 +16952,7 @@
         <v>8</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" ht="34" spans="3:23">
@@ -16977,7 +16969,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
@@ -16992,16 +16984,16 @@
         <v>471</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="S10" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="T10" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T10" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="U10" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="V10" s="1">
         <v>0.4</v>
@@ -17015,7 +17007,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
@@ -17024,7 +17016,7 @@
         <v>10</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
@@ -17042,23 +17034,23 @@
         <v>20</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="P11" s="20"/>
       <c r="Q11" s="1" t="s">
         <v>494</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="S11" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="T11" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T11" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="U11" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="V11" s="1">
         <v>10</v>
@@ -17072,7 +17064,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>36</v>
@@ -17081,7 +17073,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H12" s="20"/>
       <c r="K12" s="24"/>
@@ -17095,23 +17087,23 @@
         <v>20</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="P12" s="20"/>
       <c r="Q12" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="V12" s="1">
         <v>5</v>
@@ -17120,7 +17112,7 @@
         <v>5</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" ht="51" spans="3:23">
@@ -17137,7 +17129,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="I13" s="8">
         <v>4</v>
@@ -17156,23 +17148,23 @@
         <v>20</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="P13" s="20"/>
       <c r="Q13" s="1" t="s">
         <v>471</v>
       </c>
       <c r="R13" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="S13" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="S13" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="T13" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="V13" s="1">
         <v>0.15</v>
@@ -17187,7 +17179,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>36</v>
@@ -17196,7 +17188,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="I14" s="8">
         <v>2</v>
@@ -17215,34 +17207,34 @@
         <v>20</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>488</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T14" s="1" t="s">
         <v>488</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="V14" s="1">
         <v>8</v>
       </c>
       <c r="AC14" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="AE14" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="15" ht="51" spans="3:31">
@@ -17259,7 +17251,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20">
@@ -17279,23 +17271,23 @@
         <v>20</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="P15" s="20"/>
       <c r="Q15" s="1" t="s">
         <v>471</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="V15" s="1">
         <v>0.2</v>
@@ -17305,13 +17297,13 @@
         <v>2</v>
       </c>
       <c r="AC15" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="AE15" s="1" t="s">
         <v>599</v>
-      </c>
-      <c r="AD15" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="16" ht="34" spans="3:31">
@@ -17319,7 +17311,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>36</v>
@@ -17328,7 +17320,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
@@ -17344,23 +17336,23 @@
         <v>20</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="P16" s="20"/>
       <c r="Q16" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>484</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Y16" s="1" t="s">
         <v>494</v>
@@ -17372,10 +17364,10 @@
         <v>472</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" ht="51" spans="3:31">
@@ -17383,7 +17375,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>36</v>
@@ -17392,7 +17384,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -17408,26 +17400,26 @@
         <v>20</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="P17" s="20"/>
       <c r="Q17" s="1" t="s">
         <v>488</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T17" s="1" t="s">
         <v>488</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="Y17" s="1">
         <v>30</v>
@@ -17436,10 +17428,10 @@
         <v>2</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="18" ht="51" spans="3:31">
@@ -17447,7 +17439,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>29</v>
@@ -17456,7 +17448,7 @@
         <v>20</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
@@ -17472,16 +17464,16 @@
         <v>471</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S18" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="T18" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T18" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="U18" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="V18" s="1">
         <v>1</v>
@@ -17491,7 +17483,7 @@
         <v>6</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="Y18" s="1">
         <v>90</v>
@@ -17503,13 +17495,13 @@
         <v>2</v>
       </c>
       <c r="AC18" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="AE18" s="1" t="s">
         <v>621</v>
-      </c>
-      <c r="AD18" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="19" ht="51" spans="3:31">
@@ -17517,7 +17509,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>36</v>
@@ -17526,7 +17518,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -17542,26 +17534,26 @@
         <v>20</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="P19" s="20"/>
       <c r="Q19" s="1" t="s">
         <v>488</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="T19" s="1" t="s">
         <v>488</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="Y19" s="1">
         <v>150</v>
@@ -17573,10 +17565,10 @@
         <v>4</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="20" ht="17" spans="5:31">
@@ -17590,7 +17582,7 @@
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
       <c r="X20" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="Y20" s="1">
         <v>240</v>
@@ -17602,10 +17594,10 @@
         <v>7</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21" ht="51" spans="3:31">
@@ -17613,7 +17605,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>29</v>
@@ -17622,7 +17614,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
@@ -17638,23 +17630,23 @@
         <v>20</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="P21" s="20"/>
       <c r="Q21" s="1" t="s">
         <v>472</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S21" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>639</v>
       </c>
       <c r="V21" s="1">
         <v>1.5</v>
@@ -17664,10 +17656,10 @@
         <v>2.7</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" ht="34" spans="3:31">
@@ -17684,7 +17676,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
@@ -17696,16 +17688,16 @@
       <c r="N22" s="20"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="V22" s="1">
         <v>10</v>
@@ -17715,13 +17707,13 @@
         <v>100</v>
       </c>
       <c r="AC22" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="AE22" s="1" t="s">
         <v>646</v>
-      </c>
-      <c r="AD22" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="AE22" s="1" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="23" ht="51" spans="3:31">
@@ -17738,7 +17730,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
@@ -17758,25 +17750,25 @@
       </c>
       <c r="P23" s="20"/>
       <c r="Q23" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>488</v>
       </c>
       <c r="U23" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="AE23" s="1" t="s">
         <v>651</v>
-      </c>
-      <c r="AD23" s="1" t="s">
-        <v>652</v>
-      </c>
-      <c r="AE23" s="1" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="24" ht="51" spans="3:31">
@@ -17793,7 +17785,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
@@ -17809,16 +17801,16 @@
         <v>472</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T24" s="1" t="s">
         <v>497</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="V24" s="1">
         <v>1.2</v>
@@ -17828,10 +17820,10 @@
         <v>21.6</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="25" ht="34" spans="5:31">
@@ -17850,16 +17842,16 @@
         <v>20</v>
       </c>
       <c r="O25" s="20" t="s">
+        <v>656</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="AD25" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="AC25" s="1" t="s">
+      <c r="AE25" s="1" t="s">
         <v>659</v>
-      </c>
-      <c r="AD25" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="AE25" s="1" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="26" ht="34" spans="3:31">
@@ -17867,7 +17859,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>36</v>
@@ -17876,7 +17868,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
@@ -17889,19 +17881,19 @@
       <c r="O26" s="20"/>
       <c r="P26" s="20"/>
       <c r="Q26" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S26" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="V26" s="1">
         <v>10</v>
@@ -17914,10 +17906,10 @@
         <v>466</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="27" spans="5:31">
@@ -17927,10 +17919,10 @@
       <c r="G27" s="8"/>
       <c r="M27" s="20"/>
       <c r="AD27" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="AE27" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="AE27" s="1" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="28" ht="34" spans="3:31">
@@ -17938,7 +17930,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -17947,7 +17939,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
@@ -17958,19 +17950,19 @@
       <c r="O28" s="20"/>
       <c r="P28" s="20"/>
       <c r="Q28" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="V28" s="1">
         <v>10</v>
@@ -17980,13 +17972,13 @@
         <v>150</v>
       </c>
       <c r="AC28" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="AE28" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="AD28" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="AE28" s="1" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="29" spans="5:31">
@@ -18001,10 +17993,10 @@
         <v>84</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1" spans="3:31">
@@ -18021,7 +18013,7 @@
         <v>30</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20">
@@ -18042,16 +18034,16 @@
         <v>471</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S30" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="T30" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="T30" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="U30" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="V30" s="1">
         <v>0.2</v>
@@ -18061,13 +18053,13 @@
         <v>6</v>
       </c>
       <c r="AC30" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="AD30" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="AE30" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="AD30" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="AE30" s="1" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="31" ht="34" spans="3:31">
@@ -18084,7 +18076,7 @@
         <v>30</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
@@ -18097,19 +18089,19 @@
       <c r="O31" s="20"/>
       <c r="P31" s="20"/>
       <c r="Q31" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="V31" s="1">
         <v>1.5</v>
@@ -18119,10 +18111,10 @@
         <v>12</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="32" ht="51" spans="3:31">
@@ -18139,7 +18131,7 @@
         <v>30</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
@@ -18153,19 +18145,19 @@
       <c r="O32" s="20"/>
       <c r="P32" s="20"/>
       <c r="Q32" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="V32" s="1">
         <v>0.8</v>
@@ -18178,10 +18170,10 @@
         <v>493</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="33" ht="17" spans="5:31">
@@ -18196,10 +18188,10 @@
         <v>29</v>
       </c>
       <c r="AD33" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="AE33" s="1" t="s">
         <v>689</v>
-      </c>
-      <c r="AE33" s="1" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="34" spans="5:31">
@@ -18211,10 +18203,10 @@
         <v>125</v>
       </c>
       <c r="AD34" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="AE34" s="25" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="35" ht="51" spans="3:31">
@@ -18231,7 +18223,7 @@
         <v>30</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H35" s="20"/>
       <c r="I35" s="20"/>
@@ -18250,16 +18242,16 @@
         <v>471</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="V35" s="1">
         <v>1</v>
@@ -18272,10 +18264,10 @@
         <v>497</v>
       </c>
       <c r="AD35" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="AE35" s="25" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="36" ht="17" spans="5:31">
@@ -18285,16 +18277,16 @@
       <c r="G36" s="8"/>
       <c r="L36" s="20"/>
       <c r="M36" s="20" t="s">
+        <v>697</v>
+      </c>
+      <c r="AC36" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="AD36" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="AC36" s="1" t="s">
+      <c r="AE36" s="25" t="s">
         <v>700</v>
-      </c>
-      <c r="AD36" s="1" t="s">
-        <v>701</v>
-      </c>
-      <c r="AE36" s="25" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="37" ht="17" spans="5:13">
@@ -18306,7 +18298,7 @@
         <v>3</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="38" ht="34" spans="3:21">
@@ -18314,7 +18306,7 @@
         <v>26</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>29</v>
@@ -18323,7 +18315,7 @@
         <v>40</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
@@ -18339,10 +18331,10 @@
         <v>488</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T38" s="1" t="s">
         <v>488</v>
@@ -18363,10 +18355,10 @@
         <v>125</v>
       </c>
       <c r="AD39" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="AE39" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="AE39" s="1" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="40" ht="34" spans="3:31">
@@ -18383,7 +18375,7 @@
         <v>40</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
@@ -18400,26 +18392,26 @@
         <v>472</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="W40" s="1">
         <f>4</f>
         <v>4</v>
       </c>
       <c r="AD40" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="41" spans="5:31">
@@ -18430,10 +18422,10 @@
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="AD41" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="42" ht="51" spans="3:31">
@@ -18450,7 +18442,7 @@
         <v>40</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
@@ -18465,26 +18457,26 @@
         <v>472</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="W42" s="1">
         <f>2*5</f>
         <v>10</v>
       </c>
       <c r="AD42" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="43" ht="17.6" customHeight="1" spans="5:31">
@@ -18493,10 +18485,10 @@
       </c>
       <c r="G43" s="8"/>
       <c r="AD43" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="44" ht="34" spans="3:21">
@@ -18504,7 +18496,7 @@
         <v>28</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>29</v>
@@ -18513,7 +18505,7 @@
         <v>40</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
@@ -18528,16 +18520,16 @@
         <v>471</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="45" spans="5:31">
@@ -18546,10 +18538,10 @@
       </c>
       <c r="G45" s="8"/>
       <c r="AD45" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AE45" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="46" ht="51" spans="3:31">
@@ -18566,7 +18558,7 @@
         <v>40</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
@@ -18578,22 +18570,22 @@
       <c r="O46" s="20"/>
       <c r="P46" s="20"/>
       <c r="Q46" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="AD46" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="AE46" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
     </row>
     <row r="47" spans="5:31">
@@ -18601,10 +18593,10 @@
         <v>29</v>
       </c>
       <c r="AD47" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AE47" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
     </row>
     <row r="48" ht="51" spans="3:31">
@@ -18612,7 +18604,7 @@
         <v>30</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>29</v>
@@ -18621,7 +18613,7 @@
         <v>40</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H48" s="20"/>
       <c r="I48" s="20"/>
@@ -18633,22 +18625,22 @@
       <c r="O48" s="20"/>
       <c r="P48" s="20"/>
       <c r="Q48" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T48" s="1" t="s">
         <v>497</v>
       </c>
       <c r="AD48" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="AE48" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="49" spans="5:31">
@@ -18656,10 +18648,10 @@
         <v>29</v>
       </c>
       <c r="AD49" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="AE49" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="50" ht="34" spans="3:31">
@@ -18676,25 +18668,25 @@
         <v>40</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="Q50" s="1" t="s">
         <v>488</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T50" s="1" t="s">
         <v>497</v>
       </c>
       <c r="AD50" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AE50" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="51" spans="5:31">
@@ -18702,10 +18694,10 @@
         <v>29</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AE51" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="52" ht="17.6" spans="3:31">
@@ -18713,7 +18705,7 @@
         <v>32</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>29</v>
@@ -18722,7 +18714,7 @@
         <v>40</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
@@ -18737,23 +18729,23 @@
         <v>471</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>493</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="W52" s="1">
         <f>4*6</f>
         <v>24</v>
       </c>
       <c r="AD52" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="AE52" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="53" spans="5:31">
@@ -18761,10 +18753,10 @@
         <v>29</v>
       </c>
       <c r="AD53" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="54" ht="51" spans="3:31">
@@ -18772,7 +18764,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>29</v>
@@ -18781,7 +18773,7 @@
         <v>40</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="H54" s="20"/>
       <c r="I54" s="20"/>
@@ -18796,16 +18788,16 @@
         <v>472</v>
       </c>
       <c r="R54" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="AD54" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="AE54" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="AD54" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="AE54" s="1" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="55" spans="5:31">
@@ -18813,10 +18805,10 @@
         <v>29</v>
       </c>
       <c r="AD55" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="AE55" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="56" ht="51" spans="3:19">
@@ -18833,7 +18825,7 @@
         <v>60</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="H56" s="20"/>
       <c r="I56" s="20"/>
@@ -18848,10 +18840,10 @@
         <v>472</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="57" spans="5:5">
@@ -18864,7 +18856,7 @@
         <v>35</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>29</v>
@@ -18873,7 +18865,7 @@
         <v>60</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
     </row>
     <row r="59" spans="5:19">
@@ -18893,10 +18885,10 @@
         <v>471</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="60" spans="5:5">
@@ -18909,7 +18901,7 @@
         <v>36</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>29</v>
@@ -18918,7 +18910,7 @@
         <v>60</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="62" spans="5:19">
@@ -18938,10 +18930,10 @@
         <v>468</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="63" spans="5:5">
@@ -18963,7 +18955,7 @@
         <v>60</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="H64" s="20"/>
       <c r="I64" s="20"/>
@@ -18978,10 +18970,10 @@
         <v>471</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="65" spans="5:5">
@@ -19003,7 +18995,7 @@
         <v>60</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="H66" s="20"/>
       <c r="I66" s="20"/>
@@ -19018,10 +19010,10 @@
         <v>471</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="67" spans="5:5">
@@ -19043,7 +19035,7 @@
         <v>60</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="69" spans="5:19">
@@ -19063,10 +19055,10 @@
         <v>488</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="70" spans="5:5">
@@ -19088,7 +19080,7 @@
         <v>60</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="72" spans="5:19">
@@ -19108,7 +19100,7 @@
         <v>472</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>493</v>
@@ -19124,7 +19116,7 @@
         <v>41</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>84</v>
@@ -19133,7 +19125,7 @@
         <v>60</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="H74" s="20"/>
       <c r="I74" s="20"/>
@@ -19148,10 +19140,10 @@
         <v>488</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="75" spans="5:5">
@@ -19164,7 +19156,7 @@
         <v>42</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>29</v>
@@ -19173,7 +19165,7 @@
         <v>30</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="H76" s="20"/>
       <c r="I76" s="20"/>
@@ -19188,15 +19180,15 @@
         <v>472</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="77" spans="5:5">
       <c r="E77" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="78" ht="68" spans="3:28">
@@ -19213,7 +19205,7 @@
         <v>30</v>
       </c>
       <c r="G78" s="21" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H78" s="20"/>
       <c r="I78" s="20"/>
@@ -19228,7 +19220,7 @@
         <v>472</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>493</v>
@@ -19262,7 +19254,7 @@
         <v>40</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="V80" s="26"/>
       <c r="W80" s="26"/>
@@ -19274,7 +19266,7 @@
     </row>
     <row r="81" spans="5:19">
       <c r="E81" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="H81" s="20"/>
       <c r="I81" s="20"/>
@@ -19289,7 +19281,7 @@
         <v>468</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="S81" s="1" t="s">
         <v>493</v>
@@ -19297,7 +19289,7 @@
     </row>
     <row r="82" spans="5:5">
       <c r="E82" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="83" ht="34" spans="3:22">
@@ -19346,7 +19338,7 @@
     </row>
     <row r="86" ht="17.6" spans="5:28">
       <c r="E86" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="H86" s="20"/>
       <c r="I86" s="20"/>
@@ -19361,10 +19353,10 @@
         <v>472</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="U86" s="26"/>
       <c r="V86" s="26"/>
@@ -19377,7 +19369,7 @@
     </row>
     <row r="87" ht="17.6" customHeight="1" spans="5:28">
       <c r="E87" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="U87" s="26"/>
       <c r="V87" s="26"/>
@@ -19421,10 +19413,10 @@
         <v>468</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="V89" s="26"/>
       <c r="W89" s="26"/>
@@ -19447,28 +19439,28 @@
         <v>169</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F91" s="1">
         <v>160</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
     </row>
     <row r="92" spans="5:5">
       <c r="E92" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
     </row>
     <row r="93" spans="5:5">
       <c r="E93" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="94" spans="5:5">
       <c r="E94" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -19497,16 +19489,16 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -19516,16 +19508,16 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
@@ -19546,16 +19538,16 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>773</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -19565,16 +19557,16 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
@@ -19592,52 +19584,52 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AD6" s="5"/>
       <c r="AE6" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
@@ -19653,52 +19645,52 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="AB7" s="5"/>
       <c r="AC7" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="AD7" s="5"/>
       <c r="AE7" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
@@ -19712,54 +19704,54 @@
     </row>
     <row r="8" ht="45" customHeight="1" spans="8:41">
       <c r="H8" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>774</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>776</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
@@ -19778,16 +19770,16 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -19797,16 +19789,16 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
@@ -19814,13 +19806,13 @@
       <c r="AH9" s="6"/>
       <c r="AI9" s="6"/>
       <c r="AJ9" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
@@ -19833,16 +19825,16 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -19852,16 +19844,16 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
@@ -19869,13 +19861,13 @@
       <c r="AH10" s="6"/>
       <c r="AI10" s="6"/>
       <c r="AJ10" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
@@ -19888,10 +19880,10 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -19903,10 +19895,10 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
@@ -19916,13 +19908,13 @@
       <c r="AH11" s="6"/>
       <c r="AI11" s="6"/>
       <c r="AJ11" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
@@ -19935,10 +19927,10 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -19950,10 +19942,10 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
@@ -19962,7 +19954,7 @@
     </row>
     <row r="14" spans="13:13">
       <c r="M14" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="788">
   <si>
     <t>##var</t>
   </si>
@@ -1267,6 +1267,9 @@
     <t>TransferSkills</t>
   </si>
   <si>
+    <t>Other</t>
+  </si>
+  <si>
     <t>甜蜜传递 {count} 个食物</t>
   </si>
   <si>
@@ -1341,7 +1344,7 @@
 倍率 {tiervals}</t>
   </si>
   <si>
-    <t>when:transfer</t>
+    <t>when:transfer;resultscope:ColumnAndSelf</t>
   </si>
   <si>
     <t>{cscope}
@@ -1444,7 +1447,7 @@
     <t>Down</t>
   </si>
   <si>
-    <t>modifier:add-targets;skilltype:TransferSkills</t>
+    <t>modifier:add-targets</t>
   </si>
   <si>
     <t>{ascope}食物发动甜蜜传递时
@@ -12859,7 +12862,7 @@
         <v>406</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -12875,17 +12878,17 @@
         <v>27</v>
       </c>
       <c r="P12" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R12"/>
       <c r="S12" s="33" t="s">
         <v>51</v>
       </c>
       <c r="T12" s="33" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="13" ht="17" spans="1:20">
@@ -12929,7 +12932,7 @@
         <v>386</v>
       </c>
       <c r="P13" s="19" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q13"/>
       <c r="R13"/>
@@ -12981,7 +12984,7 @@
         <v>386</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q14" t="s">
         <v>400</v>
@@ -13035,7 +13038,7 @@
         <v>386</v>
       </c>
       <c r="P15" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q15" t="s">
         <v>400</v>
@@ -13089,7 +13092,7 @@
         <v>386</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q16"/>
       <c r="R16"/>
@@ -13112,7 +13115,7 @@
         <v>381</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>383</v>
@@ -13125,7 +13128,7 @@
         <v>406</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="K17" s="1">
         <v>2</v>
@@ -13141,17 +13144,17 @@
         <v>27</v>
       </c>
       <c r="P17" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R17"/>
       <c r="S17" s="33" t="s">
         <v>62</v>
       </c>
       <c r="T17" s="33" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" ht="34" spans="1:20">
@@ -13195,7 +13198,7 @@
         <v>386</v>
       </c>
       <c r="P18" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q18"/>
       <c r="R18"/>
@@ -13231,7 +13234,7 @@
         <v>406</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="K19" s="1">
         <v>1</v>
@@ -13247,17 +13250,17 @@
         <v>27</v>
       </c>
       <c r="P19" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R19"/>
       <c r="S19" s="33" t="s">
         <v>67</v>
       </c>
       <c r="T19" s="33" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="20" ht="34" spans="1:20">
@@ -13281,7 +13284,7 @@
         <v>396</v>
       </c>
       <c r="H20" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>339</v>
@@ -13303,7 +13306,7 @@
         <v>386</v>
       </c>
       <c r="P20" s="19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q20"/>
       <c r="R20"/>
@@ -13326,7 +13329,7 @@
         <v>381</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>383</v>
@@ -13339,7 +13342,7 @@
         <v>339</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -13355,7 +13358,7 @@
         <v>386</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q21"/>
       <c r="R21"/>
@@ -13363,7 +13366,7 @@
         <v>74</v>
       </c>
       <c r="T21" s="33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="22" spans="1:20">
@@ -13407,7 +13410,7 @@
         <v>386</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q22" t="s">
         <v>400</v>
@@ -13432,7 +13435,7 @@
         <v>392</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>383</v>
@@ -13445,7 +13448,7 @@
         <v>336</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K23" s="1">
         <v>0</v>
@@ -13461,7 +13464,7 @@
         <v>386</v>
       </c>
       <c r="P23" s="19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q23"/>
       <c r="R23"/>
@@ -13469,7 +13472,7 @@
         <v>77</v>
       </c>
       <c r="T23" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" ht="34" spans="1:20">
@@ -13484,7 +13487,7 @@
         <v>402</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>383</v>
@@ -13497,7 +13500,7 @@
         <v>336</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K24" s="1">
         <v>0</v>
@@ -13513,14 +13516,14 @@
         <v>386</v>
       </c>
       <c r="P24" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="R24"/>
       <c r="S24" s="33" t="s">
         <v>82</v>
       </c>
       <c r="T24" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="25" ht="17" spans="1:20">
@@ -13545,7 +13548,7 @@
       </c>
       <c r="H25"/>
       <c r="I25" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J25" s="1" t="s">
         <v>393</v>
@@ -13564,7 +13567,7 @@
         <v>386</v>
       </c>
       <c r="P25" s="19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q25"/>
       <c r="R25"/>
@@ -13616,7 +13619,7 @@
         <v>386</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="R26"/>
       <c r="S26" s="33" t="s">
@@ -13651,7 +13654,7 @@
         <v>406</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
@@ -13667,17 +13670,17 @@
         <v>27</v>
       </c>
       <c r="P27" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q27" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R27"/>
       <c r="S27" s="33" t="s">
         <v>93</v>
       </c>
       <c r="T27" s="33" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" spans="1:20">
@@ -13692,7 +13695,7 @@
         <v>381</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>383</v>
@@ -13705,7 +13708,7 @@
         <v>339</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K28" s="1">
         <v>0</v>
@@ -13714,7 +13717,7 @@
         <v>1.5</v>
       </c>
       <c r="M28" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>27</v>
@@ -13723,7 +13726,7 @@
         <v>386</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q28"/>
       <c r="R28"/>
@@ -13731,7 +13734,7 @@
         <v>98</v>
       </c>
       <c r="T28" s="33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="29" spans="1:20">
@@ -13746,7 +13749,7 @@
         <v>381</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>383</v>
@@ -13759,7 +13762,7 @@
         <v>336</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K29" s="1">
         <v>0</v>
@@ -13775,7 +13778,7 @@
         <v>386</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q29"/>
       <c r="R29"/>
@@ -13783,7 +13786,7 @@
         <v>98</v>
       </c>
       <c r="T29" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="30" spans="1:20">
@@ -13827,7 +13830,7 @@
         <v>386</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q30"/>
       <c r="R30"/>
@@ -13879,7 +13882,7 @@
         <v>386</v>
       </c>
       <c r="P31" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q31" t="s">
         <v>400</v>
@@ -13904,22 +13907,22 @@
         <v>402</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>383</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H32" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>339</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K32" s="1">
         <v>0</v>
@@ -13928,7 +13931,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>27</v>
@@ -13937,7 +13940,7 @@
         <v>386</v>
       </c>
       <c r="P32" s="19" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q32"/>
       <c r="R32"/>
@@ -13945,7 +13948,7 @@
         <v>108</v>
       </c>
       <c r="T32" s="33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33" s="32" customFormat="1" ht="34" spans="1:20">
@@ -13960,7 +13963,7 @@
         <v>381</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>383</v>
@@ -13973,7 +13976,7 @@
         <v>342</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K33" s="1">
         <v>0</v>
@@ -13982,7 +13985,7 @@
         <v>1.5</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N33" s="1" t="s">
         <v>27</v>
@@ -13991,7 +13994,7 @@
         <v>27</v>
       </c>
       <c r="P33" s="19" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q33"/>
       <c r="R33"/>
@@ -13999,7 +14002,7 @@
         <v>114</v>
       </c>
       <c r="T33" s="33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -14024,7 +14027,7 @@
       </c>
       <c r="H34"/>
       <c r="I34" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>393</v>
@@ -14043,7 +14046,7 @@
         <v>386</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R34"/>
       <c r="S34" s="33" t="s">
@@ -14078,7 +14081,7 @@
         <v>406</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="K35" s="1">
         <v>1</v>
@@ -14094,17 +14097,17 @@
         <v>27</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q35" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R35"/>
       <c r="S35" s="33" t="s">
         <v>117</v>
       </c>
       <c r="T35" s="33" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="36" spans="1:20">
@@ -14148,7 +14151,7 @@
         <v>386</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q36" t="s">
         <v>400</v>
@@ -14173,7 +14176,7 @@
         <v>381</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>383</v>
@@ -14183,10 +14186,10 @@
       </c>
       <c r="H37"/>
       <c r="I37" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K37" s="1">
         <v>0</v>
@@ -14195,7 +14198,7 @@
         <v>1</v>
       </c>
       <c r="M37" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N37" s="1" t="s">
         <v>27</v>
@@ -14204,7 +14207,7 @@
         <v>27</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q37"/>
       <c r="R37"/>
@@ -14212,7 +14215,7 @@
         <v>120</v>
       </c>
       <c r="T37" s="33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="38" spans="1:20">
@@ -14256,7 +14259,7 @@
         <v>27</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q38"/>
       <c r="R38"/>
@@ -14301,7 +14304,7 @@
         <v>1.5</v>
       </c>
       <c r="M39" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N39" s="1" t="s">
         <v>27</v>
@@ -14310,7 +14313,7 @@
         <v>27</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q39" t="s">
         <v>400</v>
@@ -14335,7 +14338,7 @@
         <v>381</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>383</v>
@@ -14345,10 +14348,10 @@
       </c>
       <c r="H40"/>
       <c r="I40" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K40" s="1">
         <v>3</v>
@@ -14357,7 +14360,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N40" s="1" t="s">
         <v>27</v>
@@ -14366,17 +14369,17 @@
         <v>27</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q40" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R40"/>
       <c r="S40" s="33" t="s">
         <v>129</v>
       </c>
       <c r="T40" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" ht="34" spans="1:20">
@@ -14391,22 +14394,22 @@
         <v>402</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>383</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H41" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>342</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -14415,7 +14418,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N41" s="1" t="s">
         <v>27</v>
@@ -14424,7 +14427,7 @@
         <v>27</v>
       </c>
       <c r="P41" s="19" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q41"/>
       <c r="R41"/>
@@ -14432,7 +14435,7 @@
         <v>132</v>
       </c>
       <c r="T41" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="42" spans="1:20">
@@ -14447,7 +14450,7 @@
         <v>402</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>383</v>
@@ -14460,7 +14463,7 @@
         <v>339</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K42" s="1">
         <v>0</v>
@@ -14476,7 +14479,7 @@
         <v>386</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q42"/>
       <c r="R42"/>
@@ -14484,7 +14487,7 @@
         <v>135</v>
       </c>
       <c r="T42" s="33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" ht="17" spans="1:20">
@@ -14528,7 +14531,7 @@
         <v>386</v>
       </c>
       <c r="P43" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q43" t="s">
         <v>400</v>
@@ -14553,7 +14556,7 @@
         <v>381</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>383</v>
@@ -14566,7 +14569,7 @@
         <v>336</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K44" s="1">
         <v>0</v>
@@ -14575,7 +14578,7 @@
         <v>30</v>
       </c>
       <c r="M44" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>27</v>
@@ -14584,7 +14587,7 @@
         <v>386</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q44"/>
       <c r="R44"/>
@@ -14592,7 +14595,7 @@
         <v>138</v>
       </c>
       <c r="T44" s="33" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" ht="34" spans="1:20">
@@ -14634,7 +14637,7 @@
         <v>386</v>
       </c>
       <c r="P45" s="19" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q45"/>
       <c r="R45"/>
@@ -14657,7 +14660,7 @@
         <v>381</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>383</v>
@@ -14670,7 +14673,7 @@
         <v>406</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
       <c r="K46" s="1">
         <v>3</v>
@@ -14686,17 +14689,17 @@
         <v>27</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q46" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R46"/>
       <c r="S46" s="33" t="s">
         <v>141</v>
       </c>
       <c r="T46" s="33" t="s">
-        <v>448</v>
+        <v>407</v>
       </c>
     </row>
     <row r="47" spans="1:20">
@@ -14711,7 +14714,7 @@
         <v>381</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>383</v>
@@ -14724,7 +14727,7 @@
         <v>342</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K47" s="1">
         <v>0</v>
@@ -14733,7 +14736,7 @@
         <v>2</v>
       </c>
       <c r="M47" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>27</v>
@@ -14742,7 +14745,7 @@
         <v>27</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q47"/>
       <c r="R47"/>
@@ -14750,7 +14753,7 @@
         <v>145</v>
       </c>
       <c r="T47" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="48" ht="34" spans="1:20">
@@ -14762,19 +14765,19 @@
         <v>380</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>383</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H48" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>397</v>
@@ -14789,7 +14792,7 @@
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>27</v>
@@ -14798,7 +14801,7 @@
         <v>386</v>
       </c>
       <c r="P48" s="19" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q48" t="s">
         <v>400</v>
@@ -14852,7 +14855,7 @@
         <v>27</v>
       </c>
       <c r="P49" s="19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q49"/>
       <c r="R49"/>
@@ -14888,7 +14891,7 @@
         <v>406</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K50" s="1">
         <v>1</v>
@@ -14904,17 +14907,17 @@
         <v>27</v>
       </c>
       <c r="P50" s="19" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q50" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R50"/>
       <c r="S50" s="33" t="s">
         <v>148</v>
       </c>
       <c r="T50" s="33" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="51" ht="34" spans="1:20">
@@ -14958,7 +14961,7 @@
         <v>27</v>
       </c>
       <c r="P51" s="19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q51"/>
       <c r="R51"/>
@@ -14981,7 +14984,7 @@
         <v>381</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>383</v>
@@ -14994,7 +14997,7 @@
         <v>342</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K52" s="1">
         <v>0</v>
@@ -15003,7 +15006,7 @@
         <v>2</v>
       </c>
       <c r="M52" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>27</v>
@@ -15012,7 +15015,7 @@
         <v>27</v>
       </c>
       <c r="P52" s="19" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q52"/>
       <c r="R52"/>
@@ -15020,7 +15023,7 @@
         <v>154</v>
       </c>
       <c r="T52" s="33" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="53" ht="34" spans="1:20">
@@ -15032,10 +15035,10 @@
         <v>380</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>383</v>
@@ -15044,7 +15047,7 @@
         <v>396</v>
       </c>
       <c r="H53" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>397</v>
@@ -15065,7 +15068,7 @@
         <v>386</v>
       </c>
       <c r="P53" s="19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q53" t="s">
         <v>400</v>
@@ -15100,10 +15103,10 @@
       </c>
       <c r="H54"/>
       <c r="I54" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K54" s="1">
         <v>0</v>
@@ -15112,7 +15115,7 @@
         <v>1</v>
       </c>
       <c r="M54" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N54" s="1" t="s">
         <v>386</v>
@@ -15121,14 +15124,14 @@
         <v>386</v>
       </c>
       <c r="P54" s="19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="R54"/>
       <c r="S54" s="33" t="s">
         <v>157</v>
       </c>
       <c r="T54" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="55" ht="34" spans="1:20">
@@ -15143,7 +15146,7 @@
         <v>381</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>383</v>
@@ -15153,10 +15156,10 @@
       </c>
       <c r="H55"/>
       <c r="I55" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K55" s="1">
         <v>0</v>
@@ -15165,7 +15168,7 @@
         <v>2</v>
       </c>
       <c r="M55" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N55" s="1" t="s">
         <v>27</v>
@@ -15174,17 +15177,17 @@
         <v>27</v>
       </c>
       <c r="P55" s="19" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q55" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R55"/>
       <c r="S55" s="33" t="s">
         <v>160</v>
       </c>
       <c r="T55" s="33" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="56" ht="34" spans="1:20">
@@ -15228,7 +15231,7 @@
         <v>27</v>
       </c>
       <c r="P56" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q56"/>
       <c r="R56"/>
@@ -15251,7 +15254,7 @@
         <v>381</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>383</v>
@@ -15261,10 +15264,10 @@
       </c>
       <c r="H57"/>
       <c r="I57" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K57" s="1">
         <v>0</v>
@@ -15273,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N57" s="1" t="s">
         <v>27</v>
@@ -15282,17 +15285,17 @@
         <v>27</v>
       </c>
       <c r="P57" s="19" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q57" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R57"/>
       <c r="S57" s="33" t="s">
         <v>163</v>
       </c>
       <c r="T57" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" spans="1:20">
@@ -15307,7 +15310,7 @@
         <v>402</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>383</v>
@@ -15320,7 +15323,7 @@
         <v>339</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K58" s="1">
         <v>0</v>
@@ -15336,7 +15339,7 @@
         <v>386</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q58"/>
       <c r="R58"/>
@@ -15344,7 +15347,7 @@
         <v>166</v>
       </c>
       <c r="T58" s="33" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="59" spans="1:20">
@@ -15369,7 +15372,7 @@
       </c>
       <c r="H59"/>
       <c r="I59" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J59" s="1" t="s">
         <v>382</v>
@@ -15381,7 +15384,7 @@
         <v>3</v>
       </c>
       <c r="M59" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N59" s="1" t="s">
         <v>27</v>
@@ -15390,7 +15393,7 @@
         <v>27</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q59"/>
       <c r="R59"/>
@@ -15779,36 +15782,36 @@
     <row r="4" ht="17.6" spans="3:20">
       <c r="C4" s="1"/>
       <c r="D4" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="S4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="T4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" ht="34" spans="3:17">
       <c r="C5" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>199</v>
@@ -15820,7 +15823,7 @@
         <v>20</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -15844,7 +15847,7 @@
         <v>20</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -15871,7 +15874,7 @@
         <v>20</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -15906,7 +15909,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -15928,18 +15931,18 @@
       </c>
       <c r="G10" s="20"/>
       <c r="I10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="J10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" ht="34" spans="3:18">
       <c r="C11" s="24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>41</v>
@@ -15951,19 +15954,19 @@
         <v>20</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P11">
         <v>2</v>
@@ -15987,13 +15990,13 @@
         <v>20</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="I12" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J12" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P12">
         <v>2</v>
@@ -16014,19 +16017,19 @@
         <v>20</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P13">
         <v>2</v>
@@ -16047,16 +16050,16 @@
         <v>20</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I14" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J14" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K14" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="P14">
         <v>2</v>
@@ -16074,16 +16077,16 @@
         <v>20</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P15">
         <v>2</v>
@@ -16107,16 +16110,16 @@
         <v>20</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J16" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K16" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P16">
         <v>2</v>
@@ -16134,16 +16137,16 @@
         <v>20</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I17" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J17" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K17" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P17">
         <v>2</v>
@@ -16172,16 +16175,16 @@
         <v>20</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="I19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="P19">
         <v>2</v>
@@ -16209,16 +16212,16 @@
         <v>20</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="I21" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J21" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K21" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="P21">
         <v>2</v>
@@ -16247,16 +16250,16 @@
         <v>20</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="P23">
         <v>2</v>
@@ -16292,16 +16295,16 @@
         <v>20</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I25" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J25" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K25" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="P25">
         <v>2</v>
@@ -16321,7 +16324,7 @@
     </row>
     <row r="27" ht="51" spans="3:23">
       <c r="C27" s="27" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>82</v>
@@ -16330,16 +16333,16 @@
         <v>84</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I27" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J27" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K27" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P27">
         <v>3</v>
@@ -16369,13 +16372,13 @@
       </c>
       <c r="F28" s="20"/>
       <c r="G28" s="20" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I28" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K28" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="V28" s="8"/>
       <c r="W28" s="20"/>
@@ -16389,16 +16392,16 @@
         <v>84</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="I29" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J29" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="V29" s="8"/>
       <c r="W29" s="20"/>
@@ -16413,16 +16416,16 @@
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="20" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="I30" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J30" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K30" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="V30" s="20"/>
       <c r="W30" s="8"/>
@@ -16437,16 +16440,16 @@
       </c>
       <c r="F31" s="20"/>
       <c r="G31" s="20" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="I31" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J31" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K31" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="V31" s="20"/>
       <c r="W31" s="19"/>
@@ -16460,16 +16463,16 @@
         <v>36</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I32" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J32" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K32" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="33" spans="3:5">
@@ -16495,16 +16498,16 @@
         <v>36</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I35" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J35" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K35" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="36" spans="3:5">
@@ -16530,16 +16533,16 @@
         <v>36</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I38" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J38" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K38" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="39" spans="3:7">
@@ -16567,13 +16570,13 @@
       </c>
       <c r="F41" s="20"/>
       <c r="G41" s="20" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I41" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J41" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="42" spans="3:5">
@@ -16600,16 +16603,16 @@
         <v>143</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I44" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J44" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K44" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="45" spans="3:7">
@@ -16623,7 +16626,7 @@
     </row>
     <row r="46" ht="34" spans="3:19">
       <c r="C46" s="29" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>126</v>
@@ -16635,10 +16638,10 @@
         <v>40</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="I46" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P46">
         <v>4</v>
@@ -16671,10 +16674,10 @@
         <v>40</v>
       </c>
       <c r="G48" s="20" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I48" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="49" spans="3:5">
@@ -16695,16 +16698,16 @@
         <v>40</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I50" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J50" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K50" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="51" spans="3:5">
@@ -16725,16 +16728,16 @@
         <v>40</v>
       </c>
       <c r="G52" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="I52" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J52" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K52" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="53" ht="17.6" spans="3:7">
@@ -16757,16 +16760,16 @@
         <v>40</v>
       </c>
       <c r="G54" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I54" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J54" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K54" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="55" spans="3:5">
@@ -16787,10 +16790,10 @@
         <v>40</v>
       </c>
       <c r="G56" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I56" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" spans="3:5">
@@ -16807,7 +16810,7 @@
     </row>
     <row r="59" ht="68" spans="3:19">
       <c r="C59" s="31" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>145</v>
@@ -16819,16 +16822,16 @@
         <v>60</v>
       </c>
       <c r="G59" s="19" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="I59" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J59" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K59" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="P59">
         <v>4</v>
@@ -16861,16 +16864,16 @@
         <v>60</v>
       </c>
       <c r="G61" s="20" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I61" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J61" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K61" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="62" spans="3:5">
@@ -16888,16 +16891,16 @@
         <v>84</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I63" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="J63" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K63" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="64" spans="3:7">
@@ -16917,16 +16920,16 @@
         <v>29</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="I65" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J65" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K65" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="66" spans="3:11">
@@ -16955,10 +16958,10 @@
         <v>29</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="I68" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K68" s="19"/>
     </row>
@@ -16988,10 +16991,10 @@
         <v>29</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I71" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" spans="3:7">
@@ -17012,7 +17015,7 @@
     </row>
     <row r="74" ht="34" spans="3:7">
       <c r="C74" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>163</v>
@@ -17024,7 +17027,7 @@
         <v>110</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="75" spans="3:7">
@@ -17055,7 +17058,7 @@
         <v>90</v>
       </c>
       <c r="G77" s="20" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="78" spans="3:7">
@@ -17086,7 +17089,7 @@
         <v>120</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="81" spans="4:7">
@@ -17116,7 +17119,7 @@
     </row>
     <row r="88" ht="51" spans="7:7">
       <c r="G88" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -17172,16 +17175,16 @@
         <v>1</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
@@ -17190,35 +17193,35 @@
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P4" s="15"/>
       <c r="Q4" s="10" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="R4" s="10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="S4" s="10" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="T4" s="10" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" ht="34" spans="3:23">
@@ -17226,7 +17229,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>36</v>
@@ -17235,13 +17238,13 @@
         <v>10</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
       <c r="K5" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="L5" s="18" t="s">
         <v>199</v>
@@ -17253,23 +17256,23 @@
         <v>20</v>
       </c>
       <c r="O5" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="P5" s="18"/>
       <c r="Q5" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="V5" s="1">
         <v>3</v>
@@ -17284,7 +17287,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>36</v>
@@ -17293,7 +17296,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H6" s="20"/>
       <c r="I6" s="20"/>
@@ -17309,23 +17312,23 @@
         <v>20</v>
       </c>
       <c r="O6" s="20" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P6" s="20"/>
       <c r="Q6" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="T6" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="V6" s="1">
         <v>5</v>
@@ -17340,7 +17343,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
@@ -17349,7 +17352,7 @@
         <v>40</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
@@ -17365,23 +17368,23 @@
         <v>20</v>
       </c>
       <c r="O7" s="20" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P7" s="20"/>
       <c r="Q7" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="W7" s="1">
         <v>30</v>
@@ -17392,7 +17395,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>36</v>
@@ -17401,7 +17404,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H8" s="20"/>
       <c r="I8" s="20"/>
@@ -17414,19 +17417,19 @@
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
       <c r="Q8" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="V8" s="1">
         <v>2</v>
@@ -17446,7 +17449,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H9" s="20"/>
       <c r="I9" s="20"/>
@@ -17462,23 +17465,23 @@
         <v>20</v>
       </c>
       <c r="O9" s="20" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P9" s="20"/>
       <c r="Q9" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="V9" s="1">
         <v>8</v>
@@ -17487,7 +17490,7 @@
         <v>8</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" ht="34" spans="3:23">
@@ -17504,7 +17507,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
@@ -17516,19 +17519,19 @@
       <c r="O10" s="20"/>
       <c r="P10" s="20"/>
       <c r="Q10" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="V10" s="1">
         <v>0.4</v>
@@ -17542,7 +17545,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>36</v>
@@ -17551,13 +17554,13 @@
         <v>10</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H11" s="20"/>
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="24" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L11" s="10" t="s">
         <v>41</v>
@@ -17569,23 +17572,23 @@
         <v>20</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P11" s="20"/>
       <c r="Q11" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="V11" s="1">
         <v>10</v>
@@ -17599,7 +17602,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>36</v>
@@ -17608,7 +17611,7 @@
         <v>10</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H12" s="20"/>
       <c r="K12" s="24"/>
@@ -17622,23 +17625,23 @@
         <v>20</v>
       </c>
       <c r="O12" s="20" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P12" s="20"/>
       <c r="Q12" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V12" s="1">
         <v>5</v>
@@ -17647,7 +17650,7 @@
         <v>5</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="13" ht="51" spans="3:23">
@@ -17664,7 +17667,7 @@
         <v>10</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="I13" s="8">
         <v>4</v>
@@ -17683,23 +17686,23 @@
         <v>20</v>
       </c>
       <c r="O13" s="20" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P13" s="20"/>
       <c r="Q13" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="V13" s="1">
         <v>0.15</v>
@@ -17714,7 +17717,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>36</v>
@@ -17723,7 +17726,7 @@
         <v>10</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="I14" s="8">
         <v>2</v>
@@ -17742,34 +17745,34 @@
         <v>20</v>
       </c>
       <c r="O14" s="20" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="V14" s="1">
         <v>8</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="15" ht="51" spans="3:31">
@@ -17786,7 +17789,7 @@
         <v>10</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H15" s="20"/>
       <c r="I15" s="20">
@@ -17806,23 +17809,23 @@
         <v>20</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="P15" s="20"/>
       <c r="Q15" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="V15" s="1">
         <v>0.2</v>
@@ -17832,13 +17835,13 @@
         <v>2</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" ht="34" spans="3:31">
@@ -17846,7 +17849,7 @@
         <v>12</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>36</v>
@@ -17855,7 +17858,7 @@
         <v>10</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H16" s="20"/>
       <c r="I16" s="20"/>
@@ -17871,38 +17874,38 @@
         <v>20</v>
       </c>
       <c r="O16" s="20" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P16" s="20"/>
       <c r="Q16" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" ht="51" spans="3:31">
@@ -17910,7 +17913,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>36</v>
@@ -17919,7 +17922,7 @@
         <v>10</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
@@ -17935,26 +17938,26 @@
         <v>20</v>
       </c>
       <c r="O17" s="20" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P17" s="20"/>
       <c r="Q17" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="Y17" s="1">
         <v>30</v>
@@ -17963,10 +17966,10 @@
         <v>2</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18" ht="51" spans="3:31">
@@ -17974,7 +17977,7 @@
         <v>14</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>29</v>
@@ -17983,7 +17986,7 @@
         <v>20</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
@@ -17996,19 +17999,19 @@
       <c r="O18" s="20"/>
       <c r="P18" s="20"/>
       <c r="Q18" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="V18" s="1">
         <v>1</v>
@@ -18018,7 +18021,7 @@
         <v>6</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Y18" s="1">
         <v>90</v>
@@ -18030,13 +18033,13 @@
         <v>2</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="19" ht="51" spans="3:31">
@@ -18044,7 +18047,7 @@
         <v>15</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>36</v>
@@ -18053,7 +18056,7 @@
         <v>20</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -18069,26 +18072,26 @@
         <v>20</v>
       </c>
       <c r="O19" s="20" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P19" s="20"/>
       <c r="Q19" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Y19" s="1">
         <v>150</v>
@@ -18100,10 +18103,10 @@
         <v>4</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="20" ht="17" spans="5:31">
@@ -18117,7 +18120,7 @@
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
       <c r="X20" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="Y20" s="1">
         <v>240</v>
@@ -18129,10 +18132,10 @@
         <v>7</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="21" ht="51" spans="3:31">
@@ -18140,7 +18143,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>29</v>
@@ -18149,7 +18152,7 @@
         <v>20</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
@@ -18165,23 +18168,23 @@
         <v>20</v>
       </c>
       <c r="O21" s="20" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P21" s="20"/>
       <c r="Q21" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="V21" s="1">
         <v>1.5</v>
@@ -18191,10 +18194,10 @@
         <v>2.7</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="22" ht="34" spans="3:31">
@@ -18211,7 +18214,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
@@ -18223,16 +18226,16 @@
       <c r="N22" s="20"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="V22" s="1">
         <v>10</v>
@@ -18242,13 +18245,13 @@
         <v>100</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="23" ht="51" spans="3:31">
@@ -18265,7 +18268,7 @@
         <v>20</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
@@ -18281,29 +18284,29 @@
         <v>20</v>
       </c>
       <c r="O23" s="20" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P23" s="20"/>
       <c r="Q23" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="24" ht="51" spans="3:31">
@@ -18320,7 +18323,7 @@
         <v>20</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
@@ -18333,19 +18336,19 @@
       <c r="O24" s="20"/>
       <c r="P24" s="20"/>
       <c r="Q24" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="V24" s="1">
         <v>1.2</v>
@@ -18355,10 +18358,10 @@
         <v>21.6</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="25" ht="34" spans="5:31">
@@ -18377,16 +18380,16 @@
         <v>20</v>
       </c>
       <c r="O25" s="20" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="26" ht="34" spans="3:31">
@@ -18394,7 +18397,7 @@
         <v>20</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>36</v>
@@ -18403,7 +18406,7 @@
         <v>20</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H26" s="20"/>
       <c r="I26" s="20"/>
@@ -18416,19 +18419,19 @@
       <c r="O26" s="20"/>
       <c r="P26" s="20"/>
       <c r="Q26" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="V26" s="1">
         <v>10</v>
@@ -18438,13 +18441,13 @@
         <v>30</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="5:31">
@@ -18454,10 +18457,10 @@
       <c r="G27" s="8"/>
       <c r="M27" s="20"/>
       <c r="AD27" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="28" ht="34" spans="3:31">
@@ -18465,7 +18468,7 @@
         <v>21</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>36</v>
@@ -18474,7 +18477,7 @@
         <v>20</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H28" s="20"/>
       <c r="I28" s="20"/>
@@ -18485,19 +18488,19 @@
       <c r="O28" s="20"/>
       <c r="P28" s="20"/>
       <c r="Q28" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="V28" s="1">
         <v>10</v>
@@ -18507,13 +18510,13 @@
         <v>150</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="29" spans="5:31">
@@ -18528,10 +18531,10 @@
         <v>84</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1" spans="3:31">
@@ -18548,7 +18551,7 @@
         <v>30</v>
       </c>
       <c r="G30" s="20" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H30" s="20"/>
       <c r="I30" s="20">
@@ -18566,19 +18569,19 @@
       <c r="O30" s="20"/>
       <c r="P30" s="20"/>
       <c r="Q30" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="V30" s="1">
         <v>0.2</v>
@@ -18588,13 +18591,13 @@
         <v>6</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="31" ht="34" spans="3:31">
@@ -18611,7 +18614,7 @@
         <v>30</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
@@ -18624,19 +18627,19 @@
       <c r="O31" s="20"/>
       <c r="P31" s="20"/>
       <c r="Q31" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="V31" s="1">
         <v>1.5</v>
@@ -18646,10 +18649,10 @@
         <v>12</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="32" ht="51" spans="3:31">
@@ -18666,7 +18669,7 @@
         <v>30</v>
       </c>
       <c r="G32" s="20" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H32" s="20"/>
       <c r="I32" s="20"/>
@@ -18680,19 +18683,19 @@
       <c r="O32" s="20"/>
       <c r="P32" s="20"/>
       <c r="Q32" s="1" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="V32" s="1">
         <v>0.8</v>
@@ -18702,13 +18705,13 @@
         <v>20</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="33" ht="17" spans="5:31">
@@ -18723,10 +18726,10 @@
         <v>29</v>
       </c>
       <c r="AD33" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AE33" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="34" spans="5:31">
@@ -18738,10 +18741,10 @@
         <v>143</v>
       </c>
       <c r="AD34" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AE34" s="25" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="35" ht="51" spans="3:31">
@@ -18758,7 +18761,7 @@
         <v>30</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H35" s="20"/>
       <c r="I35" s="20"/>
@@ -18774,19 +18777,19 @@
       <c r="O35" s="20"/>
       <c r="P35" s="20"/>
       <c r="Q35" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="V35" s="1">
         <v>1</v>
@@ -18796,13 +18799,13 @@
         <v>12</v>
       </c>
       <c r="AC35" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AD35" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AE35" s="25" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="36" ht="17" spans="5:31">
@@ -18812,16 +18815,16 @@
       <c r="G36" s="8"/>
       <c r="L36" s="20"/>
       <c r="M36" s="20" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AC36" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AD36" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AE36" s="25" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="37" ht="17" spans="5:13">
@@ -18833,7 +18836,7 @@
         <v>3</v>
       </c>
       <c r="M37" s="20" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="38" ht="34" spans="3:21">
@@ -18841,7 +18844,7 @@
         <v>26</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>29</v>
@@ -18850,7 +18853,7 @@
         <v>40</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H38" s="20"/>
       <c r="I38" s="20"/>
@@ -18863,19 +18866,19 @@
       <c r="O38" s="20"/>
       <c r="P38" s="20"/>
       <c r="Q38" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="39" spans="5:31">
@@ -18890,10 +18893,10 @@
         <v>143</v>
       </c>
       <c r="AD39" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="40" ht="34" spans="3:31">
@@ -18910,7 +18913,7 @@
         <v>40</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H40" s="20"/>
       <c r="I40" s="20"/>
@@ -18924,29 +18927,29 @@
       <c r="O40" s="20"/>
       <c r="P40" s="20"/>
       <c r="Q40" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="W40" s="1">
         <f>4</f>
         <v>4</v>
       </c>
       <c r="AD40" s="1" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="41" spans="5:31">
@@ -18957,10 +18960,10 @@
       <c r="L41" s="20"/>
       <c r="M41" s="20"/>
       <c r="AD41" s="1" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="42" ht="51" spans="3:31">
@@ -18977,7 +18980,7 @@
         <v>40</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
@@ -18989,29 +18992,29 @@
       <c r="O42" s="20"/>
       <c r="P42" s="20"/>
       <c r="Q42" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="W42" s="1">
         <f>2*5</f>
         <v>10</v>
       </c>
       <c r="AD42" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="43" ht="17.6" customHeight="1" spans="5:31">
@@ -19020,10 +19023,10 @@
       </c>
       <c r="G43" s="8"/>
       <c r="AD43" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="44" ht="34" spans="3:21">
@@ -19031,7 +19034,7 @@
         <v>28</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>29</v>
@@ -19040,7 +19043,7 @@
         <v>40</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
@@ -19052,19 +19055,19 @@
       <c r="O44" s="20"/>
       <c r="P44" s="20"/>
       <c r="Q44" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="45" spans="5:31">
@@ -19073,10 +19076,10 @@
       </c>
       <c r="G45" s="8"/>
       <c r="AD45" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AE45" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="46" ht="51" spans="3:31">
@@ -19093,7 +19096,7 @@
         <v>40</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
@@ -19105,22 +19108,22 @@
       <c r="O46" s="20"/>
       <c r="P46" s="20"/>
       <c r="Q46" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AD46" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="AE46" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="47" spans="5:31">
@@ -19128,10 +19131,10 @@
         <v>29</v>
       </c>
       <c r="AD47" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AE47" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="48" ht="51" spans="3:31">
@@ -19139,7 +19142,7 @@
         <v>30</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>29</v>
@@ -19148,7 +19151,7 @@
         <v>40</v>
       </c>
       <c r="G48" s="19" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H48" s="20"/>
       <c r="I48" s="20"/>
@@ -19160,22 +19163,22 @@
       <c r="O48" s="20"/>
       <c r="P48" s="20"/>
       <c r="Q48" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AD48" s="1" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AE48" s="1" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="49" spans="5:31">
@@ -19183,10 +19186,10 @@
         <v>29</v>
       </c>
       <c r="AD49" s="1" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AE49" s="1" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="50" ht="34" spans="3:31">
@@ -19203,25 +19206,25 @@
         <v>40</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AD50" s="1" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AE50" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="51" spans="5:31">
@@ -19229,10 +19232,10 @@
         <v>29</v>
       </c>
       <c r="AD51" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AE51" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="52" ht="17.6" spans="3:31">
@@ -19240,7 +19243,7 @@
         <v>32</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>29</v>
@@ -19249,7 +19252,7 @@
         <v>40</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
@@ -19261,26 +19264,26 @@
       <c r="O52" s="20"/>
       <c r="P52" s="20"/>
       <c r="Q52" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="W52" s="1">
         <f>4*6</f>
         <v>24</v>
       </c>
       <c r="AD52" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AE52" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="53" spans="5:31">
@@ -19288,10 +19291,10 @@
         <v>29</v>
       </c>
       <c r="AD53" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="AE53" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="54" ht="51" spans="3:31">
@@ -19299,7 +19302,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>29</v>
@@ -19308,7 +19311,7 @@
         <v>40</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H54" s="20"/>
       <c r="I54" s="20"/>
@@ -19320,19 +19323,19 @@
       <c r="O54" s="20"/>
       <c r="P54" s="20"/>
       <c r="Q54" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S54" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AD54" s="1" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AE54" s="1" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="55" spans="5:31">
@@ -19340,10 +19343,10 @@
         <v>29</v>
       </c>
       <c r="AD55" s="1" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="AE55" s="1" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="56" ht="51" spans="3:19">
@@ -19360,7 +19363,7 @@
         <v>60</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H56" s="20"/>
       <c r="I56" s="20"/>
@@ -19372,13 +19375,13 @@
       <c r="O56" s="20"/>
       <c r="P56" s="20"/>
       <c r="Q56" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S56" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="57" spans="5:5">
@@ -19391,7 +19394,7 @@
         <v>35</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>29</v>
@@ -19400,7 +19403,7 @@
         <v>60</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="59" spans="5:19">
@@ -19417,13 +19420,13 @@
       <c r="O59" s="20"/>
       <c r="P59" s="20"/>
       <c r="Q59" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S59" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="60" spans="5:5">
@@ -19436,7 +19439,7 @@
         <v>36</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>29</v>
@@ -19445,7 +19448,7 @@
         <v>60</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="62" spans="5:19">
@@ -19462,13 +19465,13 @@
       <c r="O62" s="20"/>
       <c r="P62" s="20"/>
       <c r="Q62" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="63" spans="5:5">
@@ -19490,7 +19493,7 @@
         <v>60</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H64" s="20"/>
       <c r="I64" s="20"/>
@@ -19502,13 +19505,13 @@
       <c r="O64" s="20"/>
       <c r="P64" s="20"/>
       <c r="Q64" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R64" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S64" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="65" spans="5:5">
@@ -19530,7 +19533,7 @@
         <v>60</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H66" s="20"/>
       <c r="I66" s="20"/>
@@ -19542,13 +19545,13 @@
       <c r="O66" s="20"/>
       <c r="P66" s="20"/>
       <c r="Q66" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S66" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="67" spans="5:5">
@@ -19570,7 +19573,7 @@
         <v>60</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="69" spans="5:19">
@@ -19587,13 +19590,13 @@
       <c r="O69" s="20"/>
       <c r="P69" s="20"/>
       <c r="Q69" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="70" spans="5:5">
@@ -19615,7 +19618,7 @@
         <v>60</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="72" spans="5:19">
@@ -19632,13 +19635,13 @@
       <c r="O72" s="20"/>
       <c r="P72" s="20"/>
       <c r="Q72" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R72" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="73" spans="5:5">
@@ -19651,7 +19654,7 @@
         <v>41</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>84</v>
@@ -19660,7 +19663,7 @@
         <v>60</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H74" s="20"/>
       <c r="I74" s="20"/>
@@ -19672,13 +19675,13 @@
       <c r="O74" s="20"/>
       <c r="P74" s="20"/>
       <c r="Q74" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R74" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="75" spans="5:5">
@@ -19691,7 +19694,7 @@
         <v>42</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>29</v>
@@ -19700,7 +19703,7 @@
         <v>30</v>
       </c>
       <c r="G76" s="19" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H76" s="20"/>
       <c r="I76" s="20"/>
@@ -19712,18 +19715,18 @@
       <c r="O76" s="20"/>
       <c r="P76" s="20"/>
       <c r="Q76" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R76" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="77" spans="5:5">
       <c r="E77" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="78" ht="68" spans="3:28">
@@ -19740,7 +19743,7 @@
         <v>30</v>
       </c>
       <c r="G78" s="21" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H78" s="20"/>
       <c r="I78" s="20"/>
@@ -19752,13 +19755,13 @@
       <c r="O78" s="20"/>
       <c r="P78" s="20"/>
       <c r="Q78" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R78" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="U78" s="10"/>
       <c r="V78" s="26"/>
@@ -19789,7 +19792,7 @@
         <v>40</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="V80" s="26"/>
       <c r="W80" s="26"/>
@@ -19801,7 +19804,7 @@
     </row>
     <row r="81" spans="5:19">
       <c r="E81" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H81" s="20"/>
       <c r="I81" s="20"/>
@@ -19813,18 +19816,18 @@
       <c r="O81" s="20"/>
       <c r="P81" s="20"/>
       <c r="Q81" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S81" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="82" spans="5:5">
       <c r="E82" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="83" ht="34" spans="3:22">
@@ -19841,7 +19844,7 @@
         <v>110</v>
       </c>
       <c r="G83" s="19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="V83" s="26"/>
     </row>
@@ -19873,7 +19876,7 @@
     </row>
     <row r="86" ht="17.6" spans="5:28">
       <c r="E86" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H86" s="20"/>
       <c r="I86" s="20"/>
@@ -19885,13 +19888,13 @@
       <c r="O86" s="20"/>
       <c r="P86" s="20"/>
       <c r="Q86" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S86" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="U86" s="26"/>
       <c r="V86" s="26"/>
@@ -19904,7 +19907,7 @@
     </row>
     <row r="87" ht="17.6" customHeight="1" spans="5:28">
       <c r="E87" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="U87" s="26"/>
       <c r="V87" s="26"/>
@@ -19929,7 +19932,7 @@
         <v>90</v>
       </c>
       <c r="G88" s="19" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="U88" s="26"/>
       <c r="V88" s="26"/>
@@ -19945,13 +19948,13 @@
         <v>84</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="S89" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="V89" s="26"/>
       <c r="W89" s="26"/>
@@ -19974,28 +19977,28 @@
         <v>169</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F91" s="1">
         <v>160</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="92" spans="5:5">
       <c r="E92" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="93" spans="5:5">
       <c r="E93" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="94" spans="5:5">
       <c r="E94" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -20024,16 +20027,16 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
@@ -20043,16 +20046,16 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3"/>
@@ -20073,16 +20076,16 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -20092,16 +20095,16 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AC5" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
@@ -20119,52 +20122,52 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
       <c r="X6" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Y6" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA6" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AC6" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AD6" s="5"/>
       <c r="AE6" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
@@ -20180,52 +20183,52 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
       <c r="X7" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AB7" s="5"/>
       <c r="AC7" s="3" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AD7" s="5"/>
       <c r="AE7" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
@@ -20239,54 +20242,54 @@
     </row>
     <row r="8" ht="45" customHeight="1" spans="8:41">
       <c r="H8" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="3" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Y8" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AA8" s="5"/>
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
@@ -20305,16 +20308,16 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -20324,16 +20327,16 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AC9" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
@@ -20341,13 +20344,13 @@
       <c r="AH9" s="6"/>
       <c r="AI9" s="6"/>
       <c r="AJ9" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
@@ -20360,16 +20363,16 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -20379,16 +20382,16 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AC10" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AD10" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
@@ -20396,13 +20399,13 @@
       <c r="AH10" s="6"/>
       <c r="AI10" s="6"/>
       <c r="AJ10" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AK10" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AL10" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AM10" s="6"/>
       <c r="AN10" s="6"/>
@@ -20415,10 +20418,10 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -20430,10 +20433,10 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
       <c r="AA11" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" s="2"/>
@@ -20443,13 +20446,13 @@
       <c r="AH11" s="6"/>
       <c r="AI11" s="6"/>
       <c r="AJ11" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AM11" s="6"/>
       <c r="AN11" s="6"/>
@@ -20462,10 +20465,10 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -20477,10 +20480,10 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
       <c r="AA12" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AC12" s="2"/>
       <c r="AD12" s="2"/>
@@ -20489,7 +20492,7 @@
     </row>
     <row r="14" spans="13:13">
       <c r="M14" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340" activeTab="5"/>
+    <workbookView windowHeight="15360" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="dish_base" sheetId="1" r:id="rId1"/>
@@ -6377,7 +6377,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L315"/>
+  <dimension ref="A1:L292"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -6540,7 +6540,7 @@
     <row r="5" spans="1:12">
       <c r="A5"/>
       <c r="B5" s="1" t="str">
-        <f t="shared" ref="B5:B12" si="0">C5&amp;D5</f>
+        <f>C5&amp;D5</f>
         <v>arrow_cookie_2</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -6575,7 +6575,7 @@
     <row r="6" spans="1:12">
       <c r="A6"/>
       <c r="B6" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>C6&amp;D6</f>
         <v>arrow_cookie_3</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -6610,7 +6610,7 @@
     <row r="7" spans="1:12">
       <c r="A7"/>
       <c r="B7" s="1" t="str">
-        <f t="shared" si="0"/>
+        <f>C7&amp;D7</f>
         <v>arrow_cookie_4</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -6645,8 +6645,8 @@
     <row r="8" spans="1:12">
       <c r="A8"/>
       <c r="B8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>jellyt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f>C8</f>
+        <v>jelly</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>40</v>
@@ -6682,8 +6682,8 @@
     <row r="9" spans="1:12">
       <c r="A9"/>
       <c r="B9" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>cupcaket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" ref="B9:B72" si="0">C9</f>
+        <v>cupcake</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>43</v>
@@ -6720,7 +6720,7 @@
       <c r="A10"/>
       <c r="B10" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>eggtartt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <v>eggtart</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>47</v>
@@ -6757,7 +6757,7 @@
       <c r="A11"/>
       <c r="B11" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>sugarbeant_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <v>sugarbean</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>50</v>
@@ -6794,7 +6794,7 @@
       <c r="A12"/>
       <c r="B12" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>cheesecaket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <v>cheesecake</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>53</v>
@@ -6830,8 +6830,8 @@
     <row r="13" spans="1:12">
       <c r="A13"/>
       <c r="B13" s="1" t="str">
-        <f t="shared" ref="B13:B44" si="1">C13&amp;D13</f>
-        <v>mousset_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>mousse</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>57</v>
@@ -6867,8 +6867,8 @@
     <row r="14" spans="1:12">
       <c r="A14"/>
       <c r="B14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>fruit_candyt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>fruit_candy</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>61</v>
@@ -6904,8 +6904,8 @@
     <row r="15" spans="1:12">
       <c r="A15"/>
       <c r="B15" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>choco_bart_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>choco_bar</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>66</v>
@@ -6941,8 +6941,8 @@
     <row r="16" spans="1:12">
       <c r="A16"/>
       <c r="B16" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>mochit_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>mochi</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>70</v>
@@ -6978,8 +6978,8 @@
     <row r="17" spans="1:12">
       <c r="A17"/>
       <c r="B17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cup_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>cup_cake</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>73</v>
@@ -7015,8 +7015,8 @@
     <row r="18" spans="1:12">
       <c r="A18"/>
       <c r="B18" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>creamt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>cream</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>76</v>
@@ -7052,8 +7052,8 @@
     <row r="19" spans="1:12">
       <c r="A19"/>
       <c r="B19" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>eggrollt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>eggroll</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>81</v>
@@ -7089,8 +7089,8 @@
     <row r="20" spans="1:12">
       <c r="A20"/>
       <c r="B20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>baguettet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>baguette</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>87</v>
@@ -7126,8 +7126,8 @@
     <row r="21" spans="1:12">
       <c r="A21"/>
       <c r="B21" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>tanghulut_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>tanghulu</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>92</v>
@@ -7163,8 +7163,8 @@
     <row r="22" spans="1:12">
       <c r="A22"/>
       <c r="B22" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cake_slicet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>cake_slice</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>97</v>
@@ -7200,8 +7200,8 @@
     <row r="23" spans="1:12">
       <c r="A23"/>
       <c r="B23" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>long_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>long_cake</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>102</v>
@@ -7237,8 +7237,8 @@
     <row r="24" spans="1:12">
       <c r="A24"/>
       <c r="B24" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>eclairt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>eclair</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>107</v>
@@ -7274,8 +7274,8 @@
     <row r="25" spans="1:12">
       <c r="A25"/>
       <c r="B25" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>gummyt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>gummy</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>113</v>
@@ -7311,8 +7311,8 @@
     <row r="26" spans="1:12">
       <c r="A26"/>
       <c r="B26" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>chocolate_stript_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>chocolate_strip</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>116</v>
@@ -7348,8 +7348,8 @@
     <row r="27" spans="1:12">
       <c r="A27"/>
       <c r="B27" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cake_rollt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>cake_roll</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>119</v>
@@ -7385,8 +7385,8 @@
     <row r="28" spans="1:12">
       <c r="A28"/>
       <c r="B28" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>palmiert_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>palmier</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>122</v>
@@ -7422,8 +7422,8 @@
     <row r="29" spans="1:12">
       <c r="A29"/>
       <c r="B29" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>chiffiont_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>chiffion</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>125</v>
@@ -7459,8 +7459,8 @@
     <row r="30" spans="1:12">
       <c r="A30"/>
       <c r="B30" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>maple_sugart_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>maple_sugar</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>128</v>
@@ -7496,8 +7496,8 @@
     <row r="31" spans="1:12">
       <c r="A31"/>
       <c r="B31" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>taosut_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>taosu</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>131</v>
@@ -7533,8 +7533,8 @@
     <row r="32" spans="1:12">
       <c r="A32"/>
       <c r="B32" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>wafflet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>waffle</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>134</v>
@@ -7570,8 +7570,8 @@
     <row r="33" spans="1:12">
       <c r="A33"/>
       <c r="B33" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>cream_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>cream_cake</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>137</v>
@@ -7607,8 +7607,8 @@
     <row r="34" spans="1:12">
       <c r="A34"/>
       <c r="B34" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>candycanet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>candycane</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>140</v>
@@ -7644,8 +7644,8 @@
     <row r="35" spans="1:12">
       <c r="A35"/>
       <c r="B35" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>black_forest_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>black_forest_cake</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>144</v>
@@ -7681,8 +7681,8 @@
     <row r="36" spans="1:12">
       <c r="A36"/>
       <c r="B36" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>chocolate_saucet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>chocolate_sauce</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>147</v>
@@ -7718,8 +7718,8 @@
     <row r="37" spans="1:12">
       <c r="A37"/>
       <c r="B37" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>mango_sagot_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>mango_sago</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>150</v>
@@ -7755,8 +7755,8 @@
     <row r="38" spans="1:12">
       <c r="A38"/>
       <c r="B38" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>fruit_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>fruit_cake</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>153</v>
@@ -7792,8 +7792,8 @@
     <row r="39" spans="1:12">
       <c r="A39"/>
       <c r="B39" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>parfaitt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>parfait</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>156</v>
@@ -7829,8 +7829,8 @@
     <row r="40" spans="1:12">
       <c r="A40"/>
       <c r="B40" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>marshmallowt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>marshmallow</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>159</v>
@@ -7866,8 +7866,8 @@
     <row r="41" spans="1:12">
       <c r="A41"/>
       <c r="B41" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>big_lollipopt_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>big_lollipop</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>162</v>
@@ -7903,8 +7903,8 @@
     <row r="42" spans="1:12">
       <c r="A42"/>
       <c r="B42" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>apple_piet_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>apple_pie</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>165</v>
@@ -7940,8 +7940,8 @@
     <row r="43" spans="1:12">
       <c r="A43"/>
       <c r="B43" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>double_caket_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</v>
+        <f t="shared" si="0"/>
+        <v>double_cake</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>168</v>
@@ -7976,2416 +7976,1482 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44"/>
-      <c r="B44" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="8"/>
       <c r="I44"/>
       <c r="J44"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45"/>
-      <c r="B45" s="1" t="str">
-        <f t="shared" ref="B45:B108" si="2">C45&amp;D45</f>
-        <v/>
-      </c>
+      <c r="B45" s="1"/>
       <c r="C45" s="8"/>
       <c r="I45"/>
       <c r="J45"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46"/>
-      <c r="B46" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B46" s="1"/>
       <c r="C46" s="8"/>
       <c r="I46"/>
       <c r="J46"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47"/>
-      <c r="B47" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B47" s="1"/>
       <c r="C47" s="8"/>
       <c r="I47"/>
       <c r="J47"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48"/>
-      <c r="B48" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B48" s="1"/>
       <c r="C48" s="8"/>
       <c r="I48"/>
       <c r="J48"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49"/>
-      <c r="B49" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="8"/>
       <c r="I49"/>
       <c r="J49"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50"/>
-      <c r="B50" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B50" s="1"/>
       <c r="C50" s="8"/>
       <c r="I50"/>
       <c r="J50"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51"/>
-      <c r="B51" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="8"/>
       <c r="I51"/>
       <c r="J51"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52"/>
-      <c r="B52" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="8"/>
       <c r="I52"/>
       <c r="J52"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53"/>
-      <c r="B53" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B53" s="1"/>
       <c r="I53"/>
       <c r="J53"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54"/>
-      <c r="B54" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B54" s="1"/>
       <c r="I54"/>
       <c r="J54"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55"/>
-      <c r="B55" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B55" s="1"/>
       <c r="I55"/>
       <c r="J55"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56"/>
-      <c r="B56" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B56" s="1"/>
       <c r="I56"/>
       <c r="J56"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57"/>
-      <c r="B57" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B57" s="1"/>
       <c r="I57"/>
       <c r="J57"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58"/>
-      <c r="B58" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B58" s="1"/>
       <c r="I58"/>
       <c r="J58"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59"/>
-      <c r="B59" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B59" s="1"/>
       <c r="I59"/>
       <c r="J59"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60"/>
-      <c r="B60" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B60" s="1"/>
       <c r="I60"/>
       <c r="J60"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61"/>
-      <c r="B61" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B61" s="1"/>
       <c r="I61"/>
       <c r="J61"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62"/>
-      <c r="B62" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B62" s="1"/>
       <c r="I62"/>
       <c r="J62"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63"/>
-      <c r="B63" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B63" s="1"/>
       <c r="I63"/>
       <c r="J63"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64"/>
-      <c r="B64" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B64" s="1"/>
       <c r="I64"/>
       <c r="J64"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65"/>
-      <c r="B65" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B65" s="1"/>
       <c r="I65"/>
       <c r="J65"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66"/>
-      <c r="B66" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B66" s="1"/>
       <c r="I66"/>
       <c r="J66"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67"/>
-      <c r="B67" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B67" s="1"/>
       <c r="I67"/>
       <c r="J67"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68"/>
-      <c r="B68" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B68" s="1"/>
       <c r="I68"/>
       <c r="J68"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69"/>
-      <c r="B69" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B69" s="1"/>
       <c r="I69"/>
       <c r="J69"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70"/>
-      <c r="B70" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B70" s="1"/>
       <c r="I70"/>
       <c r="J70"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71"/>
-      <c r="B71" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B71" s="1"/>
       <c r="I71"/>
       <c r="J71"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72"/>
-      <c r="B72" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B72" s="1"/>
       <c r="I72"/>
       <c r="J72"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73"/>
-      <c r="B73" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B73" s="1"/>
       <c r="I73"/>
       <c r="J73"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74"/>
-      <c r="B74" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B74" s="1"/>
       <c r="I74"/>
       <c r="J74"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75"/>
-      <c r="B75" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B75" s="1"/>
       <c r="I75"/>
       <c r="J75"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76"/>
-      <c r="B76" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B76" s="1"/>
       <c r="C76" s="8"/>
       <c r="I76"/>
       <c r="J76"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77"/>
-      <c r="B77" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B77" s="1"/>
       <c r="C77" s="8"/>
       <c r="I77"/>
       <c r="J77"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78"/>
-      <c r="B78" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B78" s="1"/>
       <c r="C78" s="8"/>
       <c r="I78"/>
       <c r="J78"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79"/>
-      <c r="B79" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B79" s="1"/>
       <c r="C79" s="8"/>
       <c r="I79"/>
       <c r="J79"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80"/>
-      <c r="B80" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B80" s="1"/>
       <c r="C80" s="8"/>
       <c r="I80"/>
       <c r="J80"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81"/>
-      <c r="B81" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B81" s="1"/>
       <c r="C81" s="8"/>
       <c r="I81"/>
       <c r="J81"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82"/>
-      <c r="B82" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B82" s="1"/>
       <c r="C82" s="8"/>
       <c r="I82"/>
       <c r="J82"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83"/>
-      <c r="B83" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B83" s="1"/>
       <c r="C83" s="8"/>
       <c r="I83"/>
       <c r="J83"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84"/>
-      <c r="B84" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B84" s="1"/>
       <c r="C84" s="8"/>
       <c r="I84"/>
       <c r="J84"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85"/>
-      <c r="B85" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B85" s="1"/>
       <c r="C85" s="8"/>
       <c r="I85"/>
       <c r="J85"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86"/>
-      <c r="B86" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B86" s="1"/>
       <c r="C86" s="8"/>
       <c r="I86"/>
       <c r="J86"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87"/>
-      <c r="B87" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B87" s="1"/>
       <c r="C87" s="8"/>
       <c r="I87"/>
       <c r="J87"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88"/>
-      <c r="B88" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B88" s="1"/>
       <c r="C88" s="8"/>
       <c r="I88"/>
       <c r="J88"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89"/>
-      <c r="B89" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B89" s="1"/>
       <c r="C89" s="8"/>
       <c r="I89"/>
       <c r="J89"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90"/>
-      <c r="B90" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B90" s="1"/>
       <c r="C90" s="8"/>
       <c r="I90"/>
       <c r="J90"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91"/>
-      <c r="B91" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B91" s="1"/>
       <c r="C91" s="8"/>
       <c r="I91"/>
       <c r="J91"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92"/>
-      <c r="B92" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B92" s="1"/>
       <c r="C92" s="8"/>
       <c r="I92"/>
       <c r="J92"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93"/>
-      <c r="B93" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B93" s="1"/>
       <c r="C93" s="8"/>
       <c r="I93"/>
       <c r="J93"/>
     </row>
     <row r="94" spans="1:10">
       <c r="A94"/>
-      <c r="B94" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B94" s="1"/>
       <c r="C94" s="8"/>
       <c r="I94"/>
       <c r="J94"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95"/>
-      <c r="B95" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B95" s="1"/>
       <c r="C95" s="8"/>
       <c r="I95"/>
       <c r="J95"/>
     </row>
     <row r="96" spans="1:10">
       <c r="A96"/>
-      <c r="B96" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B96" s="1"/>
       <c r="C96" s="8"/>
       <c r="I96"/>
       <c r="J96"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97"/>
-      <c r="B97" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B97" s="1"/>
       <c r="C97" s="8"/>
       <c r="I97"/>
       <c r="J97"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98"/>
-      <c r="B98" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B98" s="1"/>
       <c r="C98" s="8"/>
       <c r="I98"/>
       <c r="J98"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99"/>
-      <c r="B99" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B99" s="1"/>
       <c r="C99" s="8"/>
       <c r="I99"/>
       <c r="J99"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100"/>
-      <c r="B100" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B100" s="1"/>
       <c r="C100" s="8"/>
       <c r="I100"/>
       <c r="J100"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101"/>
-      <c r="B101" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B101" s="1"/>
       <c r="I101"/>
       <c r="J101"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102"/>
-      <c r="B102" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B102" s="1"/>
       <c r="I102"/>
       <c r="J102"/>
     </row>
     <row r="103" spans="1:10">
       <c r="A103"/>
-      <c r="B103" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B103" s="1"/>
       <c r="I103"/>
       <c r="J103"/>
     </row>
     <row r="104" spans="1:10">
       <c r="A104"/>
-      <c r="B104" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B104" s="1"/>
       <c r="I104"/>
       <c r="J104"/>
     </row>
     <row r="105" spans="1:10">
       <c r="A105"/>
-      <c r="B105" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B105" s="1"/>
       <c r="I105"/>
       <c r="J105"/>
     </row>
     <row r="106" spans="1:10">
       <c r="A106"/>
-      <c r="B106" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B106" s="1"/>
       <c r="I106"/>
       <c r="J106"/>
     </row>
     <row r="107" spans="1:10">
       <c r="A107"/>
-      <c r="B107" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B107" s="1"/>
       <c r="I107"/>
       <c r="J107"/>
     </row>
     <row r="108" spans="1:10">
       <c r="A108"/>
-      <c r="B108" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
+      <c r="B108" s="1"/>
       <c r="I108"/>
       <c r="J108"/>
     </row>
     <row r="109" spans="1:10">
       <c r="A109"/>
-      <c r="B109" s="1" t="str">
-        <f t="shared" ref="B109:B173" si="3">C109&amp;D109</f>
-        <v/>
-      </c>
+      <c r="B109" s="1"/>
       <c r="I109"/>
       <c r="J109"/>
     </row>
     <row r="110" spans="1:10">
       <c r="A110"/>
-      <c r="B110" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B110" s="1"/>
       <c r="I110"/>
       <c r="J110"/>
     </row>
     <row r="111" spans="1:10">
       <c r="A111"/>
-      <c r="B111" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B111" s="1"/>
       <c r="I111"/>
       <c r="J111"/>
     </row>
     <row r="112" spans="1:10">
       <c r="A112"/>
-      <c r="B112" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B112" s="1"/>
       <c r="I112"/>
       <c r="J112"/>
     </row>
     <row r="113" spans="1:10">
       <c r="A113"/>
-      <c r="B113" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B113" s="1"/>
       <c r="I113"/>
       <c r="J113"/>
     </row>
     <row r="114" spans="1:10">
       <c r="A114"/>
-      <c r="B114" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B114" s="1"/>
       <c r="I114"/>
       <c r="J114"/>
     </row>
     <row r="115" spans="1:10">
       <c r="A115"/>
-      <c r="B115" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B115" s="1"/>
       <c r="I115"/>
       <c r="J115"/>
     </row>
     <row r="116" spans="1:10">
       <c r="A116"/>
-      <c r="B116" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B116" s="1"/>
       <c r="I116"/>
       <c r="J116"/>
     </row>
     <row r="117" spans="1:10">
       <c r="A117"/>
-      <c r="B117" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B117" s="1"/>
       <c r="I117"/>
       <c r="J117"/>
     </row>
     <row r="118" spans="1:10">
       <c r="A118"/>
-      <c r="B118" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B118" s="1"/>
       <c r="I118"/>
       <c r="J118"/>
     </row>
     <row r="119" spans="1:10">
       <c r="A119"/>
-      <c r="B119" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B119" s="1"/>
       <c r="I119"/>
       <c r="J119"/>
     </row>
     <row r="120" spans="1:10">
       <c r="A120"/>
-      <c r="B120" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B120" s="1"/>
       <c r="I120"/>
       <c r="J120"/>
     </row>
     <row r="121" spans="1:10">
       <c r="A121"/>
-      <c r="B121" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B121" s="1"/>
       <c r="I121"/>
       <c r="J121"/>
     </row>
     <row r="122" spans="1:10">
       <c r="A122"/>
-      <c r="B122" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B122" s="1"/>
       <c r="I122"/>
       <c r="J122"/>
     </row>
     <row r="123" spans="1:10">
       <c r="A123"/>
-      <c r="B123" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B123" s="1"/>
       <c r="I123"/>
       <c r="J123"/>
     </row>
     <row r="124" spans="1:10">
       <c r="A124"/>
-      <c r="B124" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B124" s="1"/>
       <c r="C124" s="8"/>
       <c r="I124"/>
       <c r="J124"/>
     </row>
     <row r="125" spans="1:10">
       <c r="A125"/>
-      <c r="B125" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B125" s="1"/>
       <c r="C125" s="8"/>
       <c r="I125"/>
       <c r="J125"/>
     </row>
     <row r="126" spans="1:10">
       <c r="A126"/>
-      <c r="B126" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B126" s="1"/>
       <c r="C126" s="8"/>
       <c r="I126"/>
       <c r="J126"/>
     </row>
     <row r="127" spans="1:10">
       <c r="A127"/>
-      <c r="B127" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B127" s="1"/>
       <c r="C127" s="8"/>
       <c r="I127"/>
       <c r="J127"/>
     </row>
     <row r="128" spans="1:10">
       <c r="A128"/>
-      <c r="B128" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B128" s="1"/>
       <c r="C128" s="8"/>
       <c r="I128"/>
       <c r="J128"/>
     </row>
     <row r="129" spans="1:10">
       <c r="A129"/>
-      <c r="B129" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B129" s="1"/>
       <c r="C129" s="8"/>
       <c r="I129"/>
       <c r="J129"/>
     </row>
     <row r="130" spans="1:10">
       <c r="A130"/>
-      <c r="B130" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B130" s="1"/>
       <c r="C130" s="8"/>
       <c r="I130"/>
       <c r="J130"/>
     </row>
     <row r="131" spans="1:10">
       <c r="A131"/>
-      <c r="B131" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B131" s="1"/>
       <c r="C131" s="8"/>
       <c r="I131"/>
       <c r="J131"/>
     </row>
     <row r="132" spans="1:10">
       <c r="A132"/>
-      <c r="B132" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B132" s="1"/>
       <c r="C132" s="8"/>
       <c r="I132"/>
       <c r="J132"/>
     </row>
     <row r="133" spans="1:10">
       <c r="A133"/>
-      <c r="B133" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B133" s="1"/>
       <c r="C133" s="8"/>
       <c r="I133"/>
       <c r="J133"/>
     </row>
     <row r="134" spans="1:10">
       <c r="A134"/>
-      <c r="B134" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B134" s="1"/>
       <c r="C134" s="8"/>
       <c r="I134"/>
       <c r="J134"/>
     </row>
     <row r="135" spans="1:10">
       <c r="A135"/>
-      <c r="B135" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B135" s="1"/>
       <c r="C135" s="8"/>
       <c r="I135"/>
       <c r="J135"/>
     </row>
     <row r="136" spans="1:10">
       <c r="A136"/>
-      <c r="B136" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B136" s="1"/>
       <c r="C136" s="8"/>
       <c r="I136"/>
       <c r="J136"/>
     </row>
     <row r="137" spans="1:10">
       <c r="A137"/>
-      <c r="B137" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B137" s="1"/>
       <c r="C137" s="8"/>
       <c r="I137"/>
       <c r="J137"/>
     </row>
     <row r="138" spans="1:10">
       <c r="A138"/>
-      <c r="B138" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B138" s="1"/>
       <c r="C138" s="8"/>
       <c r="I138"/>
       <c r="J138"/>
     </row>
     <row r="139" spans="1:10">
       <c r="A139"/>
-      <c r="B139" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B139" s="1"/>
       <c r="C139" s="8"/>
       <c r="I139"/>
       <c r="J139"/>
     </row>
     <row r="140" spans="1:10">
       <c r="A140"/>
-      <c r="B140" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B140" s="1"/>
       <c r="C140" s="8"/>
       <c r="I140"/>
       <c r="J140"/>
     </row>
     <row r="141" spans="1:10">
       <c r="A141"/>
-      <c r="B141" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B141" s="1"/>
       <c r="C141" s="8"/>
       <c r="I141"/>
       <c r="J141"/>
     </row>
     <row r="142" spans="1:10">
       <c r="A142"/>
-      <c r="B142" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B142" s="1"/>
       <c r="C142" s="8"/>
       <c r="I142"/>
       <c r="J142"/>
     </row>
     <row r="143" spans="1:10">
       <c r="A143"/>
-      <c r="B143" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B143" s="1"/>
       <c r="C143" s="8"/>
       <c r="I143"/>
       <c r="J143"/>
     </row>
     <row r="144" spans="1:10">
       <c r="A144"/>
-      <c r="B144" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B144" s="1"/>
       <c r="C144" s="8"/>
       <c r="I144"/>
       <c r="J144"/>
     </row>
     <row r="145" spans="1:10">
       <c r="A145"/>
-      <c r="B145" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B145" s="1"/>
       <c r="C145" s="8"/>
       <c r="I145"/>
       <c r="J145"/>
     </row>
     <row r="146" spans="1:10">
       <c r="A146"/>
-      <c r="B146" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B146" s="1"/>
       <c r="C146" s="8"/>
       <c r="I146"/>
       <c r="J146"/>
     </row>
     <row r="147" spans="1:10">
       <c r="A147"/>
-      <c r="B147" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B147" s="1"/>
       <c r="C147" s="8"/>
       <c r="I147"/>
       <c r="J147"/>
     </row>
     <row r="148" spans="1:10">
       <c r="A148"/>
-      <c r="B148" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B148" s="1"/>
       <c r="C148" s="8"/>
       <c r="I148"/>
       <c r="J148"/>
     </row>
     <row r="149" spans="1:10">
       <c r="A149"/>
-      <c r="B149" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B149" s="1"/>
       <c r="I149"/>
       <c r="J149"/>
     </row>
     <row r="150" spans="1:10">
       <c r="A150"/>
-      <c r="B150" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B150" s="1"/>
       <c r="I150"/>
       <c r="J150"/>
     </row>
     <row r="151" spans="1:10">
       <c r="A151"/>
-      <c r="B151" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B151" s="1"/>
       <c r="I151"/>
       <c r="J151"/>
     </row>
     <row r="152" spans="1:10">
       <c r="A152"/>
-      <c r="B152" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B152" s="1"/>
       <c r="I152"/>
       <c r="J152"/>
     </row>
     <row r="153" spans="1:10">
       <c r="A153"/>
-      <c r="B153" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B153" s="1"/>
       <c r="I153"/>
       <c r="J153"/>
     </row>
     <row r="154" spans="1:10">
       <c r="A154"/>
-      <c r="B154" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B154" s="1"/>
       <c r="I154"/>
       <c r="J154"/>
     </row>
     <row r="155" spans="1:10">
       <c r="A155"/>
-      <c r="B155" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B155" s="1"/>
       <c r="I155"/>
       <c r="J155"/>
     </row>
     <row r="156" spans="1:10">
       <c r="A156"/>
-      <c r="B156" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B156" s="1"/>
       <c r="I156"/>
       <c r="J156"/>
     </row>
     <row r="157" spans="1:10">
       <c r="A157"/>
-      <c r="B157" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B157" s="1"/>
       <c r="I157"/>
       <c r="J157"/>
     </row>
     <row r="158" spans="1:10">
       <c r="A158"/>
-      <c r="B158" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B158" s="1"/>
       <c r="I158"/>
       <c r="J158"/>
     </row>
     <row r="159" spans="1:10">
       <c r="A159"/>
-      <c r="B159" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B159" s="1"/>
       <c r="I159"/>
       <c r="J159"/>
     </row>
     <row r="160" spans="1:10">
       <c r="A160"/>
-      <c r="B160" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B160" s="1"/>
       <c r="I160"/>
       <c r="J160"/>
     </row>
     <row r="161" spans="1:10">
       <c r="A161"/>
-      <c r="B161" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B161" s="1"/>
       <c r="I161"/>
       <c r="J161"/>
     </row>
     <row r="162" spans="1:10">
       <c r="A162"/>
-      <c r="B162" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B162" s="1"/>
       <c r="I162"/>
       <c r="J162"/>
     </row>
     <row r="163" spans="1:10">
       <c r="A163"/>
-      <c r="B163" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B163" s="1"/>
       <c r="I163"/>
       <c r="J163"/>
     </row>
     <row r="164" spans="1:10">
       <c r="A164"/>
-      <c r="B164" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B164" s="1"/>
       <c r="I164"/>
       <c r="J164"/>
     </row>
     <row r="165" spans="1:10">
       <c r="A165"/>
-      <c r="B165" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B165" s="1"/>
       <c r="I165"/>
       <c r="J165"/>
     </row>
     <row r="166" spans="1:10">
       <c r="A166"/>
-      <c r="B166" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B166" s="1"/>
       <c r="I166"/>
       <c r="J166"/>
     </row>
     <row r="167" spans="1:10">
       <c r="A167"/>
-      <c r="B167" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B167" s="1"/>
       <c r="I167"/>
       <c r="J167"/>
     </row>
     <row r="168" spans="1:10">
       <c r="A168"/>
-      <c r="B168" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B168" s="1"/>
       <c r="I168"/>
       <c r="J168"/>
     </row>
     <row r="169" spans="1:10">
       <c r="A169"/>
-      <c r="B169" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B169" s="1"/>
       <c r="I169"/>
       <c r="J169"/>
     </row>
     <row r="170" spans="1:10">
       <c r="A170"/>
-      <c r="B170" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B170" s="1"/>
       <c r="I170"/>
       <c r="J170"/>
     </row>
     <row r="171" spans="1:10">
       <c r="A171"/>
-      <c r="B171" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B171" s="1"/>
       <c r="I171"/>
       <c r="J171"/>
     </row>
     <row r="172" spans="1:10">
       <c r="A172"/>
-      <c r="B172" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B172" s="1"/>
       <c r="C172" s="8"/>
       <c r="I172"/>
       <c r="J172"/>
     </row>
     <row r="173" spans="1:10">
       <c r="A173"/>
-      <c r="B173" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
+      <c r="B173" s="1"/>
       <c r="C173" s="8"/>
       <c r="I173"/>
       <c r="J173"/>
     </row>
     <row r="174" spans="1:10">
       <c r="A174"/>
-      <c r="B174" s="1" t="str">
-        <f t="shared" ref="B174:B237" si="4">C174&amp;D174</f>
-        <v/>
-      </c>
+      <c r="B174" s="1"/>
       <c r="C174" s="8"/>
       <c r="I174"/>
       <c r="J174"/>
     </row>
     <row r="175" spans="1:10">
       <c r="A175"/>
-      <c r="B175" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B175" s="1"/>
       <c r="C175" s="8"/>
       <c r="I175"/>
       <c r="J175"/>
     </row>
     <row r="176" spans="1:10">
       <c r="A176"/>
-      <c r="B176" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B176" s="1"/>
       <c r="C176" s="8"/>
       <c r="I176"/>
       <c r="J176"/>
     </row>
     <row r="177" spans="1:10">
       <c r="A177"/>
-      <c r="B177" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B177" s="1"/>
       <c r="C177" s="8"/>
       <c r="I177"/>
       <c r="J177"/>
     </row>
     <row r="178" spans="1:10">
       <c r="A178"/>
-      <c r="B178" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B178" s="1"/>
       <c r="C178" s="8"/>
       <c r="I178"/>
       <c r="J178"/>
     </row>
     <row r="179" spans="1:10">
       <c r="A179"/>
-      <c r="B179" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B179" s="1"/>
       <c r="C179" s="8"/>
       <c r="I179"/>
       <c r="J179"/>
     </row>
     <row r="180" spans="1:10">
       <c r="A180"/>
-      <c r="B180" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B180" s="1"/>
       <c r="C180" s="8"/>
       <c r="I180"/>
       <c r="J180"/>
     </row>
     <row r="181" spans="1:10">
       <c r="A181"/>
-      <c r="B181" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B181" s="1"/>
       <c r="C181" s="8"/>
       <c r="I181"/>
       <c r="J181"/>
     </row>
     <row r="182" spans="1:10">
       <c r="A182"/>
-      <c r="B182" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B182" s="1"/>
       <c r="C182" s="8"/>
       <c r="I182"/>
       <c r="J182"/>
     </row>
     <row r="183" spans="1:10">
       <c r="A183"/>
-      <c r="B183" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B183" s="1"/>
       <c r="C183" s="8"/>
       <c r="I183"/>
       <c r="J183"/>
     </row>
     <row r="184" spans="1:10">
       <c r="A184"/>
-      <c r="B184" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B184" s="1"/>
       <c r="C184" s="8"/>
       <c r="I184"/>
       <c r="J184"/>
     </row>
     <row r="185" spans="1:10">
       <c r="A185"/>
-      <c r="B185" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B185" s="1"/>
       <c r="C185" s="8"/>
       <c r="I185"/>
       <c r="J185"/>
     </row>
     <row r="186" spans="1:10">
       <c r="A186"/>
-      <c r="B186" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B186" s="1"/>
       <c r="C186" s="8"/>
       <c r="I186"/>
       <c r="J186"/>
     </row>
     <row r="187" spans="1:10">
       <c r="A187"/>
-      <c r="B187" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B187" s="1"/>
       <c r="C187" s="8"/>
       <c r="I187"/>
       <c r="J187"/>
     </row>
     <row r="188" spans="1:10">
       <c r="A188"/>
-      <c r="B188" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B188" s="1"/>
       <c r="C188" s="8"/>
       <c r="I188"/>
       <c r="J188"/>
     </row>
     <row r="189" spans="1:10">
       <c r="A189"/>
-      <c r="B189" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B189" s="1"/>
       <c r="C189" s="8"/>
       <c r="I189"/>
       <c r="J189"/>
     </row>
     <row r="190" spans="1:10">
       <c r="A190"/>
-      <c r="B190" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B190" s="1"/>
       <c r="C190" s="8"/>
       <c r="I190"/>
       <c r="J190"/>
     </row>
     <row r="191" spans="1:10">
       <c r="A191"/>
-      <c r="B191" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B191" s="1"/>
       <c r="C191" s="8"/>
       <c r="I191"/>
       <c r="J191"/>
     </row>
     <row r="192" spans="1:10">
       <c r="A192"/>
-      <c r="B192" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B192" s="1"/>
       <c r="C192" s="8"/>
       <c r="I192"/>
       <c r="J192"/>
     </row>
     <row r="193" spans="1:10">
       <c r="A193"/>
-      <c r="B193" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B193" s="1"/>
       <c r="C193" s="8"/>
       <c r="I193"/>
       <c r="J193"/>
     </row>
     <row r="194" spans="1:10">
       <c r="A194"/>
-      <c r="B194" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B194" s="1"/>
       <c r="C194" s="8"/>
       <c r="I194"/>
       <c r="J194"/>
     </row>
     <row r="195" spans="1:10">
       <c r="A195"/>
-      <c r="B195" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B195" s="1"/>
       <c r="C195" s="8"/>
       <c r="I195"/>
       <c r="J195"/>
     </row>
     <row r="196" spans="1:10">
       <c r="A196"/>
-      <c r="B196" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B196" s="1"/>
       <c r="C196" s="8"/>
       <c r="I196"/>
       <c r="J196"/>
     </row>
     <row r="197" spans="1:10">
       <c r="A197"/>
-      <c r="B197" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B197" s="1"/>
       <c r="I197"/>
       <c r="J197"/>
     </row>
     <row r="198" spans="1:10">
       <c r="A198"/>
-      <c r="B198" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B198" s="1"/>
       <c r="I198"/>
       <c r="J198"/>
     </row>
     <row r="199" spans="1:10">
       <c r="A199"/>
-      <c r="B199" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B199" s="1"/>
       <c r="I199"/>
       <c r="J199"/>
     </row>
     <row r="200" spans="1:10">
       <c r="A200"/>
-      <c r="B200" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B200" s="1"/>
       <c r="I200"/>
       <c r="J200"/>
     </row>
     <row r="201" spans="1:10">
       <c r="A201"/>
-      <c r="B201" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B201" s="1"/>
       <c r="I201"/>
       <c r="J201"/>
     </row>
     <row r="202" spans="1:10">
       <c r="A202"/>
-      <c r="B202" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B202" s="1"/>
       <c r="I202"/>
       <c r="J202"/>
     </row>
     <row r="203" spans="1:10">
       <c r="A203"/>
-      <c r="B203" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B203" s="1"/>
       <c r="I203"/>
       <c r="J203"/>
     </row>
     <row r="204" spans="1:10">
       <c r="A204"/>
-      <c r="B204" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B204" s="1"/>
       <c r="I204"/>
       <c r="J204"/>
     </row>
     <row r="205" spans="1:10">
       <c r="A205"/>
-      <c r="B205" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B205" s="1"/>
       <c r="I205"/>
       <c r="J205"/>
     </row>
     <row r="206" spans="1:10">
       <c r="A206"/>
-      <c r="B206" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B206" s="1"/>
       <c r="I206"/>
       <c r="J206"/>
     </row>
     <row r="207" spans="1:10">
       <c r="A207"/>
-      <c r="B207" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B207" s="1"/>
       <c r="I207"/>
       <c r="J207"/>
     </row>
     <row r="208" spans="1:10">
       <c r="A208"/>
-      <c r="B208" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B208" s="1"/>
       <c r="I208"/>
       <c r="J208"/>
     </row>
     <row r="209" spans="1:10">
       <c r="A209"/>
-      <c r="B209" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B209" s="1"/>
       <c r="I209"/>
       <c r="J209"/>
     </row>
     <row r="210" spans="1:10">
       <c r="A210"/>
-      <c r="B210" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B210" s="1"/>
       <c r="I210"/>
       <c r="J210"/>
     </row>
     <row r="211" spans="1:10">
       <c r="A211"/>
-      <c r="B211" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B211" s="1"/>
       <c r="I211"/>
       <c r="J211"/>
     </row>
     <row r="212" spans="1:10">
       <c r="A212"/>
-      <c r="B212" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B212" s="1"/>
       <c r="I212"/>
       <c r="J212"/>
     </row>
     <row r="213" spans="1:10">
       <c r="A213"/>
-      <c r="B213" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B213" s="1"/>
       <c r="I213"/>
       <c r="J213"/>
     </row>
     <row r="214" spans="1:10">
       <c r="A214"/>
-      <c r="B214" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B214" s="1"/>
       <c r="I214"/>
       <c r="J214"/>
     </row>
     <row r="215" spans="1:10">
       <c r="A215"/>
-      <c r="B215" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B215" s="1"/>
       <c r="I215"/>
       <c r="J215"/>
     </row>
     <row r="216" spans="1:10">
       <c r="A216"/>
-      <c r="B216" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B216" s="1"/>
       <c r="I216"/>
       <c r="J216"/>
     </row>
     <row r="217" spans="1:10">
       <c r="A217"/>
-      <c r="B217" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B217" s="1"/>
       <c r="I217"/>
       <c r="J217"/>
     </row>
     <row r="218" spans="1:9">
       <c r="A218"/>
-      <c r="B218" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B218" s="1"/>
       <c r="I218"/>
     </row>
     <row r="219" spans="1:10">
       <c r="A219"/>
-      <c r="B219" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B219" s="1"/>
       <c r="I219"/>
       <c r="J219"/>
     </row>
     <row r="220" spans="1:10">
       <c r="A220"/>
-      <c r="B220" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B220" s="1"/>
       <c r="C220" s="8"/>
       <c r="I220"/>
       <c r="J220"/>
     </row>
     <row r="221" spans="1:10">
       <c r="A221"/>
-      <c r="B221" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B221" s="1"/>
       <c r="C221" s="8"/>
       <c r="I221"/>
       <c r="J221"/>
     </row>
     <row r="222" spans="1:10">
       <c r="A222"/>
-      <c r="B222" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B222" s="1"/>
       <c r="C222" s="8"/>
       <c r="I222"/>
       <c r="J222"/>
     </row>
     <row r="223" spans="1:10">
       <c r="A223"/>
-      <c r="B223" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B223" s="1"/>
       <c r="C223" s="8"/>
       <c r="I223"/>
       <c r="J223"/>
     </row>
     <row r="224" spans="1:10">
       <c r="A224"/>
-      <c r="B224" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B224" s="1"/>
       <c r="C224" s="8"/>
       <c r="I224"/>
       <c r="J224"/>
     </row>
     <row r="225" spans="1:10">
       <c r="A225"/>
-      <c r="B225" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B225" s="1"/>
       <c r="C225" s="8"/>
       <c r="I225"/>
       <c r="J225"/>
     </row>
     <row r="226" spans="1:10">
       <c r="A226"/>
-      <c r="B226" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B226" s="1"/>
       <c r="C226" s="8"/>
       <c r="I226"/>
       <c r="J226"/>
     </row>
     <row r="227" spans="1:10">
       <c r="A227"/>
-      <c r="B227" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B227" s="1"/>
       <c r="C227" s="8"/>
       <c r="I227"/>
       <c r="J227"/>
     </row>
     <row r="228" spans="1:10">
       <c r="A228"/>
-      <c r="B228" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B228" s="1"/>
       <c r="C228" s="8"/>
       <c r="I228"/>
       <c r="J228"/>
     </row>
     <row r="229" spans="1:10">
       <c r="A229"/>
-      <c r="B229" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B229" s="1"/>
       <c r="C229" s="8"/>
       <c r="I229"/>
       <c r="J229"/>
     </row>
     <row r="230" spans="1:10">
       <c r="A230"/>
-      <c r="B230" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B230" s="1"/>
       <c r="C230" s="8"/>
       <c r="I230"/>
       <c r="J230"/>
     </row>
     <row r="231" spans="1:10">
       <c r="A231"/>
-      <c r="B231" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B231" s="1"/>
       <c r="C231" s="8"/>
       <c r="I231"/>
       <c r="J231"/>
     </row>
     <row r="232" spans="1:10">
       <c r="A232"/>
-      <c r="B232" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B232" s="1"/>
       <c r="C232" s="8"/>
       <c r="I232"/>
       <c r="J232"/>
     </row>
     <row r="233" spans="1:10">
       <c r="A233"/>
-      <c r="B233" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B233" s="1"/>
       <c r="C233" s="8"/>
       <c r="I233"/>
       <c r="J233"/>
     </row>
     <row r="234" spans="1:10">
       <c r="A234"/>
-      <c r="B234" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B234" s="1"/>
       <c r="C234" s="8"/>
       <c r="I234"/>
       <c r="J234"/>
     </row>
     <row r="235" spans="1:10">
       <c r="A235"/>
-      <c r="B235" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B235" s="1"/>
       <c r="C235" s="8"/>
       <c r="I235"/>
       <c r="J235"/>
     </row>
     <row r="236" spans="1:10">
       <c r="A236"/>
-      <c r="B236" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B236" s="1"/>
       <c r="C236" s="8"/>
       <c r="I236"/>
       <c r="J236"/>
     </row>
     <row r="237" spans="1:10">
       <c r="A237"/>
-      <c r="B237" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
+      <c r="B237" s="1"/>
       <c r="C237" s="8"/>
       <c r="I237"/>
       <c r="J237"/>
     </row>
     <row r="238" spans="1:10">
       <c r="A238"/>
-      <c r="B238" s="1" t="str">
-        <f t="shared" ref="B238:B301" si="5">C238&amp;D238</f>
-        <v/>
-      </c>
+      <c r="B238" s="1"/>
       <c r="C238" s="8"/>
       <c r="I238"/>
       <c r="J238"/>
     </row>
     <row r="239" spans="1:10">
       <c r="A239"/>
-      <c r="B239" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B239" s="1"/>
       <c r="C239" s="8"/>
       <c r="I239"/>
       <c r="J239"/>
     </row>
     <row r="240" spans="1:10">
       <c r="A240"/>
-      <c r="B240" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B240" s="1"/>
       <c r="C240" s="8"/>
       <c r="I240"/>
       <c r="J240"/>
     </row>
     <row r="241" spans="1:10">
       <c r="A241"/>
-      <c r="B241" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B241" s="1"/>
       <c r="C241" s="8"/>
       <c r="I241"/>
       <c r="J241"/>
     </row>
     <row r="242" spans="1:10">
       <c r="A242"/>
-      <c r="B242" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B242" s="1"/>
       <c r="C242" s="8"/>
       <c r="I242"/>
       <c r="J242"/>
     </row>
     <row r="243" spans="1:10">
       <c r="A243"/>
-      <c r="B243" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B243" s="1"/>
       <c r="C243" s="8"/>
       <c r="I243"/>
       <c r="J243"/>
     </row>
     <row r="244" spans="1:10">
       <c r="A244"/>
-      <c r="B244" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B244" s="1"/>
       <c r="C244" s="8"/>
       <c r="I244"/>
       <c r="J244"/>
     </row>
     <row r="245" spans="1:10">
       <c r="A245"/>
-      <c r="B245" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B245" s="1"/>
       <c r="I245"/>
       <c r="J245"/>
     </row>
     <row r="246" spans="1:10">
       <c r="A246"/>
-      <c r="B246" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B246" s="1"/>
       <c r="I246"/>
       <c r="J246"/>
     </row>
     <row r="247" spans="1:10">
       <c r="A247"/>
-      <c r="B247" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B247" s="1"/>
       <c r="I247"/>
       <c r="J247"/>
     </row>
     <row r="248" spans="1:10">
       <c r="A248"/>
-      <c r="B248" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B248" s="1"/>
       <c r="I248"/>
       <c r="J248"/>
     </row>
     <row r="249" spans="1:10">
       <c r="A249"/>
-      <c r="B249" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B249" s="1"/>
       <c r="I249"/>
       <c r="J249"/>
     </row>
     <row r="250" spans="1:10">
       <c r="A250"/>
-      <c r="B250" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B250" s="1"/>
       <c r="I250"/>
       <c r="J250"/>
     </row>
     <row r="251" spans="1:10">
       <c r="A251"/>
-      <c r="B251" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B251" s="1"/>
       <c r="I251"/>
       <c r="J251"/>
     </row>
     <row r="252" spans="1:10">
       <c r="A252"/>
-      <c r="B252" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B252" s="1"/>
       <c r="I252"/>
       <c r="J252"/>
     </row>
     <row r="253" spans="1:10">
       <c r="A253"/>
-      <c r="B253" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B253" s="1"/>
       <c r="I253"/>
       <c r="J253"/>
     </row>
     <row r="254" spans="1:10">
       <c r="A254"/>
-      <c r="B254" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B254" s="1"/>
       <c r="I254"/>
       <c r="J254"/>
     </row>
     <row r="255" spans="1:10">
       <c r="A255"/>
-      <c r="B255" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B255" s="1"/>
       <c r="I255"/>
       <c r="J255"/>
     </row>
     <row r="256" spans="1:10">
       <c r="A256"/>
-      <c r="B256" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B256" s="1"/>
       <c r="I256"/>
       <c r="J256"/>
     </row>
     <row r="257" spans="1:10">
       <c r="A257"/>
-      <c r="B257" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B257" s="1"/>
       <c r="I257"/>
       <c r="J257"/>
     </row>
     <row r="258" spans="1:10">
       <c r="A258"/>
-      <c r="B258" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B258" s="1"/>
       <c r="I258"/>
       <c r="J258"/>
     </row>
     <row r="259" spans="1:10">
       <c r="A259"/>
-      <c r="B259" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+      <c r="B259" s="1"/>
       <c r="I259"/>
       <c r="J259"/>
     </row>
-    <row r="260" spans="2:2">
-      <c r="B260" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="2:2">
-      <c r="B261" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="2:2">
-      <c r="B262" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="2:2">
-      <c r="B263" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="2:2">
-      <c r="B264" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="2:2">
-      <c r="B265" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="2:2">
-      <c r="B266" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="2:2">
-      <c r="B267" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="2:3">
-      <c r="B268" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="268" spans="3:3">
       <c r="C268" s="8"/>
     </row>
-    <row r="269" spans="2:3">
-      <c r="B269" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="269" spans="3:3">
       <c r="C269" s="8"/>
     </row>
-    <row r="270" spans="2:3">
-      <c r="B270" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="270" spans="3:3">
       <c r="C270" s="8"/>
     </row>
-    <row r="271" spans="2:3">
-      <c r="B271" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="271" spans="3:3">
       <c r="C271" s="8"/>
     </row>
-    <row r="272" spans="2:3">
-      <c r="B272" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="272" spans="3:3">
       <c r="C272" s="8"/>
     </row>
-    <row r="273" spans="2:3">
-      <c r="B273" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="273" spans="3:3">
       <c r="C273" s="8"/>
     </row>
-    <row r="274" spans="2:3">
-      <c r="B274" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="274" spans="3:3">
       <c r="C274" s="8"/>
     </row>
-    <row r="275" spans="2:3">
-      <c r="B275" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="275" spans="3:3">
       <c r="C275" s="8"/>
     </row>
-    <row r="276" spans="2:3">
-      <c r="B276" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="276" spans="3:3">
       <c r="C276" s="8"/>
     </row>
-    <row r="277" spans="2:3">
-      <c r="B277" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="277" spans="3:3">
       <c r="C277" s="8"/>
     </row>
-    <row r="278" spans="2:3">
-      <c r="B278" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="278" spans="3:3">
       <c r="C278" s="8"/>
     </row>
-    <row r="279" spans="2:3">
-      <c r="B279" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="279" spans="3:3">
       <c r="C279" s="8"/>
     </row>
-    <row r="280" spans="2:3">
-      <c r="B280" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="280" spans="3:3">
       <c r="C280" s="8"/>
     </row>
-    <row r="281" spans="2:3">
-      <c r="B281" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="281" spans="3:3">
       <c r="C281" s="8"/>
     </row>
-    <row r="282" spans="2:3">
-      <c r="B282" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="282" spans="3:3">
       <c r="C282" s="8"/>
     </row>
-    <row r="283" spans="2:3">
-      <c r="B283" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="283" spans="3:3">
       <c r="C283" s="8"/>
     </row>
-    <row r="284" spans="2:3">
-      <c r="B284" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="284" spans="3:3">
       <c r="C284" s="8"/>
     </row>
-    <row r="285" spans="2:3">
-      <c r="B285" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="285" spans="3:3">
       <c r="C285" s="8"/>
     </row>
-    <row r="286" spans="2:3">
-      <c r="B286" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="286" spans="3:3">
       <c r="C286" s="8"/>
     </row>
-    <row r="287" spans="2:3">
-      <c r="B287" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="287" spans="3:3">
       <c r="C287" s="8"/>
     </row>
-    <row r="288" spans="2:3">
-      <c r="B288" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="288" spans="3:3">
       <c r="C288" s="8"/>
     </row>
-    <row r="289" spans="2:3">
-      <c r="B289" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="289" spans="3:3">
       <c r="C289" s="8"/>
     </row>
-    <row r="290" spans="2:3">
-      <c r="B290" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="290" spans="3:3">
       <c r="C290" s="8"/>
     </row>
-    <row r="291" spans="2:3">
-      <c r="B291" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="291" spans="3:3">
       <c r="C291" s="8"/>
     </row>
-    <row r="292" spans="2:3">
-      <c r="B292" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
+    <row r="292" spans="3:3">
       <c r="C292" s="8"/>
-    </row>
-    <row r="293" spans="2:2">
-      <c r="B293" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="2:2">
-      <c r="B294" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="2:2">
-      <c r="B295" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="2:2">
-      <c r="B296" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="2:2">
-      <c r="B297" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="2:2">
-      <c r="B298" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="2:2">
-      <c r="B299" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="2:2">
-      <c r="B300" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="301" spans="2:2">
-      <c r="B301" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="302" spans="2:2">
-      <c r="B302" s="1" t="str">
-        <f t="shared" ref="B302:B308" si="6">C302&amp;D302</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303" spans="2:2">
-      <c r="B303" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="304" spans="2:2">
-      <c r="B304" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="305" spans="2:2">
-      <c r="B305" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="306" spans="2:2">
-      <c r="B306" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="307" spans="2:2">
-      <c r="B307" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="308" spans="2:2">
-      <c r="B308" s="1" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-    </row>
-    <row r="309" spans="2:2">
-      <c r="B309" s="1" t="str">
-        <f t="shared" ref="B309:B315" si="7">C309&amp;D309</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310" spans="2:2">
-      <c r="B310" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="311" spans="2:2">
-      <c r="B311" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="312" spans="2:2">
-      <c r="B312" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="313" spans="2:2">
-      <c r="B313" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="314" spans="2:2">
-      <c r="B314" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-    </row>
-    <row r="315" spans="2:2">
-      <c r="B315" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -7976,1405 +7976,1189 @@
     </row>
     <row r="44" spans="1:10">
       <c r="A44"/>
-      <c r="B44" s="1"/>
       <c r="C44" s="8"/>
       <c r="I44"/>
       <c r="J44"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45"/>
-      <c r="B45" s="1"/>
       <c r="C45" s="8"/>
       <c r="I45"/>
       <c r="J45"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46"/>
-      <c r="B46" s="1"/>
       <c r="C46" s="8"/>
       <c r="I46"/>
       <c r="J46"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47"/>
-      <c r="B47" s="1"/>
       <c r="C47" s="8"/>
       <c r="I47"/>
       <c r="J47"/>
     </row>
     <row r="48" spans="1:10">
       <c r="A48"/>
-      <c r="B48" s="1"/>
       <c r="C48" s="8"/>
       <c r="I48"/>
       <c r="J48"/>
     </row>
     <row r="49" spans="1:10">
       <c r="A49"/>
-      <c r="B49" s="1"/>
       <c r="C49" s="8"/>
       <c r="I49"/>
       <c r="J49"/>
     </row>
     <row r="50" spans="1:10">
       <c r="A50"/>
-      <c r="B50" s="1"/>
       <c r="C50" s="8"/>
       <c r="I50"/>
       <c r="J50"/>
     </row>
     <row r="51" spans="1:10">
       <c r="A51"/>
-      <c r="B51" s="1"/>
       <c r="C51" s="8"/>
       <c r="I51"/>
       <c r="J51"/>
     </row>
     <row r="52" spans="1:10">
       <c r="A52"/>
-      <c r="B52" s="1"/>
       <c r="C52" s="8"/>
       <c r="I52"/>
       <c r="J52"/>
     </row>
     <row r="53" spans="1:10">
       <c r="A53"/>
-      <c r="B53" s="1"/>
       <c r="I53"/>
       <c r="J53"/>
     </row>
     <row r="54" spans="1:10">
       <c r="A54"/>
-      <c r="B54" s="1"/>
       <c r="I54"/>
       <c r="J54"/>
     </row>
     <row r="55" spans="1:10">
       <c r="A55"/>
-      <c r="B55" s="1"/>
       <c r="I55"/>
       <c r="J55"/>
     </row>
     <row r="56" spans="1:10">
       <c r="A56"/>
-      <c r="B56" s="1"/>
       <c r="I56"/>
       <c r="J56"/>
     </row>
     <row r="57" spans="1:10">
       <c r="A57"/>
-      <c r="B57" s="1"/>
       <c r="I57"/>
       <c r="J57"/>
     </row>
     <row r="58" spans="1:10">
       <c r="A58"/>
-      <c r="B58" s="1"/>
       <c r="I58"/>
       <c r="J58"/>
     </row>
     <row r="59" spans="1:10">
       <c r="A59"/>
-      <c r="B59" s="1"/>
       <c r="I59"/>
       <c r="J59"/>
     </row>
     <row r="60" spans="1:10">
       <c r="A60"/>
-      <c r="B60" s="1"/>
       <c r="I60"/>
       <c r="J60"/>
     </row>
     <row r="61" spans="1:10">
       <c r="A61"/>
-      <c r="B61" s="1"/>
       <c r="I61"/>
       <c r="J61"/>
     </row>
     <row r="62" spans="1:10">
       <c r="A62"/>
-      <c r="B62" s="1"/>
       <c r="I62"/>
       <c r="J62"/>
     </row>
     <row r="63" spans="1:10">
       <c r="A63"/>
-      <c r="B63" s="1"/>
       <c r="I63"/>
       <c r="J63"/>
     </row>
     <row r="64" spans="1:10">
       <c r="A64"/>
-      <c r="B64" s="1"/>
       <c r="I64"/>
       <c r="J64"/>
     </row>
     <row r="65" spans="1:10">
       <c r="A65"/>
-      <c r="B65" s="1"/>
       <c r="I65"/>
       <c r="J65"/>
     </row>
     <row r="66" spans="1:10">
       <c r="A66"/>
-      <c r="B66" s="1"/>
       <c r="I66"/>
       <c r="J66"/>
     </row>
     <row r="67" spans="1:10">
       <c r="A67"/>
-      <c r="B67" s="1"/>
       <c r="I67"/>
       <c r="J67"/>
     </row>
     <row r="68" spans="1:10">
       <c r="A68"/>
-      <c r="B68" s="1"/>
       <c r="I68"/>
       <c r="J68"/>
     </row>
     <row r="69" spans="1:10">
       <c r="A69"/>
-      <c r="B69" s="1"/>
       <c r="I69"/>
       <c r="J69"/>
     </row>
     <row r="70" spans="1:10">
       <c r="A70"/>
-      <c r="B70" s="1"/>
       <c r="I70"/>
       <c r="J70"/>
     </row>
     <row r="71" spans="1:10">
       <c r="A71"/>
-      <c r="B71" s="1"/>
       <c r="I71"/>
       <c r="J71"/>
     </row>
     <row r="72" spans="1:10">
       <c r="A72"/>
-      <c r="B72" s="1"/>
       <c r="I72"/>
       <c r="J72"/>
     </row>
     <row r="73" spans="1:10">
       <c r="A73"/>
-      <c r="B73" s="1"/>
       <c r="I73"/>
       <c r="J73"/>
     </row>
     <row r="74" spans="1:10">
       <c r="A74"/>
-      <c r="B74" s="1"/>
       <c r="I74"/>
       <c r="J74"/>
     </row>
     <row r="75" spans="1:10">
       <c r="A75"/>
-      <c r="B75" s="1"/>
       <c r="I75"/>
       <c r="J75"/>
     </row>
     <row r="76" spans="1:10">
       <c r="A76"/>
-      <c r="B76" s="1"/>
       <c r="C76" s="8"/>
       <c r="I76"/>
       <c r="J76"/>
     </row>
     <row r="77" spans="1:10">
       <c r="A77"/>
-      <c r="B77" s="1"/>
       <c r="C77" s="8"/>
       <c r="I77"/>
       <c r="J77"/>
     </row>
     <row r="78" spans="1:10">
       <c r="A78"/>
-      <c r="B78" s="1"/>
       <c r="C78" s="8"/>
       <c r="I78"/>
       <c r="J78"/>
     </row>
     <row r="79" spans="1:10">
       <c r="A79"/>
-      <c r="B79" s="1"/>
       <c r="C79" s="8"/>
       <c r="I79"/>
       <c r="J79"/>
     </row>
     <row r="80" spans="1:10">
       <c r="A80"/>
-      <c r="B80" s="1"/>
       <c r="C80" s="8"/>
       <c r="I80"/>
       <c r="J80"/>
     </row>
     <row r="81" spans="1:10">
       <c r="A81"/>
-      <c r="B81" s="1"/>
       <c r="C81" s="8"/>
       <c r="I81"/>
       <c r="J81"/>
     </row>
     <row r="82" spans="1:10">
       <c r="A82"/>
-      <c r="B82" s="1"/>
       <c r="C82" s="8"/>
       <c r="I82"/>
       <c r="J82"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83"/>
-      <c r="B83" s="1"/>
       <c r="C83" s="8"/>
       <c r="I83"/>
       <c r="J83"/>
     </row>
     <row r="84" spans="1:10">
       <c r="A84"/>
-      <c r="B84" s="1"/>
       <c r="C84" s="8"/>
       <c r="I84"/>
       <c r="J84"/>
     </row>
     <row r="85" spans="1:10">
       <c r="A85"/>
-      <c r="B85" s="1"/>
       <c r="C85" s="8"/>
       <c r="I85"/>
       <c r="J85"/>
     </row>
     <row r="86" spans="1:10">
       <c r="A86"/>
-      <c r="B86" s="1"/>
       <c r="C86" s="8"/>
       <c r="I86"/>
       <c r="J86"/>
     </row>
     <row r="87" spans="1:10">
       <c r="A87"/>
-      <c r="B87" s="1"/>
       <c r="C87" s="8"/>
       <c r="I87"/>
       <c r="J87"/>
     </row>
     <row r="88" spans="1:10">
       <c r="A88"/>
-      <c r="B88" s="1"/>
       <c r="C88" s="8"/>
       <c r="I88"/>
       <c r="J88"/>
     </row>
     <row r="89" spans="1:10">
       <c r="A89"/>
-      <c r="B89" s="1"/>
       <c r="C89" s="8"/>
       <c r="I89"/>
       <c r="J89"/>
     </row>
     <row r="90" spans="1:10">
       <c r="A90"/>
-      <c r="B90" s="1"/>
       <c r="C90" s="8"/>
       <c r="I90"/>
       <c r="J90"/>
     </row>
     <row r="91" spans="1:10">
       <c r="A91"/>
-      <c r="B91" s="1"/>
       <c r="C91" s="8"/>
       <c r="I91"/>
       <c r="J91"/>
     </row>
     <row r="92" spans="1:10">
       <c r="A92"/>
-      <c r="B92" s="1"/>
       <c r="C92" s="8"/>
       <c r="I92"/>
       <c r="J92"/>
     </row>
     <row r="93" spans="1:10">
       <c r="A93"/>
-      <c r="B93" s="1"/>
       <c r="C93" s="8"/>
       <c r="I93"/>
       <c r="J93"/>
     </row>
     <row r="94" spans="1:10">
       <c r="A94"/>
-      <c r="B94" s="1"/>
       <c r="C94" s="8"/>
       <c r="I94"/>
       <c r="J94"/>
     </row>
     <row r="95" spans="1:10">
       <c r="A95"/>
-      <c r="B95" s="1"/>
       <c r="C95" s="8"/>
       <c r="I95"/>
       <c r="J95"/>
     </row>
     <row r="96" spans="1:10">
       <c r="A96"/>
-      <c r="B96" s="1"/>
       <c r="C96" s="8"/>
       <c r="I96"/>
       <c r="J96"/>
     </row>
     <row r="97" spans="1:10">
       <c r="A97"/>
-      <c r="B97" s="1"/>
       <c r="C97" s="8"/>
       <c r="I97"/>
       <c r="J97"/>
     </row>
     <row r="98" spans="1:10">
       <c r="A98"/>
-      <c r="B98" s="1"/>
       <c r="C98" s="8"/>
       <c r="I98"/>
       <c r="J98"/>
     </row>
     <row r="99" spans="1:10">
       <c r="A99"/>
-      <c r="B99" s="1"/>
       <c r="C99" s="8"/>
       <c r="I99"/>
       <c r="J99"/>
     </row>
     <row r="100" spans="1:10">
       <c r="A100"/>
-      <c r="B100" s="1"/>
       <c r="C100" s="8"/>
       <c r="I100"/>
       <c r="J100"/>
     </row>
     <row r="101" spans="1:10">
       <c r="A101"/>
-      <c r="B101" s="1"/>
       <c r="I101"/>
       <c r="J101"/>
     </row>
     <row r="102" spans="1:10">
       <c r="A102"/>
-      <c r="B102" s="1"/>
       <c r="I102"/>
       <c r="J102"/>
     </row>
     <row r="103" spans="1:10">
       <c r="A103"/>
-      <c r="B103" s="1"/>
       <c r="I103"/>
       <c r="J103"/>
     </row>
     <row r="104" spans="1:10">
       <c r="A104"/>
-      <c r="B104" s="1"/>
       <c r="I104"/>
       <c r="J104"/>
     </row>
     <row r="105" spans="1:10">
       <c r="A105"/>
-      <c r="B105" s="1"/>
       <c r="I105"/>
       <c r="J105"/>
     </row>
     <row r="106" spans="1:10">
       <c r="A106"/>
-      <c r="B106" s="1"/>
       <c r="I106"/>
       <c r="J106"/>
     </row>
     <row r="107" spans="1:10">
       <c r="A107"/>
-      <c r="B107" s="1"/>
       <c r="I107"/>
       <c r="J107"/>
     </row>
     <row r="108" spans="1:10">
       <c r="A108"/>
-      <c r="B108" s="1"/>
       <c r="I108"/>
       <c r="J108"/>
     </row>
     <row r="109" spans="1:10">
       <c r="A109"/>
-      <c r="B109" s="1"/>
       <c r="I109"/>
       <c r="J109"/>
     </row>
     <row r="110" spans="1:10">
       <c r="A110"/>
-      <c r="B110" s="1"/>
       <c r="I110"/>
       <c r="J110"/>
     </row>
     <row r="111" spans="1:10">
       <c r="A111"/>
-      <c r="B111" s="1"/>
       <c r="I111"/>
       <c r="J111"/>
     </row>
     <row r="112" spans="1:10">
       <c r="A112"/>
-      <c r="B112" s="1"/>
       <c r="I112"/>
       <c r="J112"/>
     </row>
     <row r="113" spans="1:10">
       <c r="A113"/>
-      <c r="B113" s="1"/>
       <c r="I113"/>
       <c r="J113"/>
     </row>
     <row r="114" spans="1:10">
       <c r="A114"/>
-      <c r="B114" s="1"/>
       <c r="I114"/>
       <c r="J114"/>
     </row>
     <row r="115" spans="1:10">
       <c r="A115"/>
-      <c r="B115" s="1"/>
       <c r="I115"/>
       <c r="J115"/>
     </row>
     <row r="116" spans="1:10">
       <c r="A116"/>
-      <c r="B116" s="1"/>
       <c r="I116"/>
       <c r="J116"/>
     </row>
     <row r="117" spans="1:10">
       <c r="A117"/>
-      <c r="B117" s="1"/>
       <c r="I117"/>
       <c r="J117"/>
     </row>
     <row r="118" spans="1:10">
       <c r="A118"/>
-      <c r="B118" s="1"/>
       <c r="I118"/>
       <c r="J118"/>
     </row>
     <row r="119" spans="1:10">
       <c r="A119"/>
-      <c r="B119" s="1"/>
       <c r="I119"/>
       <c r="J119"/>
     </row>
     <row r="120" spans="1:10">
       <c r="A120"/>
-      <c r="B120" s="1"/>
       <c r="I120"/>
       <c r="J120"/>
     </row>
     <row r="121" spans="1:10">
       <c r="A121"/>
-      <c r="B121" s="1"/>
       <c r="I121"/>
       <c r="J121"/>
     </row>
     <row r="122" spans="1:10">
       <c r="A122"/>
-      <c r="B122" s="1"/>
       <c r="I122"/>
       <c r="J122"/>
     </row>
     <row r="123" spans="1:10">
       <c r="A123"/>
-      <c r="B123" s="1"/>
       <c r="I123"/>
       <c r="J123"/>
     </row>
     <row r="124" spans="1:10">
       <c r="A124"/>
-      <c r="B124" s="1"/>
       <c r="C124" s="8"/>
       <c r="I124"/>
       <c r="J124"/>
     </row>
     <row r="125" spans="1:10">
       <c r="A125"/>
-      <c r="B125" s="1"/>
       <c r="C125" s="8"/>
       <c r="I125"/>
       <c r="J125"/>
     </row>
     <row r="126" spans="1:10">
       <c r="A126"/>
-      <c r="B126" s="1"/>
       <c r="C126" s="8"/>
       <c r="I126"/>
       <c r="J126"/>
     </row>
     <row r="127" spans="1:10">
       <c r="A127"/>
-      <c r="B127" s="1"/>
       <c r="C127" s="8"/>
       <c r="I127"/>
       <c r="J127"/>
     </row>
     <row r="128" spans="1:10">
       <c r="A128"/>
-      <c r="B128" s="1"/>
       <c r="C128" s="8"/>
       <c r="I128"/>
       <c r="J128"/>
     </row>
     <row r="129" spans="1:10">
       <c r="A129"/>
-      <c r="B129" s="1"/>
       <c r="C129" s="8"/>
       <c r="I129"/>
       <c r="J129"/>
     </row>
     <row r="130" spans="1:10">
       <c r="A130"/>
-      <c r="B130" s="1"/>
       <c r="C130" s="8"/>
       <c r="I130"/>
       <c r="J130"/>
     </row>
     <row r="131" spans="1:10">
       <c r="A131"/>
-      <c r="B131" s="1"/>
       <c r="C131" s="8"/>
       <c r="I131"/>
       <c r="J131"/>
     </row>
     <row r="132" spans="1:10">
       <c r="A132"/>
-      <c r="B132" s="1"/>
       <c r="C132" s="8"/>
       <c r="I132"/>
       <c r="J132"/>
     </row>
     <row r="133" spans="1:10">
       <c r="A133"/>
-      <c r="B133" s="1"/>
       <c r="C133" s="8"/>
       <c r="I133"/>
       <c r="J133"/>
     </row>
     <row r="134" spans="1:10">
       <c r="A134"/>
-      <c r="B134" s="1"/>
       <c r="C134" s="8"/>
       <c r="I134"/>
       <c r="J134"/>
     </row>
     <row r="135" spans="1:10">
       <c r="A135"/>
-      <c r="B135" s="1"/>
       <c r="C135" s="8"/>
       <c r="I135"/>
       <c r="J135"/>
     </row>
     <row r="136" spans="1:10">
       <c r="A136"/>
-      <c r="B136" s="1"/>
       <c r="C136" s="8"/>
       <c r="I136"/>
       <c r="J136"/>
     </row>
     <row r="137" spans="1:10">
       <c r="A137"/>
-      <c r="B137" s="1"/>
       <c r="C137" s="8"/>
       <c r="I137"/>
       <c r="J137"/>
     </row>
     <row r="138" spans="1:10">
       <c r="A138"/>
-      <c r="B138" s="1"/>
       <c r="C138" s="8"/>
       <c r="I138"/>
       <c r="J138"/>
     </row>
     <row r="139" spans="1:10">
       <c r="A139"/>
-      <c r="B139" s="1"/>
       <c r="C139" s="8"/>
       <c r="I139"/>
       <c r="J139"/>
     </row>
     <row r="140" spans="1:10">
       <c r="A140"/>
-      <c r="B140" s="1"/>
       <c r="C140" s="8"/>
       <c r="I140"/>
       <c r="J140"/>
     </row>
     <row r="141" spans="1:10">
       <c r="A141"/>
-      <c r="B141" s="1"/>
       <c r="C141" s="8"/>
       <c r="I141"/>
       <c r="J141"/>
     </row>
     <row r="142" spans="1:10">
       <c r="A142"/>
-      <c r="B142" s="1"/>
       <c r="C142" s="8"/>
       <c r="I142"/>
       <c r="J142"/>
     </row>
     <row r="143" spans="1:10">
       <c r="A143"/>
-      <c r="B143" s="1"/>
       <c r="C143" s="8"/>
       <c r="I143"/>
       <c r="J143"/>
     </row>
     <row r="144" spans="1:10">
       <c r="A144"/>
-      <c r="B144" s="1"/>
       <c r="C144" s="8"/>
       <c r="I144"/>
       <c r="J144"/>
     </row>
     <row r="145" spans="1:10">
       <c r="A145"/>
-      <c r="B145" s="1"/>
       <c r="C145" s="8"/>
       <c r="I145"/>
       <c r="J145"/>
     </row>
     <row r="146" spans="1:10">
       <c r="A146"/>
-      <c r="B146" s="1"/>
       <c r="C146" s="8"/>
       <c r="I146"/>
       <c r="J146"/>
     </row>
     <row r="147" spans="1:10">
       <c r="A147"/>
-      <c r="B147" s="1"/>
       <c r="C147" s="8"/>
       <c r="I147"/>
       <c r="J147"/>
     </row>
     <row r="148" spans="1:10">
       <c r="A148"/>
-      <c r="B148" s="1"/>
       <c r="C148" s="8"/>
       <c r="I148"/>
       <c r="J148"/>
     </row>
     <row r="149" spans="1:10">
       <c r="A149"/>
-      <c r="B149" s="1"/>
       <c r="I149"/>
       <c r="J149"/>
     </row>
     <row r="150" spans="1:10">
       <c r="A150"/>
-      <c r="B150" s="1"/>
       <c r="I150"/>
       <c r="J150"/>
     </row>
     <row r="151" spans="1:10">
       <c r="A151"/>
-      <c r="B151" s="1"/>
       <c r="I151"/>
       <c r="J151"/>
     </row>
     <row r="152" spans="1:10">
       <c r="A152"/>
-      <c r="B152" s="1"/>
       <c r="I152"/>
       <c r="J152"/>
     </row>
     <row r="153" spans="1:10">
       <c r="A153"/>
-      <c r="B153" s="1"/>
       <c r="I153"/>
       <c r="J153"/>
     </row>
     <row r="154" spans="1:10">
       <c r="A154"/>
-      <c r="B154" s="1"/>
       <c r="I154"/>
       <c r="J154"/>
     </row>
     <row r="155" spans="1:10">
       <c r="A155"/>
-      <c r="B155" s="1"/>
       <c r="I155"/>
       <c r="J155"/>
     </row>
     <row r="156" spans="1:10">
       <c r="A156"/>
-      <c r="B156" s="1"/>
       <c r="I156"/>
       <c r="J156"/>
     </row>
     <row r="157" spans="1:10">
       <c r="A157"/>
-      <c r="B157" s="1"/>
       <c r="I157"/>
       <c r="J157"/>
     </row>
     <row r="158" spans="1:10">
       <c r="A158"/>
-      <c r="B158" s="1"/>
       <c r="I158"/>
       <c r="J158"/>
     </row>
     <row r="159" spans="1:10">
       <c r="A159"/>
-      <c r="B159" s="1"/>
       <c r="I159"/>
       <c r="J159"/>
     </row>
     <row r="160" spans="1:10">
       <c r="A160"/>
-      <c r="B160" s="1"/>
       <c r="I160"/>
       <c r="J160"/>
     </row>
     <row r="161" spans="1:10">
       <c r="A161"/>
-      <c r="B161" s="1"/>
       <c r="I161"/>
       <c r="J161"/>
     </row>
     <row r="162" spans="1:10">
       <c r="A162"/>
-      <c r="B162" s="1"/>
       <c r="I162"/>
       <c r="J162"/>
     </row>
     <row r="163" spans="1:10">
       <c r="A163"/>
-      <c r="B163" s="1"/>
       <c r="I163"/>
       <c r="J163"/>
     </row>
     <row r="164" spans="1:10">
       <c r="A164"/>
-      <c r="B164" s="1"/>
       <c r="I164"/>
       <c r="J164"/>
     </row>
     <row r="165" spans="1:10">
       <c r="A165"/>
-      <c r="B165" s="1"/>
       <c r="I165"/>
       <c r="J165"/>
     </row>
     <row r="166" spans="1:10">
       <c r="A166"/>
-      <c r="B166" s="1"/>
       <c r="I166"/>
       <c r="J166"/>
     </row>
     <row r="167" spans="1:10">
       <c r="A167"/>
-      <c r="B167" s="1"/>
       <c r="I167"/>
       <c r="J167"/>
     </row>
     <row r="168" spans="1:10">
       <c r="A168"/>
-      <c r="B168" s="1"/>
       <c r="I168"/>
       <c r="J168"/>
     </row>
     <row r="169" spans="1:10">
       <c r="A169"/>
-      <c r="B169" s="1"/>
       <c r="I169"/>
       <c r="J169"/>
     </row>
     <row r="170" spans="1:10">
       <c r="A170"/>
-      <c r="B170" s="1"/>
       <c r="I170"/>
       <c r="J170"/>
     </row>
     <row r="171" spans="1:10">
       <c r="A171"/>
-      <c r="B171" s="1"/>
       <c r="I171"/>
       <c r="J171"/>
     </row>
     <row r="172" spans="1:10">
       <c r="A172"/>
-      <c r="B172" s="1"/>
       <c r="C172" s="8"/>
       <c r="I172"/>
       <c r="J172"/>
     </row>
     <row r="173" spans="1:10">
       <c r="A173"/>
-      <c r="B173" s="1"/>
       <c r="C173" s="8"/>
       <c r="I173"/>
       <c r="J173"/>
     </row>
     <row r="174" spans="1:10">
       <c r="A174"/>
-      <c r="B174" s="1"/>
       <c r="C174" s="8"/>
       <c r="I174"/>
       <c r="J174"/>
     </row>
     <row r="175" spans="1:10">
       <c r="A175"/>
-      <c r="B175" s="1"/>
       <c r="C175" s="8"/>
       <c r="I175"/>
       <c r="J175"/>
     </row>
     <row r="176" spans="1:10">
       <c r="A176"/>
-      <c r="B176" s="1"/>
       <c r="C176" s="8"/>
       <c r="I176"/>
       <c r="J176"/>
     </row>
     <row r="177" spans="1:10">
       <c r="A177"/>
-      <c r="B177" s="1"/>
       <c r="C177" s="8"/>
       <c r="I177"/>
       <c r="J177"/>
     </row>
     <row r="178" spans="1:10">
       <c r="A178"/>
-      <c r="B178" s="1"/>
       <c r="C178" s="8"/>
       <c r="I178"/>
       <c r="J178"/>
     </row>
     <row r="179" spans="1:10">
       <c r="A179"/>
-      <c r="B179" s="1"/>
       <c r="C179" s="8"/>
       <c r="I179"/>
       <c r="J179"/>
     </row>
     <row r="180" spans="1:10">
       <c r="A180"/>
-      <c r="B180" s="1"/>
       <c r="C180" s="8"/>
       <c r="I180"/>
       <c r="J180"/>
     </row>
     <row r="181" spans="1:10">
       <c r="A181"/>
-      <c r="B181" s="1"/>
       <c r="C181" s="8"/>
       <c r="I181"/>
       <c r="J181"/>
     </row>
     <row r="182" spans="1:10">
       <c r="A182"/>
-      <c r="B182" s="1"/>
       <c r="C182" s="8"/>
       <c r="I182"/>
       <c r="J182"/>
     </row>
     <row r="183" spans="1:10">
       <c r="A183"/>
-      <c r="B183" s="1"/>
       <c r="C183" s="8"/>
       <c r="I183"/>
       <c r="J183"/>
     </row>
     <row r="184" spans="1:10">
       <c r="A184"/>
-      <c r="B184" s="1"/>
       <c r="C184" s="8"/>
       <c r="I184"/>
       <c r="J184"/>
     </row>
     <row r="185" spans="1:10">
       <c r="A185"/>
-      <c r="B185" s="1"/>
       <c r="C185" s="8"/>
       <c r="I185"/>
       <c r="J185"/>
     </row>
     <row r="186" spans="1:10">
       <c r="A186"/>
-      <c r="B186" s="1"/>
       <c r="C186" s="8"/>
       <c r="I186"/>
       <c r="J186"/>
     </row>
     <row r="187" spans="1:10">
       <c r="A187"/>
-      <c r="B187" s="1"/>
       <c r="C187" s="8"/>
       <c r="I187"/>
       <c r="J187"/>
     </row>
     <row r="188" spans="1:10">
       <c r="A188"/>
-      <c r="B188" s="1"/>
       <c r="C188" s="8"/>
       <c r="I188"/>
       <c r="J188"/>
     </row>
     <row r="189" spans="1:10">
       <c r="A189"/>
-      <c r="B189" s="1"/>
       <c r="C189" s="8"/>
       <c r="I189"/>
       <c r="J189"/>
     </row>
     <row r="190" spans="1:10">
       <c r="A190"/>
-      <c r="B190" s="1"/>
       <c r="C190" s="8"/>
       <c r="I190"/>
       <c r="J190"/>
     </row>
     <row r="191" spans="1:10">
       <c r="A191"/>
-      <c r="B191" s="1"/>
       <c r="C191" s="8"/>
       <c r="I191"/>
       <c r="J191"/>
     </row>
     <row r="192" spans="1:10">
       <c r="A192"/>
-      <c r="B192" s="1"/>
       <c r="C192" s="8"/>
       <c r="I192"/>
       <c r="J192"/>
     </row>
     <row r="193" spans="1:10">
       <c r="A193"/>
-      <c r="B193" s="1"/>
       <c r="C193" s="8"/>
       <c r="I193"/>
       <c r="J193"/>
     </row>
     <row r="194" spans="1:10">
       <c r="A194"/>
-      <c r="B194" s="1"/>
       <c r="C194" s="8"/>
       <c r="I194"/>
       <c r="J194"/>
     </row>
     <row r="195" spans="1:10">
       <c r="A195"/>
-      <c r="B195" s="1"/>
       <c r="C195" s="8"/>
       <c r="I195"/>
       <c r="J195"/>
     </row>
     <row r="196" spans="1:10">
       <c r="A196"/>
-      <c r="B196" s="1"/>
       <c r="C196" s="8"/>
       <c r="I196"/>
       <c r="J196"/>
     </row>
     <row r="197" spans="1:10">
       <c r="A197"/>
-      <c r="B197" s="1"/>
       <c r="I197"/>
       <c r="J197"/>
     </row>
     <row r="198" spans="1:10">
       <c r="A198"/>
-      <c r="B198" s="1"/>
       <c r="I198"/>
       <c r="J198"/>
     </row>
     <row r="199" spans="1:10">
       <c r="A199"/>
-      <c r="B199" s="1"/>
       <c r="I199"/>
       <c r="J199"/>
     </row>
     <row r="200" spans="1:10">
       <c r="A200"/>
-      <c r="B200" s="1"/>
       <c r="I200"/>
       <c r="J200"/>
     </row>
     <row r="201" spans="1:10">
       <c r="A201"/>
-      <c r="B201" s="1"/>
       <c r="I201"/>
       <c r="J201"/>
     </row>
     <row r="202" spans="1:10">
       <c r="A202"/>
-      <c r="B202" s="1"/>
       <c r="I202"/>
       <c r="J202"/>
     </row>
     <row r="203" spans="1:10">
       <c r="A203"/>
-      <c r="B203" s="1"/>
       <c r="I203"/>
       <c r="J203"/>
     </row>
     <row r="204" spans="1:10">
       <c r="A204"/>
-      <c r="B204" s="1"/>
       <c r="I204"/>
       <c r="J204"/>
     </row>
     <row r="205" spans="1:10">
       <c r="A205"/>
-      <c r="B205" s="1"/>
       <c r="I205"/>
       <c r="J205"/>
     </row>
     <row r="206" spans="1:10">
       <c r="A206"/>
-      <c r="B206" s="1"/>
       <c r="I206"/>
       <c r="J206"/>
     </row>
     <row r="207" spans="1:10">
       <c r="A207"/>
-      <c r="B207" s="1"/>
       <c r="I207"/>
       <c r="J207"/>
     </row>
     <row r="208" spans="1:10">
       <c r="A208"/>
-      <c r="B208" s="1"/>
       <c r="I208"/>
       <c r="J208"/>
     </row>
     <row r="209" spans="1:10">
       <c r="A209"/>
-      <c r="B209" s="1"/>
       <c r="I209"/>
       <c r="J209"/>
     </row>
     <row r="210" spans="1:10">
       <c r="A210"/>
-      <c r="B210" s="1"/>
       <c r="I210"/>
       <c r="J210"/>
     </row>
     <row r="211" spans="1:10">
       <c r="A211"/>
-      <c r="B211" s="1"/>
       <c r="I211"/>
       <c r="J211"/>
     </row>
     <row r="212" spans="1:10">
       <c r="A212"/>
-      <c r="B212" s="1"/>
       <c r="I212"/>
       <c r="J212"/>
     </row>
     <row r="213" spans="1:10">
       <c r="A213"/>
-      <c r="B213" s="1"/>
       <c r="I213"/>
       <c r="J213"/>
     </row>
     <row r="214" spans="1:10">
       <c r="A214"/>
-      <c r="B214" s="1"/>
       <c r="I214"/>
       <c r="J214"/>
     </row>
     <row r="215" spans="1:10">
       <c r="A215"/>
-      <c r="B215" s="1"/>
       <c r="I215"/>
       <c r="J215"/>
     </row>
     <row r="216" spans="1:10">
       <c r="A216"/>
-      <c r="B216" s="1"/>
       <c r="I216"/>
       <c r="J216"/>
     </row>
     <row r="217" spans="1:10">
       <c r="A217"/>
-      <c r="B217" s="1"/>
       <c r="I217"/>
       <c r="J217"/>
     </row>
     <row r="218" spans="1:9">
       <c r="A218"/>
-      <c r="B218" s="1"/>
       <c r="I218"/>
     </row>
     <row r="219" spans="1:10">
       <c r="A219"/>
-      <c r="B219" s="1"/>
       <c r="I219"/>
       <c r="J219"/>
     </row>
     <row r="220" spans="1:10">
       <c r="A220"/>
-      <c r="B220" s="1"/>
       <c r="C220" s="8"/>
       <c r="I220"/>
       <c r="J220"/>
     </row>
     <row r="221" spans="1:10">
       <c r="A221"/>
-      <c r="B221" s="1"/>
       <c r="C221" s="8"/>
       <c r="I221"/>
       <c r="J221"/>
     </row>
     <row r="222" spans="1:10">
       <c r="A222"/>
-      <c r="B222" s="1"/>
       <c r="C222" s="8"/>
       <c r="I222"/>
       <c r="J222"/>
     </row>
     <row r="223" spans="1:10">
       <c r="A223"/>
-      <c r="B223" s="1"/>
       <c r="C223" s="8"/>
       <c r="I223"/>
       <c r="J223"/>
     </row>
     <row r="224" spans="1:10">
       <c r="A224"/>
-      <c r="B224" s="1"/>
       <c r="C224" s="8"/>
       <c r="I224"/>
       <c r="J224"/>
     </row>
     <row r="225" spans="1:10">
       <c r="A225"/>
-      <c r="B225" s="1"/>
       <c r="C225" s="8"/>
       <c r="I225"/>
       <c r="J225"/>
     </row>
     <row r="226" spans="1:10">
       <c r="A226"/>
-      <c r="B226" s="1"/>
       <c r="C226" s="8"/>
       <c r="I226"/>
       <c r="J226"/>
     </row>
     <row r="227" spans="1:10">
       <c r="A227"/>
-      <c r="B227" s="1"/>
       <c r="C227" s="8"/>
       <c r="I227"/>
       <c r="J227"/>
     </row>
     <row r="228" spans="1:10">
       <c r="A228"/>
-      <c r="B228" s="1"/>
       <c r="C228" s="8"/>
       <c r="I228"/>
       <c r="J228"/>
     </row>
     <row r="229" spans="1:10">
       <c r="A229"/>
-      <c r="B229" s="1"/>
       <c r="C229" s="8"/>
       <c r="I229"/>
       <c r="J229"/>
     </row>
     <row r="230" spans="1:10">
       <c r="A230"/>
-      <c r="B230" s="1"/>
       <c r="C230" s="8"/>
       <c r="I230"/>
       <c r="J230"/>
     </row>
     <row r="231" spans="1:10">
       <c r="A231"/>
-      <c r="B231" s="1"/>
       <c r="C231" s="8"/>
       <c r="I231"/>
       <c r="J231"/>
     </row>
     <row r="232" spans="1:10">
       <c r="A232"/>
-      <c r="B232" s="1"/>
       <c r="C232" s="8"/>
       <c r="I232"/>
       <c r="J232"/>
     </row>
     <row r="233" spans="1:10">
       <c r="A233"/>
-      <c r="B233" s="1"/>
       <c r="C233" s="8"/>
       <c r="I233"/>
       <c r="J233"/>
     </row>
     <row r="234" spans="1:10">
       <c r="A234"/>
-      <c r="B234" s="1"/>
       <c r="C234" s="8"/>
       <c r="I234"/>
       <c r="J234"/>
     </row>
     <row r="235" spans="1:10">
       <c r="A235"/>
-      <c r="B235" s="1"/>
       <c r="C235" s="8"/>
       <c r="I235"/>
       <c r="J235"/>
     </row>
     <row r="236" spans="1:10">
       <c r="A236"/>
-      <c r="B236" s="1"/>
       <c r="C236" s="8"/>
       <c r="I236"/>
       <c r="J236"/>
     </row>
     <row r="237" spans="1:10">
       <c r="A237"/>
-      <c r="B237" s="1"/>
       <c r="C237" s="8"/>
       <c r="I237"/>
       <c r="J237"/>
     </row>
     <row r="238" spans="1:10">
       <c r="A238"/>
-      <c r="B238" s="1"/>
       <c r="C238" s="8"/>
       <c r="I238"/>
       <c r="J238"/>
     </row>
     <row r="239" spans="1:10">
       <c r="A239"/>
-      <c r="B239" s="1"/>
       <c r="C239" s="8"/>
       <c r="I239"/>
       <c r="J239"/>
     </row>
     <row r="240" spans="1:10">
       <c r="A240"/>
-      <c r="B240" s="1"/>
       <c r="C240" s="8"/>
       <c r="I240"/>
       <c r="J240"/>
     </row>
     <row r="241" spans="1:10">
       <c r="A241"/>
-      <c r="B241" s="1"/>
       <c r="C241" s="8"/>
       <c r="I241"/>
       <c r="J241"/>
     </row>
     <row r="242" spans="1:10">
       <c r="A242"/>
-      <c r="B242" s="1"/>
       <c r="C242" s="8"/>
       <c r="I242"/>
       <c r="J242"/>
     </row>
     <row r="243" spans="1:10">
       <c r="A243"/>
-      <c r="B243" s="1"/>
       <c r="C243" s="8"/>
       <c r="I243"/>
       <c r="J243"/>
     </row>
     <row r="244" spans="1:10">
       <c r="A244"/>
-      <c r="B244" s="1"/>
       <c r="C244" s="8"/>
       <c r="I244"/>
       <c r="J244"/>
     </row>
     <row r="245" spans="1:10">
       <c r="A245"/>
-      <c r="B245" s="1"/>
       <c r="I245"/>
       <c r="J245"/>
     </row>
     <row r="246" spans="1:10">
       <c r="A246"/>
-      <c r="B246" s="1"/>
       <c r="I246"/>
       <c r="J246"/>
     </row>
     <row r="247" spans="1:10">
       <c r="A247"/>
-      <c r="B247" s="1"/>
       <c r="I247"/>
       <c r="J247"/>
     </row>
     <row r="248" spans="1:10">
       <c r="A248"/>
-      <c r="B248" s="1"/>
       <c r="I248"/>
       <c r="J248"/>
     </row>
     <row r="249" spans="1:10">
       <c r="A249"/>
-      <c r="B249" s="1"/>
       <c r="I249"/>
       <c r="J249"/>
     </row>
     <row r="250" spans="1:10">
       <c r="A250"/>
-      <c r="B250" s="1"/>
       <c r="I250"/>
       <c r="J250"/>
     </row>
     <row r="251" spans="1:10">
       <c r="A251"/>
-      <c r="B251" s="1"/>
       <c r="I251"/>
       <c r="J251"/>
     </row>
     <row r="252" spans="1:10">
       <c r="A252"/>
-      <c r="B252" s="1"/>
       <c r="I252"/>
       <c r="J252"/>
     </row>
     <row r="253" spans="1:10">
       <c r="A253"/>
-      <c r="B253" s="1"/>
       <c r="I253"/>
       <c r="J253"/>
     </row>
     <row r="254" spans="1:10">
       <c r="A254"/>
-      <c r="B254" s="1"/>
       <c r="I254"/>
       <c r="J254"/>
     </row>
     <row r="255" spans="1:10">
       <c r="A255"/>
-      <c r="B255" s="1"/>
       <c r="I255"/>
       <c r="J255"/>
     </row>
     <row r="256" spans="1:10">
       <c r="A256"/>
-      <c r="B256" s="1"/>
       <c r="I256"/>
       <c r="J256"/>
     </row>
     <row r="257" spans="1:10">
       <c r="A257"/>
-      <c r="B257" s="1"/>
       <c r="I257"/>
       <c r="J257"/>
     </row>
     <row r="258" spans="1:10">
       <c r="A258"/>
-      <c r="B258" s="1"/>
       <c r="I258"/>
       <c r="J258"/>
     </row>
     <row r="259" spans="1:10">
       <c r="A259"/>
-      <c r="B259" s="1"/>
       <c r="I259"/>
       <c r="J259"/>
     </row>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" r:id="Rb61518f9784a46aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" r:id="Rb866d1b55a5e4cb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" r:id="Rbecf20cae5f64073"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" r:id="Rf95d53d0e10d4029"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cake_layer_buff" sheetId="5" r:id="R4c4122d1ea7f484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sub_skill" sheetId="6" r:id="Re69342928f244e49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计新" sheetId="9" r:id="Rcc8b11544ae44673"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计" sheetId="7" r:id="Red2940db322c4a24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置" sheetId="8" r:id="R105b37eb7f9c425c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" r:id="Ra49def1f2cc247ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" r:id="Rb6234b209424429b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" r:id="R25581d148fe14676"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" r:id="R020285e1efd64e48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cake_layer_buff" sheetId="5" r:id="R52d9bcfa7b9b4cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sub_skill" sheetId="6" r:id="R3962b01070ef4012"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计新" sheetId="9" r:id="R3639c2d3ee474185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计" sheetId="7" r:id="R3d90c16825b44dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置" sheetId="8" r:id="Rc876a931c62a4934"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1083,9 +1083,6 @@
     <x:t xml:space="preserve">actionParam</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">isPassive</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">signed</x:t>
   </x:si>
   <x:si>
@@ -1126,9 +1123,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">行为参数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">是否被动</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">数值正负号</x:t>
@@ -10494,11 +10488,9 @@
         <x:v>355</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="Q1" s="1" t="s">
         <x:v>282</x:v>
       </x:c>
+      <x:c r="Q1" s="1"/>
       <x:c r="R1"/>
       <x:c r="S1"/>
       <x:c r="T1"/>
@@ -10508,53 +10500,51 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="D2" s="1" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="D2" s="1" t="s">
+      <x:c r="E2" s="1" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="E2" s="1" t="s">
+      <x:c r="F2" s="1" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="F2" s="1" t="s">
+      <x:c r="G2" s="1" t="s">
         <x:v>361</x:v>
       </x:c>
-      <x:c r="G2" s="1" t="s">
+      <x:c r="H2" s="1" t="s">
         <x:v>362</x:v>
       </x:c>
-      <x:c r="H2" s="1" t="s">
+      <x:c r="I2" s="1" t="s">
         <x:v>363</x:v>
       </x:c>
-      <x:c r="I2" s="1" t="s">
+      <x:c r="J2" s="1" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="J2" s="1" t="s">
+      <x:c r="K2" s="1" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="K2" s="1" t="s">
+      <x:c r="L2" s="1" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="L2" s="1" t="s">
+      <x:c r="M2" s="1" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="M2" s="1" t="s">
+      <x:c r="N2" s="1" t="s">
         <x:v>368</x:v>
       </x:c>
-      <x:c r="N2" s="1" t="s">
+      <x:c r="O2" s="1" t="s">
         <x:v>369</x:v>
       </x:c>
-      <x:c r="O2" s="1" t="s">
+      <x:c r="P2" s="1" t="s">
         <x:v>370</x:v>
       </x:c>
-      <x:c r="P2" s="1" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="Q2" s="1" t="s">
-        <x:v>372</x:v>
-      </x:c>
+      <x:c r="Q2" s="1"/>
       <x:c r="R2"/>
       <x:c r="S2"/>
       <x:c r="T2"/>
@@ -10567,19 +10557,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
+      <x:c r="F3" s="1" t="s">
         <x:v>374</x:v>
       </x:c>
-      <x:c r="E3" s="1" t="s">
+      <x:c r="G3" s="1" t="s">
         <x:v>375</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>377</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>21</x:v>
@@ -10588,7 +10578,7 @@
         <x:v>333</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
         <x:v>22</x:v>
@@ -10603,21 +10593,19 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="O3" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P3" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="Q3" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="R3"/>
+      <x:c r="Q3" s="1"/>
+      <x:c r="R3" t="s">
+        <x:v>376</x:v>
+      </x:c>
       <x:c r="S3" s="1" t="s">
-        <x:v>378</x:v>
-      </x:c>
-      <x:c r="T3" s="1" t="s">
-        <x:v>378</x:v>
-      </x:c>
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="T3"/>
     </x:row>
     <x:row r="4" ht="34">
       <x:c r="A4"/>
@@ -10625,26 +10613,26 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
+      <x:c r="F4" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E4" s="1" t="s">
+      <x:c r="G4" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H4"/>
       <x:c r="I4" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="K4" s="1">
         <x:v>0</x:v>
@@ -10654,22 +10642,20 @@
       </x:c>
       <x:c r="M4"/>
       <x:c r="N4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O4" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P4" s="19" t="s">
-        <x:v>386</x:v>
-      </x:c>
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="P4" s="19"/>
       <x:c r="Q4"/>
-      <x:c r="R4"/>
+      <x:c r="R4" t="s">
+        <x:v>198</x:v>
+      </x:c>
       <x:c r="S4" s="33" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="T4" s="33" t="s">
-        <x:v>384</x:v>
-      </x:c>
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="T4"/>
     </x:row>
     <x:row r="5" ht="34">
       <x:c r="A5"/>
@@ -10677,26 +10663,26 @@
         <x:v>207</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
+      <x:c r="F5" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
+      <x:c r="G5" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H5"/>
       <x:c r="I5" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K5" s="1">
         <x:v>0</x:v>
@@ -10706,22 +10692,20 @@
       </x:c>
       <x:c r="M5"/>
       <x:c r="N5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O5" s="1" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="P5" s="19"/>
+      <x:c r="Q5"/>
+      <x:c r="R5" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="S5" s="33" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="P5" s="19" t="s">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="Q5"/>
-      <x:c r="R5"/>
-      <x:c r="S5" s="33" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="T5" s="33" t="s">
-        <x:v>387</x:v>
-      </x:c>
+      <x:c r="T5"/>
     </x:row>
     <x:row r="6" ht="34">
       <x:c r="A6"/>
@@ -10729,26 +10713,26 @@
         <x:v>208</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
+      <x:c r="F6" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="s">
+      <x:c r="G6" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H6"/>
       <x:c r="I6" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="K6" s="1">
         <x:v>0</x:v>
@@ -10758,22 +10742,20 @@
       </x:c>
       <x:c r="M6"/>
       <x:c r="N6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O6" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P6" s="19" t="s">
-        <x:v>386</x:v>
-      </x:c>
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="P6" s="19"/>
       <x:c r="Q6"/>
-      <x:c r="R6"/>
+      <x:c r="R6" t="s">
+        <x:v>200</x:v>
+      </x:c>
       <x:c r="S6" s="33" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="T6" s="33" t="s">
-        <x:v>389</x:v>
-      </x:c>
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="T6"/>
     </x:row>
     <x:row r="7" ht="34">
       <x:c r="A7"/>
@@ -10781,26 +10763,26 @@
         <x:v>209</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
+      <x:c r="F7" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
+      <x:c r="G7" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H7"/>
       <x:c r="I7" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="K7" s="1">
         <x:v>0</x:v>
@@ -10810,22 +10792,20 @@
       </x:c>
       <x:c r="M7"/>
       <x:c r="N7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O7" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P7" s="19" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="P7" s="19"/>
+      <x:c r="Q7"/>
+      <x:c r="R7" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="S7" s="33" t="s">
         <x:v>388</x:v>
       </x:c>
-      <x:c r="Q7"/>
-      <x:c r="R7"/>
-      <x:c r="S7" s="33" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="T7" s="33" t="s">
-        <x:v>390</x:v>
-      </x:c>
+      <x:c r="T7"/>
     </x:row>
     <x:row r="8" ht="34">
       <x:c r="A8"/>
@@ -10833,26 +10813,26 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H8"/>
       <x:c r="I8" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K8" s="1">
         <x:v>0</x:v>
@@ -10862,22 +10842,20 @@
       </x:c>
       <x:c r="M8"/>
       <x:c r="N8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O8" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P8" s="19" t="s">
-        <x:v>393</x:v>
-      </x:c>
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="P8" s="19"/>
       <x:c r="Q8"/>
-      <x:c r="R8"/>
+      <x:c r="R8" t="s">
+        <x:v>41</x:v>
+      </x:c>
       <x:c r="S8" s="33" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="T8" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T8"/>
     </x:row>
     <x:row r="9" ht="34">
       <x:c r="A9"/>
@@ -10885,26 +10863,26 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H9"/>
       <x:c r="I9" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K9" s="1">
         <x:v>0</x:v>
@@ -10914,24 +10892,22 @@
       </x:c>
       <x:c r="M9"/>
       <x:c r="N9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O9" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="P9" s="19" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q9"/>
+      <x:c r="R9" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="S9" s="33" t="s">
         <x:v>398</x:v>
       </x:c>
-      <x:c r="Q9" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R9"/>
-      <x:c r="S9" s="33" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="T9" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+      <x:c r="T9"/>
     </x:row>
     <x:row r="10" ht="34">
       <x:c r="A10"/>
@@ -10939,26 +10915,26 @@
         <x:v>212</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H10"/>
       <x:c r="I10" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K10" s="1">
         <x:v>0</x:v>
@@ -10968,22 +10944,20 @@
       </x:c>
       <x:c r="M10"/>
       <x:c r="N10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O10" s="1" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="P10" s="19"/>
+      <x:c r="Q10"/>
+      <x:c r="R10" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="S10" s="33" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="P10" s="19" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="Q10"/>
-      <x:c r="R10"/>
-      <x:c r="S10" s="33" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="T10" s="33" t="s">
-        <x:v>387</x:v>
-      </x:c>
+      <x:c r="T10"/>
     </x:row>
     <x:row r="11" ht="34">
       <x:c r="A11"/>
@@ -10991,26 +10965,26 @@
         <x:v>214</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>394</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H11"/>
       <x:c r="I11" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="K11" s="1">
         <x:v>0</x:v>
@@ -11020,22 +10994,20 @@
       </x:c>
       <x:c r="M11"/>
       <x:c r="N11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O11" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P11" s="19" t="s">
-        <x:v>403</x:v>
-      </x:c>
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="P11" s="19"/>
       <x:c r="Q11"/>
-      <x:c r="R11"/>
+      <x:c r="R11" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="S11" s="33" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="T11" s="33" t="s">
-        <x:v>384</x:v>
-      </x:c>
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="T11"/>
     </x:row>
     <x:row r="12" ht="17">
       <x:c r="A12"/>
@@ -11043,26 +11015,26 @@
         <x:v>215</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H12"/>
       <x:c r="I12" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K12" s="1">
         <x:v>1</x:v>
@@ -11075,21 +11047,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P12" s="19" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q12" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R12"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q12"/>
+      <x:c r="R12" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="S12" s="33" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="T12" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T12"/>
     </x:row>
     <x:row r="13" ht="17">
       <x:c r="A13"/>
@@ -11097,26 +11067,26 @@
         <x:v>217</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H13"/>
       <x:c r="I13" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K13" s="1">
         <x:v>0</x:v>
@@ -11126,22 +11096,20 @@
       </x:c>
       <x:c r="M13"/>
       <x:c r="N13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O13" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P13" s="19" t="s">
-        <x:v>409</x:v>
-      </x:c>
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="P13" s="19"/>
       <x:c r="Q13"/>
-      <x:c r="R13"/>
+      <x:c r="R13" t="s">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="S13" s="33" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="T13" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
@@ -11149,26 +11117,26 @@
         <x:v>218</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H14"/>
       <x:c r="I14" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K14" s="1">
         <x:v>0</x:v>
@@ -11178,24 +11146,22 @@
       </x:c>
       <x:c r="M14"/>
       <x:c r="N14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O14" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="P14" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="Q14" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R14"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q14"/>
+      <x:c r="R14" t="s">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="S14" s="33" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="T14" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T14"/>
     </x:row>
     <x:row r="15" ht="34">
       <x:c r="A15"/>
@@ -11203,26 +11169,26 @@
         <x:v>219</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H15"/>
       <x:c r="I15" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K15" s="1">
         <x:v>0</x:v>
@@ -11232,24 +11198,22 @@
       </x:c>
       <x:c r="M15"/>
       <x:c r="N15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O15" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="P15" s="19" t="s">
-        <x:v>411</x:v>
-      </x:c>
-      <x:c r="Q15" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R15"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q15"/>
+      <x:c r="R15" t="s">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="S15" s="33" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="T15" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
@@ -11257,26 +11221,26 @@
         <x:v>221</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="F16" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H16"/>
       <x:c r="I16" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>390</x:v>
+        <x:v>388</x:v>
       </x:c>
       <x:c r="K16" s="1">
         <x:v>0</x:v>
@@ -11286,22 +11250,20 @@
       </x:c>
       <x:c r="M16"/>
       <x:c r="N16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O16" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P16" s="1" t="s">
-        <x:v>412</x:v>
-      </x:c>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="P16" s="1"/>
       <x:c r="Q16"/>
-      <x:c r="R16"/>
+      <x:c r="R16" t="s">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="S16" s="33" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="T16" s="33" t="s">
-        <x:v>390</x:v>
-      </x:c>
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="T16"/>
     </x:row>
     <x:row r="17" ht="17">
       <x:c r="A17"/>
@@ -11309,26 +11271,26 @@
         <x:v>222</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H17"/>
       <x:c r="I17" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K17" s="1">
         <x:v>2</x:v>
@@ -11341,21 +11303,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P17" s="19" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q17" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R17"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q17"/>
+      <x:c r="R17" t="s">
+        <x:v>62</x:v>
+      </x:c>
       <x:c r="S17" s="33" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="T17" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T17"/>
     </x:row>
     <x:row r="18" ht="34">
       <x:c r="A18"/>
@@ -11363,26 +11323,26 @@
         <x:v>224</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H18"/>
       <x:c r="I18" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K18" s="1">
         <x:v>0</x:v>
@@ -11392,22 +11352,20 @@
       </x:c>
       <x:c r="M18"/>
       <x:c r="N18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O18" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P18" s="19" t="s">
-        <x:v>414</x:v>
-      </x:c>
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="P18" s="19"/>
       <x:c r="Q18"/>
-      <x:c r="R18"/>
+      <x:c r="R18" t="s">
+        <x:v>67</x:v>
+      </x:c>
       <x:c r="S18" s="33" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T18" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T18"/>
     </x:row>
     <x:row r="19" ht="17">
       <x:c r="A19"/>
@@ -11415,26 +11373,26 @@
         <x:v>225</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H19"/>
       <x:c r="I19" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K19" s="1">
         <x:v>1</x:v>
@@ -11447,21 +11405,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P19" s="19" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q19" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R19"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q19"/>
+      <x:c r="R19" t="s">
+        <x:v>67</x:v>
+      </x:c>
       <x:c r="S19" s="33" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="T19" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T19"/>
     </x:row>
     <x:row r="20" ht="34">
       <x:c r="A20"/>
@@ -11469,28 +11425,28 @@
         <x:v>226</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H20" t="s">
-        <x:v>415</x:v>
+        <x:v>413</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>389</x:v>
+        <x:v>387</x:v>
       </x:c>
       <x:c r="K20" s="1">
         <x:v>0</x:v>
@@ -11500,22 +11456,20 @@
       </x:c>
       <x:c r="M20"/>
       <x:c r="N20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O20" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P20" s="19" t="s">
-        <x:v>416</x:v>
-      </x:c>
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="P20" s="19"/>
       <x:c r="Q20"/>
-      <x:c r="R20"/>
+      <x:c r="R20" t="s">
+        <x:v>71</x:v>
+      </x:c>
       <x:c r="S20" s="33" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="T20" s="33" t="s">
-        <x:v>389</x:v>
-      </x:c>
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="T20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
@@ -11523,26 +11477,26 @@
         <x:v>228</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H21"/>
       <x:c r="I21" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="K21" s="1">
         <x:v>0</x:v>
@@ -11552,22 +11506,20 @@
       </x:c>
       <x:c r="M21"/>
       <x:c r="N21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O21" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P21" s="1" t="s">
-        <x:v>412</x:v>
-      </x:c>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="P21" s="1"/>
       <x:c r="Q21"/>
-      <x:c r="R21"/>
+      <x:c r="R21" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="S21" s="33" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="T21" s="33" t="s">
-        <x:v>417</x:v>
-      </x:c>
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="T21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
@@ -11575,26 +11527,26 @@
         <x:v>229</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="F22" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
+      <x:c r="G22" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H22"/>
       <x:c r="I22" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K22" s="1">
         <x:v>0</x:v>
@@ -11604,24 +11556,22 @@
       </x:c>
       <x:c r="M22"/>
       <x:c r="N22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O22" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="P22" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="Q22" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R22"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q22"/>
+      <x:c r="R22" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="S22" s="33" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="T22" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T22"/>
     </x:row>
     <x:row r="23" ht="34">
       <x:c r="A23"/>
@@ -11629,26 +11579,26 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H23"/>
       <x:c r="I23" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="K23" s="1">
         <x:v>0</x:v>
@@ -11658,22 +11608,20 @@
       </x:c>
       <x:c r="M23"/>
       <x:c r="N23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O23" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P23" s="19" t="s">
-        <x:v>419</x:v>
-      </x:c>
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="P23" s="19"/>
       <x:c r="Q23"/>
-      <x:c r="R23"/>
+      <x:c r="R23" t="s">
+        <x:v>77</x:v>
+      </x:c>
       <x:c r="S23" s="33" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="T23" s="33" t="s">
-        <x:v>418</x:v>
-      </x:c>
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="T23"/>
     </x:row>
     <x:row r="24" ht="34">
       <x:c r="A24"/>
@@ -11681,26 +11629,26 @@
         <x:v>231</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H24"/>
       <x:c r="I24" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="K24" s="1">
         <x:v>0</x:v>
@@ -11710,21 +11658,20 @@
       </x:c>
       <x:c r="M24"/>
       <x:c r="N24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O24" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P24" s="19" t="s">
-        <x:v>414</x:v>
-      </x:c>
-      <x:c r="R24"/>
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="P24" s="19"/>
+      <x:c r="Q24"/>
+      <x:c r="R24" t="s">
+        <x:v>82</x:v>
+      </x:c>
       <x:c r="S24" s="33" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="T24" s="33" t="s">
-        <x:v>420</x:v>
-      </x:c>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="T24"/>
     </x:row>
     <x:row r="25" ht="17">
       <x:c r="A25"/>
@@ -11732,26 +11679,26 @@
         <x:v>232</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H25"/>
       <x:c r="I25" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K25" s="1">
         <x:v>0</x:v>
@@ -11761,22 +11708,20 @@
       </x:c>
       <x:c r="M25"/>
       <x:c r="N25" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O25" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P25" s="19" t="s">
-        <x:v>422</x:v>
-      </x:c>
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="P25" s="19"/>
       <x:c r="Q25"/>
-      <x:c r="R25"/>
+      <x:c r="R25" t="s">
+        <x:v>88</x:v>
+      </x:c>
       <x:c r="S25" s="33" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="T25" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T25"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
@@ -11784,26 +11729,26 @@
         <x:v>234</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
+      <x:c r="F26" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E26" s="1" t="s">
+      <x:c r="G26" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H26"/>
       <x:c r="I26" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="K26" s="1">
         <x:v>0</x:v>
@@ -11813,21 +11758,20 @@
       </x:c>
       <x:c r="M26"/>
       <x:c r="N26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O26" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P26" s="1" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="R26"/>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="P26" s="1"/>
+      <x:c r="Q26"/>
+      <x:c r="R26" t="s">
+        <x:v>93</x:v>
+      </x:c>
       <x:c r="S26" s="33" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="T26" s="33" t="s">
-        <x:v>384</x:v>
-      </x:c>
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="T26"/>
     </x:row>
     <x:row r="27" ht="17">
       <x:c r="A27"/>
@@ -11835,26 +11779,26 @@
         <x:v>235</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H27"/>
       <x:c r="I27" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K27" s="1">
         <x:v>1</x:v>
@@ -11867,21 +11811,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P27" s="19" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q27" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R27"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q27"/>
+      <x:c r="R27" t="s">
+        <x:v>93</x:v>
+      </x:c>
       <x:c r="S27" s="33" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="T27" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T27"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
@@ -11889,26 +11831,26 @@
         <x:v>237</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>423</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H28"/>
       <x:c r="I28" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="K28" s="1">
         <x:v>0</x:v>
@@ -11917,25 +11859,23 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="M28" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="N28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O28" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P28" s="1" t="s">
-        <x:v>425</x:v>
-      </x:c>
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="P28" s="1"/>
       <x:c r="Q28"/>
-      <x:c r="R28"/>
+      <x:c r="R28" t="s">
+        <x:v>98</x:v>
+      </x:c>
       <x:c r="S28" s="33" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="T28" s="33" t="s">
-        <x:v>423</x:v>
-      </x:c>
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="T28"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
@@ -11943,26 +11883,26 @@
         <x:v>238</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H29"/>
       <x:c r="I29" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="K29" s="1">
         <x:v>0</x:v>
@@ -11972,22 +11912,20 @@
       </x:c>
       <x:c r="M29"/>
       <x:c r="N29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O29" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P29" s="1" t="s">
-        <x:v>409</x:v>
-      </x:c>
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="P29" s="1"/>
       <x:c r="Q29"/>
-      <x:c r="R29"/>
+      <x:c r="R29" t="s">
+        <x:v>98</x:v>
+      </x:c>
       <x:c r="S29" s="33" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="T29" s="33" t="s">
-        <x:v>420</x:v>
-      </x:c>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="T29"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
@@ -11995,26 +11933,26 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H30"/>
       <x:c r="I30" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K30" s="1">
         <x:v>0</x:v>
@@ -12024,22 +11962,20 @@
       </x:c>
       <x:c r="M30"/>
       <x:c r="N30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O30" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P30" s="1" t="s">
-        <x:v>412</x:v>
-      </x:c>
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="P30" s="1"/>
       <x:c r="Q30"/>
-      <x:c r="R30"/>
+      <x:c r="R30" t="s">
+        <x:v>103</x:v>
+      </x:c>
       <x:c r="S30" s="33" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="T30" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T30"/>
     </x:row>
     <x:row r="31" ht="17">
       <x:c r="A31"/>
@@ -12047,26 +11983,26 @@
         <x:v>241</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="F31" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E31" s="1" t="s">
+      <x:c r="G31" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G31" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H31"/>
       <x:c r="I31" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K31" s="1">
         <x:v>0</x:v>
@@ -12076,24 +12012,22 @@
       </x:c>
       <x:c r="M31"/>
       <x:c r="N31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O31" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="P31" s="19" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="Q31" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R31"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q31"/>
+      <x:c r="R31" t="s">
+        <x:v>103</x:v>
+      </x:c>
       <x:c r="S31" s="33" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="T31" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T31"/>
     </x:row>
     <x:row r="32" ht="34">
       <x:c r="A32"/>
@@ -12101,28 +12035,28 @@
         <x:v>242</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="H32" t="s">
-        <x:v>427</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="I32" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="K32" s="1">
         <x:v>0</x:v>
@@ -12131,25 +12065,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M32" t="s">
-        <x:v>428</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="N32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O32" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P32" s="19" t="s">
-        <x:v>429</x:v>
-      </x:c>
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="P32" s="19"/>
       <x:c r="Q32"/>
-      <x:c r="R32"/>
+      <x:c r="R32" t="s">
+        <x:v>108</x:v>
+      </x:c>
       <x:c r="S32" s="33" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="T32" s="33" t="s">
-        <x:v>417</x:v>
-      </x:c>
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="T32"/>
     </x:row>
     <x:row r="33" s="32" customFormat="1" ht="34">
       <x:c r="A33" s="8"/>
@@ -12157,26 +12089,26 @@
         <x:v>243</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H33" s="1"/>
       <x:c r="I33" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="K33" s="1">
         <x:v>0</x:v>
@@ -12185,25 +12117,23 @@
         <x:v>1.3</x:v>
       </x:c>
       <x:c r="M33" s="1" t="s">
-        <x:v>430</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="N33" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O33" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P33" s="19" t="s">
-        <x:v>431</x:v>
-      </x:c>
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="P33" s="19"/>
       <x:c r="Q33"/>
-      <x:c r="R33"/>
+      <x:c r="R33" t="s">
+        <x:v>114</x:v>
+      </x:c>
       <x:c r="S33" s="33" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="T33" s="33" t="s">
-        <x:v>417</x:v>
-      </x:c>
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="T33"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
@@ -12211,26 +12141,26 @@
         <x:v>245</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F34" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H34"/>
       <x:c r="I34" s="1" t="s">
-        <x:v>432</x:v>
+        <x:v>430</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K34" s="1">
         <x:v>0</x:v>
@@ -12240,21 +12170,20 @@
       </x:c>
       <x:c r="M34"/>
       <x:c r="N34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O34" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P34" s="1" t="s">
-        <x:v>433</x:v>
-      </x:c>
-      <x:c r="R34"/>
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="P34" s="1"/>
+      <x:c r="Q34"/>
+      <x:c r="R34" t="s">
+        <x:v>117</x:v>
+      </x:c>
       <x:c r="S34" s="33" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="T34" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T34"/>
     </x:row>
     <x:row r="35" ht="17">
       <x:c r="A35"/>
@@ -12262,26 +12191,26 @@
         <x:v>246</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H35"/>
       <x:c r="I35" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K35" s="1">
         <x:v>1</x:v>
@@ -12294,21 +12223,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P35" s="19" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q35" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R35"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q35"/>
+      <x:c r="R35" t="s">
+        <x:v>117</x:v>
+      </x:c>
       <x:c r="S35" s="33" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="T35" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T35"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
@@ -12316,26 +12243,26 @@
         <x:v>248</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D36" s="1" t="s">
+      <x:c r="F36" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E36" s="1" t="s">
+      <x:c r="G36" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H36"/>
       <x:c r="I36" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K36" s="1">
         <x:v>0</x:v>
@@ -12345,24 +12272,22 @@
       </x:c>
       <x:c r="M36"/>
       <x:c r="N36" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O36" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="P36" s="1" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="Q36" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R36"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q36"/>
+      <x:c r="R36" t="s">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="S36" s="33" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="T36" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T36"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37"/>
@@ -12370,26 +12295,26 @@
         <x:v>249</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E37" s="1" t="s">
-        <x:v>423</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H37"/>
       <x:c r="I37" s="1" t="s">
-        <x:v>434</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>423</x:v>
+        <x:v>421</x:v>
       </x:c>
       <x:c r="K37" s="1">
         <x:v>0</x:v>
@@ -12398,25 +12323,23 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M37" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="N37" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O37" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P37" s="1" t="s">
-        <x:v>435</x:v>
-      </x:c>
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="P37" s="1"/>
       <x:c r="Q37"/>
-      <x:c r="R37"/>
+      <x:c r="R37" t="s">
+        <x:v>120</x:v>
+      </x:c>
       <x:c r="S37" s="33" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="T37" s="33" t="s">
-        <x:v>423</x:v>
-      </x:c>
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="T37"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38"/>
@@ -12424,26 +12347,26 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D38" s="1" t="s">
+      <x:c r="F38" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E38" s="1" t="s">
+      <x:c r="G38" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G38" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H38"/>
       <x:c r="I38" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>387</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="K38" s="1">
         <x:v>0</x:v>
@@ -12456,19 +12379,17 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O38" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P38" s="1" t="s">
-        <x:v>436</x:v>
-      </x:c>
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="P38" s="1"/>
       <x:c r="Q38"/>
-      <x:c r="R38"/>
+      <x:c r="R38" t="s">
+        <x:v>123</x:v>
+      </x:c>
       <x:c r="S38" s="33" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="T38" s="33" t="s">
-        <x:v>387</x:v>
-      </x:c>
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="T38"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39"/>
@@ -12476,26 +12397,26 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D39" s="1" t="s">
+      <x:c r="F39" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E39" s="1" t="s">
+      <x:c r="G39" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G39" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H39"/>
       <x:c r="I39" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K39" s="1">
         <x:v>0</x:v>
@@ -12504,27 +12425,25 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="M39" t="s">
-        <x:v>437</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="N39" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="P39" s="1" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="Q39" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R39"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q39"/>
+      <x:c r="R39" t="s">
+        <x:v>126</x:v>
+      </x:c>
       <x:c r="S39" s="33" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="T39" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T39"/>
     </x:row>
     <x:row r="40" ht="34">
       <x:c r="A40"/>
@@ -12532,26 +12451,26 @@
         <x:v>252</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H40"/>
       <x:c r="I40" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="K40" s="1">
         <x:v>3</x:v>
@@ -12560,27 +12479,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M40" t="s">
-        <x:v>440</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="N40" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>439</x:v>
       </x:c>
       <x:c r="P40" s="19" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="Q40" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R40"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q40"/>
+      <x:c r="R40" t="s">
+        <x:v>129</x:v>
+      </x:c>
       <x:c r="S40" s="33" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="T40" s="33" t="s">
-        <x:v>418</x:v>
-      </x:c>
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="T40"/>
     </x:row>
     <x:row r="41" ht="34">
       <x:c r="A41"/>
@@ -12588,28 +12505,28 @@
         <x:v>253</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="F41" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="H41" t="s">
-        <x:v>442</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="I41" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="K41" s="1">
         <x:v>0</x:v>
@@ -12618,25 +12535,23 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M41" t="s">
-        <x:v>443</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="N41" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O41" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P41" s="19" t="s">
-        <x:v>444</x:v>
-      </x:c>
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="P41" s="19"/>
       <x:c r="Q41"/>
-      <x:c r="R41"/>
+      <x:c r="R41" t="s">
+        <x:v>132</x:v>
+      </x:c>
       <x:c r="S41" s="33" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="T41" s="33" t="s">
-        <x:v>420</x:v>
-      </x:c>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="T41"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
@@ -12644,26 +12559,26 @@
         <x:v>254</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="F42" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H42"/>
       <x:c r="I42" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="K42" s="1">
         <x:v>0</x:v>
@@ -12673,22 +12588,20 @@
       </x:c>
       <x:c r="M42"/>
       <x:c r="N42" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O42" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P42" s="1" t="s">
-        <x:v>445</x:v>
-      </x:c>
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="P42" s="1"/>
       <x:c r="Q42"/>
-      <x:c r="R42"/>
+      <x:c r="R42" t="s">
+        <x:v>135</x:v>
+      </x:c>
       <x:c r="S42" s="33" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="T42" s="33" t="s">
-        <x:v>417</x:v>
-      </x:c>
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="T42"/>
     </x:row>
     <x:row r="43" ht="17">
       <x:c r="A43"/>
@@ -12696,26 +12609,26 @@
         <x:v>256</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D43" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E43" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D43" s="1" t="s">
+      <x:c r="F43" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E43" s="1" t="s">
+      <x:c r="G43" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G43" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H43"/>
       <x:c r="I43" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K43" s="1">
         <x:v>0</x:v>
@@ -12725,24 +12638,22 @@
       </x:c>
       <x:c r="M43"/>
       <x:c r="N43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O43" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="P43" s="19" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="Q43" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R43"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q43"/>
+      <x:c r="R43" t="s">
+        <x:v>138</x:v>
+      </x:c>
       <x:c r="S43" s="33" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="T43" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T43"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44"/>
@@ -12750,26 +12661,26 @@
         <x:v>257</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H44"/>
       <x:c r="I44" s="1" t="s">
         <x:v>335</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
-        <x:v>417</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="K44" s="1">
         <x:v>0</x:v>
@@ -12778,25 +12689,23 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="M44" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="N44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O44" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P44" s="1" t="s">
-        <x:v>446</x:v>
-      </x:c>
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="P44" s="1"/>
       <x:c r="Q44"/>
-      <x:c r="R44"/>
+      <x:c r="R44" t="s">
+        <x:v>138</x:v>
+      </x:c>
       <x:c r="S44" s="33" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="T44" s="33" t="s">
-        <x:v>417</x:v>
-      </x:c>
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="T44"/>
     </x:row>
     <x:row r="45" ht="34">
       <x:c r="A45"/>
@@ -12804,25 +12713,25 @@
         <x:v>259</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D45" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="E45" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D45" s="1" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="E45" s="1" t="s">
-        <x:v>381</x:v>
-      </x:c>
       <x:c r="F45" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="I45" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J45" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="K45" s="1">
         <x:v>0</x:v>
@@ -12831,22 +12740,20 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N45" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O45" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P45" s="19" t="s">
-        <x:v>447</x:v>
-      </x:c>
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="P45" s="19"/>
       <x:c r="Q45"/>
-      <x:c r="R45"/>
+      <x:c r="R45" t="s">
+        <x:v>141</x:v>
+      </x:c>
       <x:c r="S45" s="33" t="s">
         <x:v>141</x:v>
       </x:c>
-      <x:c r="T45" s="33" t="s">
-        <x:v>141</x:v>
-      </x:c>
+      <x:c r="T45"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46"/>
@@ -12854,26 +12761,26 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H46"/>
       <x:c r="I46" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J46" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K46" s="1">
         <x:v>3</x:v>
@@ -12886,21 +12793,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P46" s="1" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q46" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R46"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q46"/>
+      <x:c r="R46" t="s">
+        <x:v>141</x:v>
+      </x:c>
       <x:c r="S46" s="33" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="T46" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T46"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47"/>
@@ -12908,26 +12813,26 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E47" s="1" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E47" s="1" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H47"/>
       <x:c r="I47" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J47" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="K47" s="1">
         <x:v>0</x:v>
@@ -12936,25 +12841,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M47" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="N47" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O47" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P47" s="1" t="s">
-        <x:v>449</x:v>
-      </x:c>
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="P47" s="1"/>
       <x:c r="Q47"/>
-      <x:c r="R47"/>
+      <x:c r="R47" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="S47" s="33" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="T47" s="33" t="s">
-        <x:v>420</x:v>
-      </x:c>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="T47"/>
     </x:row>
     <x:row r="48" ht="34">
       <x:c r="A48"/>
@@ -12962,28 +12865,28 @@
         <x:v>263</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>450</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F48" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>426</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="H48" t="s">
-        <x:v>451</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="I48" s="1" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="J48" s="1" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="K48" s="1">
         <x:v>0</x:v>
@@ -12992,27 +12895,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M48" t="s">
-        <x:v>452</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="N48" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O48" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="P48" s="19" t="s">
-        <x:v>453</x:v>
-      </x:c>
-      <x:c r="Q48" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R48"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q48"/>
+      <x:c r="R48" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="S48" s="33" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="T48" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T48"/>
     </x:row>
     <x:row r="49" ht="17">
       <x:c r="A49"/>
@@ -13020,26 +12921,26 @@
         <x:v>265</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D49" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D49" s="1" t="s">
+      <x:c r="F49" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E49" s="1" t="s">
+      <x:c r="G49" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G49" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H49"/>
       <x:c r="I49" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J49" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="K49" s="1">
         <x:v>0</x:v>
@@ -13052,19 +12953,17 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O49" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P49" s="19" t="s">
-        <x:v>436</x:v>
-      </x:c>
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="P49" s="19"/>
       <x:c r="Q49"/>
-      <x:c r="R49"/>
+      <x:c r="R49" t="s">
+        <x:v>148</x:v>
+      </x:c>
       <x:c r="S49" s="33" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="T49" s="33" t="s">
-        <x:v>384</x:v>
-      </x:c>
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="T49"/>
     </x:row>
     <x:row r="50" ht="17">
       <x:c r="A50"/>
@@ -13072,26 +12971,26 @@
         <x:v>266</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E50" s="1" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E50" s="1" t="s">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H50"/>
       <x:c r="I50" s="1" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="J50" s="1" t="s">
-        <x:v>406</x:v>
+        <x:v>404</x:v>
       </x:c>
       <x:c r="K50" s="1">
         <x:v>1</x:v>
@@ -13104,21 +13003,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O50" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>405</x:v>
       </x:c>
       <x:c r="P50" s="19" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="Q50" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R50"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q50"/>
+      <x:c r="R50" t="s">
+        <x:v>148</x:v>
+      </x:c>
       <x:c r="S50" s="33" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="T50" s="33" t="s">
-        <x:v>406</x:v>
-      </x:c>
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="T50"/>
     </x:row>
     <x:row r="51" ht="34">
       <x:c r="A51"/>
@@ -13126,26 +13023,26 @@
         <x:v>267</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="F51" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H51"/>
       <x:c r="I51" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J51" s="1" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="K51" s="1">
         <x:v>0</x:v>
@@ -13158,19 +13055,17 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O51" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P51" s="19" t="s">
-        <x:v>454</x:v>
-      </x:c>
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="P51" s="19"/>
       <x:c r="Q51"/>
-      <x:c r="R51"/>
+      <x:c r="R51" t="s">
+        <x:v>151</x:v>
+      </x:c>
       <x:c r="S51" s="33" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="T51" s="33" t="s">
-        <x:v>392</x:v>
-      </x:c>
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="T51"/>
     </x:row>
     <x:row r="52" ht="17">
       <x:c r="A52"/>
@@ -13178,26 +13073,26 @@
         <x:v>269</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E52" s="1" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E52" s="1" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H52"/>
       <x:c r="I52" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J52" s="1" t="s">
-        <x:v>420</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="K52" s="1">
         <x:v>0</x:v>
@@ -13206,25 +13101,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M52" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="N52" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O52" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P52" s="19" t="s">
-        <x:v>449</x:v>
-      </x:c>
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="P52" s="19"/>
       <x:c r="Q52"/>
-      <x:c r="R52"/>
+      <x:c r="R52" t="s">
+        <x:v>154</x:v>
+      </x:c>
       <x:c r="S52" s="33" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="T52" s="33" t="s">
-        <x:v>420</x:v>
-      </x:c>
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="T52"/>
     </x:row>
     <x:row r="53" ht="34">
       <x:c r="A53"/>
@@ -13232,28 +13125,28 @@
         <x:v>270</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>455</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F53" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="H53" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="I53" s="1" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="J53" s="1" t="s">
         <x:v>395</x:v>
-      </x:c>
-      <x:c r="H53" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="I53" s="1" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="J53" s="1" t="s">
-        <x:v>397</x:v>
       </x:c>
       <x:c r="K53" s="1">
         <x:v>0</x:v>
@@ -13262,24 +13155,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="N53" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O53" s="1" t="s">
-        <x:v>385</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="P53" s="19" t="s">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="Q53" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="R53"/>
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="Q53"/>
+      <x:c r="R53" t="s">
+        <x:v>154</x:v>
+      </x:c>
       <x:c r="S53" s="33" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="T53" s="33" t="s">
-        <x:v>400</x:v>
-      </x:c>
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="T53"/>
     </x:row>
     <x:row r="54" ht="34">
       <x:c r="A54"/>
@@ -13287,26 +13178,26 @@
         <x:v>271</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E54" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D54" s="1" t="s">
+      <x:c r="F54" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E54" s="1" t="s">
+      <x:c r="G54" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F54" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G54" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H54"/>
       <x:c r="I54" s="1" t="s">
-        <x:v>421</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="J54" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="K54" s="1">
         <x:v>0</x:v>
@@ -13315,24 +13206,23 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M54" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="N54" s="1" t="str">
-        <x:v>false</x:v>
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="N54" s="1" t="s">
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O54" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P54" s="19" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="R54"/>
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="P54" s="19"/>
+      <x:c r="Q54"/>
+      <x:c r="R54" t="s">
+        <x:v>157</x:v>
+      </x:c>
       <x:c r="S54" s="33" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="T54" s="33" t="s">
-        <x:v>418</x:v>
-      </x:c>
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="T54"/>
     </x:row>
     <x:row r="55" ht="34">
       <x:c r="A55"/>
@@ -13340,26 +13230,26 @@
         <x:v>272</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E55" s="1" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E55" s="1" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="F55" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H55"/>
       <x:c r="I55" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="J55" s="1" t="s">
-        <x:v>460</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="K55" s="1">
         <x:v>0</x:v>
@@ -13368,27 +13258,25 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M55" t="s">
-        <x:v>461</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="N55" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O55" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="P55" s="19" t="s">
-        <x:v>462</x:v>
-      </x:c>
-      <x:c r="Q55" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R55"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q55"/>
+      <x:c r="R55" t="s">
+        <x:v>160</x:v>
+      </x:c>
       <x:c r="S55" s="33" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="T55" s="33" t="s">
-        <x:v>460</x:v>
-      </x:c>
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="T55"/>
     </x:row>
     <x:row r="56" ht="34">
       <x:c r="A56"/>
@@ -13396,26 +13284,26 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>381</x:v>
-      </x:c>
       <x:c r="F56" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H56"/>
       <x:c r="I56" s="1" t="s">
         <x:v>341</x:v>
       </x:c>
       <x:c r="J56" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="K56" s="1">
         <x:v>0</x:v>
@@ -13428,19 +13316,17 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="O56" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P56" s="19" t="s">
-        <x:v>463</x:v>
-      </x:c>
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="P56" s="19"/>
       <x:c r="Q56"/>
-      <x:c r="R56"/>
+      <x:c r="R56" t="s">
+        <x:v>163</x:v>
+      </x:c>
       <x:c r="S56" s="33" t="s">
         <x:v>163</x:v>
       </x:c>
-      <x:c r="T56" s="33" t="s">
-        <x:v>163</x:v>
-      </x:c>
+      <x:c r="T56"/>
     </x:row>
     <x:row r="57" ht="17">
       <x:c r="A57"/>
@@ -13448,26 +13334,26 @@
         <x:v>275</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E57" s="1" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E57" s="1" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="F57" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="H57"/>
       <x:c r="I57" s="1" t="s">
-        <x:v>439</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="J57" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="K57" s="1">
         <x:v>0</x:v>
@@ -13476,27 +13362,25 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="M57" t="s">
-        <x:v>464</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="N57" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O57" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="P57" s="19" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="Q57" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="R57"/>
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="Q57"/>
+      <x:c r="R57" t="s">
+        <x:v>163</x:v>
+      </x:c>
       <x:c r="S57" s="33" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="T57" s="33" t="s">
-        <x:v>418</x:v>
-      </x:c>
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="T57"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58"/>
@@ -13504,26 +13388,26 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="F58" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="H58"/>
       <x:c r="I58" s="1" t="s">
         <x:v>338</x:v>
       </x:c>
       <x:c r="J58" s="1" t="s">
-        <x:v>418</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="K58" s="1">
         <x:v>0</x:v>
@@ -13533,22 +13417,20 @@
       </x:c>
       <x:c r="M58"/>
       <x:c r="N58" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="O58" s="1" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="P58" s="1" t="s">
-        <x:v>466</x:v>
-      </x:c>
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="P58" s="1"/>
       <x:c r="Q58"/>
-      <x:c r="R58"/>
+      <x:c r="R58" t="s">
+        <x:v>166</x:v>
+      </x:c>
       <x:c r="S58" s="33" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="T58" s="33" t="s">
-        <x:v>418</x:v>
-      </x:c>
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="T58"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59"/>
@@ -13556,26 +13438,26 @@
         <x:v>277</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="D59" s="1" t="s">
+      <x:c r="F59" s="1" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="E59" s="1" t="s">
+      <x:c r="G59" s="1" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="F59" s="1" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="G59" s="1" t="s">
-        <x:v>383</x:v>
       </x:c>
       <x:c r="H59"/>
       <x:c r="I59" s="1" t="s">
-        <x:v>467</x:v>
+        <x:v>465</x:v>
       </x:c>
       <x:c r="J59" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="K59" s="1">
         <x:v>0</x:v>
@@ -13584,25 +13466,23 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M59" t="s">
-        <x:v>424</x:v>
+        <x:v>422</x:v>
       </x:c>
       <x:c r="N59" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="O59" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="P59" s="1" t="s">
-        <x:v>468</x:v>
-      </x:c>
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="P59" s="1"/>
       <x:c r="Q59"/>
-      <x:c r="R59"/>
+      <x:c r="R59" t="s">
+        <x:v>169</x:v>
+      </x:c>
       <x:c r="S59" s="33" t="s">
         <x:v>169</x:v>
       </x:c>
-      <x:c r="T59" s="33" t="s">
-        <x:v>169</x:v>
-      </x:c>
+      <x:c r="T59"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60"/>
@@ -13979,36 +13859,36 @@
     <x:row r="4" ht="17.600000381469727">
       <x:c r="C4" s="1"/>
       <x:c r="D4" s="10" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="E4" s="10" t="s">
+      <x:c r="G4" s="10" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="F4" s="10" t="s">
+      <x:c r="P4" t="s">
         <x:v>471</x:v>
       </x:c>
-      <x:c r="G4" s="10" t="s">
+      <x:c r="Q4" t="s">
         <x:v>472</x:v>
       </x:c>
-      <x:c r="P4" t="s">
+      <x:c r="R4" t="s">
         <x:v>473</x:v>
       </x:c>
-      <x:c r="Q4" t="s">
+      <x:c r="S4" t="s">
         <x:v>474</x:v>
       </x:c>
-      <x:c r="R4" t="s">
+      <x:c r="T4" t="s">
         <x:v>475</x:v>
-      </x:c>
-      <x:c r="S4" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="T4" t="s">
-        <x:v>477</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34">
       <x:c r="C5" s="23" t="s">
-        <x:v>478</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D5" s="18" t="s">
         <x:v>198</x:v>
@@ -14020,7 +13900,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G5" s="18" t="s">
-        <x:v>479</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="H5">
         <x:v>1</x:v>
@@ -14044,7 +13924,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G6" s="20" t="s">
-        <x:v>480</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="H6">
         <x:v>1</x:v>
@@ -14071,7 +13951,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="20" t="s">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="H7">
         <x:v>1</x:v>
@@ -14106,7 +13986,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G9" s="20" t="s">
-        <x:v>482</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="H9">
         <x:v>1</x:v>
@@ -14128,18 +14008,18 @@
       </x:c>
       <x:c r="G10" s="20"/>
       <x:c r="I10" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="J10" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="K10" t="s">
         <x:v>483</x:v>
-      </x:c>
-      <x:c r="J10" t="s">
-        <x:v>484</x:v>
-      </x:c>
-      <x:c r="K10" t="s">
-        <x:v>485</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34">
       <x:c r="C11" s="24" t="s">
-        <x:v>486</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
         <x:v>41</x:v>
@@ -14151,19 +14031,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G11" s="17" t="s">
-        <x:v>487</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="H11">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I11" t="s">
-        <x:v>488</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="J11" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K11" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="P11">
         <x:v>2</x:v>
@@ -14187,13 +14067,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G12" s="20" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="I12" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="J12" t="s">
         <x:v>490</x:v>
-      </x:c>
-      <x:c r="I12" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="J12" t="s">
-        <x:v>492</x:v>
       </x:c>
       <x:c r="P12">
         <x:v>2</x:v>
@@ -14214,19 +14094,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G13" s="20" t="s">
-        <x:v>493</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="H13">
         <x:v>1</x:v>
       </x:c>
       <x:c r="I13" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J13" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K13" t="s">
-        <x:v>495</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="P13">
         <x:v>2</x:v>
@@ -14247,16 +14127,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G14" s="20" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="I14" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="J14" t="s">
         <x:v>496</x:v>
       </x:c>
-      <x:c r="I14" t="s">
+      <x:c r="K14" t="s">
         <x:v>497</x:v>
-      </x:c>
-      <x:c r="J14" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="K14" t="s">
-        <x:v>499</x:v>
       </x:c>
       <x:c r="P14">
         <x:v>2</x:v>
@@ -14274,16 +14154,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G15" s="20" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="I15" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="J15" t="s">
         <x:v>500</x:v>
       </x:c>
-      <x:c r="I15" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="J15" t="s">
-        <x:v>502</x:v>
-      </x:c>
       <x:c r="K15" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="P15">
         <x:v>2</x:v>
@@ -14307,16 +14187,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G16" s="20" t="s">
-        <x:v>503</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="I16" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="J16" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="K16" t="s">
-        <x:v>495</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="P16">
         <x:v>2</x:v>
@@ -14334,16 +14214,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="20" t="s">
-        <x:v>505</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="I17" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="J17" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K17" t="s">
-        <x:v>506</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="P17">
         <x:v>2</x:v>
@@ -14372,16 +14252,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G19" s="20" t="s">
-        <x:v>507</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="I19" t="s">
-        <x:v>508</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="J19" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="K19" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="P19">
         <x:v>2</x:v>
@@ -14409,16 +14289,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G21" s="20" t="s">
-        <x:v>509</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="I21" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J21" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K21" t="s">
-        <x:v>510</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="P21">
         <x:v>2</x:v>
@@ -14447,16 +14327,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G23" s="20" t="s">
-        <x:v>511</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="I23" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J23" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K23" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="P23">
         <x:v>2</x:v>
@@ -14492,16 +14372,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G25" s="20" t="s">
-        <x:v>513</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="I25" t="s">
-        <x:v>488</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="J25" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="K25" t="s">
-        <x:v>514</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="P25">
         <x:v>2</x:v>
@@ -14521,7 +14401,7 @@
     </x:row>
     <x:row r="27" ht="51">
       <x:c r="C27" s="27" t="s">
-        <x:v>515</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="D27" s="8" t="s">
         <x:v>82</x:v>
@@ -14530,16 +14410,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="G27" s="20" t="s">
-        <x:v>516</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="I27" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J27" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="K27" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="P27">
         <x:v>3</x:v>
@@ -14569,13 +14449,13 @@
       </x:c>
       <x:c r="F28" s="20"/>
       <x:c r="G28" s="20" t="s">
-        <x:v>518</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="I28" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="K28" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="V28" s="8"/>
       <x:c r="W28" s="20"/>
@@ -14589,16 +14469,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="G29" s="20" t="s">
-        <x:v>519</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="I29" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="J29" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="K29" t="s">
         <x:v>497</x:v>
-      </x:c>
-      <x:c r="J29" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="K29" t="s">
-        <x:v>499</x:v>
       </x:c>
       <x:c r="V29" s="8"/>
       <x:c r="W29" s="20"/>
@@ -14613,16 +14493,16 @@
       </x:c>
       <x:c r="F30" s="20"/>
       <x:c r="G30" s="20" t="s">
-        <x:v>520</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="I30" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J30" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="K30" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="V30" s="20"/>
       <x:c r="W30" s="8"/>
@@ -14637,16 +14517,16 @@
       </x:c>
       <x:c r="F31" s="20"/>
       <x:c r="G31" s="20" t="s">
-        <x:v>521</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="I31" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J31" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K31" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="V31" s="20"/>
       <x:c r="W31" s="19"/>
@@ -14660,16 +14540,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="G32" s="20" t="s">
-        <x:v>522</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="I32" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J32" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K32" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -14695,16 +14575,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="G35" s="20" t="s">
-        <x:v>523</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="I35" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="J35" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K35" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -14730,16 +14610,16 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="G38" s="20" t="s">
-        <x:v>524</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="I38" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="J38" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="K38" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -14767,13 +14647,13 @@
       </x:c>
       <x:c r="F41" s="20"/>
       <x:c r="G41" s="20" t="s">
-        <x:v>525</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="I41" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J41" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -14800,16 +14680,16 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="G44" s="20" t="s">
-        <x:v>526</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="I44" t="s">
-        <x:v>488</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="J44" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K44" t="s">
-        <x:v>495</x:v>
+        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -14823,7 +14703,7 @@
     </x:row>
     <x:row r="46" ht="34">
       <x:c r="C46" s="29" t="s">
-        <x:v>527</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="D46" s="15" t="s">
         <x:v>126</x:v>
@@ -14835,10 +14715,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G46" s="20" t="s">
-        <x:v>528</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="I46" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="P46">
         <x:v>4</x:v>
@@ -14871,10 +14751,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G48" s="20" t="s">
-        <x:v>529</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="I48" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -14895,16 +14775,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G50" s="20" t="s">
-        <x:v>530</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="I50" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J50" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K50" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -14925,16 +14805,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G52" s="20" t="s">
-        <x:v>531</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="I52" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J52" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="K52" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="17.600000381469727">
@@ -14957,16 +14837,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G54" s="20" t="s">
-        <x:v>532</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="I54" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J54" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="K54" t="s">
-        <x:v>506</x:v>
+        <x:v>504</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -14987,10 +14867,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G56" s="20" t="s">
-        <x:v>533</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="I56" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -15007,7 +14887,7 @@
     </x:row>
     <x:row r="59" ht="68">
       <x:c r="C59" s="31" t="s">
-        <x:v>534</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="D59" s="10" t="s">
         <x:v>145</x:v>
@@ -15019,16 +14899,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G59" s="19" t="s">
-        <x:v>535</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="I59" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J59" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K59" t="s">
-        <x:v>517</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="P59">
         <x:v>4</x:v>
@@ -15061,16 +14941,16 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G61" s="20" t="s">
-        <x:v>536</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="I61" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="J61" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K61" t="s">
-        <x:v>512</x:v>
+        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -15088,16 +14968,16 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="G63" s="19" t="s">
-        <x:v>537</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="I63" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="J63" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K63" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -15117,16 +14997,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="G65" s="19" t="s">
-        <x:v>538</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="I65" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="J65" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="K65" t="s">
-        <x:v>489</x:v>
+        <x:v>487</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -15155,10 +15035,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="G68" s="19" t="s">
-        <x:v>539</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="I68" t="s">
-        <x:v>494</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="K68" s="19"/>
     </x:row>
@@ -15188,10 +15068,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="G71" s="19" t="s">
-        <x:v>540</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="I71" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -15212,7 +15092,7 @@
     </x:row>
     <x:row r="74" ht="34">
       <x:c r="C74" s="20" t="s">
-        <x:v>541</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="D74" s="15" t="s">
         <x:v>163</x:v>
@@ -15224,7 +15104,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="G74" s="19" t="s">
-        <x:v>542</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -15255,7 +15135,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="G77" s="20" t="s">
-        <x:v>543</x:v>
+        <x:v>541</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -15286,7 +15166,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>544</x:v>
+        <x:v>542</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -15316,7 +15196,7 @@
     </x:row>
     <x:row r="88" ht="51">
       <x:c r="G88" s="19" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15369,16 +15249,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="E4" s="10" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="F4" s="10" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="E4" s="10" t="s">
+      <x:c r="G4" s="10" t="s">
         <x:v>470</x:v>
-      </x:c>
-      <x:c r="F4" s="10" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="G4" s="10" t="s">
-        <x:v>472</x:v>
       </x:c>
       <x:c r="H4" s="15"/>
       <x:c r="I4" s="15"/>
@@ -15387,35 +15267,35 @@
       </x:c>
       <x:c r="K4" s="1"/>
       <x:c r="L4" s="10" t="s">
+        <x:v>467</x:v>
+      </x:c>
+      <x:c r="M4" s="10" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="N4" s="10" t="s">
         <x:v>469</x:v>
       </x:c>
-      <x:c r="M4" s="10" t="s">
+      <x:c r="O4" s="10" t="s">
         <x:v>470</x:v>
-      </x:c>
-      <x:c r="N4" s="10" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="O4" s="10" t="s">
-        <x:v>472</x:v>
       </x:c>
       <x:c r="P4" s="15"/>
       <x:c r="Q4" s="10" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="R4" s="10" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="S4" s="10" t="s">
         <x:v>546</x:v>
       </x:c>
-      <x:c r="R4" s="10" t="s">
+      <x:c r="T4" s="10" t="s">
         <x:v>547</x:v>
       </x:c>
-      <x:c r="S4" s="10" t="s">
+      <x:c r="U4" s="10" t="s">
         <x:v>548</x:v>
       </x:c>
-      <x:c r="T4" s="10" t="s">
+      <x:c r="V4" s="1" t="s">
         <x:v>549</x:v>
-      </x:c>
-      <x:c r="U4" s="10" t="s">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="V4" s="1" t="s">
-        <x:v>551</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34">
@@ -15423,7 +15303,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>552</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>36</x:v>
@@ -15432,13 +15312,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G5" s="17" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="H5" s="18"/>
       <x:c r="I5" s="18"/>
       <x:c r="J5" s="18"/>
       <x:c r="K5" s="23" t="s">
-        <x:v>478</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="L5" s="18" t="s">
         <x:v>198</x:v>
@@ -15450,23 +15330,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O5" s="18" t="s">
-        <x:v>479</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="P5" s="18"/>
       <x:c r="Q5" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R5" s="1" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="S5" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="T5" s="1" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="S5" s="1" t="s">
+      <x:c r="U5" s="1" t="s">
         <x:v>555</x:v>
-      </x:c>
-      <x:c r="T5" s="1" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="U5" s="1" t="s">
-        <x:v>557</x:v>
       </x:c>
       <x:c r="V5" s="1">
         <x:v>3</x:v>
@@ -15481,7 +15361,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="11" t="s">
-        <x:v>558</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>36</x:v>
@@ -15490,7 +15370,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G6" s="19" t="s">
-        <x:v>559</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="H6" s="20"/>
       <x:c r="I6" s="20"/>
@@ -15506,23 +15386,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O6" s="20" t="s">
-        <x:v>480</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="P6" s="20"/>
       <x:c r="Q6" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="R6" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="S6" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T6" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="U6" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="V6" s="1">
         <x:v>5</x:v>
@@ -15537,7 +15417,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>562</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>36</x:v>
@@ -15546,7 +15426,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G7" s="19" t="s">
-        <x:v>563</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="H7" s="20"/>
       <x:c r="I7" s="20"/>
@@ -15562,23 +15442,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O7" s="20" t="s">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="P7" s="20"/>
       <x:c r="Q7" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="R7" s="1" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="S7" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="T7" s="1" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="S7" s="1" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="T7" s="1" t="s">
-        <x:v>556</x:v>
-      </x:c>
       <x:c r="U7" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="W7" s="1">
         <x:v>30</x:v>
@@ -15589,7 +15469,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>565</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>36</x:v>
@@ -15598,7 +15478,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G8" s="19" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="H8" s="20"/>
       <x:c r="I8" s="20"/>
@@ -15611,19 +15491,19 @@
       <x:c r="O8" s="20"/>
       <x:c r="P8" s="20"/>
       <x:c r="Q8" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="R8" s="1" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="S8" s="1" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="T8" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="U8" s="1" t="s">
         <x:v>567</x:v>
-      </x:c>
-      <x:c r="S8" s="1" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="T8" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="U8" s="1" t="s">
-        <x:v>569</x:v>
       </x:c>
       <x:c r="V8" s="1">
         <x:v>2</x:v>
@@ -15643,7 +15523,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G9" s="19" t="s">
-        <x:v>570</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="H9" s="20"/>
       <x:c r="I9" s="20"/>
@@ -15659,23 +15539,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O9" s="20" t="s">
-        <x:v>482</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="P9" s="20"/>
       <x:c r="Q9" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="R9" s="1" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="S9" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="T9" s="1" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="S9" s="1" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="T9" s="1" t="s">
-        <x:v>556</x:v>
-      </x:c>
       <x:c r="U9" s="1" t="s">
-        <x:v>571</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="V9" s="1">
         <x:v>8</x:v>
@@ -15684,7 +15564,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="X9" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>570</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34">
@@ -15701,7 +15581,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G10" s="19" t="s">
-        <x:v>573</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="H10" s="20"/>
       <x:c r="I10" s="20"/>
@@ -15713,19 +15593,19 @@
       <x:c r="O10" s="20"/>
       <x:c r="P10" s="20"/>
       <x:c r="Q10" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R10" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="S10" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T10" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="U10" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="V10" s="1">
         <x:v>0.4</x:v>
@@ -15739,7 +15619,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>36</x:v>
@@ -15748,13 +15628,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G11" s="19" t="s">
-        <x:v>577</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="H11" s="20"/>
       <x:c r="I11" s="20"/>
       <x:c r="J11" s="20"/>
       <x:c r="K11" s="24" t="s">
-        <x:v>486</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="L11" s="10" t="s">
         <x:v>41</x:v>
@@ -15766,23 +15646,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O11" s="17" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="P11" s="20"/>
       <x:c r="Q11" s="1" t="s">
-        <x:v>498</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="R11" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="S11" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T11" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="U11" s="1" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="V11" s="1">
         <x:v>10</x:v>
@@ -15796,7 +15676,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D12" s="11" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>36</x:v>
@@ -15805,7 +15685,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G12" s="19" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="H12" s="20"/>
       <x:c r="K12" s="24"/>
@@ -15819,23 +15699,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O12" s="20" t="s">
-        <x:v>582</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="P12" s="20"/>
       <x:c r="Q12" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="R12" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="S12" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T12" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="U12" s="1" t="s">
-        <x:v>584</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="V12" s="1">
         <x:v>5</x:v>
@@ -15844,7 +15724,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AD12" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>583</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="51">
@@ -15861,7 +15741,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G13" s="19" t="s">
-        <x:v>586</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="I13" s="8">
         <x:v>4</x:v>
@@ -15880,23 +15760,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O13" s="20" t="s">
-        <x:v>587</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="P13" s="20"/>
       <x:c r="Q13" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R13" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="S13" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T13" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="U13" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="V13" s="1">
         <x:v>0.15</x:v>
@@ -15911,7 +15791,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="12" t="s">
-        <x:v>590</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>36</x:v>
@@ -15920,7 +15800,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="I14" s="8">
         <x:v>2</x:v>
@@ -15939,34 +15819,34 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O14" s="20" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="Q14" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="R14" s="1" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="S14" s="1" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="T14" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="U14" s="1" t="s">
         <x:v>592</x:v>
-      </x:c>
-      <x:c r="Q14" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="R14" s="1" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="S14" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="T14" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="U14" s="1" t="s">
-        <x:v>594</x:v>
       </x:c>
       <x:c r="V14" s="1">
         <x:v>8</x:v>
       </x:c>
       <x:c r="AC14" s="1" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="AD14" s="1" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="AE14" s="1" t="s">
         <x:v>595</x:v>
-      </x:c>
-      <x:c r="AD14" s="1" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="AE14" s="1" t="s">
-        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="51">
@@ -15983,7 +15863,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G15" s="21" t="s">
-        <x:v>598</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="H15" s="20"/>
       <x:c r="I15" s="20">
@@ -16003,23 +15883,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O15" s="20" t="s">
-        <x:v>599</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="P15" s="20"/>
       <x:c r="Q15" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R15" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="S15" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T15" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="U15" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="V15" s="1">
         <x:v>0.2</x:v>
@@ -16029,13 +15909,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AC15" s="1" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="AD15" s="1" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="AE15" s="1" t="s">
         <x:v>601</x:v>
-      </x:c>
-      <x:c r="AD15" s="1" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="AE15" s="1" t="s">
-        <x:v>603</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34">
@@ -16043,7 +15923,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>604</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>36</x:v>
@@ -16052,7 +15932,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="19" t="s">
-        <x:v>605</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="H16" s="20"/>
       <x:c r="I16" s="20"/>
@@ -16068,38 +15948,38 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O16" s="20" t="s">
-        <x:v>606</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="P16" s="20"/>
       <x:c r="Q16" s="1" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="R16" s="1" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="S16" s="1" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="T16" s="1" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="U16" s="1" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="Y16" s="1" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="Z16" s="1" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="AA16" s="1" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="AD16" s="1" t="s">
         <x:v>607</x:v>
       </x:c>
-      <x:c r="R16" s="1" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="S16" s="1" t="s">
-        <x:v>488</x:v>
-      </x:c>
-      <x:c r="T16" s="1" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="U16" s="1" t="s">
+      <x:c r="AE16" s="1" t="s">
         <x:v>608</x:v>
-      </x:c>
-      <x:c r="Y16" s="1" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="Z16" s="1" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="AA16" s="1" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="AD16" s="1" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="AE16" s="1" t="s">
-        <x:v>610</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="51">
@@ -16107,7 +15987,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="D17" s="13" t="s">
-        <x:v>611</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>36</x:v>
@@ -16116,7 +15996,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G17" s="19" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H17" s="20"/>
       <x:c r="I17" s="20"/>
@@ -16132,26 +16012,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O17" s="20" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="P17" s="20"/>
       <x:c r="Q17" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="R17" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="S17" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="T17" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="U17" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="X17" s="1" t="s">
-        <x:v>615</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="Y17" s="1">
         <x:v>30</x:v>
@@ -16160,10 +16040,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AD17" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="AE17" s="1" t="s">
-        <x:v>617</x:v>
+        <x:v>615</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="51">
@@ -16171,7 +16051,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="10" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>29</x:v>
@@ -16180,7 +16060,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G18" s="19" t="s">
-        <x:v>619</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="H18" s="20"/>
       <x:c r="I18" s="20"/>
@@ -16193,19 +16073,19 @@
       <x:c r="O18" s="20"/>
       <x:c r="P18" s="20"/>
       <x:c r="Q18" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R18" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S18" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T18" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="U18" s="1" t="s">
-        <x:v>621</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="V18" s="1">
         <x:v>1</x:v>
@@ -16215,7 +16095,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="X18" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="Y18" s="1">
         <x:v>90</x:v>
@@ -16227,13 +16107,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AC18" s="1" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="AD18" s="1" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="AE18" s="1" t="s">
         <x:v>623</x:v>
-      </x:c>
-      <x:c r="AD18" s="1" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="AE18" s="1" t="s">
-        <x:v>625</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="51">
@@ -16241,7 +16121,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D19" s="12" t="s">
-        <x:v>626</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>36</x:v>
@@ -16250,7 +16130,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G19" s="22" t="s">
-        <x:v>627</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="H19" s="20"/>
       <x:c r="I19" s="20"/>
@@ -16266,26 +16146,26 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O19" s="20" t="s">
-        <x:v>628</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="P19" s="20"/>
       <x:c r="Q19" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="R19" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S19" s="1" t="s">
-        <x:v>568</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="T19" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="U19" s="1" t="s">
-        <x:v>629</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="X19" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="Y19" s="1">
         <x:v>150</x:v>
@@ -16297,10 +16177,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD19" s="1" t="s">
-        <x:v>631</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="AE19" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>630</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="17">
@@ -16314,7 +16194,7 @@
       <x:c r="N20" s="20"/>
       <x:c r="O20" s="20"/>
       <x:c r="X20" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="Y20" s="1">
         <x:v>240</x:v>
@@ -16326,10 +16206,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AD20" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="AE20" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>633</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="51">
@@ -16337,7 +16217,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="D21" s="11" t="s">
-        <x:v>636</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>29</x:v>
@@ -16346,7 +16226,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G21" s="19" t="s">
-        <x:v>637</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="H21" s="20"/>
       <x:c r="I21" s="20"/>
@@ -16362,23 +16242,23 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O21" s="20" t="s">
-        <x:v>638</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="P21" s="20"/>
       <x:c r="Q21" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R21" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S21" s="1" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="T21" s="1" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="U21" s="1" t="s">
         <x:v>639</x:v>
-      </x:c>
-      <x:c r="T21" s="1" t="s">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="U21" s="1" t="s">
-        <x:v>641</x:v>
       </x:c>
       <x:c r="V21" s="1">
         <x:v>1.5</x:v>
@@ -16388,10 +16268,10 @@
         <x:v>2.6999999999999997</x:v>
       </x:c>
       <x:c r="AD21" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="AE21" s="1" t="s">
-        <x:v>643</x:v>
+        <x:v>641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="34">
@@ -16408,7 +16288,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G22" s="20" t="s">
-        <x:v>644</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="H22" s="20"/>
       <x:c r="I22" s="20"/>
@@ -16420,16 +16300,16 @@
       <x:c r="N22" s="20"/>
       <x:c r="P22" s="20"/>
       <x:c r="Q22" s="1" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="R22" s="1" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="S22" s="1" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="T22" s="1" t="s">
         <x:v>645</x:v>
-      </x:c>
-      <x:c r="R22" s="1" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="S22" s="1" t="s">
-        <x:v>497</x:v>
-      </x:c>
-      <x:c r="T22" s="1" t="s">
-        <x:v>647</x:v>
       </x:c>
       <x:c r="V22" s="1">
         <x:v>10</x:v>
@@ -16439,13 +16319,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="AC22" s="1" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="AD22" s="1" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="AE22" s="1" t="s">
         <x:v>648</x:v>
-      </x:c>
-      <x:c r="AD22" s="1" t="s">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="AE22" s="1" t="s">
-        <x:v>650</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="51">
@@ -16462,7 +16342,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G23" s="20" t="s">
-        <x:v>651</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="H23" s="20"/>
       <x:c r="I23" s="20"/>
@@ -16478,29 +16358,29 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O23" s="20" t="s">
-        <x:v>511</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="P23" s="20"/>
       <x:c r="Q23" s="1" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="R23" s="1" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="S23" s="1" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="T23" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="U23" s="1" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="AD23" s="1" t="s">
         <x:v>652</x:v>
       </x:c>
-      <x:c r="R23" s="1" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="S23" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="T23" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="U23" s="1" t="s">
+      <x:c r="AE23" s="1" t="s">
         <x:v>653</x:v>
-      </x:c>
-      <x:c r="AD23" s="1" t="s">
-        <x:v>654</x:v>
-      </x:c>
-      <x:c r="AE23" s="1" t="s">
-        <x:v>655</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="51">
@@ -16517,7 +16397,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G24" s="20" t="s">
-        <x:v>656</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="H24" s="20"/>
       <x:c r="I24" s="20"/>
@@ -16530,19 +16410,19 @@
       <x:c r="O24" s="20"/>
       <x:c r="P24" s="20"/>
       <x:c r="Q24" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R24" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S24" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="T24" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="U24" s="1" t="s">
-        <x:v>657</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="V24" s="1">
         <x:v>1.2</x:v>
@@ -16552,10 +16432,10 @@
         <x:v>21.599999999999998</x:v>
       </x:c>
       <x:c r="AD24" s="1" t="s">
-        <x:v>658</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="AE24" s="1" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="34">
@@ -16574,16 +16454,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="O25" s="20" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="AC25" s="1" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="AD25" s="1" t="s">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="AC25" s="1" t="s">
+      <x:c r="AE25" s="1" t="s">
         <x:v>661</x:v>
-      </x:c>
-      <x:c r="AD25" s="1" t="s">
-        <x:v>662</x:v>
-      </x:c>
-      <x:c r="AE25" s="1" t="s">
-        <x:v>663</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34">
@@ -16591,7 +16471,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="D26" s="11" t="s">
-        <x:v>664</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>36</x:v>
@@ -16600,7 +16480,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G26" s="20" t="s">
-        <x:v>665</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="H26" s="20"/>
       <x:c r="I26" s="20"/>
@@ -16613,19 +16493,19 @@
       <x:c r="O26" s="20"/>
       <x:c r="P26" s="20"/>
       <x:c r="Q26" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="R26" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S26" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T26" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="U26" s="1" t="s">
-        <x:v>666</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="V26" s="1">
         <x:v>10</x:v>
@@ -16635,13 +16515,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AC26" s="1" t="s">
-        <x:v>470</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="AD26" s="1" t="s">
-        <x:v>667</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="AE26" s="1" t="s">
-        <x:v>668</x:v>
+        <x:v>666</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -16651,10 +16531,10 @@
       <x:c r="G27" s="8"/>
       <x:c r="M27" s="20"/>
       <x:c r="AD27" s="1" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="AE27" s="1" t="s">
         <x:v>667</x:v>
-      </x:c>
-      <x:c r="AE27" s="1" t="s">
-        <x:v>669</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="34">
@@ -16662,7 +16542,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="D28" s="11" t="s">
-        <x:v>670</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>36</x:v>
@@ -16671,7 +16551,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G28" s="20" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="H28" s="20"/>
       <x:c r="I28" s="20"/>
@@ -16682,19 +16562,19 @@
       <x:c r="O28" s="20"/>
       <x:c r="P28" s="20"/>
       <x:c r="Q28" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="R28" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S28" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T28" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="U28" s="1" t="s">
-        <x:v>673</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="V28" s="1">
         <x:v>10</x:v>
@@ -16704,13 +16584,13 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="AC28" s="1" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="AD28" s="1" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="AE28" s="1" t="s">
         <x:v>674</x:v>
-      </x:c>
-      <x:c r="AD28" s="1" t="s">
-        <x:v>675</x:v>
-      </x:c>
-      <x:c r="AE28" s="1" t="s">
-        <x:v>676</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -16725,10 +16605,10 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="AD29" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="AE29" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>676</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="52" customHeight="1">
@@ -16745,7 +16625,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G30" s="20" t="s">
-        <x:v>679</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="H30" s="20"/>
       <x:c r="I30" s="20">
@@ -16763,19 +16643,19 @@
       <x:c r="O30" s="20"/>
       <x:c r="P30" s="20"/>
       <x:c r="Q30" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R30" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S30" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T30" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="U30" s="1" t="s">
-        <x:v>680</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="V30" s="1">
         <x:v>0.2</x:v>
@@ -16785,13 +16665,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AC30" s="1" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="AD30" s="1" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="AE30" s="1" t="s">
         <x:v>681</x:v>
-      </x:c>
-      <x:c r="AD30" s="1" t="s">
-        <x:v>682</x:v>
-      </x:c>
-      <x:c r="AE30" s="1" t="s">
-        <x:v>683</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="34">
@@ -16808,7 +16688,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G31" s="20" t="s">
-        <x:v>684</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="H31" s="20"/>
       <x:c r="I31" s="20"/>
@@ -16821,19 +16701,19 @@
       <x:c r="O31" s="20"/>
       <x:c r="P31" s="20"/>
       <x:c r="Q31" s="1" t="s">
-        <x:v>685</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="R31" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S31" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T31" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="U31" s="1" t="s">
-        <x:v>686</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="V31" s="1">
         <x:v>1.5</x:v>
@@ -16843,10 +16723,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AD31" s="1" t="s">
-        <x:v>687</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="AE31" s="1" t="s">
-        <x:v>688</x:v>
+        <x:v>686</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="51">
@@ -16863,7 +16743,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G32" s="20" t="s">
-        <x:v>689</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="H32" s="20"/>
       <x:c r="I32" s="20"/>
@@ -16877,19 +16757,19 @@
       <x:c r="O32" s="20"/>
       <x:c r="P32" s="20"/>
       <x:c r="Q32" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="R32" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S32" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="T32" s="1" t="s">
-        <x:v>647</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="U32" s="1" t="s">
-        <x:v>690</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="V32" s="1">
         <x:v>0.8</x:v>
@@ -16899,13 +16779,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AC32" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="AD32" s="1" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="AE32" s="1" t="s">
-        <x:v>692</x:v>
+        <x:v>690</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="17">
@@ -16920,10 +16800,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AD33" s="1" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="AE33" s="1" t="s">
         <x:v>691</x:v>
-      </x:c>
-      <x:c r="AE33" s="1" t="s">
-        <x:v>693</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -16935,10 +16815,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="AD34" s="1" t="s">
-        <x:v>694</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="AE34" s="25" t="s">
-        <x:v>695</x:v>
+        <x:v>693</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="51">
@@ -16955,7 +16835,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G35" s="20" t="s">
-        <x:v>696</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="H35" s="20"/>
       <x:c r="I35" s="20"/>
@@ -16971,19 +16851,19 @@
       <x:c r="O35" s="20"/>
       <x:c r="P35" s="20"/>
       <x:c r="Q35" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R35" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S35" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T35" s="1" t="s">
-        <x:v>697</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="U35" s="1" t="s">
-        <x:v>698</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="V35" s="1">
         <x:v>1</x:v>
@@ -16993,13 +16873,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AC35" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="AD35" s="1" t="s">
-        <x:v>699</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="AE35" s="25" t="s">
-        <x:v>700</x:v>
+        <x:v>698</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="17">
@@ -17009,16 +16889,16 @@
       <x:c r="G36" s="8"/>
       <x:c r="L36" s="20"/>
       <x:c r="M36" s="20" t="s">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="AC36" s="1" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="AD36" s="1" t="s">
         <x:v>701</x:v>
       </x:c>
-      <x:c r="AC36" s="1" t="s">
+      <x:c r="AE36" s="25" t="s">
         <x:v>702</x:v>
-      </x:c>
-      <x:c r="AD36" s="1" t="s">
-        <x:v>703</x:v>
-      </x:c>
-      <x:c r="AE36" s="25" t="s">
-        <x:v>704</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="17">
@@ -17030,7 +16910,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M37" s="20" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="34">
@@ -17038,7 +16918,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
-        <x:v>705</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
         <x:v>29</x:v>
@@ -17047,7 +16927,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G38" s="20" t="s">
-        <x:v>706</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="H38" s="20"/>
       <x:c r="I38" s="20"/>
@@ -17060,19 +16940,19 @@
       <x:c r="O38" s="20"/>
       <x:c r="P38" s="20"/>
       <x:c r="Q38" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="R38" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S38" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="T38" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="U38" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -17087,10 +16967,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="AD39" s="1" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="AE39" s="1" t="s">
         <x:v>595</x:v>
-      </x:c>
-      <x:c r="AE39" s="1" t="s">
-        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="34">
@@ -17107,7 +16987,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G40" s="20" t="s">
-        <x:v>707</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="H40" s="20"/>
       <x:c r="I40" s="20"/>
@@ -17121,29 +17001,29 @@
       <x:c r="O40" s="20"/>
       <x:c r="P40" s="20"/>
       <x:c r="Q40" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R40" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S40" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T40" s="1" t="s">
-        <x:v>647</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="U40" s="1" t="s">
-        <x:v>708</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="W40" s="1" t="n">
         <x:f>4</x:f>
         <x:v>4</x:v>
       </x:c>
       <x:c r="AD40" s="1" t="s">
-        <x:v>709</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="AE40" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -17154,10 +17034,10 @@
       <x:c r="L41" s="20"/>
       <x:c r="M41" s="20"/>
       <x:c r="AD41" s="1" t="s">
-        <x:v>711</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="AE41" s="1" t="s">
-        <x:v>712</x:v>
+        <x:v>710</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="51">
@@ -17174,7 +17054,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G42" s="20" t="s">
-        <x:v>713</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="H42" s="20"/>
       <x:c r="I42" s="20"/>
@@ -17186,29 +17066,29 @@
       <x:c r="O42" s="20"/>
       <x:c r="P42" s="20"/>
       <x:c r="Q42" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R42" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S42" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T42" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="U42" s="1" t="s">
-        <x:v>714</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="W42" s="1" t="n">
         <x:f>2*5</x:f>
         <x:v>10</x:v>
       </x:c>
       <x:c r="AD42" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="AE42" s="1" t="s">
-        <x:v>716</x:v>
+        <x:v>714</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="17.600000381469727" customHeight="1">
@@ -17217,10 +17097,10 @@
       </x:c>
       <x:c r="G43" s="8"/>
       <x:c r="AD43" s="1" t="s">
-        <x:v>717</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="AE43" s="1" t="s">
-        <x:v>718</x:v>
+        <x:v>716</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="34">
@@ -17228,7 +17108,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="D44" s="10" t="s">
-        <x:v>719</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
         <x:v>29</x:v>
@@ -17237,7 +17117,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G44" s="20" t="s">
-        <x:v>720</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="H44" s="20"/>
       <x:c r="I44" s="20"/>
@@ -17249,19 +17129,19 @@
       <x:c r="O44" s="20"/>
       <x:c r="P44" s="20"/>
       <x:c r="Q44" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R44" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S44" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T44" s="1" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="U44" s="1" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -17270,10 +17150,10 @@
       </x:c>
       <x:c r="G45" s="8"/>
       <x:c r="AD45" s="1" t="s">
-        <x:v>722</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="AE45" s="1" t="s">
-        <x:v>723</x:v>
+        <x:v>721</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="51">
@@ -17290,7 +17170,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G46" s="20" t="s">
-        <x:v>724</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="H46" s="20"/>
       <x:c r="I46" s="20"/>
@@ -17302,22 +17182,22 @@
       <x:c r="O46" s="20"/>
       <x:c r="P46" s="20"/>
       <x:c r="Q46" s="1" t="s">
-        <x:v>645</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="R46" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S46" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="T46" s="1" t="s">
-        <x:v>697</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="AD46" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="AE46" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -17325,10 +17205,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AD47" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="AE47" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="51">
@@ -17336,7 +17216,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D48" s="10" t="s">
-        <x:v>729</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
         <x:v>29</x:v>
@@ -17345,7 +17225,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G48" s="19" t="s">
-        <x:v>730</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="H48" s="20"/>
       <x:c r="I48" s="20"/>
@@ -17357,22 +17237,22 @@
       <x:c r="O48" s="20"/>
       <x:c r="P48" s="20"/>
       <x:c r="Q48" s="1" t="s">
-        <x:v>645</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="R48" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S48" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="T48" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="AD48" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="AE48" s="1" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -17380,10 +17260,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AD49" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="AE49" s="1" t="s">
-        <x:v>734</x:v>
+        <x:v>732</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="34">
@@ -17400,25 +17280,25 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G50" s="19" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="Q50" s="1" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="R50" s="1" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="S50" s="1" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="T50" s="1" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="AD50" s="1" t="s">
+        <x:v>734</x:v>
+      </x:c>
+      <x:c r="AE50" s="1" t="s">
         <x:v>735</x:v>
-      </x:c>
-      <x:c r="Q50" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="R50" s="1" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="S50" s="1" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="T50" s="1" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="AD50" s="1" t="s">
-        <x:v>736</x:v>
-      </x:c>
-      <x:c r="AE50" s="1" t="s">
-        <x:v>737</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -17426,10 +17306,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AD51" s="1" t="s">
-        <x:v>738</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="AE51" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>737</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="17.600000381469727">
@@ -17437,7 +17317,7 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="D52" s="12" t="s">
-        <x:v>740</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>29</x:v>
@@ -17446,7 +17326,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="H52" s="20"/>
       <x:c r="I52" s="20"/>
@@ -17458,26 +17338,26 @@
       <x:c r="O52" s="20"/>
       <x:c r="P52" s="20"/>
       <x:c r="Q52" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R52" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S52" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="T52" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="W52" s="1" t="n">
         <x:f>4*6</x:f>
         <x:v>24</x:v>
       </x:c>
       <x:c r="AD52" s="1" t="s">
-        <x:v>743</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="AE52" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>742</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -17485,10 +17365,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AD53" s="1" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="AE53" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>744</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="51">
@@ -17496,7 +17376,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="D54" s="16" t="s">
-        <x:v>747</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>29</x:v>
@@ -17505,7 +17385,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G54" s="19" t="s">
-        <x:v>748</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="H54" s="20"/>
       <x:c r="I54" s="20"/>
@@ -17517,19 +17397,19 @@
       <x:c r="O54" s="20"/>
       <x:c r="P54" s="20"/>
       <x:c r="Q54" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R54" s="1" t="s">
+        <x:v>747</x:v>
+      </x:c>
+      <x:c r="S54" s="1" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="AD54" s="1" t="s">
+        <x:v>748</x:v>
+      </x:c>
+      <x:c r="AE54" s="1" t="s">
         <x:v>749</x:v>
-      </x:c>
-      <x:c r="S54" s="1" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="AD54" s="1" t="s">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="AE54" s="1" t="s">
-        <x:v>751</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -17537,10 +17417,10 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AD55" s="1" t="s">
-        <x:v>752</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="AE55" s="1" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="51">
@@ -17557,7 +17437,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G56" s="19" t="s">
-        <x:v>754</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="H56" s="20"/>
       <x:c r="I56" s="20"/>
@@ -17569,13 +17449,13 @@
       <x:c r="O56" s="20"/>
       <x:c r="P56" s="20"/>
       <x:c r="Q56" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R56" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="S56" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -17588,7 +17468,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="D58" s="10" t="s">
-        <x:v>755</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
         <x:v>29</x:v>
@@ -17597,7 +17477,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G58" s="19" t="s">
-        <x:v>756</x:v>
+        <x:v>754</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -17614,13 +17494,13 @@
       <x:c r="O59" s="20"/>
       <x:c r="P59" s="20"/>
       <x:c r="Q59" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R59" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S59" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -17633,7 +17513,7 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="D61" s="12" t="s">
-        <x:v>757</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
         <x:v>29</x:v>
@@ -17642,7 +17522,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G61" s="19" t="s">
-        <x:v>758</x:v>
+        <x:v>756</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -17659,13 +17539,13 @@
       <x:c r="O62" s="20"/>
       <x:c r="P62" s="20"/>
       <x:c r="Q62" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="R62" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S62" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -17687,7 +17567,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G64" s="19" t="s">
-        <x:v>759</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="H64" s="20"/>
       <x:c r="I64" s="20"/>
@@ -17699,13 +17579,13 @@
       <x:c r="O64" s="20"/>
       <x:c r="P64" s="20"/>
       <x:c r="Q64" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R64" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S64" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -17727,7 +17607,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G66" s="19" t="s">
-        <x:v>760</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="H66" s="20"/>
       <x:c r="I66" s="20"/>
@@ -17739,13 +17619,13 @@
       <x:c r="O66" s="20"/>
       <x:c r="P66" s="20"/>
       <x:c r="Q66" s="1" t="s">
-        <x:v>475</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="R66" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S66" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -17767,7 +17647,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G68" s="19" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -17784,13 +17664,13 @@
       <x:c r="O69" s="20"/>
       <x:c r="P69" s="20"/>
       <x:c r="Q69" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="R69" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S69" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -17812,7 +17692,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G71" s="19" t="s">
-        <x:v>762</x:v>
+        <x:v>760</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -17829,13 +17709,13 @@
       <x:c r="O72" s="20"/>
       <x:c r="P72" s="20"/>
       <x:c r="Q72" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R72" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S72" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -17848,7 +17728,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="D74" s="16" t="s">
-        <x:v>763</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
         <x:v>84</x:v>
@@ -17857,7 +17737,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="G74" s="19" t="s">
-        <x:v>764</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="H74" s="20"/>
       <x:c r="I74" s="20"/>
@@ -17869,13 +17749,13 @@
       <x:c r="O74" s="20"/>
       <x:c r="P74" s="20"/>
       <x:c r="Q74" s="1" t="s">
-        <x:v>492</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="R74" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S74" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -17888,7 +17768,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="D76" s="12" t="s">
-        <x:v>765</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
         <x:v>29</x:v>
@@ -17897,7 +17777,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G76" s="19" t="s">
-        <x:v>766</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="H76" s="20"/>
       <x:c r="I76" s="20"/>
@@ -17909,18 +17789,18 @@
       <x:c r="O76" s="20"/>
       <x:c r="P76" s="20"/>
       <x:c r="Q76" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R76" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="S76" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="E77" s="1" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="68">
@@ -17937,7 +17817,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G78" s="21" t="s">
-        <x:v>767</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="H78" s="20"/>
       <x:c r="I78" s="20"/>
@@ -17949,13 +17829,13 @@
       <x:c r="O78" s="20"/>
       <x:c r="P78" s="20"/>
       <x:c r="Q78" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R78" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="S78" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="U78" s="10"/>
       <x:c r="V78" s="26"/>
@@ -17986,7 +17866,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G80" s="19" t="s">
-        <x:v>768</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="V80" s="26"/>
       <x:c r="W80" s="26"/>
@@ -17998,7 +17878,7 @@
     </x:row>
     <x:row r="81">
       <x:c r="E81" s="1" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="H81" s="20"/>
       <x:c r="I81" s="20"/>
@@ -18010,18 +17890,18 @@
       <x:c r="O81" s="20"/>
       <x:c r="P81" s="20"/>
       <x:c r="Q81" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="R81" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="S81" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="E82" s="1" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="34">
@@ -18038,7 +17918,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="G83" s="19" t="s">
-        <x:v>542</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="V83" s="26"/>
     </x:row>
@@ -18070,7 +17950,7 @@
     </x:row>
     <x:row r="86" ht="17.600000381469727">
       <x:c r="E86" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="H86" s="20"/>
       <x:c r="I86" s="20"/>
@@ -18082,13 +17962,13 @@
       <x:c r="O86" s="20"/>
       <x:c r="P86" s="20"/>
       <x:c r="Q86" s="1" t="s">
-        <x:v>476</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="R86" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="S86" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="U86" s="26"/>
       <x:c r="V86" s="26"/>
@@ -18101,7 +17981,7 @@
     </x:row>
     <x:row r="87" ht="17.600000381469727" customHeight="1">
       <x:c r="E87" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="U87" s="26"/>
       <x:c r="V87" s="26"/>
@@ -18126,7 +18006,7 @@
         <x:v>90</x:v>
       </x:c>
       <x:c r="G88" s="19" t="s">
-        <x:v>545</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="U88" s="26"/>
       <x:c r="V88" s="26"/>
@@ -18142,13 +18022,13 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="Q89" s="1" t="s">
-        <x:v>472</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="R89" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="S89" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="V89" s="26"/>
       <x:c r="W89" s="26"/>
@@ -18171,28 +18051,28 @@
         <x:v>169</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="F91" s="1">
         <x:v>160</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>771</x:v>
+        <x:v>769</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="E92" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>768</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="E93" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>770</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="E94" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>770</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -18218,16 +18098,16 @@
       <x:c r="K4" s="3"/>
       <x:c r="L4" s="3"/>
       <x:c r="M4" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="N4" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="O4" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="P4" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="Q4" s="3"/>
       <x:c r="R4" s="3"/>
@@ -18237,16 +18117,16 @@
       <x:c r="Y4" s="3"/>
       <x:c r="Z4" s="3"/>
       <x:c r="AA4" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AB4" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AC4" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AD4" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AE4" s="3"/>
       <x:c r="AF4" s="3"/>
@@ -18267,16 +18147,16 @@
       <x:c r="K5" s="3"/>
       <x:c r="L5" s="3"/>
       <x:c r="M5" s="3" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="N5" s="3" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="O5" s="3" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="P5" s="3" t="s">
         <x:v>773</x:v>
-      </x:c>
-      <x:c r="N5" s="3" t="s">
-        <x:v>773</x:v>
-      </x:c>
-      <x:c r="O5" s="3" t="s">
-        <x:v>773</x:v>
-      </x:c>
-      <x:c r="P5" s="3" t="s">
-        <x:v>775</x:v>
       </x:c>
       <x:c r="Q5" s="3"/>
       <x:c r="R5" s="3"/>
@@ -18286,16 +18166,16 @@
       <x:c r="Y5" s="3"/>
       <x:c r="Z5" s="3"/>
       <x:c r="AA5" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AB5" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AC5" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AD5" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AE5" s="3"/>
       <x:c r="AF5" s="3"/>
@@ -18313,52 +18193,52 @@
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2"/>
       <x:c r="J6" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="K6" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="L6" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="M6" s="4" t="s">
-        <x:v>777</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
       <x:c r="P6" s="5"/>
       <x:c r="Q6" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="V6" s="2"/>
       <x:c r="W6" s="2"/>
       <x:c r="X6" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="Y6" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="Z6" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="AA6" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="AB6" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="AC6" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="AD6" s="5"/>
       <x:c r="AE6" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="AF6" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="AG6" s="6"/>
       <x:c r="AH6" s="6"/>
@@ -18374,52 +18254,52 @@
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
       <x:c r="J7" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="K7" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="L7" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="M7" s="4" t="s">
-        <x:v>782</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="4" t="s">
-        <x:v>782</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="P7" s="5"/>
       <x:c r="Q7" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="V7" s="2"/>
       <x:c r="W7" s="2"/>
       <x:c r="X7" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="Y7" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="Z7" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="AA7" s="3" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="AB7" s="5"/>
       <x:c r="AC7" s="3" t="s">
-        <x:v>774</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="AD7" s="5"/>
       <x:c r="AE7" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="AF7" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="AG7" s="6"/>
       <x:c r="AH7" s="6"/>
@@ -18433,54 +18313,54 @@
     </x:row>
     <x:row r="8" ht="45" customHeight="1">
       <x:c r="H8" s="3" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="I8" s="3" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="J8" s="3" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="K8" s="3" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="L8" s="3" t="s">
         <x:v>776</x:v>
-      </x:c>
-      <x:c r="I8" s="3" t="s">
-        <x:v>776</x:v>
-      </x:c>
-      <x:c r="J8" s="3" t="s">
-        <x:v>776</x:v>
-      </x:c>
-      <x:c r="K8" s="3" t="s">
-        <x:v>776</x:v>
-      </x:c>
-      <x:c r="L8" s="3" t="s">
-        <x:v>778</x:v>
       </x:c>
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
       <x:c r="P8" s="5"/>
       <x:c r="Q8" s="3" t="s">
-        <x:v>778</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>776</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="V8" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="W8" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="X8" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="Y8" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="Z8" s="3" t="s">
-        <x:v>779</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="AA8" s="5"/>
       <x:c r="AB8" s="5"/>
       <x:c r="AC8" s="5"/>
       <x:c r="AD8" s="5"/>
       <x:c r="AE8" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="AF8" s="3" t="s">
-        <x:v>781</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="AG8" s="6"/>
       <x:c r="AH8" s="6"/>
@@ -18499,16 +18379,16 @@
       <x:c r="K9" s="3"/>
       <x:c r="L9" s="3"/>
       <x:c r="M9" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="N9" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="O9" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="P9" s="3" t="s">
-        <x:v>775</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="Q9" s="3"/>
       <x:c r="R9" s="3"/>
@@ -18518,16 +18398,16 @@
       <x:c r="Y9" s="3"/>
       <x:c r="Z9" s="3"/>
       <x:c r="AA9" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AB9" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AC9" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AD9" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AE9" s="3"/>
       <x:c r="AF9" s="3"/>
@@ -18535,13 +18415,13 @@
       <x:c r="AH9" s="6"/>
       <x:c r="AI9" s="6"/>
       <x:c r="AJ9" s="2" t="s">
-        <x:v>784</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="AK9" s="2" t="s">
-        <x:v>784</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="AL9" s="2" t="s">
-        <x:v>784</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="AM9" s="6"/>
       <x:c r="AN9" s="6"/>
@@ -18554,16 +18434,16 @@
       <x:c r="K10" s="3"/>
       <x:c r="L10" s="3"/>
       <x:c r="M10" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="N10" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="O10" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="P10" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="Q10" s="3"/>
       <x:c r="R10" s="3"/>
@@ -18573,16 +18453,16 @@
       <x:c r="Y10" s="3"/>
       <x:c r="Z10" s="3"/>
       <x:c r="AA10" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AB10" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AC10" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AD10" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AE10" s="3"/>
       <x:c r="AF10" s="3"/>
@@ -18590,13 +18470,13 @@
       <x:c r="AH10" s="6"/>
       <x:c r="AI10" s="6"/>
       <x:c r="AJ10" s="2" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="AK10" s="2" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="AL10" s="2" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="AM10" s="6"/>
       <x:c r="AN10" s="6"/>
@@ -18609,10 +18489,10 @@
       <x:c r="K11" s="2"/>
       <x:c r="L11" s="2"/>
       <x:c r="M11" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="N11" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="O11" s="2"/>
       <x:c r="P11" s="2"/>
@@ -18624,10 +18504,10 @@
       <x:c r="Y11" s="2"/>
       <x:c r="Z11" s="2"/>
       <x:c r="AA11" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AB11" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AC11" s="2"/>
       <x:c r="AD11" s="2"/>
@@ -18637,13 +18517,13 @@
       <x:c r="AH11" s="6"/>
       <x:c r="AI11" s="6"/>
       <x:c r="AJ11" s="2" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="AK11" s="2" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="AL11" s="2" t="s">
-        <x:v>785</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="AM11" s="6"/>
       <x:c r="AN11" s="6"/>
@@ -18656,10 +18536,10 @@
       <x:c r="K12" s="2"/>
       <x:c r="L12" s="2"/>
       <x:c r="M12" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="N12" s="3" t="s">
-        <x:v>773</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="O12" s="2"/>
       <x:c r="P12" s="2"/>
@@ -18671,10 +18551,10 @@
       <x:c r="Y12" s="2"/>
       <x:c r="Z12" s="2"/>
       <x:c r="AA12" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AB12" s="3" t="s">
-        <x:v>783</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="AC12" s="2"/>
       <x:c r="AD12" s="2"/>
@@ -18683,7 +18563,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="M14" s="1" t="s">
-        <x:v>786</x:v>
+        <x:v>784</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GourmetProject/GameConfig/Datas/dish.xlsx
+++ b/GourmetProject/GameConfig/Datas/dish.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" r:id="R1ac9c19333b745c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" r:id="R8c3711a6b4704606"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" r:id="Rb1a8e3ebae254eb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" r:id="R11a1a4fb4f754e90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cake_layer_buff" sheetId="5" r:id="Ra01794a61b6a44a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sub_skill" sheetId="6" r:id="R56972f6da0a642c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计新" sheetId="9" r:id="R9874a73c4a364553"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置" sheetId="8" r:id="R9b288f1ac58a4c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_base" sheetId="1" r:id="R8eba09af5c0e487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dish_variant" sheetId="2" r:id="R02e1f55aed2f4f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill" sheetId="3" r:id="Rf88d20c53d8b458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="flavor" sheetId="4" r:id="Rfed65e6323134d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cake_layer_buff" sheetId="5" r:id="Rf9e2b4cff8e94586"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sub_skill" sheetId="6" r:id="Rf636764f7d3b46fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食物设计新" sheetId="9" r:id="R4d9c9a4f4fcd408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置" sheetId="8" r:id="R42cf0881a32a4c8b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -179,409 +179,88 @@
     <x:t xml:space="preserve">本技能独占的有序子技能ID列表（| 分隔，命名为 skillId_序号）</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_1</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_2_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_3_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_3</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干3</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_arrow_cookie_4_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">arrow_cookie_4</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">箭头饼干4</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_jelly_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">jelly</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">果冻</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cupcake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cupcake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">糖霜蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_eggtart_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eggtart</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蛋挞</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_sugarbean_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_sugarbean_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sugarbean</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">糖豆</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cheesecake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cheesecake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cheesecake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">芝士蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_mousse_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mousse</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">慕斯蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_fruit_candy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_fruit_candy_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fruit_candy</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">水果糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_choco_bar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_choco_bar_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">choco_bar</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">巧克力棒</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_mochi_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mochi</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">麻薯</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cup_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cup_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cup_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">杯子蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cream</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">奶油</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_eggroll_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eggroll</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蛋卷</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_baguette_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">baguette</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">法棍</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_tanghulu_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_tanghulu_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tanghulu</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">糖葫芦</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_cake_slice_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cake_slice_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cake_slice</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">蛋糕切角</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_long_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_long_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">long_cake</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">长条蛋糕</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_eclair_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">eclair</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">闪电泡芙</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_gummy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gummy</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">软糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_chocolate_strip_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_chocolate_strip_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">chocolate_strip</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">巧克力条</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cake_roll_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cake_roll_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cake_roll</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蛋糕卷</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_palmier_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">palmier</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">蝴蝶酥</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_chiffion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">chiffion</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">戚风蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_maple_sugar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">maple_sugar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">枫糖</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_taosu_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">taosu</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">桃酥</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_waffle_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">waffle</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">华夫饼</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cream_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_cream_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">cream_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">奶油蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_candycane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_candycane_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">candycane</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">拐杖糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_black_forest_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_black_forest_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">black_forest_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">黑森林蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_chocolate_sauce_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_chocolate_sauce_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">chocolate_sauce</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">巧克力酱</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_mango_sago_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">mango_sago</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">杨枝甘露</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_fruit_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_fruit_cake_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">fruit_cake</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">水果蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_parfait_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">parfait</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">芭菲</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_marshmallow_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">marshmallow</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">棉花糖</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">sk_big_lollipop_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_big_lollipop_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">big_lollipop</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">大棒棒糖</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_apple_pie_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">apple_pie</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">苹果派</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">sk_double_cake_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">double_cake</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">双层蛋糕</x:t>
@@ -914,16 +593,49 @@
     <x:t xml:space="preserve">ColumnAndSelf</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">奶油</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">All</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">RowAndSelf</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">法棍</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">蛋糕切角</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Category</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">长条蛋糕</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">闪电泡芙</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">巧克力条</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">枫糖</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">华夫饼</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">巧克力酱</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">芭菲</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">Down</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">苹果派</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">食物</x:t>
@@ -1060,9 +772,6 @@
     <x:t xml:space="preserve">份数+蛋糕</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">首个结算时
 所有食物分数+20</x:t>
   </x:si>
@@ -1103,9 +812,6 @@
     <x:t xml:space="preserve">所有</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用02</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">处于边缘时
 边缘食物分数+30</x:t>
   </x:si>
@@ -1141,56 +847,32 @@
 欢乐蛋糕 +10 层</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每有1个空格
 欢乐蛋糕+5层</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">传递01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">左侧及自身倍率+1
 甜蜜传递至1个食物</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">份数01</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每有1个占2格的食物
 此类食物分数+8</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用03</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每次结算
 分数永久-20</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用04</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">将本行食物中最高分数的1/4
 加至本行其他食物上</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用05</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">每有1个装饰品
 本列分数+10</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用06</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本列倍率+2
 营业结束后1/10概率移除食物</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">传递02</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">结算后
@@ -1201,9 +883,6 @@
     <x:t xml:space="preserve">风味强化</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕02</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本列每有1个蛋糕
 欢乐蛋糕+10层</x:t>
   </x:si>
@@ -1215,9 +894,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">空主动道具槽加分</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">份数02</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">周围及自身
@@ -1281,29 +957,14 @@
     <x:t xml:space="preserve">营业结束概率获得格子</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">蛋糕03</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">蛋糕04</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">欢乐蛋糕+20～80层</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">份数03</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">空格视为2份食物</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">份数04</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">本列每个食物
 将技能数计入份数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">传递03</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">结算后
@@ -1311,9 +972,6 @@
 额外选择1个目标</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">传递04</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本行
 每有1份食物，倍率+0.1
 甜蜜传递至5个食物</x:t>
@@ -1388,14 +1046,8 @@
     <x:t xml:space="preserve">.X</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">通用07</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">本行
 每有1个风味，倍率+0.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">通用08</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">处于非边缘时
@@ -1630,7 +1282,7 @@
       <x:name val="宋体"/>
     </x:font>
   </x:fonts>
-  <x:fills count="41">
+  <x:fills count="42">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1832,8 +1484,13 @@
         <x:fgColor theme="9" tint="0.39998"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF8C6A43"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -1926,6 +1583,34 @@
       </x:top>
       <x:bottom style="double">
         <x:color theme="4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9C8B4"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE6DDD3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE6DDD3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE6DDD3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE6DDD3"/>
       </x:bottom>
     </x:border>
   </x:borders>
@@ -2076,7 +1761,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="34">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -2176,6 +1861,34 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="41" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
@@ -2629,11 +2342,11 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="18.384614944458008" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="220" style="1" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="10.307692527770996" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="13.461538314819336" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="20" style="1" customWidth="1"/>
-    <x:col min="6" max="6" width="21.153846740722656" style="1" customWidth="1"/>
+    <x:col min="6" max="6" width="250" style="1" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="25.538461685180664" style="1" customWidth="1"/>
     <x:col min="8" max="8" width="20.076923370361328" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="17.615385055541992" style="1" customWidth="1"/>
@@ -3614,10 +3327,10 @@
     <x:row r="16">
       <x:c r="A16" s="26"/>
       <x:c r="B16" s="1" t="str">
-        <x:v>codename_general_01</x:v>
+        <x:v>caramel_pudding</x:v>
       </x:c>
       <x:c r="C16" s="1" t="str">
-        <x:v>通用01</x:v>
+        <x:v>焦糖布丁</x:v>
       </x:c>
       <x:c r="D16" s="1" t="n">
         <x:v>20</x:v>
@@ -3626,7 +3339,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F16" s="1" t="str">
-        <x:v>sk_codename_general_01</x:v>
+        <x:v>sk_caramel_pudding</x:v>
       </x:c>
       <x:c r="G16" s="26"/>
       <x:c r="H16" s="1" t="n">
@@ -4067,10 +3780,10 @@
     <x:row r="25">
       <x:c r="A25" s="26"/>
       <x:c r="B25" s="26" t="str">
-        <x:v>cream</x:v>
+        <x:v>cream_puff</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>奶油</x:v>
+        <x:v>奶油泡芙</x:v>
       </x:c>
       <x:c r="D25" s="26" t="n">
         <x:v>20</x:v>
@@ -4079,7 +3792,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F25" s="26" t="str">
-        <x:v>sk_cream</x:v>
+        <x:v>sk_cream_puff</x:v>
       </x:c>
       <x:c r="G25" s="26"/>
       <x:c r="H25" s="26" t="n">
@@ -4163,10 +3876,10 @@
     <x:row r="27">
       <x:c r="A27" s="26"/>
       <x:c r="B27" s="1" t="str">
-        <x:v>codename_general_02</x:v>
+        <x:v>ice_cream</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
-        <x:v>通用02</x:v>
+        <x:v>冰淇淋</x:v>
       </x:c>
       <x:c r="D27" s="1" t="n">
         <x:v>100</x:v>
@@ -4175,7 +3888,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F27" s="1" t="str">
-        <x:v>sk_codename_general_02</x:v>
+        <x:v>sk_ice_cream</x:v>
       </x:c>
       <x:c r="G27" s="26"/>
       <x:c r="H27" s="1" t="n">
@@ -4351,10 +4064,10 @@
     <x:row r="30">
       <x:c r="A30" s="26"/>
       <x:c r="B30" s="1" t="str">
-        <x:v>baguette</x:v>
+        <x:v>osmanthus_cake</x:v>
       </x:c>
       <x:c r="C30" s="1" t="str">
-        <x:v>法棍</x:v>
+        <x:v>桂花糕</x:v>
       </x:c>
       <x:c r="D30" s="1" t="n">
         <x:v>30</x:v>
@@ -4363,7 +4076,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F30" s="1" t="str">
-        <x:v>sk_baguette</x:v>
+        <x:v>sk_osmanthus_cake</x:v>
       </x:c>
       <x:c r="G30" s="1"/>
       <x:c r="H30" s="1" t="n">
@@ -4487,10 +4200,10 @@
     <x:row r="32">
       <x:c r="A32" s="26"/>
       <x:c r="B32" s="26" t="str">
-        <x:v>cake_slice</x:v>
+        <x:v>napoleon_cake</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>蛋糕切角</x:v>
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
       <x:c r="D32" s="26" t="n">
         <x:v>30</x:v>
@@ -4499,7 +4212,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F32" s="26" t="str">
-        <x:v>sk_cake_slice</x:v>
+        <x:v>sk_napoleon_cake</x:v>
       </x:c>
       <x:c r="G32" s="26" t="str">
         <x:v>cake</x:v>
@@ -4535,10 +4248,10 @@
     <x:row r="33">
       <x:c r="A33" s="26"/>
       <x:c r="B33" s="26" t="str">
-        <x:v>long_cake</x:v>
+        <x:v>honey_cake</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>长条蛋糕</x:v>
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
       <x:c r="D33" s="26" t="n">
         <x:v>30</x:v>
@@ -4547,7 +4260,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F33" s="26" t="str">
-        <x:v>sk_long_cake</x:v>
+        <x:v>sk_honey_cake</x:v>
       </x:c>
       <x:c r="G33" s="26" t="str">
         <x:v>cake</x:v>
@@ -4583,10 +4296,10 @@
     <x:row r="34">
       <x:c r="A34" s="26"/>
       <x:c r="B34" s="1" t="str">
-        <x:v>codename_cake_01</x:v>
+        <x:v>tree_ring_cake</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
-        <x:v>蛋糕01</x:v>
+        <x:v>年轮蛋糕</x:v>
       </x:c>
       <x:c r="D34" s="1" t="n">
         <x:v>30</x:v>
@@ -4595,7 +4308,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F34" s="1" t="str">
-        <x:v>sk_codename_cake_01</x:v>
+        <x:v>sk_tree_ring_cake</x:v>
       </x:c>
       <x:c r="G34" s="26" t="str">
         <x:v>cake</x:v>
@@ -4653,10 +4366,10 @@
     <x:row r="35">
       <x:c r="A35" s="26"/>
       <x:c r="B35" s="26" t="str">
-        <x:v>codename_transfer_01</x:v>
+        <x:v>nougat</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>传递01</x:v>
+        <x:v>牛轧糖</x:v>
       </x:c>
       <x:c r="D35" s="26" t="n">
         <x:v>30</x:v>
@@ -4665,7 +4378,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F35" s="26" t="str">
-        <x:v>sk_codename_transfer_01</x:v>
+        <x:v>sk_nougat</x:v>
       </x:c>
       <x:c r="G35" s="26"/>
       <x:c r="H35" s="26" t="n">
@@ -4699,10 +4412,10 @@
     <x:row r="36">
       <x:c r="A36" s="26"/>
       <x:c r="B36" s="26" t="str">
-        <x:v>codename_serving_01</x:v>
+        <x:v>hawthorn_cake</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>份数01</x:v>
+        <x:v>山楂糕</x:v>
       </x:c>
       <x:c r="D36" s="26" t="n">
         <x:v>30</x:v>
@@ -4711,7 +4424,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F36" s="26" t="str">
-        <x:v>sk_codename_serving_01</x:v>
+        <x:v>sk_hawthorn_cake</x:v>
       </x:c>
       <x:c r="G36" s="26"/>
       <x:c r="H36" s="26" t="n">
@@ -4745,10 +4458,10 @@
     <x:row r="37">
       <x:c r="A37" s="26"/>
       <x:c r="B37" s="1" t="str">
-        <x:v>codename_general_03</x:v>
+        <x:v>souffle</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
-        <x:v>通用03</x:v>
+        <x:v>舒芙蕾</x:v>
       </x:c>
       <x:c r="D37" s="1" t="n">
         <x:v>300</x:v>
@@ -4757,7 +4470,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F37" s="1" t="str">
-        <x:v>sk_codename_general_03</x:v>
+        <x:v>sk_souffle</x:v>
       </x:c>
       <x:c r="G37" s="26"/>
       <x:c r="H37" s="1" t="n">
@@ -4813,10 +4526,10 @@
     <x:row r="38">
       <x:c r="A38" s="26"/>
       <x:c r="B38" s="26" t="str">
-        <x:v>codename_general_04</x:v>
+        <x:v>fruit_tart</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>通用04</x:v>
+        <x:v>水果挞</x:v>
       </x:c>
       <x:c r="D38" s="26" t="n">
         <x:v>30</x:v>
@@ -4825,7 +4538,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F38" s="26" t="str">
-        <x:v>sk_codename_general_04</x:v>
+        <x:v>sk_fruit_tart</x:v>
       </x:c>
       <x:c r="G38" s="26"/>
       <x:c r="H38" s="26" t="n">
@@ -4859,10 +4572,10 @@
     <x:row r="39">
       <x:c r="A39" s="26"/>
       <x:c r="B39" s="26" t="str">
-        <x:v>codename_general_05</x:v>
+        <x:v>strawberry_sundae</x:v>
       </x:c>
       <x:c r="C39" s="26" t="str">
-        <x:v>通用05</x:v>
+        <x:v>草莓圣代</x:v>
       </x:c>
       <x:c r="D39" s="26" t="n">
         <x:v>30</x:v>
@@ -4871,7 +4584,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F39" s="26" t="str">
-        <x:v>sk_codename_general_05</x:v>
+        <x:v>sk_strawberry_sundae</x:v>
       </x:c>
       <x:c r="G39" s="26"/>
       <x:c r="H39" s="26" t="n">
@@ -4986,10 +4699,10 @@
     <x:row r="42">
       <x:c r="A42" s="26"/>
       <x:c r="B42" s="26" t="str">
-        <x:v>codename_general_06</x:v>
+        <x:v>rock_sugar_pear</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>通用06</x:v>
+        <x:v>冰糖雪梨</x:v>
       </x:c>
       <x:c r="D42" s="26" t="n">
         <x:v>30</x:v>
@@ -4998,7 +4711,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F42" s="26" t="str">
-        <x:v>sk_codename_general_06</x:v>
+        <x:v>sk_rock_sugar_pear</x:v>
       </x:c>
       <x:c r="G42" s="26"/>
       <x:c r="H42" s="26" t="n">
@@ -5113,10 +4826,10 @@
     <x:row r="45">
       <x:c r="A45" s="26"/>
       <x:c r="B45" s="1" t="str">
-        <x:v>codename_transfer_02</x:v>
+        <x:v>popping_candy</x:v>
       </x:c>
       <x:c r="C45" s="1" t="str">
-        <x:v>传递02</x:v>
+        <x:v>跳跳糖</x:v>
       </x:c>
       <x:c r="D45" s="1" t="n">
         <x:v>30</x:v>
@@ -5125,7 +4838,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F45" s="1" t="str">
-        <x:v>sk_codename_transfer_02</x:v>
+        <x:v>sk_popping_candy</x:v>
       </x:c>
       <x:c r="G45" s="1"/>
       <x:c r="H45" s="1" t="n">
@@ -5261,10 +4974,10 @@
     <x:row r="48">
       <x:c r="A48" s="26"/>
       <x:c r="B48" s="26" t="str">
-        <x:v>codename_cake_02</x:v>
+        <x:v>mille_crepe_cake</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>蛋糕02</x:v>
+        <x:v>千层蛋糕</x:v>
       </x:c>
       <x:c r="D48" s="26" t="n">
         <x:v>30</x:v>
@@ -5273,7 +4986,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F48" s="26" t="str">
-        <x:v>sk_codename_cake_02</x:v>
+        <x:v>sk_mille_crepe_cake</x:v>
       </x:c>
       <x:c r="G48" s="26" t="str">
         <x:v>cake</x:v>
@@ -5390,10 +5103,10 @@
     <x:row r="51">
       <x:c r="A51" s="26"/>
       <x:c r="B51" s="1" t="str">
-        <x:v>codename_serving_02</x:v>
+        <x:v>soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="C51" s="1" t="str">
-        <x:v>份数02</x:v>
+        <x:v>驴打滚</x:v>
       </x:c>
       <x:c r="D51" s="1" t="n">
         <x:v>30</x:v>
@@ -5402,7 +5115,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F51" s="1" t="str">
-        <x:v>sk_codename_serving_02</x:v>
+        <x:v>sk_soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="G51" s="26"/>
       <x:c r="H51" s="1" t="n">
@@ -5538,10 +5251,10 @@
     <x:row r="54">
       <x:c r="A54" s="26"/>
       <x:c r="B54" s="26" t="str">
-        <x:v>eclair</x:v>
+        <x:v>sachima</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>闪电泡芙</x:v>
+        <x:v>沙琪玛</x:v>
       </x:c>
       <x:c r="D54" s="26" t="n">
         <x:v>30</x:v>
@@ -5550,7 +5263,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F54" s="26" t="str">
-        <x:v>sk_eclair</x:v>
+        <x:v>sk_sachima</x:v>
       </x:c>
       <x:c r="G54" s="26"/>
       <x:c r="H54" s="26" t="n">
@@ -5792,10 +5505,10 @@
     <x:row r="60">
       <x:c r="A60" s="26"/>
       <x:c r="B60" s="1" t="str">
-        <x:v>chocolate_strip</x:v>
+        <x:v>chocolate_wafer</x:v>
       </x:c>
       <x:c r="C60" s="1" t="str">
-        <x:v>巧克力条</x:v>
+        <x:v>巧克力威化</x:v>
       </x:c>
       <x:c r="D60" s="1" t="n">
         <x:v>30</x:v>
@@ -5804,7 +5517,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F60" s="1" t="str">
-        <x:v>sk_chocolate_strip</x:v>
+        <x:v>sk_chocolate_wafer</x:v>
       </x:c>
       <x:c r="G60" s="26"/>
       <x:c r="H60" s="1" t="n">
@@ -6069,10 +5782,10 @@
     <x:row r="66">
       <x:c r="A66" s="26"/>
       <x:c r="B66" s="26" t="str">
-        <x:v>codename_cake_03</x:v>
+        <x:v>fondant_cake</x:v>
       </x:c>
       <x:c r="C66" s="26" t="str">
-        <x:v>蛋糕03</x:v>
+        <x:v>翻糖蛋糕</x:v>
       </x:c>
       <x:c r="D66" s="26" t="n">
         <x:v>30</x:v>
@@ -6081,7 +5794,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F66" s="26" t="str">
-        <x:v>sk_codename_cake_03</x:v>
+        <x:v>sk_fondant_cake</x:v>
       </x:c>
       <x:c r="G66" s="26" t="str">
         <x:v>cake</x:v>
@@ -6168,10 +5881,10 @@
     <x:row r="68">
       <x:c r="A68" s="26"/>
       <x:c r="B68" s="26" t="str">
-        <x:v>codename_cake_04</x:v>
+        <x:v>matcha_cake</x:v>
       </x:c>
       <x:c r="C68" s="26" t="str">
-        <x:v>蛋糕04</x:v>
+        <x:v>抹茶蛋糕</x:v>
       </x:c>
       <x:c r="D68" s="26" t="n">
         <x:v>30</x:v>
@@ -6180,7 +5893,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F68" s="26" t="str">
-        <x:v>sk_codename_cake_04</x:v>
+        <x:v>sk_matcha_cake</x:v>
       </x:c>
       <x:c r="G68" s="26" t="str">
         <x:v>cake</x:v>
@@ -6246,10 +5959,10 @@
     <x:row r="70">
       <x:c r="A70" s="26"/>
       <x:c r="B70" s="1" t="str">
-        <x:v>codename_serving_03</x:v>
+        <x:v>mung_bean_cake</x:v>
       </x:c>
       <x:c r="C70" s="1" t="str">
-        <x:v>份数03</x:v>
+        <x:v>绿豆糕</x:v>
       </x:c>
       <x:c r="D70" s="1" t="n">
         <x:v>30</x:v>
@@ -6258,7 +5971,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F70" s="1" t="str">
-        <x:v>sk_codename_serving_03</x:v>
+        <x:v>sk_mung_bean_cake</x:v>
       </x:c>
       <x:c r="G70" s="26"/>
       <x:c r="H70" s="1" t="n">
@@ -6343,10 +6056,10 @@
     <x:row r="72">
       <x:c r="A72" s="26"/>
       <x:c r="B72" s="26" t="str">
-        <x:v>codename_serving_04</x:v>
+        <x:v>egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="C72" s="26" t="str">
-        <x:v>份数04</x:v>
+        <x:v>蛋黄酥</x:v>
       </x:c>
       <x:c r="D72" s="26" t="n">
         <x:v>30</x:v>
@@ -6355,7 +6068,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F72" s="26" t="str">
-        <x:v>sk_codename_serving_04</x:v>
+        <x:v>sk_egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="G72" s="26"/>
       <x:c r="H72" s="26" t="n">
@@ -6442,10 +6155,10 @@
     <x:row r="74">
       <x:c r="A74" s="26"/>
       <x:c r="B74" s="26" t="str">
-        <x:v>codename_transfer_03</x:v>
+        <x:v>chocolate_truffle</x:v>
       </x:c>
       <x:c r="C74" s="26" t="str">
-        <x:v>传递03</x:v>
+        <x:v>松露巧克力</x:v>
       </x:c>
       <x:c r="D74" s="26" t="n">
         <x:v>30</x:v>
@@ -6454,7 +6167,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F74" s="26" t="str">
-        <x:v>sk_codename_transfer_03</x:v>
+        <x:v>sk_chocolate_truffle</x:v>
       </x:c>
       <x:c r="G74" s="26"/>
       <x:c r="H74" s="26" t="n">
@@ -6518,10 +6231,10 @@
     <x:row r="76">
       <x:c r="A76" s="26"/>
       <x:c r="B76" s="1" t="str">
-        <x:v>codename_transfer_04</x:v>
+        <x:v>liquor_chocolate</x:v>
       </x:c>
       <x:c r="C76" s="1" t="str">
-        <x:v>传递04</x:v>
+        <x:v>酒心巧克力</x:v>
       </x:c>
       <x:c r="D76" s="1" t="n">
         <x:v>30</x:v>
@@ -6530,7 +6243,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F76" s="1" t="str">
-        <x:v>sk_codename_transfer_04</x:v>
+        <x:v>sk_liquor_chocolate</x:v>
       </x:c>
       <x:c r="G76" s="26"/>
       <x:c r="H76" s="1" t="n">
@@ -6794,10 +6507,10 @@
     <x:row r="82">
       <x:c r="A82" s="26"/>
       <x:c r="B82" s="26" t="str">
-        <x:v>maple_sugar</x:v>
+        <x:v>toffee_candy</x:v>
       </x:c>
       <x:c r="C82" s="26" t="str">
-        <x:v>枫糖</x:v>
+        <x:v>太妃糖</x:v>
       </x:c>
       <x:c r="D82" s="26" t="n">
         <x:v>40</x:v>
@@ -6806,7 +6519,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F82" s="26" t="str">
-        <x:v>sk_maple_sugar</x:v>
+        <x:v>sk_toffee_candy</x:v>
       </x:c>
       <x:c r="G82" s="26"/>
       <x:c r="H82" s="26" t="n">
@@ -6917,10 +6630,10 @@
     <x:row r="86">
       <x:c r="A86" s="26"/>
       <x:c r="B86" s="26" t="str">
-        <x:v>waffle</x:v>
+        <x:v>brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="C86" s="26" t="str">
-        <x:v>华夫饼</x:v>
+        <x:v>红糖发糕</x:v>
       </x:c>
       <x:c r="D86" s="26" t="n">
         <x:v>40</x:v>
@@ -6929,7 +6642,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F86" s="26" t="str">
-        <x:v>sk_waffle</x:v>
+        <x:v>sk_brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="G86" s="26"/>
       <x:c r="H86" s="26" t="n">
@@ -7079,10 +6792,10 @@
     <x:row r="93">
       <x:c r="A93" s="26"/>
       <x:c r="B93" s="26" t="str">
-        <x:v>codename_general_07</x:v>
+        <x:v>fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="C93" s="26" t="str">
-        <x:v>通用07</x:v>
+        <x:v>水果刨冰</x:v>
       </x:c>
       <x:c r="D93" s="26" t="n">
         <x:v>40</x:v>
@@ -7091,7 +6804,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F93" s="26" t="str">
-        <x:v>sk_codename_general_07</x:v>
+        <x:v>sk_fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="G93" s="26"/>
       <x:c r="H93" s="26" t="n">
@@ -7127,10 +6840,10 @@
     <x:row r="95">
       <x:c r="A95" s="26"/>
       <x:c r="B95" s="26" t="str">
-        <x:v>codename_general_08</x:v>
+        <x:v>coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="C95" s="26" t="str">
-        <x:v>通用08</x:v>
+        <x:v>椰奶冻</x:v>
       </x:c>
       <x:c r="D95" s="26" t="n">
         <x:v>40</x:v>
@@ -7139,7 +6852,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F95" s="26" t="str">
-        <x:v>sk_codename_general_08</x:v>
+        <x:v>sk_coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="G95" s="26"/>
       <x:c r="H95" s="26" t="n">
@@ -7224,10 +6937,10 @@
     <x:row r="99">
       <x:c r="A99" s="26"/>
       <x:c r="B99" s="26" t="str">
-        <x:v>chocolate_sauce</x:v>
+        <x:v>nama_chocolate</x:v>
       </x:c>
       <x:c r="C99" s="26" t="str">
-        <x:v>巧克力酱</x:v>
+        <x:v>生巧克力</x:v>
       </x:c>
       <x:c r="D99" s="26" t="n">
         <x:v>60</x:v>
@@ -7236,7 +6949,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F99" s="26" t="str">
-        <x:v>sk_chocolate_sauce</x:v>
+        <x:v>sk_nama_chocolate</x:v>
       </x:c>
       <x:c r="G99" s="26"/>
       <x:c r="H99" s="26" t="n">
@@ -7379,10 +7092,10 @@
     <x:row r="106">
       <x:c r="A106" s="26"/>
       <x:c r="B106" s="26" t="str">
-        <x:v>parfait</x:v>
+        <x:v>fermented_rice_balls</x:v>
       </x:c>
       <x:c r="C106" s="26" t="str">
-        <x:v>芭菲</x:v>
+        <x:v>酒酿圆子</x:v>
       </x:c>
       <x:c r="D106" s="26" t="n">
         <x:v>60</x:v>
@@ -7391,7 +7104,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F106" s="26" t="str">
-        <x:v>sk_parfait</x:v>
+        <x:v>sk_fermented_rice_balls</x:v>
       </x:c>
       <x:c r="G106" s="26"/>
       <x:c r="H106" s="26" t="n">
@@ -7562,10 +7275,10 @@
     <x:row r="115">
       <x:c r="A115" s="26"/>
       <x:c r="B115" s="26" t="str">
-        <x:v>apple_pie</x:v>
+        <x:v>double_skin_milk</x:v>
       </x:c>
       <x:c r="C115" s="26" t="str">
-        <x:v>苹果派</x:v>
+        <x:v>双皮奶</x:v>
       </x:c>
       <x:c r="D115" s="26" t="n">
         <x:v>100</x:v>
@@ -7574,7 +7287,7 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="F115" s="26" t="str">
-        <x:v>sk_apple_pie</x:v>
+        <x:v>sk_double_skin_milk</x:v>
       </x:c>
       <x:c r="G115" s="26"/>
       <x:c r="H115" s="26" t="n">
@@ -7701,10 +7414,10 @@
     <x:row r="122">
       <x:c r="A122" s="26"/>
       <x:c r="B122" s="26" t="str">
-        <x:v>mantou</x:v>
+        <x:v>custard_bun</x:v>
       </x:c>
       <x:c r="C122" s="26" t="str">
-        <x:v>馒头</x:v>
+        <x:v>奶黄包</x:v>
       </x:c>
       <x:c r="D122" s="26" t="n">
         <x:v>10</x:v>
@@ -7737,8 +7450,8 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="21.461538314819336" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="20.384614944458008" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="220" style="1" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="220" style="1" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="38" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="15.15384578704834" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="10.307692527770996" style="1" customWidth="1"/>
@@ -8220,10 +7933,10 @@
       <x:c r="A14" s="31"/>
       <x:c r="B14" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_01</x:v>
+        <x:v>caramel_pudding</x:v>
       </x:c>
       <x:c r="C14" s="1" t="str">
-        <x:v>codename_general_01</x:v>
+        <x:v>caramel_pudding</x:v>
       </x:c>
       <x:c r="D14" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8250,7 +7963,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L14" s="31" t="str">
-        <x:v>通用01</x:v>
+        <x:v>焦糖布丁</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8405,10 +8118,10 @@
       <x:c r="A19" s="31"/>
       <x:c r="B19" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>cream</x:v>
+        <x:v>cream_puff</x:v>
       </x:c>
       <x:c r="C19" s="1" t="str">
-        <x:v>cream</x:v>
+        <x:v>cream_puff</x:v>
       </x:c>
       <x:c r="D19" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8435,17 +8148,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L19" s="31" t="str">
-        <x:v>奶油</x:v>
+        <x:v>奶油泡芙</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="31"/>
       <x:c r="B20" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_02</x:v>
+        <x:v>ice_cream</x:v>
       </x:c>
       <x:c r="C20" s="1" t="str">
-        <x:v>codename_general_02</x:v>
+        <x:v>ice_cream</x:v>
       </x:c>
       <x:c r="D20" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8472,7 +8185,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L20" s="31" t="str">
-        <x:v>通用02</x:v>
+        <x:v>冰淇淋</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -8516,10 +8229,10 @@
       <x:c r="A22" s="31"/>
       <x:c r="B22" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>baguette</x:v>
+        <x:v>osmanthus_cake</x:v>
       </x:c>
       <x:c r="C22" s="1" t="str">
-        <x:v>baguette</x:v>
+        <x:v>osmanthus_cake</x:v>
       </x:c>
       <x:c r="D22" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8546,7 +8259,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L22" s="31" t="str">
-        <x:v>法棍</x:v>
+        <x:v>桂花糕</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -8590,10 +8303,10 @@
       <x:c r="A24" s="31"/>
       <x:c r="B24" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>cake_slice</x:v>
+        <x:v>napoleon_cake</x:v>
       </x:c>
       <x:c r="C24" s="1" t="str">
-        <x:v>cake_slice</x:v>
+        <x:v>napoleon_cake</x:v>
       </x:c>
       <x:c r="D24" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8620,17 +8333,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L24" s="31" t="str">
-        <x:v>蛋糕切角</x:v>
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="31"/>
       <x:c r="B25" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>long_cake</x:v>
+        <x:v>honey_cake</x:v>
       </x:c>
       <x:c r="C25" s="1" t="str">
-        <x:v>long_cake</x:v>
+        <x:v>honey_cake</x:v>
       </x:c>
       <x:c r="D25" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8657,17 +8370,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L25" s="31" t="str">
-        <x:v>长条蛋糕</x:v>
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="31"/>
       <x:c r="B26" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_01</x:v>
+        <x:v>tree_ring_cake</x:v>
       </x:c>
       <x:c r="C26" s="1" t="str">
-        <x:v>codename_cake_01</x:v>
+        <x:v>tree_ring_cake</x:v>
       </x:c>
       <x:c r="D26" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8694,17 +8407,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L26" s="31" t="str">
-        <x:v>蛋糕01</x:v>
+        <x:v>年轮蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="31"/>
       <x:c r="B27" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_transfer_01</x:v>
+        <x:v>nougat</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
-        <x:v>codename_transfer_01</x:v>
+        <x:v>nougat</x:v>
       </x:c>
       <x:c r="D27" s="32" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8731,17 +8444,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L27" s="31" t="str">
-        <x:v>传递01</x:v>
+        <x:v>牛轧糖</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="31"/>
       <x:c r="B28" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_01</x:v>
+        <x:v>hawthorn_cake</x:v>
       </x:c>
       <x:c r="C28" s="8" t="str">
-        <x:v>codename_serving_01</x:v>
+        <x:v>hawthorn_cake</x:v>
       </x:c>
       <x:c r="D28" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8768,17 +8481,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L28" s="31" t="str">
-        <x:v>份数01</x:v>
+        <x:v>山楂糕</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="31"/>
       <x:c r="B29" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_03</x:v>
+        <x:v>souffle</x:v>
       </x:c>
       <x:c r="C29" s="8" t="str">
-        <x:v>codename_general_03</x:v>
+        <x:v>souffle</x:v>
       </x:c>
       <x:c r="D29" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8805,17 +8518,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L29" s="31" t="str">
-        <x:v>通用03</x:v>
+        <x:v>舒芙蕾</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="31"/>
       <x:c r="B30" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_04</x:v>
+        <x:v>fruit_tart</x:v>
       </x:c>
       <x:c r="C30" s="8" t="str">
-        <x:v>codename_general_04</x:v>
+        <x:v>fruit_tart</x:v>
       </x:c>
       <x:c r="D30" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8842,17 +8555,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L30" s="31" t="str">
-        <x:v>通用04</x:v>
+        <x:v>水果挞</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="31"/>
       <x:c r="B31" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_05</x:v>
+        <x:v>strawberry_sundae</x:v>
       </x:c>
       <x:c r="C31" s="8" t="str">
-        <x:v>codename_general_05</x:v>
+        <x:v>strawberry_sundae</x:v>
       </x:c>
       <x:c r="D31" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8879,17 +8592,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L31" s="31" t="str">
-        <x:v>通用05</x:v>
+        <x:v>草莓圣代</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="31"/>
       <x:c r="B32" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_general_06</x:v>
+        <x:v>rock_sugar_pear</x:v>
       </x:c>
       <x:c r="C32" s="8" t="str">
-        <x:v>codename_general_06</x:v>
+        <x:v>rock_sugar_pear</x:v>
       </x:c>
       <x:c r="D32" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8916,17 +8629,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L32" s="31" t="str">
-        <x:v>通用06</x:v>
+        <x:v>冰糖雪梨</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="31"/>
       <x:c r="B33" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_transfer_02</x:v>
+        <x:v>popping_candy</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
-        <x:v>codename_transfer_02</x:v>
+        <x:v>popping_candy</x:v>
       </x:c>
       <x:c r="D33" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8953,17 +8666,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L33" s="31" t="str">
-        <x:v>传递02</x:v>
+        <x:v>跳跳糖</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="31"/>
       <x:c r="B34" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_02</x:v>
+        <x:v>mille_crepe_cake</x:v>
       </x:c>
       <x:c r="C34" s="8" t="str">
-        <x:v>codename_cake_02</x:v>
+        <x:v>mille_crepe_cake</x:v>
       </x:c>
       <x:c r="D34" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -8990,17 +8703,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L34" s="31" t="str">
-        <x:v>蛋糕02</x:v>
+        <x:v>千层蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="31"/>
       <x:c r="B35" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_02</x:v>
+        <x:v>soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="C35" s="8" t="str">
-        <x:v>codename_serving_02</x:v>
+        <x:v>soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="D35" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9027,17 +8740,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L35" s="31" t="str">
-        <x:v>份数02</x:v>
+        <x:v>驴打滚</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="31"/>
       <x:c r="B36" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>eclair</x:v>
+        <x:v>sachima</x:v>
       </x:c>
       <x:c r="C36" s="8" t="str">
-        <x:v>eclair</x:v>
+        <x:v>sachima</x:v>
       </x:c>
       <x:c r="D36" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9064,7 +8777,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L36" s="31" t="str">
-        <x:v>闪电泡芙</x:v>
+        <x:v>沙琪玛</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -9108,10 +8821,10 @@
       <x:c r="A38" s="31"/>
       <x:c r="B38" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>chocolate_strip</x:v>
+        <x:v>chocolate_wafer</x:v>
       </x:c>
       <x:c r="C38" s="8" t="str">
-        <x:v>chocolate_strip</x:v>
+        <x:v>chocolate_wafer</x:v>
       </x:c>
       <x:c r="D38" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9138,7 +8851,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L38" s="31" t="str">
-        <x:v>巧克力条</x:v>
+        <x:v>巧克力威化</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -9182,10 +8895,10 @@
       <x:c r="A40" s="31"/>
       <x:c r="B40" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_03</x:v>
+        <x:v>fondant_cake</x:v>
       </x:c>
       <x:c r="C40" s="8" t="str">
-        <x:v>codename_cake_03</x:v>
+        <x:v>fondant_cake</x:v>
       </x:c>
       <x:c r="D40" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9212,17 +8925,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L40" s="31" t="str">
-        <x:v>蛋糕03</x:v>
+        <x:v>翻糖蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="31"/>
       <x:c r="B41" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_cake_04</x:v>
+        <x:v>matcha_cake</x:v>
       </x:c>
       <x:c r="C41" s="8" t="str">
-        <x:v>codename_cake_04</x:v>
+        <x:v>matcha_cake</x:v>
       </x:c>
       <x:c r="D41" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9249,17 +8962,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L41" s="31" t="str">
-        <x:v>蛋糕04</x:v>
+        <x:v>抹茶蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="31"/>
       <x:c r="B42" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_03</x:v>
+        <x:v>mung_bean_cake</x:v>
       </x:c>
       <x:c r="C42" s="8" t="str">
-        <x:v>codename_serving_03</x:v>
+        <x:v>mung_bean_cake</x:v>
       </x:c>
       <x:c r="D42" s="1" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9286,17 +8999,17 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L42" s="31" t="str">
-        <x:v>份数03</x:v>
+        <x:v>绿豆糕</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="31"/>
       <x:c r="B43" s="1" t="str">
         <x:f t="shared" si="0"/>
-        <x:v>codename_serving_04</x:v>
+        <x:v>egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
-        <x:v>codename_serving_04</x:v>
+        <x:v>egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="D43" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9323,16 +9036,16 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L43" s="31" t="str">
-        <x:v>份数04</x:v>
+        <x:v>蛋黄酥</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="31"/>
       <x:c r="B44" s="31" t="str">
-        <x:v>codename_transfer_03</x:v>
+        <x:v>chocolate_truffle</x:v>
       </x:c>
       <x:c r="C44" s="8" t="str">
-        <x:v>codename_transfer_03</x:v>
+        <x:v>chocolate_truffle</x:v>
       </x:c>
       <x:c r="D44" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9359,16 +9072,16 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L44" t="str">
-        <x:v>传递03</x:v>
+        <x:v>松露巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="31"/>
       <x:c r="B45" s="31" t="str">
-        <x:v>codename_transfer_04</x:v>
+        <x:v>liquor_chocolate</x:v>
       </x:c>
       <x:c r="C45" s="8" t="str">
-        <x:v>codename_transfer_04</x:v>
+        <x:v>liquor_chocolate</x:v>
       </x:c>
       <x:c r="D45" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9395,7 +9108,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L45" t="str">
-        <x:v>传递04</x:v>
+        <x:v>酒心巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -9473,10 +9186,10 @@
     <x:row r="48">
       <x:c r="A48" s="31"/>
       <x:c r="B48" s="31" t="str">
-        <x:v>maple_sugar</x:v>
+        <x:v>toffee_candy</x:v>
       </x:c>
       <x:c r="C48" s="8" t="str">
-        <x:v>maple_sugar</x:v>
+        <x:v>toffee_candy</x:v>
       </x:c>
       <x:c r="D48" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9503,7 +9216,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L48" t="str">
-        <x:v>枫糖</x:v>
+        <x:v>太妃糖</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -9545,10 +9258,10 @@
     <x:row r="50">
       <x:c r="A50" s="31"/>
       <x:c r="B50" s="31" t="str">
-        <x:v>waffle</x:v>
+        <x:v>brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="C50" s="8" t="str">
-        <x:v>waffle</x:v>
+        <x:v>brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="D50" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9575,7 +9288,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L50" t="str">
-        <x:v>华夫饼</x:v>
+        <x:v>红糖发糕</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -9653,10 +9366,10 @@
     <x:row r="53">
       <x:c r="A53" s="31"/>
       <x:c r="B53" s="31" t="str">
-        <x:v>codename_general_07</x:v>
+        <x:v>fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="C53" s="31" t="str">
-        <x:v>codename_general_07</x:v>
+        <x:v>fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="D53" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9683,16 +9396,16 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L53" t="str">
-        <x:v>通用07</x:v>
+        <x:v>水果刨冰</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="31"/>
       <x:c r="B54" s="31" t="str">
-        <x:v>codename_general_08</x:v>
+        <x:v>coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="C54" s="31" t="str">
-        <x:v>codename_general_08</x:v>
+        <x:v>coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="D54" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9719,7 +9432,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L54" t="str">
-        <x:v>通用08</x:v>
+        <x:v>椰奶冻</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -9761,10 +9474,10 @@
     <x:row r="56">
       <x:c r="A56" s="31"/>
       <x:c r="B56" s="31" t="str">
-        <x:v>chocolate_sauce</x:v>
+        <x:v>nama_chocolate</x:v>
       </x:c>
       <x:c r="C56" s="31" t="str">
-        <x:v>chocolate_sauce</x:v>
+        <x:v>nama_chocolate</x:v>
       </x:c>
       <x:c r="D56" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9791,7 +9504,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L56" t="str">
-        <x:v>巧克力酱</x:v>
+        <x:v>生巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -9869,10 +9582,10 @@
     <x:row r="59">
       <x:c r="A59" s="31"/>
       <x:c r="B59" s="31" t="str">
-        <x:v>parfait</x:v>
+        <x:v>fermented_rice_balls</x:v>
       </x:c>
       <x:c r="C59" s="31" t="str">
-        <x:v>parfait</x:v>
+        <x:v>fermented_rice_balls</x:v>
       </x:c>
       <x:c r="D59" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -9899,7 +9612,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L59" t="str">
-        <x:v>芭菲</x:v>
+        <x:v>酒酿圆子</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -9977,10 +9690,10 @@
     <x:row r="62">
       <x:c r="A62" s="31"/>
       <x:c r="B62" s="31" t="str">
-        <x:v>apple_pie</x:v>
+        <x:v>double_skin_milk</x:v>
       </x:c>
       <x:c r="C62" s="31" t="str">
-        <x:v>apple_pie</x:v>
+        <x:v>double_skin_milk</x:v>
       </x:c>
       <x:c r="D62" s="31" t="str">
         <x:v>t_sweet|t_sour|t_salty|t_bitter|t_numb|t_rust</x:v>
@@ -10007,7 +9720,7 @@
         <x:v>Deg0</x:v>
       </x:c>
       <x:c r="L62" t="str">
-        <x:v>苹果派</x:v>
+        <x:v>双皮奶</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -11210,14 +10923,15 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="26" customWidth="1"/>
-    <x:col min="2" max="2" width="23.230770111083984" style="26" customWidth="1"/>
+    <x:col min="2" max="2" width="240" style="26" hidden="0" customWidth="1"/>
     <x:col min="3" max="4" width="53.230770111083984" style="26" customWidth="1"/>
     <x:col min="5" max="6" width="9" style="26" customWidth="0"/>
-    <x:col min="7" max="7" width="36.38461685180664" style="26" customWidth="1"/>
-    <x:col min="8" max="8" width="28.923076629638672" style="26" customWidth="1"/>
+    <x:col min="7" max="7" width="240" style="26" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="240" style="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="9" style="26" customWidth="0"/>
-    <x:col min="10" max="10" width="17.30769157409668" style="26" customWidth="1"/>
+    <x:col min="10" max="10" width="220" style="26" hidden="0" customWidth="1"/>
     <x:col min="11" max="16384" width="9" style="26" customWidth="0"/>
+    <x:col min="3" max="3" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -11261,14 +10975,14 @@
       <x:c r="C4" s="26" t="str">
         <x:v>sk_arrow_cookie_1_1</x:v>
       </x:c>
-      <x:c r="G4" s="26" t="s">
+      <x:c r="G4" s="26" t="str">
+        <x:v>sk_arrow_cookie_1_1</x:v>
+      </x:c>
+      <x:c r="J4" s="26" t="str">
+        <x:v>arrow_cookie_1</x:v>
+      </x:c>
+      <x:c r="K4" s="26" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="J4" s="26" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="K4" s="26" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -11279,14 +10993,14 @@
       <x:c r="C5" s="26" t="str">
         <x:v>sk_arrow_cookie_2_1</x:v>
       </x:c>
-      <x:c r="G5" s="26" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="J5" s="26" t="s">
-        <x:v>58</x:v>
+      <x:c r="G5" s="26" t="str">
+        <x:v>sk_arrow_cookie_2_1</x:v>
+      </x:c>
+      <x:c r="J5" s="26" t="str">
+        <x:v>arrow_cookie_2</x:v>
       </x:c>
       <x:c r="K5" s="26" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -11297,14 +11011,14 @@
       <x:c r="C6" s="26" t="str">
         <x:v>sk_arrow_cookie_3_1</x:v>
       </x:c>
-      <x:c r="G6" s="26" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="J6" s="26" t="s">
-        <x:v>61</x:v>
+      <x:c r="G6" s="26" t="str">
+        <x:v>sk_arrow_cookie_3_1</x:v>
+      </x:c>
+      <x:c r="J6" s="26" t="str">
+        <x:v>arrow_cookie_3</x:v>
       </x:c>
       <x:c r="K6" s="26" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -11315,14 +11029,14 @@
       <x:c r="C7" s="26" t="str">
         <x:v>sk_arrow_cookie_4_1</x:v>
       </x:c>
-      <x:c r="G7" s="26" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="J7" s="26" t="s">
-        <x:v>64</x:v>
+      <x:c r="G7" s="26" t="str">
+        <x:v>sk_arrow_cookie_4_1</x:v>
+      </x:c>
+      <x:c r="J7" s="26" t="str">
+        <x:v>arrow_cookie_4</x:v>
       </x:c>
       <x:c r="K7" s="26" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -11333,14 +11047,14 @@
       <x:c r="C8" s="26" t="str">
         <x:v>sk_jelly_1</x:v>
       </x:c>
-      <x:c r="G8" s="26" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="J8" s="26" t="s">
-        <x:v>67</x:v>
+      <x:c r="G8" s="26" t="str">
+        <x:v>sk_jelly_1</x:v>
+      </x:c>
+      <x:c r="J8" s="26" t="str">
+        <x:v>jelly</x:v>
       </x:c>
       <x:c r="K8" s="26" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -11351,14 +11065,14 @@
       <x:c r="C9" s="26" t="str">
         <x:v>sk_cupcake_1</x:v>
       </x:c>
-      <x:c r="G9" s="26" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="J9" s="26" t="s">
-        <x:v>70</x:v>
+      <x:c r="G9" s="26" t="str">
+        <x:v>sk_cupcake_1</x:v>
+      </x:c>
+      <x:c r="J9" s="26" t="str">
+        <x:v>cupcake</x:v>
       </x:c>
       <x:c r="K9" s="26" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -11369,14 +11083,14 @@
       <x:c r="C10" s="26" t="str">
         <x:v>sk_eggtart_1</x:v>
       </x:c>
-      <x:c r="G10" s="26" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="J10" s="26" t="s">
-        <x:v>73</x:v>
+      <x:c r="G10" s="26" t="str">
+        <x:v>sk_eggtart_1</x:v>
+      </x:c>
+      <x:c r="J10" s="26" t="str">
+        <x:v>eggtart</x:v>
       </x:c>
       <x:c r="K10" s="26" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -11387,17 +11101,17 @@
       <x:c r="C11" s="26" t="str">
         <x:v>sk_sugarbean_1|sk_sugarbean_2</x:v>
       </x:c>
-      <x:c r="G11" s="26" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="H11" s="26" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="J11" s="26" t="s">
-        <x:v>77</x:v>
+      <x:c r="G11" s="26" t="str">
+        <x:v>sk_sugarbean_1</x:v>
+      </x:c>
+      <x:c r="H11" s="26" t="str">
+        <x:v>sk_sugarbean_2</x:v>
+      </x:c>
+      <x:c r="J11" s="26" t="str">
+        <x:v>sugarbean</x:v>
       </x:c>
       <x:c r="K11" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -11408,17 +11122,17 @@
       <x:c r="C12" s="26" t="str">
         <x:v>sk_cheesecake_1|sk_cheesecake_2</x:v>
       </x:c>
-      <x:c r="G12" s="26" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H12" s="26" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="J12" s="26" t="s">
-        <x:v>81</x:v>
+      <x:c r="G12" s="26" t="str">
+        <x:v>sk_cheesecake_1</x:v>
+      </x:c>
+      <x:c r="H12" s="26" t="str">
+        <x:v>sk_cheesecake_2</x:v>
+      </x:c>
+      <x:c r="J12" s="26" t="str">
+        <x:v>cheesecake</x:v>
       </x:c>
       <x:c r="K12" s="26" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -11429,35 +11143,35 @@
       <x:c r="C13" s="26" t="str">
         <x:v>sk_mousse_1</x:v>
       </x:c>
-      <x:c r="G13" s="26" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="J13" s="26" t="s">
-        <x:v>84</x:v>
+      <x:c r="G13" s="26" t="str">
+        <x:v>sk_mousse_1</x:v>
+      </x:c>
+      <x:c r="J13" s="26" t="str">
+        <x:v>mousse</x:v>
       </x:c>
       <x:c r="K13" s="26" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
       <x:c r="B14" s="26" t="str">
-        <x:v>sk_codename_general_01</x:v>
+        <x:v>sk_caramel_pudding</x:v>
       </x:c>
       <x:c r="C14" s="26" t="str">
-        <x:v>sk_codename_general_01_1</x:v>
-      </x:c>
-      <x:c r="G14" s="26" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="H14" s="26" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="J14" s="26" t="s">
-        <x:v>88</x:v>
+        <x:v>sk_caramel_pudding_1</x:v>
+      </x:c>
+      <x:c r="G14" s="26" t="str">
+        <x:v>sk_fruit_candy_1</x:v>
+      </x:c>
+      <x:c r="H14" s="26" t="str">
+        <x:v>sk_fruit_candy_2</x:v>
+      </x:c>
+      <x:c r="J14" s="26" t="str">
+        <x:v>fruit_candy</x:v>
       </x:c>
       <x:c r="K14" s="26" t="s">
-        <x:v>89</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -11468,17 +11182,17 @@
       <x:c r="C15" s="26" t="str">
         <x:v>sk_fruit_candy_1|sk_fruit_candy_2</x:v>
       </x:c>
-      <x:c r="G15" s="26" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="H15" s="26" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="J15" s="26" t="s">
-        <x:v>92</x:v>
+      <x:c r="G15" s="26" t="str">
+        <x:v>sk_choco_bar_1</x:v>
+      </x:c>
+      <x:c r="H15" s="26" t="str">
+        <x:v>sk_choco_bar_2</x:v>
+      </x:c>
+      <x:c r="J15" s="26" t="str">
+        <x:v>choco_bar</x:v>
       </x:c>
       <x:c r="K15" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -11489,14 +11203,14 @@
       <x:c r="C16" s="26" t="str">
         <x:v>sk_choco_bar_1|sk_choco_bar_2</x:v>
       </x:c>
-      <x:c r="G16" s="26" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="J16" s="26" t="s">
-        <x:v>95</x:v>
+      <x:c r="G16" s="26" t="str">
+        <x:v>sk_mochi_1</x:v>
+      </x:c>
+      <x:c r="J16" s="26" t="str">
+        <x:v>mochi</x:v>
       </x:c>
       <x:c r="K16" s="26" t="s">
-        <x:v>96</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -11507,17 +11221,17 @@
       <x:c r="C17" s="26" t="str">
         <x:v>sk_mochi_1</x:v>
       </x:c>
-      <x:c r="G17" s="26" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="H17" s="26" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="J17" s="26" t="s">
-        <x:v>99</x:v>
+      <x:c r="G17" s="26" t="str">
+        <x:v>sk_cup_cake_1</x:v>
+      </x:c>
+      <x:c r="H17" s="26" t="str">
+        <x:v>sk_cup_cake_2</x:v>
+      </x:c>
+      <x:c r="J17" s="26" t="str">
+        <x:v>cup_cake</x:v>
       </x:c>
       <x:c r="K17" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -11528,50 +11242,50 @@
       <x:c r="C18" s="26" t="str">
         <x:v>sk_cup_cake_1|sk_cup_cake_2</x:v>
       </x:c>
-      <x:c r="G18" s="26" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="J18" s="26" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="K18" s="26" t="s">
-        <x:v>103</x:v>
+      <x:c r="G18" s="26" t="str">
+        <x:v>sk_cream_puff_1</x:v>
+      </x:c>
+      <x:c r="J18" s="26" t="str">
+        <x:v>cream_puff</x:v>
+      </x:c>
+      <x:c r="K18" s="26" t="str">
+        <x:v>奶油泡芙</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
       <x:c r="B19" s="26" t="str">
-        <x:v>sk_cream</x:v>
+        <x:v>sk_cream_puff</x:v>
       </x:c>
       <x:c r="C19" s="26" t="str">
-        <x:v>sk_cream_1</x:v>
-      </x:c>
-      <x:c r="G19" s="26" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="J19" s="26" t="s">
-        <x:v>105</x:v>
+        <x:v>sk_cream_puff_1</x:v>
+      </x:c>
+      <x:c r="G19" s="26" t="str">
+        <x:v>sk_eggroll_1</x:v>
+      </x:c>
+      <x:c r="J19" s="26" t="str">
+        <x:v>eggroll</x:v>
       </x:c>
       <x:c r="K19" s="26" t="s">
-        <x:v>106</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
       <x:c r="B20" s="26" t="str">
-        <x:v>sk_codename_general_02</x:v>
+        <x:v>sk_ice_cream</x:v>
       </x:c>
       <x:c r="C20" s="26" t="str">
-        <x:v>sk_codename_general_02_1</x:v>
-      </x:c>
-      <x:c r="G20" s="26" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="J20" s="26" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="K20" s="26" t="s">
-        <x:v>109</x:v>
+        <x:v>sk_ice_cream_1</x:v>
+      </x:c>
+      <x:c r="G20" s="26" t="str">
+        <x:v>sk_osmanthus_cake_1</x:v>
+      </x:c>
+      <x:c r="J20" s="26" t="str">
+        <x:v>osmanthus_cake</x:v>
+      </x:c>
+      <x:c r="K20" s="26" t="str">
+        <x:v>桂花糕</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -11582,38 +11296,38 @@
       <x:c r="C21" s="26" t="str">
         <x:v>sk_eggroll_1</x:v>
       </x:c>
-      <x:c r="G21" s="26" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="H21" s="26" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="J21" s="26" t="s">
-        <x:v>112</x:v>
+      <x:c r="G21" s="26" t="str">
+        <x:v>sk_tanghulu_1</x:v>
+      </x:c>
+      <x:c r="H21" s="26" t="str">
+        <x:v>sk_tanghulu_2</x:v>
+      </x:c>
+      <x:c r="J21" s="26" t="str">
+        <x:v>tanghulu</x:v>
       </x:c>
       <x:c r="K21" s="26" t="s">
-        <x:v>113</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
       <x:c r="B22" s="26" t="str">
-        <x:v>sk_baguette</x:v>
+        <x:v>sk_osmanthus_cake</x:v>
       </x:c>
       <x:c r="C22" s="26" t="str">
-        <x:v>sk_baguette_1</x:v>
-      </x:c>
-      <x:c r="G22" s="26" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="H22" s="26" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="J22" s="26" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="K22" s="26" t="s">
-        <x:v>117</x:v>
+        <x:v>sk_osmanthus_cake_1</x:v>
+      </x:c>
+      <x:c r="G22" s="26" t="str">
+        <x:v>sk_napoleon_cake_1</x:v>
+      </x:c>
+      <x:c r="H22" s="26" t="str">
+        <x:v>sk_napoleon_cake_2</x:v>
+      </x:c>
+      <x:c r="J22" s="26" t="str">
+        <x:v>napoleon_cake</x:v>
+      </x:c>
+      <x:c r="K22" s="26" t="str">
+        <x:v>拿破仑蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -11624,269 +11338,269 @@
       <x:c r="C23" s="26" t="str">
         <x:v>sk_tanghulu_1|sk_tanghulu_2</x:v>
       </x:c>
-      <x:c r="G23" s="26" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="H23" s="26" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="J23" s="26" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="K23" s="26" t="s">
-        <x:v>121</x:v>
+      <x:c r="G23" s="26" t="str">
+        <x:v>sk_honey_cake_1</x:v>
+      </x:c>
+      <x:c r="H23" s="26" t="str">
+        <x:v>sk_honey_cake_2</x:v>
+      </x:c>
+      <x:c r="J23" s="26" t="str">
+        <x:v>honey_cake</x:v>
+      </x:c>
+      <x:c r="K23" s="26" t="str">
+        <x:v>蜂蜜蛋糕</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
       <x:c r="B24" s="26" t="str">
-        <x:v>sk_cake_slice</x:v>
+        <x:v>sk_napoleon_cake</x:v>
       </x:c>
       <x:c r="C24" s="26" t="str">
-        <x:v>sk_cake_slice_1|sk_cake_slice_2</x:v>
-      </x:c>
-      <x:c r="G24" s="26" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="J24" s="26" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="K24" s="26" t="s">
-        <x:v>124</x:v>
+        <x:v>sk_napoleon_cake_1|sk_napoleon_cake_2</x:v>
+      </x:c>
+      <x:c r="G24" s="26" t="str">
+        <x:v>sk_sachima_1</x:v>
+      </x:c>
+      <x:c r="J24" s="26" t="str">
+        <x:v>sachima</x:v>
+      </x:c>
+      <x:c r="K24" s="26" t="str">
+        <x:v>沙琪玛</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
       <x:c r="B25" s="26" t="str">
-        <x:v>sk_long_cake</x:v>
+        <x:v>sk_honey_cake</x:v>
       </x:c>
       <x:c r="C25" s="26" t="str">
-        <x:v>sk_long_cake_1|sk_long_cake_2</x:v>
-      </x:c>
-      <x:c r="G25" s="26" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="J25" s="26" t="s">
-        <x:v>126</x:v>
+        <x:v>sk_honey_cake_1|sk_honey_cake_2</x:v>
+      </x:c>
+      <x:c r="G25" s="26" t="str">
+        <x:v>sk_gummy_1</x:v>
+      </x:c>
+      <x:c r="J25" s="26" t="str">
+        <x:v>gummy</x:v>
       </x:c>
       <x:c r="K25" s="26" t="s">
-        <x:v>127</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26"/>
       <x:c r="B26" s="26" t="str">
-        <x:v>sk_codename_cake_01</x:v>
+        <x:v>sk_tree_ring_cake</x:v>
       </x:c>
       <x:c r="C26" s="26" t="str">
-        <x:v>sk_codename_cake_01_1</x:v>
-      </x:c>
-      <x:c r="G26" s="26" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="H26" s="26" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="J26" s="26" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="K26" s="26" t="s">
-        <x:v>131</x:v>
+        <x:v>sk_tree_ring_cake_1</x:v>
+      </x:c>
+      <x:c r="G26" s="26" t="str">
+        <x:v>sk_chocolate_wafer_1</x:v>
+      </x:c>
+      <x:c r="H26" s="26" t="str">
+        <x:v>sk_chocolate_wafer_2</x:v>
+      </x:c>
+      <x:c r="J26" s="26" t="str">
+        <x:v>chocolate_wafer</x:v>
+      </x:c>
+      <x:c r="K26" s="26" t="str">
+        <x:v>巧克力威化</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27"/>
       <x:c r="B27" s="26" t="str">
-        <x:v>sk_codename_transfer_01</x:v>
+        <x:v>sk_nougat</x:v>
       </x:c>
       <x:c r="C27" s="26" t="str">
-        <x:v>sk_codename_transfer_01_1|sk_codename_transfer_01_2</x:v>
-      </x:c>
-      <x:c r="G27" s="26" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="H27" s="26" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="J27" s="26" t="s">
-        <x:v>134</x:v>
+        <x:v>sk_nougat_1|sk_nougat_2</x:v>
+      </x:c>
+      <x:c r="G27" s="26" t="str">
+        <x:v>sk_cake_roll_1</x:v>
+      </x:c>
+      <x:c r="H27" s="26" t="str">
+        <x:v>sk_cake_roll_2</x:v>
+      </x:c>
+      <x:c r="J27" s="26" t="str">
+        <x:v>cake_roll</x:v>
       </x:c>
       <x:c r="K27" s="26" t="s">
-        <x:v>135</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28"/>
       <x:c r="B28" s="26" t="str">
-        <x:v>sk_codename_serving_01</x:v>
+        <x:v>sk_hawthorn_cake</x:v>
       </x:c>
       <x:c r="C28" s="26" t="str">
-        <x:v>sk_codename_serving_01_1</x:v>
-      </x:c>
-      <x:c r="G28" s="26" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="J28" s="26" t="s">
-        <x:v>137</x:v>
+        <x:v>sk_hawthorn_cake_1</x:v>
+      </x:c>
+      <x:c r="G28" s="26" t="str">
+        <x:v>sk_palmier_1</x:v>
+      </x:c>
+      <x:c r="J28" s="26" t="str">
+        <x:v>palmier</x:v>
       </x:c>
       <x:c r="K28" s="26" t="s">
-        <x:v>138</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29"/>
       <x:c r="B29" s="26" t="str">
-        <x:v>sk_codename_general_03</x:v>
+        <x:v>sk_souffle</x:v>
       </x:c>
       <x:c r="C29" s="26" t="str">
-        <x:v>sk_codename_general_03_1</x:v>
-      </x:c>
-      <x:c r="G29" s="26" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="J29" s="26" t="s">
-        <x:v>140</x:v>
+        <x:v>sk_souffle_1</x:v>
+      </x:c>
+      <x:c r="G29" s="26" t="str">
+        <x:v>sk_chiffion_1</x:v>
+      </x:c>
+      <x:c r="J29" s="26" t="str">
+        <x:v>chiffion</x:v>
       </x:c>
       <x:c r="K29" s="26" t="s">
-        <x:v>141</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30"/>
       <x:c r="B30" s="26" t="str">
-        <x:v>sk_codename_general_04</x:v>
+        <x:v>sk_fruit_tart</x:v>
       </x:c>
       <x:c r="C30" s="26" t="str">
-        <x:v>sk_codename_general_04_1</x:v>
-      </x:c>
-      <x:c r="G30" s="26" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="J30" s="26" t="s">
-        <x:v>143</x:v>
-      </x:c>
-      <x:c r="K30" s="26" t="s">
-        <x:v>144</x:v>
+        <x:v>sk_fruit_tart_1</x:v>
+      </x:c>
+      <x:c r="G30" s="26" t="str">
+        <x:v>sk_toffee_candy_1</x:v>
+      </x:c>
+      <x:c r="J30" s="26" t="str">
+        <x:v>toffee_candy</x:v>
+      </x:c>
+      <x:c r="K30" s="26" t="str">
+        <x:v>太妃糖</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31"/>
       <x:c r="B31" s="26" t="str">
-        <x:v>sk_codename_general_05</x:v>
+        <x:v>sk_strawberry_sundae</x:v>
       </x:c>
       <x:c r="C31" s="26" t="str">
-        <x:v>sk_codename_general_05_1</x:v>
-      </x:c>
-      <x:c r="G31" s="26" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="J31" s="26" t="s">
-        <x:v>146</x:v>
+        <x:v>sk_strawberry_sundae_1</x:v>
+      </x:c>
+      <x:c r="G31" s="26" t="str">
+        <x:v>sk_taosu_1</x:v>
+      </x:c>
+      <x:c r="J31" s="26" t="str">
+        <x:v>taosu</x:v>
       </x:c>
       <x:c r="K31" s="26" t="s">
-        <x:v>147</x:v>
+        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32"/>
       <x:c r="B32" s="26" t="str">
-        <x:v>sk_codename_general_06</x:v>
+        <x:v>sk_rock_sugar_pear</x:v>
       </x:c>
       <x:c r="C32" s="26" t="str">
-        <x:v>sk_codename_general_06_1|sk_codename_general_06_2</x:v>
-      </x:c>
-      <x:c r="G32" s="26" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="J32" s="26" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="K32" s="26" t="s">
-        <x:v>150</x:v>
+        <x:v>sk_rock_sugar_pear_1|sk_rock_sugar_pear_2</x:v>
+      </x:c>
+      <x:c r="G32" s="26" t="str">
+        <x:v>sk_brown_sugar_steamed_cake_1</x:v>
+      </x:c>
+      <x:c r="J32" s="26" t="str">
+        <x:v>brown_sugar_steamed_cake</x:v>
+      </x:c>
+      <x:c r="K32" s="26" t="str">
+        <x:v>红糖发糕</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33"/>
       <x:c r="B33" s="26" t="str">
-        <x:v>sk_codename_transfer_02</x:v>
+        <x:v>sk_popping_candy</x:v>
       </x:c>
       <x:c r="C33" s="26" t="str">
-        <x:v>sk_codename_transfer_02_1</x:v>
-      </x:c>
-      <x:c r="G33" s="26" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="H33" s="26" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="J33" s="26" t="s">
-        <x:v>153</x:v>
+        <x:v>sk_popping_candy_1</x:v>
+      </x:c>
+      <x:c r="G33" s="26" t="str">
+        <x:v>sk_cream_cake_1</x:v>
+      </x:c>
+      <x:c r="H33" s="26" t="str">
+        <x:v>sk_cream_cake_2</x:v>
+      </x:c>
+      <x:c r="J33" s="26" t="str">
+        <x:v>cream_cake</x:v>
       </x:c>
       <x:c r="K33" s="26" t="s">
-        <x:v>154</x:v>
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34"/>
       <x:c r="B34" s="26" t="str">
-        <x:v>sk_codename_cake_02</x:v>
+        <x:v>sk_mille_crepe_cake</x:v>
       </x:c>
       <x:c r="C34" s="26" t="str">
-        <x:v>sk_codename_cake_02_1</x:v>
-      </x:c>
-      <x:c r="G34" s="26" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="H34" s="26" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="J34" s="26" t="s">
-        <x:v>157</x:v>
+        <x:v>sk_mille_crepe_cake_1</x:v>
+      </x:c>
+      <x:c r="G34" s="26" t="str">
+        <x:v>sk_candycane_1</x:v>
+      </x:c>
+      <x:c r="H34" s="26" t="str">
+        <x:v>sk_candycane_2</x:v>
+      </x:c>
+      <x:c r="J34" s="26" t="str">
+        <x:v>candycane</x:v>
       </x:c>
       <x:c r="K34" s="26" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35"/>
       <x:c r="B35" s="26" t="str">
-        <x:v>sk_codename_serving_02</x:v>
+        <x:v>sk_soybean_glutinous_roll</x:v>
       </x:c>
       <x:c r="C35" s="26" t="str">
-        <x:v>sk_codename_serving_02_1</x:v>
-      </x:c>
-      <x:c r="G35" s="26" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="H35" s="26" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="J35" s="26" t="s">
-        <x:v>161</x:v>
+        <x:v>sk_soybean_glutinous_roll_1</x:v>
+      </x:c>
+      <x:c r="G35" s="26" t="str">
+        <x:v>sk_black_forest_cake_1</x:v>
+      </x:c>
+      <x:c r="H35" s="26" t="str">
+        <x:v>sk_black_forest_cake_2</x:v>
+      </x:c>
+      <x:c r="J35" s="26" t="str">
+        <x:v>black_forest_cake</x:v>
       </x:c>
       <x:c r="K35" s="26" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36"/>
       <x:c r="B36" s="26" t="str">
-        <x:v>sk_eclair</x:v>
+        <x:v>sk_sachima</x:v>
       </x:c>
       <x:c r="C36" s="26" t="str">
-        <x:v>sk_eclair_1</x:v>
-      </x:c>
-      <x:c r="G36" s="26" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="H36" s="26" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="J36" s="26" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="K36" s="26" t="s">
-        <x:v>166</x:v>
+        <x:v>sk_sachima_1</x:v>
+      </x:c>
+      <x:c r="G36" s="26" t="str">
+        <x:v>sk_nama_chocolate_1</x:v>
+      </x:c>
+      <x:c r="H36" s="26" t="str">
+        <x:v>sk_nama_chocolate_2</x:v>
+      </x:c>
+      <x:c r="J36" s="26" t="str">
+        <x:v>nama_chocolate</x:v>
+      </x:c>
+      <x:c r="K36" s="26" t="str">
+        <x:v>生巧克力</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -11897,35 +11611,35 @@
       <x:c r="C37" s="26" t="str">
         <x:v>sk_gummy_1</x:v>
       </x:c>
-      <x:c r="G37" s="26" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="J37" s="26" t="s">
-        <x:v>168</x:v>
+      <x:c r="G37" s="26" t="str">
+        <x:v>sk_mango_sago_1</x:v>
+      </x:c>
+      <x:c r="J37" s="26" t="str">
+        <x:v>mango_sago</x:v>
       </x:c>
       <x:c r="K37" s="26" t="s">
-        <x:v>169</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38"/>
       <x:c r="B38" s="26" t="str">
-        <x:v>sk_chocolate_strip</x:v>
+        <x:v>sk_chocolate_wafer</x:v>
       </x:c>
       <x:c r="C38" s="26" t="str">
-        <x:v>sk_chocolate_strip_1|sk_chocolate_strip_2</x:v>
-      </x:c>
-      <x:c r="G38" s="26" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="H38" s="26" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="J38" s="26" t="s">
-        <x:v>172</x:v>
+        <x:v>sk_chocolate_wafer_1|sk_chocolate_wafer_2</x:v>
+      </x:c>
+      <x:c r="G38" s="26" t="str">
+        <x:v>sk_fruit_cake_1</x:v>
+      </x:c>
+      <x:c r="H38" s="26" t="str">
+        <x:v>sk_fruit_cake_2</x:v>
+      </x:c>
+      <x:c r="J38" s="26" t="str">
+        <x:v>fruit_cake</x:v>
       </x:c>
       <x:c r="K38" s="26" t="s">
-        <x:v>173</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -11936,107 +11650,107 @@
       <x:c r="C39" s="26" t="str">
         <x:v>sk_cake_roll_1|sk_cake_roll_2</x:v>
       </x:c>
-      <x:c r="G39" s="26" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="J39" s="26" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="K39" s="26" t="s">
-        <x:v>176</x:v>
+      <x:c r="G39" s="26" t="str">
+        <x:v>sk_fermented_rice_balls_1</x:v>
+      </x:c>
+      <x:c r="J39" s="26" t="str">
+        <x:v>fermented_rice_balls</x:v>
+      </x:c>
+      <x:c r="K39" s="26" t="str">
+        <x:v>酒酿圆子</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40"/>
       <x:c r="B40" s="26" t="str">
-        <x:v>sk_codename_cake_03</x:v>
+        <x:v>sk_fondant_cake</x:v>
       </x:c>
       <x:c r="C40" s="26" t="str">
-        <x:v>sk_codename_cake_03_1|sk_codename_cake_03_2</x:v>
-      </x:c>
-      <x:c r="G40" s="26" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="J40" s="26" t="s">
-        <x:v>178</x:v>
+        <x:v>sk_fondant_cake_1|sk_fondant_cake_2</x:v>
+      </x:c>
+      <x:c r="G40" s="26" t="str">
+        <x:v>sk_marshmallow_1</x:v>
+      </x:c>
+      <x:c r="J40" s="26" t="str">
+        <x:v>marshmallow</x:v>
       </x:c>
       <x:c r="K40" s="26" t="s">
-        <x:v>179</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41"/>
       <x:c r="B41" s="26" t="str">
-        <x:v>sk_codename_cake_04</x:v>
+        <x:v>sk_matcha_cake</x:v>
       </x:c>
       <x:c r="C41" s="26" t="str">
-        <x:v>sk_codename_cake_04_1</x:v>
-      </x:c>
-      <x:c r="G41" s="26" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H41" s="26" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="J41" s="26" t="s">
-        <x:v>182</x:v>
+        <x:v>sk_matcha_cake_1</x:v>
+      </x:c>
+      <x:c r="G41" s="26" t="str">
+        <x:v>sk_big_lollipop_1</x:v>
+      </x:c>
+      <x:c r="H41" s="26" t="str">
+        <x:v>sk_big_lollipop_2</x:v>
+      </x:c>
+      <x:c r="J41" s="26" t="str">
+        <x:v>big_lollipop</x:v>
       </x:c>
       <x:c r="K41" s="26" t="s">
-        <x:v>183</x:v>
+        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42"/>
       <x:c r="B42" s="26" t="str">
-        <x:v>sk_codename_serving_03</x:v>
+        <x:v>sk_mung_bean_cake</x:v>
       </x:c>
       <x:c r="C42" s="26" t="str">
-        <x:v>sk_codename_serving_03_1</x:v>
-      </x:c>
-      <x:c r="G42" s="26" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="J42" s="26" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="K42" s="26" t="s">
-        <x:v>186</x:v>
+        <x:v>sk_mung_bean_cake_1</x:v>
+      </x:c>
+      <x:c r="G42" s="26" t="str">
+        <x:v>sk_double_skin_milk_1</x:v>
+      </x:c>
+      <x:c r="J42" s="26" t="str">
+        <x:v>double_skin_milk</x:v>
+      </x:c>
+      <x:c r="K42" s="26" t="str">
+        <x:v>双皮奶</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43"/>
       <x:c r="B43" s="26" t="str">
-        <x:v>sk_codename_serving_04</x:v>
+        <x:v>sk_egg_yolk_pastry</x:v>
       </x:c>
       <x:c r="C43" s="26" t="str">
-        <x:v>sk_codename_serving_04_1</x:v>
-      </x:c>
-      <x:c r="G43" s="26" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="J43" s="26" t="s">
-        <x:v>188</x:v>
+        <x:v>sk_egg_yolk_pastry_1</x:v>
+      </x:c>
+      <x:c r="G43" s="26" t="str">
+        <x:v>sk_double_cake_1</x:v>
+      </x:c>
+      <x:c r="J43" s="26" t="str">
+        <x:v>double_cake</x:v>
       </x:c>
       <x:c r="K43" s="26" t="s">
-        <x:v>189</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44"/>
       <x:c r="B44" s="26" t="str">
-        <x:v>sk_codename_transfer_03</x:v>
+        <x:v>sk_chocolate_truffle</x:v>
       </x:c>
       <x:c r="C44" s="26" t="str">
-        <x:v>sk_codename_transfer_03_1</x:v>
+        <x:v>sk_chocolate_truffle_1</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45"/>
       <x:c r="B45" s="26" t="str">
-        <x:v>sk_codename_transfer_04</x:v>
+        <x:v>sk_liquor_chocolate</x:v>
       </x:c>
       <x:c r="C45" s="26" t="str">
-        <x:v>sk_codename_transfer_04_1|sk_codename_transfer_04_2</x:v>
+        <x:v>sk_liquor_chocolate_1|sk_liquor_chocolate_2</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -12060,10 +11774,10 @@
     <x:row r="48">
       <x:c r="A48"/>
       <x:c r="B48" s="26" t="str">
-        <x:v>sk_maple_sugar</x:v>
+        <x:v>sk_toffee_candy</x:v>
       </x:c>
       <x:c r="C48" s="26" t="str">
-        <x:v>sk_maple_sugar_1</x:v>
+        <x:v>sk_toffee_candy_1</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -12078,10 +11792,10 @@
     <x:row r="50">
       <x:c r="A50"/>
       <x:c r="B50" s="26" t="str">
-        <x:v>sk_waffle</x:v>
+        <x:v>sk_brown_sugar_steamed_cake</x:v>
       </x:c>
       <x:c r="C50" s="26" t="str">
-        <x:v>sk_waffle_1</x:v>
+        <x:v>sk_brown_sugar_steamed_cake_1</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -12105,19 +11819,19 @@
     <x:row r="53">
       <x:c r="A53"/>
       <x:c r="B53" s="26" t="str">
-        <x:v>sk_codename_general_07</x:v>
+        <x:v>sk_fruit_shaved_ice</x:v>
       </x:c>
       <x:c r="C53" s="26" t="str">
-        <x:v>sk_codename_general_07_1</x:v>
+        <x:v>sk_fruit_shaved_ice_1</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54"/>
       <x:c r="B54" s="26" t="str">
-        <x:v>sk_codename_general_08</x:v>
+        <x:v>sk_coconut_milk_jelly</x:v>
       </x:c>
       <x:c r="C54" s="26" t="str">
-        <x:v>sk_codename_general_08_1</x:v>
+        <x:v>sk_coconut_milk_jelly_1</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -12132,10 +11846,10 @@
     <x:row r="56">
       <x:c r="A56"/>
       <x:c r="B56" s="26" t="str">
-        <x:v>sk_chocolate_sauce</x:v>
+        <x:v>sk_nama_chocolate</x:v>
       </x:c>
       <x:c r="C56" s="26" t="str">
-        <x:v>sk_chocolate_sauce_1|sk_chocolate_sauce_2</x:v>
+        <x:v>sk_nama_chocolate_1|sk_nama_chocolate_2</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -12159,10 +11873,10 @@
     <x:row r="59">
       <x:c r="A59"/>
       <x:c r="B59" s="26" t="str">
-        <x:v>sk_parfait</x:v>
+        <x:v>sk_fermented_rice_balls</x:v>
       </x:c>
       <x:c r="C59" s="26" t="str">
-        <x:v>sk_parfait_1</x:v>
+        <x:v>sk_fermented_rice_balls_1</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -12186,10 +11900,10 @@
     <x:row r="62">
       <x:c r="A62"/>
       <x:c r="B62" s="26" t="str">
-        <x:v>sk_apple_pie</x:v>
+        <x:v>sk_double_skin_milk</x:v>
       </x:c>
       <x:c r="C62" s="26" t="str">
-        <x:v>sk_apple_pie_1</x:v>
+        <x:v>sk_double_skin_milk_1</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -12234,19 +11948,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="I1" t="s">
         <x:v>9</x:v>
@@ -12258,28 +11972,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="I2" s="29" t="s">
-        <x:v>202</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J2"/>
     </x:row>
@@ -12297,13 +12011,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>23</x:v>
@@ -12315,62 +12029,62 @@
     </x:row>
     <x:row r="4">
       <x:c r="B4" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="J4" t="s">
-        <x:v>210</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>40</x:v>
       </x:c>
       <x:c r="J5" t="s">
-        <x:v>215</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34">
       <x:c r="B6" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D6" s="18" t="s">
-        <x:v>218</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="G6" s="1">
         <x:v>10</x:v>
@@ -12379,48 +12093,48 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="J6" t="s">
-        <x:v>220</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>50</x:v>
       </x:c>
       <x:c r="J7" t="s">
-        <x:v>225</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34">
       <x:c r="B8" s="28" t="s">
-        <x:v>226</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C8" s="28" t="s">
-        <x:v>227</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>228</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E8" s="28" t="s">
-        <x:v>229</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F8" s="28"/>
       <x:c r="G8" s="28" t="s">
-        <x:v>230</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H8" s="28"/>
       <x:c r="I8">
@@ -12430,16 +12144,16 @@
     </x:row>
     <x:row r="9" ht="34">
       <x:c r="B9" s="28" t="s">
-        <x:v>231</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C9" s="28" t="s">
-        <x:v>232</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D9" s="12" t="s">
-        <x:v>233</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E9" s="28" t="s">
-        <x:v>234</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F9" s="28"/>
       <x:c r="G9" s="28">
@@ -12602,22 +12316,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>235</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D1" t="s">
-        <x:v>236</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E1" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="F1" t="s">
-        <x:v>191</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G1" t="s">
-        <x:v>237</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H1" t="s">
-        <x:v>190</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -12625,25 +12339,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" t="s">
-        <x:v>238</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>239</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D2" t="s">
-        <x:v>240</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="E2" t="s">
-        <x:v>241</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F2" t="s">
-        <x:v>242</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="G2" t="s">
-        <x:v>243</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H2" t="s">
-        <x:v>244</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -12663,7 +12377,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="F3" t="s">
-        <x:v>245</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G3" t="s">
         <x:v>48</x:v>
@@ -12674,7 +12388,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="B4" t="s">
-        <x:v>246</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C4">
         <x:v>0</x:v>
@@ -12683,21 +12397,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" t="s">
-        <x:v>247</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F4" t="s">
-        <x:v>248</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="G4">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H4" t="s">
-        <x:v>249</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="B5" t="s">
-        <x:v>250</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C5">
         <x:v>1</x:v>
@@ -12706,16 +12420,16 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E5" t="s">
-        <x:v>247</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F5" t="s">
-        <x:v>251</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G5">
         <x:v>0.05</x:v>
       </x:c>
       <x:c r="H5" t="s">
-        <x:v>252</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="L5">
         <x:v>8</x:v>
@@ -12726,7 +12440,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="B6" t="s">
-        <x:v>253</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C6">
         <x:v>2</x:v>
@@ -12735,16 +12449,16 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>247</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F6" t="s">
-        <x:v>254</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="G6">
         <x:v>0.02</x:v>
       </x:c>
       <x:c r="H6" t="s">
-        <x:v>255</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12757,7 +12471,7 @@
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.799999237060547"/>
   <x:cols>
     <x:col min="1" max="1" width="13.076923370361328" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="36.38461685180664" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="255" style="1" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="12.15384578704834" style="1" customWidth="1"/>
     <x:col min="4" max="4" width="19.769229888916016" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="16.384614944458008" style="1" customWidth="1"/>
@@ -12785,46 +12499,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="N1" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="O1" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="P1" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="R1" s="26"/>
       <x:c r="S1" s="26"/>
@@ -12835,49 +12549,49 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="I2" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="J2" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="K2" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="L2" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="M2" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="N2" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="O2" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="P2" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="R2" s="26"/>
       <x:c r="S2" s="26"/>
@@ -12891,34 +12605,34 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="K3" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="L3" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="M3" s="1" t="s">
         <x:v>26</x:v>
@@ -12933,10 +12647,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="R3" s="26" t="s">
-        <x:v>289</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="S3" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="T3" s="26"/>
     </x:row>
@@ -12984,10 +12698,10 @@
       <x:c r="P4" s="18"/>
       <x:c r="Q4" s="26"/>
       <x:c r="R4" s="26" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="S4" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T4" s="26"/>
     </x:row>
@@ -13035,10 +12749,10 @@
       <x:c r="P5" s="18"/>
       <x:c r="Q5" s="26"/>
       <x:c r="R5" s="26" t="s">
-        <x:v>59</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="S5" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="T5" s="26"/>
     </x:row>
@@ -13086,10 +12800,10 @@
       <x:c r="P6" s="18"/>
       <x:c r="Q6" s="26"/>
       <x:c r="R6" s="26" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="S6" s="27" t="s">
-        <x:v>292</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="T6" s="26"/>
     </x:row>
@@ -13137,10 +12851,10 @@
       <x:c r="P7" s="18"/>
       <x:c r="Q7" s="26"/>
       <x:c r="R7" s="26" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="S7" s="27" t="s">
-        <x:v>293</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="T7" s="26"/>
     </x:row>
@@ -13188,10 +12902,10 @@
       <x:c r="P8" s="18"/>
       <x:c r="Q8" s="26"/>
       <x:c r="R8" s="26" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S8" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T8" s="26"/>
     </x:row>
@@ -13241,10 +12955,10 @@
       </x:c>
       <x:c r="Q9" s="26"/>
       <x:c r="R9" s="26" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="S9" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T9" s="26"/>
     </x:row>
@@ -13292,10 +13006,10 @@
       <x:c r="P10" s="18"/>
       <x:c r="Q10" s="26"/>
       <x:c r="R10" s="26" t="s">
-        <x:v>74</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="S10" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="T10" s="26"/>
     </x:row>
@@ -13343,10 +13057,10 @@
       <x:c r="P11" s="18"/>
       <x:c r="Q11" s="26"/>
       <x:c r="R11" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S11" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T11" s="26"/>
     </x:row>
@@ -13395,10 +13109,10 @@
       </x:c>
       <x:c r="Q12" s="26"/>
       <x:c r="R12" s="26" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="S12" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T12" s="26"/>
     </x:row>
@@ -13445,10 +13159,10 @@
       <x:c r="P13" s="18"/>
       <x:c r="Q13" s="26"/>
       <x:c r="R13" s="26" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S13" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T13" s="26"/>
     </x:row>
@@ -13497,10 +13211,10 @@
       </x:c>
       <x:c r="Q14" s="26"/>
       <x:c r="R14" s="26" t="s">
-        <x:v>82</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="S14" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T14" s="26"/>
     </x:row>
@@ -13550,17 +13264,17 @@
       </x:c>
       <x:c r="Q15" s="26"/>
       <x:c r="R15" s="26" t="s">
-        <x:v>85</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="S15" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T15" s="26"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="26"/>
       <x:c r="B16" s="1" t="str">
-        <x:v>sk_codename_general_01_1</x:v>
+        <x:v>sk_caramel_pudding_1</x:v>
       </x:c>
       <x:c r="C16" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -13603,10 +13317,10 @@
       <x:c r="P16" s="26"/>
       <x:c r="Q16" s="26"/>
       <x:c r="R16" s="26" t="s">
-        <x:v>89</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S16" s="27" t="s">
-        <x:v>293</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="T16" s="26"/>
     </x:row>
@@ -13653,10 +13367,10 @@
       <x:c r="P17" s="18"/>
       <x:c r="Q17" s="26"/>
       <x:c r="R17" s="26" t="s">
-        <x:v>89</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="S17" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T17" s="26"/>
     </x:row>
@@ -13705,10 +13419,10 @@
       </x:c>
       <x:c r="Q18" s="26"/>
       <x:c r="R18" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S18" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T18" s="26"/>
     </x:row>
@@ -13756,10 +13470,10 @@
       <x:c r="P19" s="18"/>
       <x:c r="Q19" s="26"/>
       <x:c r="R19" s="26" t="s">
-        <x:v>93</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="S19" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T19" s="26"/>
     </x:row>
@@ -13808,10 +13522,10 @@
       </x:c>
       <x:c r="Q20" s="26"/>
       <x:c r="R20" s="26" t="s">
-        <x:v>96</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="S20" s="27" t="s">
-        <x:v>292</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="T20" s="26"/>
     </x:row>
@@ -13861,10 +13575,10 @@
       <x:c r="P21" s="26"/>
       <x:c r="Q21" s="26"/>
       <x:c r="R21" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S21" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T21" s="26"/>
     </x:row>
@@ -13911,10 +13625,10 @@
       <x:c r="P22" s="1"/>
       <x:c r="Q22" s="26"/>
       <x:c r="R22" s="26" t="s">
-        <x:v>100</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="S22" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T22" s="26"/>
     </x:row>
@@ -13963,17 +13677,17 @@
       </x:c>
       <x:c r="Q23" s="26"/>
       <x:c r="R23" s="26" t="s">
-        <x:v>103</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="S23" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T23" s="26"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="26"/>
       <x:c r="B24" s="1" t="str">
-        <x:v>sk_cream_1</x:v>
+        <x:v>sk_cream_puff_1</x:v>
       </x:c>
       <x:c r="C24" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14014,17 +13728,17 @@
       <x:c r="P24" s="18"/>
       <x:c r="Q24" s="26"/>
       <x:c r="R24" s="26" t="s">
-        <x:v>106</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="S24" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T24" s="26"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="26"/>
       <x:c r="B25" s="1" t="str">
-        <x:v>sk_codename_general_02_1</x:v>
+        <x:v>sk_ice_cream_1</x:v>
       </x:c>
       <x:c r="C25" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14065,10 +13779,10 @@
       <x:c r="P25" s="18"/>
       <x:c r="Q25" s="26"/>
       <x:c r="R25" s="26" t="s">
-        <x:v>109</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="S25" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T25" s="26"/>
     </x:row>
@@ -14116,17 +13830,17 @@
       <x:c r="P26" s="26"/>
       <x:c r="Q26" s="26"/>
       <x:c r="R26" s="26" t="s">
-        <x:v>113</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S26" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T26" s="26"/>
     </x:row>
     <x:row r="27" ht="17">
       <x:c r="A27" s="26"/>
       <x:c r="B27" s="1" t="str">
-        <x:v>sk_baguette_1</x:v>
+        <x:v>sk_osmanthus_cake_1</x:v>
       </x:c>
       <x:c r="C27" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14166,10 +13880,10 @@
       <x:c r="P27" s="18"/>
       <x:c r="Q27" s="26"/>
       <x:c r="R27" s="26" t="s">
-        <x:v>113</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="S27" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T27" s="26"/>
     </x:row>
@@ -14216,10 +13930,10 @@
       <x:c r="P28" s="26"/>
       <x:c r="Q28" s="26"/>
       <x:c r="R28" s="26" t="s">
-        <x:v>117</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="S28" s="27" t="s">
-        <x:v>300</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="T28" s="26"/>
     </x:row>
@@ -14268,17 +13982,17 @@
       </x:c>
       <x:c r="Q29" s="26"/>
       <x:c r="R29" s="26" t="s">
-        <x:v>117</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="S29" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T29" s="26"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="26"/>
       <x:c r="B30" s="1" t="str">
-        <x:v>sk_cake_slice_1</x:v>
+        <x:v>sk_napoleon_cake_1</x:v>
       </x:c>
       <x:c r="C30" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14320,17 +14034,17 @@
       <x:c r="P30" s="26"/>
       <x:c r="Q30" s="26"/>
       <x:c r="R30" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="S30" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T30" s="26"/>
     </x:row>
     <x:row r="31" ht="17">
       <x:c r="A31" s="26"/>
       <x:c r="B31" s="1" t="str">
-        <x:v>sk_cake_slice_2</x:v>
+        <x:v>sk_napoleon_cake_2</x:v>
       </x:c>
       <x:c r="C31" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14370,17 +14084,17 @@
       <x:c r="P31" s="18"/>
       <x:c r="Q31" s="26"/>
       <x:c r="R31" s="26" t="s">
-        <x:v>121</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="S31" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T31" s="26"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="26"/>
       <x:c r="B32" s="1" t="str">
-        <x:v>sk_long_cake_1</x:v>
+        <x:v>sk_honey_cake_1</x:v>
       </x:c>
       <x:c r="C32" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14420,17 +14134,17 @@
       <x:c r="P32" s="18"/>
       <x:c r="Q32" s="26"/>
       <x:c r="R32" s="26" t="s">
-        <x:v>124</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="S32" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T32" s="26"/>
     </x:row>
     <x:row r="33" s="25" customFormat="1">
       <x:c r="A33" s="8"/>
       <x:c r="B33" s="8" t="str">
-        <x:v>sk_long_cake_2</x:v>
+        <x:v>sk_honey_cake_2</x:v>
       </x:c>
       <x:c r="C33" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14472,17 +14186,17 @@
       </x:c>
       <x:c r="Q33" s="26"/>
       <x:c r="R33" s="26" t="s">
-        <x:v>127</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="S33" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T33" s="26"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="26"/>
       <x:c r="B34" s="1" t="str">
-        <x:v>sk_codename_cake_01_1</x:v>
+        <x:v>sk_tree_ring_cake_1</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14525,17 +14239,17 @@
       </x:c>
       <x:c r="Q34" s="26"/>
       <x:c r="R34" s="26" t="s">
-        <x:v>131</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="S34" s="27" t="s">
-        <x:v>294</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="T34" s="26"/>
     </x:row>
     <x:row r="35" ht="17">
       <x:c r="A35" s="26"/>
       <x:c r="B35" s="1" t="str">
-        <x:v>sk_codename_transfer_01_1</x:v>
+        <x:v>sk_nougat_1</x:v>
       </x:c>
       <x:c r="C35" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14575,17 +14289,17 @@
       <x:c r="P35" s="18"/>
       <x:c r="Q35" s="26"/>
       <x:c r="R35" s="26" t="s">
-        <x:v>131</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="S35" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T35" s="26"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="26"/>
       <x:c r="B36" s="1" t="str">
-        <x:v>sk_codename_transfer_01_2</x:v>
+        <x:v>sk_nougat_2</x:v>
       </x:c>
       <x:c r="C36" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14627,17 +14341,17 @@
       </x:c>
       <x:c r="Q36" s="26"/>
       <x:c r="R36" s="26" t="s">
-        <x:v>135</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="S36" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T36" s="26"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="26"/>
       <x:c r="B37" s="1" t="str">
-        <x:v>sk_codename_serving_01_1</x:v>
+        <x:v>sk_hawthorn_cake_1</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14682,17 +14396,17 @@
       <x:c r="P37" s="26"/>
       <x:c r="Q37" s="26"/>
       <x:c r="R37" s="26" t="s">
-        <x:v>135</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="S37" s="27" t="s">
-        <x:v>300</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="T37" s="26"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="26"/>
       <x:c r="B38" s="1" t="str">
-        <x:v>sk_codename_general_03_1</x:v>
+        <x:v>sk_souffle_1</x:v>
       </x:c>
       <x:c r="C38" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14733,17 +14447,17 @@
       <x:c r="P38" s="26"/>
       <x:c r="Q38" s="26"/>
       <x:c r="R38" s="26" t="s">
-        <x:v>138</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="S38" s="27" t="s">
-        <x:v>291</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="T38" s="26"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="26"/>
       <x:c r="B39" s="1" t="str">
-        <x:v>sk_codename_general_04_1</x:v>
+        <x:v>sk_fruit_tart_1</x:v>
       </x:c>
       <x:c r="C39" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14786,17 +14500,17 @@
       <x:c r="P39" s="1"/>
       <x:c r="Q39" s="26"/>
       <x:c r="R39" s="26" t="s">
-        <x:v>141</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="S39" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T39" s="26"/>
     </x:row>
     <x:row r="40" ht="17">
       <x:c r="A40" s="26"/>
       <x:c r="B40" s="1" t="str">
-        <x:v>sk_codename_general_05_1</x:v>
+        <x:v>sk_strawberry_sundae_1</x:v>
       </x:c>
       <x:c r="C40" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14839,17 +14553,17 @@
       <x:c r="P40" s="18"/>
       <x:c r="Q40" s="26"/>
       <x:c r="R40" s="26" t="s">
-        <x:v>144</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="S40" s="27" t="s">
-        <x:v>298</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="T40" s="26"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="26"/>
       <x:c r="B41" s="1" t="str">
-        <x:v>sk_codename_general_06_1</x:v>
+        <x:v>sk_rock_sugar_pear_1</x:v>
       </x:c>
       <x:c r="C41" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14889,17 +14603,17 @@
       <x:c r="P41" s="18"/>
       <x:c r="Q41" s="26"/>
       <x:c r="R41" s="26" t="s">
-        <x:v>147</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="S41" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T41" s="26"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="26"/>
       <x:c r="B42" s="1" t="str">
-        <x:v>sk_codename_general_06_2</x:v>
+        <x:v>sk_rock_sugar_pear_2</x:v>
       </x:c>
       <x:c r="C42" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14939,17 +14653,17 @@
       <x:c r="P42" s="26"/>
       <x:c r="Q42" s="26"/>
       <x:c r="R42" s="26" t="s">
-        <x:v>150</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="S42" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T42" s="26"/>
     </x:row>
     <x:row r="43" ht="17">
       <x:c r="A43" s="26"/>
       <x:c r="B43" s="1" t="str">
-        <x:v>sk_codename_transfer_02_1</x:v>
+        <x:v>sk_popping_candy_1</x:v>
       </x:c>
       <x:c r="C43" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -14992,17 +14706,17 @@
       <x:c r="P43" s="18"/>
       <x:c r="Q43" s="26"/>
       <x:c r="R43" s="26" t="s">
-        <x:v>154</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S43" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T43" s="26"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="26"/>
       <x:c r="B44" s="1" t="str">
-        <x:v>sk_codename_cake_02_1</x:v>
+        <x:v>sk_mille_crepe_cake_1</x:v>
       </x:c>
       <x:c r="C44" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15047,17 +14761,17 @@
       </x:c>
       <x:c r="Q44" s="26"/>
       <x:c r="R44" s="26" t="s">
-        <x:v>154</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="S44" s="27" t="s">
-        <x:v>297</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="T44" s="26"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="26"/>
       <x:c r="B45" s="1" t="str">
-        <x:v>sk_codename_serving_02_1</x:v>
+        <x:v>sk_soybean_glutinous_roll_1</x:v>
       </x:c>
       <x:c r="C45" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15100,17 +14814,17 @@
       <x:c r="P45" s="18"/>
       <x:c r="Q45" s="26"/>
       <x:c r="R45" s="26" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S45" s="27" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="T45" s="26"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="26"/>
       <x:c r="B46" s="1" t="str">
-        <x:v>sk_eclair_1</x:v>
+        <x:v>sk_sachima_1</x:v>
       </x:c>
       <x:c r="C46" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15155,10 +14869,10 @@
       <x:c r="P46" s="1"/>
       <x:c r="Q46" s="26"/>
       <x:c r="R46" s="26" t="s">
-        <x:v>158</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="S46" s="27" t="s">
-        <x:v>296</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="T46" s="26"/>
     </x:row>
@@ -15208,17 +14922,17 @@
       <x:c r="P47" s="26"/>
       <x:c r="Q47" s="26"/>
       <x:c r="R47" s="26" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S47" s="27" t="s">
-        <x:v>299</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="T47" s="26"/>
     </x:row>
     <x:row r="48" ht="17">
       <x:c r="A48" s="26"/>
       <x:c r="B48" s="1" t="str">
-        <x:v>sk_chocolate_strip_1</x:v>
+        <x:v>sk_chocolate_wafer_1</x:v>
       </x:c>
       <x:c r="C48" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15258,17 +14972,17 @@
       <x:c r="P48" s="18"/>
       <x:c r="Q48" s="26"/>
       <x:c r="R48" s="26" t="s">
-        <x:v>162</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="S48" s="27" t="s">
-        <x:v>295</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T48" s="26"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="26"/>
       <x:c r="B49" s="1" t="str">
-        <x:v>sk_chocolate_strip_2</x:v>
+        <x:v>sk_chocolate_wafer_2</x:v>
       </x:c>
       <x:c r="C49" s="1" t="str">
         <x:v>OnSettle</x:v>
@@ -15310,10 +15024,10 @@
       </x:c>
       <x:c r="Q49" s="26"/>
       <x:c r="R49" s="26" t="s">
-        <x:v>166</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="S49" s="27" t="s">
-        <x:v>290</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="T49" s="26"/>
     </x:row>
@@ -15362,10 +15076,10 @@
       </x:c>
       <x:c r="Q50" s="26"/>
       <x:c r="R50" s="26" t="s">
-        <x:v>166</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c